--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="77">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -464,6 +464,16 @@
       <color rgb="001B3A6B"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -698,7 +708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="269">
+  <borders count="291">
     <border>
       <left/>
       <right/>
@@ -3590,11 +3600,227 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="340">
+  <cellXfs count="427">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4377,6 +4603,246 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="273" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="273" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="274" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="277" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="271" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="280" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="284" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="284" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="285" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="287" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="288" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="282" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="283" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="289" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="290" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4451,39 +4917,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4854,2060 +5287,2314 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="inlineStr"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="268" t="n"/>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="269" t="inlineStr">
+      <c r="A1" s="340" t="inlineStr"/>
+      <c r="B1" s="421" t="n"/>
+      <c r="C1" s="421" t="n"/>
+      <c r="D1" s="421" t="n"/>
+      <c r="E1" s="421" t="n"/>
+      <c r="F1" s="421" t="n"/>
+      <c r="G1" s="421" t="n"/>
+      <c r="H1" s="421" t="n"/>
+      <c r="I1" s="421" t="n"/>
+      <c r="J1" s="421" t="n"/>
+      <c r="K1" s="421" t="n"/>
+      <c r="L1" s="342" t="inlineStr">
         <is>
           <t>AQL Inspection Record</t>
         </is>
       </c>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="268" t="n"/>
-      <c r="AF1" s="268" t="n"/>
-      <c r="AG1" s="268" t="n"/>
-      <c r="AH1" s="268" t="n"/>
-      <c r="AI1" s="268" t="n"/>
-      <c r="AJ1" s="268" t="n"/>
-      <c r="AK1" s="268" t="n"/>
-      <c r="AL1" s="268" t="n"/>
-      <c r="AM1" s="268" t="n"/>
-      <c r="AN1" s="268" t="n"/>
-      <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
-      <c r="AQ1" s="270" t="inlineStr">
+      <c r="M1" s="421" t="n"/>
+      <c r="N1" s="421" t="n"/>
+      <c r="O1" s="421" t="n"/>
+      <c r="P1" s="421" t="n"/>
+      <c r="Q1" s="421" t="n"/>
+      <c r="R1" s="421" t="n"/>
+      <c r="S1" s="421" t="n"/>
+      <c r="T1" s="421" t="n"/>
+      <c r="U1" s="421" t="n"/>
+      <c r="V1" s="421" t="n"/>
+      <c r="W1" s="421" t="n"/>
+      <c r="X1" s="421" t="n"/>
+      <c r="Y1" s="421" t="n"/>
+      <c r="Z1" s="421" t="n"/>
+      <c r="AA1" s="421" t="n"/>
+      <c r="AB1" s="421" t="n"/>
+      <c r="AC1" s="421" t="n"/>
+      <c r="AD1" s="421" t="n"/>
+      <c r="AE1" s="421" t="n"/>
+      <c r="AF1" s="421" t="n"/>
+      <c r="AG1" s="421" t="n"/>
+      <c r="AH1" s="421" t="n"/>
+      <c r="AI1" s="421" t="n"/>
+      <c r="AJ1" s="421" t="n"/>
+      <c r="AK1" s="421" t="n"/>
+      <c r="AL1" s="421" t="n"/>
+      <c r="AM1" s="421" t="n"/>
+      <c r="AN1" s="421" t="n"/>
+      <c r="AO1" s="421" t="n"/>
+      <c r="AP1" s="421" t="n"/>
+      <c r="AQ1" s="343" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="271" t="n"/>
-      <c r="AS1" s="271" t="n"/>
-      <c r="AT1" s="271" t="n"/>
-      <c r="AU1" s="271" t="n"/>
-      <c r="AV1" s="272" t="n"/>
-      <c r="AW1" s="273" t="inlineStr">
+      <c r="AR1" s="422" t="n"/>
+      <c r="AS1" s="422" t="n"/>
+      <c r="AT1" s="422" t="n"/>
+      <c r="AU1" s="422" t="n"/>
+      <c r="AV1" s="423" t="n"/>
+      <c r="AW1" s="346" t="inlineStr">
         <is>
           <t>FRM-621</t>
         </is>
       </c>
-      <c r="AX1" s="271" t="n"/>
-      <c r="AY1" s="271" t="n"/>
-      <c r="AZ1" s="271" t="n"/>
-      <c r="BA1" s="271" t="n"/>
-      <c r="BB1" s="271" t="n"/>
-      <c r="BC1" s="271" t="n"/>
-      <c r="BD1" s="274" t="n"/>
+      <c r="AX1" s="422" t="n"/>
+      <c r="AY1" s="422" t="n"/>
+      <c r="AZ1" s="422" t="n"/>
+      <c r="BA1" s="422" t="n"/>
+      <c r="BB1" s="422" t="n"/>
+      <c r="BC1" s="422" t="n"/>
+      <c r="BD1" s="423" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="270" t="inlineStr">
+      <c r="A2" s="424" t="n"/>
+      <c r="L2" s="424" t="n"/>
+      <c r="AQ2" s="343" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="271" t="n"/>
-      <c r="AS2" s="271" t="n"/>
-      <c r="AT2" s="271" t="n"/>
-      <c r="AU2" s="271" t="n"/>
-      <c r="AV2" s="272" t="n"/>
-      <c r="AW2" s="273" t="inlineStr">
+      <c r="AR2" s="422" t="n"/>
+      <c r="AS2" s="422" t="n"/>
+      <c r="AT2" s="422" t="n"/>
+      <c r="AU2" s="422" t="n"/>
+      <c r="AV2" s="423" t="n"/>
+      <c r="AW2" s="346" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="271" t="n"/>
-      <c r="AY2" s="271" t="n"/>
-      <c r="AZ2" s="271" t="n"/>
-      <c r="BA2" s="271" t="n"/>
-      <c r="BB2" s="271" t="n"/>
-      <c r="BC2" s="271" t="n"/>
-      <c r="BD2" s="274" t="n"/>
+      <c r="AX2" s="422" t="n"/>
+      <c r="AY2" s="422" t="n"/>
+      <c r="AZ2" s="422" t="n"/>
+      <c r="BA2" s="422" t="n"/>
+      <c r="BB2" s="422" t="n"/>
+      <c r="BC2" s="422" t="n"/>
+      <c r="BD2" s="423" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="L3" s="279" t="n"/>
-      <c r="M3" s="276" t="n"/>
-      <c r="N3" s="276" t="n"/>
-      <c r="O3" s="276" t="n"/>
-      <c r="P3" s="276" t="n"/>
-      <c r="Q3" s="276" t="n"/>
-      <c r="R3" s="276" t="n"/>
-      <c r="S3" s="276" t="n"/>
-      <c r="T3" s="276" t="n"/>
-      <c r="U3" s="276" t="n"/>
-      <c r="V3" s="276" t="n"/>
-      <c r="W3" s="276" t="n"/>
-      <c r="X3" s="276" t="n"/>
-      <c r="Y3" s="276" t="n"/>
-      <c r="Z3" s="276" t="n"/>
-      <c r="AA3" s="276" t="n"/>
-      <c r="AB3" s="276" t="n"/>
-      <c r="AC3" s="276" t="n"/>
-      <c r="AD3" s="276" t="n"/>
-      <c r="AE3" s="276" t="n"/>
-      <c r="AF3" s="276" t="n"/>
-      <c r="AG3" s="276" t="n"/>
-      <c r="AH3" s="276" t="n"/>
-      <c r="AI3" s="276" t="n"/>
-      <c r="AJ3" s="276" t="n"/>
-      <c r="AK3" s="276" t="n"/>
-      <c r="AL3" s="276" t="n"/>
-      <c r="AM3" s="276" t="n"/>
-      <c r="AN3" s="276" t="n"/>
-      <c r="AO3" s="276" t="n"/>
-      <c r="AP3" s="276" t="n"/>
-      <c r="AQ3" s="270" t="inlineStr">
+      <c r="A3" s="424" t="n"/>
+      <c r="L3" s="425" t="n"/>
+      <c r="M3" s="426" t="n"/>
+      <c r="N3" s="426" t="n"/>
+      <c r="O3" s="426" t="n"/>
+      <c r="P3" s="426" t="n"/>
+      <c r="Q3" s="426" t="n"/>
+      <c r="R3" s="426" t="n"/>
+      <c r="S3" s="426" t="n"/>
+      <c r="T3" s="426" t="n"/>
+      <c r="U3" s="426" t="n"/>
+      <c r="V3" s="426" t="n"/>
+      <c r="W3" s="426" t="n"/>
+      <c r="X3" s="426" t="n"/>
+      <c r="Y3" s="426" t="n"/>
+      <c r="Z3" s="426" t="n"/>
+      <c r="AA3" s="426" t="n"/>
+      <c r="AB3" s="426" t="n"/>
+      <c r="AC3" s="426" t="n"/>
+      <c r="AD3" s="426" t="n"/>
+      <c r="AE3" s="426" t="n"/>
+      <c r="AF3" s="426" t="n"/>
+      <c r="AG3" s="426" t="n"/>
+      <c r="AH3" s="426" t="n"/>
+      <c r="AI3" s="426" t="n"/>
+      <c r="AJ3" s="426" t="n"/>
+      <c r="AK3" s="426" t="n"/>
+      <c r="AL3" s="426" t="n"/>
+      <c r="AM3" s="426" t="n"/>
+      <c r="AN3" s="426" t="n"/>
+      <c r="AO3" s="426" t="n"/>
+      <c r="AP3" s="426" t="n"/>
+      <c r="AQ3" s="343" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="271" t="n"/>
-      <c r="AS3" s="271" t="n"/>
-      <c r="AT3" s="271" t="n"/>
-      <c r="AU3" s="271" t="n"/>
-      <c r="AV3" s="272" t="n"/>
-      <c r="AW3" s="273" t="inlineStr">
+      <c r="AR3" s="422" t="n"/>
+      <c r="AS3" s="422" t="n"/>
+      <c r="AT3" s="422" t="n"/>
+      <c r="AU3" s="422" t="n"/>
+      <c r="AV3" s="423" t="n"/>
+      <c r="AW3" s="346" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="271" t="n"/>
-      <c r="AY3" s="271" t="n"/>
-      <c r="AZ3" s="271" t="n"/>
-      <c r="BA3" s="271" t="n"/>
-      <c r="BB3" s="271" t="n"/>
-      <c r="BC3" s="271" t="n"/>
-      <c r="BD3" s="274" t="n"/>
+      <c r="AX3" s="422" t="n"/>
+      <c r="AY3" s="422" t="n"/>
+      <c r="AZ3" s="422" t="n"/>
+      <c r="BA3" s="422" t="n"/>
+      <c r="BB3" s="422" t="n"/>
+      <c r="BC3" s="422" t="n"/>
+      <c r="BD3" s="423" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="A4" s="424" t="n"/>
+      <c r="L4" s="351" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="270" t="inlineStr">
+      <c r="AQ4" s="343" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="271" t="n"/>
-      <c r="AS4" s="271" t="n"/>
-      <c r="AT4" s="271" t="n"/>
-      <c r="AU4" s="271" t="n"/>
-      <c r="AV4" s="272" t="n"/>
-      <c r="AW4" s="273" t="inlineStr">
+      <c r="AR4" s="422" t="n"/>
+      <c r="AS4" s="422" t="n"/>
+      <c r="AT4" s="422" t="n"/>
+      <c r="AU4" s="422" t="n"/>
+      <c r="AV4" s="423" t="n"/>
+      <c r="AW4" s="346" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="271" t="n"/>
-      <c r="AY4" s="271" t="n"/>
-      <c r="AZ4" s="271" t="n"/>
-      <c r="BA4" s="271" t="n"/>
-      <c r="BB4" s="271" t="n"/>
-      <c r="BC4" s="271" t="n"/>
-      <c r="BD4" s="274" t="n"/>
+      <c r="AX4" s="422" t="n"/>
+      <c r="AY4" s="422" t="n"/>
+      <c r="AZ4" s="422" t="n"/>
+      <c r="BA4" s="422" t="n"/>
+      <c r="BB4" s="422" t="n"/>
+      <c r="BC4" s="422" t="n"/>
+      <c r="BD4" s="423" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="281" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="425" t="n"/>
+      <c r="B5" s="426" t="n"/>
+      <c r="C5" s="426" t="n"/>
+      <c r="D5" s="426" t="n"/>
+      <c r="E5" s="426" t="n"/>
+      <c r="F5" s="426" t="n"/>
+      <c r="G5" s="426" t="n"/>
+      <c r="H5" s="426" t="n"/>
+      <c r="I5" s="426" t="n"/>
+      <c r="J5" s="426" t="n"/>
+      <c r="K5" s="426" t="n"/>
+      <c r="L5" s="352" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="270" t="inlineStr">
+      <c r="M5" s="426" t="n"/>
+      <c r="N5" s="426" t="n"/>
+      <c r="O5" s="426" t="n"/>
+      <c r="P5" s="426" t="n"/>
+      <c r="Q5" s="426" t="n"/>
+      <c r="R5" s="426" t="n"/>
+      <c r="S5" s="426" t="n"/>
+      <c r="T5" s="426" t="n"/>
+      <c r="U5" s="426" t="n"/>
+      <c r="V5" s="426" t="n"/>
+      <c r="W5" s="426" t="n"/>
+      <c r="X5" s="426" t="n"/>
+      <c r="Y5" s="426" t="n"/>
+      <c r="Z5" s="426" t="n"/>
+      <c r="AA5" s="426" t="n"/>
+      <c r="AB5" s="426" t="n"/>
+      <c r="AC5" s="426" t="n"/>
+      <c r="AD5" s="426" t="n"/>
+      <c r="AE5" s="426" t="n"/>
+      <c r="AF5" s="426" t="n"/>
+      <c r="AG5" s="426" t="n"/>
+      <c r="AH5" s="426" t="n"/>
+      <c r="AI5" s="426" t="n"/>
+      <c r="AJ5" s="426" t="n"/>
+      <c r="AK5" s="426" t="n"/>
+      <c r="AL5" s="426" t="n"/>
+      <c r="AM5" s="426" t="n"/>
+      <c r="AN5" s="426" t="n"/>
+      <c r="AO5" s="426" t="n"/>
+      <c r="AP5" s="426" t="n"/>
+      <c r="AQ5" s="343" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="271" t="n"/>
-      <c r="AS5" s="271" t="n"/>
-      <c r="AT5" s="271" t="n"/>
-      <c r="AU5" s="271" t="n"/>
-      <c r="AV5" s="272" t="n"/>
-      <c r="AW5" s="273" t="inlineStr">
+      <c r="AR5" s="422" t="n"/>
+      <c r="AS5" s="422" t="n"/>
+      <c r="AT5" s="422" t="n"/>
+      <c r="AU5" s="422" t="n"/>
+      <c r="AV5" s="423" t="n"/>
+      <c r="AW5" s="346" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="271" t="n"/>
-      <c r="AY5" s="271" t="n"/>
-      <c r="AZ5" s="271" t="n"/>
-      <c r="BA5" s="271" t="n"/>
-      <c r="BB5" s="271" t="n"/>
-      <c r="BC5" s="271" t="n"/>
-      <c r="BD5" s="274" t="n"/>
+      <c r="AX5" s="422" t="n"/>
+      <c r="AY5" s="422" t="n"/>
+      <c r="AZ5" s="422" t="n"/>
+      <c r="BA5" s="422" t="n"/>
+      <c r="BB5" s="422" t="n"/>
+      <c r="BC5" s="422" t="n"/>
+      <c r="BD5" s="423" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="inlineStr"/>
+      <c r="A6" s="353" t="inlineStr"/>
+      <c r="B6" s="420" t="n"/>
+      <c r="C6" s="420" t="n"/>
+      <c r="D6" s="420" t="n"/>
+      <c r="E6" s="420" t="n"/>
+      <c r="F6" s="420" t="n"/>
+      <c r="G6" s="420" t="n"/>
+      <c r="H6" s="420" t="n"/>
+      <c r="I6" s="420" t="n"/>
+      <c r="J6" s="420" t="n"/>
+      <c r="K6" s="420" t="n"/>
+      <c r="L6" s="420" t="n"/>
+      <c r="M6" s="420" t="n"/>
+      <c r="N6" s="420" t="n"/>
+      <c r="O6" s="420" t="n"/>
+      <c r="P6" s="420" t="n"/>
+      <c r="Q6" s="420" t="n"/>
+      <c r="R6" s="420" t="n"/>
+      <c r="S6" s="420" t="n"/>
+      <c r="T6" s="420" t="n"/>
+      <c r="U6" s="420" t="n"/>
+      <c r="V6" s="420" t="n"/>
+      <c r="W6" s="420" t="n"/>
+      <c r="X6" s="420" t="n"/>
+      <c r="Y6" s="420" t="n"/>
+      <c r="Z6" s="420" t="n"/>
+      <c r="AA6" s="420" t="n"/>
+      <c r="AB6" s="420" t="n"/>
+      <c r="AC6" s="420" t="n"/>
+      <c r="AD6" s="420" t="n"/>
+      <c r="AE6" s="420" t="n"/>
+      <c r="AF6" s="420" t="n"/>
+      <c r="AG6" s="420" t="n"/>
+      <c r="AH6" s="420" t="n"/>
+      <c r="AI6" s="420" t="n"/>
+      <c r="AJ6" s="420" t="n"/>
+      <c r="AK6" s="420" t="n"/>
+      <c r="AL6" s="420" t="n"/>
+      <c r="AM6" s="420" t="n"/>
+      <c r="AN6" s="420" t="n"/>
+      <c r="AO6" s="420" t="n"/>
+      <c r="AP6" s="420" t="n"/>
+      <c r="AQ6" s="420" t="n"/>
+      <c r="AR6" s="420" t="n"/>
+      <c r="AS6" s="420" t="n"/>
+      <c r="AT6" s="420" t="n"/>
+      <c r="AU6" s="420" t="n"/>
+      <c r="AV6" s="420" t="n"/>
+      <c r="AW6" s="420" t="n"/>
+      <c r="AX6" s="420" t="n"/>
+      <c r="AY6" s="420" t="n"/>
+      <c r="AZ6" s="420" t="n"/>
+      <c r="BA6" s="420" t="n"/>
+      <c r="BB6" s="420" t="n"/>
+      <c r="BC6" s="420" t="n"/>
+      <c r="BD6" s="420" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+      <c r="B7" s="422" t="n"/>
+      <c r="C7" s="422" t="n"/>
+      <c r="D7" s="422" t="n"/>
+      <c r="E7" s="422" t="n"/>
+      <c r="F7" s="422" t="n"/>
+      <c r="G7" s="422" t="n"/>
+      <c r="H7" s="422" t="n"/>
+      <c r="I7" s="422" t="n"/>
+      <c r="J7" s="422" t="n"/>
+      <c r="K7" s="422" t="n"/>
+      <c r="L7" s="422" t="n"/>
+      <c r="M7" s="422" t="n"/>
+      <c r="N7" s="422" t="n"/>
+      <c r="O7" s="422" t="n"/>
+      <c r="P7" s="422" t="n"/>
+      <c r="Q7" s="422" t="n"/>
+      <c r="R7" s="422" t="n"/>
+      <c r="S7" s="422" t="n"/>
+      <c r="T7" s="422" t="n"/>
+      <c r="U7" s="422" t="n"/>
+      <c r="V7" s="422" t="n"/>
+      <c r="W7" s="422" t="n"/>
+      <c r="X7" s="422" t="n"/>
+      <c r="Y7" s="422" t="n"/>
+      <c r="Z7" s="422" t="n"/>
+      <c r="AA7" s="422" t="n"/>
+      <c r="AB7" s="422" t="n"/>
+      <c r="AC7" s="422" t="n"/>
+      <c r="AD7" s="422" t="n"/>
+      <c r="AE7" s="422" t="n"/>
+      <c r="AF7" s="422" t="n"/>
+      <c r="AG7" s="422" t="n"/>
+      <c r="AH7" s="422" t="n"/>
+      <c r="AI7" s="422" t="n"/>
+      <c r="AJ7" s="422" t="n"/>
+      <c r="AK7" s="422" t="n"/>
+      <c r="AL7" s="422" t="n"/>
+      <c r="AM7" s="422" t="n"/>
+      <c r="AN7" s="422" t="n"/>
+      <c r="AO7" s="422" t="n"/>
+      <c r="AP7" s="422" t="n"/>
+      <c r="AQ7" s="422" t="n"/>
+      <c r="AR7" s="422" t="n"/>
+      <c r="AS7" s="422" t="n"/>
+      <c r="AT7" s="422" t="n"/>
+      <c r="AU7" s="422" t="n"/>
+      <c r="AV7" s="422" t="n"/>
+      <c r="AW7" s="422" t="n"/>
+      <c r="AX7" s="422" t="n"/>
+      <c r="AY7" s="422" t="n"/>
+      <c r="AZ7" s="422" t="n"/>
+      <c r="BA7" s="422" t="n"/>
+      <c r="BB7" s="422" t="n"/>
+      <c r="BC7" s="422" t="n"/>
+      <c r="BD7" s="423" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="355" t="inlineStr">
         <is>
           <t>Customer / PO Line</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="271" t="n"/>
-      <c r="H8" s="271" t="n"/>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="272" t="n"/>
-      <c r="K8" s="288" t="n"/>
-      <c r="L8" s="325" t="n"/>
-      <c r="M8" s="325" t="n"/>
-      <c r="N8" s="325" t="n"/>
-      <c r="O8" s="325" t="n"/>
-      <c r="P8" s="325" t="n"/>
-      <c r="Q8" s="325" t="n"/>
-      <c r="R8" s="325" t="n"/>
-      <c r="S8" s="325" t="n"/>
-      <c r="T8" s="325" t="n"/>
-      <c r="U8" s="325" t="n"/>
-      <c r="V8" s="325" t="n"/>
-      <c r="W8" s="325" t="n"/>
-      <c r="X8" s="325" t="n"/>
-      <c r="Y8" s="325" t="n"/>
-      <c r="Z8" s="325" t="n"/>
-      <c r="AA8" s="325" t="n"/>
-      <c r="AB8" s="326" t="n"/>
-      <c r="AC8" s="289" t="inlineStr">
+      <c r="B8" s="405" t="n"/>
+      <c r="C8" s="405" t="n"/>
+      <c r="D8" s="405" t="n"/>
+      <c r="E8" s="405" t="n"/>
+      <c r="F8" s="405" t="n"/>
+      <c r="G8" s="405" t="n"/>
+      <c r="H8" s="405" t="n"/>
+      <c r="I8" s="405" t="n"/>
+      <c r="J8" s="406" t="n"/>
+      <c r="K8" s="358" t="n"/>
+      <c r="L8" s="407" t="n"/>
+      <c r="M8" s="407" t="n"/>
+      <c r="N8" s="407" t="n"/>
+      <c r="O8" s="407" t="n"/>
+      <c r="P8" s="407" t="n"/>
+      <c r="Q8" s="407" t="n"/>
+      <c r="R8" s="407" t="n"/>
+      <c r="S8" s="407" t="n"/>
+      <c r="T8" s="407" t="n"/>
+      <c r="U8" s="407" t="n"/>
+      <c r="V8" s="407" t="n"/>
+      <c r="W8" s="407" t="n"/>
+      <c r="X8" s="407" t="n"/>
+      <c r="Y8" s="407" t="n"/>
+      <c r="Z8" s="407" t="n"/>
+      <c r="AA8" s="407" t="n"/>
+      <c r="AB8" s="408" t="n"/>
+      <c r="AC8" s="361" t="inlineStr">
         <is>
           <t>Inspection Record ID</t>
         </is>
       </c>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="272" t="n"/>
-      <c r="AM8" s="290" t="n"/>
-      <c r="AN8" s="325" t="n"/>
-      <c r="AO8" s="325" t="n"/>
-      <c r="AP8" s="325" t="n"/>
-      <c r="AQ8" s="325" t="n"/>
-      <c r="AR8" s="325" t="n"/>
-      <c r="AS8" s="325" t="n"/>
-      <c r="AT8" s="325" t="n"/>
-      <c r="AU8" s="325" t="n"/>
-      <c r="AV8" s="325" t="n"/>
-      <c r="AW8" s="325" t="n"/>
-      <c r="AX8" s="325" t="n"/>
-      <c r="AY8" s="325" t="n"/>
-      <c r="AZ8" s="325" t="n"/>
-      <c r="BA8" s="325" t="n"/>
-      <c r="BB8" s="325" t="n"/>
-      <c r="BC8" s="325" t="n"/>
-      <c r="BD8" s="327" t="n"/>
+      <c r="AD8" s="405" t="n"/>
+      <c r="AE8" s="405" t="n"/>
+      <c r="AF8" s="405" t="n"/>
+      <c r="AG8" s="405" t="n"/>
+      <c r="AH8" s="405" t="n"/>
+      <c r="AI8" s="405" t="n"/>
+      <c r="AJ8" s="405" t="n"/>
+      <c r="AK8" s="405" t="n"/>
+      <c r="AL8" s="406" t="n"/>
+      <c r="AM8" s="358" t="n"/>
+      <c r="AN8" s="407" t="n"/>
+      <c r="AO8" s="407" t="n"/>
+      <c r="AP8" s="407" t="n"/>
+      <c r="AQ8" s="407" t="n"/>
+      <c r="AR8" s="407" t="n"/>
+      <c r="AS8" s="407" t="n"/>
+      <c r="AT8" s="407" t="n"/>
+      <c r="AU8" s="407" t="n"/>
+      <c r="AV8" s="407" t="n"/>
+      <c r="AW8" s="407" t="n"/>
+      <c r="AX8" s="407" t="n"/>
+      <c r="AY8" s="407" t="n"/>
+      <c r="AZ8" s="407" t="n"/>
+      <c r="BA8" s="407" t="n"/>
+      <c r="BB8" s="407" t="n"/>
+      <c r="BC8" s="407" t="n"/>
+      <c r="BD8" s="408" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="355" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B9" s="271" t="n"/>
-      <c r="C9" s="271" t="n"/>
-      <c r="D9" s="271" t="n"/>
-      <c r="E9" s="271" t="n"/>
-      <c r="F9" s="271" t="n"/>
-      <c r="G9" s="271" t="n"/>
-      <c r="H9" s="271" t="n"/>
-      <c r="I9" s="271" t="n"/>
-      <c r="J9" s="272" t="n"/>
-      <c r="K9" s="288" t="n"/>
-      <c r="L9" s="325" t="n"/>
-      <c r="M9" s="325" t="n"/>
-      <c r="N9" s="325" t="n"/>
-      <c r="O9" s="325" t="n"/>
-      <c r="P9" s="325" t="n"/>
-      <c r="Q9" s="325" t="n"/>
-      <c r="R9" s="325" t="n"/>
-      <c r="S9" s="325" t="n"/>
-      <c r="T9" s="325" t="n"/>
-      <c r="U9" s="325" t="n"/>
-      <c r="V9" s="325" t="n"/>
-      <c r="W9" s="325" t="n"/>
-      <c r="X9" s="325" t="n"/>
-      <c r="Y9" s="325" t="n"/>
-      <c r="Z9" s="325" t="n"/>
-      <c r="AA9" s="325" t="n"/>
-      <c r="AB9" s="326" t="n"/>
-      <c r="AC9" s="289" t="inlineStr">
+      <c r="B9" s="405" t="n"/>
+      <c r="C9" s="405" t="n"/>
+      <c r="D9" s="405" t="n"/>
+      <c r="E9" s="405" t="n"/>
+      <c r="F9" s="405" t="n"/>
+      <c r="G9" s="405" t="n"/>
+      <c r="H9" s="405" t="n"/>
+      <c r="I9" s="405" t="n"/>
+      <c r="J9" s="406" t="n"/>
+      <c r="K9" s="358" t="n"/>
+      <c r="L9" s="407" t="n"/>
+      <c r="M9" s="407" t="n"/>
+      <c r="N9" s="407" t="n"/>
+      <c r="O9" s="407" t="n"/>
+      <c r="P9" s="407" t="n"/>
+      <c r="Q9" s="407" t="n"/>
+      <c r="R9" s="407" t="n"/>
+      <c r="S9" s="407" t="n"/>
+      <c r="T9" s="407" t="n"/>
+      <c r="U9" s="407" t="n"/>
+      <c r="V9" s="407" t="n"/>
+      <c r="W9" s="407" t="n"/>
+      <c r="X9" s="407" t="n"/>
+      <c r="Y9" s="407" t="n"/>
+      <c r="Z9" s="407" t="n"/>
+      <c r="AA9" s="407" t="n"/>
+      <c r="AB9" s="408" t="n"/>
+      <c r="AC9" s="361" t="inlineStr">
         <is>
           <t>Job / Lot / Serial</t>
         </is>
       </c>
-      <c r="AD9" s="271" t="n"/>
-      <c r="AE9" s="271" t="n"/>
-      <c r="AF9" s="271" t="n"/>
-      <c r="AG9" s="271" t="n"/>
-      <c r="AH9" s="271" t="n"/>
-      <c r="AI9" s="271" t="n"/>
-      <c r="AJ9" s="271" t="n"/>
-      <c r="AK9" s="271" t="n"/>
-      <c r="AL9" s="272" t="n"/>
-      <c r="AM9" s="290" t="n"/>
-      <c r="AN9" s="325" t="n"/>
-      <c r="AO9" s="325" t="n"/>
-      <c r="AP9" s="325" t="n"/>
-      <c r="AQ9" s="325" t="n"/>
-      <c r="AR9" s="325" t="n"/>
-      <c r="AS9" s="325" t="n"/>
-      <c r="AT9" s="325" t="n"/>
-      <c r="AU9" s="325" t="n"/>
-      <c r="AV9" s="325" t="n"/>
-      <c r="AW9" s="325" t="n"/>
-      <c r="AX9" s="325" t="n"/>
-      <c r="AY9" s="325" t="n"/>
-      <c r="AZ9" s="325" t="n"/>
-      <c r="BA9" s="325" t="n"/>
-      <c r="BB9" s="325" t="n"/>
-      <c r="BC9" s="325" t="n"/>
-      <c r="BD9" s="327" t="n"/>
+      <c r="AD9" s="405" t="n"/>
+      <c r="AE9" s="405" t="n"/>
+      <c r="AF9" s="405" t="n"/>
+      <c r="AG9" s="405" t="n"/>
+      <c r="AH9" s="405" t="n"/>
+      <c r="AI9" s="405" t="n"/>
+      <c r="AJ9" s="405" t="n"/>
+      <c r="AK9" s="405" t="n"/>
+      <c r="AL9" s="406" t="n"/>
+      <c r="AM9" s="358" t="n"/>
+      <c r="AN9" s="407" t="n"/>
+      <c r="AO9" s="407" t="n"/>
+      <c r="AP9" s="407" t="n"/>
+      <c r="AQ9" s="407" t="n"/>
+      <c r="AR9" s="407" t="n"/>
+      <c r="AS9" s="407" t="n"/>
+      <c r="AT9" s="407" t="n"/>
+      <c r="AU9" s="407" t="n"/>
+      <c r="AV9" s="407" t="n"/>
+      <c r="AW9" s="407" t="n"/>
+      <c r="AX9" s="407" t="n"/>
+      <c r="AY9" s="407" t="n"/>
+      <c r="AZ9" s="407" t="n"/>
+      <c r="BA9" s="407" t="n"/>
+      <c r="BB9" s="407" t="n"/>
+      <c r="BC9" s="407" t="n"/>
+      <c r="BD9" s="408" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="355" t="inlineStr">
         <is>
           <t>Lot Qty</t>
         </is>
       </c>
-      <c r="B10" s="271" t="n"/>
-      <c r="C10" s="271" t="n"/>
-      <c r="D10" s="271" t="n"/>
-      <c r="E10" s="271" t="n"/>
-      <c r="F10" s="271" t="n"/>
-      <c r="G10" s="271" t="n"/>
-      <c r="H10" s="271" t="n"/>
-      <c r="I10" s="271" t="n"/>
-      <c r="J10" s="272" t="n"/>
-      <c r="K10" s="288" t="n"/>
-      <c r="L10" s="325" t="n"/>
-      <c r="M10" s="325" t="n"/>
-      <c r="N10" s="325" t="n"/>
-      <c r="O10" s="325" t="n"/>
-      <c r="P10" s="325" t="n"/>
-      <c r="Q10" s="325" t="n"/>
-      <c r="R10" s="325" t="n"/>
-      <c r="S10" s="325" t="n"/>
-      <c r="T10" s="325" t="n"/>
-      <c r="U10" s="325" t="n"/>
-      <c r="V10" s="325" t="n"/>
-      <c r="W10" s="325" t="n"/>
-      <c r="X10" s="325" t="n"/>
-      <c r="Y10" s="325" t="n"/>
-      <c r="Z10" s="325" t="n"/>
-      <c r="AA10" s="325" t="n"/>
-      <c r="AB10" s="326" t="n"/>
-      <c r="AC10" s="289" t="inlineStr">
+      <c r="B10" s="405" t="n"/>
+      <c r="C10" s="405" t="n"/>
+      <c r="D10" s="405" t="n"/>
+      <c r="E10" s="405" t="n"/>
+      <c r="F10" s="405" t="n"/>
+      <c r="G10" s="405" t="n"/>
+      <c r="H10" s="405" t="n"/>
+      <c r="I10" s="405" t="n"/>
+      <c r="J10" s="406" t="n"/>
+      <c r="K10" s="358" t="n"/>
+      <c r="L10" s="407" t="n"/>
+      <c r="M10" s="407" t="n"/>
+      <c r="N10" s="407" t="n"/>
+      <c r="O10" s="407" t="n"/>
+      <c r="P10" s="407" t="n"/>
+      <c r="Q10" s="407" t="n"/>
+      <c r="R10" s="407" t="n"/>
+      <c r="S10" s="407" t="n"/>
+      <c r="T10" s="407" t="n"/>
+      <c r="U10" s="407" t="n"/>
+      <c r="V10" s="407" t="n"/>
+      <c r="W10" s="407" t="n"/>
+      <c r="X10" s="407" t="n"/>
+      <c r="Y10" s="407" t="n"/>
+      <c r="Z10" s="407" t="n"/>
+      <c r="AA10" s="407" t="n"/>
+      <c r="AB10" s="408" t="n"/>
+      <c r="AC10" s="361" t="inlineStr">
         <is>
           <t>Characteristic Class</t>
         </is>
       </c>
-      <c r="AD10" s="271" t="n"/>
-      <c r="AE10" s="271" t="n"/>
-      <c r="AF10" s="271" t="n"/>
-      <c r="AG10" s="271" t="n"/>
-      <c r="AH10" s="271" t="n"/>
-      <c r="AI10" s="271" t="n"/>
-      <c r="AJ10" s="271" t="n"/>
-      <c r="AK10" s="271" t="n"/>
-      <c r="AL10" s="272" t="n"/>
-      <c r="AM10" s="290" t="n"/>
-      <c r="AN10" s="325" t="n"/>
-      <c r="AO10" s="325" t="n"/>
-      <c r="AP10" s="325" t="n"/>
-      <c r="AQ10" s="325" t="n"/>
-      <c r="AR10" s="325" t="n"/>
-      <c r="AS10" s="325" t="n"/>
-      <c r="AT10" s="325" t="n"/>
-      <c r="AU10" s="325" t="n"/>
-      <c r="AV10" s="325" t="n"/>
-      <c r="AW10" s="325" t="n"/>
-      <c r="AX10" s="325" t="n"/>
-      <c r="AY10" s="325" t="n"/>
-      <c r="AZ10" s="325" t="n"/>
-      <c r="BA10" s="325" t="n"/>
-      <c r="BB10" s="325" t="n"/>
-      <c r="BC10" s="325" t="n"/>
-      <c r="BD10" s="327" t="n"/>
+      <c r="AD10" s="405" t="n"/>
+      <c r="AE10" s="405" t="n"/>
+      <c r="AF10" s="405" t="n"/>
+      <c r="AG10" s="405" t="n"/>
+      <c r="AH10" s="405" t="n"/>
+      <c r="AI10" s="405" t="n"/>
+      <c r="AJ10" s="405" t="n"/>
+      <c r="AK10" s="405" t="n"/>
+      <c r="AL10" s="406" t="n"/>
+      <c r="AM10" s="358" t="n"/>
+      <c r="AN10" s="407" t="n"/>
+      <c r="AO10" s="407" t="n"/>
+      <c r="AP10" s="407" t="n"/>
+      <c r="AQ10" s="407" t="n"/>
+      <c r="AR10" s="407" t="n"/>
+      <c r="AS10" s="407" t="n"/>
+      <c r="AT10" s="407" t="n"/>
+      <c r="AU10" s="407" t="n"/>
+      <c r="AV10" s="407" t="n"/>
+      <c r="AW10" s="407" t="n"/>
+      <c r="AX10" s="407" t="n"/>
+      <c r="AY10" s="407" t="n"/>
+      <c r="AZ10" s="407" t="n"/>
+      <c r="BA10" s="407" t="n"/>
+      <c r="BB10" s="407" t="n"/>
+      <c r="BC10" s="407" t="n"/>
+      <c r="BD10" s="408" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="355" t="inlineStr">
         <is>
           <t>AQL</t>
         </is>
       </c>
-      <c r="B11" s="271" t="n"/>
-      <c r="C11" s="271" t="n"/>
-      <c r="D11" s="271" t="n"/>
-      <c r="E11" s="271" t="n"/>
-      <c r="F11" s="271" t="n"/>
-      <c r="G11" s="271" t="n"/>
-      <c r="H11" s="271" t="n"/>
-      <c r="I11" s="271" t="n"/>
-      <c r="J11" s="272" t="n"/>
-      <c r="K11" s="288" t="n"/>
-      <c r="L11" s="325" t="n"/>
-      <c r="M11" s="325" t="n"/>
-      <c r="N11" s="325" t="n"/>
-      <c r="O11" s="325" t="n"/>
-      <c r="P11" s="325" t="n"/>
-      <c r="Q11" s="325" t="n"/>
-      <c r="R11" s="325" t="n"/>
-      <c r="S11" s="325" t="n"/>
-      <c r="T11" s="325" t="n"/>
-      <c r="U11" s="325" t="n"/>
-      <c r="V11" s="325" t="n"/>
-      <c r="W11" s="325" t="n"/>
-      <c r="X11" s="325" t="n"/>
-      <c r="Y11" s="325" t="n"/>
-      <c r="Z11" s="325" t="n"/>
-      <c r="AA11" s="325" t="n"/>
-      <c r="AB11" s="326" t="n"/>
-      <c r="AC11" s="289" t="inlineStr">
+      <c r="B11" s="405" t="n"/>
+      <c r="C11" s="405" t="n"/>
+      <c r="D11" s="405" t="n"/>
+      <c r="E11" s="405" t="n"/>
+      <c r="F11" s="405" t="n"/>
+      <c r="G11" s="405" t="n"/>
+      <c r="H11" s="405" t="n"/>
+      <c r="I11" s="405" t="n"/>
+      <c r="J11" s="406" t="n"/>
+      <c r="K11" s="358" t="n"/>
+      <c r="L11" s="407" t="n"/>
+      <c r="M11" s="407" t="n"/>
+      <c r="N11" s="407" t="n"/>
+      <c r="O11" s="407" t="n"/>
+      <c r="P11" s="407" t="n"/>
+      <c r="Q11" s="407" t="n"/>
+      <c r="R11" s="407" t="n"/>
+      <c r="S11" s="407" t="n"/>
+      <c r="T11" s="407" t="n"/>
+      <c r="U11" s="407" t="n"/>
+      <c r="V11" s="407" t="n"/>
+      <c r="W11" s="407" t="n"/>
+      <c r="X11" s="407" t="n"/>
+      <c r="Y11" s="407" t="n"/>
+      <c r="Z11" s="407" t="n"/>
+      <c r="AA11" s="407" t="n"/>
+      <c r="AB11" s="408" t="n"/>
+      <c r="AC11" s="361" t="inlineStr">
         <is>
           <t>Inspection Level</t>
         </is>
       </c>
-      <c r="AD11" s="271" t="n"/>
-      <c r="AE11" s="271" t="n"/>
-      <c r="AF11" s="271" t="n"/>
-      <c r="AG11" s="271" t="n"/>
-      <c r="AH11" s="271" t="n"/>
-      <c r="AI11" s="271" t="n"/>
-      <c r="AJ11" s="271" t="n"/>
-      <c r="AK11" s="271" t="n"/>
-      <c r="AL11" s="272" t="n"/>
-      <c r="AM11" s="290" t="n"/>
-      <c r="AN11" s="325" t="n"/>
-      <c r="AO11" s="325" t="n"/>
-      <c r="AP11" s="325" t="n"/>
-      <c r="AQ11" s="325" t="n"/>
-      <c r="AR11" s="325" t="n"/>
-      <c r="AS11" s="325" t="n"/>
-      <c r="AT11" s="325" t="n"/>
-      <c r="AU11" s="325" t="n"/>
-      <c r="AV11" s="325" t="n"/>
-      <c r="AW11" s="325" t="n"/>
-      <c r="AX11" s="325" t="n"/>
-      <c r="AY11" s="325" t="n"/>
-      <c r="AZ11" s="325" t="n"/>
-      <c r="BA11" s="325" t="n"/>
-      <c r="BB11" s="325" t="n"/>
-      <c r="BC11" s="325" t="n"/>
-      <c r="BD11" s="327" t="n"/>
+      <c r="AD11" s="405" t="n"/>
+      <c r="AE11" s="405" t="n"/>
+      <c r="AF11" s="405" t="n"/>
+      <c r="AG11" s="405" t="n"/>
+      <c r="AH11" s="405" t="n"/>
+      <c r="AI11" s="405" t="n"/>
+      <c r="AJ11" s="405" t="n"/>
+      <c r="AK11" s="405" t="n"/>
+      <c r="AL11" s="406" t="n"/>
+      <c r="AM11" s="358" t="n"/>
+      <c r="AN11" s="407" t="n"/>
+      <c r="AO11" s="407" t="n"/>
+      <c r="AP11" s="407" t="n"/>
+      <c r="AQ11" s="407" t="n"/>
+      <c r="AR11" s="407" t="n"/>
+      <c r="AS11" s="407" t="n"/>
+      <c r="AT11" s="407" t="n"/>
+      <c r="AU11" s="407" t="n"/>
+      <c r="AV11" s="407" t="n"/>
+      <c r="AW11" s="407" t="n"/>
+      <c r="AX11" s="407" t="n"/>
+      <c r="AY11" s="407" t="n"/>
+      <c r="AZ11" s="407" t="n"/>
+      <c r="BA11" s="407" t="n"/>
+      <c r="BB11" s="407" t="n"/>
+      <c r="BC11" s="407" t="n"/>
+      <c r="BD11" s="408" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="355" t="inlineStr">
         <is>
           <t>Code Letter</t>
         </is>
       </c>
-      <c r="B12" s="271" t="n"/>
-      <c r="C12" s="271" t="n"/>
-      <c r="D12" s="271" t="n"/>
-      <c r="E12" s="271" t="n"/>
-      <c r="F12" s="271" t="n"/>
-      <c r="G12" s="271" t="n"/>
-      <c r="H12" s="271" t="n"/>
-      <c r="I12" s="271" t="n"/>
-      <c r="J12" s="272" t="n"/>
-      <c r="K12" s="288" t="n"/>
-      <c r="L12" s="325" t="n"/>
-      <c r="M12" s="325" t="n"/>
-      <c r="N12" s="325" t="n"/>
-      <c r="O12" s="325" t="n"/>
-      <c r="P12" s="325" t="n"/>
-      <c r="Q12" s="325" t="n"/>
-      <c r="R12" s="325" t="n"/>
-      <c r="S12" s="325" t="n"/>
-      <c r="T12" s="325" t="n"/>
-      <c r="U12" s="325" t="n"/>
-      <c r="V12" s="325" t="n"/>
-      <c r="W12" s="325" t="n"/>
-      <c r="X12" s="325" t="n"/>
-      <c r="Y12" s="325" t="n"/>
-      <c r="Z12" s="325" t="n"/>
-      <c r="AA12" s="325" t="n"/>
-      <c r="AB12" s="326" t="n"/>
-      <c r="AC12" s="289" t="inlineStr">
+      <c r="B12" s="405" t="n"/>
+      <c r="C12" s="405" t="n"/>
+      <c r="D12" s="405" t="n"/>
+      <c r="E12" s="405" t="n"/>
+      <c r="F12" s="405" t="n"/>
+      <c r="G12" s="405" t="n"/>
+      <c r="H12" s="405" t="n"/>
+      <c r="I12" s="405" t="n"/>
+      <c r="J12" s="406" t="n"/>
+      <c r="K12" s="358" t="n"/>
+      <c r="L12" s="407" t="n"/>
+      <c r="M12" s="407" t="n"/>
+      <c r="N12" s="407" t="n"/>
+      <c r="O12" s="407" t="n"/>
+      <c r="P12" s="407" t="n"/>
+      <c r="Q12" s="407" t="n"/>
+      <c r="R12" s="407" t="n"/>
+      <c r="S12" s="407" t="n"/>
+      <c r="T12" s="407" t="n"/>
+      <c r="U12" s="407" t="n"/>
+      <c r="V12" s="407" t="n"/>
+      <c r="W12" s="407" t="n"/>
+      <c r="X12" s="407" t="n"/>
+      <c r="Y12" s="407" t="n"/>
+      <c r="Z12" s="407" t="n"/>
+      <c r="AA12" s="407" t="n"/>
+      <c r="AB12" s="408" t="n"/>
+      <c r="AC12" s="361" t="inlineStr">
         <is>
           <t>Sample Size</t>
         </is>
       </c>
-      <c r="AD12" s="271" t="n"/>
-      <c r="AE12" s="271" t="n"/>
-      <c r="AF12" s="271" t="n"/>
-      <c r="AG12" s="271" t="n"/>
-      <c r="AH12" s="271" t="n"/>
-      <c r="AI12" s="271" t="n"/>
-      <c r="AJ12" s="271" t="n"/>
-      <c r="AK12" s="271" t="n"/>
-      <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
-      <c r="AN12" s="325" t="n"/>
-      <c r="AO12" s="325" t="n"/>
-      <c r="AP12" s="325" t="n"/>
-      <c r="AQ12" s="325" t="n"/>
-      <c r="AR12" s="325" t="n"/>
-      <c r="AS12" s="325" t="n"/>
-      <c r="AT12" s="325" t="n"/>
-      <c r="AU12" s="325" t="n"/>
-      <c r="AV12" s="325" t="n"/>
-      <c r="AW12" s="325" t="n"/>
-      <c r="AX12" s="325" t="n"/>
-      <c r="AY12" s="325" t="n"/>
-      <c r="AZ12" s="325" t="n"/>
-      <c r="BA12" s="325" t="n"/>
-      <c r="BB12" s="325" t="n"/>
-      <c r="BC12" s="325" t="n"/>
-      <c r="BD12" s="327" t="n"/>
+      <c r="AD12" s="405" t="n"/>
+      <c r="AE12" s="405" t="n"/>
+      <c r="AF12" s="405" t="n"/>
+      <c r="AG12" s="405" t="n"/>
+      <c r="AH12" s="405" t="n"/>
+      <c r="AI12" s="405" t="n"/>
+      <c r="AJ12" s="405" t="n"/>
+      <c r="AK12" s="405" t="n"/>
+      <c r="AL12" s="406" t="n"/>
+      <c r="AM12" s="358" t="n"/>
+      <c r="AN12" s="407" t="n"/>
+      <c r="AO12" s="407" t="n"/>
+      <c r="AP12" s="407" t="n"/>
+      <c r="AQ12" s="407" t="n"/>
+      <c r="AR12" s="407" t="n"/>
+      <c r="AS12" s="407" t="n"/>
+      <c r="AT12" s="407" t="n"/>
+      <c r="AU12" s="407" t="n"/>
+      <c r="AV12" s="407" t="n"/>
+      <c r="AW12" s="407" t="n"/>
+      <c r="AX12" s="407" t="n"/>
+      <c r="AY12" s="407" t="n"/>
+      <c r="AZ12" s="407" t="n"/>
+      <c r="BA12" s="407" t="n"/>
+      <c r="BB12" s="407" t="n"/>
+      <c r="BC12" s="407" t="n"/>
+      <c r="BD12" s="408" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="287" t="inlineStr">
+      <c r="A13" s="355" t="inlineStr">
         <is>
           <t>Ac / Re</t>
         </is>
       </c>
-      <c r="B13" s="271" t="n"/>
-      <c r="C13" s="271" t="n"/>
-      <c r="D13" s="271" t="n"/>
-      <c r="E13" s="271" t="n"/>
-      <c r="F13" s="271" t="n"/>
-      <c r="G13" s="271" t="n"/>
-      <c r="H13" s="271" t="n"/>
-      <c r="I13" s="271" t="n"/>
-      <c r="J13" s="272" t="n"/>
-      <c r="K13" s="288" t="n"/>
-      <c r="L13" s="325" t="n"/>
-      <c r="M13" s="325" t="n"/>
-      <c r="N13" s="325" t="n"/>
-      <c r="O13" s="325" t="n"/>
-      <c r="P13" s="325" t="n"/>
-      <c r="Q13" s="325" t="n"/>
-      <c r="R13" s="325" t="n"/>
-      <c r="S13" s="325" t="n"/>
-      <c r="T13" s="325" t="n"/>
-      <c r="U13" s="325" t="n"/>
-      <c r="V13" s="325" t="n"/>
-      <c r="W13" s="325" t="n"/>
-      <c r="X13" s="325" t="n"/>
-      <c r="Y13" s="325" t="n"/>
-      <c r="Z13" s="325" t="n"/>
-      <c r="AA13" s="325" t="n"/>
-      <c r="AB13" s="326" t="n"/>
-      <c r="AC13" s="289" t="inlineStr">
+      <c r="B13" s="405" t="n"/>
+      <c r="C13" s="405" t="n"/>
+      <c r="D13" s="405" t="n"/>
+      <c r="E13" s="405" t="n"/>
+      <c r="F13" s="405" t="n"/>
+      <c r="G13" s="405" t="n"/>
+      <c r="H13" s="405" t="n"/>
+      <c r="I13" s="405" t="n"/>
+      <c r="J13" s="406" t="n"/>
+      <c r="K13" s="358" t="n"/>
+      <c r="L13" s="407" t="n"/>
+      <c r="M13" s="407" t="n"/>
+      <c r="N13" s="407" t="n"/>
+      <c r="O13" s="407" t="n"/>
+      <c r="P13" s="407" t="n"/>
+      <c r="Q13" s="407" t="n"/>
+      <c r="R13" s="407" t="n"/>
+      <c r="S13" s="407" t="n"/>
+      <c r="T13" s="407" t="n"/>
+      <c r="U13" s="407" t="n"/>
+      <c r="V13" s="407" t="n"/>
+      <c r="W13" s="407" t="n"/>
+      <c r="X13" s="407" t="n"/>
+      <c r="Y13" s="407" t="n"/>
+      <c r="Z13" s="407" t="n"/>
+      <c r="AA13" s="407" t="n"/>
+      <c r="AB13" s="408" t="n"/>
+      <c r="AC13" s="361" t="inlineStr">
         <is>
           <t>Switching Status</t>
         </is>
       </c>
-      <c r="AD13" s="271" t="n"/>
-      <c r="AE13" s="271" t="n"/>
-      <c r="AF13" s="271" t="n"/>
-      <c r="AG13" s="271" t="n"/>
-      <c r="AH13" s="271" t="n"/>
-      <c r="AI13" s="271" t="n"/>
-      <c r="AJ13" s="271" t="n"/>
-      <c r="AK13" s="271" t="n"/>
-      <c r="AL13" s="272" t="n"/>
-      <c r="AM13" s="290" t="n"/>
-      <c r="AN13" s="325" t="n"/>
-      <c r="AO13" s="325" t="n"/>
-      <c r="AP13" s="325" t="n"/>
-      <c r="AQ13" s="325" t="n"/>
-      <c r="AR13" s="325" t="n"/>
-      <c r="AS13" s="325" t="n"/>
-      <c r="AT13" s="325" t="n"/>
-      <c r="AU13" s="325" t="n"/>
-      <c r="AV13" s="325" t="n"/>
-      <c r="AW13" s="325" t="n"/>
-      <c r="AX13" s="325" t="n"/>
-      <c r="AY13" s="325" t="n"/>
-      <c r="AZ13" s="325" t="n"/>
-      <c r="BA13" s="325" t="n"/>
-      <c r="BB13" s="325" t="n"/>
-      <c r="BC13" s="325" t="n"/>
-      <c r="BD13" s="327" t="n"/>
+      <c r="AD13" s="405" t="n"/>
+      <c r="AE13" s="405" t="n"/>
+      <c r="AF13" s="405" t="n"/>
+      <c r="AG13" s="405" t="n"/>
+      <c r="AH13" s="405" t="n"/>
+      <c r="AI13" s="405" t="n"/>
+      <c r="AJ13" s="405" t="n"/>
+      <c r="AK13" s="405" t="n"/>
+      <c r="AL13" s="406" t="n"/>
+      <c r="AM13" s="358" t="n"/>
+      <c r="AN13" s="407" t="n"/>
+      <c r="AO13" s="407" t="n"/>
+      <c r="AP13" s="407" t="n"/>
+      <c r="AQ13" s="407" t="n"/>
+      <c r="AR13" s="407" t="n"/>
+      <c r="AS13" s="407" t="n"/>
+      <c r="AT13" s="407" t="n"/>
+      <c r="AU13" s="407" t="n"/>
+      <c r="AV13" s="407" t="n"/>
+      <c r="AW13" s="407" t="n"/>
+      <c r="AX13" s="407" t="n"/>
+      <c r="AY13" s="407" t="n"/>
+      <c r="AZ13" s="407" t="n"/>
+      <c r="BA13" s="407" t="n"/>
+      <c r="BB13" s="407" t="n"/>
+      <c r="BC13" s="407" t="n"/>
+      <c r="BD13" s="408" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="287" t="inlineStr">
+      <c r="A14" s="355" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B14" s="271" t="n"/>
-      <c r="C14" s="271" t="n"/>
-      <c r="D14" s="271" t="n"/>
-      <c r="E14" s="271" t="n"/>
-      <c r="F14" s="271" t="n"/>
-      <c r="G14" s="271" t="n"/>
-      <c r="H14" s="271" t="n"/>
-      <c r="I14" s="271" t="n"/>
-      <c r="J14" s="272" t="n"/>
-      <c r="K14" s="288" t="n"/>
-      <c r="L14" s="325" t="n"/>
-      <c r="M14" s="325" t="n"/>
-      <c r="N14" s="325" t="n"/>
-      <c r="O14" s="325" t="n"/>
-      <c r="P14" s="325" t="n"/>
-      <c r="Q14" s="325" t="n"/>
-      <c r="R14" s="325" t="n"/>
-      <c r="S14" s="325" t="n"/>
-      <c r="T14" s="325" t="n"/>
-      <c r="U14" s="325" t="n"/>
-      <c r="V14" s="325" t="n"/>
-      <c r="W14" s="325" t="n"/>
-      <c r="X14" s="325" t="n"/>
-      <c r="Y14" s="325" t="n"/>
-      <c r="Z14" s="325" t="n"/>
-      <c r="AA14" s="325" t="n"/>
-      <c r="AB14" s="326" t="n"/>
-      <c r="AC14" s="289" t="inlineStr">
+      <c r="B14" s="400" t="n"/>
+      <c r="C14" s="400" t="n"/>
+      <c r="D14" s="400" t="n"/>
+      <c r="E14" s="400" t="n"/>
+      <c r="F14" s="400" t="n"/>
+      <c r="G14" s="400" t="n"/>
+      <c r="H14" s="400" t="n"/>
+      <c r="I14" s="400" t="n"/>
+      <c r="J14" s="401" t="n"/>
+      <c r="K14" s="358" t="n"/>
+      <c r="L14" s="409" t="n"/>
+      <c r="M14" s="409" t="n"/>
+      <c r="N14" s="409" t="n"/>
+      <c r="O14" s="409" t="n"/>
+      <c r="P14" s="409" t="n"/>
+      <c r="Q14" s="409" t="n"/>
+      <c r="R14" s="409" t="n"/>
+      <c r="S14" s="409" t="n"/>
+      <c r="T14" s="409" t="n"/>
+      <c r="U14" s="409" t="n"/>
+      <c r="V14" s="409" t="n"/>
+      <c r="W14" s="409" t="n"/>
+      <c r="X14" s="409" t="n"/>
+      <c r="Y14" s="409" t="n"/>
+      <c r="Z14" s="409" t="n"/>
+      <c r="AA14" s="409" t="n"/>
+      <c r="AB14" s="410" t="n"/>
+      <c r="AC14" s="361" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD14" s="271" t="n"/>
-      <c r="AE14" s="271" t="n"/>
-      <c r="AF14" s="271" t="n"/>
-      <c r="AG14" s="271" t="n"/>
-      <c r="AH14" s="271" t="n"/>
-      <c r="AI14" s="271" t="n"/>
-      <c r="AJ14" s="271" t="n"/>
-      <c r="AK14" s="271" t="n"/>
-      <c r="AL14" s="272" t="n"/>
-      <c r="AM14" s="290" t="n"/>
-      <c r="AN14" s="325" t="n"/>
-      <c r="AO14" s="325" t="n"/>
-      <c r="AP14" s="325" t="n"/>
-      <c r="AQ14" s="325" t="n"/>
-      <c r="AR14" s="325" t="n"/>
-      <c r="AS14" s="325" t="n"/>
-      <c r="AT14" s="325" t="n"/>
-      <c r="AU14" s="325" t="n"/>
-      <c r="AV14" s="325" t="n"/>
-      <c r="AW14" s="325" t="n"/>
-      <c r="AX14" s="325" t="n"/>
-      <c r="AY14" s="325" t="n"/>
-      <c r="AZ14" s="325" t="n"/>
-      <c r="BA14" s="325" t="n"/>
-      <c r="BB14" s="325" t="n"/>
-      <c r="BC14" s="325" t="n"/>
-      <c r="BD14" s="327" t="n"/>
+      <c r="AD14" s="400" t="n"/>
+      <c r="AE14" s="400" t="n"/>
+      <c r="AF14" s="400" t="n"/>
+      <c r="AG14" s="400" t="n"/>
+      <c r="AH14" s="400" t="n"/>
+      <c r="AI14" s="400" t="n"/>
+      <c r="AJ14" s="400" t="n"/>
+      <c r="AK14" s="400" t="n"/>
+      <c r="AL14" s="401" t="n"/>
+      <c r="AM14" s="358" t="n"/>
+      <c r="AN14" s="409" t="n"/>
+      <c r="AO14" s="409" t="n"/>
+      <c r="AP14" s="409" t="n"/>
+      <c r="AQ14" s="409" t="n"/>
+      <c r="AR14" s="409" t="n"/>
+      <c r="AS14" s="409" t="n"/>
+      <c r="AT14" s="409" t="n"/>
+      <c r="AU14" s="409" t="n"/>
+      <c r="AV14" s="409" t="n"/>
+      <c r="AW14" s="409" t="n"/>
+      <c r="AX14" s="409" t="n"/>
+      <c r="AY14" s="409" t="n"/>
+      <c r="AZ14" s="409" t="n"/>
+      <c r="BA14" s="409" t="n"/>
+      <c r="BB14" s="409" t="n"/>
+      <c r="BC14" s="409" t="n"/>
+      <c r="BD14" s="410" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="287" t="inlineStr">
+      <c r="A15" s="355" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="271" t="n"/>
-      <c r="D15" s="271" t="n"/>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="271" t="n"/>
-      <c r="H15" s="271" t="n"/>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="272" t="n"/>
-      <c r="K15" s="288" t="n"/>
-      <c r="L15" s="325" t="n"/>
-      <c r="M15" s="325" t="n"/>
-      <c r="N15" s="325" t="n"/>
-      <c r="O15" s="325" t="n"/>
-      <c r="P15" s="325" t="n"/>
-      <c r="Q15" s="325" t="n"/>
-      <c r="R15" s="325" t="n"/>
-      <c r="S15" s="325" t="n"/>
-      <c r="T15" s="325" t="n"/>
-      <c r="U15" s="325" t="n"/>
-      <c r="V15" s="325" t="n"/>
-      <c r="W15" s="325" t="n"/>
-      <c r="X15" s="325" t="n"/>
-      <c r="Y15" s="325" t="n"/>
-      <c r="Z15" s="325" t="n"/>
-      <c r="AA15" s="325" t="n"/>
-      <c r="AB15" s="326" t="n"/>
-      <c r="AC15" s="289" t="inlineStr">
+      <c r="B15" s="405" t="n"/>
+      <c r="C15" s="405" t="n"/>
+      <c r="D15" s="405" t="n"/>
+      <c r="E15" s="405" t="n"/>
+      <c r="F15" s="405" t="n"/>
+      <c r="G15" s="405" t="n"/>
+      <c r="H15" s="405" t="n"/>
+      <c r="I15" s="405" t="n"/>
+      <c r="J15" s="406" t="n"/>
+      <c r="K15" s="358" t="n"/>
+      <c r="L15" s="407" t="n"/>
+      <c r="M15" s="407" t="n"/>
+      <c r="N15" s="407" t="n"/>
+      <c r="O15" s="407" t="n"/>
+      <c r="P15" s="407" t="n"/>
+      <c r="Q15" s="407" t="n"/>
+      <c r="R15" s="407" t="n"/>
+      <c r="S15" s="407" t="n"/>
+      <c r="T15" s="407" t="n"/>
+      <c r="U15" s="407" t="n"/>
+      <c r="V15" s="407" t="n"/>
+      <c r="W15" s="407" t="n"/>
+      <c r="X15" s="407" t="n"/>
+      <c r="Y15" s="407" t="n"/>
+      <c r="Z15" s="407" t="n"/>
+      <c r="AA15" s="407" t="n"/>
+      <c r="AB15" s="408" t="n"/>
+      <c r="AC15" s="361" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="272" t="n"/>
-      <c r="AM15" s="290" t="n"/>
-      <c r="AN15" s="325" t="n"/>
-      <c r="AO15" s="325" t="n"/>
-      <c r="AP15" s="325" t="n"/>
-      <c r="AQ15" s="325" t="n"/>
-      <c r="AR15" s="325" t="n"/>
-      <c r="AS15" s="325" t="n"/>
-      <c r="AT15" s="325" t="n"/>
-      <c r="AU15" s="325" t="n"/>
-      <c r="AV15" s="325" t="n"/>
-      <c r="AW15" s="325" t="n"/>
-      <c r="AX15" s="325" t="n"/>
-      <c r="AY15" s="325" t="n"/>
-      <c r="AZ15" s="325" t="n"/>
-      <c r="BA15" s="325" t="n"/>
-      <c r="BB15" s="325" t="n"/>
-      <c r="BC15" s="325" t="n"/>
-      <c r="BD15" s="327" t="n"/>
+      <c r="AD15" s="405" t="n"/>
+      <c r="AE15" s="405" t="n"/>
+      <c r="AF15" s="405" t="n"/>
+      <c r="AG15" s="405" t="n"/>
+      <c r="AH15" s="405" t="n"/>
+      <c r="AI15" s="405" t="n"/>
+      <c r="AJ15" s="405" t="n"/>
+      <c r="AK15" s="405" t="n"/>
+      <c r="AL15" s="406" t="n"/>
+      <c r="AM15" s="358" t="n"/>
+      <c r="AN15" s="407" t="n"/>
+      <c r="AO15" s="407" t="n"/>
+      <c r="AP15" s="407" t="n"/>
+      <c r="AQ15" s="407" t="n"/>
+      <c r="AR15" s="407" t="n"/>
+      <c r="AS15" s="407" t="n"/>
+      <c r="AT15" s="407" t="n"/>
+      <c r="AU15" s="407" t="n"/>
+      <c r="AV15" s="407" t="n"/>
+      <c r="AW15" s="407" t="n"/>
+      <c r="AX15" s="407" t="n"/>
+      <c r="AY15" s="407" t="n"/>
+      <c r="AZ15" s="407" t="n"/>
+      <c r="BA15" s="407" t="n"/>
+      <c r="BB15" s="407" t="n"/>
+      <c r="BC15" s="407" t="n"/>
+      <c r="BD15" s="408" t="n"/>
     </row>
     <row r="16" ht="4" customHeight="1">
-      <c r="A16" s="291" t="n"/>
-      <c r="K16" s="292" t="n"/>
-      <c r="AC16" s="293" t="n"/>
-      <c r="AM16" s="294" t="n"/>
+      <c r="A16" s="364" t="n"/>
+      <c r="B16" s="353" t="n"/>
+      <c r="C16" s="353" t="n"/>
+      <c r="D16" s="353" t="n"/>
+      <c r="E16" s="353" t="n"/>
+      <c r="F16" s="353" t="n"/>
+      <c r="G16" s="353" t="n"/>
+      <c r="H16" s="353" t="n"/>
+      <c r="I16" s="353" t="n"/>
+      <c r="J16" s="353" t="n"/>
+      <c r="K16" s="365" t="n"/>
+      <c r="L16" s="353" t="n"/>
+      <c r="M16" s="353" t="n"/>
+      <c r="N16" s="353" t="n"/>
+      <c r="O16" s="353" t="n"/>
+      <c r="P16" s="353" t="n"/>
+      <c r="Q16" s="353" t="n"/>
+      <c r="R16" s="353" t="n"/>
+      <c r="S16" s="353" t="n"/>
+      <c r="T16" s="353" t="n"/>
+      <c r="U16" s="353" t="n"/>
+      <c r="V16" s="353" t="n"/>
+      <c r="W16" s="353" t="n"/>
+      <c r="X16" s="353" t="n"/>
+      <c r="Y16" s="353" t="n"/>
+      <c r="Z16" s="353" t="n"/>
+      <c r="AA16" s="353" t="n"/>
+      <c r="AB16" s="353" t="n"/>
+      <c r="AC16" s="364" t="n"/>
+      <c r="AD16" s="353" t="n"/>
+      <c r="AE16" s="353" t="n"/>
+      <c r="AF16" s="353" t="n"/>
+      <c r="AG16" s="353" t="n"/>
+      <c r="AH16" s="353" t="n"/>
+      <c r="AI16" s="353" t="n"/>
+      <c r="AJ16" s="353" t="n"/>
+      <c r="AK16" s="353" t="n"/>
+      <c r="AL16" s="353" t="n"/>
+      <c r="AM16" s="365" t="n"/>
+      <c r="AN16" s="353" t="n"/>
+      <c r="AO16" s="353" t="n"/>
+      <c r="AP16" s="353" t="n"/>
+      <c r="AQ16" s="353" t="n"/>
+      <c r="AR16" s="353" t="n"/>
+      <c r="AS16" s="353" t="n"/>
+      <c r="AT16" s="353" t="n"/>
+      <c r="AU16" s="353" t="n"/>
+      <c r="AV16" s="353" t="n"/>
+      <c r="AW16" s="353" t="n"/>
+      <c r="AX16" s="353" t="n"/>
+      <c r="AY16" s="353" t="n"/>
+      <c r="AZ16" s="353" t="n"/>
+      <c r="BA16" s="353" t="n"/>
+      <c r="BB16" s="353" t="n"/>
+      <c r="BC16" s="353" t="n"/>
+      <c r="BD16" s="353" t="n"/>
     </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="284" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B17" s="285" t="n"/>
-      <c r="C17" s="285" t="n"/>
-      <c r="D17" s="285" t="n"/>
-      <c r="E17" s="285" t="n"/>
-      <c r="F17" s="285" t="n"/>
-      <c r="G17" s="285" t="n"/>
-      <c r="H17" s="285" t="n"/>
-      <c r="I17" s="285" t="n"/>
-      <c r="J17" s="285" t="n"/>
-      <c r="K17" s="285" t="n"/>
-      <c r="L17" s="285" t="n"/>
-      <c r="M17" s="285" t="n"/>
-      <c r="N17" s="285" t="n"/>
-      <c r="O17" s="285" t="n"/>
-      <c r="P17" s="285" t="n"/>
-      <c r="Q17" s="285" t="n"/>
-      <c r="R17" s="285" t="n"/>
-      <c r="S17" s="285" t="n"/>
-      <c r="T17" s="285" t="n"/>
-      <c r="U17" s="285" t="n"/>
-      <c r="V17" s="285" t="n"/>
-      <c r="W17" s="285" t="n"/>
-      <c r="X17" s="285" t="n"/>
-      <c r="Y17" s="285" t="n"/>
-      <c r="Z17" s="285" t="n"/>
-      <c r="AA17" s="285" t="n"/>
-      <c r="AB17" s="285" t="n"/>
-      <c r="AC17" s="285" t="n"/>
-      <c r="AD17" s="285" t="n"/>
-      <c r="AE17" s="285" t="n"/>
-      <c r="AF17" s="285" t="n"/>
-      <c r="AG17" s="285" t="n"/>
-      <c r="AH17" s="285" t="n"/>
-      <c r="AI17" s="285" t="n"/>
-      <c r="AJ17" s="285" t="n"/>
-      <c r="AK17" s="285" t="n"/>
-      <c r="AL17" s="285" t="n"/>
-      <c r="AM17" s="285" t="n"/>
-      <c r="AN17" s="285" t="n"/>
-      <c r="AO17" s="285" t="n"/>
-      <c r="AP17" s="285" t="n"/>
-      <c r="AQ17" s="285" t="n"/>
-      <c r="AR17" s="285" t="n"/>
-      <c r="AS17" s="285" t="n"/>
-      <c r="AT17" s="285" t="n"/>
-      <c r="AU17" s="285" t="n"/>
-      <c r="AV17" s="285" t="n"/>
-      <c r="AW17" s="285" t="n"/>
-      <c r="AX17" s="285" t="n"/>
-      <c r="AY17" s="285" t="n"/>
-      <c r="AZ17" s="285" t="n"/>
-      <c r="BA17" s="285" t="n"/>
-      <c r="BB17" s="285" t="n"/>
-      <c r="BC17" s="285" t="n"/>
-      <c r="BD17" s="286" t="n"/>
+      <c r="B17" s="405" t="n"/>
+      <c r="C17" s="405" t="n"/>
+      <c r="D17" s="405" t="n"/>
+      <c r="E17" s="405" t="n"/>
+      <c r="F17" s="405" t="n"/>
+      <c r="G17" s="405" t="n"/>
+      <c r="H17" s="405" t="n"/>
+      <c r="I17" s="405" t="n"/>
+      <c r="J17" s="405" t="n"/>
+      <c r="K17" s="405" t="n"/>
+      <c r="L17" s="405" t="n"/>
+      <c r="M17" s="405" t="n"/>
+      <c r="N17" s="405" t="n"/>
+      <c r="O17" s="405" t="n"/>
+      <c r="P17" s="405" t="n"/>
+      <c r="Q17" s="405" t="n"/>
+      <c r="R17" s="405" t="n"/>
+      <c r="S17" s="405" t="n"/>
+      <c r="T17" s="405" t="n"/>
+      <c r="U17" s="405" t="n"/>
+      <c r="V17" s="405" t="n"/>
+      <c r="W17" s="405" t="n"/>
+      <c r="X17" s="405" t="n"/>
+      <c r="Y17" s="405" t="n"/>
+      <c r="Z17" s="405" t="n"/>
+      <c r="AA17" s="405" t="n"/>
+      <c r="AB17" s="405" t="n"/>
+      <c r="AC17" s="405" t="n"/>
+      <c r="AD17" s="405" t="n"/>
+      <c r="AE17" s="405" t="n"/>
+      <c r="AF17" s="405" t="n"/>
+      <c r="AG17" s="405" t="n"/>
+      <c r="AH17" s="405" t="n"/>
+      <c r="AI17" s="405" t="n"/>
+      <c r="AJ17" s="405" t="n"/>
+      <c r="AK17" s="405" t="n"/>
+      <c r="AL17" s="405" t="n"/>
+      <c r="AM17" s="405" t="n"/>
+      <c r="AN17" s="405" t="n"/>
+      <c r="AO17" s="405" t="n"/>
+      <c r="AP17" s="405" t="n"/>
+      <c r="AQ17" s="405" t="n"/>
+      <c r="AR17" s="405" t="n"/>
+      <c r="AS17" s="405" t="n"/>
+      <c r="AT17" s="405" t="n"/>
+      <c r="AU17" s="405" t="n"/>
+      <c r="AV17" s="405" t="n"/>
+      <c r="AW17" s="405" t="n"/>
+      <c r="AX17" s="405" t="n"/>
+      <c r="AY17" s="405" t="n"/>
+      <c r="AZ17" s="405" t="n"/>
+      <c r="BA17" s="405" t="n"/>
+      <c r="BB17" s="405" t="n"/>
+      <c r="BC17" s="405" t="n"/>
+      <c r="BD17" s="406" t="n"/>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="295" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="366" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="271" t="n"/>
-      <c r="C18" s="272" t="n"/>
-      <c r="D18" s="296" t="inlineStr">
+      <c r="B18" s="405" t="n"/>
+      <c r="C18" s="406" t="n"/>
+      <c r="D18" s="367" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="E18" s="271" t="n"/>
-      <c r="F18" s="271" t="n"/>
-      <c r="G18" s="272" t="n"/>
-      <c r="H18" s="296" t="inlineStr">
+      <c r="E18" s="405" t="n"/>
+      <c r="F18" s="405" t="n"/>
+      <c r="G18" s="406" t="n"/>
+      <c r="H18" s="367" t="inlineStr">
         <is>
           <t>Sample ID / Serial</t>
         </is>
       </c>
-      <c r="I18" s="271" t="n"/>
-      <c r="J18" s="271" t="n"/>
-      <c r="K18" s="271" t="n"/>
-      <c r="L18" s="271" t="n"/>
-      <c r="M18" s="271" t="n"/>
-      <c r="N18" s="271" t="n"/>
-      <c r="O18" s="271" t="n"/>
-      <c r="P18" s="271" t="n"/>
-      <c r="Q18" s="271" t="n"/>
-      <c r="R18" s="271" t="n"/>
-      <c r="S18" s="271" t="n"/>
-      <c r="T18" s="271" t="n"/>
-      <c r="U18" s="271" t="n"/>
-      <c r="V18" s="271" t="n"/>
-      <c r="W18" s="271" t="n"/>
-      <c r="X18" s="271" t="n"/>
-      <c r="Y18" s="271" t="n"/>
-      <c r="Z18" s="272" t="n"/>
-      <c r="AA18" s="296" t="inlineStr">
+      <c r="I18" s="405" t="n"/>
+      <c r="J18" s="405" t="n"/>
+      <c r="K18" s="405" t="n"/>
+      <c r="L18" s="405" t="n"/>
+      <c r="M18" s="405" t="n"/>
+      <c r="N18" s="405" t="n"/>
+      <c r="O18" s="405" t="n"/>
+      <c r="P18" s="405" t="n"/>
+      <c r="Q18" s="405" t="n"/>
+      <c r="R18" s="405" t="n"/>
+      <c r="S18" s="405" t="n"/>
+      <c r="T18" s="405" t="n"/>
+      <c r="U18" s="405" t="n"/>
+      <c r="V18" s="405" t="n"/>
+      <c r="W18" s="405" t="n"/>
+      <c r="X18" s="405" t="n"/>
+      <c r="Y18" s="405" t="n"/>
+      <c r="Z18" s="406" t="n"/>
+      <c r="AA18" s="367" t="inlineStr">
         <is>
           <t>Observation / Measured Result</t>
         </is>
       </c>
-      <c r="AB18" s="271" t="n"/>
-      <c r="AC18" s="271" t="n"/>
-      <c r="AD18" s="271" t="n"/>
-      <c r="AE18" s="271" t="n"/>
-      <c r="AF18" s="271" t="n"/>
-      <c r="AG18" s="271" t="n"/>
-      <c r="AH18" s="271" t="n"/>
-      <c r="AI18" s="271" t="n"/>
-      <c r="AJ18" s="271" t="n"/>
-      <c r="AK18" s="271" t="n"/>
-      <c r="AL18" s="271" t="n"/>
-      <c r="AM18" s="271" t="n"/>
-      <c r="AN18" s="271" t="n"/>
-      <c r="AO18" s="271" t="n"/>
-      <c r="AP18" s="271" t="n"/>
-      <c r="AQ18" s="272" t="n"/>
-      <c r="AR18" s="296" t="inlineStr">
+      <c r="AB18" s="405" t="n"/>
+      <c r="AC18" s="405" t="n"/>
+      <c r="AD18" s="405" t="n"/>
+      <c r="AE18" s="405" t="n"/>
+      <c r="AF18" s="405" t="n"/>
+      <c r="AG18" s="405" t="n"/>
+      <c r="AH18" s="405" t="n"/>
+      <c r="AI18" s="405" t="n"/>
+      <c r="AJ18" s="405" t="n"/>
+      <c r="AK18" s="405" t="n"/>
+      <c r="AL18" s="405" t="n"/>
+      <c r="AM18" s="405" t="n"/>
+      <c r="AN18" s="405" t="n"/>
+      <c r="AO18" s="405" t="n"/>
+      <c r="AP18" s="405" t="n"/>
+      <c r="AQ18" s="406" t="n"/>
+      <c r="AR18" s="367" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS18" s="271" t="n"/>
-      <c r="AT18" s="271" t="n"/>
-      <c r="AU18" s="271" t="n"/>
-      <c r="AV18" s="271" t="n"/>
-      <c r="AW18" s="272" t="n"/>
-      <c r="AX18" s="296" t="inlineStr">
+      <c r="AS18" s="405" t="n"/>
+      <c r="AT18" s="405" t="n"/>
+      <c r="AU18" s="405" t="n"/>
+      <c r="AV18" s="405" t="n"/>
+      <c r="AW18" s="406" t="n"/>
+      <c r="AX18" s="367" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY18" s="271" t="n"/>
-      <c r="AZ18" s="271" t="n"/>
-      <c r="BA18" s="272" t="n"/>
-      <c r="BB18" s="297" t="inlineStr">
+      <c r="AY18" s="405" t="n"/>
+      <c r="AZ18" s="405" t="n"/>
+      <c r="BA18" s="406" t="n"/>
+      <c r="BB18" s="367" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC18" s="271" t="n"/>
-      <c r="BD18" s="274" t="n"/>
+      <c r="BC18" s="405" t="n"/>
+      <c r="BD18" s="406" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="298">
+      <c r="A19" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B19" s="276" t="n"/>
-      <c r="C19" s="277" t="n"/>
-      <c r="D19" s="299" t="inlineStr">
+      <c r="B19" s="411" t="n"/>
+      <c r="C19" s="412" t="n"/>
+      <c r="D19" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="328" t="n"/>
-      <c r="F19" s="328" t="n"/>
-      <c r="G19" s="329" t="n"/>
-      <c r="H19" s="300" t="n"/>
-      <c r="I19" s="328" t="n"/>
-      <c r="J19" s="328" t="n"/>
-      <c r="K19" s="328" t="n"/>
-      <c r="L19" s="328" t="n"/>
-      <c r="M19" s="328" t="n"/>
-      <c r="N19" s="328" t="n"/>
-      <c r="O19" s="328" t="n"/>
-      <c r="P19" s="328" t="n"/>
-      <c r="Q19" s="328" t="n"/>
-      <c r="R19" s="328" t="n"/>
-      <c r="S19" s="328" t="n"/>
-      <c r="T19" s="328" t="n"/>
-      <c r="U19" s="328" t="n"/>
-      <c r="V19" s="328" t="n"/>
-      <c r="W19" s="328" t="n"/>
-      <c r="X19" s="328" t="n"/>
-      <c r="Y19" s="328" t="n"/>
-      <c r="Z19" s="329" t="n"/>
-      <c r="AA19" s="301" t="n"/>
-      <c r="AB19" s="328" t="n"/>
-      <c r="AC19" s="328" t="n"/>
-      <c r="AD19" s="328" t="n"/>
-      <c r="AE19" s="328" t="n"/>
-      <c r="AF19" s="328" t="n"/>
-      <c r="AG19" s="328" t="n"/>
-      <c r="AH19" s="328" t="n"/>
-      <c r="AI19" s="328" t="n"/>
-      <c r="AJ19" s="328" t="n"/>
-      <c r="AK19" s="328" t="n"/>
-      <c r="AL19" s="328" t="n"/>
-      <c r="AM19" s="328" t="n"/>
-      <c r="AN19" s="328" t="n"/>
-      <c r="AO19" s="328" t="n"/>
-      <c r="AP19" s="328" t="n"/>
-      <c r="AQ19" s="329" t="n"/>
-      <c r="AR19" s="300" t="n"/>
-      <c r="AS19" s="328" t="n"/>
-      <c r="AT19" s="328" t="n"/>
-      <c r="AU19" s="328" t="n"/>
-      <c r="AV19" s="328" t="n"/>
-      <c r="AW19" s="329" t="n"/>
-      <c r="AX19" s="300" t="n"/>
-      <c r="AY19" s="328" t="n"/>
-      <c r="AZ19" s="328" t="n"/>
-      <c r="BA19" s="329" t="n"/>
-      <c r="BB19" s="302" t="n"/>
-      <c r="BC19" s="328" t="n"/>
-      <c r="BD19" s="330" t="n"/>
+      <c r="E19" s="413" t="n"/>
+      <c r="F19" s="413" t="n"/>
+      <c r="G19" s="414" t="n"/>
+      <c r="H19" s="374" t="n"/>
+      <c r="I19" s="413" t="n"/>
+      <c r="J19" s="413" t="n"/>
+      <c r="K19" s="413" t="n"/>
+      <c r="L19" s="413" t="n"/>
+      <c r="M19" s="413" t="n"/>
+      <c r="N19" s="413" t="n"/>
+      <c r="O19" s="413" t="n"/>
+      <c r="P19" s="413" t="n"/>
+      <c r="Q19" s="413" t="n"/>
+      <c r="R19" s="413" t="n"/>
+      <c r="S19" s="413" t="n"/>
+      <c r="T19" s="413" t="n"/>
+      <c r="U19" s="413" t="n"/>
+      <c r="V19" s="413" t="n"/>
+      <c r="W19" s="413" t="n"/>
+      <c r="X19" s="413" t="n"/>
+      <c r="Y19" s="413" t="n"/>
+      <c r="Z19" s="414" t="n"/>
+      <c r="AA19" s="375" t="n"/>
+      <c r="AB19" s="413" t="n"/>
+      <c r="AC19" s="413" t="n"/>
+      <c r="AD19" s="413" t="n"/>
+      <c r="AE19" s="413" t="n"/>
+      <c r="AF19" s="413" t="n"/>
+      <c r="AG19" s="413" t="n"/>
+      <c r="AH19" s="413" t="n"/>
+      <c r="AI19" s="413" t="n"/>
+      <c r="AJ19" s="413" t="n"/>
+      <c r="AK19" s="413" t="n"/>
+      <c r="AL19" s="413" t="n"/>
+      <c r="AM19" s="413" t="n"/>
+      <c r="AN19" s="413" t="n"/>
+      <c r="AO19" s="413" t="n"/>
+      <c r="AP19" s="413" t="n"/>
+      <c r="AQ19" s="414" t="n"/>
+      <c r="AR19" s="374" t="n"/>
+      <c r="AS19" s="413" t="n"/>
+      <c r="AT19" s="413" t="n"/>
+      <c r="AU19" s="413" t="n"/>
+      <c r="AV19" s="413" t="n"/>
+      <c r="AW19" s="414" t="n"/>
+      <c r="AX19" s="374" t="n"/>
+      <c r="AY19" s="413" t="n"/>
+      <c r="AZ19" s="413" t="n"/>
+      <c r="BA19" s="414" t="n"/>
+      <c r="BB19" s="376" t="n"/>
+      <c r="BC19" s="413" t="n"/>
+      <c r="BD19" s="414" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="298">
+      <c r="A20" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B20" s="276" t="n"/>
-      <c r="C20" s="277" t="n"/>
-      <c r="D20" s="299" t="inlineStr">
+      <c r="B20" s="411" t="n"/>
+      <c r="C20" s="412" t="n"/>
+      <c r="D20" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="328" t="n"/>
-      <c r="F20" s="328" t="n"/>
-      <c r="G20" s="329" t="n"/>
-      <c r="H20" s="300" t="n"/>
-      <c r="I20" s="328" t="n"/>
-      <c r="J20" s="328" t="n"/>
-      <c r="K20" s="328" t="n"/>
-      <c r="L20" s="328" t="n"/>
-      <c r="M20" s="328" t="n"/>
-      <c r="N20" s="328" t="n"/>
-      <c r="O20" s="328" t="n"/>
-      <c r="P20" s="328" t="n"/>
-      <c r="Q20" s="328" t="n"/>
-      <c r="R20" s="328" t="n"/>
-      <c r="S20" s="328" t="n"/>
-      <c r="T20" s="328" t="n"/>
-      <c r="U20" s="328" t="n"/>
-      <c r="V20" s="328" t="n"/>
-      <c r="W20" s="328" t="n"/>
-      <c r="X20" s="328" t="n"/>
-      <c r="Y20" s="328" t="n"/>
-      <c r="Z20" s="329" t="n"/>
-      <c r="AA20" s="301" t="n"/>
-      <c r="AB20" s="328" t="n"/>
-      <c r="AC20" s="328" t="n"/>
-      <c r="AD20" s="328" t="n"/>
-      <c r="AE20" s="328" t="n"/>
-      <c r="AF20" s="328" t="n"/>
-      <c r="AG20" s="328" t="n"/>
-      <c r="AH20" s="328" t="n"/>
-      <c r="AI20" s="328" t="n"/>
-      <c r="AJ20" s="328" t="n"/>
-      <c r="AK20" s="328" t="n"/>
-      <c r="AL20" s="328" t="n"/>
-      <c r="AM20" s="328" t="n"/>
-      <c r="AN20" s="328" t="n"/>
-      <c r="AO20" s="328" t="n"/>
-      <c r="AP20" s="328" t="n"/>
-      <c r="AQ20" s="329" t="n"/>
-      <c r="AR20" s="300" t="n"/>
-      <c r="AS20" s="328" t="n"/>
-      <c r="AT20" s="328" t="n"/>
-      <c r="AU20" s="328" t="n"/>
-      <c r="AV20" s="328" t="n"/>
-      <c r="AW20" s="329" t="n"/>
-      <c r="AX20" s="300" t="n"/>
-      <c r="AY20" s="328" t="n"/>
-      <c r="AZ20" s="328" t="n"/>
-      <c r="BA20" s="329" t="n"/>
-      <c r="BB20" s="302" t="n"/>
-      <c r="BC20" s="328" t="n"/>
-      <c r="BD20" s="330" t="n"/>
+      <c r="E20" s="413" t="n"/>
+      <c r="F20" s="413" t="n"/>
+      <c r="G20" s="414" t="n"/>
+      <c r="H20" s="374" t="n"/>
+      <c r="I20" s="413" t="n"/>
+      <c r="J20" s="413" t="n"/>
+      <c r="K20" s="413" t="n"/>
+      <c r="L20" s="413" t="n"/>
+      <c r="M20" s="413" t="n"/>
+      <c r="N20" s="413" t="n"/>
+      <c r="O20" s="413" t="n"/>
+      <c r="P20" s="413" t="n"/>
+      <c r="Q20" s="413" t="n"/>
+      <c r="R20" s="413" t="n"/>
+      <c r="S20" s="413" t="n"/>
+      <c r="T20" s="413" t="n"/>
+      <c r="U20" s="413" t="n"/>
+      <c r="V20" s="413" t="n"/>
+      <c r="W20" s="413" t="n"/>
+      <c r="X20" s="413" t="n"/>
+      <c r="Y20" s="413" t="n"/>
+      <c r="Z20" s="414" t="n"/>
+      <c r="AA20" s="375" t="n"/>
+      <c r="AB20" s="413" t="n"/>
+      <c r="AC20" s="413" t="n"/>
+      <c r="AD20" s="413" t="n"/>
+      <c r="AE20" s="413" t="n"/>
+      <c r="AF20" s="413" t="n"/>
+      <c r="AG20" s="413" t="n"/>
+      <c r="AH20" s="413" t="n"/>
+      <c r="AI20" s="413" t="n"/>
+      <c r="AJ20" s="413" t="n"/>
+      <c r="AK20" s="413" t="n"/>
+      <c r="AL20" s="413" t="n"/>
+      <c r="AM20" s="413" t="n"/>
+      <c r="AN20" s="413" t="n"/>
+      <c r="AO20" s="413" t="n"/>
+      <c r="AP20" s="413" t="n"/>
+      <c r="AQ20" s="414" t="n"/>
+      <c r="AR20" s="374" t="n"/>
+      <c r="AS20" s="413" t="n"/>
+      <c r="AT20" s="413" t="n"/>
+      <c r="AU20" s="413" t="n"/>
+      <c r="AV20" s="413" t="n"/>
+      <c r="AW20" s="414" t="n"/>
+      <c r="AX20" s="374" t="n"/>
+      <c r="AY20" s="413" t="n"/>
+      <c r="AZ20" s="413" t="n"/>
+      <c r="BA20" s="414" t="n"/>
+      <c r="BB20" s="376" t="n"/>
+      <c r="BC20" s="413" t="n"/>
+      <c r="BD20" s="414" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="298">
+      <c r="A21" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B21" s="276" t="n"/>
-      <c r="C21" s="277" t="n"/>
-      <c r="D21" s="299" t="inlineStr">
+      <c r="B21" s="411" t="n"/>
+      <c r="C21" s="412" t="n"/>
+      <c r="D21" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="328" t="n"/>
-      <c r="F21" s="328" t="n"/>
-      <c r="G21" s="329" t="n"/>
-      <c r="H21" s="300" t="n"/>
-      <c r="I21" s="328" t="n"/>
-      <c r="J21" s="328" t="n"/>
-      <c r="K21" s="328" t="n"/>
-      <c r="L21" s="328" t="n"/>
-      <c r="M21" s="328" t="n"/>
-      <c r="N21" s="328" t="n"/>
-      <c r="O21" s="328" t="n"/>
-      <c r="P21" s="328" t="n"/>
-      <c r="Q21" s="328" t="n"/>
-      <c r="R21" s="328" t="n"/>
-      <c r="S21" s="328" t="n"/>
-      <c r="T21" s="328" t="n"/>
-      <c r="U21" s="328" t="n"/>
-      <c r="V21" s="328" t="n"/>
-      <c r="W21" s="328" t="n"/>
-      <c r="X21" s="328" t="n"/>
-      <c r="Y21" s="328" t="n"/>
-      <c r="Z21" s="329" t="n"/>
-      <c r="AA21" s="301" t="n"/>
-      <c r="AB21" s="328" t="n"/>
-      <c r="AC21" s="328" t="n"/>
-      <c r="AD21" s="328" t="n"/>
-      <c r="AE21" s="328" t="n"/>
-      <c r="AF21" s="328" t="n"/>
-      <c r="AG21" s="328" t="n"/>
-      <c r="AH21" s="328" t="n"/>
-      <c r="AI21" s="328" t="n"/>
-      <c r="AJ21" s="328" t="n"/>
-      <c r="AK21" s="328" t="n"/>
-      <c r="AL21" s="328" t="n"/>
-      <c r="AM21" s="328" t="n"/>
-      <c r="AN21" s="328" t="n"/>
-      <c r="AO21" s="328" t="n"/>
-      <c r="AP21" s="328" t="n"/>
-      <c r="AQ21" s="329" t="n"/>
-      <c r="AR21" s="300" t="n"/>
-      <c r="AS21" s="328" t="n"/>
-      <c r="AT21" s="328" t="n"/>
-      <c r="AU21" s="328" t="n"/>
-      <c r="AV21" s="328" t="n"/>
-      <c r="AW21" s="329" t="n"/>
-      <c r="AX21" s="300" t="n"/>
-      <c r="AY21" s="328" t="n"/>
-      <c r="AZ21" s="328" t="n"/>
-      <c r="BA21" s="329" t="n"/>
-      <c r="BB21" s="302" t="n"/>
-      <c r="BC21" s="328" t="n"/>
-      <c r="BD21" s="330" t="n"/>
+      <c r="E21" s="413" t="n"/>
+      <c r="F21" s="413" t="n"/>
+      <c r="G21" s="414" t="n"/>
+      <c r="H21" s="374" t="n"/>
+      <c r="I21" s="413" t="n"/>
+      <c r="J21" s="413" t="n"/>
+      <c r="K21" s="413" t="n"/>
+      <c r="L21" s="413" t="n"/>
+      <c r="M21" s="413" t="n"/>
+      <c r="N21" s="413" t="n"/>
+      <c r="O21" s="413" t="n"/>
+      <c r="P21" s="413" t="n"/>
+      <c r="Q21" s="413" t="n"/>
+      <c r="R21" s="413" t="n"/>
+      <c r="S21" s="413" t="n"/>
+      <c r="T21" s="413" t="n"/>
+      <c r="U21" s="413" t="n"/>
+      <c r="V21" s="413" t="n"/>
+      <c r="W21" s="413" t="n"/>
+      <c r="X21" s="413" t="n"/>
+      <c r="Y21" s="413" t="n"/>
+      <c r="Z21" s="414" t="n"/>
+      <c r="AA21" s="375" t="n"/>
+      <c r="AB21" s="413" t="n"/>
+      <c r="AC21" s="413" t="n"/>
+      <c r="AD21" s="413" t="n"/>
+      <c r="AE21" s="413" t="n"/>
+      <c r="AF21" s="413" t="n"/>
+      <c r="AG21" s="413" t="n"/>
+      <c r="AH21" s="413" t="n"/>
+      <c r="AI21" s="413" t="n"/>
+      <c r="AJ21" s="413" t="n"/>
+      <c r="AK21" s="413" t="n"/>
+      <c r="AL21" s="413" t="n"/>
+      <c r="AM21" s="413" t="n"/>
+      <c r="AN21" s="413" t="n"/>
+      <c r="AO21" s="413" t="n"/>
+      <c r="AP21" s="413" t="n"/>
+      <c r="AQ21" s="414" t="n"/>
+      <c r="AR21" s="374" t="n"/>
+      <c r="AS21" s="413" t="n"/>
+      <c r="AT21" s="413" t="n"/>
+      <c r="AU21" s="413" t="n"/>
+      <c r="AV21" s="413" t="n"/>
+      <c r="AW21" s="414" t="n"/>
+      <c r="AX21" s="374" t="n"/>
+      <c r="AY21" s="413" t="n"/>
+      <c r="AZ21" s="413" t="n"/>
+      <c r="BA21" s="414" t="n"/>
+      <c r="BB21" s="376" t="n"/>
+      <c r="BC21" s="413" t="n"/>
+      <c r="BD21" s="414" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="298">
+      <c r="A22" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B22" s="276" t="n"/>
-      <c r="C22" s="277" t="n"/>
-      <c r="D22" s="299" t="inlineStr">
+      <c r="B22" s="411" t="n"/>
+      <c r="C22" s="412" t="n"/>
+      <c r="D22" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="328" t="n"/>
-      <c r="F22" s="328" t="n"/>
-      <c r="G22" s="329" t="n"/>
-      <c r="H22" s="300" t="n"/>
-      <c r="I22" s="328" t="n"/>
-      <c r="J22" s="328" t="n"/>
-      <c r="K22" s="328" t="n"/>
-      <c r="L22" s="328" t="n"/>
-      <c r="M22" s="328" t="n"/>
-      <c r="N22" s="328" t="n"/>
-      <c r="O22" s="328" t="n"/>
-      <c r="P22" s="328" t="n"/>
-      <c r="Q22" s="328" t="n"/>
-      <c r="R22" s="328" t="n"/>
-      <c r="S22" s="328" t="n"/>
-      <c r="T22" s="328" t="n"/>
-      <c r="U22" s="328" t="n"/>
-      <c r="V22" s="328" t="n"/>
-      <c r="W22" s="328" t="n"/>
-      <c r="X22" s="328" t="n"/>
-      <c r="Y22" s="328" t="n"/>
-      <c r="Z22" s="329" t="n"/>
-      <c r="AA22" s="301" t="n"/>
-      <c r="AB22" s="328" t="n"/>
-      <c r="AC22" s="328" t="n"/>
-      <c r="AD22" s="328" t="n"/>
-      <c r="AE22" s="328" t="n"/>
-      <c r="AF22" s="328" t="n"/>
-      <c r="AG22" s="328" t="n"/>
-      <c r="AH22" s="328" t="n"/>
-      <c r="AI22" s="328" t="n"/>
-      <c r="AJ22" s="328" t="n"/>
-      <c r="AK22" s="328" t="n"/>
-      <c r="AL22" s="328" t="n"/>
-      <c r="AM22" s="328" t="n"/>
-      <c r="AN22" s="328" t="n"/>
-      <c r="AO22" s="328" t="n"/>
-      <c r="AP22" s="328" t="n"/>
-      <c r="AQ22" s="329" t="n"/>
-      <c r="AR22" s="300" t="n"/>
-      <c r="AS22" s="328" t="n"/>
-      <c r="AT22" s="328" t="n"/>
-      <c r="AU22" s="328" t="n"/>
-      <c r="AV22" s="328" t="n"/>
-      <c r="AW22" s="329" t="n"/>
-      <c r="AX22" s="300" t="n"/>
-      <c r="AY22" s="328" t="n"/>
-      <c r="AZ22" s="328" t="n"/>
-      <c r="BA22" s="329" t="n"/>
-      <c r="BB22" s="302" t="n"/>
-      <c r="BC22" s="328" t="n"/>
-      <c r="BD22" s="330" t="n"/>
+      <c r="E22" s="413" t="n"/>
+      <c r="F22" s="413" t="n"/>
+      <c r="G22" s="414" t="n"/>
+      <c r="H22" s="374" t="n"/>
+      <c r="I22" s="413" t="n"/>
+      <c r="J22" s="413" t="n"/>
+      <c r="K22" s="413" t="n"/>
+      <c r="L22" s="413" t="n"/>
+      <c r="M22" s="413" t="n"/>
+      <c r="N22" s="413" t="n"/>
+      <c r="O22" s="413" t="n"/>
+      <c r="P22" s="413" t="n"/>
+      <c r="Q22" s="413" t="n"/>
+      <c r="R22" s="413" t="n"/>
+      <c r="S22" s="413" t="n"/>
+      <c r="T22" s="413" t="n"/>
+      <c r="U22" s="413" t="n"/>
+      <c r="V22" s="413" t="n"/>
+      <c r="W22" s="413" t="n"/>
+      <c r="X22" s="413" t="n"/>
+      <c r="Y22" s="413" t="n"/>
+      <c r="Z22" s="414" t="n"/>
+      <c r="AA22" s="375" t="n"/>
+      <c r="AB22" s="413" t="n"/>
+      <c r="AC22" s="413" t="n"/>
+      <c r="AD22" s="413" t="n"/>
+      <c r="AE22" s="413" t="n"/>
+      <c r="AF22" s="413" t="n"/>
+      <c r="AG22" s="413" t="n"/>
+      <c r="AH22" s="413" t="n"/>
+      <c r="AI22" s="413" t="n"/>
+      <c r="AJ22" s="413" t="n"/>
+      <c r="AK22" s="413" t="n"/>
+      <c r="AL22" s="413" t="n"/>
+      <c r="AM22" s="413" t="n"/>
+      <c r="AN22" s="413" t="n"/>
+      <c r="AO22" s="413" t="n"/>
+      <c r="AP22" s="413" t="n"/>
+      <c r="AQ22" s="414" t="n"/>
+      <c r="AR22" s="374" t="n"/>
+      <c r="AS22" s="413" t="n"/>
+      <c r="AT22" s="413" t="n"/>
+      <c r="AU22" s="413" t="n"/>
+      <c r="AV22" s="413" t="n"/>
+      <c r="AW22" s="414" t="n"/>
+      <c r="AX22" s="374" t="n"/>
+      <c r="AY22" s="413" t="n"/>
+      <c r="AZ22" s="413" t="n"/>
+      <c r="BA22" s="414" t="n"/>
+      <c r="BB22" s="376" t="n"/>
+      <c r="BC22" s="413" t="n"/>
+      <c r="BD22" s="414" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="298">
+      <c r="A23" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B23" s="276" t="n"/>
-      <c r="C23" s="277" t="n"/>
-      <c r="D23" s="299" t="inlineStr">
+      <c r="B23" s="411" t="n"/>
+      <c r="C23" s="412" t="n"/>
+      <c r="D23" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="328" t="n"/>
-      <c r="F23" s="328" t="n"/>
-      <c r="G23" s="329" t="n"/>
-      <c r="H23" s="300" t="n"/>
-      <c r="I23" s="328" t="n"/>
-      <c r="J23" s="328" t="n"/>
-      <c r="K23" s="328" t="n"/>
-      <c r="L23" s="328" t="n"/>
-      <c r="M23" s="328" t="n"/>
-      <c r="N23" s="328" t="n"/>
-      <c r="O23" s="328" t="n"/>
-      <c r="P23" s="328" t="n"/>
-      <c r="Q23" s="328" t="n"/>
-      <c r="R23" s="328" t="n"/>
-      <c r="S23" s="328" t="n"/>
-      <c r="T23" s="328" t="n"/>
-      <c r="U23" s="328" t="n"/>
-      <c r="V23" s="328" t="n"/>
-      <c r="W23" s="328" t="n"/>
-      <c r="X23" s="328" t="n"/>
-      <c r="Y23" s="328" t="n"/>
-      <c r="Z23" s="329" t="n"/>
-      <c r="AA23" s="301" t="n"/>
-      <c r="AB23" s="328" t="n"/>
-      <c r="AC23" s="328" t="n"/>
-      <c r="AD23" s="328" t="n"/>
-      <c r="AE23" s="328" t="n"/>
-      <c r="AF23" s="328" t="n"/>
-      <c r="AG23" s="328" t="n"/>
-      <c r="AH23" s="328" t="n"/>
-      <c r="AI23" s="328" t="n"/>
-      <c r="AJ23" s="328" t="n"/>
-      <c r="AK23" s="328" t="n"/>
-      <c r="AL23" s="328" t="n"/>
-      <c r="AM23" s="328" t="n"/>
-      <c r="AN23" s="328" t="n"/>
-      <c r="AO23" s="328" t="n"/>
-      <c r="AP23" s="328" t="n"/>
-      <c r="AQ23" s="329" t="n"/>
-      <c r="AR23" s="300" t="n"/>
-      <c r="AS23" s="328" t="n"/>
-      <c r="AT23" s="328" t="n"/>
-      <c r="AU23" s="328" t="n"/>
-      <c r="AV23" s="328" t="n"/>
-      <c r="AW23" s="329" t="n"/>
-      <c r="AX23" s="300" t="n"/>
-      <c r="AY23" s="328" t="n"/>
-      <c r="AZ23" s="328" t="n"/>
-      <c r="BA23" s="329" t="n"/>
-      <c r="BB23" s="302" t="n"/>
-      <c r="BC23" s="328" t="n"/>
-      <c r="BD23" s="330" t="n"/>
+      <c r="E23" s="413" t="n"/>
+      <c r="F23" s="413" t="n"/>
+      <c r="G23" s="414" t="n"/>
+      <c r="H23" s="374" t="n"/>
+      <c r="I23" s="413" t="n"/>
+      <c r="J23" s="413" t="n"/>
+      <c r="K23" s="413" t="n"/>
+      <c r="L23" s="413" t="n"/>
+      <c r="M23" s="413" t="n"/>
+      <c r="N23" s="413" t="n"/>
+      <c r="O23" s="413" t="n"/>
+      <c r="P23" s="413" t="n"/>
+      <c r="Q23" s="413" t="n"/>
+      <c r="R23" s="413" t="n"/>
+      <c r="S23" s="413" t="n"/>
+      <c r="T23" s="413" t="n"/>
+      <c r="U23" s="413" t="n"/>
+      <c r="V23" s="413" t="n"/>
+      <c r="W23" s="413" t="n"/>
+      <c r="X23" s="413" t="n"/>
+      <c r="Y23" s="413" t="n"/>
+      <c r="Z23" s="414" t="n"/>
+      <c r="AA23" s="375" t="n"/>
+      <c r="AB23" s="413" t="n"/>
+      <c r="AC23" s="413" t="n"/>
+      <c r="AD23" s="413" t="n"/>
+      <c r="AE23" s="413" t="n"/>
+      <c r="AF23" s="413" t="n"/>
+      <c r="AG23" s="413" t="n"/>
+      <c r="AH23" s="413" t="n"/>
+      <c r="AI23" s="413" t="n"/>
+      <c r="AJ23" s="413" t="n"/>
+      <c r="AK23" s="413" t="n"/>
+      <c r="AL23" s="413" t="n"/>
+      <c r="AM23" s="413" t="n"/>
+      <c r="AN23" s="413" t="n"/>
+      <c r="AO23" s="413" t="n"/>
+      <c r="AP23" s="413" t="n"/>
+      <c r="AQ23" s="414" t="n"/>
+      <c r="AR23" s="374" t="n"/>
+      <c r="AS23" s="413" t="n"/>
+      <c r="AT23" s="413" t="n"/>
+      <c r="AU23" s="413" t="n"/>
+      <c r="AV23" s="413" t="n"/>
+      <c r="AW23" s="414" t="n"/>
+      <c r="AX23" s="374" t="n"/>
+      <c r="AY23" s="413" t="n"/>
+      <c r="AZ23" s="413" t="n"/>
+      <c r="BA23" s="414" t="n"/>
+      <c r="BB23" s="376" t="n"/>
+      <c r="BC23" s="413" t="n"/>
+      <c r="BD23" s="414" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="298">
+      <c r="A24" s="368">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B24" s="276" t="n"/>
-      <c r="C24" s="277" t="n"/>
-      <c r="D24" s="299" t="inlineStr">
+      <c r="B24" s="411" t="n"/>
+      <c r="C24" s="412" t="n"/>
+      <c r="D24" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="328" t="n"/>
-      <c r="F24" s="328" t="n"/>
-      <c r="G24" s="329" t="n"/>
-      <c r="H24" s="300" t="n"/>
-      <c r="I24" s="328" t="n"/>
-      <c r="J24" s="328" t="n"/>
-      <c r="K24" s="328" t="n"/>
-      <c r="L24" s="328" t="n"/>
-      <c r="M24" s="328" t="n"/>
-      <c r="N24" s="328" t="n"/>
-      <c r="O24" s="328" t="n"/>
-      <c r="P24" s="328" t="n"/>
-      <c r="Q24" s="328" t="n"/>
-      <c r="R24" s="328" t="n"/>
-      <c r="S24" s="328" t="n"/>
-      <c r="T24" s="328" t="n"/>
-      <c r="U24" s="328" t="n"/>
-      <c r="V24" s="328" t="n"/>
-      <c r="W24" s="328" t="n"/>
-      <c r="X24" s="328" t="n"/>
-      <c r="Y24" s="328" t="n"/>
-      <c r="Z24" s="329" t="n"/>
-      <c r="AA24" s="301" t="n"/>
-      <c r="AB24" s="328" t="n"/>
-      <c r="AC24" s="328" t="n"/>
-      <c r="AD24" s="328" t="n"/>
-      <c r="AE24" s="328" t="n"/>
-      <c r="AF24" s="328" t="n"/>
-      <c r="AG24" s="328" t="n"/>
-      <c r="AH24" s="328" t="n"/>
-      <c r="AI24" s="328" t="n"/>
-      <c r="AJ24" s="328" t="n"/>
-      <c r="AK24" s="328" t="n"/>
-      <c r="AL24" s="328" t="n"/>
-      <c r="AM24" s="328" t="n"/>
-      <c r="AN24" s="328" t="n"/>
-      <c r="AO24" s="328" t="n"/>
-      <c r="AP24" s="328" t="n"/>
-      <c r="AQ24" s="329" t="n"/>
-      <c r="AR24" s="300" t="n"/>
-      <c r="AS24" s="328" t="n"/>
-      <c r="AT24" s="328" t="n"/>
-      <c r="AU24" s="328" t="n"/>
-      <c r="AV24" s="328" t="n"/>
-      <c r="AW24" s="329" t="n"/>
-      <c r="AX24" s="300" t="n"/>
-      <c r="AY24" s="328" t="n"/>
-      <c r="AZ24" s="328" t="n"/>
-      <c r="BA24" s="329" t="n"/>
-      <c r="BB24" s="302" t="n"/>
-      <c r="BC24" s="328" t="n"/>
-      <c r="BD24" s="330" t="n"/>
+      <c r="E24" s="413" t="n"/>
+      <c r="F24" s="413" t="n"/>
+      <c r="G24" s="414" t="n"/>
+      <c r="H24" s="374" t="n"/>
+      <c r="I24" s="413" t="n"/>
+      <c r="J24" s="413" t="n"/>
+      <c r="K24" s="413" t="n"/>
+      <c r="L24" s="413" t="n"/>
+      <c r="M24" s="413" t="n"/>
+      <c r="N24" s="413" t="n"/>
+      <c r="O24" s="413" t="n"/>
+      <c r="P24" s="413" t="n"/>
+      <c r="Q24" s="413" t="n"/>
+      <c r="R24" s="413" t="n"/>
+      <c r="S24" s="413" t="n"/>
+      <c r="T24" s="413" t="n"/>
+      <c r="U24" s="413" t="n"/>
+      <c r="V24" s="413" t="n"/>
+      <c r="W24" s="413" t="n"/>
+      <c r="X24" s="413" t="n"/>
+      <c r="Y24" s="413" t="n"/>
+      <c r="Z24" s="414" t="n"/>
+      <c r="AA24" s="375" t="n"/>
+      <c r="AB24" s="413" t="n"/>
+      <c r="AC24" s="413" t="n"/>
+      <c r="AD24" s="413" t="n"/>
+      <c r="AE24" s="413" t="n"/>
+      <c r="AF24" s="413" t="n"/>
+      <c r="AG24" s="413" t="n"/>
+      <c r="AH24" s="413" t="n"/>
+      <c r="AI24" s="413" t="n"/>
+      <c r="AJ24" s="413" t="n"/>
+      <c r="AK24" s="413" t="n"/>
+      <c r="AL24" s="413" t="n"/>
+      <c r="AM24" s="413" t="n"/>
+      <c r="AN24" s="413" t="n"/>
+      <c r="AO24" s="413" t="n"/>
+      <c r="AP24" s="413" t="n"/>
+      <c r="AQ24" s="414" t="n"/>
+      <c r="AR24" s="374" t="n"/>
+      <c r="AS24" s="413" t="n"/>
+      <c r="AT24" s="413" t="n"/>
+      <c r="AU24" s="413" t="n"/>
+      <c r="AV24" s="413" t="n"/>
+      <c r="AW24" s="414" t="n"/>
+      <c r="AX24" s="374" t="n"/>
+      <c r="AY24" s="413" t="n"/>
+      <c r="AZ24" s="413" t="n"/>
+      <c r="BA24" s="414" t="n"/>
+      <c r="BB24" s="376" t="n"/>
+      <c r="BC24" s="413" t="n"/>
+      <c r="BD24" s="414" t="n"/>
     </row>
     <row r="25" ht="4" customHeight="1">
-      <c r="A25" s="298" t="n"/>
-      <c r="D25" s="303" t="n"/>
-      <c r="H25" s="304" t="n"/>
-      <c r="AA25" s="305" t="n"/>
-      <c r="AR25" s="306" t="n"/>
-      <c r="AX25" s="306" t="n"/>
-      <c r="BB25" s="307" t="n"/>
+      <c r="A25" s="377" t="n"/>
+      <c r="B25" s="353" t="n"/>
+      <c r="C25" s="353" t="n"/>
+      <c r="D25" s="378" t="n"/>
+      <c r="E25" s="353" t="n"/>
+      <c r="F25" s="353" t="n"/>
+      <c r="G25" s="353" t="n"/>
+      <c r="H25" s="365" t="n"/>
+      <c r="I25" s="353" t="n"/>
+      <c r="J25" s="353" t="n"/>
+      <c r="K25" s="353" t="n"/>
+      <c r="L25" s="353" t="n"/>
+      <c r="M25" s="353" t="n"/>
+      <c r="N25" s="353" t="n"/>
+      <c r="O25" s="353" t="n"/>
+      <c r="P25" s="353" t="n"/>
+      <c r="Q25" s="353" t="n"/>
+      <c r="R25" s="353" t="n"/>
+      <c r="S25" s="353" t="n"/>
+      <c r="T25" s="353" t="n"/>
+      <c r="U25" s="353" t="n"/>
+      <c r="V25" s="353" t="n"/>
+      <c r="W25" s="353" t="n"/>
+      <c r="X25" s="353" t="n"/>
+      <c r="Y25" s="353" t="n"/>
+      <c r="Z25" s="353" t="n"/>
+      <c r="AA25" s="379" t="n"/>
+      <c r="AB25" s="353" t="n"/>
+      <c r="AC25" s="353" t="n"/>
+      <c r="AD25" s="353" t="n"/>
+      <c r="AE25" s="353" t="n"/>
+      <c r="AF25" s="353" t="n"/>
+      <c r="AG25" s="353" t="n"/>
+      <c r="AH25" s="353" t="n"/>
+      <c r="AI25" s="353" t="n"/>
+      <c r="AJ25" s="353" t="n"/>
+      <c r="AK25" s="353" t="n"/>
+      <c r="AL25" s="353" t="n"/>
+      <c r="AM25" s="353" t="n"/>
+      <c r="AN25" s="353" t="n"/>
+      <c r="AO25" s="353" t="n"/>
+      <c r="AP25" s="353" t="n"/>
+      <c r="AQ25" s="353" t="n"/>
+      <c r="AR25" s="380" t="n"/>
+      <c r="AS25" s="353" t="n"/>
+      <c r="AT25" s="353" t="n"/>
+      <c r="AU25" s="353" t="n"/>
+      <c r="AV25" s="353" t="n"/>
+      <c r="AW25" s="353" t="n"/>
+      <c r="AX25" s="380" t="n"/>
+      <c r="AY25" s="353" t="n"/>
+      <c r="AZ25" s="353" t="n"/>
+      <c r="BA25" s="353" t="n"/>
+      <c r="BB25" s="381" t="n"/>
+      <c r="BC25" s="353" t="n"/>
+      <c r="BD25" s="353" t="n"/>
     </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="284" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B26" s="285" t="n"/>
-      <c r="C26" s="285" t="n"/>
-      <c r="D26" s="285" t="n"/>
-      <c r="E26" s="285" t="n"/>
-      <c r="F26" s="285" t="n"/>
-      <c r="G26" s="285" t="n"/>
-      <c r="H26" s="285" t="n"/>
-      <c r="I26" s="285" t="n"/>
-      <c r="J26" s="285" t="n"/>
-      <c r="K26" s="285" t="n"/>
-      <c r="L26" s="285" t="n"/>
-      <c r="M26" s="285" t="n"/>
-      <c r="N26" s="285" t="n"/>
-      <c r="O26" s="285" t="n"/>
-      <c r="P26" s="285" t="n"/>
-      <c r="Q26" s="285" t="n"/>
-      <c r="R26" s="285" t="n"/>
-      <c r="S26" s="285" t="n"/>
-      <c r="T26" s="285" t="n"/>
-      <c r="U26" s="285" t="n"/>
-      <c r="V26" s="285" t="n"/>
-      <c r="W26" s="285" t="n"/>
-      <c r="X26" s="285" t="n"/>
-      <c r="Y26" s="285" t="n"/>
-      <c r="Z26" s="285" t="n"/>
-      <c r="AA26" s="285" t="n"/>
-      <c r="AB26" s="285" t="n"/>
-      <c r="AC26" s="285" t="n"/>
-      <c r="AD26" s="285" t="n"/>
-      <c r="AE26" s="285" t="n"/>
-      <c r="AF26" s="285" t="n"/>
-      <c r="AG26" s="285" t="n"/>
-      <c r="AH26" s="285" t="n"/>
-      <c r="AI26" s="285" t="n"/>
-      <c r="AJ26" s="285" t="n"/>
-      <c r="AK26" s="285" t="n"/>
-      <c r="AL26" s="285" t="n"/>
-      <c r="AM26" s="285" t="n"/>
-      <c r="AN26" s="285" t="n"/>
-      <c r="AO26" s="285" t="n"/>
-      <c r="AP26" s="285" t="n"/>
-      <c r="AQ26" s="285" t="n"/>
-      <c r="AR26" s="285" t="n"/>
-      <c r="AS26" s="285" t="n"/>
-      <c r="AT26" s="285" t="n"/>
-      <c r="AU26" s="285" t="n"/>
-      <c r="AV26" s="285" t="n"/>
-      <c r="AW26" s="285" t="n"/>
-      <c r="AX26" s="285" t="n"/>
-      <c r="AY26" s="285" t="n"/>
-      <c r="AZ26" s="285" t="n"/>
-      <c r="BA26" s="285" t="n"/>
-      <c r="BB26" s="285" t="n"/>
-      <c r="BC26" s="285" t="n"/>
-      <c r="BD26" s="286" t="n"/>
+      <c r="B26" s="405" t="n"/>
+      <c r="C26" s="405" t="n"/>
+      <c r="D26" s="405" t="n"/>
+      <c r="E26" s="405" t="n"/>
+      <c r="F26" s="405" t="n"/>
+      <c r="G26" s="405" t="n"/>
+      <c r="H26" s="405" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="405" t="n"/>
+      <c r="K26" s="405" t="n"/>
+      <c r="L26" s="405" t="n"/>
+      <c r="M26" s="405" t="n"/>
+      <c r="N26" s="405" t="n"/>
+      <c r="O26" s="405" t="n"/>
+      <c r="P26" s="405" t="n"/>
+      <c r="Q26" s="405" t="n"/>
+      <c r="R26" s="405" t="n"/>
+      <c r="S26" s="405" t="n"/>
+      <c r="T26" s="405" t="n"/>
+      <c r="U26" s="405" t="n"/>
+      <c r="V26" s="405" t="n"/>
+      <c r="W26" s="405" t="n"/>
+      <c r="X26" s="405" t="n"/>
+      <c r="Y26" s="405" t="n"/>
+      <c r="Z26" s="405" t="n"/>
+      <c r="AA26" s="405" t="n"/>
+      <c r="AB26" s="405" t="n"/>
+      <c r="AC26" s="405" t="n"/>
+      <c r="AD26" s="405" t="n"/>
+      <c r="AE26" s="405" t="n"/>
+      <c r="AF26" s="405" t="n"/>
+      <c r="AG26" s="405" t="n"/>
+      <c r="AH26" s="405" t="n"/>
+      <c r="AI26" s="405" t="n"/>
+      <c r="AJ26" s="405" t="n"/>
+      <c r="AK26" s="405" t="n"/>
+      <c r="AL26" s="405" t="n"/>
+      <c r="AM26" s="405" t="n"/>
+      <c r="AN26" s="405" t="n"/>
+      <c r="AO26" s="405" t="n"/>
+      <c r="AP26" s="405" t="n"/>
+      <c r="AQ26" s="405" t="n"/>
+      <c r="AR26" s="405" t="n"/>
+      <c r="AS26" s="405" t="n"/>
+      <c r="AT26" s="405" t="n"/>
+      <c r="AU26" s="405" t="n"/>
+      <c r="AV26" s="405" t="n"/>
+      <c r="AW26" s="405" t="n"/>
+      <c r="AX26" s="405" t="n"/>
+      <c r="AY26" s="405" t="n"/>
+      <c r="AZ26" s="405" t="n"/>
+      <c r="BA26" s="405" t="n"/>
+      <c r="BB26" s="405" t="n"/>
+      <c r="BC26" s="405" t="n"/>
+      <c r="BD26" s="406" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="287" t="inlineStr">
+      <c r="A27" s="355" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="B27" s="271" t="n"/>
-      <c r="C27" s="271" t="n"/>
-      <c r="D27" s="271" t="n"/>
-      <c r="E27" s="271" t="n"/>
-      <c r="F27" s="271" t="n"/>
-      <c r="G27" s="271" t="n"/>
-      <c r="H27" s="271" t="n"/>
-      <c r="I27" s="271" t="n"/>
-      <c r="J27" s="272" t="n"/>
-      <c r="K27" s="288" t="n"/>
-      <c r="L27" s="325" t="n"/>
-      <c r="M27" s="325" t="n"/>
-      <c r="N27" s="325" t="n"/>
-      <c r="O27" s="325" t="n"/>
-      <c r="P27" s="325" t="n"/>
-      <c r="Q27" s="325" t="n"/>
-      <c r="R27" s="325" t="n"/>
-      <c r="S27" s="325" t="n"/>
-      <c r="T27" s="325" t="n"/>
-      <c r="U27" s="325" t="n"/>
-      <c r="V27" s="325" t="n"/>
-      <c r="W27" s="325" t="n"/>
-      <c r="X27" s="325" t="n"/>
-      <c r="Y27" s="325" t="n"/>
-      <c r="Z27" s="325" t="n"/>
-      <c r="AA27" s="325" t="n"/>
-      <c r="AB27" s="326" t="n"/>
-      <c r="AC27" s="289" t="inlineStr">
+      <c r="B27" s="405" t="n"/>
+      <c r="C27" s="405" t="n"/>
+      <c r="D27" s="405" t="n"/>
+      <c r="E27" s="405" t="n"/>
+      <c r="F27" s="405" t="n"/>
+      <c r="G27" s="405" t="n"/>
+      <c r="H27" s="405" t="n"/>
+      <c r="I27" s="405" t="n"/>
+      <c r="J27" s="406" t="n"/>
+      <c r="K27" s="358" t="n"/>
+      <c r="L27" s="407" t="n"/>
+      <c r="M27" s="407" t="n"/>
+      <c r="N27" s="407" t="n"/>
+      <c r="O27" s="407" t="n"/>
+      <c r="P27" s="407" t="n"/>
+      <c r="Q27" s="407" t="n"/>
+      <c r="R27" s="407" t="n"/>
+      <c r="S27" s="407" t="n"/>
+      <c r="T27" s="407" t="n"/>
+      <c r="U27" s="407" t="n"/>
+      <c r="V27" s="407" t="n"/>
+      <c r="W27" s="407" t="n"/>
+      <c r="X27" s="407" t="n"/>
+      <c r="Y27" s="407" t="n"/>
+      <c r="Z27" s="407" t="n"/>
+      <c r="AA27" s="407" t="n"/>
+      <c r="AB27" s="408" t="n"/>
+      <c r="AC27" s="361" t="inlineStr">
         <is>
           <t>AQL Disposition</t>
         </is>
       </c>
-      <c r="AD27" s="271" t="n"/>
-      <c r="AE27" s="271" t="n"/>
-      <c r="AF27" s="271" t="n"/>
-      <c r="AG27" s="271" t="n"/>
-      <c r="AH27" s="271" t="n"/>
-      <c r="AI27" s="271" t="n"/>
-      <c r="AJ27" s="271" t="n"/>
-      <c r="AK27" s="271" t="n"/>
-      <c r="AL27" s="272" t="n"/>
-      <c r="AM27" s="290" t="n"/>
-      <c r="AN27" s="325" t="n"/>
-      <c r="AO27" s="325" t="n"/>
-      <c r="AP27" s="325" t="n"/>
-      <c r="AQ27" s="325" t="n"/>
-      <c r="AR27" s="325" t="n"/>
-      <c r="AS27" s="325" t="n"/>
-      <c r="AT27" s="325" t="n"/>
-      <c r="AU27" s="325" t="n"/>
-      <c r="AV27" s="325" t="n"/>
-      <c r="AW27" s="325" t="n"/>
-      <c r="AX27" s="325" t="n"/>
-      <c r="AY27" s="325" t="n"/>
-      <c r="AZ27" s="325" t="n"/>
-      <c r="BA27" s="325" t="n"/>
-      <c r="BB27" s="325" t="n"/>
-      <c r="BC27" s="325" t="n"/>
-      <c r="BD27" s="327" t="n"/>
+      <c r="AD27" s="405" t="n"/>
+      <c r="AE27" s="405" t="n"/>
+      <c r="AF27" s="405" t="n"/>
+      <c r="AG27" s="405" t="n"/>
+      <c r="AH27" s="405" t="n"/>
+      <c r="AI27" s="405" t="n"/>
+      <c r="AJ27" s="405" t="n"/>
+      <c r="AK27" s="405" t="n"/>
+      <c r="AL27" s="406" t="n"/>
+      <c r="AM27" s="358" t="n"/>
+      <c r="AN27" s="407" t="n"/>
+      <c r="AO27" s="407" t="n"/>
+      <c r="AP27" s="407" t="n"/>
+      <c r="AQ27" s="407" t="n"/>
+      <c r="AR27" s="407" t="n"/>
+      <c r="AS27" s="407" t="n"/>
+      <c r="AT27" s="407" t="n"/>
+      <c r="AU27" s="407" t="n"/>
+      <c r="AV27" s="407" t="n"/>
+      <c r="AW27" s="407" t="n"/>
+      <c r="AX27" s="407" t="n"/>
+      <c r="AY27" s="407" t="n"/>
+      <c r="AZ27" s="407" t="n"/>
+      <c r="BA27" s="407" t="n"/>
+      <c r="BB27" s="407" t="n"/>
+      <c r="BC27" s="407" t="n"/>
+      <c r="BD27" s="408" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="287" t="inlineStr">
+      <c r="A28" s="355" t="inlineStr">
         <is>
           <t>100% Sort Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B28" s="271" t="n"/>
-      <c r="C28" s="271" t="n"/>
-      <c r="D28" s="271" t="n"/>
-      <c r="E28" s="271" t="n"/>
-      <c r="F28" s="271" t="n"/>
-      <c r="G28" s="271" t="n"/>
-      <c r="H28" s="271" t="n"/>
-      <c r="I28" s="271" t="n"/>
-      <c r="J28" s="272" t="n"/>
-      <c r="K28" s="288" t="n"/>
-      <c r="L28" s="325" t="n"/>
-      <c r="M28" s="325" t="n"/>
-      <c r="N28" s="325" t="n"/>
-      <c r="O28" s="325" t="n"/>
-      <c r="P28" s="325" t="n"/>
-      <c r="Q28" s="325" t="n"/>
-      <c r="R28" s="325" t="n"/>
-      <c r="S28" s="325" t="n"/>
-      <c r="T28" s="325" t="n"/>
-      <c r="U28" s="325" t="n"/>
-      <c r="V28" s="325" t="n"/>
-      <c r="W28" s="325" t="n"/>
-      <c r="X28" s="325" t="n"/>
-      <c r="Y28" s="325" t="n"/>
-      <c r="Z28" s="325" t="n"/>
-      <c r="AA28" s="325" t="n"/>
-      <c r="AB28" s="326" t="n"/>
-      <c r="AC28" s="289" t="inlineStr">
+      <c r="B28" s="405" t="n"/>
+      <c r="C28" s="405" t="n"/>
+      <c r="D28" s="405" t="n"/>
+      <c r="E28" s="405" t="n"/>
+      <c r="F28" s="405" t="n"/>
+      <c r="G28" s="405" t="n"/>
+      <c r="H28" s="405" t="n"/>
+      <c r="I28" s="405" t="n"/>
+      <c r="J28" s="406" t="n"/>
+      <c r="K28" s="358" t="n"/>
+      <c r="L28" s="407" t="n"/>
+      <c r="M28" s="407" t="n"/>
+      <c r="N28" s="407" t="n"/>
+      <c r="O28" s="407" t="n"/>
+      <c r="P28" s="407" t="n"/>
+      <c r="Q28" s="407" t="n"/>
+      <c r="R28" s="407" t="n"/>
+      <c r="S28" s="407" t="n"/>
+      <c r="T28" s="407" t="n"/>
+      <c r="U28" s="407" t="n"/>
+      <c r="V28" s="407" t="n"/>
+      <c r="W28" s="407" t="n"/>
+      <c r="X28" s="407" t="n"/>
+      <c r="Y28" s="407" t="n"/>
+      <c r="Z28" s="407" t="n"/>
+      <c r="AA28" s="407" t="n"/>
+      <c r="AB28" s="408" t="n"/>
+      <c r="AC28" s="361" t="inlineStr">
         <is>
           <t>Linked NCR Ref</t>
         </is>
       </c>
-      <c r="AD28" s="271" t="n"/>
-      <c r="AE28" s="271" t="n"/>
-      <c r="AF28" s="271" t="n"/>
-      <c r="AG28" s="271" t="n"/>
-      <c r="AH28" s="271" t="n"/>
-      <c r="AI28" s="271" t="n"/>
-      <c r="AJ28" s="271" t="n"/>
-      <c r="AK28" s="271" t="n"/>
-      <c r="AL28" s="272" t="n"/>
-      <c r="AM28" s="290" t="n"/>
-      <c r="AN28" s="325" t="n"/>
-      <c r="AO28" s="325" t="n"/>
-      <c r="AP28" s="325" t="n"/>
-      <c r="AQ28" s="325" t="n"/>
-      <c r="AR28" s="325" t="n"/>
-      <c r="AS28" s="325" t="n"/>
-      <c r="AT28" s="325" t="n"/>
-      <c r="AU28" s="325" t="n"/>
-      <c r="AV28" s="325" t="n"/>
-      <c r="AW28" s="325" t="n"/>
-      <c r="AX28" s="325" t="n"/>
-      <c r="AY28" s="325" t="n"/>
-      <c r="AZ28" s="325" t="n"/>
-      <c r="BA28" s="325" t="n"/>
-      <c r="BB28" s="325" t="n"/>
-      <c r="BC28" s="325" t="n"/>
-      <c r="BD28" s="327" t="n"/>
+      <c r="AD28" s="405" t="n"/>
+      <c r="AE28" s="405" t="n"/>
+      <c r="AF28" s="405" t="n"/>
+      <c r="AG28" s="405" t="n"/>
+      <c r="AH28" s="405" t="n"/>
+      <c r="AI28" s="405" t="n"/>
+      <c r="AJ28" s="405" t="n"/>
+      <c r="AK28" s="405" t="n"/>
+      <c r="AL28" s="406" t="n"/>
+      <c r="AM28" s="358" t="n"/>
+      <c r="AN28" s="407" t="n"/>
+      <c r="AO28" s="407" t="n"/>
+      <c r="AP28" s="407" t="n"/>
+      <c r="AQ28" s="407" t="n"/>
+      <c r="AR28" s="407" t="n"/>
+      <c r="AS28" s="407" t="n"/>
+      <c r="AT28" s="407" t="n"/>
+      <c r="AU28" s="407" t="n"/>
+      <c r="AV28" s="407" t="n"/>
+      <c r="AW28" s="407" t="n"/>
+      <c r="AX28" s="407" t="n"/>
+      <c r="AY28" s="407" t="n"/>
+      <c r="AZ28" s="407" t="n"/>
+      <c r="BA28" s="407" t="n"/>
+      <c r="BB28" s="407" t="n"/>
+      <c r="BC28" s="407" t="n"/>
+      <c r="BD28" s="408" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="287" t="inlineStr">
+      <c r="A29" s="355" t="inlineStr">
         <is>
           <t>Lot Release Decision</t>
         </is>
       </c>
-      <c r="B29" s="271" t="n"/>
-      <c r="C29" s="271" t="n"/>
-      <c r="D29" s="271" t="n"/>
-      <c r="E29" s="271" t="n"/>
-      <c r="F29" s="271" t="n"/>
-      <c r="G29" s="271" t="n"/>
-      <c r="H29" s="271" t="n"/>
-      <c r="I29" s="271" t="n"/>
-      <c r="J29" s="272" t="n"/>
-      <c r="K29" s="288" t="n"/>
-      <c r="L29" s="325" t="n"/>
-      <c r="M29" s="325" t="n"/>
-      <c r="N29" s="325" t="n"/>
-      <c r="O29" s="325" t="n"/>
-      <c r="P29" s="325" t="n"/>
-      <c r="Q29" s="325" t="n"/>
-      <c r="R29" s="325" t="n"/>
-      <c r="S29" s="325" t="n"/>
-      <c r="T29" s="325" t="n"/>
-      <c r="U29" s="325" t="n"/>
-      <c r="V29" s="325" t="n"/>
-      <c r="W29" s="325" t="n"/>
-      <c r="X29" s="325" t="n"/>
-      <c r="Y29" s="325" t="n"/>
-      <c r="Z29" s="325" t="n"/>
-      <c r="AA29" s="325" t="n"/>
-      <c r="AB29" s="326" t="n"/>
-      <c r="AC29" s="289" t="inlineStr">
+      <c r="B29" s="405" t="n"/>
+      <c r="C29" s="405" t="n"/>
+      <c r="D29" s="405" t="n"/>
+      <c r="E29" s="405" t="n"/>
+      <c r="F29" s="405" t="n"/>
+      <c r="G29" s="405" t="n"/>
+      <c r="H29" s="405" t="n"/>
+      <c r="I29" s="405" t="n"/>
+      <c r="J29" s="406" t="n"/>
+      <c r="K29" s="358" t="n"/>
+      <c r="L29" s="407" t="n"/>
+      <c r="M29" s="407" t="n"/>
+      <c r="N29" s="407" t="n"/>
+      <c r="O29" s="407" t="n"/>
+      <c r="P29" s="407" t="n"/>
+      <c r="Q29" s="407" t="n"/>
+      <c r="R29" s="407" t="n"/>
+      <c r="S29" s="407" t="n"/>
+      <c r="T29" s="407" t="n"/>
+      <c r="U29" s="407" t="n"/>
+      <c r="V29" s="407" t="n"/>
+      <c r="W29" s="407" t="n"/>
+      <c r="X29" s="407" t="n"/>
+      <c r="Y29" s="407" t="n"/>
+      <c r="Z29" s="407" t="n"/>
+      <c r="AA29" s="407" t="n"/>
+      <c r="AB29" s="408" t="n"/>
+      <c r="AC29" s="361" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="AD29" s="271" t="n"/>
-      <c r="AE29" s="271" t="n"/>
-      <c r="AF29" s="271" t="n"/>
-      <c r="AG29" s="271" t="n"/>
-      <c r="AH29" s="271" t="n"/>
-      <c r="AI29" s="271" t="n"/>
-      <c r="AJ29" s="271" t="n"/>
-      <c r="AK29" s="271" t="n"/>
-      <c r="AL29" s="272" t="n"/>
-      <c r="AM29" s="290" t="n"/>
-      <c r="AN29" s="325" t="n"/>
-      <c r="AO29" s="325" t="n"/>
-      <c r="AP29" s="325" t="n"/>
-      <c r="AQ29" s="325" t="n"/>
-      <c r="AR29" s="325" t="n"/>
-      <c r="AS29" s="325" t="n"/>
-      <c r="AT29" s="325" t="n"/>
-      <c r="AU29" s="325" t="n"/>
-      <c r="AV29" s="325" t="n"/>
-      <c r="AW29" s="325" t="n"/>
-      <c r="AX29" s="325" t="n"/>
-      <c r="AY29" s="325" t="n"/>
-      <c r="AZ29" s="325" t="n"/>
-      <c r="BA29" s="325" t="n"/>
-      <c r="BB29" s="325" t="n"/>
-      <c r="BC29" s="325" t="n"/>
-      <c r="BD29" s="327" t="n"/>
+      <c r="AD29" s="405" t="n"/>
+      <c r="AE29" s="405" t="n"/>
+      <c r="AF29" s="405" t="n"/>
+      <c r="AG29" s="405" t="n"/>
+      <c r="AH29" s="405" t="n"/>
+      <c r="AI29" s="405" t="n"/>
+      <c r="AJ29" s="405" t="n"/>
+      <c r="AK29" s="405" t="n"/>
+      <c r="AL29" s="406" t="n"/>
+      <c r="AM29" s="358" t="n"/>
+      <c r="AN29" s="407" t="n"/>
+      <c r="AO29" s="407" t="n"/>
+      <c r="AP29" s="407" t="n"/>
+      <c r="AQ29" s="407" t="n"/>
+      <c r="AR29" s="407" t="n"/>
+      <c r="AS29" s="407" t="n"/>
+      <c r="AT29" s="407" t="n"/>
+      <c r="AU29" s="407" t="n"/>
+      <c r="AV29" s="407" t="n"/>
+      <c r="AW29" s="407" t="n"/>
+      <c r="AX29" s="407" t="n"/>
+      <c r="AY29" s="407" t="n"/>
+      <c r="AZ29" s="407" t="n"/>
+      <c r="BA29" s="407" t="n"/>
+      <c r="BB29" s="407" t="n"/>
+      <c r="BC29" s="407" t="n"/>
+      <c r="BD29" s="408" t="n"/>
     </row>
     <row r="30" ht="4" customHeight="1">
-      <c r="A30" s="298" t="n"/>
-      <c r="D30" s="303" t="n"/>
-      <c r="H30" s="292" t="n"/>
-      <c r="AA30" s="305" t="n"/>
-      <c r="AR30" s="306" t="n"/>
-      <c r="AX30" s="306" t="n"/>
-      <c r="BB30" s="307" t="n"/>
+      <c r="A30" s="377" t="n"/>
+      <c r="B30" s="353" t="n"/>
+      <c r="C30" s="353" t="n"/>
+      <c r="D30" s="378" t="n"/>
+      <c r="E30" s="353" t="n"/>
+      <c r="F30" s="353" t="n"/>
+      <c r="G30" s="353" t="n"/>
+      <c r="H30" s="365" t="n"/>
+      <c r="I30" s="353" t="n"/>
+      <c r="J30" s="353" t="n"/>
+      <c r="K30" s="353" t="n"/>
+      <c r="L30" s="353" t="n"/>
+      <c r="M30" s="353" t="n"/>
+      <c r="N30" s="353" t="n"/>
+      <c r="O30" s="353" t="n"/>
+      <c r="P30" s="353" t="n"/>
+      <c r="Q30" s="353" t="n"/>
+      <c r="R30" s="353" t="n"/>
+      <c r="S30" s="353" t="n"/>
+      <c r="T30" s="353" t="n"/>
+      <c r="U30" s="353" t="n"/>
+      <c r="V30" s="353" t="n"/>
+      <c r="W30" s="353" t="n"/>
+      <c r="X30" s="353" t="n"/>
+      <c r="Y30" s="353" t="n"/>
+      <c r="Z30" s="353" t="n"/>
+      <c r="AA30" s="379" t="n"/>
+      <c r="AB30" s="353" t="n"/>
+      <c r="AC30" s="353" t="n"/>
+      <c r="AD30" s="353" t="n"/>
+      <c r="AE30" s="353" t="n"/>
+      <c r="AF30" s="353" t="n"/>
+      <c r="AG30" s="353" t="n"/>
+      <c r="AH30" s="353" t="n"/>
+      <c r="AI30" s="353" t="n"/>
+      <c r="AJ30" s="353" t="n"/>
+      <c r="AK30" s="353" t="n"/>
+      <c r="AL30" s="353" t="n"/>
+      <c r="AM30" s="353" t="n"/>
+      <c r="AN30" s="353" t="n"/>
+      <c r="AO30" s="353" t="n"/>
+      <c r="AP30" s="353" t="n"/>
+      <c r="AQ30" s="353" t="n"/>
+      <c r="AR30" s="380" t="n"/>
+      <c r="AS30" s="353" t="n"/>
+      <c r="AT30" s="353" t="n"/>
+      <c r="AU30" s="353" t="n"/>
+      <c r="AV30" s="353" t="n"/>
+      <c r="AW30" s="353" t="n"/>
+      <c r="AX30" s="380" t="n"/>
+      <c r="AY30" s="353" t="n"/>
+      <c r="AZ30" s="353" t="n"/>
+      <c r="BA30" s="353" t="n"/>
+      <c r="BB30" s="381" t="n"/>
+      <c r="BC30" s="353" t="n"/>
+      <c r="BD30" s="353" t="n"/>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="284" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B31" s="285" t="n"/>
-      <c r="C31" s="285" t="n"/>
-      <c r="D31" s="285" t="n"/>
-      <c r="E31" s="285" t="n"/>
-      <c r="F31" s="285" t="n"/>
-      <c r="G31" s="285" t="n"/>
-      <c r="H31" s="285" t="n"/>
-      <c r="I31" s="285" t="n"/>
-      <c r="J31" s="285" t="n"/>
-      <c r="K31" s="285" t="n"/>
-      <c r="L31" s="285" t="n"/>
-      <c r="M31" s="285" t="n"/>
-      <c r="N31" s="285" t="n"/>
-      <c r="O31" s="285" t="n"/>
-      <c r="P31" s="285" t="n"/>
-      <c r="Q31" s="285" t="n"/>
-      <c r="R31" s="285" t="n"/>
-      <c r="S31" s="285" t="n"/>
-      <c r="T31" s="285" t="n"/>
-      <c r="U31" s="285" t="n"/>
-      <c r="V31" s="285" t="n"/>
-      <c r="W31" s="285" t="n"/>
-      <c r="X31" s="285" t="n"/>
-      <c r="Y31" s="285" t="n"/>
-      <c r="Z31" s="285" t="n"/>
-      <c r="AA31" s="285" t="n"/>
-      <c r="AB31" s="285" t="n"/>
-      <c r="AC31" s="285" t="n"/>
-      <c r="AD31" s="285" t="n"/>
-      <c r="AE31" s="285" t="n"/>
-      <c r="AF31" s="285" t="n"/>
-      <c r="AG31" s="285" t="n"/>
-      <c r="AH31" s="285" t="n"/>
-      <c r="AI31" s="285" t="n"/>
-      <c r="AJ31" s="285" t="n"/>
-      <c r="AK31" s="285" t="n"/>
-      <c r="AL31" s="285" t="n"/>
-      <c r="AM31" s="285" t="n"/>
-      <c r="AN31" s="285" t="n"/>
-      <c r="AO31" s="285" t="n"/>
-      <c r="AP31" s="285" t="n"/>
-      <c r="AQ31" s="285" t="n"/>
-      <c r="AR31" s="285" t="n"/>
-      <c r="AS31" s="285" t="n"/>
-      <c r="AT31" s="285" t="n"/>
-      <c r="AU31" s="285" t="n"/>
-      <c r="AV31" s="285" t="n"/>
-      <c r="AW31" s="285" t="n"/>
-      <c r="AX31" s="285" t="n"/>
-      <c r="AY31" s="285" t="n"/>
-      <c r="AZ31" s="285" t="n"/>
-      <c r="BA31" s="285" t="n"/>
-      <c r="BB31" s="285" t="n"/>
-      <c r="BC31" s="285" t="n"/>
-      <c r="BD31" s="286" t="n"/>
+      <c r="B31" s="405" t="n"/>
+      <c r="C31" s="405" t="n"/>
+      <c r="D31" s="405" t="n"/>
+      <c r="E31" s="405" t="n"/>
+      <c r="F31" s="405" t="n"/>
+      <c r="G31" s="405" t="n"/>
+      <c r="H31" s="405" t="n"/>
+      <c r="I31" s="405" t="n"/>
+      <c r="J31" s="405" t="n"/>
+      <c r="K31" s="405" t="n"/>
+      <c r="L31" s="405" t="n"/>
+      <c r="M31" s="405" t="n"/>
+      <c r="N31" s="405" t="n"/>
+      <c r="O31" s="405" t="n"/>
+      <c r="P31" s="405" t="n"/>
+      <c r="Q31" s="405" t="n"/>
+      <c r="R31" s="405" t="n"/>
+      <c r="S31" s="405" t="n"/>
+      <c r="T31" s="405" t="n"/>
+      <c r="U31" s="405" t="n"/>
+      <c r="V31" s="405" t="n"/>
+      <c r="W31" s="405" t="n"/>
+      <c r="X31" s="405" t="n"/>
+      <c r="Y31" s="405" t="n"/>
+      <c r="Z31" s="405" t="n"/>
+      <c r="AA31" s="405" t="n"/>
+      <c r="AB31" s="405" t="n"/>
+      <c r="AC31" s="405" t="n"/>
+      <c r="AD31" s="405" t="n"/>
+      <c r="AE31" s="405" t="n"/>
+      <c r="AF31" s="405" t="n"/>
+      <c r="AG31" s="405" t="n"/>
+      <c r="AH31" s="405" t="n"/>
+      <c r="AI31" s="405" t="n"/>
+      <c r="AJ31" s="405" t="n"/>
+      <c r="AK31" s="405" t="n"/>
+      <c r="AL31" s="405" t="n"/>
+      <c r="AM31" s="405" t="n"/>
+      <c r="AN31" s="405" t="n"/>
+      <c r="AO31" s="405" t="n"/>
+      <c r="AP31" s="405" t="n"/>
+      <c r="AQ31" s="405" t="n"/>
+      <c r="AR31" s="405" t="n"/>
+      <c r="AS31" s="405" t="n"/>
+      <c r="AT31" s="405" t="n"/>
+      <c r="AU31" s="405" t="n"/>
+      <c r="AV31" s="405" t="n"/>
+      <c r="AW31" s="405" t="n"/>
+      <c r="AX31" s="405" t="n"/>
+      <c r="AY31" s="405" t="n"/>
+      <c r="AZ31" s="405" t="n"/>
+      <c r="BA31" s="405" t="n"/>
+      <c r="BB31" s="405" t="n"/>
+      <c r="BC31" s="405" t="n"/>
+      <c r="BD31" s="406" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="50" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="382" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B32" s="285" t="n"/>
-      <c r="C32" s="285" t="n"/>
-      <c r="D32" s="285" t="n"/>
-      <c r="E32" s="285" t="n"/>
-      <c r="F32" s="285" t="n"/>
-      <c r="G32" s="285" t="n"/>
-      <c r="H32" s="285" t="n"/>
-      <c r="I32" s="285" t="n"/>
-      <c r="J32" s="285" t="n"/>
-      <c r="K32" s="285" t="n"/>
-      <c r="L32" s="285" t="n"/>
-      <c r="M32" s="285" t="n"/>
-      <c r="N32" s="285" t="n"/>
-      <c r="O32" s="285" t="n"/>
-      <c r="P32" s="285" t="n"/>
-      <c r="Q32" s="285" t="n"/>
-      <c r="R32" s="285" t="n"/>
-      <c r="S32" s="51" t="inlineStr">
+      <c r="B32" s="400" t="n"/>
+      <c r="C32" s="400" t="n"/>
+      <c r="D32" s="400" t="n"/>
+      <c r="E32" s="400" t="n"/>
+      <c r="F32" s="400" t="n"/>
+      <c r="G32" s="400" t="n"/>
+      <c r="H32" s="400" t="n"/>
+      <c r="I32" s="400" t="n"/>
+      <c r="J32" s="400" t="n"/>
+      <c r="K32" s="400" t="n"/>
+      <c r="L32" s="400" t="n"/>
+      <c r="M32" s="400" t="n"/>
+      <c r="N32" s="400" t="n"/>
+      <c r="O32" s="400" t="n"/>
+      <c r="P32" s="400" t="n"/>
+      <c r="Q32" s="400" t="n"/>
+      <c r="R32" s="400" t="n"/>
+      <c r="S32" s="383" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T32" s="285" t="n"/>
-      <c r="U32" s="285" t="n"/>
-      <c r="V32" s="285" t="n"/>
-      <c r="W32" s="285" t="n"/>
-      <c r="X32" s="285" t="n"/>
-      <c r="Y32" s="285" t="n"/>
-      <c r="Z32" s="285" t="n"/>
-      <c r="AA32" s="285" t="n"/>
-      <c r="AB32" s="285" t="n"/>
-      <c r="AC32" s="285" t="n"/>
-      <c r="AD32" s="285" t="n"/>
-      <c r="AE32" s="285" t="n"/>
-      <c r="AF32" s="285" t="n"/>
-      <c r="AG32" s="285" t="n"/>
-      <c r="AH32" s="285" t="n"/>
-      <c r="AI32" s="285" t="n"/>
-      <c r="AJ32" s="285" t="n"/>
-      <c r="AK32" s="308" t="inlineStr">
+      <c r="T32" s="400" t="n"/>
+      <c r="U32" s="400" t="n"/>
+      <c r="V32" s="400" t="n"/>
+      <c r="W32" s="400" t="n"/>
+      <c r="X32" s="400" t="n"/>
+      <c r="Y32" s="400" t="n"/>
+      <c r="Z32" s="400" t="n"/>
+      <c r="AA32" s="400" t="n"/>
+      <c r="AB32" s="400" t="n"/>
+      <c r="AC32" s="400" t="n"/>
+      <c r="AD32" s="400" t="n"/>
+      <c r="AE32" s="400" t="n"/>
+      <c r="AF32" s="400" t="n"/>
+      <c r="AG32" s="400" t="n"/>
+      <c r="AH32" s="400" t="n"/>
+      <c r="AI32" s="400" t="n"/>
+      <c r="AJ32" s="400" t="n"/>
+      <c r="AK32" s="384" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL32" s="285" t="n"/>
-      <c r="AM32" s="285" t="n"/>
-      <c r="AN32" s="285" t="n"/>
-      <c r="AO32" s="285" t="n"/>
-      <c r="AP32" s="285" t="n"/>
-      <c r="AQ32" s="285" t="n"/>
-      <c r="AR32" s="285" t="n"/>
-      <c r="AS32" s="285" t="n"/>
-      <c r="AT32" s="285" t="n"/>
-      <c r="AU32" s="285" t="n"/>
-      <c r="AV32" s="285" t="n"/>
-      <c r="AW32" s="285" t="n"/>
-      <c r="AX32" s="285" t="n"/>
-      <c r="AY32" s="285" t="n"/>
-      <c r="AZ32" s="285" t="n"/>
-      <c r="BA32" s="285" t="n"/>
-      <c r="BB32" s="285" t="n"/>
-      <c r="BC32" s="285" t="n"/>
-      <c r="BD32" s="286" t="n"/>
+      <c r="AL32" s="400" t="n"/>
+      <c r="AM32" s="400" t="n"/>
+      <c r="AN32" s="400" t="n"/>
+      <c r="AO32" s="400" t="n"/>
+      <c r="AP32" s="400" t="n"/>
+      <c r="AQ32" s="400" t="n"/>
+      <c r="AR32" s="400" t="n"/>
+      <c r="AS32" s="400" t="n"/>
+      <c r="AT32" s="400" t="n"/>
+      <c r="AU32" s="400" t="n"/>
+      <c r="AV32" s="400" t="n"/>
+      <c r="AW32" s="400" t="n"/>
+      <c r="AX32" s="400" t="n"/>
+      <c r="AY32" s="400" t="n"/>
+      <c r="AZ32" s="400" t="n"/>
+      <c r="BA32" s="400" t="n"/>
+      <c r="BB32" s="400" t="n"/>
+      <c r="BC32" s="400" t="n"/>
+      <c r="BD32" s="401" t="n"/>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="309" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="385" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B33" s="331" t="n"/>
-      <c r="C33" s="331" t="n"/>
-      <c r="D33" s="331" t="n"/>
-      <c r="E33" s="331" t="n"/>
-      <c r="F33" s="331" t="n"/>
-      <c r="G33" s="331" t="n"/>
-      <c r="H33" s="331" t="n"/>
-      <c r="I33" s="331" t="n"/>
-      <c r="J33" s="331" t="n"/>
-      <c r="K33" s="331" t="n"/>
-      <c r="L33" s="331" t="n"/>
-      <c r="M33" s="331" t="n"/>
-      <c r="N33" s="331" t="n"/>
-      <c r="O33" s="331" t="n"/>
-      <c r="P33" s="331" t="n"/>
-      <c r="Q33" s="331" t="n"/>
-      <c r="R33" s="332" t="n"/>
-      <c r="S33" s="309" t="inlineStr">
+      <c r="B33" s="415" t="n"/>
+      <c r="C33" s="415" t="n"/>
+      <c r="D33" s="415" t="n"/>
+      <c r="E33" s="415" t="n"/>
+      <c r="F33" s="415" t="n"/>
+      <c r="G33" s="415" t="n"/>
+      <c r="H33" s="415" t="n"/>
+      <c r="I33" s="415" t="n"/>
+      <c r="J33" s="415" t="n"/>
+      <c r="K33" s="415" t="n"/>
+      <c r="L33" s="415" t="n"/>
+      <c r="M33" s="415" t="n"/>
+      <c r="N33" s="415" t="n"/>
+      <c r="O33" s="415" t="n"/>
+      <c r="P33" s="415" t="n"/>
+      <c r="Q33" s="415" t="n"/>
+      <c r="R33" s="416" t="n"/>
+      <c r="S33" s="385" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T33" s="331" t="n"/>
-      <c r="U33" s="331" t="n"/>
-      <c r="V33" s="331" t="n"/>
-      <c r="W33" s="331" t="n"/>
-      <c r="X33" s="331" t="n"/>
-      <c r="Y33" s="331" t="n"/>
-      <c r="Z33" s="331" t="n"/>
-      <c r="AA33" s="331" t="n"/>
-      <c r="AB33" s="331" t="n"/>
-      <c r="AC33" s="331" t="n"/>
-      <c r="AD33" s="331" t="n"/>
-      <c r="AE33" s="331" t="n"/>
-      <c r="AF33" s="331" t="n"/>
-      <c r="AG33" s="331" t="n"/>
-      <c r="AH33" s="331" t="n"/>
-      <c r="AI33" s="331" t="n"/>
-      <c r="AJ33" s="332" t="n"/>
-      <c r="AK33" s="309" t="inlineStr">
+      <c r="T33" s="415" t="n"/>
+      <c r="U33" s="415" t="n"/>
+      <c r="V33" s="415" t="n"/>
+      <c r="W33" s="415" t="n"/>
+      <c r="X33" s="415" t="n"/>
+      <c r="Y33" s="415" t="n"/>
+      <c r="Z33" s="415" t="n"/>
+      <c r="AA33" s="415" t="n"/>
+      <c r="AB33" s="415" t="n"/>
+      <c r="AC33" s="415" t="n"/>
+      <c r="AD33" s="415" t="n"/>
+      <c r="AE33" s="415" t="n"/>
+      <c r="AF33" s="415" t="n"/>
+      <c r="AG33" s="415" t="n"/>
+      <c r="AH33" s="415" t="n"/>
+      <c r="AI33" s="415" t="n"/>
+      <c r="AJ33" s="416" t="n"/>
+      <c r="AK33" s="385" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL33" s="331" t="n"/>
-      <c r="AM33" s="331" t="n"/>
-      <c r="AN33" s="331" t="n"/>
-      <c r="AO33" s="331" t="n"/>
-      <c r="AP33" s="331" t="n"/>
-      <c r="AQ33" s="331" t="n"/>
-      <c r="AR33" s="331" t="n"/>
-      <c r="AS33" s="331" t="n"/>
-      <c r="AT33" s="331" t="n"/>
-      <c r="AU33" s="331" t="n"/>
-      <c r="AV33" s="331" t="n"/>
-      <c r="AW33" s="331" t="n"/>
-      <c r="AX33" s="331" t="n"/>
-      <c r="AY33" s="331" t="n"/>
-      <c r="AZ33" s="331" t="n"/>
-      <c r="BA33" s="331" t="n"/>
-      <c r="BB33" s="331" t="n"/>
-      <c r="BC33" s="331" t="n"/>
-      <c r="BD33" s="332" t="n"/>
+      <c r="AL33" s="415" t="n"/>
+      <c r="AM33" s="415" t="n"/>
+      <c r="AN33" s="415" t="n"/>
+      <c r="AO33" s="415" t="n"/>
+      <c r="AP33" s="415" t="n"/>
+      <c r="AQ33" s="415" t="n"/>
+      <c r="AR33" s="415" t="n"/>
+      <c r="AS33" s="415" t="n"/>
+      <c r="AT33" s="415" t="n"/>
+      <c r="AU33" s="415" t="n"/>
+      <c r="AV33" s="415" t="n"/>
+      <c r="AW33" s="415" t="n"/>
+      <c r="AX33" s="415" t="n"/>
+      <c r="AY33" s="415" t="n"/>
+      <c r="AZ33" s="415" t="n"/>
+      <c r="BA33" s="415" t="n"/>
+      <c r="BB33" s="415" t="n"/>
+      <c r="BC33" s="415" t="n"/>
+      <c r="BD33" s="416" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="333" t="n"/>
-      <c r="B34" s="334" t="n"/>
-      <c r="C34" s="334" t="n"/>
-      <c r="D34" s="334" t="n"/>
-      <c r="E34" s="334" t="n"/>
-      <c r="F34" s="334" t="n"/>
-      <c r="G34" s="334" t="n"/>
-      <c r="H34" s="334" t="n"/>
-      <c r="I34" s="334" t="n"/>
-      <c r="J34" s="334" t="n"/>
-      <c r="K34" s="334" t="n"/>
-      <c r="L34" s="334" t="n"/>
-      <c r="M34" s="334" t="n"/>
-      <c r="N34" s="334" t="n"/>
-      <c r="O34" s="334" t="n"/>
-      <c r="P34" s="334" t="n"/>
-      <c r="Q34" s="334" t="n"/>
-      <c r="R34" s="335" t="n"/>
-      <c r="S34" s="333" t="n"/>
-      <c r="T34" s="334" t="n"/>
-      <c r="U34" s="334" t="n"/>
-      <c r="V34" s="334" t="n"/>
-      <c r="W34" s="334" t="n"/>
-      <c r="X34" s="334" t="n"/>
-      <c r="Y34" s="334" t="n"/>
-      <c r="Z34" s="334" t="n"/>
-      <c r="AA34" s="334" t="n"/>
-      <c r="AB34" s="334" t="n"/>
-      <c r="AC34" s="334" t="n"/>
-      <c r="AD34" s="334" t="n"/>
-      <c r="AE34" s="334" t="n"/>
-      <c r="AF34" s="334" t="n"/>
-      <c r="AG34" s="334" t="n"/>
-      <c r="AH34" s="334" t="n"/>
-      <c r="AI34" s="334" t="n"/>
-      <c r="AJ34" s="335" t="n"/>
-      <c r="AK34" s="333" t="n"/>
-      <c r="AL34" s="334" t="n"/>
-      <c r="AM34" s="334" t="n"/>
-      <c r="AN34" s="334" t="n"/>
-      <c r="AO34" s="334" t="n"/>
-      <c r="AP34" s="334" t="n"/>
-      <c r="AQ34" s="334" t="n"/>
-      <c r="AR34" s="334" t="n"/>
-      <c r="AS34" s="334" t="n"/>
-      <c r="AT34" s="334" t="n"/>
-      <c r="AU34" s="334" t="n"/>
-      <c r="AV34" s="334" t="n"/>
-      <c r="AW34" s="334" t="n"/>
-      <c r="AX34" s="334" t="n"/>
-      <c r="AY34" s="334" t="n"/>
-      <c r="AZ34" s="334" t="n"/>
-      <c r="BA34" s="334" t="n"/>
-      <c r="BB34" s="334" t="n"/>
-      <c r="BC34" s="334" t="n"/>
-      <c r="BD34" s="335" t="n"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="417" t="n"/>
+      <c r="B34" s="389" t="n"/>
+      <c r="C34" s="389" t="n"/>
+      <c r="D34" s="389" t="n"/>
+      <c r="E34" s="389" t="n"/>
+      <c r="F34" s="389" t="n"/>
+      <c r="G34" s="389" t="n"/>
+      <c r="H34" s="389" t="n"/>
+      <c r="I34" s="389" t="n"/>
+      <c r="J34" s="389" t="n"/>
+      <c r="K34" s="389" t="n"/>
+      <c r="L34" s="389" t="n"/>
+      <c r="M34" s="389" t="n"/>
+      <c r="N34" s="389" t="n"/>
+      <c r="O34" s="389" t="n"/>
+      <c r="P34" s="389" t="n"/>
+      <c r="Q34" s="389" t="n"/>
+      <c r="R34" s="418" t="n"/>
+      <c r="S34" s="417" t="n"/>
+      <c r="T34" s="389" t="n"/>
+      <c r="U34" s="389" t="n"/>
+      <c r="V34" s="389" t="n"/>
+      <c r="W34" s="389" t="n"/>
+      <c r="X34" s="389" t="n"/>
+      <c r="Y34" s="389" t="n"/>
+      <c r="Z34" s="389" t="n"/>
+      <c r="AA34" s="389" t="n"/>
+      <c r="AB34" s="389" t="n"/>
+      <c r="AC34" s="389" t="n"/>
+      <c r="AD34" s="389" t="n"/>
+      <c r="AE34" s="389" t="n"/>
+      <c r="AF34" s="389" t="n"/>
+      <c r="AG34" s="389" t="n"/>
+      <c r="AH34" s="389" t="n"/>
+      <c r="AI34" s="389" t="n"/>
+      <c r="AJ34" s="418" t="n"/>
+      <c r="AK34" s="417" t="n"/>
+      <c r="AL34" s="389" t="n"/>
+      <c r="AM34" s="389" t="n"/>
+      <c r="AN34" s="389" t="n"/>
+      <c r="AO34" s="389" t="n"/>
+      <c r="AP34" s="389" t="n"/>
+      <c r="AQ34" s="389" t="n"/>
+      <c r="AR34" s="389" t="n"/>
+      <c r="AS34" s="389" t="n"/>
+      <c r="AT34" s="389" t="n"/>
+      <c r="AU34" s="389" t="n"/>
+      <c r="AV34" s="389" t="n"/>
+      <c r="AW34" s="389" t="n"/>
+      <c r="AX34" s="389" t="n"/>
+      <c r="AY34" s="389" t="n"/>
+      <c r="AZ34" s="389" t="n"/>
+      <c r="BA34" s="389" t="n"/>
+      <c r="BB34" s="389" t="n"/>
+      <c r="BC34" s="389" t="n"/>
+      <c r="BD34" s="418" t="n"/>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="336" t="n"/>
-      <c r="B35" s="337" t="n"/>
-      <c r="C35" s="337" t="n"/>
-      <c r="D35" s="337" t="n"/>
-      <c r="E35" s="337" t="n"/>
-      <c r="F35" s="337" t="n"/>
-      <c r="G35" s="337" t="n"/>
-      <c r="H35" s="337" t="n"/>
-      <c r="I35" s="337" t="n"/>
-      <c r="J35" s="337" t="n"/>
-      <c r="K35" s="337" t="n"/>
-      <c r="L35" s="337" t="n"/>
-      <c r="M35" s="337" t="n"/>
-      <c r="N35" s="337" t="n"/>
-      <c r="O35" s="337" t="n"/>
-      <c r="P35" s="337" t="n"/>
-      <c r="Q35" s="337" t="n"/>
-      <c r="R35" s="338" t="n"/>
-      <c r="S35" s="336" t="n"/>
-      <c r="T35" s="337" t="n"/>
-      <c r="U35" s="337" t="n"/>
-      <c r="V35" s="337" t="n"/>
-      <c r="W35" s="337" t="n"/>
-      <c r="X35" s="337" t="n"/>
-      <c r="Y35" s="337" t="n"/>
-      <c r="Z35" s="337" t="n"/>
-      <c r="AA35" s="337" t="n"/>
-      <c r="AB35" s="337" t="n"/>
-      <c r="AC35" s="337" t="n"/>
-      <c r="AD35" s="337" t="n"/>
-      <c r="AE35" s="337" t="n"/>
-      <c r="AF35" s="337" t="n"/>
-      <c r="AG35" s="337" t="n"/>
-      <c r="AH35" s="337" t="n"/>
-      <c r="AI35" s="337" t="n"/>
-      <c r="AJ35" s="338" t="n"/>
-      <c r="AK35" s="336" t="n"/>
-      <c r="AL35" s="337" t="n"/>
-      <c r="AM35" s="337" t="n"/>
-      <c r="AN35" s="337" t="n"/>
-      <c r="AO35" s="337" t="n"/>
-      <c r="AP35" s="337" t="n"/>
-      <c r="AQ35" s="337" t="n"/>
-      <c r="AR35" s="337" t="n"/>
-      <c r="AS35" s="337" t="n"/>
-      <c r="AT35" s="337" t="n"/>
-      <c r="AU35" s="337" t="n"/>
-      <c r="AV35" s="337" t="n"/>
-      <c r="AW35" s="337" t="n"/>
-      <c r="AX35" s="337" t="n"/>
-      <c r="AY35" s="337" t="n"/>
-      <c r="AZ35" s="337" t="n"/>
-      <c r="BA35" s="337" t="n"/>
-      <c r="BB35" s="337" t="n"/>
-      <c r="BC35" s="337" t="n"/>
-      <c r="BD35" s="338" t="n"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="419" t="n"/>
+      <c r="B35" s="413" t="n"/>
+      <c r="C35" s="413" t="n"/>
+      <c r="D35" s="413" t="n"/>
+      <c r="E35" s="413" t="n"/>
+      <c r="F35" s="413" t="n"/>
+      <c r="G35" s="413" t="n"/>
+      <c r="H35" s="413" t="n"/>
+      <c r="I35" s="413" t="n"/>
+      <c r="J35" s="413" t="n"/>
+      <c r="K35" s="413" t="n"/>
+      <c r="L35" s="413" t="n"/>
+      <c r="M35" s="413" t="n"/>
+      <c r="N35" s="413" t="n"/>
+      <c r="O35" s="413" t="n"/>
+      <c r="P35" s="413" t="n"/>
+      <c r="Q35" s="413" t="n"/>
+      <c r="R35" s="414" t="n"/>
+      <c r="S35" s="419" t="n"/>
+      <c r="T35" s="413" t="n"/>
+      <c r="U35" s="413" t="n"/>
+      <c r="V35" s="413" t="n"/>
+      <c r="W35" s="413" t="n"/>
+      <c r="X35" s="413" t="n"/>
+      <c r="Y35" s="413" t="n"/>
+      <c r="Z35" s="413" t="n"/>
+      <c r="AA35" s="413" t="n"/>
+      <c r="AB35" s="413" t="n"/>
+      <c r="AC35" s="413" t="n"/>
+      <c r="AD35" s="413" t="n"/>
+      <c r="AE35" s="413" t="n"/>
+      <c r="AF35" s="413" t="n"/>
+      <c r="AG35" s="413" t="n"/>
+      <c r="AH35" s="413" t="n"/>
+      <c r="AI35" s="413" t="n"/>
+      <c r="AJ35" s="414" t="n"/>
+      <c r="AK35" s="419" t="n"/>
+      <c r="AL35" s="413" t="n"/>
+      <c r="AM35" s="413" t="n"/>
+      <c r="AN35" s="413" t="n"/>
+      <c r="AO35" s="413" t="n"/>
+      <c r="AP35" s="413" t="n"/>
+      <c r="AQ35" s="413" t="n"/>
+      <c r="AR35" s="413" t="n"/>
+      <c r="AS35" s="413" t="n"/>
+      <c r="AT35" s="413" t="n"/>
+      <c r="AU35" s="413" t="n"/>
+      <c r="AV35" s="413" t="n"/>
+      <c r="AW35" s="413" t="n"/>
+      <c r="AX35" s="413" t="n"/>
+      <c r="AY35" s="413" t="n"/>
+      <c r="AZ35" s="413" t="n"/>
+      <c r="BA35" s="413" t="n"/>
+      <c r="BB35" s="413" t="n"/>
+      <c r="BC35" s="413" t="n"/>
+      <c r="BD35" s="414" t="n"/>
     </row>
     <row r="36" ht="4" customHeight="1">
-      <c r="A36" s="298" t="n"/>
-      <c r="D36" s="292" t="n"/>
-      <c r="R36" s="292" t="n"/>
-      <c r="AI36" s="306" t="n"/>
-      <c r="AP36" s="306" t="n"/>
-      <c r="AW36" s="306" t="n"/>
-      <c r="BA36" s="312" t="n"/>
+      <c r="A36" s="377" t="n"/>
+      <c r="B36" s="353" t="n"/>
+      <c r="C36" s="353" t="n"/>
+      <c r="D36" s="365" t="n"/>
+      <c r="E36" s="353" t="n"/>
+      <c r="F36" s="353" t="n"/>
+      <c r="G36" s="353" t="n"/>
+      <c r="H36" s="353" t="n"/>
+      <c r="I36" s="353" t="n"/>
+      <c r="J36" s="353" t="n"/>
+      <c r="K36" s="353" t="n"/>
+      <c r="L36" s="353" t="n"/>
+      <c r="M36" s="353" t="n"/>
+      <c r="N36" s="353" t="n"/>
+      <c r="O36" s="353" t="n"/>
+      <c r="P36" s="353" t="n"/>
+      <c r="Q36" s="353" t="n"/>
+      <c r="R36" s="365" t="n"/>
+      <c r="S36" s="353" t="n"/>
+      <c r="T36" s="353" t="n"/>
+      <c r="U36" s="353" t="n"/>
+      <c r="V36" s="353" t="n"/>
+      <c r="W36" s="353" t="n"/>
+      <c r="X36" s="353" t="n"/>
+      <c r="Y36" s="353" t="n"/>
+      <c r="Z36" s="353" t="n"/>
+      <c r="AA36" s="353" t="n"/>
+      <c r="AB36" s="353" t="n"/>
+      <c r="AC36" s="353" t="n"/>
+      <c r="AD36" s="353" t="n"/>
+      <c r="AE36" s="353" t="n"/>
+      <c r="AF36" s="353" t="n"/>
+      <c r="AG36" s="353" t="n"/>
+      <c r="AH36" s="353" t="n"/>
+      <c r="AI36" s="380" t="n"/>
+      <c r="AJ36" s="353" t="n"/>
+      <c r="AK36" s="353" t="n"/>
+      <c r="AL36" s="353" t="n"/>
+      <c r="AM36" s="353" t="n"/>
+      <c r="AN36" s="353" t="n"/>
+      <c r="AO36" s="353" t="n"/>
+      <c r="AP36" s="380" t="n"/>
+      <c r="AQ36" s="353" t="n"/>
+      <c r="AR36" s="353" t="n"/>
+      <c r="AS36" s="353" t="n"/>
+      <c r="AT36" s="353" t="n"/>
+      <c r="AU36" s="353" t="n"/>
+      <c r="AV36" s="353" t="n"/>
+      <c r="AW36" s="380" t="n"/>
+      <c r="AX36" s="353" t="n"/>
+      <c r="AY36" s="353" t="n"/>
+      <c r="AZ36" s="353" t="n"/>
+      <c r="BA36" s="380" t="n"/>
+      <c r="BB36" s="353" t="n"/>
+      <c r="BC36" s="353" t="n"/>
+      <c r="BD36" s="353" t="n"/>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="339" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="392" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="276" t="n"/>
-      <c r="C37" s="276" t="n"/>
-      <c r="D37" s="276" t="n"/>
-      <c r="E37" s="276" t="n"/>
-      <c r="F37" s="276" t="n"/>
-      <c r="G37" s="276" t="n"/>
-      <c r="H37" s="276" t="n"/>
-      <c r="I37" s="276" t="n"/>
-      <c r="J37" s="276" t="n"/>
-      <c r="K37" s="276" t="n"/>
-      <c r="L37" s="276" t="n"/>
-      <c r="M37" s="276" t="n"/>
-      <c r="N37" s="276" t="n"/>
-      <c r="O37" s="276" t="n"/>
-      <c r="P37" s="276" t="n"/>
-      <c r="Q37" s="276" t="n"/>
-      <c r="R37" s="276" t="n"/>
-      <c r="S37" s="276" t="n"/>
-      <c r="T37" s="276" t="n"/>
-      <c r="U37" s="276" t="n"/>
-      <c r="V37" s="276" t="n"/>
-      <c r="W37" s="276" t="n"/>
-      <c r="X37" s="276" t="n"/>
-      <c r="Y37" s="276" t="n"/>
-      <c r="Z37" s="276" t="n"/>
-      <c r="AA37" s="276" t="n"/>
-      <c r="AB37" s="276" t="n"/>
-      <c r="AC37" s="276" t="n"/>
-      <c r="AD37" s="276" t="n"/>
-      <c r="AE37" s="276" t="n"/>
-      <c r="AF37" s="276" t="n"/>
-      <c r="AG37" s="276" t="n"/>
-      <c r="AH37" s="276" t="n"/>
-      <c r="AI37" s="276" t="n"/>
-      <c r="AJ37" s="276" t="n"/>
-      <c r="AK37" s="276" t="n"/>
-      <c r="AL37" s="276" t="n"/>
-      <c r="AM37" s="276" t="n"/>
-      <c r="AN37" s="276" t="n"/>
-      <c r="AO37" s="276" t="n"/>
-      <c r="AP37" s="276" t="n"/>
-      <c r="AQ37" s="276" t="n"/>
-      <c r="AR37" s="276" t="n"/>
-      <c r="AS37" s="276" t="n"/>
-      <c r="AT37" s="276" t="n"/>
-      <c r="AU37" s="276" t="n"/>
-      <c r="AV37" s="276" t="n"/>
-      <c r="AW37" s="276" t="n"/>
-      <c r="AX37" s="276" t="n"/>
-      <c r="AY37" s="276" t="n"/>
-      <c r="AZ37" s="276" t="n"/>
-      <c r="BA37" s="276" t="n"/>
-      <c r="BB37" s="276" t="n"/>
-      <c r="BC37" s="276" t="n"/>
-      <c r="BD37" s="277" t="n"/>
+      <c r="B37" s="411" t="n"/>
+      <c r="C37" s="411" t="n"/>
+      <c r="D37" s="411" t="n"/>
+      <c r="E37" s="411" t="n"/>
+      <c r="F37" s="411" t="n"/>
+      <c r="G37" s="411" t="n"/>
+      <c r="H37" s="411" t="n"/>
+      <c r="I37" s="411" t="n"/>
+      <c r="J37" s="411" t="n"/>
+      <c r="K37" s="411" t="n"/>
+      <c r="L37" s="411" t="n"/>
+      <c r="M37" s="411" t="n"/>
+      <c r="N37" s="411" t="n"/>
+      <c r="O37" s="411" t="n"/>
+      <c r="P37" s="411" t="n"/>
+      <c r="Q37" s="411" t="n"/>
+      <c r="R37" s="411" t="n"/>
+      <c r="S37" s="411" t="n"/>
+      <c r="T37" s="411" t="n"/>
+      <c r="U37" s="411" t="n"/>
+      <c r="V37" s="411" t="n"/>
+      <c r="W37" s="411" t="n"/>
+      <c r="X37" s="411" t="n"/>
+      <c r="Y37" s="411" t="n"/>
+      <c r="Z37" s="411" t="n"/>
+      <c r="AA37" s="411" t="n"/>
+      <c r="AB37" s="411" t="n"/>
+      <c r="AC37" s="411" t="n"/>
+      <c r="AD37" s="411" t="n"/>
+      <c r="AE37" s="411" t="n"/>
+      <c r="AF37" s="411" t="n"/>
+      <c r="AG37" s="411" t="n"/>
+      <c r="AH37" s="411" t="n"/>
+      <c r="AI37" s="411" t="n"/>
+      <c r="AJ37" s="411" t="n"/>
+      <c r="AK37" s="411" t="n"/>
+      <c r="AL37" s="411" t="n"/>
+      <c r="AM37" s="411" t="n"/>
+      <c r="AN37" s="411" t="n"/>
+      <c r="AO37" s="411" t="n"/>
+      <c r="AP37" s="411" t="n"/>
+      <c r="AQ37" s="411" t="n"/>
+      <c r="AR37" s="411" t="n"/>
+      <c r="AS37" s="411" t="n"/>
+      <c r="AT37" s="411" t="n"/>
+      <c r="AU37" s="411" t="n"/>
+      <c r="AV37" s="411" t="n"/>
+      <c r="AW37" s="411" t="n"/>
+      <c r="AX37" s="411" t="n"/>
+      <c r="AY37" s="411" t="n"/>
+      <c r="AZ37" s="411" t="n"/>
+      <c r="BA37" s="411" t="n"/>
+      <c r="BB37" s="411" t="n"/>
+      <c r="BC37" s="411" t="n"/>
+      <c r="BD37" s="412" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -7072,7 +7759,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7413,31 +8099,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="422" t="n"/>
+      <c r="C1" s="422" t="n"/>
+      <c r="D1" s="422" t="n"/>
+      <c r="E1" s="422" t="n"/>
+      <c r="F1" s="422" t="n"/>
+      <c r="G1" s="423" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="321" t="inlineStr">
@@ -7445,244 +8196,830 @@
           <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="322" t="inlineStr">
+      <c r="A4" s="366" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="322" t="inlineStr">
+      <c r="B4" s="366" t="inlineStr">
         <is>
           <t>Sample No.</t>
         </is>
       </c>
-      <c r="C4" s="322" t="inlineStr">
+      <c r="C4" s="366" t="inlineStr">
         <is>
           <t>ID / Serial</t>
         </is>
       </c>
-      <c r="D4" s="322" t="inlineStr">
+      <c r="D4" s="366" t="inlineStr">
         <is>
           <t>Measured Result / Observation</t>
         </is>
       </c>
-      <c r="E4" s="322" t="inlineStr">
+      <c r="E4" s="366" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F4" s="322" t="inlineStr">
+      <c r="F4" s="366" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="G4" s="322" t="inlineStr">
+      <c r="G4" s="366" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H4" s="322" t="inlineStr">
+      <c r="H4" s="366" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="323">
+      <c r="A5" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="324" t="n"/>
-      <c r="C5" s="324" t="n"/>
-      <c r="D5" s="324" t="n"/>
-      <c r="E5" s="324" t="n"/>
-      <c r="F5" s="324" t="n"/>
-      <c r="G5" s="324" t="n"/>
-      <c r="H5" s="324" t="n"/>
+      <c r="B5" s="395" t="n"/>
+      <c r="C5" s="395" t="n"/>
+      <c r="D5" s="395" t="n"/>
+      <c r="E5" s="395" t="n"/>
+      <c r="F5" s="395" t="n"/>
+      <c r="G5" s="395" t="n"/>
+      <c r="H5" s="395" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="323">
+      <c r="A6" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="324" t="n"/>
-      <c r="C6" s="324" t="n"/>
-      <c r="D6" s="324" t="n"/>
-      <c r="E6" s="324" t="n"/>
-      <c r="F6" s="324" t="n"/>
-      <c r="G6" s="324" t="n"/>
-      <c r="H6" s="324" t="n"/>
+      <c r="B6" s="395" t="n"/>
+      <c r="C6" s="395" t="n"/>
+      <c r="D6" s="395" t="n"/>
+      <c r="E6" s="395" t="n"/>
+      <c r="F6" s="395" t="n"/>
+      <c r="G6" s="395" t="n"/>
+      <c r="H6" s="395" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="323">
+      <c r="A7" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="324" t="n"/>
-      <c r="C7" s="324" t="n"/>
-      <c r="D7" s="324" t="n"/>
-      <c r="E7" s="324" t="n"/>
-      <c r="F7" s="324" t="n"/>
-      <c r="G7" s="324" t="n"/>
-      <c r="H7" s="324" t="n"/>
+      <c r="B7" s="395" t="n"/>
+      <c r="C7" s="395" t="n"/>
+      <c r="D7" s="395" t="n"/>
+      <c r="E7" s="395" t="n"/>
+      <c r="F7" s="395" t="n"/>
+      <c r="G7" s="395" t="n"/>
+      <c r="H7" s="395" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="323">
+      <c r="A8" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="324" t="n"/>
-      <c r="C8" s="324" t="n"/>
-      <c r="D8" s="324" t="n"/>
-      <c r="E8" s="324" t="n"/>
-      <c r="F8" s="324" t="n"/>
-      <c r="G8" s="324" t="n"/>
-      <c r="H8" s="324" t="n"/>
+      <c r="B8" s="397" t="n"/>
+      <c r="C8" s="397" t="n"/>
+      <c r="D8" s="397" t="n"/>
+      <c r="E8" s="397" t="n"/>
+      <c r="F8" s="397" t="n"/>
+      <c r="G8" s="397" t="n"/>
+      <c r="H8" s="397" t="n"/>
+      <c r="I8" s="398" t="n"/>
+      <c r="J8" s="398" t="n"/>
+      <c r="K8" s="398" t="n"/>
+      <c r="L8" s="398" t="n"/>
+      <c r="M8" s="398" t="n"/>
+      <c r="N8" s="398" t="n"/>
+      <c r="O8" s="398" t="n"/>
+      <c r="P8" s="398" t="n"/>
+      <c r="Q8" s="398" t="n"/>
+      <c r="R8" s="398" t="n"/>
+      <c r="S8" s="398" t="n"/>
+      <c r="T8" s="398" t="n"/>
+      <c r="U8" s="398" t="n"/>
+      <c r="V8" s="398" t="n"/>
+      <c r="W8" s="398" t="n"/>
+      <c r="X8" s="398" t="n"/>
+      <c r="Y8" s="398" t="n"/>
+      <c r="Z8" s="398" t="n"/>
+      <c r="AA8" s="398" t="n"/>
+      <c r="AB8" s="398" t="n"/>
+      <c r="AC8" s="398" t="n"/>
+      <c r="AD8" s="398" t="n"/>
+      <c r="AE8" s="398" t="n"/>
+      <c r="AF8" s="398" t="n"/>
+      <c r="AG8" s="398" t="n"/>
+      <c r="AH8" s="398" t="n"/>
+      <c r="AI8" s="398" t="n"/>
+      <c r="AJ8" s="398" t="n"/>
+      <c r="AK8" s="398" t="n"/>
+      <c r="AL8" s="398" t="n"/>
+      <c r="AM8" s="398" t="n"/>
+      <c r="AN8" s="398" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="323">
+      <c r="A9" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="324" t="n"/>
-      <c r="C9" s="324" t="n"/>
-      <c r="D9" s="324" t="n"/>
-      <c r="E9" s="324" t="n"/>
-      <c r="F9" s="324" t="n"/>
-      <c r="G9" s="324" t="n"/>
-      <c r="H9" s="324" t="n"/>
+      <c r="B9" s="397" t="n"/>
+      <c r="C9" s="397" t="n"/>
+      <c r="D9" s="397" t="n"/>
+      <c r="E9" s="397" t="n"/>
+      <c r="F9" s="397" t="n"/>
+      <c r="G9" s="397" t="n"/>
+      <c r="H9" s="397" t="n"/>
+      <c r="I9" s="398" t="n"/>
+      <c r="J9" s="398" t="n"/>
+      <c r="K9" s="398" t="n"/>
+      <c r="L9" s="398" t="n"/>
+      <c r="M9" s="398" t="n"/>
+      <c r="N9" s="398" t="n"/>
+      <c r="O9" s="398" t="n"/>
+      <c r="P9" s="398" t="n"/>
+      <c r="Q9" s="398" t="n"/>
+      <c r="R9" s="398" t="n"/>
+      <c r="S9" s="398" t="n"/>
+      <c r="T9" s="398" t="n"/>
+      <c r="U9" s="398" t="n"/>
+      <c r="V9" s="398" t="n"/>
+      <c r="W9" s="398" t="n"/>
+      <c r="X9" s="398" t="n"/>
+      <c r="Y9" s="398" t="n"/>
+      <c r="Z9" s="398" t="n"/>
+      <c r="AA9" s="398" t="n"/>
+      <c r="AB9" s="398" t="n"/>
+      <c r="AC9" s="398" t="n"/>
+      <c r="AD9" s="398" t="n"/>
+      <c r="AE9" s="398" t="n"/>
+      <c r="AF9" s="398" t="n"/>
+      <c r="AG9" s="398" t="n"/>
+      <c r="AH9" s="398" t="n"/>
+      <c r="AI9" s="398" t="n"/>
+      <c r="AJ9" s="398" t="n"/>
+      <c r="AK9" s="398" t="n"/>
+      <c r="AL9" s="398" t="n"/>
+      <c r="AM9" s="398" t="n"/>
+      <c r="AN9" s="398" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="323">
+      <c r="A10" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="324" t="n"/>
-      <c r="C10" s="324" t="n"/>
-      <c r="D10" s="324" t="n"/>
-      <c r="E10" s="324" t="n"/>
-      <c r="F10" s="324" t="n"/>
-      <c r="G10" s="324" t="n"/>
-      <c r="H10" s="324" t="n"/>
+      <c r="B10" s="397" t="n"/>
+      <c r="C10" s="397" t="n"/>
+      <c r="D10" s="397" t="n"/>
+      <c r="E10" s="397" t="n"/>
+      <c r="F10" s="397" t="n"/>
+      <c r="G10" s="397" t="n"/>
+      <c r="H10" s="397" t="n"/>
+      <c r="I10" s="398" t="n"/>
+      <c r="J10" s="398" t="n"/>
+      <c r="K10" s="398" t="n"/>
+      <c r="L10" s="398" t="n"/>
+      <c r="M10" s="398" t="n"/>
+      <c r="N10" s="398" t="n"/>
+      <c r="O10" s="398" t="n"/>
+      <c r="P10" s="398" t="n"/>
+      <c r="Q10" s="398" t="n"/>
+      <c r="R10" s="398" t="n"/>
+      <c r="S10" s="398" t="n"/>
+      <c r="T10" s="398" t="n"/>
+      <c r="U10" s="398" t="n"/>
+      <c r="V10" s="398" t="n"/>
+      <c r="W10" s="398" t="n"/>
+      <c r="X10" s="398" t="n"/>
+      <c r="Y10" s="398" t="n"/>
+      <c r="Z10" s="398" t="n"/>
+      <c r="AA10" s="398" t="n"/>
+      <c r="AB10" s="398" t="n"/>
+      <c r="AC10" s="398" t="n"/>
+      <c r="AD10" s="398" t="n"/>
+      <c r="AE10" s="398" t="n"/>
+      <c r="AF10" s="398" t="n"/>
+      <c r="AG10" s="398" t="n"/>
+      <c r="AH10" s="398" t="n"/>
+      <c r="AI10" s="398" t="n"/>
+      <c r="AJ10" s="398" t="n"/>
+      <c r="AK10" s="398" t="n"/>
+      <c r="AL10" s="398" t="n"/>
+      <c r="AM10" s="398" t="n"/>
+      <c r="AN10" s="398" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="323">
+      <c r="A11" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="324" t="n"/>
-      <c r="C11" s="324" t="n"/>
-      <c r="D11" s="324" t="n"/>
-      <c r="E11" s="324" t="n"/>
-      <c r="F11" s="324" t="n"/>
-      <c r="G11" s="324" t="n"/>
-      <c r="H11" s="324" t="n"/>
+      <c r="B11" s="397" t="n"/>
+      <c r="C11" s="397" t="n"/>
+      <c r="D11" s="397" t="n"/>
+      <c r="E11" s="397" t="n"/>
+      <c r="F11" s="397" t="n"/>
+      <c r="G11" s="397" t="n"/>
+      <c r="H11" s="397" t="n"/>
+      <c r="I11" s="398" t="n"/>
+      <c r="J11" s="398" t="n"/>
+      <c r="K11" s="398" t="n"/>
+      <c r="L11" s="398" t="n"/>
+      <c r="M11" s="398" t="n"/>
+      <c r="N11" s="398" t="n"/>
+      <c r="O11" s="398" t="n"/>
+      <c r="P11" s="398" t="n"/>
+      <c r="Q11" s="398" t="n"/>
+      <c r="R11" s="398" t="n"/>
+      <c r="S11" s="398" t="n"/>
+      <c r="T11" s="398" t="n"/>
+      <c r="U11" s="398" t="n"/>
+      <c r="V11" s="398" t="n"/>
+      <c r="W11" s="398" t="n"/>
+      <c r="X11" s="398" t="n"/>
+      <c r="Y11" s="398" t="n"/>
+      <c r="Z11" s="398" t="n"/>
+      <c r="AA11" s="398" t="n"/>
+      <c r="AB11" s="398" t="n"/>
+      <c r="AC11" s="398" t="n"/>
+      <c r="AD11" s="398" t="n"/>
+      <c r="AE11" s="398" t="n"/>
+      <c r="AF11" s="398" t="n"/>
+      <c r="AG11" s="398" t="n"/>
+      <c r="AH11" s="398" t="n"/>
+      <c r="AI11" s="398" t="n"/>
+      <c r="AJ11" s="398" t="n"/>
+      <c r="AK11" s="398" t="n"/>
+      <c r="AL11" s="398" t="n"/>
+      <c r="AM11" s="398" t="n"/>
+      <c r="AN11" s="398" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="323">
+      <c r="A12" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="324" t="n"/>
-      <c r="C12" s="324" t="n"/>
-      <c r="D12" s="324" t="n"/>
-      <c r="E12" s="324" t="n"/>
-      <c r="F12" s="324" t="n"/>
-      <c r="G12" s="324" t="n"/>
-      <c r="H12" s="324" t="n"/>
+      <c r="B12" s="397" t="n"/>
+      <c r="C12" s="397" t="n"/>
+      <c r="D12" s="397" t="n"/>
+      <c r="E12" s="397" t="n"/>
+      <c r="F12" s="397" t="n"/>
+      <c r="G12" s="397" t="n"/>
+      <c r="H12" s="397" t="n"/>
+      <c r="I12" s="398" t="n"/>
+      <c r="J12" s="398" t="n"/>
+      <c r="K12" s="398" t="n"/>
+      <c r="L12" s="398" t="n"/>
+      <c r="M12" s="398" t="n"/>
+      <c r="N12" s="398" t="n"/>
+      <c r="O12" s="398" t="n"/>
+      <c r="P12" s="398" t="n"/>
+      <c r="Q12" s="398" t="n"/>
+      <c r="R12" s="398" t="n"/>
+      <c r="S12" s="398" t="n"/>
+      <c r="T12" s="398" t="n"/>
+      <c r="U12" s="398" t="n"/>
+      <c r="V12" s="398" t="n"/>
+      <c r="W12" s="398" t="n"/>
+      <c r="X12" s="398" t="n"/>
+      <c r="Y12" s="398" t="n"/>
+      <c r="Z12" s="398" t="n"/>
+      <c r="AA12" s="398" t="n"/>
+      <c r="AB12" s="398" t="n"/>
+      <c r="AC12" s="398" t="n"/>
+      <c r="AD12" s="398" t="n"/>
+      <c r="AE12" s="398" t="n"/>
+      <c r="AF12" s="398" t="n"/>
+      <c r="AG12" s="398" t="n"/>
+      <c r="AH12" s="398" t="n"/>
+      <c r="AI12" s="398" t="n"/>
+      <c r="AJ12" s="398" t="n"/>
+      <c r="AK12" s="398" t="n"/>
+      <c r="AL12" s="398" t="n"/>
+      <c r="AM12" s="398" t="n"/>
+      <c r="AN12" s="398" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="323">
+      <c r="A13" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="324" t="n"/>
-      <c r="C13" s="324" t="n"/>
-      <c r="D13" s="324" t="n"/>
-      <c r="E13" s="324" t="n"/>
-      <c r="F13" s="324" t="n"/>
-      <c r="G13" s="324" t="n"/>
-      <c r="H13" s="324" t="n"/>
+      <c r="B13" s="397" t="n"/>
+      <c r="C13" s="397" t="n"/>
+      <c r="D13" s="397" t="n"/>
+      <c r="E13" s="397" t="n"/>
+      <c r="F13" s="397" t="n"/>
+      <c r="G13" s="397" t="n"/>
+      <c r="H13" s="397" t="n"/>
+      <c r="I13" s="398" t="n"/>
+      <c r="J13" s="398" t="n"/>
+      <c r="K13" s="398" t="n"/>
+      <c r="L13" s="398" t="n"/>
+      <c r="M13" s="398" t="n"/>
+      <c r="N13" s="398" t="n"/>
+      <c r="O13" s="398" t="n"/>
+      <c r="P13" s="398" t="n"/>
+      <c r="Q13" s="398" t="n"/>
+      <c r="R13" s="398" t="n"/>
+      <c r="S13" s="398" t="n"/>
+      <c r="T13" s="398" t="n"/>
+      <c r="U13" s="398" t="n"/>
+      <c r="V13" s="398" t="n"/>
+      <c r="W13" s="398" t="n"/>
+      <c r="X13" s="398" t="n"/>
+      <c r="Y13" s="398" t="n"/>
+      <c r="Z13" s="398" t="n"/>
+      <c r="AA13" s="398" t="n"/>
+      <c r="AB13" s="398" t="n"/>
+      <c r="AC13" s="398" t="n"/>
+      <c r="AD13" s="398" t="n"/>
+      <c r="AE13" s="398" t="n"/>
+      <c r="AF13" s="398" t="n"/>
+      <c r="AG13" s="398" t="n"/>
+      <c r="AH13" s="398" t="n"/>
+      <c r="AI13" s="398" t="n"/>
+      <c r="AJ13" s="398" t="n"/>
+      <c r="AK13" s="398" t="n"/>
+      <c r="AL13" s="398" t="n"/>
+      <c r="AM13" s="398" t="n"/>
+      <c r="AN13" s="398" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="323">
+      <c r="A14" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="324" t="n"/>
-      <c r="C14" s="324" t="n"/>
-      <c r="D14" s="324" t="n"/>
-      <c r="E14" s="324" t="n"/>
-      <c r="F14" s="324" t="n"/>
-      <c r="G14" s="324" t="n"/>
-      <c r="H14" s="324" t="n"/>
+      <c r="B14" s="397" t="n"/>
+      <c r="C14" s="397" t="n"/>
+      <c r="D14" s="397" t="n"/>
+      <c r="E14" s="397" t="n"/>
+      <c r="F14" s="397" t="n"/>
+      <c r="G14" s="397" t="n"/>
+      <c r="H14" s="397" t="n"/>
+      <c r="I14" s="398" t="n"/>
+      <c r="J14" s="398" t="n"/>
+      <c r="K14" s="398" t="n"/>
+      <c r="L14" s="398" t="n"/>
+      <c r="M14" s="398" t="n"/>
+      <c r="N14" s="398" t="n"/>
+      <c r="O14" s="398" t="n"/>
+      <c r="P14" s="398" t="n"/>
+      <c r="Q14" s="398" t="n"/>
+      <c r="R14" s="398" t="n"/>
+      <c r="S14" s="398" t="n"/>
+      <c r="T14" s="398" t="n"/>
+      <c r="U14" s="398" t="n"/>
+      <c r="V14" s="398" t="n"/>
+      <c r="W14" s="398" t="n"/>
+      <c r="X14" s="398" t="n"/>
+      <c r="Y14" s="398" t="n"/>
+      <c r="Z14" s="398" t="n"/>
+      <c r="AA14" s="398" t="n"/>
+      <c r="AB14" s="398" t="n"/>
+      <c r="AC14" s="398" t="n"/>
+      <c r="AD14" s="398" t="n"/>
+      <c r="AE14" s="398" t="n"/>
+      <c r="AF14" s="398" t="n"/>
+      <c r="AG14" s="398" t="n"/>
+      <c r="AH14" s="398" t="n"/>
+      <c r="AI14" s="398" t="n"/>
+      <c r="AJ14" s="398" t="n"/>
+      <c r="AK14" s="398" t="n"/>
+      <c r="AL14" s="398" t="n"/>
+      <c r="AM14" s="398" t="n"/>
+      <c r="AN14" s="398" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="323">
+      <c r="A15" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B15" s="324" t="n"/>
-      <c r="C15" s="324" t="n"/>
-      <c r="D15" s="324" t="n"/>
-      <c r="E15" s="324" t="n"/>
-      <c r="F15" s="324" t="n"/>
-      <c r="G15" s="324" t="n"/>
-      <c r="H15" s="324" t="n"/>
+      <c r="B15" s="397" t="n"/>
+      <c r="C15" s="397" t="n"/>
+      <c r="D15" s="397" t="n"/>
+      <c r="E15" s="397" t="n"/>
+      <c r="F15" s="397" t="n"/>
+      <c r="G15" s="397" t="n"/>
+      <c r="H15" s="397" t="n"/>
+      <c r="I15" s="398" t="n"/>
+      <c r="J15" s="398" t="n"/>
+      <c r="K15" s="398" t="n"/>
+      <c r="L15" s="398" t="n"/>
+      <c r="M15" s="398" t="n"/>
+      <c r="N15" s="398" t="n"/>
+      <c r="O15" s="398" t="n"/>
+      <c r="P15" s="398" t="n"/>
+      <c r="Q15" s="398" t="n"/>
+      <c r="R15" s="398" t="n"/>
+      <c r="S15" s="398" t="n"/>
+      <c r="T15" s="398" t="n"/>
+      <c r="U15" s="398" t="n"/>
+      <c r="V15" s="398" t="n"/>
+      <c r="W15" s="398" t="n"/>
+      <c r="X15" s="398" t="n"/>
+      <c r="Y15" s="398" t="n"/>
+      <c r="Z15" s="398" t="n"/>
+      <c r="AA15" s="398" t="n"/>
+      <c r="AB15" s="398" t="n"/>
+      <c r="AC15" s="398" t="n"/>
+      <c r="AD15" s="398" t="n"/>
+      <c r="AE15" s="398" t="n"/>
+      <c r="AF15" s="398" t="n"/>
+      <c r="AG15" s="398" t="n"/>
+      <c r="AH15" s="398" t="n"/>
+      <c r="AI15" s="398" t="n"/>
+      <c r="AJ15" s="398" t="n"/>
+      <c r="AK15" s="398" t="n"/>
+      <c r="AL15" s="398" t="n"/>
+      <c r="AM15" s="398" t="n"/>
+      <c r="AN15" s="398" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="323">
+      <c r="A16" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B16" s="324" t="n"/>
-      <c r="C16" s="324" t="n"/>
-      <c r="D16" s="324" t="n"/>
-      <c r="E16" s="324" t="n"/>
-      <c r="F16" s="324" t="n"/>
-      <c r="G16" s="324" t="n"/>
-      <c r="H16" s="324" t="n"/>
+      <c r="B16" s="397" t="n"/>
+      <c r="C16" s="397" t="n"/>
+      <c r="D16" s="397" t="n"/>
+      <c r="E16" s="397" t="n"/>
+      <c r="F16" s="397" t="n"/>
+      <c r="G16" s="397" t="n"/>
+      <c r="H16" s="397" t="n"/>
+      <c r="I16" s="398" t="n"/>
+      <c r="J16" s="398" t="n"/>
+      <c r="K16" s="398" t="n"/>
+      <c r="L16" s="398" t="n"/>
+      <c r="M16" s="398" t="n"/>
+      <c r="N16" s="398" t="n"/>
+      <c r="O16" s="398" t="n"/>
+      <c r="P16" s="398" t="n"/>
+      <c r="Q16" s="398" t="n"/>
+      <c r="R16" s="398" t="n"/>
+      <c r="S16" s="398" t="n"/>
+      <c r="T16" s="398" t="n"/>
+      <c r="U16" s="398" t="n"/>
+      <c r="V16" s="398" t="n"/>
+      <c r="W16" s="398" t="n"/>
+      <c r="X16" s="398" t="n"/>
+      <c r="Y16" s="398" t="n"/>
+      <c r="Z16" s="398" t="n"/>
+      <c r="AA16" s="398" t="n"/>
+      <c r="AB16" s="398" t="n"/>
+      <c r="AC16" s="398" t="n"/>
+      <c r="AD16" s="398" t="n"/>
+      <c r="AE16" s="398" t="n"/>
+      <c r="AF16" s="398" t="n"/>
+      <c r="AG16" s="398" t="n"/>
+      <c r="AH16" s="398" t="n"/>
+      <c r="AI16" s="398" t="n"/>
+      <c r="AJ16" s="398" t="n"/>
+      <c r="AK16" s="398" t="n"/>
+      <c r="AL16" s="398" t="n"/>
+      <c r="AM16" s="398" t="n"/>
+      <c r="AN16" s="398" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="323">
+      <c r="A17" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B17" s="324" t="n"/>
-      <c r="C17" s="324" t="n"/>
-      <c r="D17" s="324" t="n"/>
-      <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="324" t="n"/>
-      <c r="H17" s="324" t="n"/>
+      <c r="B17" s="397" t="n"/>
+      <c r="C17" s="397" t="n"/>
+      <c r="D17" s="397" t="n"/>
+      <c r="E17" s="397" t="n"/>
+      <c r="F17" s="397" t="n"/>
+      <c r="G17" s="397" t="n"/>
+      <c r="H17" s="397" t="n"/>
+      <c r="I17" s="398" t="n"/>
+      <c r="J17" s="398" t="n"/>
+      <c r="K17" s="398" t="n"/>
+      <c r="L17" s="398" t="n"/>
+      <c r="M17" s="398" t="n"/>
+      <c r="N17" s="398" t="n"/>
+      <c r="O17" s="398" t="n"/>
+      <c r="P17" s="398" t="n"/>
+      <c r="Q17" s="398" t="n"/>
+      <c r="R17" s="398" t="n"/>
+      <c r="S17" s="398" t="n"/>
+      <c r="T17" s="398" t="n"/>
+      <c r="U17" s="398" t="n"/>
+      <c r="V17" s="398" t="n"/>
+      <c r="W17" s="398" t="n"/>
+      <c r="X17" s="398" t="n"/>
+      <c r="Y17" s="398" t="n"/>
+      <c r="Z17" s="398" t="n"/>
+      <c r="AA17" s="398" t="n"/>
+      <c r="AB17" s="398" t="n"/>
+      <c r="AC17" s="398" t="n"/>
+      <c r="AD17" s="398" t="n"/>
+      <c r="AE17" s="398" t="n"/>
+      <c r="AF17" s="398" t="n"/>
+      <c r="AG17" s="398" t="n"/>
+      <c r="AH17" s="398" t="n"/>
+      <c r="AI17" s="398" t="n"/>
+      <c r="AJ17" s="398" t="n"/>
+      <c r="AK17" s="398" t="n"/>
+      <c r="AL17" s="398" t="n"/>
+      <c r="AM17" s="398" t="n"/>
+      <c r="AN17" s="398" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="323">
+      <c r="A18" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B18" s="324" t="n"/>
-      <c r="C18" s="324" t="n"/>
-      <c r="D18" s="324" t="n"/>
-      <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="324" t="n"/>
-      <c r="H18" s="324" t="n"/>
+      <c r="B18" s="397" t="n"/>
+      <c r="C18" s="397" t="n"/>
+      <c r="D18" s="397" t="n"/>
+      <c r="E18" s="397" t="n"/>
+      <c r="F18" s="397" t="n"/>
+      <c r="G18" s="397" t="n"/>
+      <c r="H18" s="397" t="n"/>
+      <c r="I18" s="398" t="n"/>
+      <c r="J18" s="398" t="n"/>
+      <c r="K18" s="398" t="n"/>
+      <c r="L18" s="398" t="n"/>
+      <c r="M18" s="398" t="n"/>
+      <c r="N18" s="398" t="n"/>
+      <c r="O18" s="398" t="n"/>
+      <c r="P18" s="398" t="n"/>
+      <c r="Q18" s="398" t="n"/>
+      <c r="R18" s="398" t="n"/>
+      <c r="S18" s="398" t="n"/>
+      <c r="T18" s="398" t="n"/>
+      <c r="U18" s="398" t="n"/>
+      <c r="V18" s="398" t="n"/>
+      <c r="W18" s="398" t="n"/>
+      <c r="X18" s="398" t="n"/>
+      <c r="Y18" s="398" t="n"/>
+      <c r="Z18" s="398" t="n"/>
+      <c r="AA18" s="398" t="n"/>
+      <c r="AB18" s="398" t="n"/>
+      <c r="AC18" s="398" t="n"/>
+      <c r="AD18" s="398" t="n"/>
+      <c r="AE18" s="398" t="n"/>
+      <c r="AF18" s="398" t="n"/>
+      <c r="AG18" s="398" t="n"/>
+      <c r="AH18" s="398" t="n"/>
+      <c r="AI18" s="398" t="n"/>
+      <c r="AJ18" s="398" t="n"/>
+      <c r="AK18" s="398" t="n"/>
+      <c r="AL18" s="398" t="n"/>
+      <c r="AM18" s="398" t="n"/>
+      <c r="AN18" s="398" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="323">
+      <c r="A19" s="396">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B19" s="324" t="n"/>
-      <c r="C19" s="324" t="n"/>
-      <c r="D19" s="324" t="n"/>
-      <c r="E19" s="324" t="n"/>
-      <c r="F19" s="324" t="n"/>
-      <c r="G19" s="324" t="n"/>
-      <c r="H19" s="324" t="n"/>
+      <c r="B19" s="397" t="n"/>
+      <c r="C19" s="397" t="n"/>
+      <c r="D19" s="397" t="n"/>
+      <c r="E19" s="397" t="n"/>
+      <c r="F19" s="397" t="n"/>
+      <c r="G19" s="397" t="n"/>
+      <c r="H19" s="397" t="n"/>
+      <c r="I19" s="398" t="n"/>
+      <c r="J19" s="398" t="n"/>
+      <c r="K19" s="398" t="n"/>
+      <c r="L19" s="398" t="n"/>
+      <c r="M19" s="398" t="n"/>
+      <c r="N19" s="398" t="n"/>
+      <c r="O19" s="398" t="n"/>
+      <c r="P19" s="398" t="n"/>
+      <c r="Q19" s="398" t="n"/>
+      <c r="R19" s="398" t="n"/>
+      <c r="S19" s="398" t="n"/>
+      <c r="T19" s="398" t="n"/>
+      <c r="U19" s="398" t="n"/>
+      <c r="V19" s="398" t="n"/>
+      <c r="W19" s="398" t="n"/>
+      <c r="X19" s="398" t="n"/>
+      <c r="Y19" s="398" t="n"/>
+      <c r="Z19" s="398" t="n"/>
+      <c r="AA19" s="398" t="n"/>
+      <c r="AB19" s="398" t="n"/>
+      <c r="AC19" s="398" t="n"/>
+      <c r="AD19" s="398" t="n"/>
+      <c r="AE19" s="398" t="n"/>
+      <c r="AF19" s="398" t="n"/>
+      <c r="AG19" s="398" t="n"/>
+      <c r="AH19" s="398" t="n"/>
+      <c r="AI19" s="398" t="n"/>
+      <c r="AJ19" s="398" t="n"/>
+      <c r="AK19" s="398" t="n"/>
+      <c r="AL19" s="398" t="n"/>
+      <c r="AM19" s="398" t="n"/>
+      <c r="AN19" s="398" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -7695,7 +9032,8 @@
       <formula1>'LISTS'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7708,30 +9046,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="422" t="n"/>
+      <c r="C1" s="422" t="n"/>
+      <c r="D1" s="422" t="n"/>
+      <c r="E1" s="422" t="n"/>
+      <c r="F1" s="422" t="n"/>
+      <c r="G1" s="423" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="321" t="inlineStr">
@@ -7739,54 +9143,202 @@
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="322" t="inlineStr">
+      <c r="A4" s="366" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="322" t="inlineStr">
+      <c r="B4" s="366" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="322" t="inlineStr">
+      <c r="C4" s="366" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="348" t="n"/>
+      <c r="E4" s="348" t="n"/>
+      <c r="F4" s="348" t="n"/>
+      <c r="G4" s="348" t="n"/>
+      <c r="H4" s="348" t="n"/>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="323" t="inlineStr">
+      <c r="A5" s="394" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="324" t="inlineStr">
+      <c r="B5" s="395" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="324" t="inlineStr">
+      <c r="C5" s="395" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="348" t="n"/>
+      <c r="E5" s="348" t="n"/>
+      <c r="F5" s="348" t="n"/>
+      <c r="G5" s="348" t="n"/>
+      <c r="H5" s="348" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="323" t="inlineStr">
+      <c r="A6" s="394" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="324" t="inlineStr">
+      <c r="B6" s="395" t="inlineStr">
         <is>
           <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
         </is>
       </c>
-      <c r="C6" s="324" t="inlineStr">
+      <c r="C6" s="395" t="inlineStr">
         <is>
           <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
@@ -7794,159 +9346,529 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="348" t="n"/>
+      <c r="E6" s="348" t="n"/>
+      <c r="F6" s="348" t="n"/>
+      <c r="G6" s="348" t="n"/>
+      <c r="H6" s="348" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="323" t="inlineStr">
+      <c r="A7" s="394" t="inlineStr">
         <is>
           <t>SOP SOP-603</t>
         </is>
       </c>
-      <c r="B7" s="324" t="inlineStr">
+      <c r="B7" s="395" t="inlineStr">
         <is>
           <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="324" t="inlineStr">
+      <c r="C7" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
         </is>
       </c>
+      <c r="D7" s="348" t="n"/>
+      <c r="E7" s="348" t="n"/>
+      <c r="F7" s="348" t="n"/>
+      <c r="G7" s="348" t="n"/>
+      <c r="H7" s="348" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="323" t="inlineStr">
+      <c r="A8" s="396" t="inlineStr">
         <is>
           <t>WI WI-603</t>
         </is>
       </c>
-      <c r="B8" s="324" t="inlineStr">
+      <c r="B8" s="397" t="inlineStr">
         <is>
           <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
         </is>
       </c>
-      <c r="C8" s="324" t="inlineStr">
+      <c r="C8" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
         </is>
       </c>
+      <c r="D8" s="398" t="n"/>
+      <c r="E8" s="398" t="n"/>
+      <c r="F8" s="398" t="n"/>
+      <c r="G8" s="398" t="n"/>
+      <c r="H8" s="398" t="n"/>
+      <c r="I8" s="398" t="n"/>
+      <c r="J8" s="398" t="n"/>
+      <c r="K8" s="398" t="n"/>
+      <c r="L8" s="398" t="n"/>
+      <c r="M8" s="398" t="n"/>
+      <c r="N8" s="398" t="n"/>
+      <c r="O8" s="398" t="n"/>
+      <c r="P8" s="398" t="n"/>
+      <c r="Q8" s="398" t="n"/>
+      <c r="R8" s="398" t="n"/>
+      <c r="S8" s="398" t="n"/>
+      <c r="T8" s="398" t="n"/>
+      <c r="U8" s="398" t="n"/>
+      <c r="V8" s="398" t="n"/>
+      <c r="W8" s="398" t="n"/>
+      <c r="X8" s="398" t="n"/>
+      <c r="Y8" s="398" t="n"/>
+      <c r="Z8" s="398" t="n"/>
+      <c r="AA8" s="398" t="n"/>
+      <c r="AB8" s="398" t="n"/>
+      <c r="AC8" s="398" t="n"/>
+      <c r="AD8" s="398" t="n"/>
+      <c r="AE8" s="398" t="n"/>
+      <c r="AF8" s="398" t="n"/>
+      <c r="AG8" s="398" t="n"/>
+      <c r="AH8" s="398" t="n"/>
+      <c r="AI8" s="398" t="n"/>
+      <c r="AJ8" s="398" t="n"/>
+      <c r="AK8" s="398" t="n"/>
+      <c r="AL8" s="398" t="n"/>
+      <c r="AM8" s="398" t="n"/>
+      <c r="AN8" s="398" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="323" t="inlineStr">
+      <c r="A9" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="324" t="inlineStr">
+      <c r="B9" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="324" t="inlineStr">
+      <c r="C9" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
+      <c r="D9" s="398" t="n"/>
+      <c r="E9" s="398" t="n"/>
+      <c r="F9" s="398" t="n"/>
+      <c r="G9" s="398" t="n"/>
+      <c r="H9" s="398" t="n"/>
+      <c r="I9" s="398" t="n"/>
+      <c r="J9" s="398" t="n"/>
+      <c r="K9" s="398" t="n"/>
+      <c r="L9" s="398" t="n"/>
+      <c r="M9" s="398" t="n"/>
+      <c r="N9" s="398" t="n"/>
+      <c r="O9" s="398" t="n"/>
+      <c r="P9" s="398" t="n"/>
+      <c r="Q9" s="398" t="n"/>
+      <c r="R9" s="398" t="n"/>
+      <c r="S9" s="398" t="n"/>
+      <c r="T9" s="398" t="n"/>
+      <c r="U9" s="398" t="n"/>
+      <c r="V9" s="398" t="n"/>
+      <c r="W9" s="398" t="n"/>
+      <c r="X9" s="398" t="n"/>
+      <c r="Y9" s="398" t="n"/>
+      <c r="Z9" s="398" t="n"/>
+      <c r="AA9" s="398" t="n"/>
+      <c r="AB9" s="398" t="n"/>
+      <c r="AC9" s="398" t="n"/>
+      <c r="AD9" s="398" t="n"/>
+      <c r="AE9" s="398" t="n"/>
+      <c r="AF9" s="398" t="n"/>
+      <c r="AG9" s="398" t="n"/>
+      <c r="AH9" s="398" t="n"/>
+      <c r="AI9" s="398" t="n"/>
+      <c r="AJ9" s="398" t="n"/>
+      <c r="AK9" s="398" t="n"/>
+      <c r="AL9" s="398" t="n"/>
+      <c r="AM9" s="398" t="n"/>
+      <c r="AN9" s="398" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="323" t="inlineStr">
+      <c r="A10" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="324" t="inlineStr">
+      <c r="B10" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="324" t="inlineStr">
+      <c r="C10" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
+      <c r="D10" s="398" t="n"/>
+      <c r="E10" s="398" t="n"/>
+      <c r="F10" s="398" t="n"/>
+      <c r="G10" s="398" t="n"/>
+      <c r="H10" s="398" t="n"/>
+      <c r="I10" s="398" t="n"/>
+      <c r="J10" s="398" t="n"/>
+      <c r="K10" s="398" t="n"/>
+      <c r="L10" s="398" t="n"/>
+      <c r="M10" s="398" t="n"/>
+      <c r="N10" s="398" t="n"/>
+      <c r="O10" s="398" t="n"/>
+      <c r="P10" s="398" t="n"/>
+      <c r="Q10" s="398" t="n"/>
+      <c r="R10" s="398" t="n"/>
+      <c r="S10" s="398" t="n"/>
+      <c r="T10" s="398" t="n"/>
+      <c r="U10" s="398" t="n"/>
+      <c r="V10" s="398" t="n"/>
+      <c r="W10" s="398" t="n"/>
+      <c r="X10" s="398" t="n"/>
+      <c r="Y10" s="398" t="n"/>
+      <c r="Z10" s="398" t="n"/>
+      <c r="AA10" s="398" t="n"/>
+      <c r="AB10" s="398" t="n"/>
+      <c r="AC10" s="398" t="n"/>
+      <c r="AD10" s="398" t="n"/>
+      <c r="AE10" s="398" t="n"/>
+      <c r="AF10" s="398" t="n"/>
+      <c r="AG10" s="398" t="n"/>
+      <c r="AH10" s="398" t="n"/>
+      <c r="AI10" s="398" t="n"/>
+      <c r="AJ10" s="398" t="n"/>
+      <c r="AK10" s="398" t="n"/>
+      <c r="AL10" s="398" t="n"/>
+      <c r="AM10" s="398" t="n"/>
+      <c r="AN10" s="398" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="323" t="inlineStr">
+      <c r="A11" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="324" t="inlineStr">
+      <c r="B11" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="324" t="inlineStr">
+      <c r="C11" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
+      <c r="D11" s="398" t="n"/>
+      <c r="E11" s="398" t="n"/>
+      <c r="F11" s="398" t="n"/>
+      <c r="G11" s="398" t="n"/>
+      <c r="H11" s="398" t="n"/>
+      <c r="I11" s="398" t="n"/>
+      <c r="J11" s="398" t="n"/>
+      <c r="K11" s="398" t="n"/>
+      <c r="L11" s="398" t="n"/>
+      <c r="M11" s="398" t="n"/>
+      <c r="N11" s="398" t="n"/>
+      <c r="O11" s="398" t="n"/>
+      <c r="P11" s="398" t="n"/>
+      <c r="Q11" s="398" t="n"/>
+      <c r="R11" s="398" t="n"/>
+      <c r="S11" s="398" t="n"/>
+      <c r="T11" s="398" t="n"/>
+      <c r="U11" s="398" t="n"/>
+      <c r="V11" s="398" t="n"/>
+      <c r="W11" s="398" t="n"/>
+      <c r="X11" s="398" t="n"/>
+      <c r="Y11" s="398" t="n"/>
+      <c r="Z11" s="398" t="n"/>
+      <c r="AA11" s="398" t="n"/>
+      <c r="AB11" s="398" t="n"/>
+      <c r="AC11" s="398" t="n"/>
+      <c r="AD11" s="398" t="n"/>
+      <c r="AE11" s="398" t="n"/>
+      <c r="AF11" s="398" t="n"/>
+      <c r="AG11" s="398" t="n"/>
+      <c r="AH11" s="398" t="n"/>
+      <c r="AI11" s="398" t="n"/>
+      <c r="AJ11" s="398" t="n"/>
+      <c r="AK11" s="398" t="n"/>
+      <c r="AL11" s="398" t="n"/>
+      <c r="AM11" s="398" t="n"/>
+      <c r="AN11" s="398" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="323" t="inlineStr">
+      <c r="A12" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="324" t="inlineStr">
+      <c r="B12" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="324" t="inlineStr">
+      <c r="C12" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
+      <c r="D12" s="398" t="n"/>
+      <c r="E12" s="398" t="n"/>
+      <c r="F12" s="398" t="n"/>
+      <c r="G12" s="398" t="n"/>
+      <c r="H12" s="398" t="n"/>
+      <c r="I12" s="398" t="n"/>
+      <c r="J12" s="398" t="n"/>
+      <c r="K12" s="398" t="n"/>
+      <c r="L12" s="398" t="n"/>
+      <c r="M12" s="398" t="n"/>
+      <c r="N12" s="398" t="n"/>
+      <c r="O12" s="398" t="n"/>
+      <c r="P12" s="398" t="n"/>
+      <c r="Q12" s="398" t="n"/>
+      <c r="R12" s="398" t="n"/>
+      <c r="S12" s="398" t="n"/>
+      <c r="T12" s="398" t="n"/>
+      <c r="U12" s="398" t="n"/>
+      <c r="V12" s="398" t="n"/>
+      <c r="W12" s="398" t="n"/>
+      <c r="X12" s="398" t="n"/>
+      <c r="Y12" s="398" t="n"/>
+      <c r="Z12" s="398" t="n"/>
+      <c r="AA12" s="398" t="n"/>
+      <c r="AB12" s="398" t="n"/>
+      <c r="AC12" s="398" t="n"/>
+      <c r="AD12" s="398" t="n"/>
+      <c r="AE12" s="398" t="n"/>
+      <c r="AF12" s="398" t="n"/>
+      <c r="AG12" s="398" t="n"/>
+      <c r="AH12" s="398" t="n"/>
+      <c r="AI12" s="398" t="n"/>
+      <c r="AJ12" s="398" t="n"/>
+      <c r="AK12" s="398" t="n"/>
+      <c r="AL12" s="398" t="n"/>
+      <c r="AM12" s="398" t="n"/>
+      <c r="AN12" s="398" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="323" t="inlineStr">
+      <c r="A13" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="324" t="inlineStr">
+      <c r="B13" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="324" t="inlineStr">
+      <c r="C13" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
+      <c r="D13" s="398" t="n"/>
+      <c r="E13" s="398" t="n"/>
+      <c r="F13" s="398" t="n"/>
+      <c r="G13" s="398" t="n"/>
+      <c r="H13" s="398" t="n"/>
+      <c r="I13" s="398" t="n"/>
+      <c r="J13" s="398" t="n"/>
+      <c r="K13" s="398" t="n"/>
+      <c r="L13" s="398" t="n"/>
+      <c r="M13" s="398" t="n"/>
+      <c r="N13" s="398" t="n"/>
+      <c r="O13" s="398" t="n"/>
+      <c r="P13" s="398" t="n"/>
+      <c r="Q13" s="398" t="n"/>
+      <c r="R13" s="398" t="n"/>
+      <c r="S13" s="398" t="n"/>
+      <c r="T13" s="398" t="n"/>
+      <c r="U13" s="398" t="n"/>
+      <c r="V13" s="398" t="n"/>
+      <c r="W13" s="398" t="n"/>
+      <c r="X13" s="398" t="n"/>
+      <c r="Y13" s="398" t="n"/>
+      <c r="Z13" s="398" t="n"/>
+      <c r="AA13" s="398" t="n"/>
+      <c r="AB13" s="398" t="n"/>
+      <c r="AC13" s="398" t="n"/>
+      <c r="AD13" s="398" t="n"/>
+      <c r="AE13" s="398" t="n"/>
+      <c r="AF13" s="398" t="n"/>
+      <c r="AG13" s="398" t="n"/>
+      <c r="AH13" s="398" t="n"/>
+      <c r="AI13" s="398" t="n"/>
+      <c r="AJ13" s="398" t="n"/>
+      <c r="AK13" s="398" t="n"/>
+      <c r="AL13" s="398" t="n"/>
+      <c r="AM13" s="398" t="n"/>
+      <c r="AN13" s="398" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="323" t="inlineStr">
+      <c r="A14" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="324" t="inlineStr">
+      <c r="B14" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="324" t="inlineStr">
+      <c r="C14" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D14" s="398" t="n"/>
+      <c r="E14" s="398" t="n"/>
+      <c r="F14" s="398" t="n"/>
+      <c r="G14" s="398" t="n"/>
+      <c r="H14" s="398" t="n"/>
+      <c r="I14" s="398" t="n"/>
+      <c r="J14" s="398" t="n"/>
+      <c r="K14" s="398" t="n"/>
+      <c r="L14" s="398" t="n"/>
+      <c r="M14" s="398" t="n"/>
+      <c r="N14" s="398" t="n"/>
+      <c r="O14" s="398" t="n"/>
+      <c r="P14" s="398" t="n"/>
+      <c r="Q14" s="398" t="n"/>
+      <c r="R14" s="398" t="n"/>
+      <c r="S14" s="398" t="n"/>
+      <c r="T14" s="398" t="n"/>
+      <c r="U14" s="398" t="n"/>
+      <c r="V14" s="398" t="n"/>
+      <c r="W14" s="398" t="n"/>
+      <c r="X14" s="398" t="n"/>
+      <c r="Y14" s="398" t="n"/>
+      <c r="Z14" s="398" t="n"/>
+      <c r="AA14" s="398" t="n"/>
+      <c r="AB14" s="398" t="n"/>
+      <c r="AC14" s="398" t="n"/>
+      <c r="AD14" s="398" t="n"/>
+      <c r="AE14" s="398" t="n"/>
+      <c r="AF14" s="398" t="n"/>
+      <c r="AG14" s="398" t="n"/>
+      <c r="AH14" s="398" t="n"/>
+      <c r="AI14" s="398" t="n"/>
+      <c r="AJ14" s="398" t="n"/>
+      <c r="AK14" s="398" t="n"/>
+      <c r="AL14" s="398" t="n"/>
+      <c r="AM14" s="398" t="n"/>
+      <c r="AN14" s="398" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="323" t="inlineStr">
+      <c r="A15" s="396" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="324" t="inlineStr">
+      <c r="B15" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="324" t="inlineStr">
+      <c r="C15" s="397" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
+      <c r="D15" s="398" t="n"/>
+      <c r="E15" s="398" t="n"/>
+      <c r="F15" s="398" t="n"/>
+      <c r="G15" s="398" t="n"/>
+      <c r="H15" s="398" t="n"/>
+      <c r="I15" s="398" t="n"/>
+      <c r="J15" s="398" t="n"/>
+      <c r="K15" s="398" t="n"/>
+      <c r="L15" s="398" t="n"/>
+      <c r="M15" s="398" t="n"/>
+      <c r="N15" s="398" t="n"/>
+      <c r="O15" s="398" t="n"/>
+      <c r="P15" s="398" t="n"/>
+      <c r="Q15" s="398" t="n"/>
+      <c r="R15" s="398" t="n"/>
+      <c r="S15" s="398" t="n"/>
+      <c r="T15" s="398" t="n"/>
+      <c r="U15" s="398" t="n"/>
+      <c r="V15" s="398" t="n"/>
+      <c r="W15" s="398" t="n"/>
+      <c r="X15" s="398" t="n"/>
+      <c r="Y15" s="398" t="n"/>
+      <c r="Z15" s="398" t="n"/>
+      <c r="AA15" s="398" t="n"/>
+      <c r="AB15" s="398" t="n"/>
+      <c r="AC15" s="398" t="n"/>
+      <c r="AD15" s="398" t="n"/>
+      <c r="AE15" s="398" t="n"/>
+      <c r="AF15" s="398" t="n"/>
+      <c r="AG15" s="398" t="n"/>
+      <c r="AH15" s="398" t="n"/>
+      <c r="AI15" s="398" t="n"/>
+      <c r="AJ15" s="398" t="n"/>
+      <c r="AK15" s="398" t="n"/>
+      <c r="AL15" s="398" t="n"/>
+      <c r="AM15" s="398" t="n"/>
+      <c r="AN15" s="398" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -7955,7 +9877,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7965,30 +9888,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="422" t="n"/>
+      <c r="C1" s="422" t="n"/>
+      <c r="D1" s="422" t="n"/>
+      <c r="E1" s="422" t="n"/>
+      <c r="F1" s="422" t="n"/>
+      <c r="G1" s="423" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="321" t="inlineStr">
@@ -7996,92 +9985,351 @@
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="322" t="inlineStr">
+      <c r="A4" s="366" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="322" t="inlineStr">
+      <c r="B4" s="366" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="322" t="inlineStr">
+      <c r="C4" s="366" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="348" t="n"/>
+      <c r="E4" s="348" t="n"/>
+      <c r="F4" s="348" t="n"/>
+      <c r="G4" s="348" t="n"/>
+      <c r="H4" s="348" t="n"/>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="323" t="inlineStr">
+      <c r="A5" s="394" t="inlineStr">
         <is>
           <t>Evidence item 1</t>
         </is>
       </c>
-      <c r="B5" s="324" t="inlineStr">
+      <c r="B5" s="395" t="inlineStr">
         <is>
           <t>Reference to the correct evidence folder, shared location or dossier package.</t>
         </is>
       </c>
-      <c r="C5" s="324" t="inlineStr">
+      <c r="C5" s="395" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
+      <c r="D5" s="348" t="n"/>
+      <c r="E5" s="348" t="n"/>
+      <c r="F5" s="348" t="n"/>
+      <c r="G5" s="348" t="n"/>
+      <c r="H5" s="348" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="323" t="inlineStr">
+      <c r="A6" s="394" t="inlineStr">
         <is>
           <t>Evidence item 2</t>
         </is>
       </c>
-      <c r="B6" s="324" t="inlineStr">
+      <c r="B6" s="395" t="inlineStr">
         <is>
           <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
         </is>
       </c>
-      <c r="C6" s="324" t="inlineStr">
+      <c r="C6" s="395" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
+      <c r="D6" s="348" t="n"/>
+      <c r="E6" s="348" t="n"/>
+      <c r="F6" s="348" t="n"/>
+      <c r="G6" s="348" t="n"/>
+      <c r="H6" s="348" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="323" t="inlineStr">
+      <c r="A7" s="394" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B7" s="324" t="inlineStr">
+      <c r="B7" s="395" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C7" s="324" t="inlineStr">
+      <c r="C7" s="395" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D7" s="348" t="n"/>
+      <c r="E7" s="348" t="n"/>
+      <c r="F7" s="348" t="n"/>
+      <c r="G7" s="348" t="n"/>
+      <c r="H7" s="348" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="323" t="inlineStr">
+      <c r="A8" s="396" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="324" t="inlineStr">
+      <c r="B8" s="397" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="324" t="inlineStr">
+      <c r="C8" s="397" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D8" s="398" t="n"/>
+      <c r="E8" s="398" t="n"/>
+      <c r="F8" s="398" t="n"/>
+      <c r="G8" s="398" t="n"/>
+      <c r="H8" s="398" t="n"/>
+      <c r="I8" s="398" t="n"/>
+      <c r="J8" s="398" t="n"/>
+      <c r="K8" s="398" t="n"/>
+      <c r="L8" s="398" t="n"/>
+      <c r="M8" s="398" t="n"/>
+      <c r="N8" s="398" t="n"/>
+      <c r="O8" s="398" t="n"/>
+      <c r="P8" s="398" t="n"/>
+      <c r="Q8" s="398" t="n"/>
+      <c r="R8" s="398" t="n"/>
+      <c r="S8" s="398" t="n"/>
+      <c r="T8" s="398" t="n"/>
+      <c r="U8" s="398" t="n"/>
+      <c r="V8" s="398" t="n"/>
+      <c r="W8" s="398" t="n"/>
+      <c r="X8" s="398" t="n"/>
+      <c r="Y8" s="398" t="n"/>
+      <c r="Z8" s="398" t="n"/>
+      <c r="AA8" s="398" t="n"/>
+      <c r="AB8" s="398" t="n"/>
+      <c r="AC8" s="398" t="n"/>
+      <c r="AD8" s="398" t="n"/>
+      <c r="AE8" s="398" t="n"/>
+      <c r="AF8" s="398" t="n"/>
+      <c r="AG8" s="398" t="n"/>
+      <c r="AH8" s="398" t="n"/>
+      <c r="AI8" s="398" t="n"/>
+      <c r="AJ8" s="398" t="n"/>
+      <c r="AK8" s="398" t="n"/>
+      <c r="AL8" s="398" t="n"/>
+      <c r="AM8" s="398" t="n"/>
+      <c r="AN8" s="398" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -8090,6 +10338,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="79">
+  <fonts count="84">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -474,8 +474,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -707,8 +734,33 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="291">
+  <borders count="319">
     <border>
       <left/>
       <right/>
@@ -3815,12 +3867,308 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="427">
+  <cellXfs count="542">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4843,6 +5191,333 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="314" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="313" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="315" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="317" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="305" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="308" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="314" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="314" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="314" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="316" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="270" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="304" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="307" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="311" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="302" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="303" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="314" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="313" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="273" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="270" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="273" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="305" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4917,6 +5592,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5287,906 +6082,996 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="340" t="inlineStr"/>
-      <c r="B1" s="421" t="n"/>
-      <c r="C1" s="421" t="n"/>
-      <c r="D1" s="421" t="n"/>
-      <c r="E1" s="421" t="n"/>
-      <c r="F1" s="421" t="n"/>
-      <c r="G1" s="421" t="n"/>
-      <c r="H1" s="421" t="n"/>
-      <c r="I1" s="421" t="n"/>
-      <c r="J1" s="421" t="n"/>
-      <c r="K1" s="421" t="n"/>
-      <c r="L1" s="342" t="inlineStr">
+      <c r="A1" s="427" t="inlineStr"/>
+      <c r="B1" s="428" t="n"/>
+      <c r="C1" s="428" t="n"/>
+      <c r="D1" s="428" t="n"/>
+      <c r="E1" s="428" t="n"/>
+      <c r="F1" s="428" t="n"/>
+      <c r="G1" s="428" t="n"/>
+      <c r="H1" s="428" t="n"/>
+      <c r="I1" s="428" t="n"/>
+      <c r="J1" s="428" t="n"/>
+      <c r="K1" s="429" t="n"/>
+      <c r="L1" s="430" t="inlineStr">
         <is>
           <t>AQL Inspection Record</t>
         </is>
       </c>
-      <c r="M1" s="421" t="n"/>
-      <c r="N1" s="421" t="n"/>
-      <c r="O1" s="421" t="n"/>
-      <c r="P1" s="421" t="n"/>
-      <c r="Q1" s="421" t="n"/>
-      <c r="R1" s="421" t="n"/>
-      <c r="S1" s="421" t="n"/>
-      <c r="T1" s="421" t="n"/>
-      <c r="U1" s="421" t="n"/>
-      <c r="V1" s="421" t="n"/>
-      <c r="W1" s="421" t="n"/>
-      <c r="X1" s="421" t="n"/>
-      <c r="Y1" s="421" t="n"/>
-      <c r="Z1" s="421" t="n"/>
-      <c r="AA1" s="421" t="n"/>
-      <c r="AB1" s="421" t="n"/>
-      <c r="AC1" s="421" t="n"/>
-      <c r="AD1" s="421" t="n"/>
-      <c r="AE1" s="421" t="n"/>
-      <c r="AF1" s="421" t="n"/>
-      <c r="AG1" s="421" t="n"/>
-      <c r="AH1" s="421" t="n"/>
-      <c r="AI1" s="421" t="n"/>
-      <c r="AJ1" s="421" t="n"/>
-      <c r="AK1" s="421" t="n"/>
-      <c r="AL1" s="421" t="n"/>
-      <c r="AM1" s="421" t="n"/>
-      <c r="AN1" s="421" t="n"/>
-      <c r="AO1" s="421" t="n"/>
-      <c r="AP1" s="421" t="n"/>
-      <c r="AQ1" s="343" t="inlineStr">
+      <c r="M1" s="431" t="n"/>
+      <c r="N1" s="431" t="n"/>
+      <c r="O1" s="431" t="n"/>
+      <c r="P1" s="431" t="n"/>
+      <c r="Q1" s="431" t="n"/>
+      <c r="R1" s="431" t="n"/>
+      <c r="S1" s="431" t="n"/>
+      <c r="T1" s="431" t="n"/>
+      <c r="U1" s="431" t="n"/>
+      <c r="V1" s="431" t="n"/>
+      <c r="W1" s="431" t="n"/>
+      <c r="X1" s="431" t="n"/>
+      <c r="Y1" s="431" t="n"/>
+      <c r="Z1" s="431" t="n"/>
+      <c r="AA1" s="431" t="n"/>
+      <c r="AB1" s="431" t="n"/>
+      <c r="AC1" s="431" t="n"/>
+      <c r="AD1" s="431" t="n"/>
+      <c r="AE1" s="431" t="n"/>
+      <c r="AF1" s="431" t="n"/>
+      <c r="AG1" s="431" t="n"/>
+      <c r="AH1" s="431" t="n"/>
+      <c r="AI1" s="431" t="n"/>
+      <c r="AJ1" s="431" t="n"/>
+      <c r="AK1" s="431" t="n"/>
+      <c r="AL1" s="431" t="n"/>
+      <c r="AM1" s="431" t="n"/>
+      <c r="AN1" s="431" t="n"/>
+      <c r="AO1" s="431" t="n"/>
+      <c r="AP1" s="432" t="n"/>
+      <c r="AQ1" s="433" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="422" t="n"/>
-      <c r="AS1" s="422" t="n"/>
-      <c r="AT1" s="422" t="n"/>
-      <c r="AU1" s="422" t="n"/>
-      <c r="AV1" s="423" t="n"/>
-      <c r="AW1" s="346" t="inlineStr">
+      <c r="AR1" s="434" t="n"/>
+      <c r="AS1" s="434" t="n"/>
+      <c r="AT1" s="434" t="n"/>
+      <c r="AU1" s="434" t="n"/>
+      <c r="AV1" s="435" t="n"/>
+      <c r="AW1" s="436" t="inlineStr">
         <is>
           <t>FRM-621</t>
         </is>
       </c>
-      <c r="AX1" s="422" t="n"/>
-      <c r="AY1" s="422" t="n"/>
-      <c r="AZ1" s="422" t="n"/>
-      <c r="BA1" s="422" t="n"/>
-      <c r="BB1" s="422" t="n"/>
-      <c r="BC1" s="422" t="n"/>
-      <c r="BD1" s="423" t="n"/>
+      <c r="AX1" s="437" t="n"/>
+      <c r="AY1" s="437" t="n"/>
+      <c r="AZ1" s="437" t="n"/>
+      <c r="BA1" s="437" t="n"/>
+      <c r="BB1" s="437" t="n"/>
+      <c r="BC1" s="437" t="n"/>
+      <c r="BD1" s="438" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="424" t="n"/>
-      <c r="L2" s="424" t="n"/>
-      <c r="AQ2" s="343" t="inlineStr">
+      <c r="A2" s="439" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="25" t="n"/>
+      <c r="I2" s="25" t="n"/>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="440" t="n"/>
+      <c r="L2" s="441" t="n"/>
+      <c r="M2" s="442" t="n"/>
+      <c r="N2" s="442" t="n"/>
+      <c r="O2" s="442" t="n"/>
+      <c r="P2" s="442" t="n"/>
+      <c r="Q2" s="442" t="n"/>
+      <c r="R2" s="442" t="n"/>
+      <c r="S2" s="442" t="n"/>
+      <c r="T2" s="442" t="n"/>
+      <c r="U2" s="442" t="n"/>
+      <c r="V2" s="442" t="n"/>
+      <c r="W2" s="442" t="n"/>
+      <c r="X2" s="442" t="n"/>
+      <c r="Y2" s="442" t="n"/>
+      <c r="Z2" s="442" t="n"/>
+      <c r="AA2" s="442" t="n"/>
+      <c r="AB2" s="442" t="n"/>
+      <c r="AC2" s="442" t="n"/>
+      <c r="AD2" s="442" t="n"/>
+      <c r="AE2" s="442" t="n"/>
+      <c r="AF2" s="442" t="n"/>
+      <c r="AG2" s="442" t="n"/>
+      <c r="AH2" s="442" t="n"/>
+      <c r="AI2" s="442" t="n"/>
+      <c r="AJ2" s="442" t="n"/>
+      <c r="AK2" s="442" t="n"/>
+      <c r="AL2" s="442" t="n"/>
+      <c r="AM2" s="442" t="n"/>
+      <c r="AN2" s="442" t="n"/>
+      <c r="AO2" s="442" t="n"/>
+      <c r="AP2" s="443" t="n"/>
+      <c r="AQ2" s="444" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="422" t="n"/>
-      <c r="AS2" s="422" t="n"/>
-      <c r="AT2" s="422" t="n"/>
-      <c r="AU2" s="422" t="n"/>
-      <c r="AV2" s="423" t="n"/>
-      <c r="AW2" s="346" t="inlineStr">
+      <c r="AR2" s="445" t="n"/>
+      <c r="AS2" s="445" t="n"/>
+      <c r="AT2" s="445" t="n"/>
+      <c r="AU2" s="445" t="n"/>
+      <c r="AV2" s="446" t="n"/>
+      <c r="AW2" s="447" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="422" t="n"/>
-      <c r="AY2" s="422" t="n"/>
-      <c r="AZ2" s="422" t="n"/>
-      <c r="BA2" s="422" t="n"/>
-      <c r="BB2" s="422" t="n"/>
-      <c r="BC2" s="422" t="n"/>
-      <c r="BD2" s="423" t="n"/>
+      <c r="AX2" s="448" t="n"/>
+      <c r="AY2" s="448" t="n"/>
+      <c r="AZ2" s="448" t="n"/>
+      <c r="BA2" s="448" t="n"/>
+      <c r="BB2" s="448" t="n"/>
+      <c r="BC2" s="448" t="n"/>
+      <c r="BD2" s="449" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="424" t="n"/>
-      <c r="L3" s="425" t="n"/>
-      <c r="M3" s="426" t="n"/>
-      <c r="N3" s="426" t="n"/>
-      <c r="O3" s="426" t="n"/>
-      <c r="P3" s="426" t="n"/>
-      <c r="Q3" s="426" t="n"/>
-      <c r="R3" s="426" t="n"/>
-      <c r="S3" s="426" t="n"/>
-      <c r="T3" s="426" t="n"/>
-      <c r="U3" s="426" t="n"/>
-      <c r="V3" s="426" t="n"/>
-      <c r="W3" s="426" t="n"/>
-      <c r="X3" s="426" t="n"/>
-      <c r="Y3" s="426" t="n"/>
-      <c r="Z3" s="426" t="n"/>
-      <c r="AA3" s="426" t="n"/>
-      <c r="AB3" s="426" t="n"/>
-      <c r="AC3" s="426" t="n"/>
-      <c r="AD3" s="426" t="n"/>
-      <c r="AE3" s="426" t="n"/>
-      <c r="AF3" s="426" t="n"/>
-      <c r="AG3" s="426" t="n"/>
-      <c r="AH3" s="426" t="n"/>
-      <c r="AI3" s="426" t="n"/>
-      <c r="AJ3" s="426" t="n"/>
-      <c r="AK3" s="426" t="n"/>
-      <c r="AL3" s="426" t="n"/>
-      <c r="AM3" s="426" t="n"/>
-      <c r="AN3" s="426" t="n"/>
-      <c r="AO3" s="426" t="n"/>
-      <c r="AP3" s="426" t="n"/>
-      <c r="AQ3" s="343" t="inlineStr">
+      <c r="A3" s="439" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="440" t="n"/>
+      <c r="L3" s="441" t="n"/>
+      <c r="M3" s="442" t="n"/>
+      <c r="N3" s="442" t="n"/>
+      <c r="O3" s="442" t="n"/>
+      <c r="P3" s="442" t="n"/>
+      <c r="Q3" s="442" t="n"/>
+      <c r="R3" s="442" t="n"/>
+      <c r="S3" s="442" t="n"/>
+      <c r="T3" s="442" t="n"/>
+      <c r="U3" s="442" t="n"/>
+      <c r="V3" s="442" t="n"/>
+      <c r="W3" s="442" t="n"/>
+      <c r="X3" s="442" t="n"/>
+      <c r="Y3" s="442" t="n"/>
+      <c r="Z3" s="442" t="n"/>
+      <c r="AA3" s="442" t="n"/>
+      <c r="AB3" s="442" t="n"/>
+      <c r="AC3" s="442" t="n"/>
+      <c r="AD3" s="442" t="n"/>
+      <c r="AE3" s="442" t="n"/>
+      <c r="AF3" s="442" t="n"/>
+      <c r="AG3" s="442" t="n"/>
+      <c r="AH3" s="442" t="n"/>
+      <c r="AI3" s="442" t="n"/>
+      <c r="AJ3" s="442" t="n"/>
+      <c r="AK3" s="442" t="n"/>
+      <c r="AL3" s="442" t="n"/>
+      <c r="AM3" s="442" t="n"/>
+      <c r="AN3" s="442" t="n"/>
+      <c r="AO3" s="442" t="n"/>
+      <c r="AP3" s="443" t="n"/>
+      <c r="AQ3" s="444" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="422" t="n"/>
-      <c r="AS3" s="422" t="n"/>
-      <c r="AT3" s="422" t="n"/>
-      <c r="AU3" s="422" t="n"/>
-      <c r="AV3" s="423" t="n"/>
-      <c r="AW3" s="346" t="inlineStr">
+      <c r="AR3" s="445" t="n"/>
+      <c r="AS3" s="445" t="n"/>
+      <c r="AT3" s="445" t="n"/>
+      <c r="AU3" s="445" t="n"/>
+      <c r="AV3" s="446" t="n"/>
+      <c r="AW3" s="447" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="422" t="n"/>
-      <c r="AY3" s="422" t="n"/>
-      <c r="AZ3" s="422" t="n"/>
-      <c r="BA3" s="422" t="n"/>
-      <c r="BB3" s="422" t="n"/>
-      <c r="BC3" s="422" t="n"/>
-      <c r="BD3" s="423" t="n"/>
+      <c r="AX3" s="448" t="n"/>
+      <c r="AY3" s="448" t="n"/>
+      <c r="AZ3" s="448" t="n"/>
+      <c r="BA3" s="448" t="n"/>
+      <c r="BB3" s="448" t="n"/>
+      <c r="BC3" s="448" t="n"/>
+      <c r="BD3" s="449" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="424" t="n"/>
-      <c r="L4" s="351" t="inlineStr">
+      <c r="A4" s="439" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="440" t="n"/>
+      <c r="L4" s="450" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="343" t="inlineStr">
+      <c r="M4" s="451" t="n"/>
+      <c r="N4" s="451" t="n"/>
+      <c r="O4" s="451" t="n"/>
+      <c r="P4" s="451" t="n"/>
+      <c r="Q4" s="451" t="n"/>
+      <c r="R4" s="451" t="n"/>
+      <c r="S4" s="451" t="n"/>
+      <c r="T4" s="451" t="n"/>
+      <c r="U4" s="451" t="n"/>
+      <c r="V4" s="451" t="n"/>
+      <c r="W4" s="451" t="n"/>
+      <c r="X4" s="451" t="n"/>
+      <c r="Y4" s="451" t="n"/>
+      <c r="Z4" s="451" t="n"/>
+      <c r="AA4" s="451" t="n"/>
+      <c r="AB4" s="451" t="n"/>
+      <c r="AC4" s="451" t="n"/>
+      <c r="AD4" s="451" t="n"/>
+      <c r="AE4" s="451" t="n"/>
+      <c r="AF4" s="451" t="n"/>
+      <c r="AG4" s="451" t="n"/>
+      <c r="AH4" s="451" t="n"/>
+      <c r="AI4" s="451" t="n"/>
+      <c r="AJ4" s="451" t="n"/>
+      <c r="AK4" s="451" t="n"/>
+      <c r="AL4" s="451" t="n"/>
+      <c r="AM4" s="451" t="n"/>
+      <c r="AN4" s="451" t="n"/>
+      <c r="AO4" s="451" t="n"/>
+      <c r="AP4" s="452" t="n"/>
+      <c r="AQ4" s="444" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="422" t="n"/>
-      <c r="AS4" s="422" t="n"/>
-      <c r="AT4" s="422" t="n"/>
-      <c r="AU4" s="422" t="n"/>
-      <c r="AV4" s="423" t="n"/>
-      <c r="AW4" s="346" t="inlineStr">
+      <c r="AR4" s="445" t="n"/>
+      <c r="AS4" s="445" t="n"/>
+      <c r="AT4" s="445" t="n"/>
+      <c r="AU4" s="445" t="n"/>
+      <c r="AV4" s="446" t="n"/>
+      <c r="AW4" s="447" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="422" t="n"/>
-      <c r="AY4" s="422" t="n"/>
-      <c r="AZ4" s="422" t="n"/>
-      <c r="BA4" s="422" t="n"/>
-      <c r="BB4" s="422" t="n"/>
-      <c r="BC4" s="422" t="n"/>
-      <c r="BD4" s="423" t="n"/>
+      <c r="AX4" s="448" t="n"/>
+      <c r="AY4" s="448" t="n"/>
+      <c r="AZ4" s="448" t="n"/>
+      <c r="BA4" s="448" t="n"/>
+      <c r="BB4" s="448" t="n"/>
+      <c r="BC4" s="448" t="n"/>
+      <c r="BD4" s="449" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="425" t="n"/>
-      <c r="B5" s="426" t="n"/>
-      <c r="C5" s="426" t="n"/>
-      <c r="D5" s="426" t="n"/>
-      <c r="E5" s="426" t="n"/>
-      <c r="F5" s="426" t="n"/>
-      <c r="G5" s="426" t="n"/>
-      <c r="H5" s="426" t="n"/>
-      <c r="I5" s="426" t="n"/>
-      <c r="J5" s="426" t="n"/>
-      <c r="K5" s="426" t="n"/>
-      <c r="L5" s="352" t="inlineStr">
+      <c r="A5" s="453" t="n"/>
+      <c r="B5" s="454" t="n"/>
+      <c r="C5" s="454" t="n"/>
+      <c r="D5" s="454" t="n"/>
+      <c r="E5" s="454" t="n"/>
+      <c r="F5" s="454" t="n"/>
+      <c r="G5" s="454" t="n"/>
+      <c r="H5" s="454" t="n"/>
+      <c r="I5" s="454" t="n"/>
+      <c r="J5" s="454" t="n"/>
+      <c r="K5" s="455" t="n"/>
+      <c r="L5" s="456" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="426" t="n"/>
-      <c r="N5" s="426" t="n"/>
-      <c r="O5" s="426" t="n"/>
-      <c r="P5" s="426" t="n"/>
-      <c r="Q5" s="426" t="n"/>
-      <c r="R5" s="426" t="n"/>
-      <c r="S5" s="426" t="n"/>
-      <c r="T5" s="426" t="n"/>
-      <c r="U5" s="426" t="n"/>
-      <c r="V5" s="426" t="n"/>
-      <c r="W5" s="426" t="n"/>
-      <c r="X5" s="426" t="n"/>
-      <c r="Y5" s="426" t="n"/>
-      <c r="Z5" s="426" t="n"/>
-      <c r="AA5" s="426" t="n"/>
-      <c r="AB5" s="426" t="n"/>
-      <c r="AC5" s="426" t="n"/>
-      <c r="AD5" s="426" t="n"/>
-      <c r="AE5" s="426" t="n"/>
-      <c r="AF5" s="426" t="n"/>
-      <c r="AG5" s="426" t="n"/>
-      <c r="AH5" s="426" t="n"/>
-      <c r="AI5" s="426" t="n"/>
-      <c r="AJ5" s="426" t="n"/>
-      <c r="AK5" s="426" t="n"/>
-      <c r="AL5" s="426" t="n"/>
-      <c r="AM5" s="426" t="n"/>
-      <c r="AN5" s="426" t="n"/>
-      <c r="AO5" s="426" t="n"/>
-      <c r="AP5" s="426" t="n"/>
-      <c r="AQ5" s="343" t="inlineStr">
+      <c r="M5" s="457" t="n"/>
+      <c r="N5" s="457" t="n"/>
+      <c r="O5" s="457" t="n"/>
+      <c r="P5" s="457" t="n"/>
+      <c r="Q5" s="457" t="n"/>
+      <c r="R5" s="457" t="n"/>
+      <c r="S5" s="457" t="n"/>
+      <c r="T5" s="457" t="n"/>
+      <c r="U5" s="457" t="n"/>
+      <c r="V5" s="457" t="n"/>
+      <c r="W5" s="457" t="n"/>
+      <c r="X5" s="457" t="n"/>
+      <c r="Y5" s="457" t="n"/>
+      <c r="Z5" s="457" t="n"/>
+      <c r="AA5" s="457" t="n"/>
+      <c r="AB5" s="457" t="n"/>
+      <c r="AC5" s="457" t="n"/>
+      <c r="AD5" s="457" t="n"/>
+      <c r="AE5" s="457" t="n"/>
+      <c r="AF5" s="457" t="n"/>
+      <c r="AG5" s="457" t="n"/>
+      <c r="AH5" s="457" t="n"/>
+      <c r="AI5" s="457" t="n"/>
+      <c r="AJ5" s="457" t="n"/>
+      <c r="AK5" s="457" t="n"/>
+      <c r="AL5" s="457" t="n"/>
+      <c r="AM5" s="457" t="n"/>
+      <c r="AN5" s="457" t="n"/>
+      <c r="AO5" s="457" t="n"/>
+      <c r="AP5" s="458" t="n"/>
+      <c r="AQ5" s="459" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="422" t="n"/>
-      <c r="AS5" s="422" t="n"/>
-      <c r="AT5" s="422" t="n"/>
-      <c r="AU5" s="422" t="n"/>
-      <c r="AV5" s="423" t="n"/>
-      <c r="AW5" s="346" t="inlineStr">
+      <c r="AR5" s="460" t="n"/>
+      <c r="AS5" s="460" t="n"/>
+      <c r="AT5" s="460" t="n"/>
+      <c r="AU5" s="460" t="n"/>
+      <c r="AV5" s="461" t="n"/>
+      <c r="AW5" s="462" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="422" t="n"/>
-      <c r="AY5" s="422" t="n"/>
-      <c r="AZ5" s="422" t="n"/>
-      <c r="BA5" s="422" t="n"/>
-      <c r="BB5" s="422" t="n"/>
-      <c r="BC5" s="422" t="n"/>
-      <c r="BD5" s="423" t="n"/>
+      <c r="AX5" s="463" t="n"/>
+      <c r="AY5" s="463" t="n"/>
+      <c r="AZ5" s="463" t="n"/>
+      <c r="BA5" s="463" t="n"/>
+      <c r="BB5" s="463" t="n"/>
+      <c r="BC5" s="463" t="n"/>
+      <c r="BD5" s="464" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="353" t="inlineStr"/>
-      <c r="B6" s="420" t="n"/>
-      <c r="C6" s="420" t="n"/>
-      <c r="D6" s="420" t="n"/>
-      <c r="E6" s="420" t="n"/>
-      <c r="F6" s="420" t="n"/>
-      <c r="G6" s="420" t="n"/>
-      <c r="H6" s="420" t="n"/>
-      <c r="I6" s="420" t="n"/>
-      <c r="J6" s="420" t="n"/>
-      <c r="K6" s="420" t="n"/>
-      <c r="L6" s="420" t="n"/>
-      <c r="M6" s="420" t="n"/>
-      <c r="N6" s="420" t="n"/>
-      <c r="O6" s="420" t="n"/>
-      <c r="P6" s="420" t="n"/>
-      <c r="Q6" s="420" t="n"/>
-      <c r="R6" s="420" t="n"/>
-      <c r="S6" s="420" t="n"/>
-      <c r="T6" s="420" t="n"/>
-      <c r="U6" s="420" t="n"/>
-      <c r="V6" s="420" t="n"/>
-      <c r="W6" s="420" t="n"/>
-      <c r="X6" s="420" t="n"/>
-      <c r="Y6" s="420" t="n"/>
-      <c r="Z6" s="420" t="n"/>
-      <c r="AA6" s="420" t="n"/>
-      <c r="AB6" s="420" t="n"/>
-      <c r="AC6" s="420" t="n"/>
-      <c r="AD6" s="420" t="n"/>
-      <c r="AE6" s="420" t="n"/>
-      <c r="AF6" s="420" t="n"/>
-      <c r="AG6" s="420" t="n"/>
-      <c r="AH6" s="420" t="n"/>
-      <c r="AI6" s="420" t="n"/>
-      <c r="AJ6" s="420" t="n"/>
-      <c r="AK6" s="420" t="n"/>
-      <c r="AL6" s="420" t="n"/>
-      <c r="AM6" s="420" t="n"/>
-      <c r="AN6" s="420" t="n"/>
-      <c r="AO6" s="420" t="n"/>
-      <c r="AP6" s="420" t="n"/>
-      <c r="AQ6" s="420" t="n"/>
-      <c r="AR6" s="420" t="n"/>
-      <c r="AS6" s="420" t="n"/>
-      <c r="AT6" s="420" t="n"/>
-      <c r="AU6" s="420" t="n"/>
-      <c r="AV6" s="420" t="n"/>
-      <c r="AW6" s="420" t="n"/>
-      <c r="AX6" s="420" t="n"/>
-      <c r="AY6" s="420" t="n"/>
-      <c r="AZ6" s="420" t="n"/>
-      <c r="BA6" s="420" t="n"/>
-      <c r="BB6" s="420" t="n"/>
-      <c r="BC6" s="420" t="n"/>
-      <c r="BD6" s="420" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="465" t="n"/>
+      <c r="B6" s="465" t="n"/>
+      <c r="C6" s="465" t="n"/>
+      <c r="D6" s="465" t="n"/>
+      <c r="E6" s="465" t="n"/>
+      <c r="F6" s="465" t="n"/>
+      <c r="G6" s="465" t="n"/>
+      <c r="H6" s="465" t="n"/>
+      <c r="I6" s="465" t="n"/>
+      <c r="J6" s="465" t="n"/>
+      <c r="K6" s="465" t="n"/>
+      <c r="L6" s="465" t="n"/>
+      <c r="M6" s="465" t="n"/>
+      <c r="N6" s="465" t="n"/>
+      <c r="O6" s="465" t="n"/>
+      <c r="P6" s="465" t="n"/>
+      <c r="Q6" s="465" t="n"/>
+      <c r="R6" s="465" t="n"/>
+      <c r="S6" s="465" t="n"/>
+      <c r="T6" s="465" t="n"/>
+      <c r="U6" s="465" t="n"/>
+      <c r="V6" s="465" t="n"/>
+      <c r="W6" s="465" t="n"/>
+      <c r="X6" s="465" t="n"/>
+      <c r="Y6" s="465" t="n"/>
+      <c r="Z6" s="465" t="n"/>
+      <c r="AA6" s="465" t="n"/>
+      <c r="AB6" s="465" t="n"/>
+      <c r="AC6" s="465" t="n"/>
+      <c r="AD6" s="465" t="n"/>
+      <c r="AE6" s="465" t="n"/>
+      <c r="AF6" s="465" t="n"/>
+      <c r="AG6" s="465" t="n"/>
+      <c r="AH6" s="465" t="n"/>
+      <c r="AI6" s="465" t="n"/>
+      <c r="AJ6" s="465" t="n"/>
+      <c r="AK6" s="465" t="n"/>
+      <c r="AL6" s="465" t="n"/>
+      <c r="AM6" s="465" t="n"/>
+      <c r="AN6" s="465" t="n"/>
+      <c r="AO6" s="465" t="n"/>
+      <c r="AP6" s="465" t="n"/>
+      <c r="AQ6" s="465" t="n"/>
+      <c r="AR6" s="465" t="n"/>
+      <c r="AS6" s="465" t="n"/>
+      <c r="AT6" s="465" t="n"/>
+      <c r="AU6" s="465" t="n"/>
+      <c r="AV6" s="465" t="n"/>
+      <c r="AW6" s="465" t="n"/>
+      <c r="AX6" s="465" t="n"/>
+      <c r="AY6" s="465" t="n"/>
+      <c r="AZ6" s="465" t="n"/>
+      <c r="BA6" s="465" t="n"/>
+      <c r="BB6" s="465" t="n"/>
+      <c r="BC6" s="465" t="n"/>
+      <c r="BD6" s="465" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="354" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="466" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="422" t="n"/>
-      <c r="C7" s="422" t="n"/>
-      <c r="D7" s="422" t="n"/>
-      <c r="E7" s="422" t="n"/>
-      <c r="F7" s="422" t="n"/>
-      <c r="G7" s="422" t="n"/>
-      <c r="H7" s="422" t="n"/>
-      <c r="I7" s="422" t="n"/>
-      <c r="J7" s="422" t="n"/>
-      <c r="K7" s="422" t="n"/>
-      <c r="L7" s="422" t="n"/>
-      <c r="M7" s="422" t="n"/>
-      <c r="N7" s="422" t="n"/>
-      <c r="O7" s="422" t="n"/>
-      <c r="P7" s="422" t="n"/>
-      <c r="Q7" s="422" t="n"/>
-      <c r="R7" s="422" t="n"/>
-      <c r="S7" s="422" t="n"/>
-      <c r="T7" s="422" t="n"/>
-      <c r="U7" s="422" t="n"/>
-      <c r="V7" s="422" t="n"/>
-      <c r="W7" s="422" t="n"/>
-      <c r="X7" s="422" t="n"/>
-      <c r="Y7" s="422" t="n"/>
-      <c r="Z7" s="422" t="n"/>
-      <c r="AA7" s="422" t="n"/>
-      <c r="AB7" s="422" t="n"/>
-      <c r="AC7" s="422" t="n"/>
-      <c r="AD7" s="422" t="n"/>
-      <c r="AE7" s="422" t="n"/>
-      <c r="AF7" s="422" t="n"/>
-      <c r="AG7" s="422" t="n"/>
-      <c r="AH7" s="422" t="n"/>
-      <c r="AI7" s="422" t="n"/>
-      <c r="AJ7" s="422" t="n"/>
-      <c r="AK7" s="422" t="n"/>
-      <c r="AL7" s="422" t="n"/>
-      <c r="AM7" s="422" t="n"/>
-      <c r="AN7" s="422" t="n"/>
-      <c r="AO7" s="422" t="n"/>
-      <c r="AP7" s="422" t="n"/>
-      <c r="AQ7" s="422" t="n"/>
-      <c r="AR7" s="422" t="n"/>
-      <c r="AS7" s="422" t="n"/>
-      <c r="AT7" s="422" t="n"/>
-      <c r="AU7" s="422" t="n"/>
-      <c r="AV7" s="422" t="n"/>
-      <c r="AW7" s="422" t="n"/>
-      <c r="AX7" s="422" t="n"/>
-      <c r="AY7" s="422" t="n"/>
-      <c r="AZ7" s="422" t="n"/>
-      <c r="BA7" s="422" t="n"/>
-      <c r="BB7" s="422" t="n"/>
-      <c r="BC7" s="422" t="n"/>
-      <c r="BD7" s="423" t="n"/>
+      <c r="B7" s="467" t="n"/>
+      <c r="C7" s="467" t="n"/>
+      <c r="D7" s="467" t="n"/>
+      <c r="E7" s="467" t="n"/>
+      <c r="F7" s="467" t="n"/>
+      <c r="G7" s="467" t="n"/>
+      <c r="H7" s="467" t="n"/>
+      <c r="I7" s="467" t="n"/>
+      <c r="J7" s="467" t="n"/>
+      <c r="K7" s="467" t="n"/>
+      <c r="L7" s="467" t="n"/>
+      <c r="M7" s="467" t="n"/>
+      <c r="N7" s="467" t="n"/>
+      <c r="O7" s="467" t="n"/>
+      <c r="P7" s="467" t="n"/>
+      <c r="Q7" s="467" t="n"/>
+      <c r="R7" s="467" t="n"/>
+      <c r="S7" s="467" t="n"/>
+      <c r="T7" s="467" t="n"/>
+      <c r="U7" s="467" t="n"/>
+      <c r="V7" s="467" t="n"/>
+      <c r="W7" s="467" t="n"/>
+      <c r="X7" s="467" t="n"/>
+      <c r="Y7" s="467" t="n"/>
+      <c r="Z7" s="467" t="n"/>
+      <c r="AA7" s="467" t="n"/>
+      <c r="AB7" s="467" t="n"/>
+      <c r="AC7" s="467" t="n"/>
+      <c r="AD7" s="467" t="n"/>
+      <c r="AE7" s="467" t="n"/>
+      <c r="AF7" s="467" t="n"/>
+      <c r="AG7" s="467" t="n"/>
+      <c r="AH7" s="467" t="n"/>
+      <c r="AI7" s="467" t="n"/>
+      <c r="AJ7" s="467" t="n"/>
+      <c r="AK7" s="467" t="n"/>
+      <c r="AL7" s="467" t="n"/>
+      <c r="AM7" s="467" t="n"/>
+      <c r="AN7" s="467" t="n"/>
+      <c r="AO7" s="467" t="n"/>
+      <c r="AP7" s="467" t="n"/>
+      <c r="AQ7" s="467" t="n"/>
+      <c r="AR7" s="467" t="n"/>
+      <c r="AS7" s="467" t="n"/>
+      <c r="AT7" s="467" t="n"/>
+      <c r="AU7" s="467" t="n"/>
+      <c r="AV7" s="467" t="n"/>
+      <c r="AW7" s="467" t="n"/>
+      <c r="AX7" s="467" t="n"/>
+      <c r="AY7" s="467" t="n"/>
+      <c r="AZ7" s="467" t="n"/>
+      <c r="BA7" s="467" t="n"/>
+      <c r="BB7" s="467" t="n"/>
+      <c r="BC7" s="467" t="n"/>
+      <c r="BD7" s="468" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="355" t="inlineStr">
+      <c r="A8" s="469" t="inlineStr">
         <is>
           <t>Customer / PO Line</t>
         </is>
       </c>
-      <c r="B8" s="405" t="n"/>
-      <c r="C8" s="405" t="n"/>
-      <c r="D8" s="405" t="n"/>
-      <c r="E8" s="405" t="n"/>
-      <c r="F8" s="405" t="n"/>
-      <c r="G8" s="405" t="n"/>
-      <c r="H8" s="405" t="n"/>
-      <c r="I8" s="405" t="n"/>
-      <c r="J8" s="406" t="n"/>
-      <c r="K8" s="358" t="n"/>
-      <c r="L8" s="407" t="n"/>
-      <c r="M8" s="407" t="n"/>
-      <c r="N8" s="407" t="n"/>
-      <c r="O8" s="407" t="n"/>
-      <c r="P8" s="407" t="n"/>
-      <c r="Q8" s="407" t="n"/>
-      <c r="R8" s="407" t="n"/>
-      <c r="S8" s="407" t="n"/>
-      <c r="T8" s="407" t="n"/>
-      <c r="U8" s="407" t="n"/>
-      <c r="V8" s="407" t="n"/>
-      <c r="W8" s="407" t="n"/>
-      <c r="X8" s="407" t="n"/>
-      <c r="Y8" s="407" t="n"/>
-      <c r="Z8" s="407" t="n"/>
-      <c r="AA8" s="407" t="n"/>
-      <c r="AB8" s="408" t="n"/>
-      <c r="AC8" s="361" t="inlineStr">
+      <c r="B8" s="470" t="n"/>
+      <c r="C8" s="470" t="n"/>
+      <c r="D8" s="470" t="n"/>
+      <c r="E8" s="470" t="n"/>
+      <c r="F8" s="470" t="n"/>
+      <c r="G8" s="470" t="n"/>
+      <c r="H8" s="470" t="n"/>
+      <c r="I8" s="470" t="n"/>
+      <c r="J8" s="470" t="n"/>
+      <c r="K8" s="471" t="n"/>
+      <c r="L8" s="472" t="n"/>
+      <c r="M8" s="472" t="n"/>
+      <c r="N8" s="472" t="n"/>
+      <c r="O8" s="472" t="n"/>
+      <c r="P8" s="472" t="n"/>
+      <c r="Q8" s="472" t="n"/>
+      <c r="R8" s="472" t="n"/>
+      <c r="S8" s="472" t="n"/>
+      <c r="T8" s="472" t="n"/>
+      <c r="U8" s="472" t="n"/>
+      <c r="V8" s="472" t="n"/>
+      <c r="W8" s="472" t="n"/>
+      <c r="X8" s="472" t="n"/>
+      <c r="Y8" s="472" t="n"/>
+      <c r="Z8" s="472" t="n"/>
+      <c r="AA8" s="472" t="n"/>
+      <c r="AB8" s="472" t="n"/>
+      <c r="AC8" s="473" t="inlineStr">
         <is>
           <t>Inspection Record ID</t>
         </is>
       </c>
-      <c r="AD8" s="405" t="n"/>
-      <c r="AE8" s="405" t="n"/>
-      <c r="AF8" s="405" t="n"/>
-      <c r="AG8" s="405" t="n"/>
-      <c r="AH8" s="405" t="n"/>
-      <c r="AI8" s="405" t="n"/>
-      <c r="AJ8" s="405" t="n"/>
-      <c r="AK8" s="405" t="n"/>
-      <c r="AL8" s="406" t="n"/>
-      <c r="AM8" s="358" t="n"/>
-      <c r="AN8" s="407" t="n"/>
-      <c r="AO8" s="407" t="n"/>
-      <c r="AP8" s="407" t="n"/>
-      <c r="AQ8" s="407" t="n"/>
-      <c r="AR8" s="407" t="n"/>
-      <c r="AS8" s="407" t="n"/>
-      <c r="AT8" s="407" t="n"/>
-      <c r="AU8" s="407" t="n"/>
-      <c r="AV8" s="407" t="n"/>
-      <c r="AW8" s="407" t="n"/>
-      <c r="AX8" s="407" t="n"/>
-      <c r="AY8" s="407" t="n"/>
-      <c r="AZ8" s="407" t="n"/>
-      <c r="BA8" s="407" t="n"/>
-      <c r="BB8" s="407" t="n"/>
-      <c r="BC8" s="407" t="n"/>
-      <c r="BD8" s="408" t="n"/>
+      <c r="AD8" s="470" t="n"/>
+      <c r="AE8" s="470" t="n"/>
+      <c r="AF8" s="470" t="n"/>
+      <c r="AG8" s="470" t="n"/>
+      <c r="AH8" s="470" t="n"/>
+      <c r="AI8" s="470" t="n"/>
+      <c r="AJ8" s="470" t="n"/>
+      <c r="AK8" s="470" t="n"/>
+      <c r="AL8" s="470" t="n"/>
+      <c r="AM8" s="471" t="n"/>
+      <c r="AN8" s="472" t="n"/>
+      <c r="AO8" s="472" t="n"/>
+      <c r="AP8" s="472" t="n"/>
+      <c r="AQ8" s="472" t="n"/>
+      <c r="AR8" s="472" t="n"/>
+      <c r="AS8" s="472" t="n"/>
+      <c r="AT8" s="472" t="n"/>
+      <c r="AU8" s="472" t="n"/>
+      <c r="AV8" s="472" t="n"/>
+      <c r="AW8" s="472" t="n"/>
+      <c r="AX8" s="472" t="n"/>
+      <c r="AY8" s="472" t="n"/>
+      <c r="AZ8" s="472" t="n"/>
+      <c r="BA8" s="472" t="n"/>
+      <c r="BB8" s="472" t="n"/>
+      <c r="BC8" s="472" t="n"/>
+      <c r="BD8" s="474" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="355" t="inlineStr">
+      <c r="A9" s="475" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B9" s="405" t="n"/>
-      <c r="C9" s="405" t="n"/>
-      <c r="D9" s="405" t="n"/>
-      <c r="E9" s="405" t="n"/>
-      <c r="F9" s="405" t="n"/>
-      <c r="G9" s="405" t="n"/>
-      <c r="H9" s="405" t="n"/>
-      <c r="I9" s="405" t="n"/>
-      <c r="J9" s="406" t="n"/>
-      <c r="K9" s="358" t="n"/>
-      <c r="L9" s="407" t="n"/>
-      <c r="M9" s="407" t="n"/>
-      <c r="N9" s="407" t="n"/>
-      <c r="O9" s="407" t="n"/>
-      <c r="P9" s="407" t="n"/>
-      <c r="Q9" s="407" t="n"/>
-      <c r="R9" s="407" t="n"/>
-      <c r="S9" s="407" t="n"/>
-      <c r="T9" s="407" t="n"/>
-      <c r="U9" s="407" t="n"/>
-      <c r="V9" s="407" t="n"/>
-      <c r="W9" s="407" t="n"/>
-      <c r="X9" s="407" t="n"/>
-      <c r="Y9" s="407" t="n"/>
-      <c r="Z9" s="407" t="n"/>
-      <c r="AA9" s="407" t="n"/>
-      <c r="AB9" s="408" t="n"/>
-      <c r="AC9" s="361" t="inlineStr">
+      <c r="B9" s="344" t="n"/>
+      <c r="C9" s="344" t="n"/>
+      <c r="D9" s="344" t="n"/>
+      <c r="E9" s="344" t="n"/>
+      <c r="F9" s="344" t="n"/>
+      <c r="G9" s="344" t="n"/>
+      <c r="H9" s="344" t="n"/>
+      <c r="I9" s="344" t="n"/>
+      <c r="J9" s="344" t="n"/>
+      <c r="K9" s="476" t="n"/>
+      <c r="L9" s="362" t="n"/>
+      <c r="M9" s="362" t="n"/>
+      <c r="N9" s="362" t="n"/>
+      <c r="O9" s="362" t="n"/>
+      <c r="P9" s="362" t="n"/>
+      <c r="Q9" s="362" t="n"/>
+      <c r="R9" s="362" t="n"/>
+      <c r="S9" s="362" t="n"/>
+      <c r="T9" s="362" t="n"/>
+      <c r="U9" s="362" t="n"/>
+      <c r="V9" s="362" t="n"/>
+      <c r="W9" s="362" t="n"/>
+      <c r="X9" s="362" t="n"/>
+      <c r="Y9" s="362" t="n"/>
+      <c r="Z9" s="362" t="n"/>
+      <c r="AA9" s="362" t="n"/>
+      <c r="AB9" s="362" t="n"/>
+      <c r="AC9" s="477" t="inlineStr">
         <is>
           <t>Job / Lot / Serial</t>
         </is>
       </c>
-      <c r="AD9" s="405" t="n"/>
-      <c r="AE9" s="405" t="n"/>
-      <c r="AF9" s="405" t="n"/>
-      <c r="AG9" s="405" t="n"/>
-      <c r="AH9" s="405" t="n"/>
-      <c r="AI9" s="405" t="n"/>
-      <c r="AJ9" s="405" t="n"/>
-      <c r="AK9" s="405" t="n"/>
-      <c r="AL9" s="406" t="n"/>
-      <c r="AM9" s="358" t="n"/>
-      <c r="AN9" s="407" t="n"/>
-      <c r="AO9" s="407" t="n"/>
-      <c r="AP9" s="407" t="n"/>
-      <c r="AQ9" s="407" t="n"/>
-      <c r="AR9" s="407" t="n"/>
-      <c r="AS9" s="407" t="n"/>
-      <c r="AT9" s="407" t="n"/>
-      <c r="AU9" s="407" t="n"/>
-      <c r="AV9" s="407" t="n"/>
-      <c r="AW9" s="407" t="n"/>
-      <c r="AX9" s="407" t="n"/>
-      <c r="AY9" s="407" t="n"/>
-      <c r="AZ9" s="407" t="n"/>
-      <c r="BA9" s="407" t="n"/>
-      <c r="BB9" s="407" t="n"/>
-      <c r="BC9" s="407" t="n"/>
-      <c r="BD9" s="408" t="n"/>
+      <c r="AD9" s="344" t="n"/>
+      <c r="AE9" s="344" t="n"/>
+      <c r="AF9" s="344" t="n"/>
+      <c r="AG9" s="344" t="n"/>
+      <c r="AH9" s="344" t="n"/>
+      <c r="AI9" s="344" t="n"/>
+      <c r="AJ9" s="344" t="n"/>
+      <c r="AK9" s="344" t="n"/>
+      <c r="AL9" s="344" t="n"/>
+      <c r="AM9" s="476" t="n"/>
+      <c r="AN9" s="362" t="n"/>
+      <c r="AO9" s="362" t="n"/>
+      <c r="AP9" s="362" t="n"/>
+      <c r="AQ9" s="362" t="n"/>
+      <c r="AR9" s="362" t="n"/>
+      <c r="AS9" s="362" t="n"/>
+      <c r="AT9" s="362" t="n"/>
+      <c r="AU9" s="362" t="n"/>
+      <c r="AV9" s="362" t="n"/>
+      <c r="AW9" s="362" t="n"/>
+      <c r="AX9" s="362" t="n"/>
+      <c r="AY9" s="362" t="n"/>
+      <c r="AZ9" s="362" t="n"/>
+      <c r="BA9" s="362" t="n"/>
+      <c r="BB9" s="362" t="n"/>
+      <c r="BC9" s="362" t="n"/>
+      <c r="BD9" s="478" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="355" t="inlineStr">
+      <c r="A10" s="475" t="inlineStr">
         <is>
           <t>Lot Qty</t>
         </is>
       </c>
-      <c r="B10" s="405" t="n"/>
-      <c r="C10" s="405" t="n"/>
-      <c r="D10" s="405" t="n"/>
-      <c r="E10" s="405" t="n"/>
-      <c r="F10" s="405" t="n"/>
-      <c r="G10" s="405" t="n"/>
-      <c r="H10" s="405" t="n"/>
-      <c r="I10" s="405" t="n"/>
-      <c r="J10" s="406" t="n"/>
-      <c r="K10" s="358" t="n"/>
-      <c r="L10" s="407" t="n"/>
-      <c r="M10" s="407" t="n"/>
-      <c r="N10" s="407" t="n"/>
-      <c r="O10" s="407" t="n"/>
-      <c r="P10" s="407" t="n"/>
-      <c r="Q10" s="407" t="n"/>
-      <c r="R10" s="407" t="n"/>
-      <c r="S10" s="407" t="n"/>
-      <c r="T10" s="407" t="n"/>
-      <c r="U10" s="407" t="n"/>
-      <c r="V10" s="407" t="n"/>
-      <c r="W10" s="407" t="n"/>
-      <c r="X10" s="407" t="n"/>
-      <c r="Y10" s="407" t="n"/>
-      <c r="Z10" s="407" t="n"/>
-      <c r="AA10" s="407" t="n"/>
-      <c r="AB10" s="408" t="n"/>
-      <c r="AC10" s="361" t="inlineStr">
+      <c r="B10" s="344" t="n"/>
+      <c r="C10" s="344" t="n"/>
+      <c r="D10" s="344" t="n"/>
+      <c r="E10" s="344" t="n"/>
+      <c r="F10" s="344" t="n"/>
+      <c r="G10" s="344" t="n"/>
+      <c r="H10" s="344" t="n"/>
+      <c r="I10" s="344" t="n"/>
+      <c r="J10" s="344" t="n"/>
+      <c r="K10" s="476" t="n"/>
+      <c r="L10" s="362" t="n"/>
+      <c r="M10" s="362" t="n"/>
+      <c r="N10" s="362" t="n"/>
+      <c r="O10" s="362" t="n"/>
+      <c r="P10" s="362" t="n"/>
+      <c r="Q10" s="362" t="n"/>
+      <c r="R10" s="362" t="n"/>
+      <c r="S10" s="362" t="n"/>
+      <c r="T10" s="362" t="n"/>
+      <c r="U10" s="362" t="n"/>
+      <c r="V10" s="362" t="n"/>
+      <c r="W10" s="362" t="n"/>
+      <c r="X10" s="362" t="n"/>
+      <c r="Y10" s="362" t="n"/>
+      <c r="Z10" s="362" t="n"/>
+      <c r="AA10" s="362" t="n"/>
+      <c r="AB10" s="362" t="n"/>
+      <c r="AC10" s="477" t="inlineStr">
         <is>
           <t>Characteristic Class</t>
         </is>
       </c>
-      <c r="AD10" s="405" t="n"/>
-      <c r="AE10" s="405" t="n"/>
-      <c r="AF10" s="405" t="n"/>
-      <c r="AG10" s="405" t="n"/>
-      <c r="AH10" s="405" t="n"/>
-      <c r="AI10" s="405" t="n"/>
-      <c r="AJ10" s="405" t="n"/>
-      <c r="AK10" s="405" t="n"/>
-      <c r="AL10" s="406" t="n"/>
-      <c r="AM10" s="358" t="n"/>
-      <c r="AN10" s="407" t="n"/>
-      <c r="AO10" s="407" t="n"/>
-      <c r="AP10" s="407" t="n"/>
-      <c r="AQ10" s="407" t="n"/>
-      <c r="AR10" s="407" t="n"/>
-      <c r="AS10" s="407" t="n"/>
-      <c r="AT10" s="407" t="n"/>
-      <c r="AU10" s="407" t="n"/>
-      <c r="AV10" s="407" t="n"/>
-      <c r="AW10" s="407" t="n"/>
-      <c r="AX10" s="407" t="n"/>
-      <c r="AY10" s="407" t="n"/>
-      <c r="AZ10" s="407" t="n"/>
-      <c r="BA10" s="407" t="n"/>
-      <c r="BB10" s="407" t="n"/>
-      <c r="BC10" s="407" t="n"/>
-      <c r="BD10" s="408" t="n"/>
+      <c r="AD10" s="344" t="n"/>
+      <c r="AE10" s="344" t="n"/>
+      <c r="AF10" s="344" t="n"/>
+      <c r="AG10" s="344" t="n"/>
+      <c r="AH10" s="344" t="n"/>
+      <c r="AI10" s="344" t="n"/>
+      <c r="AJ10" s="344" t="n"/>
+      <c r="AK10" s="344" t="n"/>
+      <c r="AL10" s="344" t="n"/>
+      <c r="AM10" s="476" t="n"/>
+      <c r="AN10" s="362" t="n"/>
+      <c r="AO10" s="362" t="n"/>
+      <c r="AP10" s="362" t="n"/>
+      <c r="AQ10" s="362" t="n"/>
+      <c r="AR10" s="362" t="n"/>
+      <c r="AS10" s="362" t="n"/>
+      <c r="AT10" s="362" t="n"/>
+      <c r="AU10" s="362" t="n"/>
+      <c r="AV10" s="362" t="n"/>
+      <c r="AW10" s="362" t="n"/>
+      <c r="AX10" s="362" t="n"/>
+      <c r="AY10" s="362" t="n"/>
+      <c r="AZ10" s="362" t="n"/>
+      <c r="BA10" s="362" t="n"/>
+      <c r="BB10" s="362" t="n"/>
+      <c r="BC10" s="362" t="n"/>
+      <c r="BD10" s="478" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="355" t="inlineStr">
+      <c r="A11" s="475" t="inlineStr">
         <is>
           <t>AQL</t>
         </is>
       </c>
-      <c r="B11" s="405" t="n"/>
-      <c r="C11" s="405" t="n"/>
-      <c r="D11" s="405" t="n"/>
-      <c r="E11" s="405" t="n"/>
-      <c r="F11" s="405" t="n"/>
-      <c r="G11" s="405" t="n"/>
-      <c r="H11" s="405" t="n"/>
-      <c r="I11" s="405" t="n"/>
-      <c r="J11" s="406" t="n"/>
-      <c r="K11" s="358" t="n"/>
-      <c r="L11" s="407" t="n"/>
-      <c r="M11" s="407" t="n"/>
-      <c r="N11" s="407" t="n"/>
-      <c r="O11" s="407" t="n"/>
-      <c r="P11" s="407" t="n"/>
-      <c r="Q11" s="407" t="n"/>
-      <c r="R11" s="407" t="n"/>
-      <c r="S11" s="407" t="n"/>
-      <c r="T11" s="407" t="n"/>
-      <c r="U11" s="407" t="n"/>
-      <c r="V11" s="407" t="n"/>
-      <c r="W11" s="407" t="n"/>
-      <c r="X11" s="407" t="n"/>
-      <c r="Y11" s="407" t="n"/>
-      <c r="Z11" s="407" t="n"/>
-      <c r="AA11" s="407" t="n"/>
-      <c r="AB11" s="408" t="n"/>
-      <c r="AC11" s="361" t="inlineStr">
+      <c r="B11" s="344" t="n"/>
+      <c r="C11" s="344" t="n"/>
+      <c r="D11" s="344" t="n"/>
+      <c r="E11" s="344" t="n"/>
+      <c r="F11" s="344" t="n"/>
+      <c r="G11" s="344" t="n"/>
+      <c r="H11" s="344" t="n"/>
+      <c r="I11" s="344" t="n"/>
+      <c r="J11" s="344" t="n"/>
+      <c r="K11" s="476" t="n"/>
+      <c r="L11" s="362" t="n"/>
+      <c r="M11" s="362" t="n"/>
+      <c r="N11" s="362" t="n"/>
+      <c r="O11" s="362" t="n"/>
+      <c r="P11" s="362" t="n"/>
+      <c r="Q11" s="362" t="n"/>
+      <c r="R11" s="362" t="n"/>
+      <c r="S11" s="362" t="n"/>
+      <c r="T11" s="362" t="n"/>
+      <c r="U11" s="362" t="n"/>
+      <c r="V11" s="362" t="n"/>
+      <c r="W11" s="362" t="n"/>
+      <c r="X11" s="362" t="n"/>
+      <c r="Y11" s="362" t="n"/>
+      <c r="Z11" s="362" t="n"/>
+      <c r="AA11" s="362" t="n"/>
+      <c r="AB11" s="362" t="n"/>
+      <c r="AC11" s="477" t="inlineStr">
         <is>
           <t>Inspection Level</t>
         </is>
       </c>
-      <c r="AD11" s="405" t="n"/>
-      <c r="AE11" s="405" t="n"/>
-      <c r="AF11" s="405" t="n"/>
-      <c r="AG11" s="405" t="n"/>
-      <c r="AH11" s="405" t="n"/>
-      <c r="AI11" s="405" t="n"/>
-      <c r="AJ11" s="405" t="n"/>
-      <c r="AK11" s="405" t="n"/>
-      <c r="AL11" s="406" t="n"/>
-      <c r="AM11" s="358" t="n"/>
-      <c r="AN11" s="407" t="n"/>
-      <c r="AO11" s="407" t="n"/>
-      <c r="AP11" s="407" t="n"/>
-      <c r="AQ11" s="407" t="n"/>
-      <c r="AR11" s="407" t="n"/>
-      <c r="AS11" s="407" t="n"/>
-      <c r="AT11" s="407" t="n"/>
-      <c r="AU11" s="407" t="n"/>
-      <c r="AV11" s="407" t="n"/>
-      <c r="AW11" s="407" t="n"/>
-      <c r="AX11" s="407" t="n"/>
-      <c r="AY11" s="407" t="n"/>
-      <c r="AZ11" s="407" t="n"/>
-      <c r="BA11" s="407" t="n"/>
-      <c r="BB11" s="407" t="n"/>
-      <c r="BC11" s="407" t="n"/>
-      <c r="BD11" s="408" t="n"/>
+      <c r="AD11" s="344" t="n"/>
+      <c r="AE11" s="344" t="n"/>
+      <c r="AF11" s="344" t="n"/>
+      <c r="AG11" s="344" t="n"/>
+      <c r="AH11" s="344" t="n"/>
+      <c r="AI11" s="344" t="n"/>
+      <c r="AJ11" s="344" t="n"/>
+      <c r="AK11" s="344" t="n"/>
+      <c r="AL11" s="344" t="n"/>
+      <c r="AM11" s="476" t="n"/>
+      <c r="AN11" s="362" t="n"/>
+      <c r="AO11" s="362" t="n"/>
+      <c r="AP11" s="362" t="n"/>
+      <c r="AQ11" s="362" t="n"/>
+      <c r="AR11" s="362" t="n"/>
+      <c r="AS11" s="362" t="n"/>
+      <c r="AT11" s="362" t="n"/>
+      <c r="AU11" s="362" t="n"/>
+      <c r="AV11" s="362" t="n"/>
+      <c r="AW11" s="362" t="n"/>
+      <c r="AX11" s="362" t="n"/>
+      <c r="AY11" s="362" t="n"/>
+      <c r="AZ11" s="362" t="n"/>
+      <c r="BA11" s="362" t="n"/>
+      <c r="BB11" s="362" t="n"/>
+      <c r="BC11" s="362" t="n"/>
+      <c r="BD11" s="478" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="355" t="inlineStr">
+      <c r="A12" s="475" t="inlineStr">
         <is>
           <t>Code Letter</t>
         </is>
       </c>
-      <c r="B12" s="405" t="n"/>
-      <c r="C12" s="405" t="n"/>
-      <c r="D12" s="405" t="n"/>
-      <c r="E12" s="405" t="n"/>
-      <c r="F12" s="405" t="n"/>
-      <c r="G12" s="405" t="n"/>
-      <c r="H12" s="405" t="n"/>
-      <c r="I12" s="405" t="n"/>
-      <c r="J12" s="406" t="n"/>
-      <c r="K12" s="358" t="n"/>
-      <c r="L12" s="407" t="n"/>
-      <c r="M12" s="407" t="n"/>
-      <c r="N12" s="407" t="n"/>
-      <c r="O12" s="407" t="n"/>
-      <c r="P12" s="407" t="n"/>
-      <c r="Q12" s="407" t="n"/>
-      <c r="R12" s="407" t="n"/>
-      <c r="S12" s="407" t="n"/>
-      <c r="T12" s="407" t="n"/>
-      <c r="U12" s="407" t="n"/>
-      <c r="V12" s="407" t="n"/>
-      <c r="W12" s="407" t="n"/>
-      <c r="X12" s="407" t="n"/>
-      <c r="Y12" s="407" t="n"/>
-      <c r="Z12" s="407" t="n"/>
-      <c r="AA12" s="407" t="n"/>
-      <c r="AB12" s="408" t="n"/>
-      <c r="AC12" s="361" t="inlineStr">
+      <c r="B12" s="344" t="n"/>
+      <c r="C12" s="344" t="n"/>
+      <c r="D12" s="344" t="n"/>
+      <c r="E12" s="344" t="n"/>
+      <c r="F12" s="344" t="n"/>
+      <c r="G12" s="344" t="n"/>
+      <c r="H12" s="344" t="n"/>
+      <c r="I12" s="344" t="n"/>
+      <c r="J12" s="344" t="n"/>
+      <c r="K12" s="476" t="n"/>
+      <c r="L12" s="362" t="n"/>
+      <c r="M12" s="362" t="n"/>
+      <c r="N12" s="362" t="n"/>
+      <c r="O12" s="362" t="n"/>
+      <c r="P12" s="362" t="n"/>
+      <c r="Q12" s="362" t="n"/>
+      <c r="R12" s="362" t="n"/>
+      <c r="S12" s="362" t="n"/>
+      <c r="T12" s="362" t="n"/>
+      <c r="U12" s="362" t="n"/>
+      <c r="V12" s="362" t="n"/>
+      <c r="W12" s="362" t="n"/>
+      <c r="X12" s="362" t="n"/>
+      <c r="Y12" s="362" t="n"/>
+      <c r="Z12" s="362" t="n"/>
+      <c r="AA12" s="362" t="n"/>
+      <c r="AB12" s="362" t="n"/>
+      <c r="AC12" s="477" t="inlineStr">
         <is>
           <t>Sample Size</t>
         </is>
       </c>
-      <c r="AD12" s="405" t="n"/>
-      <c r="AE12" s="405" t="n"/>
-      <c r="AF12" s="405" t="n"/>
-      <c r="AG12" s="405" t="n"/>
-      <c r="AH12" s="405" t="n"/>
-      <c r="AI12" s="405" t="n"/>
-      <c r="AJ12" s="405" t="n"/>
-      <c r="AK12" s="405" t="n"/>
-      <c r="AL12" s="406" t="n"/>
-      <c r="AM12" s="358" t="n"/>
-      <c r="AN12" s="407" t="n"/>
-      <c r="AO12" s="407" t="n"/>
-      <c r="AP12" s="407" t="n"/>
-      <c r="AQ12" s="407" t="n"/>
-      <c r="AR12" s="407" t="n"/>
-      <c r="AS12" s="407" t="n"/>
-      <c r="AT12" s="407" t="n"/>
-      <c r="AU12" s="407" t="n"/>
-      <c r="AV12" s="407" t="n"/>
-      <c r="AW12" s="407" t="n"/>
-      <c r="AX12" s="407" t="n"/>
-      <c r="AY12" s="407" t="n"/>
-      <c r="AZ12" s="407" t="n"/>
-      <c r="BA12" s="407" t="n"/>
-      <c r="BB12" s="407" t="n"/>
-      <c r="BC12" s="407" t="n"/>
-      <c r="BD12" s="408" t="n"/>
+      <c r="AD12" s="344" t="n"/>
+      <c r="AE12" s="344" t="n"/>
+      <c r="AF12" s="344" t="n"/>
+      <c r="AG12" s="344" t="n"/>
+      <c r="AH12" s="344" t="n"/>
+      <c r="AI12" s="344" t="n"/>
+      <c r="AJ12" s="344" t="n"/>
+      <c r="AK12" s="344" t="n"/>
+      <c r="AL12" s="344" t="n"/>
+      <c r="AM12" s="476" t="n"/>
+      <c r="AN12" s="362" t="n"/>
+      <c r="AO12" s="362" t="n"/>
+      <c r="AP12" s="362" t="n"/>
+      <c r="AQ12" s="362" t="n"/>
+      <c r="AR12" s="362" t="n"/>
+      <c r="AS12" s="362" t="n"/>
+      <c r="AT12" s="362" t="n"/>
+      <c r="AU12" s="362" t="n"/>
+      <c r="AV12" s="362" t="n"/>
+      <c r="AW12" s="362" t="n"/>
+      <c r="AX12" s="362" t="n"/>
+      <c r="AY12" s="362" t="n"/>
+      <c r="AZ12" s="362" t="n"/>
+      <c r="BA12" s="362" t="n"/>
+      <c r="BB12" s="362" t="n"/>
+      <c r="BC12" s="362" t="n"/>
+      <c r="BD12" s="478" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="355" t="inlineStr">
+      <c r="A13" s="475" t="inlineStr">
         <is>
           <t>Ac / Re</t>
         </is>
       </c>
-      <c r="B13" s="405" t="n"/>
-      <c r="C13" s="405" t="n"/>
-      <c r="D13" s="405" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="405" t="n"/>
-      <c r="G13" s="405" t="n"/>
-      <c r="H13" s="405" t="n"/>
-      <c r="I13" s="405" t="n"/>
-      <c r="J13" s="406" t="n"/>
-      <c r="K13" s="358" t="n"/>
-      <c r="L13" s="407" t="n"/>
-      <c r="M13" s="407" t="n"/>
-      <c r="N13" s="407" t="n"/>
-      <c r="O13" s="407" t="n"/>
-      <c r="P13" s="407" t="n"/>
-      <c r="Q13" s="407" t="n"/>
-      <c r="R13" s="407" t="n"/>
-      <c r="S13" s="407" t="n"/>
-      <c r="T13" s="407" t="n"/>
-      <c r="U13" s="407" t="n"/>
-      <c r="V13" s="407" t="n"/>
-      <c r="W13" s="407" t="n"/>
-      <c r="X13" s="407" t="n"/>
-      <c r="Y13" s="407" t="n"/>
-      <c r="Z13" s="407" t="n"/>
-      <c r="AA13" s="407" t="n"/>
-      <c r="AB13" s="408" t="n"/>
-      <c r="AC13" s="361" t="inlineStr">
+      <c r="B13" s="344" t="n"/>
+      <c r="C13" s="344" t="n"/>
+      <c r="D13" s="344" t="n"/>
+      <c r="E13" s="344" t="n"/>
+      <c r="F13" s="344" t="n"/>
+      <c r="G13" s="344" t="n"/>
+      <c r="H13" s="344" t="n"/>
+      <c r="I13" s="344" t="n"/>
+      <c r="J13" s="344" t="n"/>
+      <c r="K13" s="476" t="n"/>
+      <c r="L13" s="362" t="n"/>
+      <c r="M13" s="362" t="n"/>
+      <c r="N13" s="362" t="n"/>
+      <c r="O13" s="362" t="n"/>
+      <c r="P13" s="362" t="n"/>
+      <c r="Q13" s="362" t="n"/>
+      <c r="R13" s="362" t="n"/>
+      <c r="S13" s="362" t="n"/>
+      <c r="T13" s="362" t="n"/>
+      <c r="U13" s="362" t="n"/>
+      <c r="V13" s="362" t="n"/>
+      <c r="W13" s="362" t="n"/>
+      <c r="X13" s="362" t="n"/>
+      <c r="Y13" s="362" t="n"/>
+      <c r="Z13" s="362" t="n"/>
+      <c r="AA13" s="362" t="n"/>
+      <c r="AB13" s="362" t="n"/>
+      <c r="AC13" s="477" t="inlineStr">
         <is>
           <t>Switching Status</t>
         </is>
       </c>
-      <c r="AD13" s="405" t="n"/>
-      <c r="AE13" s="405" t="n"/>
-      <c r="AF13" s="405" t="n"/>
-      <c r="AG13" s="405" t="n"/>
-      <c r="AH13" s="405" t="n"/>
-      <c r="AI13" s="405" t="n"/>
-      <c r="AJ13" s="405" t="n"/>
-      <c r="AK13" s="405" t="n"/>
-      <c r="AL13" s="406" t="n"/>
-      <c r="AM13" s="358" t="n"/>
-      <c r="AN13" s="407" t="n"/>
-      <c r="AO13" s="407" t="n"/>
-      <c r="AP13" s="407" t="n"/>
-      <c r="AQ13" s="407" t="n"/>
-      <c r="AR13" s="407" t="n"/>
-      <c r="AS13" s="407" t="n"/>
-      <c r="AT13" s="407" t="n"/>
-      <c r="AU13" s="407" t="n"/>
-      <c r="AV13" s="407" t="n"/>
-      <c r="AW13" s="407" t="n"/>
-      <c r="AX13" s="407" t="n"/>
-      <c r="AY13" s="407" t="n"/>
-      <c r="AZ13" s="407" t="n"/>
-      <c r="BA13" s="407" t="n"/>
-      <c r="BB13" s="407" t="n"/>
-      <c r="BC13" s="407" t="n"/>
-      <c r="BD13" s="408" t="n"/>
+      <c r="AD13" s="344" t="n"/>
+      <c r="AE13" s="344" t="n"/>
+      <c r="AF13" s="344" t="n"/>
+      <c r="AG13" s="344" t="n"/>
+      <c r="AH13" s="344" t="n"/>
+      <c r="AI13" s="344" t="n"/>
+      <c r="AJ13" s="344" t="n"/>
+      <c r="AK13" s="344" t="n"/>
+      <c r="AL13" s="344" t="n"/>
+      <c r="AM13" s="476" t="n"/>
+      <c r="AN13" s="362" t="n"/>
+      <c r="AO13" s="362" t="n"/>
+      <c r="AP13" s="362" t="n"/>
+      <c r="AQ13" s="362" t="n"/>
+      <c r="AR13" s="362" t="n"/>
+      <c r="AS13" s="362" t="n"/>
+      <c r="AT13" s="362" t="n"/>
+      <c r="AU13" s="362" t="n"/>
+      <c r="AV13" s="362" t="n"/>
+      <c r="AW13" s="362" t="n"/>
+      <c r="AX13" s="362" t="n"/>
+      <c r="AY13" s="362" t="n"/>
+      <c r="AZ13" s="362" t="n"/>
+      <c r="BA13" s="362" t="n"/>
+      <c r="BB13" s="362" t="n"/>
+      <c r="BC13" s="362" t="n"/>
+      <c r="BD13" s="478" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="355" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="475" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B14" s="400" t="n"/>
-      <c r="C14" s="400" t="n"/>
-      <c r="D14" s="400" t="n"/>
-      <c r="E14" s="400" t="n"/>
-      <c r="F14" s="400" t="n"/>
-      <c r="G14" s="400" t="n"/>
-      <c r="H14" s="400" t="n"/>
-      <c r="I14" s="400" t="n"/>
-      <c r="J14" s="401" t="n"/>
-      <c r="K14" s="358" t="n"/>
-      <c r="L14" s="409" t="n"/>
-      <c r="M14" s="409" t="n"/>
-      <c r="N14" s="409" t="n"/>
-      <c r="O14" s="409" t="n"/>
-      <c r="P14" s="409" t="n"/>
-      <c r="Q14" s="409" t="n"/>
-      <c r="R14" s="409" t="n"/>
-      <c r="S14" s="409" t="n"/>
-      <c r="T14" s="409" t="n"/>
-      <c r="U14" s="409" t="n"/>
-      <c r="V14" s="409" t="n"/>
-      <c r="W14" s="409" t="n"/>
-      <c r="X14" s="409" t="n"/>
-      <c r="Y14" s="409" t="n"/>
-      <c r="Z14" s="409" t="n"/>
-      <c r="AA14" s="409" t="n"/>
-      <c r="AB14" s="410" t="n"/>
-      <c r="AC14" s="361" t="inlineStr">
+      <c r="B14" s="344" t="n"/>
+      <c r="C14" s="344" t="n"/>
+      <c r="D14" s="344" t="n"/>
+      <c r="E14" s="344" t="n"/>
+      <c r="F14" s="344" t="n"/>
+      <c r="G14" s="344" t="n"/>
+      <c r="H14" s="344" t="n"/>
+      <c r="I14" s="344" t="n"/>
+      <c r="J14" s="344" t="n"/>
+      <c r="K14" s="476" t="n"/>
+      <c r="L14" s="362" t="n"/>
+      <c r="M14" s="362" t="n"/>
+      <c r="N14" s="362" t="n"/>
+      <c r="O14" s="362" t="n"/>
+      <c r="P14" s="362" t="n"/>
+      <c r="Q14" s="362" t="n"/>
+      <c r="R14" s="362" t="n"/>
+      <c r="S14" s="362" t="n"/>
+      <c r="T14" s="362" t="n"/>
+      <c r="U14" s="362" t="n"/>
+      <c r="V14" s="362" t="n"/>
+      <c r="W14" s="362" t="n"/>
+      <c r="X14" s="362" t="n"/>
+      <c r="Y14" s="362" t="n"/>
+      <c r="Z14" s="362" t="n"/>
+      <c r="AA14" s="362" t="n"/>
+      <c r="AB14" s="362" t="n"/>
+      <c r="AC14" s="477" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD14" s="400" t="n"/>
-      <c r="AE14" s="400" t="n"/>
-      <c r="AF14" s="400" t="n"/>
-      <c r="AG14" s="400" t="n"/>
-      <c r="AH14" s="400" t="n"/>
-      <c r="AI14" s="400" t="n"/>
-      <c r="AJ14" s="400" t="n"/>
-      <c r="AK14" s="400" t="n"/>
-      <c r="AL14" s="401" t="n"/>
-      <c r="AM14" s="358" t="n"/>
-      <c r="AN14" s="409" t="n"/>
-      <c r="AO14" s="409" t="n"/>
-      <c r="AP14" s="409" t="n"/>
-      <c r="AQ14" s="409" t="n"/>
-      <c r="AR14" s="409" t="n"/>
-      <c r="AS14" s="409" t="n"/>
-      <c r="AT14" s="409" t="n"/>
-      <c r="AU14" s="409" t="n"/>
-      <c r="AV14" s="409" t="n"/>
-      <c r="AW14" s="409" t="n"/>
-      <c r="AX14" s="409" t="n"/>
-      <c r="AY14" s="409" t="n"/>
-      <c r="AZ14" s="409" t="n"/>
-      <c r="BA14" s="409" t="n"/>
-      <c r="BB14" s="409" t="n"/>
-      <c r="BC14" s="409" t="n"/>
-      <c r="BD14" s="410" t="n"/>
+      <c r="AD14" s="344" t="n"/>
+      <c r="AE14" s="344" t="n"/>
+      <c r="AF14" s="344" t="n"/>
+      <c r="AG14" s="344" t="n"/>
+      <c r="AH14" s="344" t="n"/>
+      <c r="AI14" s="344" t="n"/>
+      <c r="AJ14" s="344" t="n"/>
+      <c r="AK14" s="344" t="n"/>
+      <c r="AL14" s="344" t="n"/>
+      <c r="AM14" s="476" t="n"/>
+      <c r="AN14" s="362" t="n"/>
+      <c r="AO14" s="362" t="n"/>
+      <c r="AP14" s="362" t="n"/>
+      <c r="AQ14" s="362" t="n"/>
+      <c r="AR14" s="362" t="n"/>
+      <c r="AS14" s="362" t="n"/>
+      <c r="AT14" s="362" t="n"/>
+      <c r="AU14" s="362" t="n"/>
+      <c r="AV14" s="362" t="n"/>
+      <c r="AW14" s="362" t="n"/>
+      <c r="AX14" s="362" t="n"/>
+      <c r="AY14" s="362" t="n"/>
+      <c r="AZ14" s="362" t="n"/>
+      <c r="BA14" s="362" t="n"/>
+      <c r="BB14" s="362" t="n"/>
+      <c r="BC14" s="362" t="n"/>
+      <c r="BD14" s="478" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="355" t="inlineStr">
+      <c r="A15" s="479" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B15" s="405" t="n"/>
-      <c r="C15" s="405" t="n"/>
-      <c r="D15" s="405" t="n"/>
-      <c r="E15" s="405" t="n"/>
-      <c r="F15" s="405" t="n"/>
-      <c r="G15" s="405" t="n"/>
-      <c r="H15" s="405" t="n"/>
-      <c r="I15" s="405" t="n"/>
-      <c r="J15" s="406" t="n"/>
-      <c r="K15" s="358" t="n"/>
-      <c r="L15" s="407" t="n"/>
-      <c r="M15" s="407" t="n"/>
-      <c r="N15" s="407" t="n"/>
-      <c r="O15" s="407" t="n"/>
-      <c r="P15" s="407" t="n"/>
-      <c r="Q15" s="407" t="n"/>
-      <c r="R15" s="407" t="n"/>
-      <c r="S15" s="407" t="n"/>
-      <c r="T15" s="407" t="n"/>
-      <c r="U15" s="407" t="n"/>
-      <c r="V15" s="407" t="n"/>
-      <c r="W15" s="407" t="n"/>
-      <c r="X15" s="407" t="n"/>
-      <c r="Y15" s="407" t="n"/>
-      <c r="Z15" s="407" t="n"/>
-      <c r="AA15" s="407" t="n"/>
-      <c r="AB15" s="408" t="n"/>
-      <c r="AC15" s="361" t="inlineStr">
+      <c r="B15" s="480" t="n"/>
+      <c r="C15" s="480" t="n"/>
+      <c r="D15" s="480" t="n"/>
+      <c r="E15" s="480" t="n"/>
+      <c r="F15" s="480" t="n"/>
+      <c r="G15" s="480" t="n"/>
+      <c r="H15" s="480" t="n"/>
+      <c r="I15" s="480" t="n"/>
+      <c r="J15" s="480" t="n"/>
+      <c r="K15" s="481" t="n"/>
+      <c r="L15" s="482" t="n"/>
+      <c r="M15" s="482" t="n"/>
+      <c r="N15" s="482" t="n"/>
+      <c r="O15" s="482" t="n"/>
+      <c r="P15" s="482" t="n"/>
+      <c r="Q15" s="482" t="n"/>
+      <c r="R15" s="482" t="n"/>
+      <c r="S15" s="482" t="n"/>
+      <c r="T15" s="482" t="n"/>
+      <c r="U15" s="482" t="n"/>
+      <c r="V15" s="482" t="n"/>
+      <c r="W15" s="482" t="n"/>
+      <c r="X15" s="482" t="n"/>
+      <c r="Y15" s="482" t="n"/>
+      <c r="Z15" s="482" t="n"/>
+      <c r="AA15" s="482" t="n"/>
+      <c r="AB15" s="482" t="n"/>
+      <c r="AC15" s="483" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="AD15" s="405" t="n"/>
-      <c r="AE15" s="405" t="n"/>
-      <c r="AF15" s="405" t="n"/>
-      <c r="AG15" s="405" t="n"/>
-      <c r="AH15" s="405" t="n"/>
-      <c r="AI15" s="405" t="n"/>
-      <c r="AJ15" s="405" t="n"/>
-      <c r="AK15" s="405" t="n"/>
-      <c r="AL15" s="406" t="n"/>
-      <c r="AM15" s="358" t="n"/>
-      <c r="AN15" s="407" t="n"/>
-      <c r="AO15" s="407" t="n"/>
-      <c r="AP15" s="407" t="n"/>
-      <c r="AQ15" s="407" t="n"/>
-      <c r="AR15" s="407" t="n"/>
-      <c r="AS15" s="407" t="n"/>
-      <c r="AT15" s="407" t="n"/>
-      <c r="AU15" s="407" t="n"/>
-      <c r="AV15" s="407" t="n"/>
-      <c r="AW15" s="407" t="n"/>
-      <c r="AX15" s="407" t="n"/>
-      <c r="AY15" s="407" t="n"/>
-      <c r="AZ15" s="407" t="n"/>
-      <c r="BA15" s="407" t="n"/>
-      <c r="BB15" s="407" t="n"/>
-      <c r="BC15" s="407" t="n"/>
-      <c r="BD15" s="408" t="n"/>
+      <c r="AD15" s="480" t="n"/>
+      <c r="AE15" s="480" t="n"/>
+      <c r="AF15" s="480" t="n"/>
+      <c r="AG15" s="480" t="n"/>
+      <c r="AH15" s="480" t="n"/>
+      <c r="AI15" s="480" t="n"/>
+      <c r="AJ15" s="480" t="n"/>
+      <c r="AK15" s="480" t="n"/>
+      <c r="AL15" s="480" t="n"/>
+      <c r="AM15" s="481" t="n"/>
+      <c r="AN15" s="482" t="n"/>
+      <c r="AO15" s="482" t="n"/>
+      <c r="AP15" s="482" t="n"/>
+      <c r="AQ15" s="482" t="n"/>
+      <c r="AR15" s="482" t="n"/>
+      <c r="AS15" s="482" t="n"/>
+      <c r="AT15" s="482" t="n"/>
+      <c r="AU15" s="482" t="n"/>
+      <c r="AV15" s="482" t="n"/>
+      <c r="AW15" s="482" t="n"/>
+      <c r="AX15" s="482" t="n"/>
+      <c r="AY15" s="482" t="n"/>
+      <c r="AZ15" s="482" t="n"/>
+      <c r="BA15" s="482" t="n"/>
+      <c r="BB15" s="482" t="n"/>
+      <c r="BC15" s="482" t="n"/>
+      <c r="BD15" s="484" t="n"/>
     </row>
-    <row r="16" ht="4" customHeight="1">
+    <row r="16" ht="3" customHeight="1">
       <c r="A16" s="364" t="n"/>
       <c r="B16" s="353" t="n"/>
       <c r="C16" s="353" t="n"/>
@@ -6244,545 +7129,545 @@
       <c r="BC16" s="353" t="n"/>
       <c r="BD16" s="353" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="354" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="466" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B17" s="405" t="n"/>
-      <c r="C17" s="405" t="n"/>
-      <c r="D17" s="405" t="n"/>
-      <c r="E17" s="405" t="n"/>
-      <c r="F17" s="405" t="n"/>
-      <c r="G17" s="405" t="n"/>
-      <c r="H17" s="405" t="n"/>
-      <c r="I17" s="405" t="n"/>
-      <c r="J17" s="405" t="n"/>
-      <c r="K17" s="405" t="n"/>
-      <c r="L17" s="405" t="n"/>
-      <c r="M17" s="405" t="n"/>
-      <c r="N17" s="405" t="n"/>
-      <c r="O17" s="405" t="n"/>
-      <c r="P17" s="405" t="n"/>
-      <c r="Q17" s="405" t="n"/>
-      <c r="R17" s="405" t="n"/>
-      <c r="S17" s="405" t="n"/>
-      <c r="T17" s="405" t="n"/>
-      <c r="U17" s="405" t="n"/>
-      <c r="V17" s="405" t="n"/>
-      <c r="W17" s="405" t="n"/>
-      <c r="X17" s="405" t="n"/>
-      <c r="Y17" s="405" t="n"/>
-      <c r="Z17" s="405" t="n"/>
-      <c r="AA17" s="405" t="n"/>
-      <c r="AB17" s="405" t="n"/>
-      <c r="AC17" s="405" t="n"/>
-      <c r="AD17" s="405" t="n"/>
-      <c r="AE17" s="405" t="n"/>
-      <c r="AF17" s="405" t="n"/>
-      <c r="AG17" s="405" t="n"/>
-      <c r="AH17" s="405" t="n"/>
-      <c r="AI17" s="405" t="n"/>
-      <c r="AJ17" s="405" t="n"/>
-      <c r="AK17" s="405" t="n"/>
-      <c r="AL17" s="405" t="n"/>
-      <c r="AM17" s="405" t="n"/>
-      <c r="AN17" s="405" t="n"/>
-      <c r="AO17" s="405" t="n"/>
-      <c r="AP17" s="405" t="n"/>
-      <c r="AQ17" s="405" t="n"/>
-      <c r="AR17" s="405" t="n"/>
-      <c r="AS17" s="405" t="n"/>
-      <c r="AT17" s="405" t="n"/>
-      <c r="AU17" s="405" t="n"/>
-      <c r="AV17" s="405" t="n"/>
-      <c r="AW17" s="405" t="n"/>
-      <c r="AX17" s="405" t="n"/>
-      <c r="AY17" s="405" t="n"/>
-      <c r="AZ17" s="405" t="n"/>
-      <c r="BA17" s="405" t="n"/>
-      <c r="BB17" s="405" t="n"/>
-      <c r="BC17" s="405" t="n"/>
-      <c r="BD17" s="406" t="n"/>
+      <c r="B17" s="467" t="n"/>
+      <c r="C17" s="467" t="n"/>
+      <c r="D17" s="467" t="n"/>
+      <c r="E17" s="467" t="n"/>
+      <c r="F17" s="467" t="n"/>
+      <c r="G17" s="467" t="n"/>
+      <c r="H17" s="467" t="n"/>
+      <c r="I17" s="467" t="n"/>
+      <c r="J17" s="467" t="n"/>
+      <c r="K17" s="467" t="n"/>
+      <c r="L17" s="467" t="n"/>
+      <c r="M17" s="467" t="n"/>
+      <c r="N17" s="467" t="n"/>
+      <c r="O17" s="467" t="n"/>
+      <c r="P17" s="467" t="n"/>
+      <c r="Q17" s="467" t="n"/>
+      <c r="R17" s="467" t="n"/>
+      <c r="S17" s="467" t="n"/>
+      <c r="T17" s="467" t="n"/>
+      <c r="U17" s="467" t="n"/>
+      <c r="V17" s="467" t="n"/>
+      <c r="W17" s="467" t="n"/>
+      <c r="X17" s="467" t="n"/>
+      <c r="Y17" s="467" t="n"/>
+      <c r="Z17" s="467" t="n"/>
+      <c r="AA17" s="467" t="n"/>
+      <c r="AB17" s="467" t="n"/>
+      <c r="AC17" s="467" t="n"/>
+      <c r="AD17" s="467" t="n"/>
+      <c r="AE17" s="467" t="n"/>
+      <c r="AF17" s="467" t="n"/>
+      <c r="AG17" s="467" t="n"/>
+      <c r="AH17" s="467" t="n"/>
+      <c r="AI17" s="467" t="n"/>
+      <c r="AJ17" s="467" t="n"/>
+      <c r="AK17" s="467" t="n"/>
+      <c r="AL17" s="467" t="n"/>
+      <c r="AM17" s="467" t="n"/>
+      <c r="AN17" s="467" t="n"/>
+      <c r="AO17" s="467" t="n"/>
+      <c r="AP17" s="467" t="n"/>
+      <c r="AQ17" s="467" t="n"/>
+      <c r="AR17" s="467" t="n"/>
+      <c r="AS17" s="467" t="n"/>
+      <c r="AT17" s="467" t="n"/>
+      <c r="AU17" s="467" t="n"/>
+      <c r="AV17" s="467" t="n"/>
+      <c r="AW17" s="467" t="n"/>
+      <c r="AX17" s="467" t="n"/>
+      <c r="AY17" s="467" t="n"/>
+      <c r="AZ17" s="467" t="n"/>
+      <c r="BA17" s="467" t="n"/>
+      <c r="BB17" s="467" t="n"/>
+      <c r="BC17" s="467" t="n"/>
+      <c r="BD17" s="468" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="366" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="485" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="405" t="n"/>
-      <c r="C18" s="406" t="n"/>
-      <c r="D18" s="367" t="inlineStr">
+      <c r="B18" s="486" t="n"/>
+      <c r="C18" s="486" t="n"/>
+      <c r="D18" s="487" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="E18" s="405" t="n"/>
-      <c r="F18" s="405" t="n"/>
-      <c r="G18" s="406" t="n"/>
-      <c r="H18" s="367" t="inlineStr">
+      <c r="E18" s="486" t="n"/>
+      <c r="F18" s="486" t="n"/>
+      <c r="G18" s="486" t="n"/>
+      <c r="H18" s="487" t="inlineStr">
         <is>
           <t>Sample ID / Serial</t>
         </is>
       </c>
-      <c r="I18" s="405" t="n"/>
-      <c r="J18" s="405" t="n"/>
-      <c r="K18" s="405" t="n"/>
-      <c r="L18" s="405" t="n"/>
-      <c r="M18" s="405" t="n"/>
-      <c r="N18" s="405" t="n"/>
-      <c r="O18" s="405" t="n"/>
-      <c r="P18" s="405" t="n"/>
-      <c r="Q18" s="405" t="n"/>
-      <c r="R18" s="405" t="n"/>
-      <c r="S18" s="405" t="n"/>
-      <c r="T18" s="405" t="n"/>
-      <c r="U18" s="405" t="n"/>
-      <c r="V18" s="405" t="n"/>
-      <c r="W18" s="405" t="n"/>
-      <c r="X18" s="405" t="n"/>
-      <c r="Y18" s="405" t="n"/>
-      <c r="Z18" s="406" t="n"/>
-      <c r="AA18" s="367" t="inlineStr">
+      <c r="I18" s="486" t="n"/>
+      <c r="J18" s="486" t="n"/>
+      <c r="K18" s="486" t="n"/>
+      <c r="L18" s="486" t="n"/>
+      <c r="M18" s="486" t="n"/>
+      <c r="N18" s="486" t="n"/>
+      <c r="O18" s="486" t="n"/>
+      <c r="P18" s="486" t="n"/>
+      <c r="Q18" s="486" t="n"/>
+      <c r="R18" s="486" t="n"/>
+      <c r="S18" s="486" t="n"/>
+      <c r="T18" s="486" t="n"/>
+      <c r="U18" s="486" t="n"/>
+      <c r="V18" s="486" t="n"/>
+      <c r="W18" s="486" t="n"/>
+      <c r="X18" s="486" t="n"/>
+      <c r="Y18" s="486" t="n"/>
+      <c r="Z18" s="486" t="n"/>
+      <c r="AA18" s="487" t="inlineStr">
         <is>
           <t>Observation / Measured Result</t>
         </is>
       </c>
-      <c r="AB18" s="405" t="n"/>
-      <c r="AC18" s="405" t="n"/>
-      <c r="AD18" s="405" t="n"/>
-      <c r="AE18" s="405" t="n"/>
-      <c r="AF18" s="405" t="n"/>
-      <c r="AG18" s="405" t="n"/>
-      <c r="AH18" s="405" t="n"/>
-      <c r="AI18" s="405" t="n"/>
-      <c r="AJ18" s="405" t="n"/>
-      <c r="AK18" s="405" t="n"/>
-      <c r="AL18" s="405" t="n"/>
-      <c r="AM18" s="405" t="n"/>
-      <c r="AN18" s="405" t="n"/>
-      <c r="AO18" s="405" t="n"/>
-      <c r="AP18" s="405" t="n"/>
-      <c r="AQ18" s="406" t="n"/>
-      <c r="AR18" s="367" t="inlineStr">
+      <c r="AB18" s="486" t="n"/>
+      <c r="AC18" s="486" t="n"/>
+      <c r="AD18" s="486" t="n"/>
+      <c r="AE18" s="486" t="n"/>
+      <c r="AF18" s="486" t="n"/>
+      <c r="AG18" s="486" t="n"/>
+      <c r="AH18" s="486" t="n"/>
+      <c r="AI18" s="486" t="n"/>
+      <c r="AJ18" s="486" t="n"/>
+      <c r="AK18" s="486" t="n"/>
+      <c r="AL18" s="486" t="n"/>
+      <c r="AM18" s="486" t="n"/>
+      <c r="AN18" s="486" t="n"/>
+      <c r="AO18" s="486" t="n"/>
+      <c r="AP18" s="486" t="n"/>
+      <c r="AQ18" s="486" t="n"/>
+      <c r="AR18" s="487" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS18" s="405" t="n"/>
-      <c r="AT18" s="405" t="n"/>
-      <c r="AU18" s="405" t="n"/>
-      <c r="AV18" s="405" t="n"/>
-      <c r="AW18" s="406" t="n"/>
-      <c r="AX18" s="367" t="inlineStr">
+      <c r="AS18" s="486" t="n"/>
+      <c r="AT18" s="486" t="n"/>
+      <c r="AU18" s="486" t="n"/>
+      <c r="AV18" s="486" t="n"/>
+      <c r="AW18" s="486" t="n"/>
+      <c r="AX18" s="487" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY18" s="405" t="n"/>
-      <c r="AZ18" s="405" t="n"/>
-      <c r="BA18" s="406" t="n"/>
-      <c r="BB18" s="367" t="inlineStr">
+      <c r="AY18" s="486" t="n"/>
+      <c r="AZ18" s="486" t="n"/>
+      <c r="BA18" s="486" t="n"/>
+      <c r="BB18" s="487" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC18" s="405" t="n"/>
-      <c r="BD18" s="406" t="n"/>
+      <c r="BC18" s="486" t="n"/>
+      <c r="BD18" s="488" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="368">
+      <c r="A19" s="489">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B19" s="411" t="n"/>
-      <c r="C19" s="412" t="n"/>
-      <c r="D19" s="371" t="inlineStr">
+      <c r="B19" s="470" t="n"/>
+      <c r="C19" s="470" t="n"/>
+      <c r="D19" s="490" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="413" t="n"/>
-      <c r="F19" s="413" t="n"/>
-      <c r="G19" s="414" t="n"/>
-      <c r="H19" s="374" t="n"/>
-      <c r="I19" s="413" t="n"/>
-      <c r="J19" s="413" t="n"/>
-      <c r="K19" s="413" t="n"/>
-      <c r="L19" s="413" t="n"/>
-      <c r="M19" s="413" t="n"/>
-      <c r="N19" s="413" t="n"/>
-      <c r="O19" s="413" t="n"/>
-      <c r="P19" s="413" t="n"/>
-      <c r="Q19" s="413" t="n"/>
-      <c r="R19" s="413" t="n"/>
-      <c r="S19" s="413" t="n"/>
-      <c r="T19" s="413" t="n"/>
-      <c r="U19" s="413" t="n"/>
-      <c r="V19" s="413" t="n"/>
-      <c r="W19" s="413" t="n"/>
-      <c r="X19" s="413" t="n"/>
-      <c r="Y19" s="413" t="n"/>
-      <c r="Z19" s="414" t="n"/>
-      <c r="AA19" s="375" t="n"/>
-      <c r="AB19" s="413" t="n"/>
-      <c r="AC19" s="413" t="n"/>
-      <c r="AD19" s="413" t="n"/>
-      <c r="AE19" s="413" t="n"/>
-      <c r="AF19" s="413" t="n"/>
-      <c r="AG19" s="413" t="n"/>
-      <c r="AH19" s="413" t="n"/>
-      <c r="AI19" s="413" t="n"/>
-      <c r="AJ19" s="413" t="n"/>
-      <c r="AK19" s="413" t="n"/>
-      <c r="AL19" s="413" t="n"/>
-      <c r="AM19" s="413" t="n"/>
-      <c r="AN19" s="413" t="n"/>
-      <c r="AO19" s="413" t="n"/>
-      <c r="AP19" s="413" t="n"/>
-      <c r="AQ19" s="414" t="n"/>
-      <c r="AR19" s="374" t="n"/>
-      <c r="AS19" s="413" t="n"/>
-      <c r="AT19" s="413" t="n"/>
-      <c r="AU19" s="413" t="n"/>
-      <c r="AV19" s="413" t="n"/>
-      <c r="AW19" s="414" t="n"/>
-      <c r="AX19" s="374" t="n"/>
-      <c r="AY19" s="413" t="n"/>
-      <c r="AZ19" s="413" t="n"/>
-      <c r="BA19" s="414" t="n"/>
-      <c r="BB19" s="376" t="n"/>
-      <c r="BC19" s="413" t="n"/>
-      <c r="BD19" s="414" t="n"/>
+      <c r="E19" s="472" t="n"/>
+      <c r="F19" s="472" t="n"/>
+      <c r="G19" s="472" t="n"/>
+      <c r="H19" s="471" t="n"/>
+      <c r="I19" s="472" t="n"/>
+      <c r="J19" s="472" t="n"/>
+      <c r="K19" s="472" t="n"/>
+      <c r="L19" s="472" t="n"/>
+      <c r="M19" s="472" t="n"/>
+      <c r="N19" s="472" t="n"/>
+      <c r="O19" s="472" t="n"/>
+      <c r="P19" s="472" t="n"/>
+      <c r="Q19" s="472" t="n"/>
+      <c r="R19" s="472" t="n"/>
+      <c r="S19" s="472" t="n"/>
+      <c r="T19" s="472" t="n"/>
+      <c r="U19" s="472" t="n"/>
+      <c r="V19" s="472" t="n"/>
+      <c r="W19" s="472" t="n"/>
+      <c r="X19" s="472" t="n"/>
+      <c r="Y19" s="472" t="n"/>
+      <c r="Z19" s="472" t="n"/>
+      <c r="AA19" s="491" t="n"/>
+      <c r="AB19" s="472" t="n"/>
+      <c r="AC19" s="472" t="n"/>
+      <c r="AD19" s="472" t="n"/>
+      <c r="AE19" s="472" t="n"/>
+      <c r="AF19" s="472" t="n"/>
+      <c r="AG19" s="472" t="n"/>
+      <c r="AH19" s="472" t="n"/>
+      <c r="AI19" s="472" t="n"/>
+      <c r="AJ19" s="472" t="n"/>
+      <c r="AK19" s="472" t="n"/>
+      <c r="AL19" s="472" t="n"/>
+      <c r="AM19" s="472" t="n"/>
+      <c r="AN19" s="472" t="n"/>
+      <c r="AO19" s="472" t="n"/>
+      <c r="AP19" s="472" t="n"/>
+      <c r="AQ19" s="472" t="n"/>
+      <c r="AR19" s="471" t="n"/>
+      <c r="AS19" s="472" t="n"/>
+      <c r="AT19" s="472" t="n"/>
+      <c r="AU19" s="472" t="n"/>
+      <c r="AV19" s="472" t="n"/>
+      <c r="AW19" s="472" t="n"/>
+      <c r="AX19" s="471" t="n"/>
+      <c r="AY19" s="472" t="n"/>
+      <c r="AZ19" s="472" t="n"/>
+      <c r="BA19" s="472" t="n"/>
+      <c r="BB19" s="492" t="n"/>
+      <c r="BC19" s="472" t="n"/>
+      <c r="BD19" s="474" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="368">
+      <c r="A20" s="493">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B20" s="411" t="n"/>
-      <c r="C20" s="412" t="n"/>
-      <c r="D20" s="371" t="inlineStr">
+      <c r="B20" s="344" t="n"/>
+      <c r="C20" s="344" t="n"/>
+      <c r="D20" s="494" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="413" t="n"/>
-      <c r="F20" s="413" t="n"/>
-      <c r="G20" s="414" t="n"/>
-      <c r="H20" s="374" t="n"/>
-      <c r="I20" s="413" t="n"/>
-      <c r="J20" s="413" t="n"/>
-      <c r="K20" s="413" t="n"/>
-      <c r="L20" s="413" t="n"/>
-      <c r="M20" s="413" t="n"/>
-      <c r="N20" s="413" t="n"/>
-      <c r="O20" s="413" t="n"/>
-      <c r="P20" s="413" t="n"/>
-      <c r="Q20" s="413" t="n"/>
-      <c r="R20" s="413" t="n"/>
-      <c r="S20" s="413" t="n"/>
-      <c r="T20" s="413" t="n"/>
-      <c r="U20" s="413" t="n"/>
-      <c r="V20" s="413" t="n"/>
-      <c r="W20" s="413" t="n"/>
-      <c r="X20" s="413" t="n"/>
-      <c r="Y20" s="413" t="n"/>
-      <c r="Z20" s="414" t="n"/>
-      <c r="AA20" s="375" t="n"/>
-      <c r="AB20" s="413" t="n"/>
-      <c r="AC20" s="413" t="n"/>
-      <c r="AD20" s="413" t="n"/>
-      <c r="AE20" s="413" t="n"/>
-      <c r="AF20" s="413" t="n"/>
-      <c r="AG20" s="413" t="n"/>
-      <c r="AH20" s="413" t="n"/>
-      <c r="AI20" s="413" t="n"/>
-      <c r="AJ20" s="413" t="n"/>
-      <c r="AK20" s="413" t="n"/>
-      <c r="AL20" s="413" t="n"/>
-      <c r="AM20" s="413" t="n"/>
-      <c r="AN20" s="413" t="n"/>
-      <c r="AO20" s="413" t="n"/>
-      <c r="AP20" s="413" t="n"/>
-      <c r="AQ20" s="414" t="n"/>
-      <c r="AR20" s="374" t="n"/>
-      <c r="AS20" s="413" t="n"/>
-      <c r="AT20" s="413" t="n"/>
-      <c r="AU20" s="413" t="n"/>
-      <c r="AV20" s="413" t="n"/>
-      <c r="AW20" s="414" t="n"/>
-      <c r="AX20" s="374" t="n"/>
-      <c r="AY20" s="413" t="n"/>
-      <c r="AZ20" s="413" t="n"/>
-      <c r="BA20" s="414" t="n"/>
-      <c r="BB20" s="376" t="n"/>
-      <c r="BC20" s="413" t="n"/>
-      <c r="BD20" s="414" t="n"/>
+      <c r="E20" s="362" t="n"/>
+      <c r="F20" s="362" t="n"/>
+      <c r="G20" s="362" t="n"/>
+      <c r="H20" s="476" t="n"/>
+      <c r="I20" s="362" t="n"/>
+      <c r="J20" s="362" t="n"/>
+      <c r="K20" s="362" t="n"/>
+      <c r="L20" s="362" t="n"/>
+      <c r="M20" s="362" t="n"/>
+      <c r="N20" s="362" t="n"/>
+      <c r="O20" s="362" t="n"/>
+      <c r="P20" s="362" t="n"/>
+      <c r="Q20" s="362" t="n"/>
+      <c r="R20" s="362" t="n"/>
+      <c r="S20" s="362" t="n"/>
+      <c r="T20" s="362" t="n"/>
+      <c r="U20" s="362" t="n"/>
+      <c r="V20" s="362" t="n"/>
+      <c r="W20" s="362" t="n"/>
+      <c r="X20" s="362" t="n"/>
+      <c r="Y20" s="362" t="n"/>
+      <c r="Z20" s="362" t="n"/>
+      <c r="AA20" s="495" t="n"/>
+      <c r="AB20" s="362" t="n"/>
+      <c r="AC20" s="362" t="n"/>
+      <c r="AD20" s="362" t="n"/>
+      <c r="AE20" s="362" t="n"/>
+      <c r="AF20" s="362" t="n"/>
+      <c r="AG20" s="362" t="n"/>
+      <c r="AH20" s="362" t="n"/>
+      <c r="AI20" s="362" t="n"/>
+      <c r="AJ20" s="362" t="n"/>
+      <c r="AK20" s="362" t="n"/>
+      <c r="AL20" s="362" t="n"/>
+      <c r="AM20" s="362" t="n"/>
+      <c r="AN20" s="362" t="n"/>
+      <c r="AO20" s="362" t="n"/>
+      <c r="AP20" s="362" t="n"/>
+      <c r="AQ20" s="362" t="n"/>
+      <c r="AR20" s="476" t="n"/>
+      <c r="AS20" s="362" t="n"/>
+      <c r="AT20" s="362" t="n"/>
+      <c r="AU20" s="362" t="n"/>
+      <c r="AV20" s="362" t="n"/>
+      <c r="AW20" s="362" t="n"/>
+      <c r="AX20" s="476" t="n"/>
+      <c r="AY20" s="362" t="n"/>
+      <c r="AZ20" s="362" t="n"/>
+      <c r="BA20" s="362" t="n"/>
+      <c r="BB20" s="496" t="n"/>
+      <c r="BC20" s="362" t="n"/>
+      <c r="BD20" s="478" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="368">
+      <c r="A21" s="493">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B21" s="411" t="n"/>
-      <c r="C21" s="412" t="n"/>
-      <c r="D21" s="371" t="inlineStr">
+      <c r="B21" s="344" t="n"/>
+      <c r="C21" s="344" t="n"/>
+      <c r="D21" s="494" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="413" t="n"/>
-      <c r="F21" s="413" t="n"/>
-      <c r="G21" s="414" t="n"/>
-      <c r="H21" s="374" t="n"/>
-      <c r="I21" s="413" t="n"/>
-      <c r="J21" s="413" t="n"/>
-      <c r="K21" s="413" t="n"/>
-      <c r="L21" s="413" t="n"/>
-      <c r="M21" s="413" t="n"/>
-      <c r="N21" s="413" t="n"/>
-      <c r="O21" s="413" t="n"/>
-      <c r="P21" s="413" t="n"/>
-      <c r="Q21" s="413" t="n"/>
-      <c r="R21" s="413" t="n"/>
-      <c r="S21" s="413" t="n"/>
-      <c r="T21" s="413" t="n"/>
-      <c r="U21" s="413" t="n"/>
-      <c r="V21" s="413" t="n"/>
-      <c r="W21" s="413" t="n"/>
-      <c r="X21" s="413" t="n"/>
-      <c r="Y21" s="413" t="n"/>
-      <c r="Z21" s="414" t="n"/>
-      <c r="AA21" s="375" t="n"/>
-      <c r="AB21" s="413" t="n"/>
-      <c r="AC21" s="413" t="n"/>
-      <c r="AD21" s="413" t="n"/>
-      <c r="AE21" s="413" t="n"/>
-      <c r="AF21" s="413" t="n"/>
-      <c r="AG21" s="413" t="n"/>
-      <c r="AH21" s="413" t="n"/>
-      <c r="AI21" s="413" t="n"/>
-      <c r="AJ21" s="413" t="n"/>
-      <c r="AK21" s="413" t="n"/>
-      <c r="AL21" s="413" t="n"/>
-      <c r="AM21" s="413" t="n"/>
-      <c r="AN21" s="413" t="n"/>
-      <c r="AO21" s="413" t="n"/>
-      <c r="AP21" s="413" t="n"/>
-      <c r="AQ21" s="414" t="n"/>
-      <c r="AR21" s="374" t="n"/>
-      <c r="AS21" s="413" t="n"/>
-      <c r="AT21" s="413" t="n"/>
-      <c r="AU21" s="413" t="n"/>
-      <c r="AV21" s="413" t="n"/>
-      <c r="AW21" s="414" t="n"/>
-      <c r="AX21" s="374" t="n"/>
-      <c r="AY21" s="413" t="n"/>
-      <c r="AZ21" s="413" t="n"/>
-      <c r="BA21" s="414" t="n"/>
-      <c r="BB21" s="376" t="n"/>
-      <c r="BC21" s="413" t="n"/>
-      <c r="BD21" s="414" t="n"/>
+      <c r="E21" s="362" t="n"/>
+      <c r="F21" s="362" t="n"/>
+      <c r="G21" s="362" t="n"/>
+      <c r="H21" s="476" t="n"/>
+      <c r="I21" s="362" t="n"/>
+      <c r="J21" s="362" t="n"/>
+      <c r="K21" s="362" t="n"/>
+      <c r="L21" s="362" t="n"/>
+      <c r="M21" s="362" t="n"/>
+      <c r="N21" s="362" t="n"/>
+      <c r="O21" s="362" t="n"/>
+      <c r="P21" s="362" t="n"/>
+      <c r="Q21" s="362" t="n"/>
+      <c r="R21" s="362" t="n"/>
+      <c r="S21" s="362" t="n"/>
+      <c r="T21" s="362" t="n"/>
+      <c r="U21" s="362" t="n"/>
+      <c r="V21" s="362" t="n"/>
+      <c r="W21" s="362" t="n"/>
+      <c r="X21" s="362" t="n"/>
+      <c r="Y21" s="362" t="n"/>
+      <c r="Z21" s="362" t="n"/>
+      <c r="AA21" s="495" t="n"/>
+      <c r="AB21" s="362" t="n"/>
+      <c r="AC21" s="362" t="n"/>
+      <c r="AD21" s="362" t="n"/>
+      <c r="AE21" s="362" t="n"/>
+      <c r="AF21" s="362" t="n"/>
+      <c r="AG21" s="362" t="n"/>
+      <c r="AH21" s="362" t="n"/>
+      <c r="AI21" s="362" t="n"/>
+      <c r="AJ21" s="362" t="n"/>
+      <c r="AK21" s="362" t="n"/>
+      <c r="AL21" s="362" t="n"/>
+      <c r="AM21" s="362" t="n"/>
+      <c r="AN21" s="362" t="n"/>
+      <c r="AO21" s="362" t="n"/>
+      <c r="AP21" s="362" t="n"/>
+      <c r="AQ21" s="362" t="n"/>
+      <c r="AR21" s="476" t="n"/>
+      <c r="AS21" s="362" t="n"/>
+      <c r="AT21" s="362" t="n"/>
+      <c r="AU21" s="362" t="n"/>
+      <c r="AV21" s="362" t="n"/>
+      <c r="AW21" s="362" t="n"/>
+      <c r="AX21" s="476" t="n"/>
+      <c r="AY21" s="362" t="n"/>
+      <c r="AZ21" s="362" t="n"/>
+      <c r="BA21" s="362" t="n"/>
+      <c r="BB21" s="496" t="n"/>
+      <c r="BC21" s="362" t="n"/>
+      <c r="BD21" s="478" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="368">
+      <c r="A22" s="493">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B22" s="411" t="n"/>
-      <c r="C22" s="412" t="n"/>
-      <c r="D22" s="371" t="inlineStr">
+      <c r="B22" s="344" t="n"/>
+      <c r="C22" s="344" t="n"/>
+      <c r="D22" s="494" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="413" t="n"/>
-      <c r="F22" s="413" t="n"/>
-      <c r="G22" s="414" t="n"/>
-      <c r="H22" s="374" t="n"/>
-      <c r="I22" s="413" t="n"/>
-      <c r="J22" s="413" t="n"/>
-      <c r="K22" s="413" t="n"/>
-      <c r="L22" s="413" t="n"/>
-      <c r="M22" s="413" t="n"/>
-      <c r="N22" s="413" t="n"/>
-      <c r="O22" s="413" t="n"/>
-      <c r="P22" s="413" t="n"/>
-      <c r="Q22" s="413" t="n"/>
-      <c r="R22" s="413" t="n"/>
-      <c r="S22" s="413" t="n"/>
-      <c r="T22" s="413" t="n"/>
-      <c r="U22" s="413" t="n"/>
-      <c r="V22" s="413" t="n"/>
-      <c r="W22" s="413" t="n"/>
-      <c r="X22" s="413" t="n"/>
-      <c r="Y22" s="413" t="n"/>
-      <c r="Z22" s="414" t="n"/>
-      <c r="AA22" s="375" t="n"/>
-      <c r="AB22" s="413" t="n"/>
-      <c r="AC22" s="413" t="n"/>
-      <c r="AD22" s="413" t="n"/>
-      <c r="AE22" s="413" t="n"/>
-      <c r="AF22" s="413" t="n"/>
-      <c r="AG22" s="413" t="n"/>
-      <c r="AH22" s="413" t="n"/>
-      <c r="AI22" s="413" t="n"/>
-      <c r="AJ22" s="413" t="n"/>
-      <c r="AK22" s="413" t="n"/>
-      <c r="AL22" s="413" t="n"/>
-      <c r="AM22" s="413" t="n"/>
-      <c r="AN22" s="413" t="n"/>
-      <c r="AO22" s="413" t="n"/>
-      <c r="AP22" s="413" t="n"/>
-      <c r="AQ22" s="414" t="n"/>
-      <c r="AR22" s="374" t="n"/>
-      <c r="AS22" s="413" t="n"/>
-      <c r="AT22" s="413" t="n"/>
-      <c r="AU22" s="413" t="n"/>
-      <c r="AV22" s="413" t="n"/>
-      <c r="AW22" s="414" t="n"/>
-      <c r="AX22" s="374" t="n"/>
-      <c r="AY22" s="413" t="n"/>
-      <c r="AZ22" s="413" t="n"/>
-      <c r="BA22" s="414" t="n"/>
-      <c r="BB22" s="376" t="n"/>
-      <c r="BC22" s="413" t="n"/>
-      <c r="BD22" s="414" t="n"/>
+      <c r="E22" s="362" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="362" t="n"/>
+      <c r="H22" s="476" t="n"/>
+      <c r="I22" s="362" t="n"/>
+      <c r="J22" s="362" t="n"/>
+      <c r="K22" s="362" t="n"/>
+      <c r="L22" s="362" t="n"/>
+      <c r="M22" s="362" t="n"/>
+      <c r="N22" s="362" t="n"/>
+      <c r="O22" s="362" t="n"/>
+      <c r="P22" s="362" t="n"/>
+      <c r="Q22" s="362" t="n"/>
+      <c r="R22" s="362" t="n"/>
+      <c r="S22" s="362" t="n"/>
+      <c r="T22" s="362" t="n"/>
+      <c r="U22" s="362" t="n"/>
+      <c r="V22" s="362" t="n"/>
+      <c r="W22" s="362" t="n"/>
+      <c r="X22" s="362" t="n"/>
+      <c r="Y22" s="362" t="n"/>
+      <c r="Z22" s="362" t="n"/>
+      <c r="AA22" s="495" t="n"/>
+      <c r="AB22" s="362" t="n"/>
+      <c r="AC22" s="362" t="n"/>
+      <c r="AD22" s="362" t="n"/>
+      <c r="AE22" s="362" t="n"/>
+      <c r="AF22" s="362" t="n"/>
+      <c r="AG22" s="362" t="n"/>
+      <c r="AH22" s="362" t="n"/>
+      <c r="AI22" s="362" t="n"/>
+      <c r="AJ22" s="362" t="n"/>
+      <c r="AK22" s="362" t="n"/>
+      <c r="AL22" s="362" t="n"/>
+      <c r="AM22" s="362" t="n"/>
+      <c r="AN22" s="362" t="n"/>
+      <c r="AO22" s="362" t="n"/>
+      <c r="AP22" s="362" t="n"/>
+      <c r="AQ22" s="362" t="n"/>
+      <c r="AR22" s="476" t="n"/>
+      <c r="AS22" s="362" t="n"/>
+      <c r="AT22" s="362" t="n"/>
+      <c r="AU22" s="362" t="n"/>
+      <c r="AV22" s="362" t="n"/>
+      <c r="AW22" s="362" t="n"/>
+      <c r="AX22" s="476" t="n"/>
+      <c r="AY22" s="362" t="n"/>
+      <c r="AZ22" s="362" t="n"/>
+      <c r="BA22" s="362" t="n"/>
+      <c r="BB22" s="496" t="n"/>
+      <c r="BC22" s="362" t="n"/>
+      <c r="BD22" s="478" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="368">
+      <c r="A23" s="493">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B23" s="411" t="n"/>
-      <c r="C23" s="412" t="n"/>
-      <c r="D23" s="371" t="inlineStr">
+      <c r="B23" s="344" t="n"/>
+      <c r="C23" s="344" t="n"/>
+      <c r="D23" s="494" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="413" t="n"/>
-      <c r="F23" s="413" t="n"/>
-      <c r="G23" s="414" t="n"/>
-      <c r="H23" s="374" t="n"/>
-      <c r="I23" s="413" t="n"/>
-      <c r="J23" s="413" t="n"/>
-      <c r="K23" s="413" t="n"/>
-      <c r="L23" s="413" t="n"/>
-      <c r="M23" s="413" t="n"/>
-      <c r="N23" s="413" t="n"/>
-      <c r="O23" s="413" t="n"/>
-      <c r="P23" s="413" t="n"/>
-      <c r="Q23" s="413" t="n"/>
-      <c r="R23" s="413" t="n"/>
-      <c r="S23" s="413" t="n"/>
-      <c r="T23" s="413" t="n"/>
-      <c r="U23" s="413" t="n"/>
-      <c r="V23" s="413" t="n"/>
-      <c r="W23" s="413" t="n"/>
-      <c r="X23" s="413" t="n"/>
-      <c r="Y23" s="413" t="n"/>
-      <c r="Z23" s="414" t="n"/>
-      <c r="AA23" s="375" t="n"/>
-      <c r="AB23" s="413" t="n"/>
-      <c r="AC23" s="413" t="n"/>
-      <c r="AD23" s="413" t="n"/>
-      <c r="AE23" s="413" t="n"/>
-      <c r="AF23" s="413" t="n"/>
-      <c r="AG23" s="413" t="n"/>
-      <c r="AH23" s="413" t="n"/>
-      <c r="AI23" s="413" t="n"/>
-      <c r="AJ23" s="413" t="n"/>
-      <c r="AK23" s="413" t="n"/>
-      <c r="AL23" s="413" t="n"/>
-      <c r="AM23" s="413" t="n"/>
-      <c r="AN23" s="413" t="n"/>
-      <c r="AO23" s="413" t="n"/>
-      <c r="AP23" s="413" t="n"/>
-      <c r="AQ23" s="414" t="n"/>
-      <c r="AR23" s="374" t="n"/>
-      <c r="AS23" s="413" t="n"/>
-      <c r="AT23" s="413" t="n"/>
-      <c r="AU23" s="413" t="n"/>
-      <c r="AV23" s="413" t="n"/>
-      <c r="AW23" s="414" t="n"/>
-      <c r="AX23" s="374" t="n"/>
-      <c r="AY23" s="413" t="n"/>
-      <c r="AZ23" s="413" t="n"/>
-      <c r="BA23" s="414" t="n"/>
-      <c r="BB23" s="376" t="n"/>
-      <c r="BC23" s="413" t="n"/>
-      <c r="BD23" s="414" t="n"/>
+      <c r="E23" s="362" t="n"/>
+      <c r="F23" s="362" t="n"/>
+      <c r="G23" s="362" t="n"/>
+      <c r="H23" s="476" t="n"/>
+      <c r="I23" s="362" t="n"/>
+      <c r="J23" s="362" t="n"/>
+      <c r="K23" s="362" t="n"/>
+      <c r="L23" s="362" t="n"/>
+      <c r="M23" s="362" t="n"/>
+      <c r="N23" s="362" t="n"/>
+      <c r="O23" s="362" t="n"/>
+      <c r="P23" s="362" t="n"/>
+      <c r="Q23" s="362" t="n"/>
+      <c r="R23" s="362" t="n"/>
+      <c r="S23" s="362" t="n"/>
+      <c r="T23" s="362" t="n"/>
+      <c r="U23" s="362" t="n"/>
+      <c r="V23" s="362" t="n"/>
+      <c r="W23" s="362" t="n"/>
+      <c r="X23" s="362" t="n"/>
+      <c r="Y23" s="362" t="n"/>
+      <c r="Z23" s="362" t="n"/>
+      <c r="AA23" s="495" t="n"/>
+      <c r="AB23" s="362" t="n"/>
+      <c r="AC23" s="362" t="n"/>
+      <c r="AD23" s="362" t="n"/>
+      <c r="AE23" s="362" t="n"/>
+      <c r="AF23" s="362" t="n"/>
+      <c r="AG23" s="362" t="n"/>
+      <c r="AH23" s="362" t="n"/>
+      <c r="AI23" s="362" t="n"/>
+      <c r="AJ23" s="362" t="n"/>
+      <c r="AK23" s="362" t="n"/>
+      <c r="AL23" s="362" t="n"/>
+      <c r="AM23" s="362" t="n"/>
+      <c r="AN23" s="362" t="n"/>
+      <c r="AO23" s="362" t="n"/>
+      <c r="AP23" s="362" t="n"/>
+      <c r="AQ23" s="362" t="n"/>
+      <c r="AR23" s="476" t="n"/>
+      <c r="AS23" s="362" t="n"/>
+      <c r="AT23" s="362" t="n"/>
+      <c r="AU23" s="362" t="n"/>
+      <c r="AV23" s="362" t="n"/>
+      <c r="AW23" s="362" t="n"/>
+      <c r="AX23" s="476" t="n"/>
+      <c r="AY23" s="362" t="n"/>
+      <c r="AZ23" s="362" t="n"/>
+      <c r="BA23" s="362" t="n"/>
+      <c r="BB23" s="496" t="n"/>
+      <c r="BC23" s="362" t="n"/>
+      <c r="BD23" s="478" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="368">
+      <c r="A24" s="497">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B24" s="411" t="n"/>
-      <c r="C24" s="412" t="n"/>
-      <c r="D24" s="371" t="inlineStr">
+      <c r="B24" s="480" t="n"/>
+      <c r="C24" s="480" t="n"/>
+      <c r="D24" s="498" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="413" t="n"/>
-      <c r="F24" s="413" t="n"/>
-      <c r="G24" s="414" t="n"/>
-      <c r="H24" s="374" t="n"/>
-      <c r="I24" s="413" t="n"/>
-      <c r="J24" s="413" t="n"/>
-      <c r="K24" s="413" t="n"/>
-      <c r="L24" s="413" t="n"/>
-      <c r="M24" s="413" t="n"/>
-      <c r="N24" s="413" t="n"/>
-      <c r="O24" s="413" t="n"/>
-      <c r="P24" s="413" t="n"/>
-      <c r="Q24" s="413" t="n"/>
-      <c r="R24" s="413" t="n"/>
-      <c r="S24" s="413" t="n"/>
-      <c r="T24" s="413" t="n"/>
-      <c r="U24" s="413" t="n"/>
-      <c r="V24" s="413" t="n"/>
-      <c r="W24" s="413" t="n"/>
-      <c r="X24" s="413" t="n"/>
-      <c r="Y24" s="413" t="n"/>
-      <c r="Z24" s="414" t="n"/>
-      <c r="AA24" s="375" t="n"/>
-      <c r="AB24" s="413" t="n"/>
-      <c r="AC24" s="413" t="n"/>
-      <c r="AD24" s="413" t="n"/>
-      <c r="AE24" s="413" t="n"/>
-      <c r="AF24" s="413" t="n"/>
-      <c r="AG24" s="413" t="n"/>
-      <c r="AH24" s="413" t="n"/>
-      <c r="AI24" s="413" t="n"/>
-      <c r="AJ24" s="413" t="n"/>
-      <c r="AK24" s="413" t="n"/>
-      <c r="AL24" s="413" t="n"/>
-      <c r="AM24" s="413" t="n"/>
-      <c r="AN24" s="413" t="n"/>
-      <c r="AO24" s="413" t="n"/>
-      <c r="AP24" s="413" t="n"/>
-      <c r="AQ24" s="414" t="n"/>
-      <c r="AR24" s="374" t="n"/>
-      <c r="AS24" s="413" t="n"/>
-      <c r="AT24" s="413" t="n"/>
-      <c r="AU24" s="413" t="n"/>
-      <c r="AV24" s="413" t="n"/>
-      <c r="AW24" s="414" t="n"/>
-      <c r="AX24" s="374" t="n"/>
-      <c r="AY24" s="413" t="n"/>
-      <c r="AZ24" s="413" t="n"/>
-      <c r="BA24" s="414" t="n"/>
-      <c r="BB24" s="376" t="n"/>
-      <c r="BC24" s="413" t="n"/>
-      <c r="BD24" s="414" t="n"/>
+      <c r="E24" s="482" t="n"/>
+      <c r="F24" s="482" t="n"/>
+      <c r="G24" s="482" t="n"/>
+      <c r="H24" s="481" t="n"/>
+      <c r="I24" s="482" t="n"/>
+      <c r="J24" s="482" t="n"/>
+      <c r="K24" s="482" t="n"/>
+      <c r="L24" s="482" t="n"/>
+      <c r="M24" s="482" t="n"/>
+      <c r="N24" s="482" t="n"/>
+      <c r="O24" s="482" t="n"/>
+      <c r="P24" s="482" t="n"/>
+      <c r="Q24" s="482" t="n"/>
+      <c r="R24" s="482" t="n"/>
+      <c r="S24" s="482" t="n"/>
+      <c r="T24" s="482" t="n"/>
+      <c r="U24" s="482" t="n"/>
+      <c r="V24" s="482" t="n"/>
+      <c r="W24" s="482" t="n"/>
+      <c r="X24" s="482" t="n"/>
+      <c r="Y24" s="482" t="n"/>
+      <c r="Z24" s="482" t="n"/>
+      <c r="AA24" s="499" t="n"/>
+      <c r="AB24" s="482" t="n"/>
+      <c r="AC24" s="482" t="n"/>
+      <c r="AD24" s="482" t="n"/>
+      <c r="AE24" s="482" t="n"/>
+      <c r="AF24" s="482" t="n"/>
+      <c r="AG24" s="482" t="n"/>
+      <c r="AH24" s="482" t="n"/>
+      <c r="AI24" s="482" t="n"/>
+      <c r="AJ24" s="482" t="n"/>
+      <c r="AK24" s="482" t="n"/>
+      <c r="AL24" s="482" t="n"/>
+      <c r="AM24" s="482" t="n"/>
+      <c r="AN24" s="482" t="n"/>
+      <c r="AO24" s="482" t="n"/>
+      <c r="AP24" s="482" t="n"/>
+      <c r="AQ24" s="482" t="n"/>
+      <c r="AR24" s="481" t="n"/>
+      <c r="AS24" s="482" t="n"/>
+      <c r="AT24" s="482" t="n"/>
+      <c r="AU24" s="482" t="n"/>
+      <c r="AV24" s="482" t="n"/>
+      <c r="AW24" s="482" t="n"/>
+      <c r="AX24" s="481" t="n"/>
+      <c r="AY24" s="482" t="n"/>
+      <c r="AZ24" s="482" t="n"/>
+      <c r="BA24" s="482" t="n"/>
+      <c r="BB24" s="500" t="n"/>
+      <c r="BC24" s="482" t="n"/>
+      <c r="BD24" s="484" t="n"/>
     </row>
-    <row r="25" ht="4" customHeight="1">
+    <row r="25" ht="3" customHeight="1">
       <c r="A25" s="377" t="n"/>
       <c r="B25" s="353" t="n"/>
       <c r="C25" s="353" t="n"/>
@@ -6840,267 +7725,267 @@
       <c r="BC25" s="353" t="n"/>
       <c r="BD25" s="353" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="354" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="466" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B26" s="405" t="n"/>
-      <c r="C26" s="405" t="n"/>
-      <c r="D26" s="405" t="n"/>
-      <c r="E26" s="405" t="n"/>
-      <c r="F26" s="405" t="n"/>
-      <c r="G26" s="405" t="n"/>
-      <c r="H26" s="405" t="n"/>
-      <c r="I26" s="405" t="n"/>
-      <c r="J26" s="405" t="n"/>
-      <c r="K26" s="405" t="n"/>
-      <c r="L26" s="405" t="n"/>
-      <c r="M26" s="405" t="n"/>
-      <c r="N26" s="405" t="n"/>
-      <c r="O26" s="405" t="n"/>
-      <c r="P26" s="405" t="n"/>
-      <c r="Q26" s="405" t="n"/>
-      <c r="R26" s="405" t="n"/>
-      <c r="S26" s="405" t="n"/>
-      <c r="T26" s="405" t="n"/>
-      <c r="U26" s="405" t="n"/>
-      <c r="V26" s="405" t="n"/>
-      <c r="W26" s="405" t="n"/>
-      <c r="X26" s="405" t="n"/>
-      <c r="Y26" s="405" t="n"/>
-      <c r="Z26" s="405" t="n"/>
-      <c r="AA26" s="405" t="n"/>
-      <c r="AB26" s="405" t="n"/>
-      <c r="AC26" s="405" t="n"/>
-      <c r="AD26" s="405" t="n"/>
-      <c r="AE26" s="405" t="n"/>
-      <c r="AF26" s="405" t="n"/>
-      <c r="AG26" s="405" t="n"/>
-      <c r="AH26" s="405" t="n"/>
-      <c r="AI26" s="405" t="n"/>
-      <c r="AJ26" s="405" t="n"/>
-      <c r="AK26" s="405" t="n"/>
-      <c r="AL26" s="405" t="n"/>
-      <c r="AM26" s="405" t="n"/>
-      <c r="AN26" s="405" t="n"/>
-      <c r="AO26" s="405" t="n"/>
-      <c r="AP26" s="405" t="n"/>
-      <c r="AQ26" s="405" t="n"/>
-      <c r="AR26" s="405" t="n"/>
-      <c r="AS26" s="405" t="n"/>
-      <c r="AT26" s="405" t="n"/>
-      <c r="AU26" s="405" t="n"/>
-      <c r="AV26" s="405" t="n"/>
-      <c r="AW26" s="405" t="n"/>
-      <c r="AX26" s="405" t="n"/>
-      <c r="AY26" s="405" t="n"/>
-      <c r="AZ26" s="405" t="n"/>
-      <c r="BA26" s="405" t="n"/>
-      <c r="BB26" s="405" t="n"/>
-      <c r="BC26" s="405" t="n"/>
-      <c r="BD26" s="406" t="n"/>
+      <c r="B26" s="467" t="n"/>
+      <c r="C26" s="467" t="n"/>
+      <c r="D26" s="467" t="n"/>
+      <c r="E26" s="467" t="n"/>
+      <c r="F26" s="467" t="n"/>
+      <c r="G26" s="467" t="n"/>
+      <c r="H26" s="467" t="n"/>
+      <c r="I26" s="467" t="n"/>
+      <c r="J26" s="467" t="n"/>
+      <c r="K26" s="467" t="n"/>
+      <c r="L26" s="467" t="n"/>
+      <c r="M26" s="467" t="n"/>
+      <c r="N26" s="467" t="n"/>
+      <c r="O26" s="467" t="n"/>
+      <c r="P26" s="467" t="n"/>
+      <c r="Q26" s="467" t="n"/>
+      <c r="R26" s="467" t="n"/>
+      <c r="S26" s="467" t="n"/>
+      <c r="T26" s="467" t="n"/>
+      <c r="U26" s="467" t="n"/>
+      <c r="V26" s="467" t="n"/>
+      <c r="W26" s="467" t="n"/>
+      <c r="X26" s="467" t="n"/>
+      <c r="Y26" s="467" t="n"/>
+      <c r="Z26" s="467" t="n"/>
+      <c r="AA26" s="467" t="n"/>
+      <c r="AB26" s="467" t="n"/>
+      <c r="AC26" s="467" t="n"/>
+      <c r="AD26" s="467" t="n"/>
+      <c r="AE26" s="467" t="n"/>
+      <c r="AF26" s="467" t="n"/>
+      <c r="AG26" s="467" t="n"/>
+      <c r="AH26" s="467" t="n"/>
+      <c r="AI26" s="467" t="n"/>
+      <c r="AJ26" s="467" t="n"/>
+      <c r="AK26" s="467" t="n"/>
+      <c r="AL26" s="467" t="n"/>
+      <c r="AM26" s="467" t="n"/>
+      <c r="AN26" s="467" t="n"/>
+      <c r="AO26" s="467" t="n"/>
+      <c r="AP26" s="467" t="n"/>
+      <c r="AQ26" s="467" t="n"/>
+      <c r="AR26" s="467" t="n"/>
+      <c r="AS26" s="467" t="n"/>
+      <c r="AT26" s="467" t="n"/>
+      <c r="AU26" s="467" t="n"/>
+      <c r="AV26" s="467" t="n"/>
+      <c r="AW26" s="467" t="n"/>
+      <c r="AX26" s="467" t="n"/>
+      <c r="AY26" s="467" t="n"/>
+      <c r="AZ26" s="467" t="n"/>
+      <c r="BA26" s="467" t="n"/>
+      <c r="BB26" s="467" t="n"/>
+      <c r="BC26" s="467" t="n"/>
+      <c r="BD26" s="468" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="355" t="inlineStr">
+      <c r="A27" s="469" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="B27" s="405" t="n"/>
-      <c r="C27" s="405" t="n"/>
-      <c r="D27" s="405" t="n"/>
-      <c r="E27" s="405" t="n"/>
-      <c r="F27" s="405" t="n"/>
-      <c r="G27" s="405" t="n"/>
-      <c r="H27" s="405" t="n"/>
-      <c r="I27" s="405" t="n"/>
-      <c r="J27" s="406" t="n"/>
-      <c r="K27" s="358" t="n"/>
-      <c r="L27" s="407" t="n"/>
-      <c r="M27" s="407" t="n"/>
-      <c r="N27" s="407" t="n"/>
-      <c r="O27" s="407" t="n"/>
-      <c r="P27" s="407" t="n"/>
-      <c r="Q27" s="407" t="n"/>
-      <c r="R27" s="407" t="n"/>
-      <c r="S27" s="407" t="n"/>
-      <c r="T27" s="407" t="n"/>
-      <c r="U27" s="407" t="n"/>
-      <c r="V27" s="407" t="n"/>
-      <c r="W27" s="407" t="n"/>
-      <c r="X27" s="407" t="n"/>
-      <c r="Y27" s="407" t="n"/>
-      <c r="Z27" s="407" t="n"/>
-      <c r="AA27" s="407" t="n"/>
-      <c r="AB27" s="408" t="n"/>
-      <c r="AC27" s="361" t="inlineStr">
+      <c r="B27" s="470" t="n"/>
+      <c r="C27" s="470" t="n"/>
+      <c r="D27" s="470" t="n"/>
+      <c r="E27" s="470" t="n"/>
+      <c r="F27" s="470" t="n"/>
+      <c r="G27" s="470" t="n"/>
+      <c r="H27" s="470" t="n"/>
+      <c r="I27" s="470" t="n"/>
+      <c r="J27" s="470" t="n"/>
+      <c r="K27" s="471" t="n"/>
+      <c r="L27" s="472" t="n"/>
+      <c r="M27" s="472" t="n"/>
+      <c r="N27" s="472" t="n"/>
+      <c r="O27" s="472" t="n"/>
+      <c r="P27" s="472" t="n"/>
+      <c r="Q27" s="472" t="n"/>
+      <c r="R27" s="472" t="n"/>
+      <c r="S27" s="472" t="n"/>
+      <c r="T27" s="472" t="n"/>
+      <c r="U27" s="472" t="n"/>
+      <c r="V27" s="472" t="n"/>
+      <c r="W27" s="472" t="n"/>
+      <c r="X27" s="472" t="n"/>
+      <c r="Y27" s="472" t="n"/>
+      <c r="Z27" s="472" t="n"/>
+      <c r="AA27" s="472" t="n"/>
+      <c r="AB27" s="472" t="n"/>
+      <c r="AC27" s="473" t="inlineStr">
         <is>
           <t>AQL Disposition</t>
         </is>
       </c>
-      <c r="AD27" s="405" t="n"/>
-      <c r="AE27" s="405" t="n"/>
-      <c r="AF27" s="405" t="n"/>
-      <c r="AG27" s="405" t="n"/>
-      <c r="AH27" s="405" t="n"/>
-      <c r="AI27" s="405" t="n"/>
-      <c r="AJ27" s="405" t="n"/>
-      <c r="AK27" s="405" t="n"/>
-      <c r="AL27" s="406" t="n"/>
-      <c r="AM27" s="358" t="n"/>
-      <c r="AN27" s="407" t="n"/>
-      <c r="AO27" s="407" t="n"/>
-      <c r="AP27" s="407" t="n"/>
-      <c r="AQ27" s="407" t="n"/>
-      <c r="AR27" s="407" t="n"/>
-      <c r="AS27" s="407" t="n"/>
-      <c r="AT27" s="407" t="n"/>
-      <c r="AU27" s="407" t="n"/>
-      <c r="AV27" s="407" t="n"/>
-      <c r="AW27" s="407" t="n"/>
-      <c r="AX27" s="407" t="n"/>
-      <c r="AY27" s="407" t="n"/>
-      <c r="AZ27" s="407" t="n"/>
-      <c r="BA27" s="407" t="n"/>
-      <c r="BB27" s="407" t="n"/>
-      <c r="BC27" s="407" t="n"/>
-      <c r="BD27" s="408" t="n"/>
+      <c r="AD27" s="470" t="n"/>
+      <c r="AE27" s="470" t="n"/>
+      <c r="AF27" s="470" t="n"/>
+      <c r="AG27" s="470" t="n"/>
+      <c r="AH27" s="470" t="n"/>
+      <c r="AI27" s="470" t="n"/>
+      <c r="AJ27" s="470" t="n"/>
+      <c r="AK27" s="470" t="n"/>
+      <c r="AL27" s="470" t="n"/>
+      <c r="AM27" s="471" t="n"/>
+      <c r="AN27" s="472" t="n"/>
+      <c r="AO27" s="472" t="n"/>
+      <c r="AP27" s="472" t="n"/>
+      <c r="AQ27" s="472" t="n"/>
+      <c r="AR27" s="472" t="n"/>
+      <c r="AS27" s="472" t="n"/>
+      <c r="AT27" s="472" t="n"/>
+      <c r="AU27" s="472" t="n"/>
+      <c r="AV27" s="472" t="n"/>
+      <c r="AW27" s="472" t="n"/>
+      <c r="AX27" s="472" t="n"/>
+      <c r="AY27" s="472" t="n"/>
+      <c r="AZ27" s="472" t="n"/>
+      <c r="BA27" s="472" t="n"/>
+      <c r="BB27" s="472" t="n"/>
+      <c r="BC27" s="472" t="n"/>
+      <c r="BD27" s="474" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="355" t="inlineStr">
+      <c r="A28" s="475" t="inlineStr">
         <is>
           <t>100% Sort Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B28" s="405" t="n"/>
-      <c r="C28" s="405" t="n"/>
-      <c r="D28" s="405" t="n"/>
-      <c r="E28" s="405" t="n"/>
-      <c r="F28" s="405" t="n"/>
-      <c r="G28" s="405" t="n"/>
-      <c r="H28" s="405" t="n"/>
-      <c r="I28" s="405" t="n"/>
-      <c r="J28" s="406" t="n"/>
-      <c r="K28" s="358" t="n"/>
-      <c r="L28" s="407" t="n"/>
-      <c r="M28" s="407" t="n"/>
-      <c r="N28" s="407" t="n"/>
-      <c r="O28" s="407" t="n"/>
-      <c r="P28" s="407" t="n"/>
-      <c r="Q28" s="407" t="n"/>
-      <c r="R28" s="407" t="n"/>
-      <c r="S28" s="407" t="n"/>
-      <c r="T28" s="407" t="n"/>
-      <c r="U28" s="407" t="n"/>
-      <c r="V28" s="407" t="n"/>
-      <c r="W28" s="407" t="n"/>
-      <c r="X28" s="407" t="n"/>
-      <c r="Y28" s="407" t="n"/>
-      <c r="Z28" s="407" t="n"/>
-      <c r="AA28" s="407" t="n"/>
-      <c r="AB28" s="408" t="n"/>
-      <c r="AC28" s="361" t="inlineStr">
+      <c r="B28" s="344" t="n"/>
+      <c r="C28" s="344" t="n"/>
+      <c r="D28" s="344" t="n"/>
+      <c r="E28" s="344" t="n"/>
+      <c r="F28" s="344" t="n"/>
+      <c r="G28" s="344" t="n"/>
+      <c r="H28" s="344" t="n"/>
+      <c r="I28" s="344" t="n"/>
+      <c r="J28" s="344" t="n"/>
+      <c r="K28" s="476" t="n"/>
+      <c r="L28" s="362" t="n"/>
+      <c r="M28" s="362" t="n"/>
+      <c r="N28" s="362" t="n"/>
+      <c r="O28" s="362" t="n"/>
+      <c r="P28" s="362" t="n"/>
+      <c r="Q28" s="362" t="n"/>
+      <c r="R28" s="362" t="n"/>
+      <c r="S28" s="362" t="n"/>
+      <c r="T28" s="362" t="n"/>
+      <c r="U28" s="362" t="n"/>
+      <c r="V28" s="362" t="n"/>
+      <c r="W28" s="362" t="n"/>
+      <c r="X28" s="362" t="n"/>
+      <c r="Y28" s="362" t="n"/>
+      <c r="Z28" s="362" t="n"/>
+      <c r="AA28" s="362" t="n"/>
+      <c r="AB28" s="362" t="n"/>
+      <c r="AC28" s="477" t="inlineStr">
         <is>
           <t>Linked NCR Ref</t>
         </is>
       </c>
-      <c r="AD28" s="405" t="n"/>
-      <c r="AE28" s="405" t="n"/>
-      <c r="AF28" s="405" t="n"/>
-      <c r="AG28" s="405" t="n"/>
-      <c r="AH28" s="405" t="n"/>
-      <c r="AI28" s="405" t="n"/>
-      <c r="AJ28" s="405" t="n"/>
-      <c r="AK28" s="405" t="n"/>
-      <c r="AL28" s="406" t="n"/>
-      <c r="AM28" s="358" t="n"/>
-      <c r="AN28" s="407" t="n"/>
-      <c r="AO28" s="407" t="n"/>
-      <c r="AP28" s="407" t="n"/>
-      <c r="AQ28" s="407" t="n"/>
-      <c r="AR28" s="407" t="n"/>
-      <c r="AS28" s="407" t="n"/>
-      <c r="AT28" s="407" t="n"/>
-      <c r="AU28" s="407" t="n"/>
-      <c r="AV28" s="407" t="n"/>
-      <c r="AW28" s="407" t="n"/>
-      <c r="AX28" s="407" t="n"/>
-      <c r="AY28" s="407" t="n"/>
-      <c r="AZ28" s="407" t="n"/>
-      <c r="BA28" s="407" t="n"/>
-      <c r="BB28" s="407" t="n"/>
-      <c r="BC28" s="407" t="n"/>
-      <c r="BD28" s="408" t="n"/>
+      <c r="AD28" s="344" t="n"/>
+      <c r="AE28" s="344" t="n"/>
+      <c r="AF28" s="344" t="n"/>
+      <c r="AG28" s="344" t="n"/>
+      <c r="AH28" s="344" t="n"/>
+      <c r="AI28" s="344" t="n"/>
+      <c r="AJ28" s="344" t="n"/>
+      <c r="AK28" s="344" t="n"/>
+      <c r="AL28" s="344" t="n"/>
+      <c r="AM28" s="476" t="n"/>
+      <c r="AN28" s="362" t="n"/>
+      <c r="AO28" s="362" t="n"/>
+      <c r="AP28" s="362" t="n"/>
+      <c r="AQ28" s="362" t="n"/>
+      <c r="AR28" s="362" t="n"/>
+      <c r="AS28" s="362" t="n"/>
+      <c r="AT28" s="362" t="n"/>
+      <c r="AU28" s="362" t="n"/>
+      <c r="AV28" s="362" t="n"/>
+      <c r="AW28" s="362" t="n"/>
+      <c r="AX28" s="362" t="n"/>
+      <c r="AY28" s="362" t="n"/>
+      <c r="AZ28" s="362" t="n"/>
+      <c r="BA28" s="362" t="n"/>
+      <c r="BB28" s="362" t="n"/>
+      <c r="BC28" s="362" t="n"/>
+      <c r="BD28" s="478" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="355" t="inlineStr">
+      <c r="A29" s="479" t="inlineStr">
         <is>
           <t>Lot Release Decision</t>
         </is>
       </c>
-      <c r="B29" s="405" t="n"/>
-      <c r="C29" s="405" t="n"/>
-      <c r="D29" s="405" t="n"/>
-      <c r="E29" s="405" t="n"/>
-      <c r="F29" s="405" t="n"/>
-      <c r="G29" s="405" t="n"/>
-      <c r="H29" s="405" t="n"/>
-      <c r="I29" s="405" t="n"/>
-      <c r="J29" s="406" t="n"/>
-      <c r="K29" s="358" t="n"/>
-      <c r="L29" s="407" t="n"/>
-      <c r="M29" s="407" t="n"/>
-      <c r="N29" s="407" t="n"/>
-      <c r="O29" s="407" t="n"/>
-      <c r="P29" s="407" t="n"/>
-      <c r="Q29" s="407" t="n"/>
-      <c r="R29" s="407" t="n"/>
-      <c r="S29" s="407" t="n"/>
-      <c r="T29" s="407" t="n"/>
-      <c r="U29" s="407" t="n"/>
-      <c r="V29" s="407" t="n"/>
-      <c r="W29" s="407" t="n"/>
-      <c r="X29" s="407" t="n"/>
-      <c r="Y29" s="407" t="n"/>
-      <c r="Z29" s="407" t="n"/>
-      <c r="AA29" s="407" t="n"/>
-      <c r="AB29" s="408" t="n"/>
-      <c r="AC29" s="361" t="inlineStr">
+      <c r="B29" s="480" t="n"/>
+      <c r="C29" s="480" t="n"/>
+      <c r="D29" s="480" t="n"/>
+      <c r="E29" s="480" t="n"/>
+      <c r="F29" s="480" t="n"/>
+      <c r="G29" s="480" t="n"/>
+      <c r="H29" s="480" t="n"/>
+      <c r="I29" s="480" t="n"/>
+      <c r="J29" s="480" t="n"/>
+      <c r="K29" s="481" t="n"/>
+      <c r="L29" s="482" t="n"/>
+      <c r="M29" s="482" t="n"/>
+      <c r="N29" s="482" t="n"/>
+      <c r="O29" s="482" t="n"/>
+      <c r="P29" s="482" t="n"/>
+      <c r="Q29" s="482" t="n"/>
+      <c r="R29" s="482" t="n"/>
+      <c r="S29" s="482" t="n"/>
+      <c r="T29" s="482" t="n"/>
+      <c r="U29" s="482" t="n"/>
+      <c r="V29" s="482" t="n"/>
+      <c r="W29" s="482" t="n"/>
+      <c r="X29" s="482" t="n"/>
+      <c r="Y29" s="482" t="n"/>
+      <c r="Z29" s="482" t="n"/>
+      <c r="AA29" s="482" t="n"/>
+      <c r="AB29" s="482" t="n"/>
+      <c r="AC29" s="483" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="AD29" s="405" t="n"/>
-      <c r="AE29" s="405" t="n"/>
-      <c r="AF29" s="405" t="n"/>
-      <c r="AG29" s="405" t="n"/>
-      <c r="AH29" s="405" t="n"/>
-      <c r="AI29" s="405" t="n"/>
-      <c r="AJ29" s="405" t="n"/>
-      <c r="AK29" s="405" t="n"/>
-      <c r="AL29" s="406" t="n"/>
-      <c r="AM29" s="358" t="n"/>
-      <c r="AN29" s="407" t="n"/>
-      <c r="AO29" s="407" t="n"/>
-      <c r="AP29" s="407" t="n"/>
-      <c r="AQ29" s="407" t="n"/>
-      <c r="AR29" s="407" t="n"/>
-      <c r="AS29" s="407" t="n"/>
-      <c r="AT29" s="407" t="n"/>
-      <c r="AU29" s="407" t="n"/>
-      <c r="AV29" s="407" t="n"/>
-      <c r="AW29" s="407" t="n"/>
-      <c r="AX29" s="407" t="n"/>
-      <c r="AY29" s="407" t="n"/>
-      <c r="AZ29" s="407" t="n"/>
-      <c r="BA29" s="407" t="n"/>
-      <c r="BB29" s="407" t="n"/>
-      <c r="BC29" s="407" t="n"/>
-      <c r="BD29" s="408" t="n"/>
+      <c r="AD29" s="480" t="n"/>
+      <c r="AE29" s="480" t="n"/>
+      <c r="AF29" s="480" t="n"/>
+      <c r="AG29" s="480" t="n"/>
+      <c r="AH29" s="480" t="n"/>
+      <c r="AI29" s="480" t="n"/>
+      <c r="AJ29" s="480" t="n"/>
+      <c r="AK29" s="480" t="n"/>
+      <c r="AL29" s="480" t="n"/>
+      <c r="AM29" s="481" t="n"/>
+      <c r="AN29" s="482" t="n"/>
+      <c r="AO29" s="482" t="n"/>
+      <c r="AP29" s="482" t="n"/>
+      <c r="AQ29" s="482" t="n"/>
+      <c r="AR29" s="482" t="n"/>
+      <c r="AS29" s="482" t="n"/>
+      <c r="AT29" s="482" t="n"/>
+      <c r="AU29" s="482" t="n"/>
+      <c r="AV29" s="482" t="n"/>
+      <c r="AW29" s="482" t="n"/>
+      <c r="AX29" s="482" t="n"/>
+      <c r="AY29" s="482" t="n"/>
+      <c r="AZ29" s="482" t="n"/>
+      <c r="BA29" s="482" t="n"/>
+      <c r="BB29" s="482" t="n"/>
+      <c r="BC29" s="482" t="n"/>
+      <c r="BD29" s="484" t="n"/>
     </row>
-    <row r="30" ht="4" customHeight="1">
+    <row r="30" ht="3" customHeight="1">
       <c r="A30" s="377" t="n"/>
       <c r="B30" s="353" t="n"/>
       <c r="C30" s="353" t="n"/>
@@ -7158,325 +8043,325 @@
       <c r="BC30" s="353" t="n"/>
       <c r="BD30" s="353" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="354" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="466" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B31" s="405" t="n"/>
-      <c r="C31" s="405" t="n"/>
-      <c r="D31" s="405" t="n"/>
-      <c r="E31" s="405" t="n"/>
-      <c r="F31" s="405" t="n"/>
-      <c r="G31" s="405" t="n"/>
-      <c r="H31" s="405" t="n"/>
-      <c r="I31" s="405" t="n"/>
-      <c r="J31" s="405" t="n"/>
-      <c r="K31" s="405" t="n"/>
-      <c r="L31" s="405" t="n"/>
-      <c r="M31" s="405" t="n"/>
-      <c r="N31" s="405" t="n"/>
-      <c r="O31" s="405" t="n"/>
-      <c r="P31" s="405" t="n"/>
-      <c r="Q31" s="405" t="n"/>
-      <c r="R31" s="405" t="n"/>
-      <c r="S31" s="405" t="n"/>
-      <c r="T31" s="405" t="n"/>
-      <c r="U31" s="405" t="n"/>
-      <c r="V31" s="405" t="n"/>
-      <c r="W31" s="405" t="n"/>
-      <c r="X31" s="405" t="n"/>
-      <c r="Y31" s="405" t="n"/>
-      <c r="Z31" s="405" t="n"/>
-      <c r="AA31" s="405" t="n"/>
-      <c r="AB31" s="405" t="n"/>
-      <c r="AC31" s="405" t="n"/>
-      <c r="AD31" s="405" t="n"/>
-      <c r="AE31" s="405" t="n"/>
-      <c r="AF31" s="405" t="n"/>
-      <c r="AG31" s="405" t="n"/>
-      <c r="AH31" s="405" t="n"/>
-      <c r="AI31" s="405" t="n"/>
-      <c r="AJ31" s="405" t="n"/>
-      <c r="AK31" s="405" t="n"/>
-      <c r="AL31" s="405" t="n"/>
-      <c r="AM31" s="405" t="n"/>
-      <c r="AN31" s="405" t="n"/>
-      <c r="AO31" s="405" t="n"/>
-      <c r="AP31" s="405" t="n"/>
-      <c r="AQ31" s="405" t="n"/>
-      <c r="AR31" s="405" t="n"/>
-      <c r="AS31" s="405" t="n"/>
-      <c r="AT31" s="405" t="n"/>
-      <c r="AU31" s="405" t="n"/>
-      <c r="AV31" s="405" t="n"/>
-      <c r="AW31" s="405" t="n"/>
-      <c r="AX31" s="405" t="n"/>
-      <c r="AY31" s="405" t="n"/>
-      <c r="AZ31" s="405" t="n"/>
-      <c r="BA31" s="405" t="n"/>
-      <c r="BB31" s="405" t="n"/>
-      <c r="BC31" s="405" t="n"/>
-      <c r="BD31" s="406" t="n"/>
+      <c r="B31" s="467" t="n"/>
+      <c r="C31" s="467" t="n"/>
+      <c r="D31" s="467" t="n"/>
+      <c r="E31" s="467" t="n"/>
+      <c r="F31" s="467" t="n"/>
+      <c r="G31" s="467" t="n"/>
+      <c r="H31" s="467" t="n"/>
+      <c r="I31" s="467" t="n"/>
+      <c r="J31" s="467" t="n"/>
+      <c r="K31" s="467" t="n"/>
+      <c r="L31" s="467" t="n"/>
+      <c r="M31" s="467" t="n"/>
+      <c r="N31" s="467" t="n"/>
+      <c r="O31" s="467" t="n"/>
+      <c r="P31" s="467" t="n"/>
+      <c r="Q31" s="467" t="n"/>
+      <c r="R31" s="467" t="n"/>
+      <c r="S31" s="467" t="n"/>
+      <c r="T31" s="467" t="n"/>
+      <c r="U31" s="467" t="n"/>
+      <c r="V31" s="467" t="n"/>
+      <c r="W31" s="467" t="n"/>
+      <c r="X31" s="467" t="n"/>
+      <c r="Y31" s="467" t="n"/>
+      <c r="Z31" s="467" t="n"/>
+      <c r="AA31" s="467" t="n"/>
+      <c r="AB31" s="467" t="n"/>
+      <c r="AC31" s="467" t="n"/>
+      <c r="AD31" s="467" t="n"/>
+      <c r="AE31" s="467" t="n"/>
+      <c r="AF31" s="467" t="n"/>
+      <c r="AG31" s="467" t="n"/>
+      <c r="AH31" s="467" t="n"/>
+      <c r="AI31" s="467" t="n"/>
+      <c r="AJ31" s="467" t="n"/>
+      <c r="AK31" s="467" t="n"/>
+      <c r="AL31" s="467" t="n"/>
+      <c r="AM31" s="467" t="n"/>
+      <c r="AN31" s="467" t="n"/>
+      <c r="AO31" s="467" t="n"/>
+      <c r="AP31" s="467" t="n"/>
+      <c r="AQ31" s="467" t="n"/>
+      <c r="AR31" s="467" t="n"/>
+      <c r="AS31" s="467" t="n"/>
+      <c r="AT31" s="467" t="n"/>
+      <c r="AU31" s="467" t="n"/>
+      <c r="AV31" s="467" t="n"/>
+      <c r="AW31" s="467" t="n"/>
+      <c r="AX31" s="467" t="n"/>
+      <c r="AY31" s="467" t="n"/>
+      <c r="AZ31" s="467" t="n"/>
+      <c r="BA31" s="467" t="n"/>
+      <c r="BB31" s="467" t="n"/>
+      <c r="BC31" s="467" t="n"/>
+      <c r="BD31" s="468" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="382" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="489" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B32" s="400" t="n"/>
-      <c r="C32" s="400" t="n"/>
-      <c r="D32" s="400" t="n"/>
-      <c r="E32" s="400" t="n"/>
-      <c r="F32" s="400" t="n"/>
-      <c r="G32" s="400" t="n"/>
-      <c r="H32" s="400" t="n"/>
-      <c r="I32" s="400" t="n"/>
-      <c r="J32" s="400" t="n"/>
-      <c r="K32" s="400" t="n"/>
-      <c r="L32" s="400" t="n"/>
-      <c r="M32" s="400" t="n"/>
-      <c r="N32" s="400" t="n"/>
-      <c r="O32" s="400" t="n"/>
-      <c r="P32" s="400" t="n"/>
-      <c r="Q32" s="400" t="n"/>
-      <c r="R32" s="400" t="n"/>
-      <c r="S32" s="383" t="inlineStr">
+      <c r="B32" s="470" t="n"/>
+      <c r="C32" s="470" t="n"/>
+      <c r="D32" s="470" t="n"/>
+      <c r="E32" s="470" t="n"/>
+      <c r="F32" s="470" t="n"/>
+      <c r="G32" s="470" t="n"/>
+      <c r="H32" s="470" t="n"/>
+      <c r="I32" s="470" t="n"/>
+      <c r="J32" s="470" t="n"/>
+      <c r="K32" s="470" t="n"/>
+      <c r="L32" s="470" t="n"/>
+      <c r="M32" s="470" t="n"/>
+      <c r="N32" s="470" t="n"/>
+      <c r="O32" s="470" t="n"/>
+      <c r="P32" s="470" t="n"/>
+      <c r="Q32" s="470" t="n"/>
+      <c r="R32" s="470" t="n"/>
+      <c r="S32" s="501" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T32" s="400" t="n"/>
-      <c r="U32" s="400" t="n"/>
-      <c r="V32" s="400" t="n"/>
-      <c r="W32" s="400" t="n"/>
-      <c r="X32" s="400" t="n"/>
-      <c r="Y32" s="400" t="n"/>
-      <c r="Z32" s="400" t="n"/>
-      <c r="AA32" s="400" t="n"/>
-      <c r="AB32" s="400" t="n"/>
-      <c r="AC32" s="400" t="n"/>
-      <c r="AD32" s="400" t="n"/>
-      <c r="AE32" s="400" t="n"/>
-      <c r="AF32" s="400" t="n"/>
-      <c r="AG32" s="400" t="n"/>
-      <c r="AH32" s="400" t="n"/>
-      <c r="AI32" s="400" t="n"/>
-      <c r="AJ32" s="400" t="n"/>
-      <c r="AK32" s="384" t="inlineStr">
+      <c r="T32" s="470" t="n"/>
+      <c r="U32" s="470" t="n"/>
+      <c r="V32" s="470" t="n"/>
+      <c r="W32" s="470" t="n"/>
+      <c r="X32" s="470" t="n"/>
+      <c r="Y32" s="470" t="n"/>
+      <c r="Z32" s="470" t="n"/>
+      <c r="AA32" s="470" t="n"/>
+      <c r="AB32" s="470" t="n"/>
+      <c r="AC32" s="470" t="n"/>
+      <c r="AD32" s="470" t="n"/>
+      <c r="AE32" s="470" t="n"/>
+      <c r="AF32" s="470" t="n"/>
+      <c r="AG32" s="470" t="n"/>
+      <c r="AH32" s="470" t="n"/>
+      <c r="AI32" s="470" t="n"/>
+      <c r="AJ32" s="470" t="n"/>
+      <c r="AK32" s="501" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL32" s="400" t="n"/>
-      <c r="AM32" s="400" t="n"/>
-      <c r="AN32" s="400" t="n"/>
-      <c r="AO32" s="400" t="n"/>
-      <c r="AP32" s="400" t="n"/>
-      <c r="AQ32" s="400" t="n"/>
-      <c r="AR32" s="400" t="n"/>
-      <c r="AS32" s="400" t="n"/>
-      <c r="AT32" s="400" t="n"/>
-      <c r="AU32" s="400" t="n"/>
-      <c r="AV32" s="400" t="n"/>
-      <c r="AW32" s="400" t="n"/>
-      <c r="AX32" s="400" t="n"/>
-      <c r="AY32" s="400" t="n"/>
-      <c r="AZ32" s="400" t="n"/>
-      <c r="BA32" s="400" t="n"/>
-      <c r="BB32" s="400" t="n"/>
-      <c r="BC32" s="400" t="n"/>
-      <c r="BD32" s="401" t="n"/>
+      <c r="AL32" s="470" t="n"/>
+      <c r="AM32" s="470" t="n"/>
+      <c r="AN32" s="470" t="n"/>
+      <c r="AO32" s="470" t="n"/>
+      <c r="AP32" s="470" t="n"/>
+      <c r="AQ32" s="470" t="n"/>
+      <c r="AR32" s="470" t="n"/>
+      <c r="AS32" s="470" t="n"/>
+      <c r="AT32" s="470" t="n"/>
+      <c r="AU32" s="470" t="n"/>
+      <c r="AV32" s="470" t="n"/>
+      <c r="AW32" s="470" t="n"/>
+      <c r="AX32" s="470" t="n"/>
+      <c r="AY32" s="470" t="n"/>
+      <c r="AZ32" s="470" t="n"/>
+      <c r="BA32" s="470" t="n"/>
+      <c r="BB32" s="470" t="n"/>
+      <c r="BC32" s="470" t="n"/>
+      <c r="BD32" s="502" t="n"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="385" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="503" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B33" s="415" t="n"/>
-      <c r="C33" s="415" t="n"/>
-      <c r="D33" s="415" t="n"/>
-      <c r="E33" s="415" t="n"/>
-      <c r="F33" s="415" t="n"/>
-      <c r="G33" s="415" t="n"/>
-      <c r="H33" s="415" t="n"/>
-      <c r="I33" s="415" t="n"/>
-      <c r="J33" s="415" t="n"/>
-      <c r="K33" s="415" t="n"/>
-      <c r="L33" s="415" t="n"/>
-      <c r="M33" s="415" t="n"/>
-      <c r="N33" s="415" t="n"/>
-      <c r="O33" s="415" t="n"/>
-      <c r="P33" s="415" t="n"/>
-      <c r="Q33" s="415" t="n"/>
-      <c r="R33" s="416" t="n"/>
-      <c r="S33" s="385" t="inlineStr">
+      <c r="B33" s="362" t="n"/>
+      <c r="C33" s="362" t="n"/>
+      <c r="D33" s="362" t="n"/>
+      <c r="E33" s="362" t="n"/>
+      <c r="F33" s="362" t="n"/>
+      <c r="G33" s="362" t="n"/>
+      <c r="H33" s="362" t="n"/>
+      <c r="I33" s="362" t="n"/>
+      <c r="J33" s="362" t="n"/>
+      <c r="K33" s="362" t="n"/>
+      <c r="L33" s="362" t="n"/>
+      <c r="M33" s="362" t="n"/>
+      <c r="N33" s="362" t="n"/>
+      <c r="O33" s="362" t="n"/>
+      <c r="P33" s="362" t="n"/>
+      <c r="Q33" s="362" t="n"/>
+      <c r="R33" s="362" t="n"/>
+      <c r="S33" s="504" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T33" s="415" t="n"/>
-      <c r="U33" s="415" t="n"/>
-      <c r="V33" s="415" t="n"/>
-      <c r="W33" s="415" t="n"/>
-      <c r="X33" s="415" t="n"/>
-      <c r="Y33" s="415" t="n"/>
-      <c r="Z33" s="415" t="n"/>
-      <c r="AA33" s="415" t="n"/>
-      <c r="AB33" s="415" t="n"/>
-      <c r="AC33" s="415" t="n"/>
-      <c r="AD33" s="415" t="n"/>
-      <c r="AE33" s="415" t="n"/>
-      <c r="AF33" s="415" t="n"/>
-      <c r="AG33" s="415" t="n"/>
-      <c r="AH33" s="415" t="n"/>
-      <c r="AI33" s="415" t="n"/>
-      <c r="AJ33" s="416" t="n"/>
-      <c r="AK33" s="385" t="inlineStr">
+      <c r="T33" s="362" t="n"/>
+      <c r="U33" s="362" t="n"/>
+      <c r="V33" s="362" t="n"/>
+      <c r="W33" s="362" t="n"/>
+      <c r="X33" s="362" t="n"/>
+      <c r="Y33" s="362" t="n"/>
+      <c r="Z33" s="362" t="n"/>
+      <c r="AA33" s="362" t="n"/>
+      <c r="AB33" s="362" t="n"/>
+      <c r="AC33" s="362" t="n"/>
+      <c r="AD33" s="362" t="n"/>
+      <c r="AE33" s="362" t="n"/>
+      <c r="AF33" s="362" t="n"/>
+      <c r="AG33" s="362" t="n"/>
+      <c r="AH33" s="362" t="n"/>
+      <c r="AI33" s="362" t="n"/>
+      <c r="AJ33" s="362" t="n"/>
+      <c r="AK33" s="504" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL33" s="415" t="n"/>
-      <c r="AM33" s="415" t="n"/>
-      <c r="AN33" s="415" t="n"/>
-      <c r="AO33" s="415" t="n"/>
-      <c r="AP33" s="415" t="n"/>
-      <c r="AQ33" s="415" t="n"/>
-      <c r="AR33" s="415" t="n"/>
-      <c r="AS33" s="415" t="n"/>
-      <c r="AT33" s="415" t="n"/>
-      <c r="AU33" s="415" t="n"/>
-      <c r="AV33" s="415" t="n"/>
-      <c r="AW33" s="415" t="n"/>
-      <c r="AX33" s="415" t="n"/>
-      <c r="AY33" s="415" t="n"/>
-      <c r="AZ33" s="415" t="n"/>
-      <c r="BA33" s="415" t="n"/>
-      <c r="BB33" s="415" t="n"/>
-      <c r="BC33" s="415" t="n"/>
-      <c r="BD33" s="416" t="n"/>
+      <c r="AL33" s="362" t="n"/>
+      <c r="AM33" s="362" t="n"/>
+      <c r="AN33" s="362" t="n"/>
+      <c r="AO33" s="362" t="n"/>
+      <c r="AP33" s="362" t="n"/>
+      <c r="AQ33" s="362" t="n"/>
+      <c r="AR33" s="362" t="n"/>
+      <c r="AS33" s="362" t="n"/>
+      <c r="AT33" s="362" t="n"/>
+      <c r="AU33" s="362" t="n"/>
+      <c r="AV33" s="362" t="n"/>
+      <c r="AW33" s="362" t="n"/>
+      <c r="AX33" s="362" t="n"/>
+      <c r="AY33" s="362" t="n"/>
+      <c r="AZ33" s="362" t="n"/>
+      <c r="BA33" s="362" t="n"/>
+      <c r="BB33" s="362" t="n"/>
+      <c r="BC33" s="362" t="n"/>
+      <c r="BD33" s="478" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="417" t="n"/>
-      <c r="B34" s="389" t="n"/>
-      <c r="C34" s="389" t="n"/>
-      <c r="D34" s="389" t="n"/>
-      <c r="E34" s="389" t="n"/>
-      <c r="F34" s="389" t="n"/>
-      <c r="G34" s="389" t="n"/>
-      <c r="H34" s="389" t="n"/>
-      <c r="I34" s="389" t="n"/>
-      <c r="J34" s="389" t="n"/>
-      <c r="K34" s="389" t="n"/>
-      <c r="L34" s="389" t="n"/>
-      <c r="M34" s="389" t="n"/>
-      <c r="N34" s="389" t="n"/>
-      <c r="O34" s="389" t="n"/>
-      <c r="P34" s="389" t="n"/>
-      <c r="Q34" s="389" t="n"/>
-      <c r="R34" s="418" t="n"/>
-      <c r="S34" s="417" t="n"/>
-      <c r="T34" s="389" t="n"/>
-      <c r="U34" s="389" t="n"/>
-      <c r="V34" s="389" t="n"/>
-      <c r="W34" s="389" t="n"/>
-      <c r="X34" s="389" t="n"/>
-      <c r="Y34" s="389" t="n"/>
-      <c r="Z34" s="389" t="n"/>
-      <c r="AA34" s="389" t="n"/>
-      <c r="AB34" s="389" t="n"/>
-      <c r="AC34" s="389" t="n"/>
-      <c r="AD34" s="389" t="n"/>
-      <c r="AE34" s="389" t="n"/>
-      <c r="AF34" s="389" t="n"/>
-      <c r="AG34" s="389" t="n"/>
-      <c r="AH34" s="389" t="n"/>
-      <c r="AI34" s="389" t="n"/>
-      <c r="AJ34" s="418" t="n"/>
-      <c r="AK34" s="417" t="n"/>
-      <c r="AL34" s="389" t="n"/>
-      <c r="AM34" s="389" t="n"/>
-      <c r="AN34" s="389" t="n"/>
-      <c r="AO34" s="389" t="n"/>
-      <c r="AP34" s="389" t="n"/>
-      <c r="AQ34" s="389" t="n"/>
-      <c r="AR34" s="389" t="n"/>
-      <c r="AS34" s="389" t="n"/>
-      <c r="AT34" s="389" t="n"/>
-      <c r="AU34" s="389" t="n"/>
-      <c r="AV34" s="389" t="n"/>
-      <c r="AW34" s="389" t="n"/>
-      <c r="AX34" s="389" t="n"/>
-      <c r="AY34" s="389" t="n"/>
-      <c r="AZ34" s="389" t="n"/>
-      <c r="BA34" s="389" t="n"/>
-      <c r="BB34" s="389" t="n"/>
-      <c r="BC34" s="389" t="n"/>
-      <c r="BD34" s="418" t="n"/>
+      <c r="A34" s="505" t="n"/>
+      <c r="B34" s="362" t="n"/>
+      <c r="C34" s="362" t="n"/>
+      <c r="D34" s="362" t="n"/>
+      <c r="E34" s="362" t="n"/>
+      <c r="F34" s="362" t="n"/>
+      <c r="G34" s="362" t="n"/>
+      <c r="H34" s="362" t="n"/>
+      <c r="I34" s="362" t="n"/>
+      <c r="J34" s="362" t="n"/>
+      <c r="K34" s="362" t="n"/>
+      <c r="L34" s="362" t="n"/>
+      <c r="M34" s="362" t="n"/>
+      <c r="N34" s="362" t="n"/>
+      <c r="O34" s="362" t="n"/>
+      <c r="P34" s="362" t="n"/>
+      <c r="Q34" s="362" t="n"/>
+      <c r="R34" s="362" t="n"/>
+      <c r="S34" s="506" t="n"/>
+      <c r="T34" s="362" t="n"/>
+      <c r="U34" s="362" t="n"/>
+      <c r="V34" s="362" t="n"/>
+      <c r="W34" s="362" t="n"/>
+      <c r="X34" s="362" t="n"/>
+      <c r="Y34" s="362" t="n"/>
+      <c r="Z34" s="362" t="n"/>
+      <c r="AA34" s="362" t="n"/>
+      <c r="AB34" s="362" t="n"/>
+      <c r="AC34" s="362" t="n"/>
+      <c r="AD34" s="362" t="n"/>
+      <c r="AE34" s="362" t="n"/>
+      <c r="AF34" s="362" t="n"/>
+      <c r="AG34" s="362" t="n"/>
+      <c r="AH34" s="362" t="n"/>
+      <c r="AI34" s="362" t="n"/>
+      <c r="AJ34" s="362" t="n"/>
+      <c r="AK34" s="506" t="n"/>
+      <c r="AL34" s="362" t="n"/>
+      <c r="AM34" s="362" t="n"/>
+      <c r="AN34" s="362" t="n"/>
+      <c r="AO34" s="362" t="n"/>
+      <c r="AP34" s="362" t="n"/>
+      <c r="AQ34" s="362" t="n"/>
+      <c r="AR34" s="362" t="n"/>
+      <c r="AS34" s="362" t="n"/>
+      <c r="AT34" s="362" t="n"/>
+      <c r="AU34" s="362" t="n"/>
+      <c r="AV34" s="362" t="n"/>
+      <c r="AW34" s="362" t="n"/>
+      <c r="AX34" s="362" t="n"/>
+      <c r="AY34" s="362" t="n"/>
+      <c r="AZ34" s="362" t="n"/>
+      <c r="BA34" s="362" t="n"/>
+      <c r="BB34" s="362" t="n"/>
+      <c r="BC34" s="362" t="n"/>
+      <c r="BD34" s="478" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="419" t="n"/>
-      <c r="B35" s="413" t="n"/>
-      <c r="C35" s="413" t="n"/>
-      <c r="D35" s="413" t="n"/>
-      <c r="E35" s="413" t="n"/>
-      <c r="F35" s="413" t="n"/>
-      <c r="G35" s="413" t="n"/>
-      <c r="H35" s="413" t="n"/>
-      <c r="I35" s="413" t="n"/>
-      <c r="J35" s="413" t="n"/>
-      <c r="K35" s="413" t="n"/>
-      <c r="L35" s="413" t="n"/>
-      <c r="M35" s="413" t="n"/>
-      <c r="N35" s="413" t="n"/>
-      <c r="O35" s="413" t="n"/>
-      <c r="P35" s="413" t="n"/>
-      <c r="Q35" s="413" t="n"/>
-      <c r="R35" s="414" t="n"/>
-      <c r="S35" s="419" t="n"/>
-      <c r="T35" s="413" t="n"/>
-      <c r="U35" s="413" t="n"/>
-      <c r="V35" s="413" t="n"/>
-      <c r="W35" s="413" t="n"/>
-      <c r="X35" s="413" t="n"/>
-      <c r="Y35" s="413" t="n"/>
-      <c r="Z35" s="413" t="n"/>
-      <c r="AA35" s="413" t="n"/>
-      <c r="AB35" s="413" t="n"/>
-      <c r="AC35" s="413" t="n"/>
-      <c r="AD35" s="413" t="n"/>
-      <c r="AE35" s="413" t="n"/>
-      <c r="AF35" s="413" t="n"/>
-      <c r="AG35" s="413" t="n"/>
-      <c r="AH35" s="413" t="n"/>
-      <c r="AI35" s="413" t="n"/>
-      <c r="AJ35" s="414" t="n"/>
-      <c r="AK35" s="419" t="n"/>
-      <c r="AL35" s="413" t="n"/>
-      <c r="AM35" s="413" t="n"/>
-      <c r="AN35" s="413" t="n"/>
-      <c r="AO35" s="413" t="n"/>
-      <c r="AP35" s="413" t="n"/>
-      <c r="AQ35" s="413" t="n"/>
-      <c r="AR35" s="413" t="n"/>
-      <c r="AS35" s="413" t="n"/>
-      <c r="AT35" s="413" t="n"/>
-      <c r="AU35" s="413" t="n"/>
-      <c r="AV35" s="413" t="n"/>
-      <c r="AW35" s="413" t="n"/>
-      <c r="AX35" s="413" t="n"/>
-      <c r="AY35" s="413" t="n"/>
-      <c r="AZ35" s="413" t="n"/>
-      <c r="BA35" s="413" t="n"/>
-      <c r="BB35" s="413" t="n"/>
-      <c r="BC35" s="413" t="n"/>
-      <c r="BD35" s="414" t="n"/>
+      <c r="A35" s="507" t="n"/>
+      <c r="B35" s="482" t="n"/>
+      <c r="C35" s="482" t="n"/>
+      <c r="D35" s="482" t="n"/>
+      <c r="E35" s="482" t="n"/>
+      <c r="F35" s="482" t="n"/>
+      <c r="G35" s="482" t="n"/>
+      <c r="H35" s="482" t="n"/>
+      <c r="I35" s="482" t="n"/>
+      <c r="J35" s="482" t="n"/>
+      <c r="K35" s="482" t="n"/>
+      <c r="L35" s="482" t="n"/>
+      <c r="M35" s="482" t="n"/>
+      <c r="N35" s="482" t="n"/>
+      <c r="O35" s="482" t="n"/>
+      <c r="P35" s="482" t="n"/>
+      <c r="Q35" s="482" t="n"/>
+      <c r="R35" s="482" t="n"/>
+      <c r="S35" s="508" t="n"/>
+      <c r="T35" s="482" t="n"/>
+      <c r="U35" s="482" t="n"/>
+      <c r="V35" s="482" t="n"/>
+      <c r="W35" s="482" t="n"/>
+      <c r="X35" s="482" t="n"/>
+      <c r="Y35" s="482" t="n"/>
+      <c r="Z35" s="482" t="n"/>
+      <c r="AA35" s="482" t="n"/>
+      <c r="AB35" s="482" t="n"/>
+      <c r="AC35" s="482" t="n"/>
+      <c r="AD35" s="482" t="n"/>
+      <c r="AE35" s="482" t="n"/>
+      <c r="AF35" s="482" t="n"/>
+      <c r="AG35" s="482" t="n"/>
+      <c r="AH35" s="482" t="n"/>
+      <c r="AI35" s="482" t="n"/>
+      <c r="AJ35" s="482" t="n"/>
+      <c r="AK35" s="508" t="n"/>
+      <c r="AL35" s="482" t="n"/>
+      <c r="AM35" s="482" t="n"/>
+      <c r="AN35" s="482" t="n"/>
+      <c r="AO35" s="482" t="n"/>
+      <c r="AP35" s="482" t="n"/>
+      <c r="AQ35" s="482" t="n"/>
+      <c r="AR35" s="482" t="n"/>
+      <c r="AS35" s="482" t="n"/>
+      <c r="AT35" s="482" t="n"/>
+      <c r="AU35" s="482" t="n"/>
+      <c r="AV35" s="482" t="n"/>
+      <c r="AW35" s="482" t="n"/>
+      <c r="AX35" s="482" t="n"/>
+      <c r="AY35" s="482" t="n"/>
+      <c r="AZ35" s="482" t="n"/>
+      <c r="BA35" s="482" t="n"/>
+      <c r="BB35" s="482" t="n"/>
+      <c r="BC35" s="482" t="n"/>
+      <c r="BD35" s="484" t="n"/>
     </row>
-    <row r="36" ht="4" customHeight="1">
+    <row r="36" ht="3" customHeight="1">
       <c r="A36" s="377" t="n"/>
       <c r="B36" s="353" t="n"/>
       <c r="C36" s="353" t="n"/>
@@ -7535,66 +8420,66 @@
       <c r="BD36" s="353" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="392" t="inlineStr">
+      <c r="A37" s="509" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="411" t="n"/>
-      <c r="C37" s="411" t="n"/>
-      <c r="D37" s="411" t="n"/>
-      <c r="E37" s="411" t="n"/>
-      <c r="F37" s="411" t="n"/>
-      <c r="G37" s="411" t="n"/>
-      <c r="H37" s="411" t="n"/>
-      <c r="I37" s="411" t="n"/>
-      <c r="J37" s="411" t="n"/>
-      <c r="K37" s="411" t="n"/>
-      <c r="L37" s="411" t="n"/>
-      <c r="M37" s="411" t="n"/>
-      <c r="N37" s="411" t="n"/>
-      <c r="O37" s="411" t="n"/>
-      <c r="P37" s="411" t="n"/>
-      <c r="Q37" s="411" t="n"/>
-      <c r="R37" s="411" t="n"/>
-      <c r="S37" s="411" t="n"/>
-      <c r="T37" s="411" t="n"/>
-      <c r="U37" s="411" t="n"/>
-      <c r="V37" s="411" t="n"/>
-      <c r="W37" s="411" t="n"/>
-      <c r="X37" s="411" t="n"/>
-      <c r="Y37" s="411" t="n"/>
-      <c r="Z37" s="411" t="n"/>
-      <c r="AA37" s="411" t="n"/>
-      <c r="AB37" s="411" t="n"/>
-      <c r="AC37" s="411" t="n"/>
-      <c r="AD37" s="411" t="n"/>
-      <c r="AE37" s="411" t="n"/>
-      <c r="AF37" s="411" t="n"/>
-      <c r="AG37" s="411" t="n"/>
-      <c r="AH37" s="411" t="n"/>
-      <c r="AI37" s="411" t="n"/>
-      <c r="AJ37" s="411" t="n"/>
-      <c r="AK37" s="411" t="n"/>
-      <c r="AL37" s="411" t="n"/>
-      <c r="AM37" s="411" t="n"/>
-      <c r="AN37" s="411" t="n"/>
-      <c r="AO37" s="411" t="n"/>
-      <c r="AP37" s="411" t="n"/>
-      <c r="AQ37" s="411" t="n"/>
-      <c r="AR37" s="411" t="n"/>
-      <c r="AS37" s="411" t="n"/>
-      <c r="AT37" s="411" t="n"/>
-      <c r="AU37" s="411" t="n"/>
-      <c r="AV37" s="411" t="n"/>
-      <c r="AW37" s="411" t="n"/>
-      <c r="AX37" s="411" t="n"/>
-      <c r="AY37" s="411" t="n"/>
-      <c r="AZ37" s="411" t="n"/>
-      <c r="BA37" s="411" t="n"/>
-      <c r="BB37" s="411" t="n"/>
-      <c r="BC37" s="411" t="n"/>
-      <c r="BD37" s="412" t="n"/>
+      <c r="B37" s="510" t="n"/>
+      <c r="C37" s="510" t="n"/>
+      <c r="D37" s="510" t="n"/>
+      <c r="E37" s="510" t="n"/>
+      <c r="F37" s="510" t="n"/>
+      <c r="G37" s="510" t="n"/>
+      <c r="H37" s="510" t="n"/>
+      <c r="I37" s="510" t="n"/>
+      <c r="J37" s="510" t="n"/>
+      <c r="K37" s="510" t="n"/>
+      <c r="L37" s="510" t="n"/>
+      <c r="M37" s="510" t="n"/>
+      <c r="N37" s="510" t="n"/>
+      <c r="O37" s="510" t="n"/>
+      <c r="P37" s="510" t="n"/>
+      <c r="Q37" s="510" t="n"/>
+      <c r="R37" s="510" t="n"/>
+      <c r="S37" s="510" t="n"/>
+      <c r="T37" s="510" t="n"/>
+      <c r="U37" s="510" t="n"/>
+      <c r="V37" s="510" t="n"/>
+      <c r="W37" s="510" t="n"/>
+      <c r="X37" s="510" t="n"/>
+      <c r="Y37" s="510" t="n"/>
+      <c r="Z37" s="510" t="n"/>
+      <c r="AA37" s="510" t="n"/>
+      <c r="AB37" s="510" t="n"/>
+      <c r="AC37" s="510" t="n"/>
+      <c r="AD37" s="510" t="n"/>
+      <c r="AE37" s="510" t="n"/>
+      <c r="AF37" s="510" t="n"/>
+      <c r="AG37" s="510" t="n"/>
+      <c r="AH37" s="510" t="n"/>
+      <c r="AI37" s="510" t="n"/>
+      <c r="AJ37" s="510" t="n"/>
+      <c r="AK37" s="510" t="n"/>
+      <c r="AL37" s="510" t="n"/>
+      <c r="AM37" s="510" t="n"/>
+      <c r="AN37" s="510" t="n"/>
+      <c r="AO37" s="510" t="n"/>
+      <c r="AP37" s="510" t="n"/>
+      <c r="AQ37" s="510" t="n"/>
+      <c r="AR37" s="510" t="n"/>
+      <c r="AS37" s="510" t="n"/>
+      <c r="AT37" s="510" t="n"/>
+      <c r="AU37" s="510" t="n"/>
+      <c r="AV37" s="510" t="n"/>
+      <c r="AW37" s="510" t="n"/>
+      <c r="AX37" s="510" t="n"/>
+      <c r="AY37" s="510" t="n"/>
+      <c r="AZ37" s="510" t="n"/>
+      <c r="BA37" s="510" t="n"/>
+      <c r="BB37" s="510" t="n"/>
+      <c r="BC37" s="510" t="n"/>
+      <c r="BD37" s="511" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -7608,7 +8493,7 @@
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="119">
+  <mergeCells count="118">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AK32:BD32"/>
     <mergeCell ref="AX18:BA18"/>
@@ -7622,7 +8507,6 @@
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="A33:R35"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AK33:BD35"/>
@@ -7759,6 +8643,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7816,12 +8701,12 @@
           <t>CLOSEOUT_STATE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="348" t="inlineStr">
         <is>
           <t>ACTION_STATUS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="348" t="inlineStr">
         <is>
           <t>REASON_CODE_LIST</t>
         </is>
@@ -7863,12 +8748,12 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="348" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="348" t="inlineStr">
         <is>
           <t>CERT MISMATCH</t>
         </is>
@@ -7910,12 +8795,12 @@
           <t>NOT CLOSED</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="348" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="348" t="inlineStr">
         <is>
           <t>TRACEABILITY BREAK</t>
         </is>
@@ -7953,12 +8838,12 @@
         </is>
       </c>
       <c r="G4" s="266" t="n"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="348" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="348" t="inlineStr">
         <is>
           <t>DAMAGE</t>
         </is>
@@ -7981,108 +8866,108 @@
           <t>REJECT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="348" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
       <c r="F5" s="266" t="n"/>
       <c r="G5" s="266" t="n"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="348" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="348" t="inlineStr">
         <is>
           <t>LATE DELIVERY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="348" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
       <c r="F6" s="266" t="n"/>
       <c r="G6" s="266" t="n"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="348" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="348" t="inlineStr">
         <is>
           <t>SPEC DEVIATION</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="348" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
       </c>
       <c r="F7" s="266" t="n"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="348" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="348" t="inlineStr">
         <is>
           <t>PACKAGING ISSUE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="348" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
       </c>
       <c r="F8" s="266" t="n"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="348" t="inlineStr">
         <is>
           <t>DOC GAP</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="348" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
       <c r="F9" s="266" t="n"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="348" t="inlineStr">
         <is>
           <t>CAL STATUS ISSUE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="348" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
       <c r="F10" s="266" t="n"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="348" t="inlineStr">
         <is>
           <t>CLEANLINESS RISK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="348" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
       </c>
       <c r="F11" s="266" t="n"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="348" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
@@ -8144,882 +9029,888 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="512" t="inlineStr">
         <is>
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="422" t="n"/>
-      <c r="C1" s="422" t="n"/>
-      <c r="D1" s="422" t="n"/>
-      <c r="E1" s="422" t="n"/>
-      <c r="F1" s="422" t="n"/>
-      <c r="G1" s="423" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="428" t="n"/>
+      <c r="C1" s="428" t="n"/>
+      <c r="D1" s="428" t="n"/>
+      <c r="E1" s="428" t="n"/>
+      <c r="F1" s="428" t="n"/>
+      <c r="G1" s="428" t="n"/>
+      <c r="H1" s="513" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="431" t="n"/>
+      <c r="K1" s="431" t="n"/>
+      <c r="L1" s="431" t="n"/>
+      <c r="M1" s="431" t="n"/>
+      <c r="N1" s="431" t="n"/>
+      <c r="O1" s="431" t="n"/>
+      <c r="P1" s="431" t="n"/>
+      <c r="Q1" s="431" t="n"/>
+      <c r="R1" s="431" t="n"/>
+      <c r="S1" s="431" t="n"/>
+      <c r="T1" s="431" t="n"/>
+      <c r="U1" s="431" t="n"/>
+      <c r="V1" s="431" t="n"/>
+      <c r="W1" s="431" t="n"/>
+      <c r="X1" s="431" t="n"/>
+      <c r="Y1" s="431" t="n"/>
+      <c r="Z1" s="431" t="n"/>
+      <c r="AA1" s="431" t="n"/>
+      <c r="AB1" s="431" t="n"/>
+      <c r="AC1" s="431" t="n"/>
+      <c r="AD1" s="432" t="n"/>
+      <c r="AE1" s="433" t="n"/>
+      <c r="AF1" s="434" t="n"/>
+      <c r="AG1" s="434" t="n"/>
+      <c r="AH1" s="435" t="n"/>
+      <c r="AI1" s="436" t="n"/>
+      <c r="AJ1" s="437" t="n"/>
+      <c r="AK1" s="437" t="n"/>
+      <c r="AL1" s="437" t="n"/>
+      <c r="AM1" s="437" t="n"/>
+      <c r="AN1" s="438" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="514" t="inlineStr">
         <is>
           <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="515" t="n"/>
+      <c r="I2" s="441" t="n"/>
+      <c r="J2" s="442" t="n"/>
+      <c r="K2" s="442" t="n"/>
+      <c r="L2" s="442" t="n"/>
+      <c r="M2" s="442" t="n"/>
+      <c r="N2" s="442" t="n"/>
+      <c r="O2" s="442" t="n"/>
+      <c r="P2" s="442" t="n"/>
+      <c r="Q2" s="442" t="n"/>
+      <c r="R2" s="442" t="n"/>
+      <c r="S2" s="442" t="n"/>
+      <c r="T2" s="442" t="n"/>
+      <c r="U2" s="442" t="n"/>
+      <c r="V2" s="442" t="n"/>
+      <c r="W2" s="442" t="n"/>
+      <c r="X2" s="442" t="n"/>
+      <c r="Y2" s="442" t="n"/>
+      <c r="Z2" s="442" t="n"/>
+      <c r="AA2" s="442" t="n"/>
+      <c r="AB2" s="442" t="n"/>
+      <c r="AC2" s="442" t="n"/>
+      <c r="AD2" s="443" t="n"/>
+      <c r="AE2" s="444" t="n"/>
+      <c r="AF2" s="445" t="n"/>
+      <c r="AG2" s="445" t="n"/>
+      <c r="AH2" s="446" t="n"/>
+      <c r="AI2" s="447" t="n"/>
+      <c r="AJ2" s="448" t="n"/>
+      <c r="AK2" s="448" t="n"/>
+      <c r="AL2" s="448" t="n"/>
+      <c r="AM2" s="448" t="n"/>
+      <c r="AN2" s="449" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="516" t="n"/>
+      <c r="B3" s="517" t="n"/>
+      <c r="C3" s="517" t="n"/>
+      <c r="D3" s="517" t="n"/>
+      <c r="E3" s="517" t="n"/>
+      <c r="F3" s="517" t="n"/>
+      <c r="G3" s="517" t="n"/>
+      <c r="H3" s="515" t="n"/>
+      <c r="I3" s="441" t="n"/>
+      <c r="J3" s="442" t="n"/>
+      <c r="K3" s="442" t="n"/>
+      <c r="L3" s="442" t="n"/>
+      <c r="M3" s="442" t="n"/>
+      <c r="N3" s="442" t="n"/>
+      <c r="O3" s="442" t="n"/>
+      <c r="P3" s="442" t="n"/>
+      <c r="Q3" s="442" t="n"/>
+      <c r="R3" s="442" t="n"/>
+      <c r="S3" s="442" t="n"/>
+      <c r="T3" s="442" t="n"/>
+      <c r="U3" s="442" t="n"/>
+      <c r="V3" s="442" t="n"/>
+      <c r="W3" s="442" t="n"/>
+      <c r="X3" s="442" t="n"/>
+      <c r="Y3" s="442" t="n"/>
+      <c r="Z3" s="442" t="n"/>
+      <c r="AA3" s="442" t="n"/>
+      <c r="AB3" s="442" t="n"/>
+      <c r="AC3" s="442" t="n"/>
+      <c r="AD3" s="443" t="n"/>
+      <c r="AE3" s="444" t="n"/>
+      <c r="AF3" s="445" t="n"/>
+      <c r="AG3" s="445" t="n"/>
+      <c r="AH3" s="446" t="n"/>
+      <c r="AI3" s="447" t="n"/>
+      <c r="AJ3" s="448" t="n"/>
+      <c r="AK3" s="448" t="n"/>
+      <c r="AL3" s="448" t="n"/>
+      <c r="AM3" s="448" t="n"/>
+      <c r="AN3" s="449" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="366" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="518" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="366" t="inlineStr">
+      <c r="B4" s="519" t="inlineStr">
         <is>
           <t>Sample No.</t>
         </is>
       </c>
-      <c r="C4" s="366" t="inlineStr">
+      <c r="C4" s="519" t="inlineStr">
         <is>
           <t>ID / Serial</t>
         </is>
       </c>
-      <c r="D4" s="366" t="inlineStr">
+      <c r="D4" s="519" t="inlineStr">
         <is>
           <t>Measured Result / Observation</t>
         </is>
       </c>
-      <c r="E4" s="366" t="inlineStr">
+      <c r="E4" s="519" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F4" s="366" t="inlineStr">
+      <c r="F4" s="519" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="G4" s="366" t="inlineStr">
+      <c r="G4" s="519" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H4" s="366" t="inlineStr">
+      <c r="H4" s="520" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="I4" s="450" t="n"/>
+      <c r="J4" s="451" t="n"/>
+      <c r="K4" s="451" t="n"/>
+      <c r="L4" s="451" t="n"/>
+      <c r="M4" s="451" t="n"/>
+      <c r="N4" s="451" t="n"/>
+      <c r="O4" s="451" t="n"/>
+      <c r="P4" s="451" t="n"/>
+      <c r="Q4" s="451" t="n"/>
+      <c r="R4" s="451" t="n"/>
+      <c r="S4" s="451" t="n"/>
+      <c r="T4" s="451" t="n"/>
+      <c r="U4" s="451" t="n"/>
+      <c r="V4" s="451" t="n"/>
+      <c r="W4" s="451" t="n"/>
+      <c r="X4" s="451" t="n"/>
+      <c r="Y4" s="451" t="n"/>
+      <c r="Z4" s="451" t="n"/>
+      <c r="AA4" s="451" t="n"/>
+      <c r="AB4" s="451" t="n"/>
+      <c r="AC4" s="451" t="n"/>
+      <c r="AD4" s="452" t="n"/>
+      <c r="AE4" s="444" t="n"/>
+      <c r="AF4" s="445" t="n"/>
+      <c r="AG4" s="445" t="n"/>
+      <c r="AH4" s="446" t="n"/>
+      <c r="AI4" s="447" t="n"/>
+      <c r="AJ4" s="448" t="n"/>
+      <c r="AK4" s="448" t="n"/>
+      <c r="AL4" s="448" t="n"/>
+      <c r="AM4" s="448" t="n"/>
+      <c r="AN4" s="449" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="394">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="521">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="395" t="n"/>
-      <c r="C5" s="395" t="n"/>
-      <c r="D5" s="395" t="n"/>
-      <c r="E5" s="395" t="n"/>
-      <c r="F5" s="395" t="n"/>
-      <c r="G5" s="395" t="n"/>
-      <c r="H5" s="395" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="B5" s="522" t="n"/>
+      <c r="C5" s="522" t="n"/>
+      <c r="D5" s="522" t="n"/>
+      <c r="E5" s="522" t="n"/>
+      <c r="F5" s="522" t="n"/>
+      <c r="G5" s="522" t="n"/>
+      <c r="H5" s="523" t="n"/>
+      <c r="I5" s="456" t="n"/>
+      <c r="J5" s="457" t="n"/>
+      <c r="K5" s="457" t="n"/>
+      <c r="L5" s="457" t="n"/>
+      <c r="M5" s="457" t="n"/>
+      <c r="N5" s="457" t="n"/>
+      <c r="O5" s="457" t="n"/>
+      <c r="P5" s="457" t="n"/>
+      <c r="Q5" s="457" t="n"/>
+      <c r="R5" s="457" t="n"/>
+      <c r="S5" s="457" t="n"/>
+      <c r="T5" s="457" t="n"/>
+      <c r="U5" s="457" t="n"/>
+      <c r="V5" s="457" t="n"/>
+      <c r="W5" s="457" t="n"/>
+      <c r="X5" s="457" t="n"/>
+      <c r="Y5" s="457" t="n"/>
+      <c r="Z5" s="457" t="n"/>
+      <c r="AA5" s="457" t="n"/>
+      <c r="AB5" s="457" t="n"/>
+      <c r="AC5" s="457" t="n"/>
+      <c r="AD5" s="458" t="n"/>
+      <c r="AE5" s="459" t="n"/>
+      <c r="AF5" s="460" t="n"/>
+      <c r="AG5" s="460" t="n"/>
+      <c r="AH5" s="461" t="n"/>
+      <c r="AI5" s="462" t="n"/>
+      <c r="AJ5" s="463" t="n"/>
+      <c r="AK5" s="463" t="n"/>
+      <c r="AL5" s="463" t="n"/>
+      <c r="AM5" s="463" t="n"/>
+      <c r="AN5" s="464" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="394">
+      <c r="A6" s="524">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="395" t="n"/>
-      <c r="C6" s="395" t="n"/>
-      <c r="D6" s="395" t="n"/>
-      <c r="E6" s="395" t="n"/>
-      <c r="F6" s="395" t="n"/>
-      <c r="G6" s="395" t="n"/>
-      <c r="H6" s="395" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="B6" s="525" t="n"/>
+      <c r="C6" s="526" t="n"/>
+      <c r="D6" s="526" t="n"/>
+      <c r="E6" s="526" t="n"/>
+      <c r="F6" s="526" t="n"/>
+      <c r="G6" s="526" t="n"/>
+      <c r="H6" s="526" t="n"/>
+      <c r="I6" s="470" t="n"/>
+      <c r="J6" s="470" t="n"/>
+      <c r="K6" s="470" t="n"/>
+      <c r="L6" s="470" t="n"/>
+      <c r="M6" s="470" t="n"/>
+      <c r="N6" s="470" t="n"/>
+      <c r="O6" s="470" t="n"/>
+      <c r="P6" s="470" t="n"/>
+      <c r="Q6" s="470" t="n"/>
+      <c r="R6" s="470" t="n"/>
+      <c r="S6" s="470" t="n"/>
+      <c r="T6" s="470" t="n"/>
+      <c r="U6" s="470" t="n"/>
+      <c r="V6" s="470" t="n"/>
+      <c r="W6" s="470" t="n"/>
+      <c r="X6" s="470" t="n"/>
+      <c r="Y6" s="470" t="n"/>
+      <c r="Z6" s="470" t="n"/>
+      <c r="AA6" s="470" t="n"/>
+      <c r="AB6" s="470" t="n"/>
+      <c r="AC6" s="470" t="n"/>
+      <c r="AD6" s="470" t="n"/>
+      <c r="AE6" s="470" t="n"/>
+      <c r="AF6" s="470" t="n"/>
+      <c r="AG6" s="470" t="n"/>
+      <c r="AH6" s="470" t="n"/>
+      <c r="AI6" s="470" t="n"/>
+      <c r="AJ6" s="470" t="n"/>
+      <c r="AK6" s="470" t="n"/>
+      <c r="AL6" s="470" t="n"/>
+      <c r="AM6" s="470" t="n"/>
+      <c r="AN6" s="502" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="394">
+      <c r="A7" s="527">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="395" t="n"/>
-      <c r="C7" s="395" t="n"/>
-      <c r="D7" s="395" t="n"/>
-      <c r="E7" s="395" t="n"/>
-      <c r="F7" s="395" t="n"/>
-      <c r="G7" s="395" t="n"/>
-      <c r="H7" s="395" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="B7" s="528" t="n"/>
+      <c r="C7" s="529" t="n"/>
+      <c r="D7" s="529" t="n"/>
+      <c r="E7" s="529" t="n"/>
+      <c r="F7" s="529" t="n"/>
+      <c r="G7" s="529" t="n"/>
+      <c r="H7" s="529" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="530" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="396">
+      <c r="A8" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="397" t="n"/>
-      <c r="C8" s="397" t="n"/>
-      <c r="D8" s="397" t="n"/>
-      <c r="E8" s="397" t="n"/>
-      <c r="F8" s="397" t="n"/>
-      <c r="G8" s="397" t="n"/>
-      <c r="H8" s="397" t="n"/>
-      <c r="I8" s="398" t="n"/>
-      <c r="J8" s="398" t="n"/>
-      <c r="K8" s="398" t="n"/>
-      <c r="L8" s="398" t="n"/>
-      <c r="M8" s="398" t="n"/>
-      <c r="N8" s="398" t="n"/>
-      <c r="O8" s="398" t="n"/>
-      <c r="P8" s="398" t="n"/>
-      <c r="Q8" s="398" t="n"/>
-      <c r="R8" s="398" t="n"/>
-      <c r="S8" s="398" t="n"/>
-      <c r="T8" s="398" t="n"/>
-      <c r="U8" s="398" t="n"/>
-      <c r="V8" s="398" t="n"/>
-      <c r="W8" s="398" t="n"/>
-      <c r="X8" s="398" t="n"/>
-      <c r="Y8" s="398" t="n"/>
-      <c r="Z8" s="398" t="n"/>
-      <c r="AA8" s="398" t="n"/>
-      <c r="AB8" s="398" t="n"/>
-      <c r="AC8" s="398" t="n"/>
-      <c r="AD8" s="398" t="n"/>
-      <c r="AE8" s="398" t="n"/>
-      <c r="AF8" s="398" t="n"/>
-      <c r="AG8" s="398" t="n"/>
-      <c r="AH8" s="398" t="n"/>
-      <c r="AI8" s="398" t="n"/>
-      <c r="AJ8" s="398" t="n"/>
-      <c r="AK8" s="398" t="n"/>
-      <c r="AL8" s="398" t="n"/>
-      <c r="AM8" s="398" t="n"/>
-      <c r="AN8" s="398" t="n"/>
+      <c r="B8" s="532" t="n"/>
+      <c r="C8" s="533" t="n"/>
+      <c r="D8" s="533" t="n"/>
+      <c r="E8" s="533" t="n"/>
+      <c r="F8" s="533" t="n"/>
+      <c r="G8" s="533" t="n"/>
+      <c r="H8" s="533" t="n"/>
+      <c r="I8" s="356" t="n"/>
+      <c r="J8" s="356" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="356" t="n"/>
+      <c r="M8" s="356" t="n"/>
+      <c r="N8" s="356" t="n"/>
+      <c r="O8" s="356" t="n"/>
+      <c r="P8" s="356" t="n"/>
+      <c r="Q8" s="356" t="n"/>
+      <c r="R8" s="356" t="n"/>
+      <c r="S8" s="356" t="n"/>
+      <c r="T8" s="356" t="n"/>
+      <c r="U8" s="356" t="n"/>
+      <c r="V8" s="356" t="n"/>
+      <c r="W8" s="356" t="n"/>
+      <c r="X8" s="356" t="n"/>
+      <c r="Y8" s="356" t="n"/>
+      <c r="Z8" s="356" t="n"/>
+      <c r="AA8" s="356" t="n"/>
+      <c r="AB8" s="356" t="n"/>
+      <c r="AC8" s="356" t="n"/>
+      <c r="AD8" s="356" t="n"/>
+      <c r="AE8" s="356" t="n"/>
+      <c r="AF8" s="356" t="n"/>
+      <c r="AG8" s="356" t="n"/>
+      <c r="AH8" s="356" t="n"/>
+      <c r="AI8" s="356" t="n"/>
+      <c r="AJ8" s="356" t="n"/>
+      <c r="AK8" s="356" t="n"/>
+      <c r="AL8" s="356" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="534" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="396">
+      <c r="A9" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="397" t="n"/>
-      <c r="C9" s="397" t="n"/>
-      <c r="D9" s="397" t="n"/>
-      <c r="E9" s="397" t="n"/>
-      <c r="F9" s="397" t="n"/>
-      <c r="G9" s="397" t="n"/>
-      <c r="H9" s="397" t="n"/>
-      <c r="I9" s="398" t="n"/>
-      <c r="J9" s="398" t="n"/>
-      <c r="K9" s="398" t="n"/>
-      <c r="L9" s="398" t="n"/>
-      <c r="M9" s="398" t="n"/>
-      <c r="N9" s="398" t="n"/>
-      <c r="O9" s="398" t="n"/>
-      <c r="P9" s="398" t="n"/>
-      <c r="Q9" s="398" t="n"/>
-      <c r="R9" s="398" t="n"/>
-      <c r="S9" s="398" t="n"/>
-      <c r="T9" s="398" t="n"/>
-      <c r="U9" s="398" t="n"/>
-      <c r="V9" s="398" t="n"/>
-      <c r="W9" s="398" t="n"/>
-      <c r="X9" s="398" t="n"/>
-      <c r="Y9" s="398" t="n"/>
-      <c r="Z9" s="398" t="n"/>
-      <c r="AA9" s="398" t="n"/>
-      <c r="AB9" s="398" t="n"/>
-      <c r="AC9" s="398" t="n"/>
-      <c r="AD9" s="398" t="n"/>
-      <c r="AE9" s="398" t="n"/>
-      <c r="AF9" s="398" t="n"/>
-      <c r="AG9" s="398" t="n"/>
-      <c r="AH9" s="398" t="n"/>
-      <c r="AI9" s="398" t="n"/>
-      <c r="AJ9" s="398" t="n"/>
-      <c r="AK9" s="398" t="n"/>
-      <c r="AL9" s="398" t="n"/>
-      <c r="AM9" s="398" t="n"/>
-      <c r="AN9" s="398" t="n"/>
+      <c r="B9" s="532" t="n"/>
+      <c r="C9" s="533" t="n"/>
+      <c r="D9" s="533" t="n"/>
+      <c r="E9" s="533" t="n"/>
+      <c r="F9" s="533" t="n"/>
+      <c r="G9" s="533" t="n"/>
+      <c r="H9" s="533" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="356" t="n"/>
+      <c r="M9" s="356" t="n"/>
+      <c r="N9" s="356" t="n"/>
+      <c r="O9" s="356" t="n"/>
+      <c r="P9" s="356" t="n"/>
+      <c r="Q9" s="356" t="n"/>
+      <c r="R9" s="356" t="n"/>
+      <c r="S9" s="356" t="n"/>
+      <c r="T9" s="356" t="n"/>
+      <c r="U9" s="356" t="n"/>
+      <c r="V9" s="356" t="n"/>
+      <c r="W9" s="356" t="n"/>
+      <c r="X9" s="356" t="n"/>
+      <c r="Y9" s="356" t="n"/>
+      <c r="Z9" s="356" t="n"/>
+      <c r="AA9" s="356" t="n"/>
+      <c r="AB9" s="356" t="n"/>
+      <c r="AC9" s="356" t="n"/>
+      <c r="AD9" s="356" t="n"/>
+      <c r="AE9" s="356" t="n"/>
+      <c r="AF9" s="356" t="n"/>
+      <c r="AG9" s="356" t="n"/>
+      <c r="AH9" s="356" t="n"/>
+      <c r="AI9" s="356" t="n"/>
+      <c r="AJ9" s="356" t="n"/>
+      <c r="AK9" s="356" t="n"/>
+      <c r="AL9" s="356" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="534" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="396">
+      <c r="A10" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="397" t="n"/>
-      <c r="C10" s="397" t="n"/>
-      <c r="D10" s="397" t="n"/>
-      <c r="E10" s="397" t="n"/>
-      <c r="F10" s="397" t="n"/>
-      <c r="G10" s="397" t="n"/>
-      <c r="H10" s="397" t="n"/>
-      <c r="I10" s="398" t="n"/>
-      <c r="J10" s="398" t="n"/>
-      <c r="K10" s="398" t="n"/>
-      <c r="L10" s="398" t="n"/>
-      <c r="M10" s="398" t="n"/>
-      <c r="N10" s="398" t="n"/>
-      <c r="O10" s="398" t="n"/>
-      <c r="P10" s="398" t="n"/>
-      <c r="Q10" s="398" t="n"/>
-      <c r="R10" s="398" t="n"/>
-      <c r="S10" s="398" t="n"/>
-      <c r="T10" s="398" t="n"/>
-      <c r="U10" s="398" t="n"/>
-      <c r="V10" s="398" t="n"/>
-      <c r="W10" s="398" t="n"/>
-      <c r="X10" s="398" t="n"/>
-      <c r="Y10" s="398" t="n"/>
-      <c r="Z10" s="398" t="n"/>
-      <c r="AA10" s="398" t="n"/>
-      <c r="AB10" s="398" t="n"/>
-      <c r="AC10" s="398" t="n"/>
-      <c r="AD10" s="398" t="n"/>
-      <c r="AE10" s="398" t="n"/>
-      <c r="AF10" s="398" t="n"/>
-      <c r="AG10" s="398" t="n"/>
-      <c r="AH10" s="398" t="n"/>
-      <c r="AI10" s="398" t="n"/>
-      <c r="AJ10" s="398" t="n"/>
-      <c r="AK10" s="398" t="n"/>
-      <c r="AL10" s="398" t="n"/>
-      <c r="AM10" s="398" t="n"/>
-      <c r="AN10" s="398" t="n"/>
+      <c r="B10" s="532" t="n"/>
+      <c r="C10" s="533" t="n"/>
+      <c r="D10" s="533" t="n"/>
+      <c r="E10" s="533" t="n"/>
+      <c r="F10" s="533" t="n"/>
+      <c r="G10" s="533" t="n"/>
+      <c r="H10" s="533" t="n"/>
+      <c r="I10" s="356" t="n"/>
+      <c r="J10" s="356" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="356" t="n"/>
+      <c r="M10" s="356" t="n"/>
+      <c r="N10" s="356" t="n"/>
+      <c r="O10" s="356" t="n"/>
+      <c r="P10" s="356" t="n"/>
+      <c r="Q10" s="356" t="n"/>
+      <c r="R10" s="356" t="n"/>
+      <c r="S10" s="356" t="n"/>
+      <c r="T10" s="356" t="n"/>
+      <c r="U10" s="356" t="n"/>
+      <c r="V10" s="356" t="n"/>
+      <c r="W10" s="356" t="n"/>
+      <c r="X10" s="356" t="n"/>
+      <c r="Y10" s="356" t="n"/>
+      <c r="Z10" s="356" t="n"/>
+      <c r="AA10" s="356" t="n"/>
+      <c r="AB10" s="356" t="n"/>
+      <c r="AC10" s="356" t="n"/>
+      <c r="AD10" s="356" t="n"/>
+      <c r="AE10" s="356" t="n"/>
+      <c r="AF10" s="356" t="n"/>
+      <c r="AG10" s="356" t="n"/>
+      <c r="AH10" s="356" t="n"/>
+      <c r="AI10" s="356" t="n"/>
+      <c r="AJ10" s="356" t="n"/>
+      <c r="AK10" s="356" t="n"/>
+      <c r="AL10" s="356" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="534" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="396">
+      <c r="A11" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="397" t="n"/>
-      <c r="C11" s="397" t="n"/>
-      <c r="D11" s="397" t="n"/>
-      <c r="E11" s="397" t="n"/>
-      <c r="F11" s="397" t="n"/>
-      <c r="G11" s="397" t="n"/>
-      <c r="H11" s="397" t="n"/>
-      <c r="I11" s="398" t="n"/>
-      <c r="J11" s="398" t="n"/>
-      <c r="K11" s="398" t="n"/>
-      <c r="L11" s="398" t="n"/>
-      <c r="M11" s="398" t="n"/>
-      <c r="N11" s="398" t="n"/>
-      <c r="O11" s="398" t="n"/>
-      <c r="P11" s="398" t="n"/>
-      <c r="Q11" s="398" t="n"/>
-      <c r="R11" s="398" t="n"/>
-      <c r="S11" s="398" t="n"/>
-      <c r="T11" s="398" t="n"/>
-      <c r="U11" s="398" t="n"/>
-      <c r="V11" s="398" t="n"/>
-      <c r="W11" s="398" t="n"/>
-      <c r="X11" s="398" t="n"/>
-      <c r="Y11" s="398" t="n"/>
-      <c r="Z11" s="398" t="n"/>
-      <c r="AA11" s="398" t="n"/>
-      <c r="AB11" s="398" t="n"/>
-      <c r="AC11" s="398" t="n"/>
-      <c r="AD11" s="398" t="n"/>
-      <c r="AE11" s="398" t="n"/>
-      <c r="AF11" s="398" t="n"/>
-      <c r="AG11" s="398" t="n"/>
-      <c r="AH11" s="398" t="n"/>
-      <c r="AI11" s="398" t="n"/>
-      <c r="AJ11" s="398" t="n"/>
-      <c r="AK11" s="398" t="n"/>
-      <c r="AL11" s="398" t="n"/>
-      <c r="AM11" s="398" t="n"/>
-      <c r="AN11" s="398" t="n"/>
+      <c r="B11" s="532" t="n"/>
+      <c r="C11" s="533" t="n"/>
+      <c r="D11" s="533" t="n"/>
+      <c r="E11" s="533" t="n"/>
+      <c r="F11" s="533" t="n"/>
+      <c r="G11" s="533" t="n"/>
+      <c r="H11" s="533" t="n"/>
+      <c r="I11" s="356" t="n"/>
+      <c r="J11" s="356" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="356" t="n"/>
+      <c r="M11" s="356" t="n"/>
+      <c r="N11" s="356" t="n"/>
+      <c r="O11" s="356" t="n"/>
+      <c r="P11" s="356" t="n"/>
+      <c r="Q11" s="356" t="n"/>
+      <c r="R11" s="356" t="n"/>
+      <c r="S11" s="356" t="n"/>
+      <c r="T11" s="356" t="n"/>
+      <c r="U11" s="356" t="n"/>
+      <c r="V11" s="356" t="n"/>
+      <c r="W11" s="356" t="n"/>
+      <c r="X11" s="356" t="n"/>
+      <c r="Y11" s="356" t="n"/>
+      <c r="Z11" s="356" t="n"/>
+      <c r="AA11" s="356" t="n"/>
+      <c r="AB11" s="356" t="n"/>
+      <c r="AC11" s="356" t="n"/>
+      <c r="AD11" s="356" t="n"/>
+      <c r="AE11" s="356" t="n"/>
+      <c r="AF11" s="356" t="n"/>
+      <c r="AG11" s="356" t="n"/>
+      <c r="AH11" s="356" t="n"/>
+      <c r="AI11" s="356" t="n"/>
+      <c r="AJ11" s="356" t="n"/>
+      <c r="AK11" s="356" t="n"/>
+      <c r="AL11" s="356" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="534" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="396">
+      <c r="A12" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="397" t="n"/>
-      <c r="C12" s="397" t="n"/>
-      <c r="D12" s="397" t="n"/>
-      <c r="E12" s="397" t="n"/>
-      <c r="F12" s="397" t="n"/>
-      <c r="G12" s="397" t="n"/>
-      <c r="H12" s="397" t="n"/>
-      <c r="I12" s="398" t="n"/>
-      <c r="J12" s="398" t="n"/>
-      <c r="K12" s="398" t="n"/>
-      <c r="L12" s="398" t="n"/>
-      <c r="M12" s="398" t="n"/>
-      <c r="N12" s="398" t="n"/>
-      <c r="O12" s="398" t="n"/>
-      <c r="P12" s="398" t="n"/>
-      <c r="Q12" s="398" t="n"/>
-      <c r="R12" s="398" t="n"/>
-      <c r="S12" s="398" t="n"/>
-      <c r="T12" s="398" t="n"/>
-      <c r="U12" s="398" t="n"/>
-      <c r="V12" s="398" t="n"/>
-      <c r="W12" s="398" t="n"/>
-      <c r="X12" s="398" t="n"/>
-      <c r="Y12" s="398" t="n"/>
-      <c r="Z12" s="398" t="n"/>
-      <c r="AA12" s="398" t="n"/>
-      <c r="AB12" s="398" t="n"/>
-      <c r="AC12" s="398" t="n"/>
-      <c r="AD12" s="398" t="n"/>
-      <c r="AE12" s="398" t="n"/>
-      <c r="AF12" s="398" t="n"/>
-      <c r="AG12" s="398" t="n"/>
-      <c r="AH12" s="398" t="n"/>
-      <c r="AI12" s="398" t="n"/>
-      <c r="AJ12" s="398" t="n"/>
-      <c r="AK12" s="398" t="n"/>
-      <c r="AL12" s="398" t="n"/>
-      <c r="AM12" s="398" t="n"/>
-      <c r="AN12" s="398" t="n"/>
+      <c r="B12" s="532" t="n"/>
+      <c r="C12" s="533" t="n"/>
+      <c r="D12" s="533" t="n"/>
+      <c r="E12" s="533" t="n"/>
+      <c r="F12" s="533" t="n"/>
+      <c r="G12" s="533" t="n"/>
+      <c r="H12" s="533" t="n"/>
+      <c r="I12" s="356" t="n"/>
+      <c r="J12" s="356" t="n"/>
+      <c r="K12" s="356" t="n"/>
+      <c r="L12" s="356" t="n"/>
+      <c r="M12" s="356" t="n"/>
+      <c r="N12" s="356" t="n"/>
+      <c r="O12" s="356" t="n"/>
+      <c r="P12" s="356" t="n"/>
+      <c r="Q12" s="356" t="n"/>
+      <c r="R12" s="356" t="n"/>
+      <c r="S12" s="356" t="n"/>
+      <c r="T12" s="356" t="n"/>
+      <c r="U12" s="356" t="n"/>
+      <c r="V12" s="356" t="n"/>
+      <c r="W12" s="356" t="n"/>
+      <c r="X12" s="356" t="n"/>
+      <c r="Y12" s="356" t="n"/>
+      <c r="Z12" s="356" t="n"/>
+      <c r="AA12" s="356" t="n"/>
+      <c r="AB12" s="356" t="n"/>
+      <c r="AC12" s="356" t="n"/>
+      <c r="AD12" s="356" t="n"/>
+      <c r="AE12" s="356" t="n"/>
+      <c r="AF12" s="356" t="n"/>
+      <c r="AG12" s="356" t="n"/>
+      <c r="AH12" s="356" t="n"/>
+      <c r="AI12" s="356" t="n"/>
+      <c r="AJ12" s="356" t="n"/>
+      <c r="AK12" s="356" t="n"/>
+      <c r="AL12" s="356" t="n"/>
+      <c r="AM12" s="356" t="n"/>
+      <c r="AN12" s="534" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="396">
+      <c r="A13" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="397" t="n"/>
-      <c r="C13" s="397" t="n"/>
-      <c r="D13" s="397" t="n"/>
-      <c r="E13" s="397" t="n"/>
-      <c r="F13" s="397" t="n"/>
-      <c r="G13" s="397" t="n"/>
-      <c r="H13" s="397" t="n"/>
-      <c r="I13" s="398" t="n"/>
-      <c r="J13" s="398" t="n"/>
-      <c r="K13" s="398" t="n"/>
-      <c r="L13" s="398" t="n"/>
-      <c r="M13" s="398" t="n"/>
-      <c r="N13" s="398" t="n"/>
-      <c r="O13" s="398" t="n"/>
-      <c r="P13" s="398" t="n"/>
-      <c r="Q13" s="398" t="n"/>
-      <c r="R13" s="398" t="n"/>
-      <c r="S13" s="398" t="n"/>
-      <c r="T13" s="398" t="n"/>
-      <c r="U13" s="398" t="n"/>
-      <c r="V13" s="398" t="n"/>
-      <c r="W13" s="398" t="n"/>
-      <c r="X13" s="398" t="n"/>
-      <c r="Y13" s="398" t="n"/>
-      <c r="Z13" s="398" t="n"/>
-      <c r="AA13" s="398" t="n"/>
-      <c r="AB13" s="398" t="n"/>
-      <c r="AC13" s="398" t="n"/>
-      <c r="AD13" s="398" t="n"/>
-      <c r="AE13" s="398" t="n"/>
-      <c r="AF13" s="398" t="n"/>
-      <c r="AG13" s="398" t="n"/>
-      <c r="AH13" s="398" t="n"/>
-      <c r="AI13" s="398" t="n"/>
-      <c r="AJ13" s="398" t="n"/>
-      <c r="AK13" s="398" t="n"/>
-      <c r="AL13" s="398" t="n"/>
-      <c r="AM13" s="398" t="n"/>
-      <c r="AN13" s="398" t="n"/>
+      <c r="B13" s="532" t="n"/>
+      <c r="C13" s="533" t="n"/>
+      <c r="D13" s="533" t="n"/>
+      <c r="E13" s="533" t="n"/>
+      <c r="F13" s="533" t="n"/>
+      <c r="G13" s="533" t="n"/>
+      <c r="H13" s="533" t="n"/>
+      <c r="I13" s="356" t="n"/>
+      <c r="J13" s="356" t="n"/>
+      <c r="K13" s="356" t="n"/>
+      <c r="L13" s="356" t="n"/>
+      <c r="M13" s="356" t="n"/>
+      <c r="N13" s="356" t="n"/>
+      <c r="O13" s="356" t="n"/>
+      <c r="P13" s="356" t="n"/>
+      <c r="Q13" s="356" t="n"/>
+      <c r="R13" s="356" t="n"/>
+      <c r="S13" s="356" t="n"/>
+      <c r="T13" s="356" t="n"/>
+      <c r="U13" s="356" t="n"/>
+      <c r="V13" s="356" t="n"/>
+      <c r="W13" s="356" t="n"/>
+      <c r="X13" s="356" t="n"/>
+      <c r="Y13" s="356" t="n"/>
+      <c r="Z13" s="356" t="n"/>
+      <c r="AA13" s="356" t="n"/>
+      <c r="AB13" s="356" t="n"/>
+      <c r="AC13" s="356" t="n"/>
+      <c r="AD13" s="356" t="n"/>
+      <c r="AE13" s="356" t="n"/>
+      <c r="AF13" s="356" t="n"/>
+      <c r="AG13" s="356" t="n"/>
+      <c r="AH13" s="356" t="n"/>
+      <c r="AI13" s="356" t="n"/>
+      <c r="AJ13" s="356" t="n"/>
+      <c r="AK13" s="356" t="n"/>
+      <c r="AL13" s="356" t="n"/>
+      <c r="AM13" s="356" t="n"/>
+      <c r="AN13" s="534" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="396">
+      <c r="A14" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="397" t="n"/>
-      <c r="C14" s="397" t="n"/>
-      <c r="D14" s="397" t="n"/>
-      <c r="E14" s="397" t="n"/>
-      <c r="F14" s="397" t="n"/>
-      <c r="G14" s="397" t="n"/>
-      <c r="H14" s="397" t="n"/>
-      <c r="I14" s="398" t="n"/>
-      <c r="J14" s="398" t="n"/>
-      <c r="K14" s="398" t="n"/>
-      <c r="L14" s="398" t="n"/>
-      <c r="M14" s="398" t="n"/>
-      <c r="N14" s="398" t="n"/>
-      <c r="O14" s="398" t="n"/>
-      <c r="P14" s="398" t="n"/>
-      <c r="Q14" s="398" t="n"/>
-      <c r="R14" s="398" t="n"/>
-      <c r="S14" s="398" t="n"/>
-      <c r="T14" s="398" t="n"/>
-      <c r="U14" s="398" t="n"/>
-      <c r="V14" s="398" t="n"/>
-      <c r="W14" s="398" t="n"/>
-      <c r="X14" s="398" t="n"/>
-      <c r="Y14" s="398" t="n"/>
-      <c r="Z14" s="398" t="n"/>
-      <c r="AA14" s="398" t="n"/>
-      <c r="AB14" s="398" t="n"/>
-      <c r="AC14" s="398" t="n"/>
-      <c r="AD14" s="398" t="n"/>
-      <c r="AE14" s="398" t="n"/>
-      <c r="AF14" s="398" t="n"/>
-      <c r="AG14" s="398" t="n"/>
-      <c r="AH14" s="398" t="n"/>
-      <c r="AI14" s="398" t="n"/>
-      <c r="AJ14" s="398" t="n"/>
-      <c r="AK14" s="398" t="n"/>
-      <c r="AL14" s="398" t="n"/>
-      <c r="AM14" s="398" t="n"/>
-      <c r="AN14" s="398" t="n"/>
+      <c r="B14" s="532" t="n"/>
+      <c r="C14" s="533" t="n"/>
+      <c r="D14" s="533" t="n"/>
+      <c r="E14" s="533" t="n"/>
+      <c r="F14" s="533" t="n"/>
+      <c r="G14" s="533" t="n"/>
+      <c r="H14" s="533" t="n"/>
+      <c r="I14" s="356" t="n"/>
+      <c r="J14" s="356" t="n"/>
+      <c r="K14" s="356" t="n"/>
+      <c r="L14" s="356" t="n"/>
+      <c r="M14" s="356" t="n"/>
+      <c r="N14" s="356" t="n"/>
+      <c r="O14" s="356" t="n"/>
+      <c r="P14" s="356" t="n"/>
+      <c r="Q14" s="356" t="n"/>
+      <c r="R14" s="356" t="n"/>
+      <c r="S14" s="356" t="n"/>
+      <c r="T14" s="356" t="n"/>
+      <c r="U14" s="356" t="n"/>
+      <c r="V14" s="356" t="n"/>
+      <c r="W14" s="356" t="n"/>
+      <c r="X14" s="356" t="n"/>
+      <c r="Y14" s="356" t="n"/>
+      <c r="Z14" s="356" t="n"/>
+      <c r="AA14" s="356" t="n"/>
+      <c r="AB14" s="356" t="n"/>
+      <c r="AC14" s="356" t="n"/>
+      <c r="AD14" s="356" t="n"/>
+      <c r="AE14" s="356" t="n"/>
+      <c r="AF14" s="356" t="n"/>
+      <c r="AG14" s="356" t="n"/>
+      <c r="AH14" s="356" t="n"/>
+      <c r="AI14" s="356" t="n"/>
+      <c r="AJ14" s="356" t="n"/>
+      <c r="AK14" s="356" t="n"/>
+      <c r="AL14" s="356" t="n"/>
+      <c r="AM14" s="356" t="n"/>
+      <c r="AN14" s="534" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="396">
+      <c r="A15" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B15" s="397" t="n"/>
-      <c r="C15" s="397" t="n"/>
-      <c r="D15" s="397" t="n"/>
-      <c r="E15" s="397" t="n"/>
-      <c r="F15" s="397" t="n"/>
-      <c r="G15" s="397" t="n"/>
-      <c r="H15" s="397" t="n"/>
-      <c r="I15" s="398" t="n"/>
-      <c r="J15" s="398" t="n"/>
-      <c r="K15" s="398" t="n"/>
-      <c r="L15" s="398" t="n"/>
-      <c r="M15" s="398" t="n"/>
-      <c r="N15" s="398" t="n"/>
-      <c r="O15" s="398" t="n"/>
-      <c r="P15" s="398" t="n"/>
-      <c r="Q15" s="398" t="n"/>
-      <c r="R15" s="398" t="n"/>
-      <c r="S15" s="398" t="n"/>
-      <c r="T15" s="398" t="n"/>
-      <c r="U15" s="398" t="n"/>
-      <c r="V15" s="398" t="n"/>
-      <c r="W15" s="398" t="n"/>
-      <c r="X15" s="398" t="n"/>
-      <c r="Y15" s="398" t="n"/>
-      <c r="Z15" s="398" t="n"/>
-      <c r="AA15" s="398" t="n"/>
-      <c r="AB15" s="398" t="n"/>
-      <c r="AC15" s="398" t="n"/>
-      <c r="AD15" s="398" t="n"/>
-      <c r="AE15" s="398" t="n"/>
-      <c r="AF15" s="398" t="n"/>
-      <c r="AG15" s="398" t="n"/>
-      <c r="AH15" s="398" t="n"/>
-      <c r="AI15" s="398" t="n"/>
-      <c r="AJ15" s="398" t="n"/>
-      <c r="AK15" s="398" t="n"/>
-      <c r="AL15" s="398" t="n"/>
-      <c r="AM15" s="398" t="n"/>
-      <c r="AN15" s="398" t="n"/>
+      <c r="B15" s="532" t="n"/>
+      <c r="C15" s="533" t="n"/>
+      <c r="D15" s="533" t="n"/>
+      <c r="E15" s="533" t="n"/>
+      <c r="F15" s="533" t="n"/>
+      <c r="G15" s="533" t="n"/>
+      <c r="H15" s="533" t="n"/>
+      <c r="I15" s="356" t="n"/>
+      <c r="J15" s="356" t="n"/>
+      <c r="K15" s="356" t="n"/>
+      <c r="L15" s="356" t="n"/>
+      <c r="M15" s="356" t="n"/>
+      <c r="N15" s="356" t="n"/>
+      <c r="O15" s="356" t="n"/>
+      <c r="P15" s="356" t="n"/>
+      <c r="Q15" s="356" t="n"/>
+      <c r="R15" s="356" t="n"/>
+      <c r="S15" s="356" t="n"/>
+      <c r="T15" s="356" t="n"/>
+      <c r="U15" s="356" t="n"/>
+      <c r="V15" s="356" t="n"/>
+      <c r="W15" s="356" t="n"/>
+      <c r="X15" s="356" t="n"/>
+      <c r="Y15" s="356" t="n"/>
+      <c r="Z15" s="356" t="n"/>
+      <c r="AA15" s="356" t="n"/>
+      <c r="AB15" s="356" t="n"/>
+      <c r="AC15" s="356" t="n"/>
+      <c r="AD15" s="356" t="n"/>
+      <c r="AE15" s="356" t="n"/>
+      <c r="AF15" s="356" t="n"/>
+      <c r="AG15" s="356" t="n"/>
+      <c r="AH15" s="356" t="n"/>
+      <c r="AI15" s="356" t="n"/>
+      <c r="AJ15" s="356" t="n"/>
+      <c r="AK15" s="356" t="n"/>
+      <c r="AL15" s="356" t="n"/>
+      <c r="AM15" s="356" t="n"/>
+      <c r="AN15" s="534" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="396">
+      <c r="A16" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B16" s="397" t="n"/>
-      <c r="C16" s="397" t="n"/>
-      <c r="D16" s="397" t="n"/>
-      <c r="E16" s="397" t="n"/>
-      <c r="F16" s="397" t="n"/>
-      <c r="G16" s="397" t="n"/>
-      <c r="H16" s="397" t="n"/>
-      <c r="I16" s="398" t="n"/>
-      <c r="J16" s="398" t="n"/>
-      <c r="K16" s="398" t="n"/>
-      <c r="L16" s="398" t="n"/>
-      <c r="M16" s="398" t="n"/>
-      <c r="N16" s="398" t="n"/>
-      <c r="O16" s="398" t="n"/>
-      <c r="P16" s="398" t="n"/>
-      <c r="Q16" s="398" t="n"/>
-      <c r="R16" s="398" t="n"/>
-      <c r="S16" s="398" t="n"/>
-      <c r="T16" s="398" t="n"/>
-      <c r="U16" s="398" t="n"/>
-      <c r="V16" s="398" t="n"/>
-      <c r="W16" s="398" t="n"/>
-      <c r="X16" s="398" t="n"/>
-      <c r="Y16" s="398" t="n"/>
-      <c r="Z16" s="398" t="n"/>
-      <c r="AA16" s="398" t="n"/>
-      <c r="AB16" s="398" t="n"/>
-      <c r="AC16" s="398" t="n"/>
-      <c r="AD16" s="398" t="n"/>
-      <c r="AE16" s="398" t="n"/>
-      <c r="AF16" s="398" t="n"/>
-      <c r="AG16" s="398" t="n"/>
-      <c r="AH16" s="398" t="n"/>
-      <c r="AI16" s="398" t="n"/>
-      <c r="AJ16" s="398" t="n"/>
-      <c r="AK16" s="398" t="n"/>
-      <c r="AL16" s="398" t="n"/>
-      <c r="AM16" s="398" t="n"/>
-      <c r="AN16" s="398" t="n"/>
+      <c r="B16" s="532" t="n"/>
+      <c r="C16" s="533" t="n"/>
+      <c r="D16" s="533" t="n"/>
+      <c r="E16" s="533" t="n"/>
+      <c r="F16" s="533" t="n"/>
+      <c r="G16" s="533" t="n"/>
+      <c r="H16" s="533" t="n"/>
+      <c r="I16" s="356" t="n"/>
+      <c r="J16" s="356" t="n"/>
+      <c r="K16" s="356" t="n"/>
+      <c r="L16" s="356" t="n"/>
+      <c r="M16" s="356" t="n"/>
+      <c r="N16" s="356" t="n"/>
+      <c r="O16" s="356" t="n"/>
+      <c r="P16" s="356" t="n"/>
+      <c r="Q16" s="356" t="n"/>
+      <c r="R16" s="356" t="n"/>
+      <c r="S16" s="356" t="n"/>
+      <c r="T16" s="356" t="n"/>
+      <c r="U16" s="356" t="n"/>
+      <c r="V16" s="356" t="n"/>
+      <c r="W16" s="356" t="n"/>
+      <c r="X16" s="356" t="n"/>
+      <c r="Y16" s="356" t="n"/>
+      <c r="Z16" s="356" t="n"/>
+      <c r="AA16" s="356" t="n"/>
+      <c r="AB16" s="356" t="n"/>
+      <c r="AC16" s="356" t="n"/>
+      <c r="AD16" s="356" t="n"/>
+      <c r="AE16" s="356" t="n"/>
+      <c r="AF16" s="356" t="n"/>
+      <c r="AG16" s="356" t="n"/>
+      <c r="AH16" s="356" t="n"/>
+      <c r="AI16" s="356" t="n"/>
+      <c r="AJ16" s="356" t="n"/>
+      <c r="AK16" s="356" t="n"/>
+      <c r="AL16" s="356" t="n"/>
+      <c r="AM16" s="356" t="n"/>
+      <c r="AN16" s="534" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="396">
+      <c r="A17" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B17" s="397" t="n"/>
-      <c r="C17" s="397" t="n"/>
-      <c r="D17" s="397" t="n"/>
-      <c r="E17" s="397" t="n"/>
-      <c r="F17" s="397" t="n"/>
-      <c r="G17" s="397" t="n"/>
-      <c r="H17" s="397" t="n"/>
-      <c r="I17" s="398" t="n"/>
-      <c r="J17" s="398" t="n"/>
-      <c r="K17" s="398" t="n"/>
-      <c r="L17" s="398" t="n"/>
-      <c r="M17" s="398" t="n"/>
-      <c r="N17" s="398" t="n"/>
-      <c r="O17" s="398" t="n"/>
-      <c r="P17" s="398" t="n"/>
-      <c r="Q17" s="398" t="n"/>
-      <c r="R17" s="398" t="n"/>
-      <c r="S17" s="398" t="n"/>
-      <c r="T17" s="398" t="n"/>
-      <c r="U17" s="398" t="n"/>
-      <c r="V17" s="398" t="n"/>
-      <c r="W17" s="398" t="n"/>
-      <c r="X17" s="398" t="n"/>
-      <c r="Y17" s="398" t="n"/>
-      <c r="Z17" s="398" t="n"/>
-      <c r="AA17" s="398" t="n"/>
-      <c r="AB17" s="398" t="n"/>
-      <c r="AC17" s="398" t="n"/>
-      <c r="AD17" s="398" t="n"/>
-      <c r="AE17" s="398" t="n"/>
-      <c r="AF17" s="398" t="n"/>
-      <c r="AG17" s="398" t="n"/>
-      <c r="AH17" s="398" t="n"/>
-      <c r="AI17" s="398" t="n"/>
-      <c r="AJ17" s="398" t="n"/>
-      <c r="AK17" s="398" t="n"/>
-      <c r="AL17" s="398" t="n"/>
-      <c r="AM17" s="398" t="n"/>
-      <c r="AN17" s="398" t="n"/>
+      <c r="B17" s="532" t="n"/>
+      <c r="C17" s="533" t="n"/>
+      <c r="D17" s="533" t="n"/>
+      <c r="E17" s="533" t="n"/>
+      <c r="F17" s="533" t="n"/>
+      <c r="G17" s="533" t="n"/>
+      <c r="H17" s="533" t="n"/>
+      <c r="I17" s="356" t="n"/>
+      <c r="J17" s="356" t="n"/>
+      <c r="K17" s="356" t="n"/>
+      <c r="L17" s="356" t="n"/>
+      <c r="M17" s="356" t="n"/>
+      <c r="N17" s="356" t="n"/>
+      <c r="O17" s="356" t="n"/>
+      <c r="P17" s="356" t="n"/>
+      <c r="Q17" s="356" t="n"/>
+      <c r="R17" s="356" t="n"/>
+      <c r="S17" s="356" t="n"/>
+      <c r="T17" s="356" t="n"/>
+      <c r="U17" s="356" t="n"/>
+      <c r="V17" s="356" t="n"/>
+      <c r="W17" s="356" t="n"/>
+      <c r="X17" s="356" t="n"/>
+      <c r="Y17" s="356" t="n"/>
+      <c r="Z17" s="356" t="n"/>
+      <c r="AA17" s="356" t="n"/>
+      <c r="AB17" s="356" t="n"/>
+      <c r="AC17" s="356" t="n"/>
+      <c r="AD17" s="356" t="n"/>
+      <c r="AE17" s="356" t="n"/>
+      <c r="AF17" s="356" t="n"/>
+      <c r="AG17" s="356" t="n"/>
+      <c r="AH17" s="356" t="n"/>
+      <c r="AI17" s="356" t="n"/>
+      <c r="AJ17" s="356" t="n"/>
+      <c r="AK17" s="356" t="n"/>
+      <c r="AL17" s="356" t="n"/>
+      <c r="AM17" s="356" t="n"/>
+      <c r="AN17" s="534" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="396">
+      <c r="A18" s="531">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B18" s="397" t="n"/>
-      <c r="C18" s="397" t="n"/>
-      <c r="D18" s="397" t="n"/>
-      <c r="E18" s="397" t="n"/>
-      <c r="F18" s="397" t="n"/>
-      <c r="G18" s="397" t="n"/>
-      <c r="H18" s="397" t="n"/>
-      <c r="I18" s="398" t="n"/>
-      <c r="J18" s="398" t="n"/>
-      <c r="K18" s="398" t="n"/>
-      <c r="L18" s="398" t="n"/>
-      <c r="M18" s="398" t="n"/>
-      <c r="N18" s="398" t="n"/>
-      <c r="O18" s="398" t="n"/>
-      <c r="P18" s="398" t="n"/>
-      <c r="Q18" s="398" t="n"/>
-      <c r="R18" s="398" t="n"/>
-      <c r="S18" s="398" t="n"/>
-      <c r="T18" s="398" t="n"/>
-      <c r="U18" s="398" t="n"/>
-      <c r="V18" s="398" t="n"/>
-      <c r="W18" s="398" t="n"/>
-      <c r="X18" s="398" t="n"/>
-      <c r="Y18" s="398" t="n"/>
-      <c r="Z18" s="398" t="n"/>
-      <c r="AA18" s="398" t="n"/>
-      <c r="AB18" s="398" t="n"/>
-      <c r="AC18" s="398" t="n"/>
-      <c r="AD18" s="398" t="n"/>
-      <c r="AE18" s="398" t="n"/>
-      <c r="AF18" s="398" t="n"/>
-      <c r="AG18" s="398" t="n"/>
-      <c r="AH18" s="398" t="n"/>
-      <c r="AI18" s="398" t="n"/>
-      <c r="AJ18" s="398" t="n"/>
-      <c r="AK18" s="398" t="n"/>
-      <c r="AL18" s="398" t="n"/>
-      <c r="AM18" s="398" t="n"/>
-      <c r="AN18" s="398" t="n"/>
+      <c r="B18" s="532" t="n"/>
+      <c r="C18" s="533" t="n"/>
+      <c r="D18" s="533" t="n"/>
+      <c r="E18" s="533" t="n"/>
+      <c r="F18" s="533" t="n"/>
+      <c r="G18" s="533" t="n"/>
+      <c r="H18" s="533" t="n"/>
+      <c r="I18" s="356" t="n"/>
+      <c r="J18" s="356" t="n"/>
+      <c r="K18" s="356" t="n"/>
+      <c r="L18" s="356" t="n"/>
+      <c r="M18" s="356" t="n"/>
+      <c r="N18" s="356" t="n"/>
+      <c r="O18" s="356" t="n"/>
+      <c r="P18" s="356" t="n"/>
+      <c r="Q18" s="356" t="n"/>
+      <c r="R18" s="356" t="n"/>
+      <c r="S18" s="356" t="n"/>
+      <c r="T18" s="356" t="n"/>
+      <c r="U18" s="356" t="n"/>
+      <c r="V18" s="356" t="n"/>
+      <c r="W18" s="356" t="n"/>
+      <c r="X18" s="356" t="n"/>
+      <c r="Y18" s="356" t="n"/>
+      <c r="Z18" s="356" t="n"/>
+      <c r="AA18" s="356" t="n"/>
+      <c r="AB18" s="356" t="n"/>
+      <c r="AC18" s="356" t="n"/>
+      <c r="AD18" s="356" t="n"/>
+      <c r="AE18" s="356" t="n"/>
+      <c r="AF18" s="356" t="n"/>
+      <c r="AG18" s="356" t="n"/>
+      <c r="AH18" s="356" t="n"/>
+      <c r="AI18" s="356" t="n"/>
+      <c r="AJ18" s="356" t="n"/>
+      <c r="AK18" s="356" t="n"/>
+      <c r="AL18" s="356" t="n"/>
+      <c r="AM18" s="356" t="n"/>
+      <c r="AN18" s="534" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="396">
+      <c r="A19" s="535">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B19" s="397" t="n"/>
-      <c r="C19" s="397" t="n"/>
-      <c r="D19" s="397" t="n"/>
-      <c r="E19" s="397" t="n"/>
-      <c r="F19" s="397" t="n"/>
-      <c r="G19" s="397" t="n"/>
-      <c r="H19" s="397" t="n"/>
-      <c r="I19" s="398" t="n"/>
-      <c r="J19" s="398" t="n"/>
-      <c r="K19" s="398" t="n"/>
-      <c r="L19" s="398" t="n"/>
-      <c r="M19" s="398" t="n"/>
-      <c r="N19" s="398" t="n"/>
-      <c r="O19" s="398" t="n"/>
-      <c r="P19" s="398" t="n"/>
-      <c r="Q19" s="398" t="n"/>
-      <c r="R19" s="398" t="n"/>
-      <c r="S19" s="398" t="n"/>
-      <c r="T19" s="398" t="n"/>
-      <c r="U19" s="398" t="n"/>
-      <c r="V19" s="398" t="n"/>
-      <c r="W19" s="398" t="n"/>
-      <c r="X19" s="398" t="n"/>
-      <c r="Y19" s="398" t="n"/>
-      <c r="Z19" s="398" t="n"/>
-      <c r="AA19" s="398" t="n"/>
-      <c r="AB19" s="398" t="n"/>
-      <c r="AC19" s="398" t="n"/>
-      <c r="AD19" s="398" t="n"/>
-      <c r="AE19" s="398" t="n"/>
-      <c r="AF19" s="398" t="n"/>
-      <c r="AG19" s="398" t="n"/>
-      <c r="AH19" s="398" t="n"/>
-      <c r="AI19" s="398" t="n"/>
-      <c r="AJ19" s="398" t="n"/>
-      <c r="AK19" s="398" t="n"/>
-      <c r="AL19" s="398" t="n"/>
-      <c r="AM19" s="398" t="n"/>
-      <c r="AN19" s="398" t="n"/>
+      <c r="B19" s="536" t="n"/>
+      <c r="C19" s="537" t="n"/>
+      <c r="D19" s="537" t="n"/>
+      <c r="E19" s="537" t="n"/>
+      <c r="F19" s="537" t="n"/>
+      <c r="G19" s="537" t="n"/>
+      <c r="H19" s="537" t="n"/>
+      <c r="I19" s="538" t="n"/>
+      <c r="J19" s="538" t="n"/>
+      <c r="K19" s="538" t="n"/>
+      <c r="L19" s="538" t="n"/>
+      <c r="M19" s="538" t="n"/>
+      <c r="N19" s="538" t="n"/>
+      <c r="O19" s="538" t="n"/>
+      <c r="P19" s="538" t="n"/>
+      <c r="Q19" s="538" t="n"/>
+      <c r="R19" s="538" t="n"/>
+      <c r="S19" s="538" t="n"/>
+      <c r="T19" s="538" t="n"/>
+      <c r="U19" s="538" t="n"/>
+      <c r="V19" s="538" t="n"/>
+      <c r="W19" s="538" t="n"/>
+      <c r="X19" s="538" t="n"/>
+      <c r="Y19" s="538" t="n"/>
+      <c r="Z19" s="538" t="n"/>
+      <c r="AA19" s="538" t="n"/>
+      <c r="AB19" s="538" t="n"/>
+      <c r="AC19" s="538" t="n"/>
+      <c r="AD19" s="538" t="n"/>
+      <c r="AE19" s="538" t="n"/>
+      <c r="AF19" s="538" t="n"/>
+      <c r="AG19" s="538" t="n"/>
+      <c r="AH19" s="538" t="n"/>
+      <c r="AI19" s="538" t="n"/>
+      <c r="AJ19" s="538" t="n"/>
+      <c r="AK19" s="538" t="n"/>
+      <c r="AL19" s="538" t="n"/>
+      <c r="AM19" s="538" t="n"/>
+      <c r="AN19" s="539" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -9034,8 +9925,9 @@
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9091,254 +9983,260 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="512" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="422" t="n"/>
-      <c r="C1" s="422" t="n"/>
-      <c r="D1" s="422" t="n"/>
-      <c r="E1" s="422" t="n"/>
-      <c r="F1" s="422" t="n"/>
-      <c r="G1" s="423" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="428" t="n"/>
+      <c r="C1" s="428" t="n"/>
+      <c r="D1" s="428" t="n"/>
+      <c r="E1" s="428" t="n"/>
+      <c r="F1" s="428" t="n"/>
+      <c r="G1" s="428" t="n"/>
+      <c r="H1" s="513" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="431" t="n"/>
+      <c r="K1" s="431" t="n"/>
+      <c r="L1" s="431" t="n"/>
+      <c r="M1" s="431" t="n"/>
+      <c r="N1" s="431" t="n"/>
+      <c r="O1" s="431" t="n"/>
+      <c r="P1" s="431" t="n"/>
+      <c r="Q1" s="431" t="n"/>
+      <c r="R1" s="431" t="n"/>
+      <c r="S1" s="431" t="n"/>
+      <c r="T1" s="431" t="n"/>
+      <c r="U1" s="431" t="n"/>
+      <c r="V1" s="431" t="n"/>
+      <c r="W1" s="431" t="n"/>
+      <c r="X1" s="431" t="n"/>
+      <c r="Y1" s="431" t="n"/>
+      <c r="Z1" s="431" t="n"/>
+      <c r="AA1" s="431" t="n"/>
+      <c r="AB1" s="431" t="n"/>
+      <c r="AC1" s="431" t="n"/>
+      <c r="AD1" s="432" t="n"/>
+      <c r="AE1" s="433" t="n"/>
+      <c r="AF1" s="434" t="n"/>
+      <c r="AG1" s="434" t="n"/>
+      <c r="AH1" s="435" t="n"/>
+      <c r="AI1" s="436" t="n"/>
+      <c r="AJ1" s="437" t="n"/>
+      <c r="AK1" s="437" t="n"/>
+      <c r="AL1" s="437" t="n"/>
+      <c r="AM1" s="437" t="n"/>
+      <c r="AN1" s="438" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="514" t="inlineStr">
         <is>
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="515" t="n"/>
+      <c r="I2" s="441" t="n"/>
+      <c r="J2" s="442" t="n"/>
+      <c r="K2" s="442" t="n"/>
+      <c r="L2" s="442" t="n"/>
+      <c r="M2" s="442" t="n"/>
+      <c r="N2" s="442" t="n"/>
+      <c r="O2" s="442" t="n"/>
+      <c r="P2" s="442" t="n"/>
+      <c r="Q2" s="442" t="n"/>
+      <c r="R2" s="442" t="n"/>
+      <c r="S2" s="442" t="n"/>
+      <c r="T2" s="442" t="n"/>
+      <c r="U2" s="442" t="n"/>
+      <c r="V2" s="442" t="n"/>
+      <c r="W2" s="442" t="n"/>
+      <c r="X2" s="442" t="n"/>
+      <c r="Y2" s="442" t="n"/>
+      <c r="Z2" s="442" t="n"/>
+      <c r="AA2" s="442" t="n"/>
+      <c r="AB2" s="442" t="n"/>
+      <c r="AC2" s="442" t="n"/>
+      <c r="AD2" s="443" t="n"/>
+      <c r="AE2" s="444" t="n"/>
+      <c r="AF2" s="445" t="n"/>
+      <c r="AG2" s="445" t="n"/>
+      <c r="AH2" s="446" t="n"/>
+      <c r="AI2" s="447" t="n"/>
+      <c r="AJ2" s="448" t="n"/>
+      <c r="AK2" s="448" t="n"/>
+      <c r="AL2" s="448" t="n"/>
+      <c r="AM2" s="448" t="n"/>
+      <c r="AN2" s="449" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="516" t="n"/>
+      <c r="B3" s="517" t="n"/>
+      <c r="C3" s="517" t="n"/>
+      <c r="D3" s="517" t="n"/>
+      <c r="E3" s="517" t="n"/>
+      <c r="F3" s="517" t="n"/>
+      <c r="G3" s="517" t="n"/>
+      <c r="H3" s="515" t="n"/>
+      <c r="I3" s="441" t="n"/>
+      <c r="J3" s="442" t="n"/>
+      <c r="K3" s="442" t="n"/>
+      <c r="L3" s="442" t="n"/>
+      <c r="M3" s="442" t="n"/>
+      <c r="N3" s="442" t="n"/>
+      <c r="O3" s="442" t="n"/>
+      <c r="P3" s="442" t="n"/>
+      <c r="Q3" s="442" t="n"/>
+      <c r="R3" s="442" t="n"/>
+      <c r="S3" s="442" t="n"/>
+      <c r="T3" s="442" t="n"/>
+      <c r="U3" s="442" t="n"/>
+      <c r="V3" s="442" t="n"/>
+      <c r="W3" s="442" t="n"/>
+      <c r="X3" s="442" t="n"/>
+      <c r="Y3" s="442" t="n"/>
+      <c r="Z3" s="442" t="n"/>
+      <c r="AA3" s="442" t="n"/>
+      <c r="AB3" s="442" t="n"/>
+      <c r="AC3" s="442" t="n"/>
+      <c r="AD3" s="443" t="n"/>
+      <c r="AE3" s="444" t="n"/>
+      <c r="AF3" s="445" t="n"/>
+      <c r="AG3" s="445" t="n"/>
+      <c r="AH3" s="446" t="n"/>
+      <c r="AI3" s="447" t="n"/>
+      <c r="AJ3" s="448" t="n"/>
+      <c r="AK3" s="448" t="n"/>
+      <c r="AL3" s="448" t="n"/>
+      <c r="AM3" s="448" t="n"/>
+      <c r="AN3" s="449" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="366" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="518" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="366" t="inlineStr">
+      <c r="B4" s="519" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="366" t="inlineStr">
+      <c r="C4" s="519" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="348" t="n"/>
-      <c r="E4" s="348" t="n"/>
-      <c r="F4" s="348" t="n"/>
-      <c r="G4" s="348" t="n"/>
-      <c r="H4" s="348" t="n"/>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="D4" s="517" t="n"/>
+      <c r="E4" s="517" t="n"/>
+      <c r="F4" s="517" t="n"/>
+      <c r="G4" s="517" t="n"/>
+      <c r="H4" s="515" t="n"/>
+      <c r="I4" s="450" t="n"/>
+      <c r="J4" s="451" t="n"/>
+      <c r="K4" s="451" t="n"/>
+      <c r="L4" s="451" t="n"/>
+      <c r="M4" s="451" t="n"/>
+      <c r="N4" s="451" t="n"/>
+      <c r="O4" s="451" t="n"/>
+      <c r="P4" s="451" t="n"/>
+      <c r="Q4" s="451" t="n"/>
+      <c r="R4" s="451" t="n"/>
+      <c r="S4" s="451" t="n"/>
+      <c r="T4" s="451" t="n"/>
+      <c r="U4" s="451" t="n"/>
+      <c r="V4" s="451" t="n"/>
+      <c r="W4" s="451" t="n"/>
+      <c r="X4" s="451" t="n"/>
+      <c r="Y4" s="451" t="n"/>
+      <c r="Z4" s="451" t="n"/>
+      <c r="AA4" s="451" t="n"/>
+      <c r="AB4" s="451" t="n"/>
+      <c r="AC4" s="451" t="n"/>
+      <c r="AD4" s="452" t="n"/>
+      <c r="AE4" s="444" t="n"/>
+      <c r="AF4" s="445" t="n"/>
+      <c r="AG4" s="445" t="n"/>
+      <c r="AH4" s="446" t="n"/>
+      <c r="AI4" s="447" t="n"/>
+      <c r="AJ4" s="448" t="n"/>
+      <c r="AK4" s="448" t="n"/>
+      <c r="AL4" s="448" t="n"/>
+      <c r="AM4" s="448" t="n"/>
+      <c r="AN4" s="449" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="394" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="521" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="395" t="inlineStr">
+      <c r="B5" s="522" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="395" t="inlineStr">
+      <c r="C5" s="522" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="348" t="n"/>
-      <c r="E5" s="348" t="n"/>
-      <c r="F5" s="348" t="n"/>
-      <c r="G5" s="348" t="n"/>
-      <c r="H5" s="348" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="D5" s="540" t="n"/>
+      <c r="E5" s="540" t="n"/>
+      <c r="F5" s="540" t="n"/>
+      <c r="G5" s="540" t="n"/>
+      <c r="H5" s="541" t="n"/>
+      <c r="I5" s="456" t="n"/>
+      <c r="J5" s="457" t="n"/>
+      <c r="K5" s="457" t="n"/>
+      <c r="L5" s="457" t="n"/>
+      <c r="M5" s="457" t="n"/>
+      <c r="N5" s="457" t="n"/>
+      <c r="O5" s="457" t="n"/>
+      <c r="P5" s="457" t="n"/>
+      <c r="Q5" s="457" t="n"/>
+      <c r="R5" s="457" t="n"/>
+      <c r="S5" s="457" t="n"/>
+      <c r="T5" s="457" t="n"/>
+      <c r="U5" s="457" t="n"/>
+      <c r="V5" s="457" t="n"/>
+      <c r="W5" s="457" t="n"/>
+      <c r="X5" s="457" t="n"/>
+      <c r="Y5" s="457" t="n"/>
+      <c r="Z5" s="457" t="n"/>
+      <c r="AA5" s="457" t="n"/>
+      <c r="AB5" s="457" t="n"/>
+      <c r="AC5" s="457" t="n"/>
+      <c r="AD5" s="458" t="n"/>
+      <c r="AE5" s="459" t="n"/>
+      <c r="AF5" s="460" t="n"/>
+      <c r="AG5" s="460" t="n"/>
+      <c r="AH5" s="461" t="n"/>
+      <c r="AI5" s="462" t="n"/>
+      <c r="AJ5" s="463" t="n"/>
+      <c r="AK5" s="463" t="n"/>
+      <c r="AL5" s="463" t="n"/>
+      <c r="AM5" s="463" t="n"/>
+      <c r="AN5" s="464" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="394" t="inlineStr">
+      <c r="A6" s="524" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="395" t="inlineStr">
+      <c r="B6" s="525" t="inlineStr">
         <is>
           <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
         </is>
       </c>
-      <c r="C6" s="395" t="inlineStr">
+      <c r="C6" s="526" t="inlineStr">
         <is>
           <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
@@ -9346,529 +10244,529 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="348" t="n"/>
-      <c r="E6" s="348" t="n"/>
-      <c r="F6" s="348" t="n"/>
-      <c r="G6" s="348" t="n"/>
-      <c r="H6" s="348" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="D6" s="470" t="n"/>
+      <c r="E6" s="470" t="n"/>
+      <c r="F6" s="470" t="n"/>
+      <c r="G6" s="470" t="n"/>
+      <c r="H6" s="470" t="n"/>
+      <c r="I6" s="470" t="n"/>
+      <c r="J6" s="470" t="n"/>
+      <c r="K6" s="470" t="n"/>
+      <c r="L6" s="470" t="n"/>
+      <c r="M6" s="470" t="n"/>
+      <c r="N6" s="470" t="n"/>
+      <c r="O6" s="470" t="n"/>
+      <c r="P6" s="470" t="n"/>
+      <c r="Q6" s="470" t="n"/>
+      <c r="R6" s="470" t="n"/>
+      <c r="S6" s="470" t="n"/>
+      <c r="T6" s="470" t="n"/>
+      <c r="U6" s="470" t="n"/>
+      <c r="V6" s="470" t="n"/>
+      <c r="W6" s="470" t="n"/>
+      <c r="X6" s="470" t="n"/>
+      <c r="Y6" s="470" t="n"/>
+      <c r="Z6" s="470" t="n"/>
+      <c r="AA6" s="470" t="n"/>
+      <c r="AB6" s="470" t="n"/>
+      <c r="AC6" s="470" t="n"/>
+      <c r="AD6" s="470" t="n"/>
+      <c r="AE6" s="470" t="n"/>
+      <c r="AF6" s="470" t="n"/>
+      <c r="AG6" s="470" t="n"/>
+      <c r="AH6" s="470" t="n"/>
+      <c r="AI6" s="470" t="n"/>
+      <c r="AJ6" s="470" t="n"/>
+      <c r="AK6" s="470" t="n"/>
+      <c r="AL6" s="470" t="n"/>
+      <c r="AM6" s="470" t="n"/>
+      <c r="AN6" s="502" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="394" t="inlineStr">
+      <c r="A7" s="527" t="inlineStr">
         <is>
           <t>SOP SOP-603</t>
         </is>
       </c>
-      <c r="B7" s="395" t="inlineStr">
+      <c r="B7" s="528" t="inlineStr">
         <is>
           <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="395" t="inlineStr">
+      <c r="C7" s="529" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
         </is>
       </c>
-      <c r="D7" s="348" t="n"/>
-      <c r="E7" s="348" t="n"/>
-      <c r="F7" s="348" t="n"/>
-      <c r="G7" s="348" t="n"/>
-      <c r="H7" s="348" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="D7" s="344" t="n"/>
+      <c r="E7" s="344" t="n"/>
+      <c r="F7" s="344" t="n"/>
+      <c r="G7" s="344" t="n"/>
+      <c r="H7" s="344" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="530" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="396" t="inlineStr">
+      <c r="A8" s="531" t="inlineStr">
         <is>
           <t>WI WI-603</t>
         </is>
       </c>
-      <c r="B8" s="397" t="inlineStr">
+      <c r="B8" s="532" t="inlineStr">
         <is>
           <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
         </is>
       </c>
-      <c r="C8" s="397" t="inlineStr">
+      <c r="C8" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
         </is>
       </c>
-      <c r="D8" s="398" t="n"/>
-      <c r="E8" s="398" t="n"/>
-      <c r="F8" s="398" t="n"/>
-      <c r="G8" s="398" t="n"/>
-      <c r="H8" s="398" t="n"/>
-      <c r="I8" s="398" t="n"/>
-      <c r="J8" s="398" t="n"/>
-      <c r="K8" s="398" t="n"/>
-      <c r="L8" s="398" t="n"/>
-      <c r="M8" s="398" t="n"/>
-      <c r="N8" s="398" t="n"/>
-      <c r="O8" s="398" t="n"/>
-      <c r="P8" s="398" t="n"/>
-      <c r="Q8" s="398" t="n"/>
-      <c r="R8" s="398" t="n"/>
-      <c r="S8" s="398" t="n"/>
-      <c r="T8" s="398" t="n"/>
-      <c r="U8" s="398" t="n"/>
-      <c r="V8" s="398" t="n"/>
-      <c r="W8" s="398" t="n"/>
-      <c r="X8" s="398" t="n"/>
-      <c r="Y8" s="398" t="n"/>
-      <c r="Z8" s="398" t="n"/>
-      <c r="AA8" s="398" t="n"/>
-      <c r="AB8" s="398" t="n"/>
-      <c r="AC8" s="398" t="n"/>
-      <c r="AD8" s="398" t="n"/>
-      <c r="AE8" s="398" t="n"/>
-      <c r="AF8" s="398" t="n"/>
-      <c r="AG8" s="398" t="n"/>
-      <c r="AH8" s="398" t="n"/>
-      <c r="AI8" s="398" t="n"/>
-      <c r="AJ8" s="398" t="n"/>
-      <c r="AK8" s="398" t="n"/>
-      <c r="AL8" s="398" t="n"/>
-      <c r="AM8" s="398" t="n"/>
-      <c r="AN8" s="398" t="n"/>
+      <c r="D8" s="356" t="n"/>
+      <c r="E8" s="356" t="n"/>
+      <c r="F8" s="356" t="n"/>
+      <c r="G8" s="356" t="n"/>
+      <c r="H8" s="356" t="n"/>
+      <c r="I8" s="356" t="n"/>
+      <c r="J8" s="356" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="356" t="n"/>
+      <c r="M8" s="356" t="n"/>
+      <c r="N8" s="356" t="n"/>
+      <c r="O8" s="356" t="n"/>
+      <c r="P8" s="356" t="n"/>
+      <c r="Q8" s="356" t="n"/>
+      <c r="R8" s="356" t="n"/>
+      <c r="S8" s="356" t="n"/>
+      <c r="T8" s="356" t="n"/>
+      <c r="U8" s="356" t="n"/>
+      <c r="V8" s="356" t="n"/>
+      <c r="W8" s="356" t="n"/>
+      <c r="X8" s="356" t="n"/>
+      <c r="Y8" s="356" t="n"/>
+      <c r="Z8" s="356" t="n"/>
+      <c r="AA8" s="356" t="n"/>
+      <c r="AB8" s="356" t="n"/>
+      <c r="AC8" s="356" t="n"/>
+      <c r="AD8" s="356" t="n"/>
+      <c r="AE8" s="356" t="n"/>
+      <c r="AF8" s="356" t="n"/>
+      <c r="AG8" s="356" t="n"/>
+      <c r="AH8" s="356" t="n"/>
+      <c r="AI8" s="356" t="n"/>
+      <c r="AJ8" s="356" t="n"/>
+      <c r="AK8" s="356" t="n"/>
+      <c r="AL8" s="356" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="534" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="396" t="inlineStr">
+      <c r="A9" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="397" t="inlineStr">
+      <c r="B9" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="397" t="inlineStr">
+      <c r="C9" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
-      <c r="D9" s="398" t="n"/>
-      <c r="E9" s="398" t="n"/>
-      <c r="F9" s="398" t="n"/>
-      <c r="G9" s="398" t="n"/>
-      <c r="H9" s="398" t="n"/>
-      <c r="I9" s="398" t="n"/>
-      <c r="J9" s="398" t="n"/>
-      <c r="K9" s="398" t="n"/>
-      <c r="L9" s="398" t="n"/>
-      <c r="M9" s="398" t="n"/>
-      <c r="N9" s="398" t="n"/>
-      <c r="O9" s="398" t="n"/>
-      <c r="P9" s="398" t="n"/>
-      <c r="Q9" s="398" t="n"/>
-      <c r="R9" s="398" t="n"/>
-      <c r="S9" s="398" t="n"/>
-      <c r="T9" s="398" t="n"/>
-      <c r="U9" s="398" t="n"/>
-      <c r="V9" s="398" t="n"/>
-      <c r="W9" s="398" t="n"/>
-      <c r="X9" s="398" t="n"/>
-      <c r="Y9" s="398" t="n"/>
-      <c r="Z9" s="398" t="n"/>
-      <c r="AA9" s="398" t="n"/>
-      <c r="AB9" s="398" t="n"/>
-      <c r="AC9" s="398" t="n"/>
-      <c r="AD9" s="398" t="n"/>
-      <c r="AE9" s="398" t="n"/>
-      <c r="AF9" s="398" t="n"/>
-      <c r="AG9" s="398" t="n"/>
-      <c r="AH9" s="398" t="n"/>
-      <c r="AI9" s="398" t="n"/>
-      <c r="AJ9" s="398" t="n"/>
-      <c r="AK9" s="398" t="n"/>
-      <c r="AL9" s="398" t="n"/>
-      <c r="AM9" s="398" t="n"/>
-      <c r="AN9" s="398" t="n"/>
+      <c r="D9" s="356" t="n"/>
+      <c r="E9" s="356" t="n"/>
+      <c r="F9" s="356" t="n"/>
+      <c r="G9" s="356" t="n"/>
+      <c r="H9" s="356" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="356" t="n"/>
+      <c r="M9" s="356" t="n"/>
+      <c r="N9" s="356" t="n"/>
+      <c r="O9" s="356" t="n"/>
+      <c r="P9" s="356" t="n"/>
+      <c r="Q9" s="356" t="n"/>
+      <c r="R9" s="356" t="n"/>
+      <c r="S9" s="356" t="n"/>
+      <c r="T9" s="356" t="n"/>
+      <c r="U9" s="356" t="n"/>
+      <c r="V9" s="356" t="n"/>
+      <c r="W9" s="356" t="n"/>
+      <c r="X9" s="356" t="n"/>
+      <c r="Y9" s="356" t="n"/>
+      <c r="Z9" s="356" t="n"/>
+      <c r="AA9" s="356" t="n"/>
+      <c r="AB9" s="356" t="n"/>
+      <c r="AC9" s="356" t="n"/>
+      <c r="AD9" s="356" t="n"/>
+      <c r="AE9" s="356" t="n"/>
+      <c r="AF9" s="356" t="n"/>
+      <c r="AG9" s="356" t="n"/>
+      <c r="AH9" s="356" t="n"/>
+      <c r="AI9" s="356" t="n"/>
+      <c r="AJ9" s="356" t="n"/>
+      <c r="AK9" s="356" t="n"/>
+      <c r="AL9" s="356" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="534" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="396" t="inlineStr">
+      <c r="A10" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="397" t="inlineStr">
+      <c r="B10" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="397" t="inlineStr">
+      <c r="C10" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
-      <c r="D10" s="398" t="n"/>
-      <c r="E10" s="398" t="n"/>
-      <c r="F10" s="398" t="n"/>
-      <c r="G10" s="398" t="n"/>
-      <c r="H10" s="398" t="n"/>
-      <c r="I10" s="398" t="n"/>
-      <c r="J10" s="398" t="n"/>
-      <c r="K10" s="398" t="n"/>
-      <c r="L10" s="398" t="n"/>
-      <c r="M10" s="398" t="n"/>
-      <c r="N10" s="398" t="n"/>
-      <c r="O10" s="398" t="n"/>
-      <c r="P10" s="398" t="n"/>
-      <c r="Q10" s="398" t="n"/>
-      <c r="R10" s="398" t="n"/>
-      <c r="S10" s="398" t="n"/>
-      <c r="T10" s="398" t="n"/>
-      <c r="U10" s="398" t="n"/>
-      <c r="V10" s="398" t="n"/>
-      <c r="W10" s="398" t="n"/>
-      <c r="X10" s="398" t="n"/>
-      <c r="Y10" s="398" t="n"/>
-      <c r="Z10" s="398" t="n"/>
-      <c r="AA10" s="398" t="n"/>
-      <c r="AB10" s="398" t="n"/>
-      <c r="AC10" s="398" t="n"/>
-      <c r="AD10" s="398" t="n"/>
-      <c r="AE10" s="398" t="n"/>
-      <c r="AF10" s="398" t="n"/>
-      <c r="AG10" s="398" t="n"/>
-      <c r="AH10" s="398" t="n"/>
-      <c r="AI10" s="398" t="n"/>
-      <c r="AJ10" s="398" t="n"/>
-      <c r="AK10" s="398" t="n"/>
-      <c r="AL10" s="398" t="n"/>
-      <c r="AM10" s="398" t="n"/>
-      <c r="AN10" s="398" t="n"/>
+      <c r="D10" s="356" t="n"/>
+      <c r="E10" s="356" t="n"/>
+      <c r="F10" s="356" t="n"/>
+      <c r="G10" s="356" t="n"/>
+      <c r="H10" s="356" t="n"/>
+      <c r="I10" s="356" t="n"/>
+      <c r="J10" s="356" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="356" t="n"/>
+      <c r="M10" s="356" t="n"/>
+      <c r="N10" s="356" t="n"/>
+      <c r="O10" s="356" t="n"/>
+      <c r="P10" s="356" t="n"/>
+      <c r="Q10" s="356" t="n"/>
+      <c r="R10" s="356" t="n"/>
+      <c r="S10" s="356" t="n"/>
+      <c r="T10" s="356" t="n"/>
+      <c r="U10" s="356" t="n"/>
+      <c r="V10" s="356" t="n"/>
+      <c r="W10" s="356" t="n"/>
+      <c r="X10" s="356" t="n"/>
+      <c r="Y10" s="356" t="n"/>
+      <c r="Z10" s="356" t="n"/>
+      <c r="AA10" s="356" t="n"/>
+      <c r="AB10" s="356" t="n"/>
+      <c r="AC10" s="356" t="n"/>
+      <c r="AD10" s="356" t="n"/>
+      <c r="AE10" s="356" t="n"/>
+      <c r="AF10" s="356" t="n"/>
+      <c r="AG10" s="356" t="n"/>
+      <c r="AH10" s="356" t="n"/>
+      <c r="AI10" s="356" t="n"/>
+      <c r="AJ10" s="356" t="n"/>
+      <c r="AK10" s="356" t="n"/>
+      <c r="AL10" s="356" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="534" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="396" t="inlineStr">
+      <c r="A11" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="397" t="inlineStr">
+      <c r="B11" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="397" t="inlineStr">
+      <c r="C11" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
-      <c r="D11" s="398" t="n"/>
-      <c r="E11" s="398" t="n"/>
-      <c r="F11" s="398" t="n"/>
-      <c r="G11" s="398" t="n"/>
-      <c r="H11" s="398" t="n"/>
-      <c r="I11" s="398" t="n"/>
-      <c r="J11" s="398" t="n"/>
-      <c r="K11" s="398" t="n"/>
-      <c r="L11" s="398" t="n"/>
-      <c r="M11" s="398" t="n"/>
-      <c r="N11" s="398" t="n"/>
-      <c r="O11" s="398" t="n"/>
-      <c r="P11" s="398" t="n"/>
-      <c r="Q11" s="398" t="n"/>
-      <c r="R11" s="398" t="n"/>
-      <c r="S11" s="398" t="n"/>
-      <c r="T11" s="398" t="n"/>
-      <c r="U11" s="398" t="n"/>
-      <c r="V11" s="398" t="n"/>
-      <c r="W11" s="398" t="n"/>
-      <c r="X11" s="398" t="n"/>
-      <c r="Y11" s="398" t="n"/>
-      <c r="Z11" s="398" t="n"/>
-      <c r="AA11" s="398" t="n"/>
-      <c r="AB11" s="398" t="n"/>
-      <c r="AC11" s="398" t="n"/>
-      <c r="AD11" s="398" t="n"/>
-      <c r="AE11" s="398" t="n"/>
-      <c r="AF11" s="398" t="n"/>
-      <c r="AG11" s="398" t="n"/>
-      <c r="AH11" s="398" t="n"/>
-      <c r="AI11" s="398" t="n"/>
-      <c r="AJ11" s="398" t="n"/>
-      <c r="AK11" s="398" t="n"/>
-      <c r="AL11" s="398" t="n"/>
-      <c r="AM11" s="398" t="n"/>
-      <c r="AN11" s="398" t="n"/>
+      <c r="D11" s="356" t="n"/>
+      <c r="E11" s="356" t="n"/>
+      <c r="F11" s="356" t="n"/>
+      <c r="G11" s="356" t="n"/>
+      <c r="H11" s="356" t="n"/>
+      <c r="I11" s="356" t="n"/>
+      <c r="J11" s="356" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="356" t="n"/>
+      <c r="M11" s="356" t="n"/>
+      <c r="N11" s="356" t="n"/>
+      <c r="O11" s="356" t="n"/>
+      <c r="P11" s="356" t="n"/>
+      <c r="Q11" s="356" t="n"/>
+      <c r="R11" s="356" t="n"/>
+      <c r="S11" s="356" t="n"/>
+      <c r="T11" s="356" t="n"/>
+      <c r="U11" s="356" t="n"/>
+      <c r="V11" s="356" t="n"/>
+      <c r="W11" s="356" t="n"/>
+      <c r="X11" s="356" t="n"/>
+      <c r="Y11" s="356" t="n"/>
+      <c r="Z11" s="356" t="n"/>
+      <c r="AA11" s="356" t="n"/>
+      <c r="AB11" s="356" t="n"/>
+      <c r="AC11" s="356" t="n"/>
+      <c r="AD11" s="356" t="n"/>
+      <c r="AE11" s="356" t="n"/>
+      <c r="AF11" s="356" t="n"/>
+      <c r="AG11" s="356" t="n"/>
+      <c r="AH11" s="356" t="n"/>
+      <c r="AI11" s="356" t="n"/>
+      <c r="AJ11" s="356" t="n"/>
+      <c r="AK11" s="356" t="n"/>
+      <c r="AL11" s="356" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="534" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="396" t="inlineStr">
+      <c r="A12" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="397" t="inlineStr">
+      <c r="B12" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="397" t="inlineStr">
+      <c r="C12" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
-      <c r="D12" s="398" t="n"/>
-      <c r="E12" s="398" t="n"/>
-      <c r="F12" s="398" t="n"/>
-      <c r="G12" s="398" t="n"/>
-      <c r="H12" s="398" t="n"/>
-      <c r="I12" s="398" t="n"/>
-      <c r="J12" s="398" t="n"/>
-      <c r="K12" s="398" t="n"/>
-      <c r="L12" s="398" t="n"/>
-      <c r="M12" s="398" t="n"/>
-      <c r="N12" s="398" t="n"/>
-      <c r="O12" s="398" t="n"/>
-      <c r="P12" s="398" t="n"/>
-      <c r="Q12" s="398" t="n"/>
-      <c r="R12" s="398" t="n"/>
-      <c r="S12" s="398" t="n"/>
-      <c r="T12" s="398" t="n"/>
-      <c r="U12" s="398" t="n"/>
-      <c r="V12" s="398" t="n"/>
-      <c r="W12" s="398" t="n"/>
-      <c r="X12" s="398" t="n"/>
-      <c r="Y12" s="398" t="n"/>
-      <c r="Z12" s="398" t="n"/>
-      <c r="AA12" s="398" t="n"/>
-      <c r="AB12" s="398" t="n"/>
-      <c r="AC12" s="398" t="n"/>
-      <c r="AD12" s="398" t="n"/>
-      <c r="AE12" s="398" t="n"/>
-      <c r="AF12" s="398" t="n"/>
-      <c r="AG12" s="398" t="n"/>
-      <c r="AH12" s="398" t="n"/>
-      <c r="AI12" s="398" t="n"/>
-      <c r="AJ12" s="398" t="n"/>
-      <c r="AK12" s="398" t="n"/>
-      <c r="AL12" s="398" t="n"/>
-      <c r="AM12" s="398" t="n"/>
-      <c r="AN12" s="398" t="n"/>
+      <c r="D12" s="356" t="n"/>
+      <c r="E12" s="356" t="n"/>
+      <c r="F12" s="356" t="n"/>
+      <c r="G12" s="356" t="n"/>
+      <c r="H12" s="356" t="n"/>
+      <c r="I12" s="356" t="n"/>
+      <c r="J12" s="356" t="n"/>
+      <c r="K12" s="356" t="n"/>
+      <c r="L12" s="356" t="n"/>
+      <c r="M12" s="356" t="n"/>
+      <c r="N12" s="356" t="n"/>
+      <c r="O12" s="356" t="n"/>
+      <c r="P12" s="356" t="n"/>
+      <c r="Q12" s="356" t="n"/>
+      <c r="R12" s="356" t="n"/>
+      <c r="S12" s="356" t="n"/>
+      <c r="T12" s="356" t="n"/>
+      <c r="U12" s="356" t="n"/>
+      <c r="V12" s="356" t="n"/>
+      <c r="W12" s="356" t="n"/>
+      <c r="X12" s="356" t="n"/>
+      <c r="Y12" s="356" t="n"/>
+      <c r="Z12" s="356" t="n"/>
+      <c r="AA12" s="356" t="n"/>
+      <c r="AB12" s="356" t="n"/>
+      <c r="AC12" s="356" t="n"/>
+      <c r="AD12" s="356" t="n"/>
+      <c r="AE12" s="356" t="n"/>
+      <c r="AF12" s="356" t="n"/>
+      <c r="AG12" s="356" t="n"/>
+      <c r="AH12" s="356" t="n"/>
+      <c r="AI12" s="356" t="n"/>
+      <c r="AJ12" s="356" t="n"/>
+      <c r="AK12" s="356" t="n"/>
+      <c r="AL12" s="356" t="n"/>
+      <c r="AM12" s="356" t="n"/>
+      <c r="AN12" s="534" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="396" t="inlineStr">
+      <c r="A13" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="397" t="inlineStr">
+      <c r="B13" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="397" t="inlineStr">
+      <c r="C13" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
-      <c r="D13" s="398" t="n"/>
-      <c r="E13" s="398" t="n"/>
-      <c r="F13" s="398" t="n"/>
-      <c r="G13" s="398" t="n"/>
-      <c r="H13" s="398" t="n"/>
-      <c r="I13" s="398" t="n"/>
-      <c r="J13" s="398" t="n"/>
-      <c r="K13" s="398" t="n"/>
-      <c r="L13" s="398" t="n"/>
-      <c r="M13" s="398" t="n"/>
-      <c r="N13" s="398" t="n"/>
-      <c r="O13" s="398" t="n"/>
-      <c r="P13" s="398" t="n"/>
-      <c r="Q13" s="398" t="n"/>
-      <c r="R13" s="398" t="n"/>
-      <c r="S13" s="398" t="n"/>
-      <c r="T13" s="398" t="n"/>
-      <c r="U13" s="398" t="n"/>
-      <c r="V13" s="398" t="n"/>
-      <c r="W13" s="398" t="n"/>
-      <c r="X13" s="398" t="n"/>
-      <c r="Y13" s="398" t="n"/>
-      <c r="Z13" s="398" t="n"/>
-      <c r="AA13" s="398" t="n"/>
-      <c r="AB13" s="398" t="n"/>
-      <c r="AC13" s="398" t="n"/>
-      <c r="AD13" s="398" t="n"/>
-      <c r="AE13" s="398" t="n"/>
-      <c r="AF13" s="398" t="n"/>
-      <c r="AG13" s="398" t="n"/>
-      <c r="AH13" s="398" t="n"/>
-      <c r="AI13" s="398" t="n"/>
-      <c r="AJ13" s="398" t="n"/>
-      <c r="AK13" s="398" t="n"/>
-      <c r="AL13" s="398" t="n"/>
-      <c r="AM13" s="398" t="n"/>
-      <c r="AN13" s="398" t="n"/>
+      <c r="D13" s="356" t="n"/>
+      <c r="E13" s="356" t="n"/>
+      <c r="F13" s="356" t="n"/>
+      <c r="G13" s="356" t="n"/>
+      <c r="H13" s="356" t="n"/>
+      <c r="I13" s="356" t="n"/>
+      <c r="J13" s="356" t="n"/>
+      <c r="K13" s="356" t="n"/>
+      <c r="L13" s="356" t="n"/>
+      <c r="M13" s="356" t="n"/>
+      <c r="N13" s="356" t="n"/>
+      <c r="O13" s="356" t="n"/>
+      <c r="P13" s="356" t="n"/>
+      <c r="Q13" s="356" t="n"/>
+      <c r="R13" s="356" t="n"/>
+      <c r="S13" s="356" t="n"/>
+      <c r="T13" s="356" t="n"/>
+      <c r="U13" s="356" t="n"/>
+      <c r="V13" s="356" t="n"/>
+      <c r="W13" s="356" t="n"/>
+      <c r="X13" s="356" t="n"/>
+      <c r="Y13" s="356" t="n"/>
+      <c r="Z13" s="356" t="n"/>
+      <c r="AA13" s="356" t="n"/>
+      <c r="AB13" s="356" t="n"/>
+      <c r="AC13" s="356" t="n"/>
+      <c r="AD13" s="356" t="n"/>
+      <c r="AE13" s="356" t="n"/>
+      <c r="AF13" s="356" t="n"/>
+      <c r="AG13" s="356" t="n"/>
+      <c r="AH13" s="356" t="n"/>
+      <c r="AI13" s="356" t="n"/>
+      <c r="AJ13" s="356" t="n"/>
+      <c r="AK13" s="356" t="n"/>
+      <c r="AL13" s="356" t="n"/>
+      <c r="AM13" s="356" t="n"/>
+      <c r="AN13" s="534" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="396" t="inlineStr">
+      <c r="A14" s="531" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="397" t="inlineStr">
+      <c r="B14" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="397" t="inlineStr">
+      <c r="C14" s="533" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
-      <c r="D14" s="398" t="n"/>
-      <c r="E14" s="398" t="n"/>
-      <c r="F14" s="398" t="n"/>
-      <c r="G14" s="398" t="n"/>
-      <c r="H14" s="398" t="n"/>
-      <c r="I14" s="398" t="n"/>
-      <c r="J14" s="398" t="n"/>
-      <c r="K14" s="398" t="n"/>
-      <c r="L14" s="398" t="n"/>
-      <c r="M14" s="398" t="n"/>
-      <c r="N14" s="398" t="n"/>
-      <c r="O14" s="398" t="n"/>
-      <c r="P14" s="398" t="n"/>
-      <c r="Q14" s="398" t="n"/>
-      <c r="R14" s="398" t="n"/>
-      <c r="S14" s="398" t="n"/>
-      <c r="T14" s="398" t="n"/>
-      <c r="U14" s="398" t="n"/>
-      <c r="V14" s="398" t="n"/>
-      <c r="W14" s="398" t="n"/>
-      <c r="X14" s="398" t="n"/>
-      <c r="Y14" s="398" t="n"/>
-      <c r="Z14" s="398" t="n"/>
-      <c r="AA14" s="398" t="n"/>
-      <c r="AB14" s="398" t="n"/>
-      <c r="AC14" s="398" t="n"/>
-      <c r="AD14" s="398" t="n"/>
-      <c r="AE14" s="398" t="n"/>
-      <c r="AF14" s="398" t="n"/>
-      <c r="AG14" s="398" t="n"/>
-      <c r="AH14" s="398" t="n"/>
-      <c r="AI14" s="398" t="n"/>
-      <c r="AJ14" s="398" t="n"/>
-      <c r="AK14" s="398" t="n"/>
-      <c r="AL14" s="398" t="n"/>
-      <c r="AM14" s="398" t="n"/>
-      <c r="AN14" s="398" t="n"/>
+      <c r="D14" s="356" t="n"/>
+      <c r="E14" s="356" t="n"/>
+      <c r="F14" s="356" t="n"/>
+      <c r="G14" s="356" t="n"/>
+      <c r="H14" s="356" t="n"/>
+      <c r="I14" s="356" t="n"/>
+      <c r="J14" s="356" t="n"/>
+      <c r="K14" s="356" t="n"/>
+      <c r="L14" s="356" t="n"/>
+      <c r="M14" s="356" t="n"/>
+      <c r="N14" s="356" t="n"/>
+      <c r="O14" s="356" t="n"/>
+      <c r="P14" s="356" t="n"/>
+      <c r="Q14" s="356" t="n"/>
+      <c r="R14" s="356" t="n"/>
+      <c r="S14" s="356" t="n"/>
+      <c r="T14" s="356" t="n"/>
+      <c r="U14" s="356" t="n"/>
+      <c r="V14" s="356" t="n"/>
+      <c r="W14" s="356" t="n"/>
+      <c r="X14" s="356" t="n"/>
+      <c r="Y14" s="356" t="n"/>
+      <c r="Z14" s="356" t="n"/>
+      <c r="AA14" s="356" t="n"/>
+      <c r="AB14" s="356" t="n"/>
+      <c r="AC14" s="356" t="n"/>
+      <c r="AD14" s="356" t="n"/>
+      <c r="AE14" s="356" t="n"/>
+      <c r="AF14" s="356" t="n"/>
+      <c r="AG14" s="356" t="n"/>
+      <c r="AH14" s="356" t="n"/>
+      <c r="AI14" s="356" t="n"/>
+      <c r="AJ14" s="356" t="n"/>
+      <c r="AK14" s="356" t="n"/>
+      <c r="AL14" s="356" t="n"/>
+      <c r="AM14" s="356" t="n"/>
+      <c r="AN14" s="534" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="396" t="inlineStr">
+      <c r="A15" s="535" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="397" t="inlineStr">
+      <c r="B15" s="536" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="397" t="inlineStr">
+      <c r="C15" s="537" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
-      <c r="D15" s="398" t="n"/>
-      <c r="E15" s="398" t="n"/>
-      <c r="F15" s="398" t="n"/>
-      <c r="G15" s="398" t="n"/>
-      <c r="H15" s="398" t="n"/>
-      <c r="I15" s="398" t="n"/>
-      <c r="J15" s="398" t="n"/>
-      <c r="K15" s="398" t="n"/>
-      <c r="L15" s="398" t="n"/>
-      <c r="M15" s="398" t="n"/>
-      <c r="N15" s="398" t="n"/>
-      <c r="O15" s="398" t="n"/>
-      <c r="P15" s="398" t="n"/>
-      <c r="Q15" s="398" t="n"/>
-      <c r="R15" s="398" t="n"/>
-      <c r="S15" s="398" t="n"/>
-      <c r="T15" s="398" t="n"/>
-      <c r="U15" s="398" t="n"/>
-      <c r="V15" s="398" t="n"/>
-      <c r="W15" s="398" t="n"/>
-      <c r="X15" s="398" t="n"/>
-      <c r="Y15" s="398" t="n"/>
-      <c r="Z15" s="398" t="n"/>
-      <c r="AA15" s="398" t="n"/>
-      <c r="AB15" s="398" t="n"/>
-      <c r="AC15" s="398" t="n"/>
-      <c r="AD15" s="398" t="n"/>
-      <c r="AE15" s="398" t="n"/>
-      <c r="AF15" s="398" t="n"/>
-      <c r="AG15" s="398" t="n"/>
-      <c r="AH15" s="398" t="n"/>
-      <c r="AI15" s="398" t="n"/>
-      <c r="AJ15" s="398" t="n"/>
-      <c r="AK15" s="398" t="n"/>
-      <c r="AL15" s="398" t="n"/>
-      <c r="AM15" s="398" t="n"/>
-      <c r="AN15" s="398" t="n"/>
+      <c r="D15" s="538" t="n"/>
+      <c r="E15" s="538" t="n"/>
+      <c r="F15" s="538" t="n"/>
+      <c r="G15" s="538" t="n"/>
+      <c r="H15" s="538" t="n"/>
+      <c r="I15" s="538" t="n"/>
+      <c r="J15" s="538" t="n"/>
+      <c r="K15" s="538" t="n"/>
+      <c r="L15" s="538" t="n"/>
+      <c r="M15" s="538" t="n"/>
+      <c r="N15" s="538" t="n"/>
+      <c r="O15" s="538" t="n"/>
+      <c r="P15" s="538" t="n"/>
+      <c r="Q15" s="538" t="n"/>
+      <c r="R15" s="538" t="n"/>
+      <c r="S15" s="538" t="n"/>
+      <c r="T15" s="538" t="n"/>
+      <c r="U15" s="538" t="n"/>
+      <c r="V15" s="538" t="n"/>
+      <c r="W15" s="538" t="n"/>
+      <c r="X15" s="538" t="n"/>
+      <c r="Y15" s="538" t="n"/>
+      <c r="Z15" s="538" t="n"/>
+      <c r="AA15" s="538" t="n"/>
+      <c r="AB15" s="538" t="n"/>
+      <c r="AC15" s="538" t="n"/>
+      <c r="AD15" s="538" t="n"/>
+      <c r="AE15" s="538" t="n"/>
+      <c r="AF15" s="538" t="n"/>
+      <c r="AG15" s="538" t="n"/>
+      <c r="AH15" s="538" t="n"/>
+      <c r="AI15" s="538" t="n"/>
+      <c r="AJ15" s="538" t="n"/>
+      <c r="AK15" s="538" t="n"/>
+      <c r="AL15" s="538" t="n"/>
+      <c r="AM15" s="538" t="n"/>
+      <c r="AN15" s="539" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -9879,6 +10777,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9933,403 +10832,409 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="512" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="422" t="n"/>
-      <c r="C1" s="422" t="n"/>
-      <c r="D1" s="422" t="n"/>
-      <c r="E1" s="422" t="n"/>
-      <c r="F1" s="422" t="n"/>
-      <c r="G1" s="423" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="428" t="n"/>
+      <c r="C1" s="428" t="n"/>
+      <c r="D1" s="428" t="n"/>
+      <c r="E1" s="428" t="n"/>
+      <c r="F1" s="428" t="n"/>
+      <c r="G1" s="428" t="n"/>
+      <c r="H1" s="513" t="n"/>
+      <c r="I1" s="430" t="n"/>
+      <c r="J1" s="431" t="n"/>
+      <c r="K1" s="431" t="n"/>
+      <c r="L1" s="431" t="n"/>
+      <c r="M1" s="431" t="n"/>
+      <c r="N1" s="431" t="n"/>
+      <c r="O1" s="431" t="n"/>
+      <c r="P1" s="431" t="n"/>
+      <c r="Q1" s="431" t="n"/>
+      <c r="R1" s="431" t="n"/>
+      <c r="S1" s="431" t="n"/>
+      <c r="T1" s="431" t="n"/>
+      <c r="U1" s="431" t="n"/>
+      <c r="V1" s="431" t="n"/>
+      <c r="W1" s="431" t="n"/>
+      <c r="X1" s="431" t="n"/>
+      <c r="Y1" s="431" t="n"/>
+      <c r="Z1" s="431" t="n"/>
+      <c r="AA1" s="431" t="n"/>
+      <c r="AB1" s="431" t="n"/>
+      <c r="AC1" s="431" t="n"/>
+      <c r="AD1" s="432" t="n"/>
+      <c r="AE1" s="433" t="n"/>
+      <c r="AF1" s="434" t="n"/>
+      <c r="AG1" s="434" t="n"/>
+      <c r="AH1" s="435" t="n"/>
+      <c r="AI1" s="436" t="n"/>
+      <c r="AJ1" s="437" t="n"/>
+      <c r="AK1" s="437" t="n"/>
+      <c r="AL1" s="437" t="n"/>
+      <c r="AM1" s="437" t="n"/>
+      <c r="AN1" s="438" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="514" t="inlineStr">
         <is>
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="515" t="n"/>
+      <c r="I2" s="441" t="n"/>
+      <c r="J2" s="442" t="n"/>
+      <c r="K2" s="442" t="n"/>
+      <c r="L2" s="442" t="n"/>
+      <c r="M2" s="442" t="n"/>
+      <c r="N2" s="442" t="n"/>
+      <c r="O2" s="442" t="n"/>
+      <c r="P2" s="442" t="n"/>
+      <c r="Q2" s="442" t="n"/>
+      <c r="R2" s="442" t="n"/>
+      <c r="S2" s="442" t="n"/>
+      <c r="T2" s="442" t="n"/>
+      <c r="U2" s="442" t="n"/>
+      <c r="V2" s="442" t="n"/>
+      <c r="W2" s="442" t="n"/>
+      <c r="X2" s="442" t="n"/>
+      <c r="Y2" s="442" t="n"/>
+      <c r="Z2" s="442" t="n"/>
+      <c r="AA2" s="442" t="n"/>
+      <c r="AB2" s="442" t="n"/>
+      <c r="AC2" s="442" t="n"/>
+      <c r="AD2" s="443" t="n"/>
+      <c r="AE2" s="444" t="n"/>
+      <c r="AF2" s="445" t="n"/>
+      <c r="AG2" s="445" t="n"/>
+      <c r="AH2" s="446" t="n"/>
+      <c r="AI2" s="447" t="n"/>
+      <c r="AJ2" s="448" t="n"/>
+      <c r="AK2" s="448" t="n"/>
+      <c r="AL2" s="448" t="n"/>
+      <c r="AM2" s="448" t="n"/>
+      <c r="AN2" s="449" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="516" t="n"/>
+      <c r="B3" s="517" t="n"/>
+      <c r="C3" s="517" t="n"/>
+      <c r="D3" s="517" t="n"/>
+      <c r="E3" s="517" t="n"/>
+      <c r="F3" s="517" t="n"/>
+      <c r="G3" s="517" t="n"/>
+      <c r="H3" s="515" t="n"/>
+      <c r="I3" s="441" t="n"/>
+      <c r="J3" s="442" t="n"/>
+      <c r="K3" s="442" t="n"/>
+      <c r="L3" s="442" t="n"/>
+      <c r="M3" s="442" t="n"/>
+      <c r="N3" s="442" t="n"/>
+      <c r="O3" s="442" t="n"/>
+      <c r="P3" s="442" t="n"/>
+      <c r="Q3" s="442" t="n"/>
+      <c r="R3" s="442" t="n"/>
+      <c r="S3" s="442" t="n"/>
+      <c r="T3" s="442" t="n"/>
+      <c r="U3" s="442" t="n"/>
+      <c r="V3" s="442" t="n"/>
+      <c r="W3" s="442" t="n"/>
+      <c r="X3" s="442" t="n"/>
+      <c r="Y3" s="442" t="n"/>
+      <c r="Z3" s="442" t="n"/>
+      <c r="AA3" s="442" t="n"/>
+      <c r="AB3" s="442" t="n"/>
+      <c r="AC3" s="442" t="n"/>
+      <c r="AD3" s="443" t="n"/>
+      <c r="AE3" s="444" t="n"/>
+      <c r="AF3" s="445" t="n"/>
+      <c r="AG3" s="445" t="n"/>
+      <c r="AH3" s="446" t="n"/>
+      <c r="AI3" s="447" t="n"/>
+      <c r="AJ3" s="448" t="n"/>
+      <c r="AK3" s="448" t="n"/>
+      <c r="AL3" s="448" t="n"/>
+      <c r="AM3" s="448" t="n"/>
+      <c r="AN3" s="449" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="366" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="518" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="366" t="inlineStr">
+      <c r="B4" s="519" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="366" t="inlineStr">
+      <c r="C4" s="519" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="348" t="n"/>
-      <c r="E4" s="348" t="n"/>
-      <c r="F4" s="348" t="n"/>
-      <c r="G4" s="348" t="n"/>
-      <c r="H4" s="348" t="n"/>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="D4" s="517" t="n"/>
+      <c r="E4" s="517" t="n"/>
+      <c r="F4" s="517" t="n"/>
+      <c r="G4" s="517" t="n"/>
+      <c r="H4" s="515" t="n"/>
+      <c r="I4" s="450" t="n"/>
+      <c r="J4" s="451" t="n"/>
+      <c r="K4" s="451" t="n"/>
+      <c r="L4" s="451" t="n"/>
+      <c r="M4" s="451" t="n"/>
+      <c r="N4" s="451" t="n"/>
+      <c r="O4" s="451" t="n"/>
+      <c r="P4" s="451" t="n"/>
+      <c r="Q4" s="451" t="n"/>
+      <c r="R4" s="451" t="n"/>
+      <c r="S4" s="451" t="n"/>
+      <c r="T4" s="451" t="n"/>
+      <c r="U4" s="451" t="n"/>
+      <c r="V4" s="451" t="n"/>
+      <c r="W4" s="451" t="n"/>
+      <c r="X4" s="451" t="n"/>
+      <c r="Y4" s="451" t="n"/>
+      <c r="Z4" s="451" t="n"/>
+      <c r="AA4" s="451" t="n"/>
+      <c r="AB4" s="451" t="n"/>
+      <c r="AC4" s="451" t="n"/>
+      <c r="AD4" s="452" t="n"/>
+      <c r="AE4" s="444" t="n"/>
+      <c r="AF4" s="445" t="n"/>
+      <c r="AG4" s="445" t="n"/>
+      <c r="AH4" s="446" t="n"/>
+      <c r="AI4" s="447" t="n"/>
+      <c r="AJ4" s="448" t="n"/>
+      <c r="AK4" s="448" t="n"/>
+      <c r="AL4" s="448" t="n"/>
+      <c r="AM4" s="448" t="n"/>
+      <c r="AN4" s="449" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="394" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="521" t="inlineStr">
         <is>
           <t>Evidence item 1</t>
         </is>
       </c>
-      <c r="B5" s="395" t="inlineStr">
+      <c r="B5" s="522" t="inlineStr">
         <is>
           <t>Reference to the correct evidence folder, shared location or dossier package.</t>
         </is>
       </c>
-      <c r="C5" s="395" t="inlineStr">
+      <c r="C5" s="522" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
-      <c r="D5" s="348" t="n"/>
-      <c r="E5" s="348" t="n"/>
-      <c r="F5" s="348" t="n"/>
-      <c r="G5" s="348" t="n"/>
-      <c r="H5" s="348" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="D5" s="540" t="n"/>
+      <c r="E5" s="540" t="n"/>
+      <c r="F5" s="540" t="n"/>
+      <c r="G5" s="540" t="n"/>
+      <c r="H5" s="541" t="n"/>
+      <c r="I5" s="456" t="n"/>
+      <c r="J5" s="457" t="n"/>
+      <c r="K5" s="457" t="n"/>
+      <c r="L5" s="457" t="n"/>
+      <c r="M5" s="457" t="n"/>
+      <c r="N5" s="457" t="n"/>
+      <c r="O5" s="457" t="n"/>
+      <c r="P5" s="457" t="n"/>
+      <c r="Q5" s="457" t="n"/>
+      <c r="R5" s="457" t="n"/>
+      <c r="S5" s="457" t="n"/>
+      <c r="T5" s="457" t="n"/>
+      <c r="U5" s="457" t="n"/>
+      <c r="V5" s="457" t="n"/>
+      <c r="W5" s="457" t="n"/>
+      <c r="X5" s="457" t="n"/>
+      <c r="Y5" s="457" t="n"/>
+      <c r="Z5" s="457" t="n"/>
+      <c r="AA5" s="457" t="n"/>
+      <c r="AB5" s="457" t="n"/>
+      <c r="AC5" s="457" t="n"/>
+      <c r="AD5" s="458" t="n"/>
+      <c r="AE5" s="459" t="n"/>
+      <c r="AF5" s="460" t="n"/>
+      <c r="AG5" s="460" t="n"/>
+      <c r="AH5" s="461" t="n"/>
+      <c r="AI5" s="462" t="n"/>
+      <c r="AJ5" s="463" t="n"/>
+      <c r="AK5" s="463" t="n"/>
+      <c r="AL5" s="463" t="n"/>
+      <c r="AM5" s="463" t="n"/>
+      <c r="AN5" s="464" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="394" t="inlineStr">
+      <c r="A6" s="524" t="inlineStr">
         <is>
           <t>Evidence item 2</t>
         </is>
       </c>
-      <c r="B6" s="395" t="inlineStr">
+      <c r="B6" s="525" t="inlineStr">
         <is>
           <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
         </is>
       </c>
-      <c r="C6" s="395" t="inlineStr">
+      <c r="C6" s="526" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
-      <c r="D6" s="348" t="n"/>
-      <c r="E6" s="348" t="n"/>
-      <c r="F6" s="348" t="n"/>
-      <c r="G6" s="348" t="n"/>
-      <c r="H6" s="348" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="D6" s="470" t="n"/>
+      <c r="E6" s="470" t="n"/>
+      <c r="F6" s="470" t="n"/>
+      <c r="G6" s="470" t="n"/>
+      <c r="H6" s="470" t="n"/>
+      <c r="I6" s="470" t="n"/>
+      <c r="J6" s="470" t="n"/>
+      <c r="K6" s="470" t="n"/>
+      <c r="L6" s="470" t="n"/>
+      <c r="M6" s="470" t="n"/>
+      <c r="N6" s="470" t="n"/>
+      <c r="O6" s="470" t="n"/>
+      <c r="P6" s="470" t="n"/>
+      <c r="Q6" s="470" t="n"/>
+      <c r="R6" s="470" t="n"/>
+      <c r="S6" s="470" t="n"/>
+      <c r="T6" s="470" t="n"/>
+      <c r="U6" s="470" t="n"/>
+      <c r="V6" s="470" t="n"/>
+      <c r="W6" s="470" t="n"/>
+      <c r="X6" s="470" t="n"/>
+      <c r="Y6" s="470" t="n"/>
+      <c r="Z6" s="470" t="n"/>
+      <c r="AA6" s="470" t="n"/>
+      <c r="AB6" s="470" t="n"/>
+      <c r="AC6" s="470" t="n"/>
+      <c r="AD6" s="470" t="n"/>
+      <c r="AE6" s="470" t="n"/>
+      <c r="AF6" s="470" t="n"/>
+      <c r="AG6" s="470" t="n"/>
+      <c r="AH6" s="470" t="n"/>
+      <c r="AI6" s="470" t="n"/>
+      <c r="AJ6" s="470" t="n"/>
+      <c r="AK6" s="470" t="n"/>
+      <c r="AL6" s="470" t="n"/>
+      <c r="AM6" s="470" t="n"/>
+      <c r="AN6" s="502" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="394" t="inlineStr">
+      <c r="A7" s="527" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B7" s="395" t="inlineStr">
+      <c r="B7" s="528" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C7" s="395" t="inlineStr">
+      <c r="C7" s="529" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D7" s="348" t="n"/>
-      <c r="E7" s="348" t="n"/>
-      <c r="F7" s="348" t="n"/>
-      <c r="G7" s="348" t="n"/>
-      <c r="H7" s="348" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="D7" s="344" t="n"/>
+      <c r="E7" s="344" t="n"/>
+      <c r="F7" s="344" t="n"/>
+      <c r="G7" s="344" t="n"/>
+      <c r="H7" s="344" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="530" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="396" t="inlineStr">
+      <c r="A8" s="535" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="397" t="inlineStr">
+      <c r="B8" s="536" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="397" t="inlineStr">
+      <c r="C8" s="537" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D8" s="398" t="n"/>
-      <c r="E8" s="398" t="n"/>
-      <c r="F8" s="398" t="n"/>
-      <c r="G8" s="398" t="n"/>
-      <c r="H8" s="398" t="n"/>
-      <c r="I8" s="398" t="n"/>
-      <c r="J8" s="398" t="n"/>
-      <c r="K8" s="398" t="n"/>
-      <c r="L8" s="398" t="n"/>
-      <c r="M8" s="398" t="n"/>
-      <c r="N8" s="398" t="n"/>
-      <c r="O8" s="398" t="n"/>
-      <c r="P8" s="398" t="n"/>
-      <c r="Q8" s="398" t="n"/>
-      <c r="R8" s="398" t="n"/>
-      <c r="S8" s="398" t="n"/>
-      <c r="T8" s="398" t="n"/>
-      <c r="U8" s="398" t="n"/>
-      <c r="V8" s="398" t="n"/>
-      <c r="W8" s="398" t="n"/>
-      <c r="X8" s="398" t="n"/>
-      <c r="Y8" s="398" t="n"/>
-      <c r="Z8" s="398" t="n"/>
-      <c r="AA8" s="398" t="n"/>
-      <c r="AB8" s="398" t="n"/>
-      <c r="AC8" s="398" t="n"/>
-      <c r="AD8" s="398" t="n"/>
-      <c r="AE8" s="398" t="n"/>
-      <c r="AF8" s="398" t="n"/>
-      <c r="AG8" s="398" t="n"/>
-      <c r="AH8" s="398" t="n"/>
-      <c r="AI8" s="398" t="n"/>
-      <c r="AJ8" s="398" t="n"/>
-      <c r="AK8" s="398" t="n"/>
-      <c r="AL8" s="398" t="n"/>
-      <c r="AM8" s="398" t="n"/>
-      <c r="AN8" s="398" t="n"/>
+      <c r="D8" s="538" t="n"/>
+      <c r="E8" s="538" t="n"/>
+      <c r="F8" s="538" t="n"/>
+      <c r="G8" s="538" t="n"/>
+      <c r="H8" s="538" t="n"/>
+      <c r="I8" s="538" t="n"/>
+      <c r="J8" s="538" t="n"/>
+      <c r="K8" s="538" t="n"/>
+      <c r="L8" s="538" t="n"/>
+      <c r="M8" s="538" t="n"/>
+      <c r="N8" s="538" t="n"/>
+      <c r="O8" s="538" t="n"/>
+      <c r="P8" s="538" t="n"/>
+      <c r="Q8" s="538" t="n"/>
+      <c r="R8" s="538" t="n"/>
+      <c r="S8" s="538" t="n"/>
+      <c r="T8" s="538" t="n"/>
+      <c r="U8" s="538" t="n"/>
+      <c r="V8" s="538" t="n"/>
+      <c r="W8" s="538" t="n"/>
+      <c r="X8" s="538" t="n"/>
+      <c r="Y8" s="538" t="n"/>
+      <c r="Z8" s="538" t="n"/>
+      <c r="AA8" s="538" t="n"/>
+      <c r="AB8" s="538" t="n"/>
+      <c r="AC8" s="538" t="n"/>
+      <c r="AD8" s="538" t="n"/>
+      <c r="AE8" s="538" t="n"/>
+      <c r="AF8" s="538" t="n"/>
+      <c r="AG8" s="538" t="n"/>
+      <c r="AH8" s="538" t="n"/>
+      <c r="AI8" s="538" t="n"/>
+      <c r="AJ8" s="538" t="n"/>
+      <c r="AK8" s="538" t="n"/>
+      <c r="AL8" s="538" t="n"/>
+      <c r="AM8" s="538" t="n"/>
+      <c r="AN8" s="539" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -10340,5 +11245,6 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="84">
+  <fonts count="85">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -501,6 +501,12 @@
       <color rgb="00BBCCCC"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="52">
     <fill>
@@ -760,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="319">
+  <borders count="360">
     <border>
       <left/>
       <right/>
@@ -4162,13 +4168,484 @@
       </top>
       <bottom style="medium">
         <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="542">
+  <cellXfs count="604">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5518,6 +5995,186 @@
     </xf>
     <xf numFmtId="0" fontId="77" fillId="4" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5599,11 +6256,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>298782</colOff>
+      <row>0</row>
+      <rowOff>275446</rowOff>
     </from>
-    <ext cx="1792692" cy="517122"/>
+    <ext cx="1394316" cy="402206"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5647,6 +6304,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5677,6 +6337,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5707,6 +6370,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6082,2404 +6748,2404 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="427" t="inlineStr"/>
-      <c r="B1" s="428" t="n"/>
-      <c r="C1" s="428" t="n"/>
-      <c r="D1" s="428" t="n"/>
-      <c r="E1" s="428" t="n"/>
-      <c r="F1" s="428" t="n"/>
-      <c r="G1" s="428" t="n"/>
-      <c r="H1" s="428" t="n"/>
-      <c r="I1" s="428" t="n"/>
-      <c r="J1" s="428" t="n"/>
-      <c r="K1" s="429" t="n"/>
-      <c r="L1" s="430" t="inlineStr">
+      <c r="A1" s="542" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="543" t="inlineStr">
         <is>
           <t>AQL Inspection Record</t>
         </is>
       </c>
-      <c r="M1" s="431" t="n"/>
-      <c r="N1" s="431" t="n"/>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="431" t="n"/>
-      <c r="Q1" s="431" t="n"/>
-      <c r="R1" s="431" t="n"/>
-      <c r="S1" s="431" t="n"/>
-      <c r="T1" s="431" t="n"/>
-      <c r="U1" s="431" t="n"/>
-      <c r="V1" s="431" t="n"/>
-      <c r="W1" s="431" t="n"/>
-      <c r="X1" s="431" t="n"/>
-      <c r="Y1" s="431" t="n"/>
-      <c r="Z1" s="431" t="n"/>
-      <c r="AA1" s="431" t="n"/>
-      <c r="AB1" s="431" t="n"/>
-      <c r="AC1" s="431" t="n"/>
-      <c r="AD1" s="431" t="n"/>
-      <c r="AE1" s="431" t="n"/>
-      <c r="AF1" s="431" t="n"/>
-      <c r="AG1" s="431" t="n"/>
-      <c r="AH1" s="431" t="n"/>
-      <c r="AI1" s="431" t="n"/>
-      <c r="AJ1" s="431" t="n"/>
-      <c r="AK1" s="431" t="n"/>
-      <c r="AL1" s="431" t="n"/>
-      <c r="AM1" s="431" t="n"/>
-      <c r="AN1" s="431" t="n"/>
-      <c r="AO1" s="431" t="n"/>
-      <c r="AP1" s="432" t="n"/>
-      <c r="AQ1" s="433" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="544" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="434" t="n"/>
-      <c r="AS1" s="434" t="n"/>
-      <c r="AT1" s="434" t="n"/>
-      <c r="AU1" s="434" t="n"/>
-      <c r="AV1" s="435" t="n"/>
-      <c r="AW1" s="436" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="545" t="n"/>
+      <c r="AW1" s="546" t="inlineStr">
         <is>
           <t>FRM-621</t>
         </is>
       </c>
-      <c r="AX1" s="437" t="n"/>
-      <c r="AY1" s="437" t="n"/>
-      <c r="AZ1" s="437" t="n"/>
-      <c r="BA1" s="437" t="n"/>
-      <c r="BB1" s="437" t="n"/>
-      <c r="BC1" s="437" t="n"/>
-      <c r="BD1" s="438" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="53" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="439" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="25" t="n"/>
-      <c r="I2" s="25" t="n"/>
-      <c r="J2" s="25" t="n"/>
-      <c r="K2" s="440" t="n"/>
-      <c r="L2" s="441" t="n"/>
-      <c r="M2" s="442" t="n"/>
-      <c r="N2" s="442" t="n"/>
-      <c r="O2" s="442" t="n"/>
-      <c r="P2" s="442" t="n"/>
-      <c r="Q2" s="442" t="n"/>
-      <c r="R2" s="442" t="n"/>
-      <c r="S2" s="442" t="n"/>
-      <c r="T2" s="442" t="n"/>
-      <c r="U2" s="442" t="n"/>
-      <c r="V2" s="442" t="n"/>
-      <c r="W2" s="442" t="n"/>
-      <c r="X2" s="442" t="n"/>
-      <c r="Y2" s="442" t="n"/>
-      <c r="Z2" s="442" t="n"/>
-      <c r="AA2" s="442" t="n"/>
-      <c r="AB2" s="442" t="n"/>
-      <c r="AC2" s="442" t="n"/>
-      <c r="AD2" s="442" t="n"/>
-      <c r="AE2" s="442" t="n"/>
-      <c r="AF2" s="442" t="n"/>
-      <c r="AG2" s="442" t="n"/>
-      <c r="AH2" s="442" t="n"/>
-      <c r="AI2" s="442" t="n"/>
-      <c r="AJ2" s="442" t="n"/>
-      <c r="AK2" s="442" t="n"/>
-      <c r="AL2" s="442" t="n"/>
-      <c r="AM2" s="442" t="n"/>
-      <c r="AN2" s="442" t="n"/>
-      <c r="AO2" s="442" t="n"/>
-      <c r="AP2" s="443" t="n"/>
-      <c r="AQ2" s="444" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="10" t="n"/>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="10" t="n"/>
+      <c r="AI2" s="10" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="10" t="n"/>
+      <c r="AO2" s="10" t="n"/>
+      <c r="AP2" s="10" t="n"/>
+      <c r="AQ2" s="547" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="445" t="n"/>
-      <c r="AS2" s="445" t="n"/>
-      <c r="AT2" s="445" t="n"/>
-      <c r="AU2" s="445" t="n"/>
-      <c r="AV2" s="446" t="n"/>
-      <c r="AW2" s="447" t="inlineStr">
+      <c r="AR2" s="548" t="n"/>
+      <c r="AS2" s="548" t="n"/>
+      <c r="AT2" s="548" t="n"/>
+      <c r="AU2" s="548" t="n"/>
+      <c r="AV2" s="549" t="n"/>
+      <c r="AW2" s="550" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="448" t="n"/>
-      <c r="AY2" s="448" t="n"/>
-      <c r="AZ2" s="448" t="n"/>
-      <c r="BA2" s="448" t="n"/>
-      <c r="BB2" s="448" t="n"/>
-      <c r="BC2" s="448" t="n"/>
-      <c r="BD2" s="449" t="n"/>
+      <c r="AX2" s="548" t="n"/>
+      <c r="AY2" s="548" t="n"/>
+      <c r="AZ2" s="548" t="n"/>
+      <c r="BA2" s="548" t="n"/>
+      <c r="BB2" s="548" t="n"/>
+      <c r="BC2" s="548" t="n"/>
+      <c r="BD2" s="551" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="439" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="440" t="n"/>
-      <c r="L3" s="441" t="n"/>
-      <c r="M3" s="442" t="n"/>
-      <c r="N3" s="442" t="n"/>
-      <c r="O3" s="442" t="n"/>
-      <c r="P3" s="442" t="n"/>
-      <c r="Q3" s="442" t="n"/>
-      <c r="R3" s="442" t="n"/>
-      <c r="S3" s="442" t="n"/>
-      <c r="T3" s="442" t="n"/>
-      <c r="U3" s="442" t="n"/>
-      <c r="V3" s="442" t="n"/>
-      <c r="W3" s="442" t="n"/>
-      <c r="X3" s="442" t="n"/>
-      <c r="Y3" s="442" t="n"/>
-      <c r="Z3" s="442" t="n"/>
-      <c r="AA3" s="442" t="n"/>
-      <c r="AB3" s="442" t="n"/>
-      <c r="AC3" s="442" t="n"/>
-      <c r="AD3" s="442" t="n"/>
-      <c r="AE3" s="442" t="n"/>
-      <c r="AF3" s="442" t="n"/>
-      <c r="AG3" s="442" t="n"/>
-      <c r="AH3" s="442" t="n"/>
-      <c r="AI3" s="442" t="n"/>
-      <c r="AJ3" s="442" t="n"/>
-      <c r="AK3" s="442" t="n"/>
-      <c r="AL3" s="442" t="n"/>
-      <c r="AM3" s="442" t="n"/>
-      <c r="AN3" s="442" t="n"/>
-      <c r="AO3" s="442" t="n"/>
-      <c r="AP3" s="443" t="n"/>
-      <c r="AQ3" s="444" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
+      <c r="AI3" s="10" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="10" t="n"/>
+      <c r="AO3" s="10" t="n"/>
+      <c r="AP3" s="10" t="n"/>
+      <c r="AQ3" s="547" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="445" t="n"/>
-      <c r="AS3" s="445" t="n"/>
-      <c r="AT3" s="445" t="n"/>
-      <c r="AU3" s="445" t="n"/>
-      <c r="AV3" s="446" t="n"/>
-      <c r="AW3" s="447" t="inlineStr">
+      <c r="AR3" s="548" t="n"/>
+      <c r="AS3" s="548" t="n"/>
+      <c r="AT3" s="548" t="n"/>
+      <c r="AU3" s="548" t="n"/>
+      <c r="AV3" s="549" t="n"/>
+      <c r="AW3" s="550" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="448" t="n"/>
-      <c r="AY3" s="448" t="n"/>
-      <c r="AZ3" s="448" t="n"/>
-      <c r="BA3" s="448" t="n"/>
-      <c r="BB3" s="448" t="n"/>
-      <c r="BC3" s="448" t="n"/>
-      <c r="BD3" s="449" t="n"/>
+      <c r="AX3" s="548" t="n"/>
+      <c r="AY3" s="548" t="n"/>
+      <c r="AZ3" s="548" t="n"/>
+      <c r="BA3" s="548" t="n"/>
+      <c r="BB3" s="548" t="n"/>
+      <c r="BC3" s="548" t="n"/>
+      <c r="BD3" s="551" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="439" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="440" t="n"/>
-      <c r="L4" s="450" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="552" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="451" t="n"/>
-      <c r="N4" s="451" t="n"/>
-      <c r="O4" s="451" t="n"/>
-      <c r="P4" s="451" t="n"/>
-      <c r="Q4" s="451" t="n"/>
-      <c r="R4" s="451" t="n"/>
-      <c r="S4" s="451" t="n"/>
-      <c r="T4" s="451" t="n"/>
-      <c r="U4" s="451" t="n"/>
-      <c r="V4" s="451" t="n"/>
-      <c r="W4" s="451" t="n"/>
-      <c r="X4" s="451" t="n"/>
-      <c r="Y4" s="451" t="n"/>
-      <c r="Z4" s="451" t="n"/>
-      <c r="AA4" s="451" t="n"/>
-      <c r="AB4" s="451" t="n"/>
-      <c r="AC4" s="451" t="n"/>
-      <c r="AD4" s="451" t="n"/>
-      <c r="AE4" s="451" t="n"/>
-      <c r="AF4" s="451" t="n"/>
-      <c r="AG4" s="451" t="n"/>
-      <c r="AH4" s="451" t="n"/>
-      <c r="AI4" s="451" t="n"/>
-      <c r="AJ4" s="451" t="n"/>
-      <c r="AK4" s="451" t="n"/>
-      <c r="AL4" s="451" t="n"/>
-      <c r="AM4" s="451" t="n"/>
-      <c r="AN4" s="451" t="n"/>
-      <c r="AO4" s="451" t="n"/>
-      <c r="AP4" s="452" t="n"/>
-      <c r="AQ4" s="444" t="inlineStr">
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="10" t="n"/>
+      <c r="AI4" s="10" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="10" t="n"/>
+      <c r="AO4" s="10" t="n"/>
+      <c r="AP4" s="10" t="n"/>
+      <c r="AQ4" s="547" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="445" t="n"/>
-      <c r="AS4" s="445" t="n"/>
-      <c r="AT4" s="445" t="n"/>
-      <c r="AU4" s="445" t="n"/>
-      <c r="AV4" s="446" t="n"/>
-      <c r="AW4" s="447" t="inlineStr">
+      <c r="AR4" s="548" t="n"/>
+      <c r="AS4" s="548" t="n"/>
+      <c r="AT4" s="548" t="n"/>
+      <c r="AU4" s="548" t="n"/>
+      <c r="AV4" s="549" t="n"/>
+      <c r="AW4" s="550" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="448" t="n"/>
-      <c r="AY4" s="448" t="n"/>
-      <c r="AZ4" s="448" t="n"/>
-      <c r="BA4" s="448" t="n"/>
-      <c r="BB4" s="448" t="n"/>
-      <c r="BC4" s="448" t="n"/>
-      <c r="BD4" s="449" t="n"/>
+      <c r="AX4" s="548" t="n"/>
+      <c r="AY4" s="548" t="n"/>
+      <c r="AZ4" s="548" t="n"/>
+      <c r="BA4" s="548" t="n"/>
+      <c r="BB4" s="548" t="n"/>
+      <c r="BC4" s="548" t="n"/>
+      <c r="BD4" s="551" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="453" t="n"/>
-      <c r="B5" s="454" t="n"/>
-      <c r="C5" s="454" t="n"/>
-      <c r="D5" s="454" t="n"/>
-      <c r="E5" s="454" t="n"/>
-      <c r="F5" s="454" t="n"/>
-      <c r="G5" s="454" t="n"/>
-      <c r="H5" s="454" t="n"/>
-      <c r="I5" s="454" t="n"/>
-      <c r="J5" s="454" t="n"/>
-      <c r="K5" s="455" t="n"/>
-      <c r="L5" s="456" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="457" t="n"/>
-      <c r="N5" s="457" t="n"/>
-      <c r="O5" s="457" t="n"/>
-      <c r="P5" s="457" t="n"/>
-      <c r="Q5" s="457" t="n"/>
-      <c r="R5" s="457" t="n"/>
-      <c r="S5" s="457" t="n"/>
-      <c r="T5" s="457" t="n"/>
-      <c r="U5" s="457" t="n"/>
-      <c r="V5" s="457" t="n"/>
-      <c r="W5" s="457" t="n"/>
-      <c r="X5" s="457" t="n"/>
-      <c r="Y5" s="457" t="n"/>
-      <c r="Z5" s="457" t="n"/>
-      <c r="AA5" s="457" t="n"/>
-      <c r="AB5" s="457" t="n"/>
-      <c r="AC5" s="457" t="n"/>
-      <c r="AD5" s="457" t="n"/>
-      <c r="AE5" s="457" t="n"/>
-      <c r="AF5" s="457" t="n"/>
-      <c r="AG5" s="457" t="n"/>
-      <c r="AH5" s="457" t="n"/>
-      <c r="AI5" s="457" t="n"/>
-      <c r="AJ5" s="457" t="n"/>
-      <c r="AK5" s="457" t="n"/>
-      <c r="AL5" s="457" t="n"/>
-      <c r="AM5" s="457" t="n"/>
-      <c r="AN5" s="457" t="n"/>
-      <c r="AO5" s="457" t="n"/>
-      <c r="AP5" s="458" t="n"/>
-      <c r="AQ5" s="459" t="inlineStr">
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="19" t="n"/>
+      <c r="AF5" s="19" t="n"/>
+      <c r="AG5" s="19" t="n"/>
+      <c r="AH5" s="19" t="n"/>
+      <c r="AI5" s="19" t="n"/>
+      <c r="AJ5" s="19" t="n"/>
+      <c r="AK5" s="19" t="n"/>
+      <c r="AL5" s="19" t="n"/>
+      <c r="AM5" s="19" t="n"/>
+      <c r="AN5" s="19" t="n"/>
+      <c r="AO5" s="19" t="n"/>
+      <c r="AP5" s="19" t="n"/>
+      <c r="AQ5" s="553" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="460" t="n"/>
-      <c r="AS5" s="460" t="n"/>
-      <c r="AT5" s="460" t="n"/>
-      <c r="AU5" s="460" t="n"/>
-      <c r="AV5" s="461" t="n"/>
-      <c r="AW5" s="462" t="inlineStr">
+      <c r="AR5" s="554" t="n"/>
+      <c r="AS5" s="554" t="n"/>
+      <c r="AT5" s="554" t="n"/>
+      <c r="AU5" s="554" t="n"/>
+      <c r="AV5" s="555" t="n"/>
+      <c r="AW5" s="556" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="463" t="n"/>
-      <c r="AY5" s="463" t="n"/>
-      <c r="AZ5" s="463" t="n"/>
-      <c r="BA5" s="463" t="n"/>
-      <c r="BB5" s="463" t="n"/>
-      <c r="BC5" s="463" t="n"/>
-      <c r="BD5" s="464" t="n"/>
+      <c r="AX5" s="554" t="n"/>
+      <c r="AY5" s="554" t="n"/>
+      <c r="AZ5" s="554" t="n"/>
+      <c r="BA5" s="554" t="n"/>
+      <c r="BB5" s="554" t="n"/>
+      <c r="BC5" s="554" t="n"/>
+      <c r="BD5" s="557" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="465" t="n"/>
-      <c r="B6" s="465" t="n"/>
-      <c r="C6" s="465" t="n"/>
-      <c r="D6" s="465" t="n"/>
-      <c r="E6" s="465" t="n"/>
-      <c r="F6" s="465" t="n"/>
-      <c r="G6" s="465" t="n"/>
-      <c r="H6" s="465" t="n"/>
-      <c r="I6" s="465" t="n"/>
-      <c r="J6" s="465" t="n"/>
-      <c r="K6" s="465" t="n"/>
-      <c r="L6" s="465" t="n"/>
-      <c r="M6" s="465" t="n"/>
-      <c r="N6" s="465" t="n"/>
-      <c r="O6" s="465" t="n"/>
-      <c r="P6" s="465" t="n"/>
-      <c r="Q6" s="465" t="n"/>
-      <c r="R6" s="465" t="n"/>
-      <c r="S6" s="465" t="n"/>
-      <c r="T6" s="465" t="n"/>
-      <c r="U6" s="465" t="n"/>
-      <c r="V6" s="465" t="n"/>
-      <c r="W6" s="465" t="n"/>
-      <c r="X6" s="465" t="n"/>
-      <c r="Y6" s="465" t="n"/>
-      <c r="Z6" s="465" t="n"/>
-      <c r="AA6" s="465" t="n"/>
-      <c r="AB6" s="465" t="n"/>
-      <c r="AC6" s="465" t="n"/>
-      <c r="AD6" s="465" t="n"/>
-      <c r="AE6" s="465" t="n"/>
-      <c r="AF6" s="465" t="n"/>
-      <c r="AG6" s="465" t="n"/>
-      <c r="AH6" s="465" t="n"/>
-      <c r="AI6" s="465" t="n"/>
-      <c r="AJ6" s="465" t="n"/>
-      <c r="AK6" s="465" t="n"/>
-      <c r="AL6" s="465" t="n"/>
-      <c r="AM6" s="465" t="n"/>
-      <c r="AN6" s="465" t="n"/>
-      <c r="AO6" s="465" t="n"/>
-      <c r="AP6" s="465" t="n"/>
-      <c r="AQ6" s="465" t="n"/>
-      <c r="AR6" s="465" t="n"/>
-      <c r="AS6" s="465" t="n"/>
-      <c r="AT6" s="465" t="n"/>
-      <c r="AU6" s="465" t="n"/>
-      <c r="AV6" s="465" t="n"/>
-      <c r="AW6" s="465" t="n"/>
-      <c r="AX6" s="465" t="n"/>
-      <c r="AY6" s="465" t="n"/>
-      <c r="AZ6" s="465" t="n"/>
-      <c r="BA6" s="465" t="n"/>
-      <c r="BB6" s="465" t="n"/>
-      <c r="BC6" s="465" t="n"/>
-      <c r="BD6" s="465" t="n"/>
+      <c r="A6" s="517" t="n"/>
+      <c r="B6" s="517" t="n"/>
+      <c r="C6" s="517" t="n"/>
+      <c r="D6" s="517" t="n"/>
+      <c r="E6" s="517" t="n"/>
+      <c r="F6" s="517" t="n"/>
+      <c r="G6" s="517" t="n"/>
+      <c r="H6" s="517" t="n"/>
+      <c r="I6" s="517" t="n"/>
+      <c r="J6" s="517" t="n"/>
+      <c r="K6" s="517" t="n"/>
+      <c r="L6" s="517" t="n"/>
+      <c r="M6" s="517" t="n"/>
+      <c r="N6" s="517" t="n"/>
+      <c r="O6" s="517" t="n"/>
+      <c r="P6" s="517" t="n"/>
+      <c r="Q6" s="517" t="n"/>
+      <c r="R6" s="517" t="n"/>
+      <c r="S6" s="517" t="n"/>
+      <c r="T6" s="517" t="n"/>
+      <c r="U6" s="517" t="n"/>
+      <c r="V6" s="517" t="n"/>
+      <c r="W6" s="517" t="n"/>
+      <c r="X6" s="517" t="n"/>
+      <c r="Y6" s="517" t="n"/>
+      <c r="Z6" s="517" t="n"/>
+      <c r="AA6" s="517" t="n"/>
+      <c r="AB6" s="517" t="n"/>
+      <c r="AC6" s="517" t="n"/>
+      <c r="AD6" s="517" t="n"/>
+      <c r="AE6" s="517" t="n"/>
+      <c r="AF6" s="517" t="n"/>
+      <c r="AG6" s="517" t="n"/>
+      <c r="AH6" s="517" t="n"/>
+      <c r="AI6" s="517" t="n"/>
+      <c r="AJ6" s="517" t="n"/>
+      <c r="AK6" s="517" t="n"/>
+      <c r="AL6" s="517" t="n"/>
+      <c r="AM6" s="517" t="n"/>
+      <c r="AN6" s="517" t="n"/>
+      <c r="AO6" s="517" t="n"/>
+      <c r="AP6" s="517" t="n"/>
+      <c r="AQ6" s="517" t="n"/>
+      <c r="AR6" s="517" t="n"/>
+      <c r="AS6" s="517" t="n"/>
+      <c r="AT6" s="517" t="n"/>
+      <c r="AU6" s="517" t="n"/>
+      <c r="AV6" s="517" t="n"/>
+      <c r="AW6" s="517" t="n"/>
+      <c r="AX6" s="517" t="n"/>
+      <c r="AY6" s="517" t="n"/>
+      <c r="AZ6" s="517" t="n"/>
+      <c r="BA6" s="517" t="n"/>
+      <c r="BB6" s="517" t="n"/>
+      <c r="BC6" s="517" t="n"/>
+      <c r="BD6" s="517" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="466" t="inlineStr">
+      <c r="A7" s="558" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="467" t="n"/>
-      <c r="C7" s="467" t="n"/>
-      <c r="D7" s="467" t="n"/>
-      <c r="E7" s="467" t="n"/>
-      <c r="F7" s="467" t="n"/>
-      <c r="G7" s="467" t="n"/>
-      <c r="H7" s="467" t="n"/>
-      <c r="I7" s="467" t="n"/>
-      <c r="J7" s="467" t="n"/>
-      <c r="K7" s="467" t="n"/>
-      <c r="L7" s="467" t="n"/>
-      <c r="M7" s="467" t="n"/>
-      <c r="N7" s="467" t="n"/>
-      <c r="O7" s="467" t="n"/>
-      <c r="P7" s="467" t="n"/>
-      <c r="Q7" s="467" t="n"/>
-      <c r="R7" s="467" t="n"/>
-      <c r="S7" s="467" t="n"/>
-      <c r="T7" s="467" t="n"/>
-      <c r="U7" s="467" t="n"/>
-      <c r="V7" s="467" t="n"/>
-      <c r="W7" s="467" t="n"/>
-      <c r="X7" s="467" t="n"/>
-      <c r="Y7" s="467" t="n"/>
-      <c r="Z7" s="467" t="n"/>
-      <c r="AA7" s="467" t="n"/>
-      <c r="AB7" s="467" t="n"/>
-      <c r="AC7" s="467" t="n"/>
-      <c r="AD7" s="467" t="n"/>
-      <c r="AE7" s="467" t="n"/>
-      <c r="AF7" s="467" t="n"/>
-      <c r="AG7" s="467" t="n"/>
-      <c r="AH7" s="467" t="n"/>
-      <c r="AI7" s="467" t="n"/>
-      <c r="AJ7" s="467" t="n"/>
-      <c r="AK7" s="467" t="n"/>
-      <c r="AL7" s="467" t="n"/>
-      <c r="AM7" s="467" t="n"/>
-      <c r="AN7" s="467" t="n"/>
-      <c r="AO7" s="467" t="n"/>
-      <c r="AP7" s="467" t="n"/>
-      <c r="AQ7" s="467" t="n"/>
-      <c r="AR7" s="467" t="n"/>
-      <c r="AS7" s="467" t="n"/>
-      <c r="AT7" s="467" t="n"/>
-      <c r="AU7" s="467" t="n"/>
-      <c r="AV7" s="467" t="n"/>
-      <c r="AW7" s="467" t="n"/>
-      <c r="AX7" s="467" t="n"/>
-      <c r="AY7" s="467" t="n"/>
-      <c r="AZ7" s="467" t="n"/>
-      <c r="BA7" s="467" t="n"/>
-      <c r="BB7" s="467" t="n"/>
-      <c r="BC7" s="467" t="n"/>
-      <c r="BD7" s="468" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="27" t="n"/>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n"/>
+      <c r="AU7" s="27" t="n"/>
+      <c r="AV7" s="27" t="n"/>
+      <c r="AW7" s="27" t="n"/>
+      <c r="AX7" s="27" t="n"/>
+      <c r="AY7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="27" t="n"/>
+      <c r="BB7" s="27" t="n"/>
+      <c r="BC7" s="27" t="n"/>
+      <c r="BD7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="469" t="inlineStr">
+      <c r="A8" s="559" t="inlineStr">
         <is>
           <t>Customer / PO Line</t>
         </is>
       </c>
-      <c r="B8" s="470" t="n"/>
-      <c r="C8" s="470" t="n"/>
-      <c r="D8" s="470" t="n"/>
-      <c r="E8" s="470" t="n"/>
-      <c r="F8" s="470" t="n"/>
-      <c r="G8" s="470" t="n"/>
-      <c r="H8" s="470" t="n"/>
-      <c r="I8" s="470" t="n"/>
-      <c r="J8" s="470" t="n"/>
-      <c r="K8" s="471" t="n"/>
-      <c r="L8" s="472" t="n"/>
-      <c r="M8" s="472" t="n"/>
-      <c r="N8" s="472" t="n"/>
-      <c r="O8" s="472" t="n"/>
-      <c r="P8" s="472" t="n"/>
-      <c r="Q8" s="472" t="n"/>
-      <c r="R8" s="472" t="n"/>
-      <c r="S8" s="472" t="n"/>
-      <c r="T8" s="472" t="n"/>
-      <c r="U8" s="472" t="n"/>
-      <c r="V8" s="472" t="n"/>
-      <c r="W8" s="472" t="n"/>
-      <c r="X8" s="472" t="n"/>
-      <c r="Y8" s="472" t="n"/>
-      <c r="Z8" s="472" t="n"/>
-      <c r="AA8" s="472" t="n"/>
-      <c r="AB8" s="472" t="n"/>
-      <c r="AC8" s="473" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="560" t="n"/>
+      <c r="L8" s="561" t="n"/>
+      <c r="M8" s="561" t="n"/>
+      <c r="N8" s="561" t="n"/>
+      <c r="O8" s="561" t="n"/>
+      <c r="P8" s="561" t="n"/>
+      <c r="Q8" s="561" t="n"/>
+      <c r="R8" s="561" t="n"/>
+      <c r="S8" s="561" t="n"/>
+      <c r="T8" s="561" t="n"/>
+      <c r="U8" s="561" t="n"/>
+      <c r="V8" s="561" t="n"/>
+      <c r="W8" s="561" t="n"/>
+      <c r="X8" s="561" t="n"/>
+      <c r="Y8" s="561" t="n"/>
+      <c r="Z8" s="561" t="n"/>
+      <c r="AA8" s="561" t="n"/>
+      <c r="AB8" s="562" t="n"/>
+      <c r="AC8" s="563" t="inlineStr">
         <is>
           <t>Inspection Record ID</t>
         </is>
       </c>
-      <c r="AD8" s="470" t="n"/>
-      <c r="AE8" s="470" t="n"/>
-      <c r="AF8" s="470" t="n"/>
-      <c r="AG8" s="470" t="n"/>
-      <c r="AH8" s="470" t="n"/>
-      <c r="AI8" s="470" t="n"/>
-      <c r="AJ8" s="470" t="n"/>
-      <c r="AK8" s="470" t="n"/>
-      <c r="AL8" s="470" t="n"/>
-      <c r="AM8" s="471" t="n"/>
-      <c r="AN8" s="472" t="n"/>
-      <c r="AO8" s="472" t="n"/>
-      <c r="AP8" s="472" t="n"/>
-      <c r="AQ8" s="472" t="n"/>
-      <c r="AR8" s="472" t="n"/>
-      <c r="AS8" s="472" t="n"/>
-      <c r="AT8" s="472" t="n"/>
-      <c r="AU8" s="472" t="n"/>
-      <c r="AV8" s="472" t="n"/>
-      <c r="AW8" s="472" t="n"/>
-      <c r="AX8" s="472" t="n"/>
-      <c r="AY8" s="472" t="n"/>
-      <c r="AZ8" s="472" t="n"/>
-      <c r="BA8" s="472" t="n"/>
-      <c r="BB8" s="472" t="n"/>
-      <c r="BC8" s="472" t="n"/>
-      <c r="BD8" s="474" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="6" t="n"/>
+      <c r="AM8" s="560" t="n"/>
+      <c r="AN8" s="561" t="n"/>
+      <c r="AO8" s="561" t="n"/>
+      <c r="AP8" s="561" t="n"/>
+      <c r="AQ8" s="561" t="n"/>
+      <c r="AR8" s="561" t="n"/>
+      <c r="AS8" s="561" t="n"/>
+      <c r="AT8" s="561" t="n"/>
+      <c r="AU8" s="561" t="n"/>
+      <c r="AV8" s="561" t="n"/>
+      <c r="AW8" s="561" t="n"/>
+      <c r="AX8" s="561" t="n"/>
+      <c r="AY8" s="561" t="n"/>
+      <c r="AZ8" s="561" t="n"/>
+      <c r="BA8" s="561" t="n"/>
+      <c r="BB8" s="561" t="n"/>
+      <c r="BC8" s="561" t="n"/>
+      <c r="BD8" s="564" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="475" t="inlineStr">
+      <c r="A9" s="565" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B9" s="344" t="n"/>
-      <c r="C9" s="344" t="n"/>
-      <c r="D9" s="344" t="n"/>
-      <c r="E9" s="344" t="n"/>
-      <c r="F9" s="344" t="n"/>
-      <c r="G9" s="344" t="n"/>
-      <c r="H9" s="344" t="n"/>
-      <c r="I9" s="344" t="n"/>
-      <c r="J9" s="344" t="n"/>
-      <c r="K9" s="476" t="n"/>
-      <c r="L9" s="362" t="n"/>
-      <c r="M9" s="362" t="n"/>
-      <c r="N9" s="362" t="n"/>
-      <c r="O9" s="362" t="n"/>
-      <c r="P9" s="362" t="n"/>
-      <c r="Q9" s="362" t="n"/>
-      <c r="R9" s="362" t="n"/>
-      <c r="S9" s="362" t="n"/>
-      <c r="T9" s="362" t="n"/>
-      <c r="U9" s="362" t="n"/>
-      <c r="V9" s="362" t="n"/>
-      <c r="W9" s="362" t="n"/>
-      <c r="X9" s="362" t="n"/>
-      <c r="Y9" s="362" t="n"/>
-      <c r="Z9" s="362" t="n"/>
-      <c r="AA9" s="362" t="n"/>
-      <c r="AB9" s="362" t="n"/>
-      <c r="AC9" s="477" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="566" t="n"/>
+      <c r="L9" s="567" t="n"/>
+      <c r="M9" s="567" t="n"/>
+      <c r="N9" s="567" t="n"/>
+      <c r="O9" s="567" t="n"/>
+      <c r="P9" s="567" t="n"/>
+      <c r="Q9" s="567" t="n"/>
+      <c r="R9" s="567" t="n"/>
+      <c r="S9" s="567" t="n"/>
+      <c r="T9" s="567" t="n"/>
+      <c r="U9" s="567" t="n"/>
+      <c r="V9" s="567" t="n"/>
+      <c r="W9" s="567" t="n"/>
+      <c r="X9" s="567" t="n"/>
+      <c r="Y9" s="567" t="n"/>
+      <c r="Z9" s="567" t="n"/>
+      <c r="AA9" s="567" t="n"/>
+      <c r="AB9" s="568" t="n"/>
+      <c r="AC9" s="569" t="inlineStr">
         <is>
           <t>Job / Lot / Serial</t>
         </is>
       </c>
-      <c r="AD9" s="344" t="n"/>
-      <c r="AE9" s="344" t="n"/>
-      <c r="AF9" s="344" t="n"/>
-      <c r="AG9" s="344" t="n"/>
-      <c r="AH9" s="344" t="n"/>
-      <c r="AI9" s="344" t="n"/>
-      <c r="AJ9" s="344" t="n"/>
-      <c r="AK9" s="344" t="n"/>
-      <c r="AL9" s="344" t="n"/>
-      <c r="AM9" s="476" t="n"/>
-      <c r="AN9" s="362" t="n"/>
-      <c r="AO9" s="362" t="n"/>
-      <c r="AP9" s="362" t="n"/>
-      <c r="AQ9" s="362" t="n"/>
-      <c r="AR9" s="362" t="n"/>
-      <c r="AS9" s="362" t="n"/>
-      <c r="AT9" s="362" t="n"/>
-      <c r="AU9" s="362" t="n"/>
-      <c r="AV9" s="362" t="n"/>
-      <c r="AW9" s="362" t="n"/>
-      <c r="AX9" s="362" t="n"/>
-      <c r="AY9" s="362" t="n"/>
-      <c r="AZ9" s="362" t="n"/>
-      <c r="BA9" s="362" t="n"/>
-      <c r="BB9" s="362" t="n"/>
-      <c r="BC9" s="362" t="n"/>
-      <c r="BD9" s="478" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n"/>
+      <c r="AK9" s="12" t="n"/>
+      <c r="AL9" s="13" t="n"/>
+      <c r="AM9" s="566" t="n"/>
+      <c r="AN9" s="567" t="n"/>
+      <c r="AO9" s="567" t="n"/>
+      <c r="AP9" s="567" t="n"/>
+      <c r="AQ9" s="567" t="n"/>
+      <c r="AR9" s="567" t="n"/>
+      <c r="AS9" s="567" t="n"/>
+      <c r="AT9" s="567" t="n"/>
+      <c r="AU9" s="567" t="n"/>
+      <c r="AV9" s="567" t="n"/>
+      <c r="AW9" s="567" t="n"/>
+      <c r="AX9" s="567" t="n"/>
+      <c r="AY9" s="567" t="n"/>
+      <c r="AZ9" s="567" t="n"/>
+      <c r="BA9" s="567" t="n"/>
+      <c r="BB9" s="567" t="n"/>
+      <c r="BC9" s="567" t="n"/>
+      <c r="BD9" s="570" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="475" t="inlineStr">
+      <c r="A10" s="565" t="inlineStr">
         <is>
           <t>Lot Qty</t>
         </is>
       </c>
-      <c r="B10" s="344" t="n"/>
-      <c r="C10" s="344" t="n"/>
-      <c r="D10" s="344" t="n"/>
-      <c r="E10" s="344" t="n"/>
-      <c r="F10" s="344" t="n"/>
-      <c r="G10" s="344" t="n"/>
-      <c r="H10" s="344" t="n"/>
-      <c r="I10" s="344" t="n"/>
-      <c r="J10" s="344" t="n"/>
-      <c r="K10" s="476" t="n"/>
-      <c r="L10" s="362" t="n"/>
-      <c r="M10" s="362" t="n"/>
-      <c r="N10" s="362" t="n"/>
-      <c r="O10" s="362" t="n"/>
-      <c r="P10" s="362" t="n"/>
-      <c r="Q10" s="362" t="n"/>
-      <c r="R10" s="362" t="n"/>
-      <c r="S10" s="362" t="n"/>
-      <c r="T10" s="362" t="n"/>
-      <c r="U10" s="362" t="n"/>
-      <c r="V10" s="362" t="n"/>
-      <c r="W10" s="362" t="n"/>
-      <c r="X10" s="362" t="n"/>
-      <c r="Y10" s="362" t="n"/>
-      <c r="Z10" s="362" t="n"/>
-      <c r="AA10" s="362" t="n"/>
-      <c r="AB10" s="362" t="n"/>
-      <c r="AC10" s="477" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="566" t="n"/>
+      <c r="L10" s="567" t="n"/>
+      <c r="M10" s="567" t="n"/>
+      <c r="N10" s="567" t="n"/>
+      <c r="O10" s="567" t="n"/>
+      <c r="P10" s="567" t="n"/>
+      <c r="Q10" s="567" t="n"/>
+      <c r="R10" s="567" t="n"/>
+      <c r="S10" s="567" t="n"/>
+      <c r="T10" s="567" t="n"/>
+      <c r="U10" s="567" t="n"/>
+      <c r="V10" s="567" t="n"/>
+      <c r="W10" s="567" t="n"/>
+      <c r="X10" s="567" t="n"/>
+      <c r="Y10" s="567" t="n"/>
+      <c r="Z10" s="567" t="n"/>
+      <c r="AA10" s="567" t="n"/>
+      <c r="AB10" s="568" t="n"/>
+      <c r="AC10" s="569" t="inlineStr">
         <is>
           <t>Characteristic Class</t>
         </is>
       </c>
-      <c r="AD10" s="344" t="n"/>
-      <c r="AE10" s="344" t="n"/>
-      <c r="AF10" s="344" t="n"/>
-      <c r="AG10" s="344" t="n"/>
-      <c r="AH10" s="344" t="n"/>
-      <c r="AI10" s="344" t="n"/>
-      <c r="AJ10" s="344" t="n"/>
-      <c r="AK10" s="344" t="n"/>
-      <c r="AL10" s="344" t="n"/>
-      <c r="AM10" s="476" t="n"/>
-      <c r="AN10" s="362" t="n"/>
-      <c r="AO10" s="362" t="n"/>
-      <c r="AP10" s="362" t="n"/>
-      <c r="AQ10" s="362" t="n"/>
-      <c r="AR10" s="362" t="n"/>
-      <c r="AS10" s="362" t="n"/>
-      <c r="AT10" s="362" t="n"/>
-      <c r="AU10" s="362" t="n"/>
-      <c r="AV10" s="362" t="n"/>
-      <c r="AW10" s="362" t="n"/>
-      <c r="AX10" s="362" t="n"/>
-      <c r="AY10" s="362" t="n"/>
-      <c r="AZ10" s="362" t="n"/>
-      <c r="BA10" s="362" t="n"/>
-      <c r="BB10" s="362" t="n"/>
-      <c r="BC10" s="362" t="n"/>
-      <c r="BD10" s="478" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="566" t="n"/>
+      <c r="AN10" s="567" t="n"/>
+      <c r="AO10" s="567" t="n"/>
+      <c r="AP10" s="567" t="n"/>
+      <c r="AQ10" s="567" t="n"/>
+      <c r="AR10" s="567" t="n"/>
+      <c r="AS10" s="567" t="n"/>
+      <c r="AT10" s="567" t="n"/>
+      <c r="AU10" s="567" t="n"/>
+      <c r="AV10" s="567" t="n"/>
+      <c r="AW10" s="567" t="n"/>
+      <c r="AX10" s="567" t="n"/>
+      <c r="AY10" s="567" t="n"/>
+      <c r="AZ10" s="567" t="n"/>
+      <c r="BA10" s="567" t="n"/>
+      <c r="BB10" s="567" t="n"/>
+      <c r="BC10" s="567" t="n"/>
+      <c r="BD10" s="570" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="475" t="inlineStr">
+      <c r="A11" s="565" t="inlineStr">
         <is>
           <t>AQL</t>
         </is>
       </c>
-      <c r="B11" s="344" t="n"/>
-      <c r="C11" s="344" t="n"/>
-      <c r="D11" s="344" t="n"/>
-      <c r="E11" s="344" t="n"/>
-      <c r="F11" s="344" t="n"/>
-      <c r="G11" s="344" t="n"/>
-      <c r="H11" s="344" t="n"/>
-      <c r="I11" s="344" t="n"/>
-      <c r="J11" s="344" t="n"/>
-      <c r="K11" s="476" t="n"/>
-      <c r="L11" s="362" t="n"/>
-      <c r="M11" s="362" t="n"/>
-      <c r="N11" s="362" t="n"/>
-      <c r="O11" s="362" t="n"/>
-      <c r="P11" s="362" t="n"/>
-      <c r="Q11" s="362" t="n"/>
-      <c r="R11" s="362" t="n"/>
-      <c r="S11" s="362" t="n"/>
-      <c r="T11" s="362" t="n"/>
-      <c r="U11" s="362" t="n"/>
-      <c r="V11" s="362" t="n"/>
-      <c r="W11" s="362" t="n"/>
-      <c r="X11" s="362" t="n"/>
-      <c r="Y11" s="362" t="n"/>
-      <c r="Z11" s="362" t="n"/>
-      <c r="AA11" s="362" t="n"/>
-      <c r="AB11" s="362" t="n"/>
-      <c r="AC11" s="477" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="566" t="n"/>
+      <c r="L11" s="567" t="n"/>
+      <c r="M11" s="567" t="n"/>
+      <c r="N11" s="567" t="n"/>
+      <c r="O11" s="567" t="n"/>
+      <c r="P11" s="567" t="n"/>
+      <c r="Q11" s="567" t="n"/>
+      <c r="R11" s="567" t="n"/>
+      <c r="S11" s="567" t="n"/>
+      <c r="T11" s="567" t="n"/>
+      <c r="U11" s="567" t="n"/>
+      <c r="V11" s="567" t="n"/>
+      <c r="W11" s="567" t="n"/>
+      <c r="X11" s="567" t="n"/>
+      <c r="Y11" s="567" t="n"/>
+      <c r="Z11" s="567" t="n"/>
+      <c r="AA11" s="567" t="n"/>
+      <c r="AB11" s="568" t="n"/>
+      <c r="AC11" s="569" t="inlineStr">
         <is>
           <t>Inspection Level</t>
         </is>
       </c>
-      <c r="AD11" s="344" t="n"/>
-      <c r="AE11" s="344" t="n"/>
-      <c r="AF11" s="344" t="n"/>
-      <c r="AG11" s="344" t="n"/>
-      <c r="AH11" s="344" t="n"/>
-      <c r="AI11" s="344" t="n"/>
-      <c r="AJ11" s="344" t="n"/>
-      <c r="AK11" s="344" t="n"/>
-      <c r="AL11" s="344" t="n"/>
-      <c r="AM11" s="476" t="n"/>
-      <c r="AN11" s="362" t="n"/>
-      <c r="AO11" s="362" t="n"/>
-      <c r="AP11" s="362" t="n"/>
-      <c r="AQ11" s="362" t="n"/>
-      <c r="AR11" s="362" t="n"/>
-      <c r="AS11" s="362" t="n"/>
-      <c r="AT11" s="362" t="n"/>
-      <c r="AU11" s="362" t="n"/>
-      <c r="AV11" s="362" t="n"/>
-      <c r="AW11" s="362" t="n"/>
-      <c r="AX11" s="362" t="n"/>
-      <c r="AY11" s="362" t="n"/>
-      <c r="AZ11" s="362" t="n"/>
-      <c r="BA11" s="362" t="n"/>
-      <c r="BB11" s="362" t="n"/>
-      <c r="BC11" s="362" t="n"/>
-      <c r="BD11" s="478" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n"/>
+      <c r="AK11" s="12" t="n"/>
+      <c r="AL11" s="13" t="n"/>
+      <c r="AM11" s="566" t="n"/>
+      <c r="AN11" s="567" t="n"/>
+      <c r="AO11" s="567" t="n"/>
+      <c r="AP11" s="567" t="n"/>
+      <c r="AQ11" s="567" t="n"/>
+      <c r="AR11" s="567" t="n"/>
+      <c r="AS11" s="567" t="n"/>
+      <c r="AT11" s="567" t="n"/>
+      <c r="AU11" s="567" t="n"/>
+      <c r="AV11" s="567" t="n"/>
+      <c r="AW11" s="567" t="n"/>
+      <c r="AX11" s="567" t="n"/>
+      <c r="AY11" s="567" t="n"/>
+      <c r="AZ11" s="567" t="n"/>
+      <c r="BA11" s="567" t="n"/>
+      <c r="BB11" s="567" t="n"/>
+      <c r="BC11" s="567" t="n"/>
+      <c r="BD11" s="570" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="475" t="inlineStr">
+      <c r="A12" s="565" t="inlineStr">
         <is>
           <t>Code Letter</t>
         </is>
       </c>
-      <c r="B12" s="344" t="n"/>
-      <c r="C12" s="344" t="n"/>
-      <c r="D12" s="344" t="n"/>
-      <c r="E12" s="344" t="n"/>
-      <c r="F12" s="344" t="n"/>
-      <c r="G12" s="344" t="n"/>
-      <c r="H12" s="344" t="n"/>
-      <c r="I12" s="344" t="n"/>
-      <c r="J12" s="344" t="n"/>
-      <c r="K12" s="476" t="n"/>
-      <c r="L12" s="362" t="n"/>
-      <c r="M12" s="362" t="n"/>
-      <c r="N12" s="362" t="n"/>
-      <c r="O12" s="362" t="n"/>
-      <c r="P12" s="362" t="n"/>
-      <c r="Q12" s="362" t="n"/>
-      <c r="R12" s="362" t="n"/>
-      <c r="S12" s="362" t="n"/>
-      <c r="T12" s="362" t="n"/>
-      <c r="U12" s="362" t="n"/>
-      <c r="V12" s="362" t="n"/>
-      <c r="W12" s="362" t="n"/>
-      <c r="X12" s="362" t="n"/>
-      <c r="Y12" s="362" t="n"/>
-      <c r="Z12" s="362" t="n"/>
-      <c r="AA12" s="362" t="n"/>
-      <c r="AB12" s="362" t="n"/>
-      <c r="AC12" s="477" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="566" t="n"/>
+      <c r="L12" s="567" t="n"/>
+      <c r="M12" s="567" t="n"/>
+      <c r="N12" s="567" t="n"/>
+      <c r="O12" s="567" t="n"/>
+      <c r="P12" s="567" t="n"/>
+      <c r="Q12" s="567" t="n"/>
+      <c r="R12" s="567" t="n"/>
+      <c r="S12" s="567" t="n"/>
+      <c r="T12" s="567" t="n"/>
+      <c r="U12" s="567" t="n"/>
+      <c r="V12" s="567" t="n"/>
+      <c r="W12" s="567" t="n"/>
+      <c r="X12" s="567" t="n"/>
+      <c r="Y12" s="567" t="n"/>
+      <c r="Z12" s="567" t="n"/>
+      <c r="AA12" s="567" t="n"/>
+      <c r="AB12" s="568" t="n"/>
+      <c r="AC12" s="569" t="inlineStr">
         <is>
           <t>Sample Size</t>
         </is>
       </c>
-      <c r="AD12" s="344" t="n"/>
-      <c r="AE12" s="344" t="n"/>
-      <c r="AF12" s="344" t="n"/>
-      <c r="AG12" s="344" t="n"/>
-      <c r="AH12" s="344" t="n"/>
-      <c r="AI12" s="344" t="n"/>
-      <c r="AJ12" s="344" t="n"/>
-      <c r="AK12" s="344" t="n"/>
-      <c r="AL12" s="344" t="n"/>
-      <c r="AM12" s="476" t="n"/>
-      <c r="AN12" s="362" t="n"/>
-      <c r="AO12" s="362" t="n"/>
-      <c r="AP12" s="362" t="n"/>
-      <c r="AQ12" s="362" t="n"/>
-      <c r="AR12" s="362" t="n"/>
-      <c r="AS12" s="362" t="n"/>
-      <c r="AT12" s="362" t="n"/>
-      <c r="AU12" s="362" t="n"/>
-      <c r="AV12" s="362" t="n"/>
-      <c r="AW12" s="362" t="n"/>
-      <c r="AX12" s="362" t="n"/>
-      <c r="AY12" s="362" t="n"/>
-      <c r="AZ12" s="362" t="n"/>
-      <c r="BA12" s="362" t="n"/>
-      <c r="BB12" s="362" t="n"/>
-      <c r="BC12" s="362" t="n"/>
-      <c r="BD12" s="478" t="n"/>
+      <c r="AD12" s="12" t="n"/>
+      <c r="AE12" s="12" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="12" t="n"/>
+      <c r="AH12" s="12" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="12" t="n"/>
+      <c r="AK12" s="12" t="n"/>
+      <c r="AL12" s="13" t="n"/>
+      <c r="AM12" s="566" t="n"/>
+      <c r="AN12" s="567" t="n"/>
+      <c r="AO12" s="567" t="n"/>
+      <c r="AP12" s="567" t="n"/>
+      <c r="AQ12" s="567" t="n"/>
+      <c r="AR12" s="567" t="n"/>
+      <c r="AS12" s="567" t="n"/>
+      <c r="AT12" s="567" t="n"/>
+      <c r="AU12" s="567" t="n"/>
+      <c r="AV12" s="567" t="n"/>
+      <c r="AW12" s="567" t="n"/>
+      <c r="AX12" s="567" t="n"/>
+      <c r="AY12" s="567" t="n"/>
+      <c r="AZ12" s="567" t="n"/>
+      <c r="BA12" s="567" t="n"/>
+      <c r="BB12" s="567" t="n"/>
+      <c r="BC12" s="567" t="n"/>
+      <c r="BD12" s="570" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="475" t="inlineStr">
+      <c r="A13" s="565" t="inlineStr">
         <is>
           <t>Ac / Re</t>
         </is>
       </c>
-      <c r="B13" s="344" t="n"/>
-      <c r="C13" s="344" t="n"/>
-      <c r="D13" s="344" t="n"/>
-      <c r="E13" s="344" t="n"/>
-      <c r="F13" s="344" t="n"/>
-      <c r="G13" s="344" t="n"/>
-      <c r="H13" s="344" t="n"/>
-      <c r="I13" s="344" t="n"/>
-      <c r="J13" s="344" t="n"/>
-      <c r="K13" s="476" t="n"/>
-      <c r="L13" s="362" t="n"/>
-      <c r="M13" s="362" t="n"/>
-      <c r="N13" s="362" t="n"/>
-      <c r="O13" s="362" t="n"/>
-      <c r="P13" s="362" t="n"/>
-      <c r="Q13" s="362" t="n"/>
-      <c r="R13" s="362" t="n"/>
-      <c r="S13" s="362" t="n"/>
-      <c r="T13" s="362" t="n"/>
-      <c r="U13" s="362" t="n"/>
-      <c r="V13" s="362" t="n"/>
-      <c r="W13" s="362" t="n"/>
-      <c r="X13" s="362" t="n"/>
-      <c r="Y13" s="362" t="n"/>
-      <c r="Z13" s="362" t="n"/>
-      <c r="AA13" s="362" t="n"/>
-      <c r="AB13" s="362" t="n"/>
-      <c r="AC13" s="477" t="inlineStr">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="566" t="n"/>
+      <c r="L13" s="567" t="n"/>
+      <c r="M13" s="567" t="n"/>
+      <c r="N13" s="567" t="n"/>
+      <c r="O13" s="567" t="n"/>
+      <c r="P13" s="567" t="n"/>
+      <c r="Q13" s="567" t="n"/>
+      <c r="R13" s="567" t="n"/>
+      <c r="S13" s="567" t="n"/>
+      <c r="T13" s="567" t="n"/>
+      <c r="U13" s="567" t="n"/>
+      <c r="V13" s="567" t="n"/>
+      <c r="W13" s="567" t="n"/>
+      <c r="X13" s="567" t="n"/>
+      <c r="Y13" s="567" t="n"/>
+      <c r="Z13" s="567" t="n"/>
+      <c r="AA13" s="567" t="n"/>
+      <c r="AB13" s="568" t="n"/>
+      <c r="AC13" s="569" t="inlineStr">
         <is>
           <t>Switching Status</t>
         </is>
       </c>
-      <c r="AD13" s="344" t="n"/>
-      <c r="AE13" s="344" t="n"/>
-      <c r="AF13" s="344" t="n"/>
-      <c r="AG13" s="344" t="n"/>
-      <c r="AH13" s="344" t="n"/>
-      <c r="AI13" s="344" t="n"/>
-      <c r="AJ13" s="344" t="n"/>
-      <c r="AK13" s="344" t="n"/>
-      <c r="AL13" s="344" t="n"/>
-      <c r="AM13" s="476" t="n"/>
-      <c r="AN13" s="362" t="n"/>
-      <c r="AO13" s="362" t="n"/>
-      <c r="AP13" s="362" t="n"/>
-      <c r="AQ13" s="362" t="n"/>
-      <c r="AR13" s="362" t="n"/>
-      <c r="AS13" s="362" t="n"/>
-      <c r="AT13" s="362" t="n"/>
-      <c r="AU13" s="362" t="n"/>
-      <c r="AV13" s="362" t="n"/>
-      <c r="AW13" s="362" t="n"/>
-      <c r="AX13" s="362" t="n"/>
-      <c r="AY13" s="362" t="n"/>
-      <c r="AZ13" s="362" t="n"/>
-      <c r="BA13" s="362" t="n"/>
-      <c r="BB13" s="362" t="n"/>
-      <c r="BC13" s="362" t="n"/>
-      <c r="BD13" s="478" t="n"/>
+      <c r="AD13" s="12" t="n"/>
+      <c r="AE13" s="12" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="12" t="n"/>
+      <c r="AH13" s="12" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="12" t="n"/>
+      <c r="AK13" s="12" t="n"/>
+      <c r="AL13" s="13" t="n"/>
+      <c r="AM13" s="566" t="n"/>
+      <c r="AN13" s="567" t="n"/>
+      <c r="AO13" s="567" t="n"/>
+      <c r="AP13" s="567" t="n"/>
+      <c r="AQ13" s="567" t="n"/>
+      <c r="AR13" s="567" t="n"/>
+      <c r="AS13" s="567" t="n"/>
+      <c r="AT13" s="567" t="n"/>
+      <c r="AU13" s="567" t="n"/>
+      <c r="AV13" s="567" t="n"/>
+      <c r="AW13" s="567" t="n"/>
+      <c r="AX13" s="567" t="n"/>
+      <c r="AY13" s="567" t="n"/>
+      <c r="AZ13" s="567" t="n"/>
+      <c r="BA13" s="567" t="n"/>
+      <c r="BB13" s="567" t="n"/>
+      <c r="BC13" s="567" t="n"/>
+      <c r="BD13" s="570" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="475" t="inlineStr">
+      <c r="A14" s="565" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B14" s="344" t="n"/>
-      <c r="C14" s="344" t="n"/>
-      <c r="D14" s="344" t="n"/>
-      <c r="E14" s="344" t="n"/>
-      <c r="F14" s="344" t="n"/>
-      <c r="G14" s="344" t="n"/>
-      <c r="H14" s="344" t="n"/>
-      <c r="I14" s="344" t="n"/>
-      <c r="J14" s="344" t="n"/>
-      <c r="K14" s="476" t="n"/>
-      <c r="L14" s="362" t="n"/>
-      <c r="M14" s="362" t="n"/>
-      <c r="N14" s="362" t="n"/>
-      <c r="O14" s="362" t="n"/>
-      <c r="P14" s="362" t="n"/>
-      <c r="Q14" s="362" t="n"/>
-      <c r="R14" s="362" t="n"/>
-      <c r="S14" s="362" t="n"/>
-      <c r="T14" s="362" t="n"/>
-      <c r="U14" s="362" t="n"/>
-      <c r="V14" s="362" t="n"/>
-      <c r="W14" s="362" t="n"/>
-      <c r="X14" s="362" t="n"/>
-      <c r="Y14" s="362" t="n"/>
-      <c r="Z14" s="362" t="n"/>
-      <c r="AA14" s="362" t="n"/>
-      <c r="AB14" s="362" t="n"/>
-      <c r="AC14" s="477" t="inlineStr">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="566" t="n"/>
+      <c r="L14" s="567" t="n"/>
+      <c r="M14" s="567" t="n"/>
+      <c r="N14" s="567" t="n"/>
+      <c r="O14" s="567" t="n"/>
+      <c r="P14" s="567" t="n"/>
+      <c r="Q14" s="567" t="n"/>
+      <c r="R14" s="567" t="n"/>
+      <c r="S14" s="567" t="n"/>
+      <c r="T14" s="567" t="n"/>
+      <c r="U14" s="567" t="n"/>
+      <c r="V14" s="567" t="n"/>
+      <c r="W14" s="567" t="n"/>
+      <c r="X14" s="567" t="n"/>
+      <c r="Y14" s="567" t="n"/>
+      <c r="Z14" s="567" t="n"/>
+      <c r="AA14" s="567" t="n"/>
+      <c r="AB14" s="568" t="n"/>
+      <c r="AC14" s="569" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD14" s="344" t="n"/>
-      <c r="AE14" s="344" t="n"/>
-      <c r="AF14" s="344" t="n"/>
-      <c r="AG14" s="344" t="n"/>
-      <c r="AH14" s="344" t="n"/>
-      <c r="AI14" s="344" t="n"/>
-      <c r="AJ14" s="344" t="n"/>
-      <c r="AK14" s="344" t="n"/>
-      <c r="AL14" s="344" t="n"/>
-      <c r="AM14" s="476" t="n"/>
-      <c r="AN14" s="362" t="n"/>
-      <c r="AO14" s="362" t="n"/>
-      <c r="AP14" s="362" t="n"/>
-      <c r="AQ14" s="362" t="n"/>
-      <c r="AR14" s="362" t="n"/>
-      <c r="AS14" s="362" t="n"/>
-      <c r="AT14" s="362" t="n"/>
-      <c r="AU14" s="362" t="n"/>
-      <c r="AV14" s="362" t="n"/>
-      <c r="AW14" s="362" t="n"/>
-      <c r="AX14" s="362" t="n"/>
-      <c r="AY14" s="362" t="n"/>
-      <c r="AZ14" s="362" t="n"/>
-      <c r="BA14" s="362" t="n"/>
-      <c r="BB14" s="362" t="n"/>
-      <c r="BC14" s="362" t="n"/>
-      <c r="BD14" s="478" t="n"/>
+      <c r="AD14" s="12" t="n"/>
+      <c r="AE14" s="12" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="12" t="n"/>
+      <c r="AH14" s="12" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="12" t="n"/>
+      <c r="AK14" s="12" t="n"/>
+      <c r="AL14" s="13" t="n"/>
+      <c r="AM14" s="566" t="n"/>
+      <c r="AN14" s="567" t="n"/>
+      <c r="AO14" s="567" t="n"/>
+      <c r="AP14" s="567" t="n"/>
+      <c r="AQ14" s="567" t="n"/>
+      <c r="AR14" s="567" t="n"/>
+      <c r="AS14" s="567" t="n"/>
+      <c r="AT14" s="567" t="n"/>
+      <c r="AU14" s="567" t="n"/>
+      <c r="AV14" s="567" t="n"/>
+      <c r="AW14" s="567" t="n"/>
+      <c r="AX14" s="567" t="n"/>
+      <c r="AY14" s="567" t="n"/>
+      <c r="AZ14" s="567" t="n"/>
+      <c r="BA14" s="567" t="n"/>
+      <c r="BB14" s="567" t="n"/>
+      <c r="BC14" s="567" t="n"/>
+      <c r="BD14" s="570" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="479" t="inlineStr">
+      <c r="A15" s="571" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B15" s="480" t="n"/>
-      <c r="C15" s="480" t="n"/>
-      <c r="D15" s="480" t="n"/>
-      <c r="E15" s="480" t="n"/>
-      <c r="F15" s="480" t="n"/>
-      <c r="G15" s="480" t="n"/>
-      <c r="H15" s="480" t="n"/>
-      <c r="I15" s="480" t="n"/>
-      <c r="J15" s="480" t="n"/>
-      <c r="K15" s="481" t="n"/>
-      <c r="L15" s="482" t="n"/>
-      <c r="M15" s="482" t="n"/>
-      <c r="N15" s="482" t="n"/>
-      <c r="O15" s="482" t="n"/>
-      <c r="P15" s="482" t="n"/>
-      <c r="Q15" s="482" t="n"/>
-      <c r="R15" s="482" t="n"/>
-      <c r="S15" s="482" t="n"/>
-      <c r="T15" s="482" t="n"/>
-      <c r="U15" s="482" t="n"/>
-      <c r="V15" s="482" t="n"/>
-      <c r="W15" s="482" t="n"/>
-      <c r="X15" s="482" t="n"/>
-      <c r="Y15" s="482" t="n"/>
-      <c r="Z15" s="482" t="n"/>
-      <c r="AA15" s="482" t="n"/>
-      <c r="AB15" s="482" t="n"/>
-      <c r="AC15" s="483" t="inlineStr">
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="572" t="n"/>
+      <c r="L15" s="573" t="n"/>
+      <c r="M15" s="573" t="n"/>
+      <c r="N15" s="573" t="n"/>
+      <c r="O15" s="573" t="n"/>
+      <c r="P15" s="573" t="n"/>
+      <c r="Q15" s="573" t="n"/>
+      <c r="R15" s="573" t="n"/>
+      <c r="S15" s="573" t="n"/>
+      <c r="T15" s="573" t="n"/>
+      <c r="U15" s="573" t="n"/>
+      <c r="V15" s="573" t="n"/>
+      <c r="W15" s="573" t="n"/>
+      <c r="X15" s="573" t="n"/>
+      <c r="Y15" s="573" t="n"/>
+      <c r="Z15" s="573" t="n"/>
+      <c r="AA15" s="573" t="n"/>
+      <c r="AB15" s="574" t="n"/>
+      <c r="AC15" s="575" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="AD15" s="480" t="n"/>
-      <c r="AE15" s="480" t="n"/>
-      <c r="AF15" s="480" t="n"/>
-      <c r="AG15" s="480" t="n"/>
-      <c r="AH15" s="480" t="n"/>
-      <c r="AI15" s="480" t="n"/>
-      <c r="AJ15" s="480" t="n"/>
-      <c r="AK15" s="480" t="n"/>
-      <c r="AL15" s="480" t="n"/>
-      <c r="AM15" s="481" t="n"/>
-      <c r="AN15" s="482" t="n"/>
-      <c r="AO15" s="482" t="n"/>
-      <c r="AP15" s="482" t="n"/>
-      <c r="AQ15" s="482" t="n"/>
-      <c r="AR15" s="482" t="n"/>
-      <c r="AS15" s="482" t="n"/>
-      <c r="AT15" s="482" t="n"/>
-      <c r="AU15" s="482" t="n"/>
-      <c r="AV15" s="482" t="n"/>
-      <c r="AW15" s="482" t="n"/>
-      <c r="AX15" s="482" t="n"/>
-      <c r="AY15" s="482" t="n"/>
-      <c r="AZ15" s="482" t="n"/>
-      <c r="BA15" s="482" t="n"/>
-      <c r="BB15" s="482" t="n"/>
-      <c r="BC15" s="482" t="n"/>
-      <c r="BD15" s="484" t="n"/>
+      <c r="AD15" s="19" t="n"/>
+      <c r="AE15" s="19" t="n"/>
+      <c r="AF15" s="19" t="n"/>
+      <c r="AG15" s="19" t="n"/>
+      <c r="AH15" s="19" t="n"/>
+      <c r="AI15" s="19" t="n"/>
+      <c r="AJ15" s="19" t="n"/>
+      <c r="AK15" s="19" t="n"/>
+      <c r="AL15" s="22" t="n"/>
+      <c r="AM15" s="572" t="n"/>
+      <c r="AN15" s="573" t="n"/>
+      <c r="AO15" s="573" t="n"/>
+      <c r="AP15" s="573" t="n"/>
+      <c r="AQ15" s="573" t="n"/>
+      <c r="AR15" s="573" t="n"/>
+      <c r="AS15" s="573" t="n"/>
+      <c r="AT15" s="573" t="n"/>
+      <c r="AU15" s="573" t="n"/>
+      <c r="AV15" s="573" t="n"/>
+      <c r="AW15" s="573" t="n"/>
+      <c r="AX15" s="573" t="n"/>
+      <c r="AY15" s="573" t="n"/>
+      <c r="AZ15" s="573" t="n"/>
+      <c r="BA15" s="573" t="n"/>
+      <c r="BB15" s="573" t="n"/>
+      <c r="BC15" s="573" t="n"/>
+      <c r="BD15" s="576" t="n"/>
     </row>
     <row r="16" ht="3" customHeight="1">
-      <c r="A16" s="364" t="n"/>
-      <c r="B16" s="353" t="n"/>
-      <c r="C16" s="353" t="n"/>
-      <c r="D16" s="353" t="n"/>
-      <c r="E16" s="353" t="n"/>
-      <c r="F16" s="353" t="n"/>
-      <c r="G16" s="353" t="n"/>
-      <c r="H16" s="353" t="n"/>
-      <c r="I16" s="353" t="n"/>
-      <c r="J16" s="353" t="n"/>
-      <c r="K16" s="365" t="n"/>
-      <c r="L16" s="353" t="n"/>
-      <c r="M16" s="353" t="n"/>
-      <c r="N16" s="353" t="n"/>
-      <c r="O16" s="353" t="n"/>
-      <c r="P16" s="353" t="n"/>
-      <c r="Q16" s="353" t="n"/>
-      <c r="R16" s="353" t="n"/>
-      <c r="S16" s="353" t="n"/>
-      <c r="T16" s="353" t="n"/>
-      <c r="U16" s="353" t="n"/>
-      <c r="V16" s="353" t="n"/>
-      <c r="W16" s="353" t="n"/>
-      <c r="X16" s="353" t="n"/>
-      <c r="Y16" s="353" t="n"/>
-      <c r="Z16" s="353" t="n"/>
-      <c r="AA16" s="353" t="n"/>
-      <c r="AB16" s="353" t="n"/>
-      <c r="AC16" s="364" t="n"/>
-      <c r="AD16" s="353" t="n"/>
-      <c r="AE16" s="353" t="n"/>
-      <c r="AF16" s="353" t="n"/>
-      <c r="AG16" s="353" t="n"/>
-      <c r="AH16" s="353" t="n"/>
-      <c r="AI16" s="353" t="n"/>
-      <c r="AJ16" s="353" t="n"/>
-      <c r="AK16" s="353" t="n"/>
-      <c r="AL16" s="353" t="n"/>
-      <c r="AM16" s="365" t="n"/>
-      <c r="AN16" s="353" t="n"/>
-      <c r="AO16" s="353" t="n"/>
-      <c r="AP16" s="353" t="n"/>
-      <c r="AQ16" s="353" t="n"/>
-      <c r="AR16" s="353" t="n"/>
-      <c r="AS16" s="353" t="n"/>
-      <c r="AT16" s="353" t="n"/>
-      <c r="AU16" s="353" t="n"/>
-      <c r="AV16" s="353" t="n"/>
-      <c r="AW16" s="353" t="n"/>
-      <c r="AX16" s="353" t="n"/>
-      <c r="AY16" s="353" t="n"/>
-      <c r="AZ16" s="353" t="n"/>
-      <c r="BA16" s="353" t="n"/>
-      <c r="BB16" s="353" t="n"/>
-      <c r="BC16" s="353" t="n"/>
-      <c r="BD16" s="353" t="n"/>
+      <c r="A16" s="577" t="n"/>
+      <c r="B16" s="578" t="n"/>
+      <c r="C16" s="578" t="n"/>
+      <c r="D16" s="578" t="n"/>
+      <c r="E16" s="578" t="n"/>
+      <c r="F16" s="578" t="n"/>
+      <c r="G16" s="578" t="n"/>
+      <c r="H16" s="578" t="n"/>
+      <c r="I16" s="578" t="n"/>
+      <c r="J16" s="578" t="n"/>
+      <c r="K16" s="579" t="n"/>
+      <c r="L16" s="578" t="n"/>
+      <c r="M16" s="578" t="n"/>
+      <c r="N16" s="578" t="n"/>
+      <c r="O16" s="578" t="n"/>
+      <c r="P16" s="578" t="n"/>
+      <c r="Q16" s="578" t="n"/>
+      <c r="R16" s="578" t="n"/>
+      <c r="S16" s="578" t="n"/>
+      <c r="T16" s="578" t="n"/>
+      <c r="U16" s="578" t="n"/>
+      <c r="V16" s="578" t="n"/>
+      <c r="W16" s="578" t="n"/>
+      <c r="X16" s="578" t="n"/>
+      <c r="Y16" s="578" t="n"/>
+      <c r="Z16" s="578" t="n"/>
+      <c r="AA16" s="578" t="n"/>
+      <c r="AB16" s="578" t="n"/>
+      <c r="AC16" s="577" t="n"/>
+      <c r="AD16" s="578" t="n"/>
+      <c r="AE16" s="578" t="n"/>
+      <c r="AF16" s="578" t="n"/>
+      <c r="AG16" s="578" t="n"/>
+      <c r="AH16" s="578" t="n"/>
+      <c r="AI16" s="578" t="n"/>
+      <c r="AJ16" s="578" t="n"/>
+      <c r="AK16" s="578" t="n"/>
+      <c r="AL16" s="578" t="n"/>
+      <c r="AM16" s="579" t="n"/>
+      <c r="AN16" s="578" t="n"/>
+      <c r="AO16" s="578" t="n"/>
+      <c r="AP16" s="578" t="n"/>
+      <c r="AQ16" s="578" t="n"/>
+      <c r="AR16" s="578" t="n"/>
+      <c r="AS16" s="578" t="n"/>
+      <c r="AT16" s="578" t="n"/>
+      <c r="AU16" s="578" t="n"/>
+      <c r="AV16" s="578" t="n"/>
+      <c r="AW16" s="578" t="n"/>
+      <c r="AX16" s="578" t="n"/>
+      <c r="AY16" s="578" t="n"/>
+      <c r="AZ16" s="578" t="n"/>
+      <c r="BA16" s="578" t="n"/>
+      <c r="BB16" s="578" t="n"/>
+      <c r="BC16" s="578" t="n"/>
+      <c r="BD16" s="578" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="466" t="inlineStr">
+      <c r="A17" s="558" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B17" s="467" t="n"/>
-      <c r="C17" s="467" t="n"/>
-      <c r="D17" s="467" t="n"/>
-      <c r="E17" s="467" t="n"/>
-      <c r="F17" s="467" t="n"/>
-      <c r="G17" s="467" t="n"/>
-      <c r="H17" s="467" t="n"/>
-      <c r="I17" s="467" t="n"/>
-      <c r="J17" s="467" t="n"/>
-      <c r="K17" s="467" t="n"/>
-      <c r="L17" s="467" t="n"/>
-      <c r="M17" s="467" t="n"/>
-      <c r="N17" s="467" t="n"/>
-      <c r="O17" s="467" t="n"/>
-      <c r="P17" s="467" t="n"/>
-      <c r="Q17" s="467" t="n"/>
-      <c r="R17" s="467" t="n"/>
-      <c r="S17" s="467" t="n"/>
-      <c r="T17" s="467" t="n"/>
-      <c r="U17" s="467" t="n"/>
-      <c r="V17" s="467" t="n"/>
-      <c r="W17" s="467" t="n"/>
-      <c r="X17" s="467" t="n"/>
-      <c r="Y17" s="467" t="n"/>
-      <c r="Z17" s="467" t="n"/>
-      <c r="AA17" s="467" t="n"/>
-      <c r="AB17" s="467" t="n"/>
-      <c r="AC17" s="467" t="n"/>
-      <c r="AD17" s="467" t="n"/>
-      <c r="AE17" s="467" t="n"/>
-      <c r="AF17" s="467" t="n"/>
-      <c r="AG17" s="467" t="n"/>
-      <c r="AH17" s="467" t="n"/>
-      <c r="AI17" s="467" t="n"/>
-      <c r="AJ17" s="467" t="n"/>
-      <c r="AK17" s="467" t="n"/>
-      <c r="AL17" s="467" t="n"/>
-      <c r="AM17" s="467" t="n"/>
-      <c r="AN17" s="467" t="n"/>
-      <c r="AO17" s="467" t="n"/>
-      <c r="AP17" s="467" t="n"/>
-      <c r="AQ17" s="467" t="n"/>
-      <c r="AR17" s="467" t="n"/>
-      <c r="AS17" s="467" t="n"/>
-      <c r="AT17" s="467" t="n"/>
-      <c r="AU17" s="467" t="n"/>
-      <c r="AV17" s="467" t="n"/>
-      <c r="AW17" s="467" t="n"/>
-      <c r="AX17" s="467" t="n"/>
-      <c r="AY17" s="467" t="n"/>
-      <c r="AZ17" s="467" t="n"/>
-      <c r="BA17" s="467" t="n"/>
-      <c r="BB17" s="467" t="n"/>
-      <c r="BC17" s="467" t="n"/>
-      <c r="BD17" s="468" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="27" t="n"/>
+      <c r="P17" s="27" t="n"/>
+      <c r="Q17" s="27" t="n"/>
+      <c r="R17" s="27" t="n"/>
+      <c r="S17" s="27" t="n"/>
+      <c r="T17" s="27" t="n"/>
+      <c r="U17" s="27" t="n"/>
+      <c r="V17" s="27" t="n"/>
+      <c r="W17" s="27" t="n"/>
+      <c r="X17" s="27" t="n"/>
+      <c r="Y17" s="27" t="n"/>
+      <c r="Z17" s="27" t="n"/>
+      <c r="AA17" s="27" t="n"/>
+      <c r="AB17" s="27" t="n"/>
+      <c r="AC17" s="27" t="n"/>
+      <c r="AD17" s="27" t="n"/>
+      <c r="AE17" s="27" t="n"/>
+      <c r="AF17" s="27" t="n"/>
+      <c r="AG17" s="27" t="n"/>
+      <c r="AH17" s="27" t="n"/>
+      <c r="AI17" s="27" t="n"/>
+      <c r="AJ17" s="27" t="n"/>
+      <c r="AK17" s="27" t="n"/>
+      <c r="AL17" s="27" t="n"/>
+      <c r="AM17" s="27" t="n"/>
+      <c r="AN17" s="27" t="n"/>
+      <c r="AO17" s="27" t="n"/>
+      <c r="AP17" s="27" t="n"/>
+      <c r="AQ17" s="27" t="n"/>
+      <c r="AR17" s="27" t="n"/>
+      <c r="AS17" s="27" t="n"/>
+      <c r="AT17" s="27" t="n"/>
+      <c r="AU17" s="27" t="n"/>
+      <c r="AV17" s="27" t="n"/>
+      <c r="AW17" s="27" t="n"/>
+      <c r="AX17" s="27" t="n"/>
+      <c r="AY17" s="27" t="n"/>
+      <c r="AZ17" s="27" t="n"/>
+      <c r="BA17" s="27" t="n"/>
+      <c r="BB17" s="27" t="n"/>
+      <c r="BC17" s="27" t="n"/>
+      <c r="BD17" s="28" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="485" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="486" t="n"/>
-      <c r="C18" s="486" t="n"/>
-      <c r="D18" s="487" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="E18" s="486" t="n"/>
-      <c r="F18" s="486" t="n"/>
-      <c r="G18" s="486" t="n"/>
-      <c r="H18" s="487" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="37" t="inlineStr">
         <is>
           <t>Sample ID / Serial</t>
         </is>
       </c>
-      <c r="I18" s="486" t="n"/>
-      <c r="J18" s="486" t="n"/>
-      <c r="K18" s="486" t="n"/>
-      <c r="L18" s="486" t="n"/>
-      <c r="M18" s="486" t="n"/>
-      <c r="N18" s="486" t="n"/>
-      <c r="O18" s="486" t="n"/>
-      <c r="P18" s="486" t="n"/>
-      <c r="Q18" s="486" t="n"/>
-      <c r="R18" s="486" t="n"/>
-      <c r="S18" s="486" t="n"/>
-      <c r="T18" s="486" t="n"/>
-      <c r="U18" s="486" t="n"/>
-      <c r="V18" s="486" t="n"/>
-      <c r="W18" s="486" t="n"/>
-      <c r="X18" s="486" t="n"/>
-      <c r="Y18" s="486" t="n"/>
-      <c r="Z18" s="486" t="n"/>
-      <c r="AA18" s="487" t="inlineStr">
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+      <c r="Y18" s="5" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="37" t="inlineStr">
         <is>
           <t>Observation / Measured Result</t>
         </is>
       </c>
-      <c r="AB18" s="486" t="n"/>
-      <c r="AC18" s="486" t="n"/>
-      <c r="AD18" s="486" t="n"/>
-      <c r="AE18" s="486" t="n"/>
-      <c r="AF18" s="486" t="n"/>
-      <c r="AG18" s="486" t="n"/>
-      <c r="AH18" s="486" t="n"/>
-      <c r="AI18" s="486" t="n"/>
-      <c r="AJ18" s="486" t="n"/>
-      <c r="AK18" s="486" t="n"/>
-      <c r="AL18" s="486" t="n"/>
-      <c r="AM18" s="486" t="n"/>
-      <c r="AN18" s="486" t="n"/>
-      <c r="AO18" s="486" t="n"/>
-      <c r="AP18" s="486" t="n"/>
-      <c r="AQ18" s="486" t="n"/>
-      <c r="AR18" s="487" t="inlineStr">
+      <c r="AB18" s="5" t="n"/>
+      <c r="AC18" s="5" t="n"/>
+      <c r="AD18" s="5" t="n"/>
+      <c r="AE18" s="5" t="n"/>
+      <c r="AF18" s="5" t="n"/>
+      <c r="AG18" s="5" t="n"/>
+      <c r="AH18" s="5" t="n"/>
+      <c r="AI18" s="5" t="n"/>
+      <c r="AJ18" s="5" t="n"/>
+      <c r="AK18" s="5" t="n"/>
+      <c r="AL18" s="5" t="n"/>
+      <c r="AM18" s="5" t="n"/>
+      <c r="AN18" s="5" t="n"/>
+      <c r="AO18" s="5" t="n"/>
+      <c r="AP18" s="5" t="n"/>
+      <c r="AQ18" s="6" t="n"/>
+      <c r="AR18" s="37" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS18" s="486" t="n"/>
-      <c r="AT18" s="486" t="n"/>
-      <c r="AU18" s="486" t="n"/>
-      <c r="AV18" s="486" t="n"/>
-      <c r="AW18" s="486" t="n"/>
-      <c r="AX18" s="487" t="inlineStr">
+      <c r="AS18" s="5" t="n"/>
+      <c r="AT18" s="5" t="n"/>
+      <c r="AU18" s="5" t="n"/>
+      <c r="AV18" s="5" t="n"/>
+      <c r="AW18" s="6" t="n"/>
+      <c r="AX18" s="37" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY18" s="486" t="n"/>
-      <c r="AZ18" s="486" t="n"/>
-      <c r="BA18" s="486" t="n"/>
-      <c r="BB18" s="487" t="inlineStr">
+      <c r="AY18" s="5" t="n"/>
+      <c r="AZ18" s="5" t="n"/>
+      <c r="BA18" s="6" t="n"/>
+      <c r="BB18" s="37" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC18" s="486" t="n"/>
-      <c r="BD18" s="488" t="n"/>
+      <c r="BC18" s="5" t="n"/>
+      <c r="BD18" s="8" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="489">
+      <c r="A19" s="580">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B19" s="470" t="n"/>
-      <c r="C19" s="470" t="n"/>
-      <c r="D19" s="490" t="inlineStr">
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="581" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="472" t="n"/>
-      <c r="F19" s="472" t="n"/>
-      <c r="G19" s="472" t="n"/>
-      <c r="H19" s="471" t="n"/>
-      <c r="I19" s="472" t="n"/>
-      <c r="J19" s="472" t="n"/>
-      <c r="K19" s="472" t="n"/>
-      <c r="L19" s="472" t="n"/>
-      <c r="M19" s="472" t="n"/>
-      <c r="N19" s="472" t="n"/>
-      <c r="O19" s="472" t="n"/>
-      <c r="P19" s="472" t="n"/>
-      <c r="Q19" s="472" t="n"/>
-      <c r="R19" s="472" t="n"/>
-      <c r="S19" s="472" t="n"/>
-      <c r="T19" s="472" t="n"/>
-      <c r="U19" s="472" t="n"/>
-      <c r="V19" s="472" t="n"/>
-      <c r="W19" s="472" t="n"/>
-      <c r="X19" s="472" t="n"/>
-      <c r="Y19" s="472" t="n"/>
-      <c r="Z19" s="472" t="n"/>
-      <c r="AA19" s="491" t="n"/>
-      <c r="AB19" s="472" t="n"/>
-      <c r="AC19" s="472" t="n"/>
-      <c r="AD19" s="472" t="n"/>
-      <c r="AE19" s="472" t="n"/>
-      <c r="AF19" s="472" t="n"/>
-      <c r="AG19" s="472" t="n"/>
-      <c r="AH19" s="472" t="n"/>
-      <c r="AI19" s="472" t="n"/>
-      <c r="AJ19" s="472" t="n"/>
-      <c r="AK19" s="472" t="n"/>
-      <c r="AL19" s="472" t="n"/>
-      <c r="AM19" s="472" t="n"/>
-      <c r="AN19" s="472" t="n"/>
-      <c r="AO19" s="472" t="n"/>
-      <c r="AP19" s="472" t="n"/>
-      <c r="AQ19" s="472" t="n"/>
-      <c r="AR19" s="471" t="n"/>
-      <c r="AS19" s="472" t="n"/>
-      <c r="AT19" s="472" t="n"/>
-      <c r="AU19" s="472" t="n"/>
-      <c r="AV19" s="472" t="n"/>
-      <c r="AW19" s="472" t="n"/>
-      <c r="AX19" s="471" t="n"/>
-      <c r="AY19" s="472" t="n"/>
-      <c r="AZ19" s="472" t="n"/>
-      <c r="BA19" s="472" t="n"/>
-      <c r="BB19" s="492" t="n"/>
-      <c r="BC19" s="472" t="n"/>
-      <c r="BD19" s="474" t="n"/>
+      <c r="E19" s="561" t="n"/>
+      <c r="F19" s="561" t="n"/>
+      <c r="G19" s="562" t="n"/>
+      <c r="H19" s="560" t="n"/>
+      <c r="I19" s="561" t="n"/>
+      <c r="J19" s="561" t="n"/>
+      <c r="K19" s="561" t="n"/>
+      <c r="L19" s="561" t="n"/>
+      <c r="M19" s="561" t="n"/>
+      <c r="N19" s="561" t="n"/>
+      <c r="O19" s="561" t="n"/>
+      <c r="P19" s="561" t="n"/>
+      <c r="Q19" s="561" t="n"/>
+      <c r="R19" s="561" t="n"/>
+      <c r="S19" s="561" t="n"/>
+      <c r="T19" s="561" t="n"/>
+      <c r="U19" s="561" t="n"/>
+      <c r="V19" s="561" t="n"/>
+      <c r="W19" s="561" t="n"/>
+      <c r="X19" s="561" t="n"/>
+      <c r="Y19" s="561" t="n"/>
+      <c r="Z19" s="562" t="n"/>
+      <c r="AA19" s="582" t="n"/>
+      <c r="AB19" s="561" t="n"/>
+      <c r="AC19" s="561" t="n"/>
+      <c r="AD19" s="561" t="n"/>
+      <c r="AE19" s="561" t="n"/>
+      <c r="AF19" s="561" t="n"/>
+      <c r="AG19" s="561" t="n"/>
+      <c r="AH19" s="561" t="n"/>
+      <c r="AI19" s="561" t="n"/>
+      <c r="AJ19" s="561" t="n"/>
+      <c r="AK19" s="561" t="n"/>
+      <c r="AL19" s="561" t="n"/>
+      <c r="AM19" s="561" t="n"/>
+      <c r="AN19" s="561" t="n"/>
+      <c r="AO19" s="561" t="n"/>
+      <c r="AP19" s="561" t="n"/>
+      <c r="AQ19" s="562" t="n"/>
+      <c r="AR19" s="560" t="n"/>
+      <c r="AS19" s="561" t="n"/>
+      <c r="AT19" s="561" t="n"/>
+      <c r="AU19" s="561" t="n"/>
+      <c r="AV19" s="561" t="n"/>
+      <c r="AW19" s="562" t="n"/>
+      <c r="AX19" s="560" t="n"/>
+      <c r="AY19" s="561" t="n"/>
+      <c r="AZ19" s="561" t="n"/>
+      <c r="BA19" s="562" t="n"/>
+      <c r="BB19" s="583" t="n"/>
+      <c r="BC19" s="561" t="n"/>
+      <c r="BD19" s="564" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="493">
+      <c r="A20" s="584">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B20" s="344" t="n"/>
-      <c r="C20" s="344" t="n"/>
-      <c r="D20" s="494" t="inlineStr">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="585" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="362" t="n"/>
-      <c r="F20" s="362" t="n"/>
-      <c r="G20" s="362" t="n"/>
-      <c r="H20" s="476" t="n"/>
-      <c r="I20" s="362" t="n"/>
-      <c r="J20" s="362" t="n"/>
-      <c r="K20" s="362" t="n"/>
-      <c r="L20" s="362" t="n"/>
-      <c r="M20" s="362" t="n"/>
-      <c r="N20" s="362" t="n"/>
-      <c r="O20" s="362" t="n"/>
-      <c r="P20" s="362" t="n"/>
-      <c r="Q20" s="362" t="n"/>
-      <c r="R20" s="362" t="n"/>
-      <c r="S20" s="362" t="n"/>
-      <c r="T20" s="362" t="n"/>
-      <c r="U20" s="362" t="n"/>
-      <c r="V20" s="362" t="n"/>
-      <c r="W20" s="362" t="n"/>
-      <c r="X20" s="362" t="n"/>
-      <c r="Y20" s="362" t="n"/>
-      <c r="Z20" s="362" t="n"/>
-      <c r="AA20" s="495" t="n"/>
-      <c r="AB20" s="362" t="n"/>
-      <c r="AC20" s="362" t="n"/>
-      <c r="AD20" s="362" t="n"/>
-      <c r="AE20" s="362" t="n"/>
-      <c r="AF20" s="362" t="n"/>
-      <c r="AG20" s="362" t="n"/>
-      <c r="AH20" s="362" t="n"/>
-      <c r="AI20" s="362" t="n"/>
-      <c r="AJ20" s="362" t="n"/>
-      <c r="AK20" s="362" t="n"/>
-      <c r="AL20" s="362" t="n"/>
-      <c r="AM20" s="362" t="n"/>
-      <c r="AN20" s="362" t="n"/>
-      <c r="AO20" s="362" t="n"/>
-      <c r="AP20" s="362" t="n"/>
-      <c r="AQ20" s="362" t="n"/>
-      <c r="AR20" s="476" t="n"/>
-      <c r="AS20" s="362" t="n"/>
-      <c r="AT20" s="362" t="n"/>
-      <c r="AU20" s="362" t="n"/>
-      <c r="AV20" s="362" t="n"/>
-      <c r="AW20" s="362" t="n"/>
-      <c r="AX20" s="476" t="n"/>
-      <c r="AY20" s="362" t="n"/>
-      <c r="AZ20" s="362" t="n"/>
-      <c r="BA20" s="362" t="n"/>
-      <c r="BB20" s="496" t="n"/>
-      <c r="BC20" s="362" t="n"/>
-      <c r="BD20" s="478" t="n"/>
+      <c r="E20" s="567" t="n"/>
+      <c r="F20" s="567" t="n"/>
+      <c r="G20" s="568" t="n"/>
+      <c r="H20" s="566" t="n"/>
+      <c r="I20" s="567" t="n"/>
+      <c r="J20" s="567" t="n"/>
+      <c r="K20" s="567" t="n"/>
+      <c r="L20" s="567" t="n"/>
+      <c r="M20" s="567" t="n"/>
+      <c r="N20" s="567" t="n"/>
+      <c r="O20" s="567" t="n"/>
+      <c r="P20" s="567" t="n"/>
+      <c r="Q20" s="567" t="n"/>
+      <c r="R20" s="567" t="n"/>
+      <c r="S20" s="567" t="n"/>
+      <c r="T20" s="567" t="n"/>
+      <c r="U20" s="567" t="n"/>
+      <c r="V20" s="567" t="n"/>
+      <c r="W20" s="567" t="n"/>
+      <c r="X20" s="567" t="n"/>
+      <c r="Y20" s="567" t="n"/>
+      <c r="Z20" s="568" t="n"/>
+      <c r="AA20" s="586" t="n"/>
+      <c r="AB20" s="567" t="n"/>
+      <c r="AC20" s="567" t="n"/>
+      <c r="AD20" s="567" t="n"/>
+      <c r="AE20" s="567" t="n"/>
+      <c r="AF20" s="567" t="n"/>
+      <c r="AG20" s="567" t="n"/>
+      <c r="AH20" s="567" t="n"/>
+      <c r="AI20" s="567" t="n"/>
+      <c r="AJ20" s="567" t="n"/>
+      <c r="AK20" s="567" t="n"/>
+      <c r="AL20" s="567" t="n"/>
+      <c r="AM20" s="567" t="n"/>
+      <c r="AN20" s="567" t="n"/>
+      <c r="AO20" s="567" t="n"/>
+      <c r="AP20" s="567" t="n"/>
+      <c r="AQ20" s="568" t="n"/>
+      <c r="AR20" s="566" t="n"/>
+      <c r="AS20" s="567" t="n"/>
+      <c r="AT20" s="567" t="n"/>
+      <c r="AU20" s="567" t="n"/>
+      <c r="AV20" s="567" t="n"/>
+      <c r="AW20" s="568" t="n"/>
+      <c r="AX20" s="566" t="n"/>
+      <c r="AY20" s="567" t="n"/>
+      <c r="AZ20" s="567" t="n"/>
+      <c r="BA20" s="568" t="n"/>
+      <c r="BB20" s="587" t="n"/>
+      <c r="BC20" s="567" t="n"/>
+      <c r="BD20" s="570" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="493">
+      <c r="A21" s="584">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B21" s="344" t="n"/>
-      <c r="C21" s="344" t="n"/>
-      <c r="D21" s="494" t="inlineStr">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="585" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="362" t="n"/>
-      <c r="F21" s="362" t="n"/>
-      <c r="G21" s="362" t="n"/>
-      <c r="H21" s="476" t="n"/>
-      <c r="I21" s="362" t="n"/>
-      <c r="J21" s="362" t="n"/>
-      <c r="K21" s="362" t="n"/>
-      <c r="L21" s="362" t="n"/>
-      <c r="M21" s="362" t="n"/>
-      <c r="N21" s="362" t="n"/>
-      <c r="O21" s="362" t="n"/>
-      <c r="P21" s="362" t="n"/>
-      <c r="Q21" s="362" t="n"/>
-      <c r="R21" s="362" t="n"/>
-      <c r="S21" s="362" t="n"/>
-      <c r="T21" s="362" t="n"/>
-      <c r="U21" s="362" t="n"/>
-      <c r="V21" s="362" t="n"/>
-      <c r="W21" s="362" t="n"/>
-      <c r="X21" s="362" t="n"/>
-      <c r="Y21" s="362" t="n"/>
-      <c r="Z21" s="362" t="n"/>
-      <c r="AA21" s="495" t="n"/>
-      <c r="AB21" s="362" t="n"/>
-      <c r="AC21" s="362" t="n"/>
-      <c r="AD21" s="362" t="n"/>
-      <c r="AE21" s="362" t="n"/>
-      <c r="AF21" s="362" t="n"/>
-      <c r="AG21" s="362" t="n"/>
-      <c r="AH21" s="362" t="n"/>
-      <c r="AI21" s="362" t="n"/>
-      <c r="AJ21" s="362" t="n"/>
-      <c r="AK21" s="362" t="n"/>
-      <c r="AL21" s="362" t="n"/>
-      <c r="AM21" s="362" t="n"/>
-      <c r="AN21" s="362" t="n"/>
-      <c r="AO21" s="362" t="n"/>
-      <c r="AP21" s="362" t="n"/>
-      <c r="AQ21" s="362" t="n"/>
-      <c r="AR21" s="476" t="n"/>
-      <c r="AS21" s="362" t="n"/>
-      <c r="AT21" s="362" t="n"/>
-      <c r="AU21" s="362" t="n"/>
-      <c r="AV21" s="362" t="n"/>
-      <c r="AW21" s="362" t="n"/>
-      <c r="AX21" s="476" t="n"/>
-      <c r="AY21" s="362" t="n"/>
-      <c r="AZ21" s="362" t="n"/>
-      <c r="BA21" s="362" t="n"/>
-      <c r="BB21" s="496" t="n"/>
-      <c r="BC21" s="362" t="n"/>
-      <c r="BD21" s="478" t="n"/>
+      <c r="E21" s="567" t="n"/>
+      <c r="F21" s="567" t="n"/>
+      <c r="G21" s="568" t="n"/>
+      <c r="H21" s="566" t="n"/>
+      <c r="I21" s="567" t="n"/>
+      <c r="J21" s="567" t="n"/>
+      <c r="K21" s="567" t="n"/>
+      <c r="L21" s="567" t="n"/>
+      <c r="M21" s="567" t="n"/>
+      <c r="N21" s="567" t="n"/>
+      <c r="O21" s="567" t="n"/>
+      <c r="P21" s="567" t="n"/>
+      <c r="Q21" s="567" t="n"/>
+      <c r="R21" s="567" t="n"/>
+      <c r="S21" s="567" t="n"/>
+      <c r="T21" s="567" t="n"/>
+      <c r="U21" s="567" t="n"/>
+      <c r="V21" s="567" t="n"/>
+      <c r="W21" s="567" t="n"/>
+      <c r="X21" s="567" t="n"/>
+      <c r="Y21" s="567" t="n"/>
+      <c r="Z21" s="568" t="n"/>
+      <c r="AA21" s="586" t="n"/>
+      <c r="AB21" s="567" t="n"/>
+      <c r="AC21" s="567" t="n"/>
+      <c r="AD21" s="567" t="n"/>
+      <c r="AE21" s="567" t="n"/>
+      <c r="AF21" s="567" t="n"/>
+      <c r="AG21" s="567" t="n"/>
+      <c r="AH21" s="567" t="n"/>
+      <c r="AI21" s="567" t="n"/>
+      <c r="AJ21" s="567" t="n"/>
+      <c r="AK21" s="567" t="n"/>
+      <c r="AL21" s="567" t="n"/>
+      <c r="AM21" s="567" t="n"/>
+      <c r="AN21" s="567" t="n"/>
+      <c r="AO21" s="567" t="n"/>
+      <c r="AP21" s="567" t="n"/>
+      <c r="AQ21" s="568" t="n"/>
+      <c r="AR21" s="566" t="n"/>
+      <c r="AS21" s="567" t="n"/>
+      <c r="AT21" s="567" t="n"/>
+      <c r="AU21" s="567" t="n"/>
+      <c r="AV21" s="567" t="n"/>
+      <c r="AW21" s="568" t="n"/>
+      <c r="AX21" s="566" t="n"/>
+      <c r="AY21" s="567" t="n"/>
+      <c r="AZ21" s="567" t="n"/>
+      <c r="BA21" s="568" t="n"/>
+      <c r="BB21" s="587" t="n"/>
+      <c r="BC21" s="567" t="n"/>
+      <c r="BD21" s="570" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="493">
+      <c r="A22" s="584">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B22" s="344" t="n"/>
-      <c r="C22" s="344" t="n"/>
-      <c r="D22" s="494" t="inlineStr">
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="585" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="362" t="n"/>
-      <c r="F22" s="362" t="n"/>
-      <c r="G22" s="362" t="n"/>
-      <c r="H22" s="476" t="n"/>
-      <c r="I22" s="362" t="n"/>
-      <c r="J22" s="362" t="n"/>
-      <c r="K22" s="362" t="n"/>
-      <c r="L22" s="362" t="n"/>
-      <c r="M22" s="362" t="n"/>
-      <c r="N22" s="362" t="n"/>
-      <c r="O22" s="362" t="n"/>
-      <c r="P22" s="362" t="n"/>
-      <c r="Q22" s="362" t="n"/>
-      <c r="R22" s="362" t="n"/>
-      <c r="S22" s="362" t="n"/>
-      <c r="T22" s="362" t="n"/>
-      <c r="U22" s="362" t="n"/>
-      <c r="V22" s="362" t="n"/>
-      <c r="W22" s="362" t="n"/>
-      <c r="X22" s="362" t="n"/>
-      <c r="Y22" s="362" t="n"/>
-      <c r="Z22" s="362" t="n"/>
-      <c r="AA22" s="495" t="n"/>
-      <c r="AB22" s="362" t="n"/>
-      <c r="AC22" s="362" t="n"/>
-      <c r="AD22" s="362" t="n"/>
-      <c r="AE22" s="362" t="n"/>
-      <c r="AF22" s="362" t="n"/>
-      <c r="AG22" s="362" t="n"/>
-      <c r="AH22" s="362" t="n"/>
-      <c r="AI22" s="362" t="n"/>
-      <c r="AJ22" s="362" t="n"/>
-      <c r="AK22" s="362" t="n"/>
-      <c r="AL22" s="362" t="n"/>
-      <c r="AM22" s="362" t="n"/>
-      <c r="AN22" s="362" t="n"/>
-      <c r="AO22" s="362" t="n"/>
-      <c r="AP22" s="362" t="n"/>
-      <c r="AQ22" s="362" t="n"/>
-      <c r="AR22" s="476" t="n"/>
-      <c r="AS22" s="362" t="n"/>
-      <c r="AT22" s="362" t="n"/>
-      <c r="AU22" s="362" t="n"/>
-      <c r="AV22" s="362" t="n"/>
-      <c r="AW22" s="362" t="n"/>
-      <c r="AX22" s="476" t="n"/>
-      <c r="AY22" s="362" t="n"/>
-      <c r="AZ22" s="362" t="n"/>
-      <c r="BA22" s="362" t="n"/>
-      <c r="BB22" s="496" t="n"/>
-      <c r="BC22" s="362" t="n"/>
-      <c r="BD22" s="478" t="n"/>
+      <c r="E22" s="567" t="n"/>
+      <c r="F22" s="567" t="n"/>
+      <c r="G22" s="568" t="n"/>
+      <c r="H22" s="566" t="n"/>
+      <c r="I22" s="567" t="n"/>
+      <c r="J22" s="567" t="n"/>
+      <c r="K22" s="567" t="n"/>
+      <c r="L22" s="567" t="n"/>
+      <c r="M22" s="567" t="n"/>
+      <c r="N22" s="567" t="n"/>
+      <c r="O22" s="567" t="n"/>
+      <c r="P22" s="567" t="n"/>
+      <c r="Q22" s="567" t="n"/>
+      <c r="R22" s="567" t="n"/>
+      <c r="S22" s="567" t="n"/>
+      <c r="T22" s="567" t="n"/>
+      <c r="U22" s="567" t="n"/>
+      <c r="V22" s="567" t="n"/>
+      <c r="W22" s="567" t="n"/>
+      <c r="X22" s="567" t="n"/>
+      <c r="Y22" s="567" t="n"/>
+      <c r="Z22" s="568" t="n"/>
+      <c r="AA22" s="586" t="n"/>
+      <c r="AB22" s="567" t="n"/>
+      <c r="AC22" s="567" t="n"/>
+      <c r="AD22" s="567" t="n"/>
+      <c r="AE22" s="567" t="n"/>
+      <c r="AF22" s="567" t="n"/>
+      <c r="AG22" s="567" t="n"/>
+      <c r="AH22" s="567" t="n"/>
+      <c r="AI22" s="567" t="n"/>
+      <c r="AJ22" s="567" t="n"/>
+      <c r="AK22" s="567" t="n"/>
+      <c r="AL22" s="567" t="n"/>
+      <c r="AM22" s="567" t="n"/>
+      <c r="AN22" s="567" t="n"/>
+      <c r="AO22" s="567" t="n"/>
+      <c r="AP22" s="567" t="n"/>
+      <c r="AQ22" s="568" t="n"/>
+      <c r="AR22" s="566" t="n"/>
+      <c r="AS22" s="567" t="n"/>
+      <c r="AT22" s="567" t="n"/>
+      <c r="AU22" s="567" t="n"/>
+      <c r="AV22" s="567" t="n"/>
+      <c r="AW22" s="568" t="n"/>
+      <c r="AX22" s="566" t="n"/>
+      <c r="AY22" s="567" t="n"/>
+      <c r="AZ22" s="567" t="n"/>
+      <c r="BA22" s="568" t="n"/>
+      <c r="BB22" s="587" t="n"/>
+      <c r="BC22" s="567" t="n"/>
+      <c r="BD22" s="570" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="493">
+      <c r="A23" s="584">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B23" s="344" t="n"/>
-      <c r="C23" s="344" t="n"/>
-      <c r="D23" s="494" t="inlineStr">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="585" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="362" t="n"/>
-      <c r="F23" s="362" t="n"/>
-      <c r="G23" s="362" t="n"/>
-      <c r="H23" s="476" t="n"/>
-      <c r="I23" s="362" t="n"/>
-      <c r="J23" s="362" t="n"/>
-      <c r="K23" s="362" t="n"/>
-      <c r="L23" s="362" t="n"/>
-      <c r="M23" s="362" t="n"/>
-      <c r="N23" s="362" t="n"/>
-      <c r="O23" s="362" t="n"/>
-      <c r="P23" s="362" t="n"/>
-      <c r="Q23" s="362" t="n"/>
-      <c r="R23" s="362" t="n"/>
-      <c r="S23" s="362" t="n"/>
-      <c r="T23" s="362" t="n"/>
-      <c r="U23" s="362" t="n"/>
-      <c r="V23" s="362" t="n"/>
-      <c r="W23" s="362" t="n"/>
-      <c r="X23" s="362" t="n"/>
-      <c r="Y23" s="362" t="n"/>
-      <c r="Z23" s="362" t="n"/>
-      <c r="AA23" s="495" t="n"/>
-      <c r="AB23" s="362" t="n"/>
-      <c r="AC23" s="362" t="n"/>
-      <c r="AD23" s="362" t="n"/>
-      <c r="AE23" s="362" t="n"/>
-      <c r="AF23" s="362" t="n"/>
-      <c r="AG23" s="362" t="n"/>
-      <c r="AH23" s="362" t="n"/>
-      <c r="AI23" s="362" t="n"/>
-      <c r="AJ23" s="362" t="n"/>
-      <c r="AK23" s="362" t="n"/>
-      <c r="AL23" s="362" t="n"/>
-      <c r="AM23" s="362" t="n"/>
-      <c r="AN23" s="362" t="n"/>
-      <c r="AO23" s="362" t="n"/>
-      <c r="AP23" s="362" t="n"/>
-      <c r="AQ23" s="362" t="n"/>
-      <c r="AR23" s="476" t="n"/>
-      <c r="AS23" s="362" t="n"/>
-      <c r="AT23" s="362" t="n"/>
-      <c r="AU23" s="362" t="n"/>
-      <c r="AV23" s="362" t="n"/>
-      <c r="AW23" s="362" t="n"/>
-      <c r="AX23" s="476" t="n"/>
-      <c r="AY23" s="362" t="n"/>
-      <c r="AZ23" s="362" t="n"/>
-      <c r="BA23" s="362" t="n"/>
-      <c r="BB23" s="496" t="n"/>
-      <c r="BC23" s="362" t="n"/>
-      <c r="BD23" s="478" t="n"/>
+      <c r="E23" s="567" t="n"/>
+      <c r="F23" s="567" t="n"/>
+      <c r="G23" s="568" t="n"/>
+      <c r="H23" s="566" t="n"/>
+      <c r="I23" s="567" t="n"/>
+      <c r="J23" s="567" t="n"/>
+      <c r="K23" s="567" t="n"/>
+      <c r="L23" s="567" t="n"/>
+      <c r="M23" s="567" t="n"/>
+      <c r="N23" s="567" t="n"/>
+      <c r="O23" s="567" t="n"/>
+      <c r="P23" s="567" t="n"/>
+      <c r="Q23" s="567" t="n"/>
+      <c r="R23" s="567" t="n"/>
+      <c r="S23" s="567" t="n"/>
+      <c r="T23" s="567" t="n"/>
+      <c r="U23" s="567" t="n"/>
+      <c r="V23" s="567" t="n"/>
+      <c r="W23" s="567" t="n"/>
+      <c r="X23" s="567" t="n"/>
+      <c r="Y23" s="567" t="n"/>
+      <c r="Z23" s="568" t="n"/>
+      <c r="AA23" s="586" t="n"/>
+      <c r="AB23" s="567" t="n"/>
+      <c r="AC23" s="567" t="n"/>
+      <c r="AD23" s="567" t="n"/>
+      <c r="AE23" s="567" t="n"/>
+      <c r="AF23" s="567" t="n"/>
+      <c r="AG23" s="567" t="n"/>
+      <c r="AH23" s="567" t="n"/>
+      <c r="AI23" s="567" t="n"/>
+      <c r="AJ23" s="567" t="n"/>
+      <c r="AK23" s="567" t="n"/>
+      <c r="AL23" s="567" t="n"/>
+      <c r="AM23" s="567" t="n"/>
+      <c r="AN23" s="567" t="n"/>
+      <c r="AO23" s="567" t="n"/>
+      <c r="AP23" s="567" t="n"/>
+      <c r="AQ23" s="568" t="n"/>
+      <c r="AR23" s="566" t="n"/>
+      <c r="AS23" s="567" t="n"/>
+      <c r="AT23" s="567" t="n"/>
+      <c r="AU23" s="567" t="n"/>
+      <c r="AV23" s="567" t="n"/>
+      <c r="AW23" s="568" t="n"/>
+      <c r="AX23" s="566" t="n"/>
+      <c r="AY23" s="567" t="n"/>
+      <c r="AZ23" s="567" t="n"/>
+      <c r="BA23" s="568" t="n"/>
+      <c r="BB23" s="587" t="n"/>
+      <c r="BC23" s="567" t="n"/>
+      <c r="BD23" s="570" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="497">
+      <c r="A24" s="588">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B24" s="480" t="n"/>
-      <c r="C24" s="480" t="n"/>
-      <c r="D24" s="498" t="inlineStr">
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="589" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="482" t="n"/>
-      <c r="F24" s="482" t="n"/>
-      <c r="G24" s="482" t="n"/>
-      <c r="H24" s="481" t="n"/>
-      <c r="I24" s="482" t="n"/>
-      <c r="J24" s="482" t="n"/>
-      <c r="K24" s="482" t="n"/>
-      <c r="L24" s="482" t="n"/>
-      <c r="M24" s="482" t="n"/>
-      <c r="N24" s="482" t="n"/>
-      <c r="O24" s="482" t="n"/>
-      <c r="P24" s="482" t="n"/>
-      <c r="Q24" s="482" t="n"/>
-      <c r="R24" s="482" t="n"/>
-      <c r="S24" s="482" t="n"/>
-      <c r="T24" s="482" t="n"/>
-      <c r="U24" s="482" t="n"/>
-      <c r="V24" s="482" t="n"/>
-      <c r="W24" s="482" t="n"/>
-      <c r="X24" s="482" t="n"/>
-      <c r="Y24" s="482" t="n"/>
-      <c r="Z24" s="482" t="n"/>
-      <c r="AA24" s="499" t="n"/>
-      <c r="AB24" s="482" t="n"/>
-      <c r="AC24" s="482" t="n"/>
-      <c r="AD24" s="482" t="n"/>
-      <c r="AE24" s="482" t="n"/>
-      <c r="AF24" s="482" t="n"/>
-      <c r="AG24" s="482" t="n"/>
-      <c r="AH24" s="482" t="n"/>
-      <c r="AI24" s="482" t="n"/>
-      <c r="AJ24" s="482" t="n"/>
-      <c r="AK24" s="482" t="n"/>
-      <c r="AL24" s="482" t="n"/>
-      <c r="AM24" s="482" t="n"/>
-      <c r="AN24" s="482" t="n"/>
-      <c r="AO24" s="482" t="n"/>
-      <c r="AP24" s="482" t="n"/>
-      <c r="AQ24" s="482" t="n"/>
-      <c r="AR24" s="481" t="n"/>
-      <c r="AS24" s="482" t="n"/>
-      <c r="AT24" s="482" t="n"/>
-      <c r="AU24" s="482" t="n"/>
-      <c r="AV24" s="482" t="n"/>
-      <c r="AW24" s="482" t="n"/>
-      <c r="AX24" s="481" t="n"/>
-      <c r="AY24" s="482" t="n"/>
-      <c r="AZ24" s="482" t="n"/>
-      <c r="BA24" s="482" t="n"/>
-      <c r="BB24" s="500" t="n"/>
-      <c r="BC24" s="482" t="n"/>
-      <c r="BD24" s="484" t="n"/>
+      <c r="E24" s="573" t="n"/>
+      <c r="F24" s="573" t="n"/>
+      <c r="G24" s="574" t="n"/>
+      <c r="H24" s="572" t="n"/>
+      <c r="I24" s="573" t="n"/>
+      <c r="J24" s="573" t="n"/>
+      <c r="K24" s="573" t="n"/>
+      <c r="L24" s="573" t="n"/>
+      <c r="M24" s="573" t="n"/>
+      <c r="N24" s="573" t="n"/>
+      <c r="O24" s="573" t="n"/>
+      <c r="P24" s="573" t="n"/>
+      <c r="Q24" s="573" t="n"/>
+      <c r="R24" s="573" t="n"/>
+      <c r="S24" s="573" t="n"/>
+      <c r="T24" s="573" t="n"/>
+      <c r="U24" s="573" t="n"/>
+      <c r="V24" s="573" t="n"/>
+      <c r="W24" s="573" t="n"/>
+      <c r="X24" s="573" t="n"/>
+      <c r="Y24" s="573" t="n"/>
+      <c r="Z24" s="574" t="n"/>
+      <c r="AA24" s="590" t="n"/>
+      <c r="AB24" s="573" t="n"/>
+      <c r="AC24" s="573" t="n"/>
+      <c r="AD24" s="573" t="n"/>
+      <c r="AE24" s="573" t="n"/>
+      <c r="AF24" s="573" t="n"/>
+      <c r="AG24" s="573" t="n"/>
+      <c r="AH24" s="573" t="n"/>
+      <c r="AI24" s="573" t="n"/>
+      <c r="AJ24" s="573" t="n"/>
+      <c r="AK24" s="573" t="n"/>
+      <c r="AL24" s="573" t="n"/>
+      <c r="AM24" s="573" t="n"/>
+      <c r="AN24" s="573" t="n"/>
+      <c r="AO24" s="573" t="n"/>
+      <c r="AP24" s="573" t="n"/>
+      <c r="AQ24" s="574" t="n"/>
+      <c r="AR24" s="572" t="n"/>
+      <c r="AS24" s="573" t="n"/>
+      <c r="AT24" s="573" t="n"/>
+      <c r="AU24" s="573" t="n"/>
+      <c r="AV24" s="573" t="n"/>
+      <c r="AW24" s="574" t="n"/>
+      <c r="AX24" s="572" t="n"/>
+      <c r="AY24" s="573" t="n"/>
+      <c r="AZ24" s="573" t="n"/>
+      <c r="BA24" s="574" t="n"/>
+      <c r="BB24" s="591" t="n"/>
+      <c r="BC24" s="573" t="n"/>
+      <c r="BD24" s="576" t="n"/>
     </row>
     <row r="25" ht="3" customHeight="1">
-      <c r="A25" s="377" t="n"/>
-      <c r="B25" s="353" t="n"/>
-      <c r="C25" s="353" t="n"/>
-      <c r="D25" s="378" t="n"/>
-      <c r="E25" s="353" t="n"/>
-      <c r="F25" s="353" t="n"/>
-      <c r="G25" s="353" t="n"/>
-      <c r="H25" s="365" t="n"/>
-      <c r="I25" s="353" t="n"/>
-      <c r="J25" s="353" t="n"/>
-      <c r="K25" s="353" t="n"/>
-      <c r="L25" s="353" t="n"/>
-      <c r="M25" s="353" t="n"/>
-      <c r="N25" s="353" t="n"/>
-      <c r="O25" s="353" t="n"/>
-      <c r="P25" s="353" t="n"/>
-      <c r="Q25" s="353" t="n"/>
-      <c r="R25" s="353" t="n"/>
-      <c r="S25" s="353" t="n"/>
-      <c r="T25" s="353" t="n"/>
-      <c r="U25" s="353" t="n"/>
-      <c r="V25" s="353" t="n"/>
-      <c r="W25" s="353" t="n"/>
-      <c r="X25" s="353" t="n"/>
-      <c r="Y25" s="353" t="n"/>
-      <c r="Z25" s="353" t="n"/>
-      <c r="AA25" s="379" t="n"/>
-      <c r="AB25" s="353" t="n"/>
-      <c r="AC25" s="353" t="n"/>
-      <c r="AD25" s="353" t="n"/>
-      <c r="AE25" s="353" t="n"/>
-      <c r="AF25" s="353" t="n"/>
-      <c r="AG25" s="353" t="n"/>
-      <c r="AH25" s="353" t="n"/>
-      <c r="AI25" s="353" t="n"/>
-      <c r="AJ25" s="353" t="n"/>
-      <c r="AK25" s="353" t="n"/>
-      <c r="AL25" s="353" t="n"/>
-      <c r="AM25" s="353" t="n"/>
-      <c r="AN25" s="353" t="n"/>
-      <c r="AO25" s="353" t="n"/>
-      <c r="AP25" s="353" t="n"/>
-      <c r="AQ25" s="353" t="n"/>
-      <c r="AR25" s="380" t="n"/>
-      <c r="AS25" s="353" t="n"/>
-      <c r="AT25" s="353" t="n"/>
-      <c r="AU25" s="353" t="n"/>
-      <c r="AV25" s="353" t="n"/>
-      <c r="AW25" s="353" t="n"/>
-      <c r="AX25" s="380" t="n"/>
-      <c r="AY25" s="353" t="n"/>
-      <c r="AZ25" s="353" t="n"/>
-      <c r="BA25" s="353" t="n"/>
-      <c r="BB25" s="381" t="n"/>
-      <c r="BC25" s="353" t="n"/>
-      <c r="BD25" s="353" t="n"/>
+      <c r="A25" s="592" t="n"/>
+      <c r="B25" s="578" t="n"/>
+      <c r="C25" s="578" t="n"/>
+      <c r="D25" s="593" t="n"/>
+      <c r="E25" s="578" t="n"/>
+      <c r="F25" s="578" t="n"/>
+      <c r="G25" s="578" t="n"/>
+      <c r="H25" s="579" t="n"/>
+      <c r="I25" s="578" t="n"/>
+      <c r="J25" s="578" t="n"/>
+      <c r="K25" s="578" t="n"/>
+      <c r="L25" s="578" t="n"/>
+      <c r="M25" s="578" t="n"/>
+      <c r="N25" s="578" t="n"/>
+      <c r="O25" s="578" t="n"/>
+      <c r="P25" s="578" t="n"/>
+      <c r="Q25" s="578" t="n"/>
+      <c r="R25" s="578" t="n"/>
+      <c r="S25" s="578" t="n"/>
+      <c r="T25" s="578" t="n"/>
+      <c r="U25" s="578" t="n"/>
+      <c r="V25" s="578" t="n"/>
+      <c r="W25" s="578" t="n"/>
+      <c r="X25" s="578" t="n"/>
+      <c r="Y25" s="578" t="n"/>
+      <c r="Z25" s="578" t="n"/>
+      <c r="AA25" s="594" t="n"/>
+      <c r="AB25" s="578" t="n"/>
+      <c r="AC25" s="578" t="n"/>
+      <c r="AD25" s="578" t="n"/>
+      <c r="AE25" s="578" t="n"/>
+      <c r="AF25" s="578" t="n"/>
+      <c r="AG25" s="578" t="n"/>
+      <c r="AH25" s="578" t="n"/>
+      <c r="AI25" s="578" t="n"/>
+      <c r="AJ25" s="578" t="n"/>
+      <c r="AK25" s="578" t="n"/>
+      <c r="AL25" s="578" t="n"/>
+      <c r="AM25" s="578" t="n"/>
+      <c r="AN25" s="578" t="n"/>
+      <c r="AO25" s="578" t="n"/>
+      <c r="AP25" s="578" t="n"/>
+      <c r="AQ25" s="578" t="n"/>
+      <c r="AR25" s="595" t="n"/>
+      <c r="AS25" s="578" t="n"/>
+      <c r="AT25" s="578" t="n"/>
+      <c r="AU25" s="578" t="n"/>
+      <c r="AV25" s="578" t="n"/>
+      <c r="AW25" s="578" t="n"/>
+      <c r="AX25" s="595" t="n"/>
+      <c r="AY25" s="578" t="n"/>
+      <c r="AZ25" s="578" t="n"/>
+      <c r="BA25" s="578" t="n"/>
+      <c r="BB25" s="596" t="n"/>
+      <c r="BC25" s="578" t="n"/>
+      <c r="BD25" s="578" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="466" t="inlineStr">
+      <c r="A26" s="558" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B26" s="467" t="n"/>
-      <c r="C26" s="467" t="n"/>
-      <c r="D26" s="467" t="n"/>
-      <c r="E26" s="467" t="n"/>
-      <c r="F26" s="467" t="n"/>
-      <c r="G26" s="467" t="n"/>
-      <c r="H26" s="467" t="n"/>
-      <c r="I26" s="467" t="n"/>
-      <c r="J26" s="467" t="n"/>
-      <c r="K26" s="467" t="n"/>
-      <c r="L26" s="467" t="n"/>
-      <c r="M26" s="467" t="n"/>
-      <c r="N26" s="467" t="n"/>
-      <c r="O26" s="467" t="n"/>
-      <c r="P26" s="467" t="n"/>
-      <c r="Q26" s="467" t="n"/>
-      <c r="R26" s="467" t="n"/>
-      <c r="S26" s="467" t="n"/>
-      <c r="T26" s="467" t="n"/>
-      <c r="U26" s="467" t="n"/>
-      <c r="V26" s="467" t="n"/>
-      <c r="W26" s="467" t="n"/>
-      <c r="X26" s="467" t="n"/>
-      <c r="Y26" s="467" t="n"/>
-      <c r="Z26" s="467" t="n"/>
-      <c r="AA26" s="467" t="n"/>
-      <c r="AB26" s="467" t="n"/>
-      <c r="AC26" s="467" t="n"/>
-      <c r="AD26" s="467" t="n"/>
-      <c r="AE26" s="467" t="n"/>
-      <c r="AF26" s="467" t="n"/>
-      <c r="AG26" s="467" t="n"/>
-      <c r="AH26" s="467" t="n"/>
-      <c r="AI26" s="467" t="n"/>
-      <c r="AJ26" s="467" t="n"/>
-      <c r="AK26" s="467" t="n"/>
-      <c r="AL26" s="467" t="n"/>
-      <c r="AM26" s="467" t="n"/>
-      <c r="AN26" s="467" t="n"/>
-      <c r="AO26" s="467" t="n"/>
-      <c r="AP26" s="467" t="n"/>
-      <c r="AQ26" s="467" t="n"/>
-      <c r="AR26" s="467" t="n"/>
-      <c r="AS26" s="467" t="n"/>
-      <c r="AT26" s="467" t="n"/>
-      <c r="AU26" s="467" t="n"/>
-      <c r="AV26" s="467" t="n"/>
-      <c r="AW26" s="467" t="n"/>
-      <c r="AX26" s="467" t="n"/>
-      <c r="AY26" s="467" t="n"/>
-      <c r="AZ26" s="467" t="n"/>
-      <c r="BA26" s="467" t="n"/>
-      <c r="BB26" s="467" t="n"/>
-      <c r="BC26" s="467" t="n"/>
-      <c r="BD26" s="468" t="n"/>
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="27" t="n"/>
+      <c r="J26" s="27" t="n"/>
+      <c r="K26" s="27" t="n"/>
+      <c r="L26" s="27" t="n"/>
+      <c r="M26" s="27" t="n"/>
+      <c r="N26" s="27" t="n"/>
+      <c r="O26" s="27" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="27" t="n"/>
+      <c r="S26" s="27" t="n"/>
+      <c r="T26" s="27" t="n"/>
+      <c r="U26" s="27" t="n"/>
+      <c r="V26" s="27" t="n"/>
+      <c r="W26" s="27" t="n"/>
+      <c r="X26" s="27" t="n"/>
+      <c r="Y26" s="27" t="n"/>
+      <c r="Z26" s="27" t="n"/>
+      <c r="AA26" s="27" t="n"/>
+      <c r="AB26" s="27" t="n"/>
+      <c r="AC26" s="27" t="n"/>
+      <c r="AD26" s="27" t="n"/>
+      <c r="AE26" s="27" t="n"/>
+      <c r="AF26" s="27" t="n"/>
+      <c r="AG26" s="27" t="n"/>
+      <c r="AH26" s="27" t="n"/>
+      <c r="AI26" s="27" t="n"/>
+      <c r="AJ26" s="27" t="n"/>
+      <c r="AK26" s="27" t="n"/>
+      <c r="AL26" s="27" t="n"/>
+      <c r="AM26" s="27" t="n"/>
+      <c r="AN26" s="27" t="n"/>
+      <c r="AO26" s="27" t="n"/>
+      <c r="AP26" s="27" t="n"/>
+      <c r="AQ26" s="27" t="n"/>
+      <c r="AR26" s="27" t="n"/>
+      <c r="AS26" s="27" t="n"/>
+      <c r="AT26" s="27" t="n"/>
+      <c r="AU26" s="27" t="n"/>
+      <c r="AV26" s="27" t="n"/>
+      <c r="AW26" s="27" t="n"/>
+      <c r="AX26" s="27" t="n"/>
+      <c r="AY26" s="27" t="n"/>
+      <c r="AZ26" s="27" t="n"/>
+      <c r="BA26" s="27" t="n"/>
+      <c r="BB26" s="27" t="n"/>
+      <c r="BC26" s="27" t="n"/>
+      <c r="BD26" s="28" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="469" t="inlineStr">
+      <c r="A27" s="559" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="B27" s="470" t="n"/>
-      <c r="C27" s="470" t="n"/>
-      <c r="D27" s="470" t="n"/>
-      <c r="E27" s="470" t="n"/>
-      <c r="F27" s="470" t="n"/>
-      <c r="G27" s="470" t="n"/>
-      <c r="H27" s="470" t="n"/>
-      <c r="I27" s="470" t="n"/>
-      <c r="J27" s="470" t="n"/>
-      <c r="K27" s="471" t="n"/>
-      <c r="L27" s="472" t="n"/>
-      <c r="M27" s="472" t="n"/>
-      <c r="N27" s="472" t="n"/>
-      <c r="O27" s="472" t="n"/>
-      <c r="P27" s="472" t="n"/>
-      <c r="Q27" s="472" t="n"/>
-      <c r="R27" s="472" t="n"/>
-      <c r="S27" s="472" t="n"/>
-      <c r="T27" s="472" t="n"/>
-      <c r="U27" s="472" t="n"/>
-      <c r="V27" s="472" t="n"/>
-      <c r="W27" s="472" t="n"/>
-      <c r="X27" s="472" t="n"/>
-      <c r="Y27" s="472" t="n"/>
-      <c r="Z27" s="472" t="n"/>
-      <c r="AA27" s="472" t="n"/>
-      <c r="AB27" s="472" t="n"/>
-      <c r="AC27" s="473" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="560" t="n"/>
+      <c r="L27" s="561" t="n"/>
+      <c r="M27" s="561" t="n"/>
+      <c r="N27" s="561" t="n"/>
+      <c r="O27" s="561" t="n"/>
+      <c r="P27" s="561" t="n"/>
+      <c r="Q27" s="561" t="n"/>
+      <c r="R27" s="561" t="n"/>
+      <c r="S27" s="561" t="n"/>
+      <c r="T27" s="561" t="n"/>
+      <c r="U27" s="561" t="n"/>
+      <c r="V27" s="561" t="n"/>
+      <c r="W27" s="561" t="n"/>
+      <c r="X27" s="561" t="n"/>
+      <c r="Y27" s="561" t="n"/>
+      <c r="Z27" s="561" t="n"/>
+      <c r="AA27" s="561" t="n"/>
+      <c r="AB27" s="562" t="n"/>
+      <c r="AC27" s="563" t="inlineStr">
         <is>
           <t>AQL Disposition</t>
         </is>
       </c>
-      <c r="AD27" s="470" t="n"/>
-      <c r="AE27" s="470" t="n"/>
-      <c r="AF27" s="470" t="n"/>
-      <c r="AG27" s="470" t="n"/>
-      <c r="AH27" s="470" t="n"/>
-      <c r="AI27" s="470" t="n"/>
-      <c r="AJ27" s="470" t="n"/>
-      <c r="AK27" s="470" t="n"/>
-      <c r="AL27" s="470" t="n"/>
-      <c r="AM27" s="471" t="n"/>
-      <c r="AN27" s="472" t="n"/>
-      <c r="AO27" s="472" t="n"/>
-      <c r="AP27" s="472" t="n"/>
-      <c r="AQ27" s="472" t="n"/>
-      <c r="AR27" s="472" t="n"/>
-      <c r="AS27" s="472" t="n"/>
-      <c r="AT27" s="472" t="n"/>
-      <c r="AU27" s="472" t="n"/>
-      <c r="AV27" s="472" t="n"/>
-      <c r="AW27" s="472" t="n"/>
-      <c r="AX27" s="472" t="n"/>
-      <c r="AY27" s="472" t="n"/>
-      <c r="AZ27" s="472" t="n"/>
-      <c r="BA27" s="472" t="n"/>
-      <c r="BB27" s="472" t="n"/>
-      <c r="BC27" s="472" t="n"/>
-      <c r="BD27" s="474" t="n"/>
+      <c r="AD27" s="5" t="n"/>
+      <c r="AE27" s="5" t="n"/>
+      <c r="AF27" s="5" t="n"/>
+      <c r="AG27" s="5" t="n"/>
+      <c r="AH27" s="5" t="n"/>
+      <c r="AI27" s="5" t="n"/>
+      <c r="AJ27" s="5" t="n"/>
+      <c r="AK27" s="5" t="n"/>
+      <c r="AL27" s="6" t="n"/>
+      <c r="AM27" s="560" t="n"/>
+      <c r="AN27" s="561" t="n"/>
+      <c r="AO27" s="561" t="n"/>
+      <c r="AP27" s="561" t="n"/>
+      <c r="AQ27" s="561" t="n"/>
+      <c r="AR27" s="561" t="n"/>
+      <c r="AS27" s="561" t="n"/>
+      <c r="AT27" s="561" t="n"/>
+      <c r="AU27" s="561" t="n"/>
+      <c r="AV27" s="561" t="n"/>
+      <c r="AW27" s="561" t="n"/>
+      <c r="AX27" s="561" t="n"/>
+      <c r="AY27" s="561" t="n"/>
+      <c r="AZ27" s="561" t="n"/>
+      <c r="BA27" s="561" t="n"/>
+      <c r="BB27" s="561" t="n"/>
+      <c r="BC27" s="561" t="n"/>
+      <c r="BD27" s="564" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="475" t="inlineStr">
+      <c r="A28" s="565" t="inlineStr">
         <is>
           <t>100% Sort Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B28" s="344" t="n"/>
-      <c r="C28" s="344" t="n"/>
-      <c r="D28" s="344" t="n"/>
-      <c r="E28" s="344" t="n"/>
-      <c r="F28" s="344" t="n"/>
-      <c r="G28" s="344" t="n"/>
-      <c r="H28" s="344" t="n"/>
-      <c r="I28" s="344" t="n"/>
-      <c r="J28" s="344" t="n"/>
-      <c r="K28" s="476" t="n"/>
-      <c r="L28" s="362" t="n"/>
-      <c r="M28" s="362" t="n"/>
-      <c r="N28" s="362" t="n"/>
-      <c r="O28" s="362" t="n"/>
-      <c r="P28" s="362" t="n"/>
-      <c r="Q28" s="362" t="n"/>
-      <c r="R28" s="362" t="n"/>
-      <c r="S28" s="362" t="n"/>
-      <c r="T28" s="362" t="n"/>
-      <c r="U28" s="362" t="n"/>
-      <c r="V28" s="362" t="n"/>
-      <c r="W28" s="362" t="n"/>
-      <c r="X28" s="362" t="n"/>
-      <c r="Y28" s="362" t="n"/>
-      <c r="Z28" s="362" t="n"/>
-      <c r="AA28" s="362" t="n"/>
-      <c r="AB28" s="362" t="n"/>
-      <c r="AC28" s="477" t="inlineStr">
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="566" t="n"/>
+      <c r="L28" s="567" t="n"/>
+      <c r="M28" s="567" t="n"/>
+      <c r="N28" s="567" t="n"/>
+      <c r="O28" s="567" t="n"/>
+      <c r="P28" s="567" t="n"/>
+      <c r="Q28" s="567" t="n"/>
+      <c r="R28" s="567" t="n"/>
+      <c r="S28" s="567" t="n"/>
+      <c r="T28" s="567" t="n"/>
+      <c r="U28" s="567" t="n"/>
+      <c r="V28" s="567" t="n"/>
+      <c r="W28" s="567" t="n"/>
+      <c r="X28" s="567" t="n"/>
+      <c r="Y28" s="567" t="n"/>
+      <c r="Z28" s="567" t="n"/>
+      <c r="AA28" s="567" t="n"/>
+      <c r="AB28" s="568" t="n"/>
+      <c r="AC28" s="569" t="inlineStr">
         <is>
           <t>Linked NCR Ref</t>
         </is>
       </c>
-      <c r="AD28" s="344" t="n"/>
-      <c r="AE28" s="344" t="n"/>
-      <c r="AF28" s="344" t="n"/>
-      <c r="AG28" s="344" t="n"/>
-      <c r="AH28" s="344" t="n"/>
-      <c r="AI28" s="344" t="n"/>
-      <c r="AJ28" s="344" t="n"/>
-      <c r="AK28" s="344" t="n"/>
-      <c r="AL28" s="344" t="n"/>
-      <c r="AM28" s="476" t="n"/>
-      <c r="AN28" s="362" t="n"/>
-      <c r="AO28" s="362" t="n"/>
-      <c r="AP28" s="362" t="n"/>
-      <c r="AQ28" s="362" t="n"/>
-      <c r="AR28" s="362" t="n"/>
-      <c r="AS28" s="362" t="n"/>
-      <c r="AT28" s="362" t="n"/>
-      <c r="AU28" s="362" t="n"/>
-      <c r="AV28" s="362" t="n"/>
-      <c r="AW28" s="362" t="n"/>
-      <c r="AX28" s="362" t="n"/>
-      <c r="AY28" s="362" t="n"/>
-      <c r="AZ28" s="362" t="n"/>
-      <c r="BA28" s="362" t="n"/>
-      <c r="BB28" s="362" t="n"/>
-      <c r="BC28" s="362" t="n"/>
-      <c r="BD28" s="478" t="n"/>
+      <c r="AD28" s="12" t="n"/>
+      <c r="AE28" s="12" t="n"/>
+      <c r="AF28" s="12" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="12" t="n"/>
+      <c r="AI28" s="12" t="n"/>
+      <c r="AJ28" s="12" t="n"/>
+      <c r="AK28" s="12" t="n"/>
+      <c r="AL28" s="13" t="n"/>
+      <c r="AM28" s="566" t="n"/>
+      <c r="AN28" s="567" t="n"/>
+      <c r="AO28" s="567" t="n"/>
+      <c r="AP28" s="567" t="n"/>
+      <c r="AQ28" s="567" t="n"/>
+      <c r="AR28" s="567" t="n"/>
+      <c r="AS28" s="567" t="n"/>
+      <c r="AT28" s="567" t="n"/>
+      <c r="AU28" s="567" t="n"/>
+      <c r="AV28" s="567" t="n"/>
+      <c r="AW28" s="567" t="n"/>
+      <c r="AX28" s="567" t="n"/>
+      <c r="AY28" s="567" t="n"/>
+      <c r="AZ28" s="567" t="n"/>
+      <c r="BA28" s="567" t="n"/>
+      <c r="BB28" s="567" t="n"/>
+      <c r="BC28" s="567" t="n"/>
+      <c r="BD28" s="570" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="479" t="inlineStr">
+      <c r="A29" s="571" t="inlineStr">
         <is>
           <t>Lot Release Decision</t>
         </is>
       </c>
-      <c r="B29" s="480" t="n"/>
-      <c r="C29" s="480" t="n"/>
-      <c r="D29" s="480" t="n"/>
-      <c r="E29" s="480" t="n"/>
-      <c r="F29" s="480" t="n"/>
-      <c r="G29" s="480" t="n"/>
-      <c r="H29" s="480" t="n"/>
-      <c r="I29" s="480" t="n"/>
-      <c r="J29" s="480" t="n"/>
-      <c r="K29" s="481" t="n"/>
-      <c r="L29" s="482" t="n"/>
-      <c r="M29" s="482" t="n"/>
-      <c r="N29" s="482" t="n"/>
-      <c r="O29" s="482" t="n"/>
-      <c r="P29" s="482" t="n"/>
-      <c r="Q29" s="482" t="n"/>
-      <c r="R29" s="482" t="n"/>
-      <c r="S29" s="482" t="n"/>
-      <c r="T29" s="482" t="n"/>
-      <c r="U29" s="482" t="n"/>
-      <c r="V29" s="482" t="n"/>
-      <c r="W29" s="482" t="n"/>
-      <c r="X29" s="482" t="n"/>
-      <c r="Y29" s="482" t="n"/>
-      <c r="Z29" s="482" t="n"/>
-      <c r="AA29" s="482" t="n"/>
-      <c r="AB29" s="482" t="n"/>
-      <c r="AC29" s="483" t="inlineStr">
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="572" t="n"/>
+      <c r="L29" s="573" t="n"/>
+      <c r="M29" s="573" t="n"/>
+      <c r="N29" s="573" t="n"/>
+      <c r="O29" s="573" t="n"/>
+      <c r="P29" s="573" t="n"/>
+      <c r="Q29" s="573" t="n"/>
+      <c r="R29" s="573" t="n"/>
+      <c r="S29" s="573" t="n"/>
+      <c r="T29" s="573" t="n"/>
+      <c r="U29" s="573" t="n"/>
+      <c r="V29" s="573" t="n"/>
+      <c r="W29" s="573" t="n"/>
+      <c r="X29" s="573" t="n"/>
+      <c r="Y29" s="573" t="n"/>
+      <c r="Z29" s="573" t="n"/>
+      <c r="AA29" s="573" t="n"/>
+      <c r="AB29" s="574" t="n"/>
+      <c r="AC29" s="575" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="AD29" s="480" t="n"/>
-      <c r="AE29" s="480" t="n"/>
-      <c r="AF29" s="480" t="n"/>
-      <c r="AG29" s="480" t="n"/>
-      <c r="AH29" s="480" t="n"/>
-      <c r="AI29" s="480" t="n"/>
-      <c r="AJ29" s="480" t="n"/>
-      <c r="AK29" s="480" t="n"/>
-      <c r="AL29" s="480" t="n"/>
-      <c r="AM29" s="481" t="n"/>
-      <c r="AN29" s="482" t="n"/>
-      <c r="AO29" s="482" t="n"/>
-      <c r="AP29" s="482" t="n"/>
-      <c r="AQ29" s="482" t="n"/>
-      <c r="AR29" s="482" t="n"/>
-      <c r="AS29" s="482" t="n"/>
-      <c r="AT29" s="482" t="n"/>
-      <c r="AU29" s="482" t="n"/>
-      <c r="AV29" s="482" t="n"/>
-      <c r="AW29" s="482" t="n"/>
-      <c r="AX29" s="482" t="n"/>
-      <c r="AY29" s="482" t="n"/>
-      <c r="AZ29" s="482" t="n"/>
-      <c r="BA29" s="482" t="n"/>
-      <c r="BB29" s="482" t="n"/>
-      <c r="BC29" s="482" t="n"/>
-      <c r="BD29" s="484" t="n"/>
+      <c r="AD29" s="19" t="n"/>
+      <c r="AE29" s="19" t="n"/>
+      <c r="AF29" s="19" t="n"/>
+      <c r="AG29" s="19" t="n"/>
+      <c r="AH29" s="19" t="n"/>
+      <c r="AI29" s="19" t="n"/>
+      <c r="AJ29" s="19" t="n"/>
+      <c r="AK29" s="19" t="n"/>
+      <c r="AL29" s="22" t="n"/>
+      <c r="AM29" s="572" t="n"/>
+      <c r="AN29" s="573" t="n"/>
+      <c r="AO29" s="573" t="n"/>
+      <c r="AP29" s="573" t="n"/>
+      <c r="AQ29" s="573" t="n"/>
+      <c r="AR29" s="573" t="n"/>
+      <c r="AS29" s="573" t="n"/>
+      <c r="AT29" s="573" t="n"/>
+      <c r="AU29" s="573" t="n"/>
+      <c r="AV29" s="573" t="n"/>
+      <c r="AW29" s="573" t="n"/>
+      <c r="AX29" s="573" t="n"/>
+      <c r="AY29" s="573" t="n"/>
+      <c r="AZ29" s="573" t="n"/>
+      <c r="BA29" s="573" t="n"/>
+      <c r="BB29" s="573" t="n"/>
+      <c r="BC29" s="573" t="n"/>
+      <c r="BD29" s="576" t="n"/>
     </row>
     <row r="30" ht="3" customHeight="1">
-      <c r="A30" s="377" t="n"/>
-      <c r="B30" s="353" t="n"/>
-      <c r="C30" s="353" t="n"/>
-      <c r="D30" s="378" t="n"/>
-      <c r="E30" s="353" t="n"/>
-      <c r="F30" s="353" t="n"/>
-      <c r="G30" s="353" t="n"/>
-      <c r="H30" s="365" t="n"/>
-      <c r="I30" s="353" t="n"/>
-      <c r="J30" s="353" t="n"/>
-      <c r="K30" s="353" t="n"/>
-      <c r="L30" s="353" t="n"/>
-      <c r="M30" s="353" t="n"/>
-      <c r="N30" s="353" t="n"/>
-      <c r="O30" s="353" t="n"/>
-      <c r="P30" s="353" t="n"/>
-      <c r="Q30" s="353" t="n"/>
-      <c r="R30" s="353" t="n"/>
-      <c r="S30" s="353" t="n"/>
-      <c r="T30" s="353" t="n"/>
-      <c r="U30" s="353" t="n"/>
-      <c r="V30" s="353" t="n"/>
-      <c r="W30" s="353" t="n"/>
-      <c r="X30" s="353" t="n"/>
-      <c r="Y30" s="353" t="n"/>
-      <c r="Z30" s="353" t="n"/>
-      <c r="AA30" s="379" t="n"/>
-      <c r="AB30" s="353" t="n"/>
-      <c r="AC30" s="353" t="n"/>
-      <c r="AD30" s="353" t="n"/>
-      <c r="AE30" s="353" t="n"/>
-      <c r="AF30" s="353" t="n"/>
-      <c r="AG30" s="353" t="n"/>
-      <c r="AH30" s="353" t="n"/>
-      <c r="AI30" s="353" t="n"/>
-      <c r="AJ30" s="353" t="n"/>
-      <c r="AK30" s="353" t="n"/>
-      <c r="AL30" s="353" t="n"/>
-      <c r="AM30" s="353" t="n"/>
-      <c r="AN30" s="353" t="n"/>
-      <c r="AO30" s="353" t="n"/>
-      <c r="AP30" s="353" t="n"/>
-      <c r="AQ30" s="353" t="n"/>
-      <c r="AR30" s="380" t="n"/>
-      <c r="AS30" s="353" t="n"/>
-      <c r="AT30" s="353" t="n"/>
-      <c r="AU30" s="353" t="n"/>
-      <c r="AV30" s="353" t="n"/>
-      <c r="AW30" s="353" t="n"/>
-      <c r="AX30" s="380" t="n"/>
-      <c r="AY30" s="353" t="n"/>
-      <c r="AZ30" s="353" t="n"/>
-      <c r="BA30" s="353" t="n"/>
-      <c r="BB30" s="381" t="n"/>
-      <c r="BC30" s="353" t="n"/>
-      <c r="BD30" s="353" t="n"/>
+      <c r="A30" s="592" t="n"/>
+      <c r="B30" s="578" t="n"/>
+      <c r="C30" s="578" t="n"/>
+      <c r="D30" s="593" t="n"/>
+      <c r="E30" s="578" t="n"/>
+      <c r="F30" s="578" t="n"/>
+      <c r="G30" s="578" t="n"/>
+      <c r="H30" s="579" t="n"/>
+      <c r="I30" s="578" t="n"/>
+      <c r="J30" s="578" t="n"/>
+      <c r="K30" s="578" t="n"/>
+      <c r="L30" s="578" t="n"/>
+      <c r="M30" s="578" t="n"/>
+      <c r="N30" s="578" t="n"/>
+      <c r="O30" s="578" t="n"/>
+      <c r="P30" s="578" t="n"/>
+      <c r="Q30" s="578" t="n"/>
+      <c r="R30" s="578" t="n"/>
+      <c r="S30" s="578" t="n"/>
+      <c r="T30" s="578" t="n"/>
+      <c r="U30" s="578" t="n"/>
+      <c r="V30" s="578" t="n"/>
+      <c r="W30" s="578" t="n"/>
+      <c r="X30" s="578" t="n"/>
+      <c r="Y30" s="578" t="n"/>
+      <c r="Z30" s="578" t="n"/>
+      <c r="AA30" s="594" t="n"/>
+      <c r="AB30" s="578" t="n"/>
+      <c r="AC30" s="578" t="n"/>
+      <c r="AD30" s="578" t="n"/>
+      <c r="AE30" s="578" t="n"/>
+      <c r="AF30" s="578" t="n"/>
+      <c r="AG30" s="578" t="n"/>
+      <c r="AH30" s="578" t="n"/>
+      <c r="AI30" s="578" t="n"/>
+      <c r="AJ30" s="578" t="n"/>
+      <c r="AK30" s="578" t="n"/>
+      <c r="AL30" s="578" t="n"/>
+      <c r="AM30" s="578" t="n"/>
+      <c r="AN30" s="578" t="n"/>
+      <c r="AO30" s="578" t="n"/>
+      <c r="AP30" s="578" t="n"/>
+      <c r="AQ30" s="578" t="n"/>
+      <c r="AR30" s="595" t="n"/>
+      <c r="AS30" s="578" t="n"/>
+      <c r="AT30" s="578" t="n"/>
+      <c r="AU30" s="578" t="n"/>
+      <c r="AV30" s="578" t="n"/>
+      <c r="AW30" s="578" t="n"/>
+      <c r="AX30" s="595" t="n"/>
+      <c r="AY30" s="578" t="n"/>
+      <c r="AZ30" s="578" t="n"/>
+      <c r="BA30" s="578" t="n"/>
+      <c r="BB30" s="596" t="n"/>
+      <c r="BC30" s="578" t="n"/>
+      <c r="BD30" s="578" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="466" t="inlineStr">
+      <c r="A31" s="558" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B31" s="467" t="n"/>
-      <c r="C31" s="467" t="n"/>
-      <c r="D31" s="467" t="n"/>
-      <c r="E31" s="467" t="n"/>
-      <c r="F31" s="467" t="n"/>
-      <c r="G31" s="467" t="n"/>
-      <c r="H31" s="467" t="n"/>
-      <c r="I31" s="467" t="n"/>
-      <c r="J31" s="467" t="n"/>
-      <c r="K31" s="467" t="n"/>
-      <c r="L31" s="467" t="n"/>
-      <c r="M31" s="467" t="n"/>
-      <c r="N31" s="467" t="n"/>
-      <c r="O31" s="467" t="n"/>
-      <c r="P31" s="467" t="n"/>
-      <c r="Q31" s="467" t="n"/>
-      <c r="R31" s="467" t="n"/>
-      <c r="S31" s="467" t="n"/>
-      <c r="T31" s="467" t="n"/>
-      <c r="U31" s="467" t="n"/>
-      <c r="V31" s="467" t="n"/>
-      <c r="W31" s="467" t="n"/>
-      <c r="X31" s="467" t="n"/>
-      <c r="Y31" s="467" t="n"/>
-      <c r="Z31" s="467" t="n"/>
-      <c r="AA31" s="467" t="n"/>
-      <c r="AB31" s="467" t="n"/>
-      <c r="AC31" s="467" t="n"/>
-      <c r="AD31" s="467" t="n"/>
-      <c r="AE31" s="467" t="n"/>
-      <c r="AF31" s="467" t="n"/>
-      <c r="AG31" s="467" t="n"/>
-      <c r="AH31" s="467" t="n"/>
-      <c r="AI31" s="467" t="n"/>
-      <c r="AJ31" s="467" t="n"/>
-      <c r="AK31" s="467" t="n"/>
-      <c r="AL31" s="467" t="n"/>
-      <c r="AM31" s="467" t="n"/>
-      <c r="AN31" s="467" t="n"/>
-      <c r="AO31" s="467" t="n"/>
-      <c r="AP31" s="467" t="n"/>
-      <c r="AQ31" s="467" t="n"/>
-      <c r="AR31" s="467" t="n"/>
-      <c r="AS31" s="467" t="n"/>
-      <c r="AT31" s="467" t="n"/>
-      <c r="AU31" s="467" t="n"/>
-      <c r="AV31" s="467" t="n"/>
-      <c r="AW31" s="467" t="n"/>
-      <c r="AX31" s="467" t="n"/>
-      <c r="AY31" s="467" t="n"/>
-      <c r="AZ31" s="467" t="n"/>
-      <c r="BA31" s="467" t="n"/>
-      <c r="BB31" s="467" t="n"/>
-      <c r="BC31" s="467" t="n"/>
-      <c r="BD31" s="468" t="n"/>
+      <c r="B31" s="27" t="n"/>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="27" t="n"/>
+      <c r="H31" s="27" t="n"/>
+      <c r="I31" s="27" t="n"/>
+      <c r="J31" s="27" t="n"/>
+      <c r="K31" s="27" t="n"/>
+      <c r="L31" s="27" t="n"/>
+      <c r="M31" s="27" t="n"/>
+      <c r="N31" s="27" t="n"/>
+      <c r="O31" s="27" t="n"/>
+      <c r="P31" s="27" t="n"/>
+      <c r="Q31" s="27" t="n"/>
+      <c r="R31" s="27" t="n"/>
+      <c r="S31" s="27" t="n"/>
+      <c r="T31" s="27" t="n"/>
+      <c r="U31" s="27" t="n"/>
+      <c r="V31" s="27" t="n"/>
+      <c r="W31" s="27" t="n"/>
+      <c r="X31" s="27" t="n"/>
+      <c r="Y31" s="27" t="n"/>
+      <c r="Z31" s="27" t="n"/>
+      <c r="AA31" s="27" t="n"/>
+      <c r="AB31" s="27" t="n"/>
+      <c r="AC31" s="27" t="n"/>
+      <c r="AD31" s="27" t="n"/>
+      <c r="AE31" s="27" t="n"/>
+      <c r="AF31" s="27" t="n"/>
+      <c r="AG31" s="27" t="n"/>
+      <c r="AH31" s="27" t="n"/>
+      <c r="AI31" s="27" t="n"/>
+      <c r="AJ31" s="27" t="n"/>
+      <c r="AK31" s="27" t="n"/>
+      <c r="AL31" s="27" t="n"/>
+      <c r="AM31" s="27" t="n"/>
+      <c r="AN31" s="27" t="n"/>
+      <c r="AO31" s="27" t="n"/>
+      <c r="AP31" s="27" t="n"/>
+      <c r="AQ31" s="27" t="n"/>
+      <c r="AR31" s="27" t="n"/>
+      <c r="AS31" s="27" t="n"/>
+      <c r="AT31" s="27" t="n"/>
+      <c r="AU31" s="27" t="n"/>
+      <c r="AV31" s="27" t="n"/>
+      <c r="AW31" s="27" t="n"/>
+      <c r="AX31" s="27" t="n"/>
+      <c r="AY31" s="27" t="n"/>
+      <c r="AZ31" s="27" t="n"/>
+      <c r="BA31" s="27" t="n"/>
+      <c r="BB31" s="27" t="n"/>
+      <c r="BC31" s="27" t="n"/>
+      <c r="BD31" s="28" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="489" t="inlineStr">
+      <c r="A32" s="580" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B32" s="470" t="n"/>
-      <c r="C32" s="470" t="n"/>
-      <c r="D32" s="470" t="n"/>
-      <c r="E32" s="470" t="n"/>
-      <c r="F32" s="470" t="n"/>
-      <c r="G32" s="470" t="n"/>
-      <c r="H32" s="470" t="n"/>
-      <c r="I32" s="470" t="n"/>
-      <c r="J32" s="470" t="n"/>
-      <c r="K32" s="470" t="n"/>
-      <c r="L32" s="470" t="n"/>
-      <c r="M32" s="470" t="n"/>
-      <c r="N32" s="470" t="n"/>
-      <c r="O32" s="470" t="n"/>
-      <c r="P32" s="470" t="n"/>
-      <c r="Q32" s="470" t="n"/>
-      <c r="R32" s="470" t="n"/>
-      <c r="S32" s="501" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="597" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T32" s="470" t="n"/>
-      <c r="U32" s="470" t="n"/>
-      <c r="V32" s="470" t="n"/>
-      <c r="W32" s="470" t="n"/>
-      <c r="X32" s="470" t="n"/>
-      <c r="Y32" s="470" t="n"/>
-      <c r="Z32" s="470" t="n"/>
-      <c r="AA32" s="470" t="n"/>
-      <c r="AB32" s="470" t="n"/>
-      <c r="AC32" s="470" t="n"/>
-      <c r="AD32" s="470" t="n"/>
-      <c r="AE32" s="470" t="n"/>
-      <c r="AF32" s="470" t="n"/>
-      <c r="AG32" s="470" t="n"/>
-      <c r="AH32" s="470" t="n"/>
-      <c r="AI32" s="470" t="n"/>
-      <c r="AJ32" s="470" t="n"/>
-      <c r="AK32" s="501" t="inlineStr">
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+      <c r="Y32" s="5" t="n"/>
+      <c r="Z32" s="5" t="n"/>
+      <c r="AA32" s="5" t="n"/>
+      <c r="AB32" s="5" t="n"/>
+      <c r="AC32" s="5" t="n"/>
+      <c r="AD32" s="5" t="n"/>
+      <c r="AE32" s="5" t="n"/>
+      <c r="AF32" s="5" t="n"/>
+      <c r="AG32" s="5" t="n"/>
+      <c r="AH32" s="5" t="n"/>
+      <c r="AI32" s="5" t="n"/>
+      <c r="AJ32" s="6" t="n"/>
+      <c r="AK32" s="597" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL32" s="470" t="n"/>
-      <c r="AM32" s="470" t="n"/>
-      <c r="AN32" s="470" t="n"/>
-      <c r="AO32" s="470" t="n"/>
-      <c r="AP32" s="470" t="n"/>
-      <c r="AQ32" s="470" t="n"/>
-      <c r="AR32" s="470" t="n"/>
-      <c r="AS32" s="470" t="n"/>
-      <c r="AT32" s="470" t="n"/>
-      <c r="AU32" s="470" t="n"/>
-      <c r="AV32" s="470" t="n"/>
-      <c r="AW32" s="470" t="n"/>
-      <c r="AX32" s="470" t="n"/>
-      <c r="AY32" s="470" t="n"/>
-      <c r="AZ32" s="470" t="n"/>
-      <c r="BA32" s="470" t="n"/>
-      <c r="BB32" s="470" t="n"/>
-      <c r="BC32" s="470" t="n"/>
-      <c r="BD32" s="502" t="n"/>
+      <c r="AL32" s="5" t="n"/>
+      <c r="AM32" s="5" t="n"/>
+      <c r="AN32" s="5" t="n"/>
+      <c r="AO32" s="5" t="n"/>
+      <c r="AP32" s="5" t="n"/>
+      <c r="AQ32" s="5" t="n"/>
+      <c r="AR32" s="5" t="n"/>
+      <c r="AS32" s="5" t="n"/>
+      <c r="AT32" s="5" t="n"/>
+      <c r="AU32" s="5" t="n"/>
+      <c r="AV32" s="5" t="n"/>
+      <c r="AW32" s="5" t="n"/>
+      <c r="AX32" s="5" t="n"/>
+      <c r="AY32" s="5" t="n"/>
+      <c r="AZ32" s="5" t="n"/>
+      <c r="BA32" s="5" t="n"/>
+      <c r="BB32" s="5" t="n"/>
+      <c r="BC32" s="5" t="n"/>
+      <c r="BD32" s="8" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="503" t="inlineStr">
+      <c r="A33" s="598" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B33" s="362" t="n"/>
-      <c r="C33" s="362" t="n"/>
-      <c r="D33" s="362" t="n"/>
-      <c r="E33" s="362" t="n"/>
-      <c r="F33" s="362" t="n"/>
-      <c r="G33" s="362" t="n"/>
-      <c r="H33" s="362" t="n"/>
-      <c r="I33" s="362" t="n"/>
-      <c r="J33" s="362" t="n"/>
-      <c r="K33" s="362" t="n"/>
-      <c r="L33" s="362" t="n"/>
-      <c r="M33" s="362" t="n"/>
-      <c r="N33" s="362" t="n"/>
-      <c r="O33" s="362" t="n"/>
-      <c r="P33" s="362" t="n"/>
-      <c r="Q33" s="362" t="n"/>
-      <c r="R33" s="362" t="n"/>
-      <c r="S33" s="504" t="inlineStr">
+      <c r="B33" s="567" t="n"/>
+      <c r="C33" s="567" t="n"/>
+      <c r="D33" s="567" t="n"/>
+      <c r="E33" s="567" t="n"/>
+      <c r="F33" s="567" t="n"/>
+      <c r="G33" s="567" t="n"/>
+      <c r="H33" s="567" t="n"/>
+      <c r="I33" s="567" t="n"/>
+      <c r="J33" s="567" t="n"/>
+      <c r="K33" s="567" t="n"/>
+      <c r="L33" s="567" t="n"/>
+      <c r="M33" s="567" t="n"/>
+      <c r="N33" s="567" t="n"/>
+      <c r="O33" s="567" t="n"/>
+      <c r="P33" s="567" t="n"/>
+      <c r="Q33" s="567" t="n"/>
+      <c r="R33" s="568" t="n"/>
+      <c r="S33" s="599" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T33" s="362" t="n"/>
-      <c r="U33" s="362" t="n"/>
-      <c r="V33" s="362" t="n"/>
-      <c r="W33" s="362" t="n"/>
-      <c r="X33" s="362" t="n"/>
-      <c r="Y33" s="362" t="n"/>
-      <c r="Z33" s="362" t="n"/>
-      <c r="AA33" s="362" t="n"/>
-      <c r="AB33" s="362" t="n"/>
-      <c r="AC33" s="362" t="n"/>
-      <c r="AD33" s="362" t="n"/>
-      <c r="AE33" s="362" t="n"/>
-      <c r="AF33" s="362" t="n"/>
-      <c r="AG33" s="362" t="n"/>
-      <c r="AH33" s="362" t="n"/>
-      <c r="AI33" s="362" t="n"/>
-      <c r="AJ33" s="362" t="n"/>
-      <c r="AK33" s="504" t="inlineStr">
+      <c r="T33" s="567" t="n"/>
+      <c r="U33" s="567" t="n"/>
+      <c r="V33" s="567" t="n"/>
+      <c r="W33" s="567" t="n"/>
+      <c r="X33" s="567" t="n"/>
+      <c r="Y33" s="567" t="n"/>
+      <c r="Z33" s="567" t="n"/>
+      <c r="AA33" s="567" t="n"/>
+      <c r="AB33" s="567" t="n"/>
+      <c r="AC33" s="567" t="n"/>
+      <c r="AD33" s="567" t="n"/>
+      <c r="AE33" s="567" t="n"/>
+      <c r="AF33" s="567" t="n"/>
+      <c r="AG33" s="567" t="n"/>
+      <c r="AH33" s="567" t="n"/>
+      <c r="AI33" s="567" t="n"/>
+      <c r="AJ33" s="568" t="n"/>
+      <c r="AK33" s="599" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL33" s="362" t="n"/>
-      <c r="AM33" s="362" t="n"/>
-      <c r="AN33" s="362" t="n"/>
-      <c r="AO33" s="362" t="n"/>
-      <c r="AP33" s="362" t="n"/>
-      <c r="AQ33" s="362" t="n"/>
-      <c r="AR33" s="362" t="n"/>
-      <c r="AS33" s="362" t="n"/>
-      <c r="AT33" s="362" t="n"/>
-      <c r="AU33" s="362" t="n"/>
-      <c r="AV33" s="362" t="n"/>
-      <c r="AW33" s="362" t="n"/>
-      <c r="AX33" s="362" t="n"/>
-      <c r="AY33" s="362" t="n"/>
-      <c r="AZ33" s="362" t="n"/>
-      <c r="BA33" s="362" t="n"/>
-      <c r="BB33" s="362" t="n"/>
-      <c r="BC33" s="362" t="n"/>
-      <c r="BD33" s="478" t="n"/>
+      <c r="AL33" s="567" t="n"/>
+      <c r="AM33" s="567" t="n"/>
+      <c r="AN33" s="567" t="n"/>
+      <c r="AO33" s="567" t="n"/>
+      <c r="AP33" s="567" t="n"/>
+      <c r="AQ33" s="567" t="n"/>
+      <c r="AR33" s="567" t="n"/>
+      <c r="AS33" s="567" t="n"/>
+      <c r="AT33" s="567" t="n"/>
+      <c r="AU33" s="567" t="n"/>
+      <c r="AV33" s="567" t="n"/>
+      <c r="AW33" s="567" t="n"/>
+      <c r="AX33" s="567" t="n"/>
+      <c r="AY33" s="567" t="n"/>
+      <c r="AZ33" s="567" t="n"/>
+      <c r="BA33" s="567" t="n"/>
+      <c r="BB33" s="567" t="n"/>
+      <c r="BC33" s="567" t="n"/>
+      <c r="BD33" s="570" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="505" t="n"/>
-      <c r="B34" s="362" t="n"/>
-      <c r="C34" s="362" t="n"/>
-      <c r="D34" s="362" t="n"/>
-      <c r="E34" s="362" t="n"/>
-      <c r="F34" s="362" t="n"/>
-      <c r="G34" s="362" t="n"/>
-      <c r="H34" s="362" t="n"/>
-      <c r="I34" s="362" t="n"/>
-      <c r="J34" s="362" t="n"/>
-      <c r="K34" s="362" t="n"/>
-      <c r="L34" s="362" t="n"/>
-      <c r="M34" s="362" t="n"/>
-      <c r="N34" s="362" t="n"/>
-      <c r="O34" s="362" t="n"/>
-      <c r="P34" s="362" t="n"/>
-      <c r="Q34" s="362" t="n"/>
-      <c r="R34" s="362" t="n"/>
-      <c r="S34" s="506" t="n"/>
-      <c r="T34" s="362" t="n"/>
-      <c r="U34" s="362" t="n"/>
-      <c r="V34" s="362" t="n"/>
-      <c r="W34" s="362" t="n"/>
-      <c r="X34" s="362" t="n"/>
-      <c r="Y34" s="362" t="n"/>
-      <c r="Z34" s="362" t="n"/>
-      <c r="AA34" s="362" t="n"/>
-      <c r="AB34" s="362" t="n"/>
-      <c r="AC34" s="362" t="n"/>
-      <c r="AD34" s="362" t="n"/>
-      <c r="AE34" s="362" t="n"/>
-      <c r="AF34" s="362" t="n"/>
-      <c r="AG34" s="362" t="n"/>
-      <c r="AH34" s="362" t="n"/>
-      <c r="AI34" s="362" t="n"/>
-      <c r="AJ34" s="362" t="n"/>
-      <c r="AK34" s="506" t="n"/>
-      <c r="AL34" s="362" t="n"/>
-      <c r="AM34" s="362" t="n"/>
-      <c r="AN34" s="362" t="n"/>
-      <c r="AO34" s="362" t="n"/>
-      <c r="AP34" s="362" t="n"/>
-      <c r="AQ34" s="362" t="n"/>
-      <c r="AR34" s="362" t="n"/>
-      <c r="AS34" s="362" t="n"/>
-      <c r="AT34" s="362" t="n"/>
-      <c r="AU34" s="362" t="n"/>
-      <c r="AV34" s="362" t="n"/>
-      <c r="AW34" s="362" t="n"/>
-      <c r="AX34" s="362" t="n"/>
-      <c r="AY34" s="362" t="n"/>
-      <c r="AZ34" s="362" t="n"/>
-      <c r="BA34" s="362" t="n"/>
-      <c r="BB34" s="362" t="n"/>
-      <c r="BC34" s="362" t="n"/>
-      <c r="BD34" s="478" t="n"/>
+      <c r="A34" s="600" t="n"/>
+      <c r="B34" s="567" t="n"/>
+      <c r="C34" s="567" t="n"/>
+      <c r="D34" s="567" t="n"/>
+      <c r="E34" s="567" t="n"/>
+      <c r="F34" s="567" t="n"/>
+      <c r="G34" s="567" t="n"/>
+      <c r="H34" s="567" t="n"/>
+      <c r="I34" s="567" t="n"/>
+      <c r="J34" s="567" t="n"/>
+      <c r="K34" s="567" t="n"/>
+      <c r="L34" s="567" t="n"/>
+      <c r="M34" s="567" t="n"/>
+      <c r="N34" s="567" t="n"/>
+      <c r="O34" s="567" t="n"/>
+      <c r="P34" s="567" t="n"/>
+      <c r="Q34" s="567" t="n"/>
+      <c r="R34" s="568" t="n"/>
+      <c r="S34" s="567" t="n"/>
+      <c r="T34" s="567" t="n"/>
+      <c r="U34" s="567" t="n"/>
+      <c r="V34" s="567" t="n"/>
+      <c r="W34" s="567" t="n"/>
+      <c r="X34" s="567" t="n"/>
+      <c r="Y34" s="567" t="n"/>
+      <c r="Z34" s="567" t="n"/>
+      <c r="AA34" s="567" t="n"/>
+      <c r="AB34" s="567" t="n"/>
+      <c r="AC34" s="567" t="n"/>
+      <c r="AD34" s="567" t="n"/>
+      <c r="AE34" s="567" t="n"/>
+      <c r="AF34" s="567" t="n"/>
+      <c r="AG34" s="567" t="n"/>
+      <c r="AH34" s="567" t="n"/>
+      <c r="AI34" s="567" t="n"/>
+      <c r="AJ34" s="568" t="n"/>
+      <c r="AK34" s="567" t="n"/>
+      <c r="AL34" s="567" t="n"/>
+      <c r="AM34" s="567" t="n"/>
+      <c r="AN34" s="567" t="n"/>
+      <c r="AO34" s="567" t="n"/>
+      <c r="AP34" s="567" t="n"/>
+      <c r="AQ34" s="567" t="n"/>
+      <c r="AR34" s="567" t="n"/>
+      <c r="AS34" s="567" t="n"/>
+      <c r="AT34" s="567" t="n"/>
+      <c r="AU34" s="567" t="n"/>
+      <c r="AV34" s="567" t="n"/>
+      <c r="AW34" s="567" t="n"/>
+      <c r="AX34" s="567" t="n"/>
+      <c r="AY34" s="567" t="n"/>
+      <c r="AZ34" s="567" t="n"/>
+      <c r="BA34" s="567" t="n"/>
+      <c r="BB34" s="567" t="n"/>
+      <c r="BC34" s="567" t="n"/>
+      <c r="BD34" s="570" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="507" t="n"/>
-      <c r="B35" s="482" t="n"/>
-      <c r="C35" s="482" t="n"/>
-      <c r="D35" s="482" t="n"/>
-      <c r="E35" s="482" t="n"/>
-      <c r="F35" s="482" t="n"/>
-      <c r="G35" s="482" t="n"/>
-      <c r="H35" s="482" t="n"/>
-      <c r="I35" s="482" t="n"/>
-      <c r="J35" s="482" t="n"/>
-      <c r="K35" s="482" t="n"/>
-      <c r="L35" s="482" t="n"/>
-      <c r="M35" s="482" t="n"/>
-      <c r="N35" s="482" t="n"/>
-      <c r="O35" s="482" t="n"/>
-      <c r="P35" s="482" t="n"/>
-      <c r="Q35" s="482" t="n"/>
-      <c r="R35" s="482" t="n"/>
-      <c r="S35" s="508" t="n"/>
-      <c r="T35" s="482" t="n"/>
-      <c r="U35" s="482" t="n"/>
-      <c r="V35" s="482" t="n"/>
-      <c r="W35" s="482" t="n"/>
-      <c r="X35" s="482" t="n"/>
-      <c r="Y35" s="482" t="n"/>
-      <c r="Z35" s="482" t="n"/>
-      <c r="AA35" s="482" t="n"/>
-      <c r="AB35" s="482" t="n"/>
-      <c r="AC35" s="482" t="n"/>
-      <c r="AD35" s="482" t="n"/>
-      <c r="AE35" s="482" t="n"/>
-      <c r="AF35" s="482" t="n"/>
-      <c r="AG35" s="482" t="n"/>
-      <c r="AH35" s="482" t="n"/>
-      <c r="AI35" s="482" t="n"/>
-      <c r="AJ35" s="482" t="n"/>
-      <c r="AK35" s="508" t="n"/>
-      <c r="AL35" s="482" t="n"/>
-      <c r="AM35" s="482" t="n"/>
-      <c r="AN35" s="482" t="n"/>
-      <c r="AO35" s="482" t="n"/>
-      <c r="AP35" s="482" t="n"/>
-      <c r="AQ35" s="482" t="n"/>
-      <c r="AR35" s="482" t="n"/>
-      <c r="AS35" s="482" t="n"/>
-      <c r="AT35" s="482" t="n"/>
-      <c r="AU35" s="482" t="n"/>
-      <c r="AV35" s="482" t="n"/>
-      <c r="AW35" s="482" t="n"/>
-      <c r="AX35" s="482" t="n"/>
-      <c r="AY35" s="482" t="n"/>
-      <c r="AZ35" s="482" t="n"/>
-      <c r="BA35" s="482" t="n"/>
-      <c r="BB35" s="482" t="n"/>
-      <c r="BC35" s="482" t="n"/>
-      <c r="BD35" s="484" t="n"/>
+      <c r="A35" s="601" t="n"/>
+      <c r="B35" s="573" t="n"/>
+      <c r="C35" s="573" t="n"/>
+      <c r="D35" s="573" t="n"/>
+      <c r="E35" s="573" t="n"/>
+      <c r="F35" s="573" t="n"/>
+      <c r="G35" s="573" t="n"/>
+      <c r="H35" s="573" t="n"/>
+      <c r="I35" s="573" t="n"/>
+      <c r="J35" s="573" t="n"/>
+      <c r="K35" s="573" t="n"/>
+      <c r="L35" s="573" t="n"/>
+      <c r="M35" s="573" t="n"/>
+      <c r="N35" s="573" t="n"/>
+      <c r="O35" s="573" t="n"/>
+      <c r="P35" s="573" t="n"/>
+      <c r="Q35" s="573" t="n"/>
+      <c r="R35" s="574" t="n"/>
+      <c r="S35" s="573" t="n"/>
+      <c r="T35" s="573" t="n"/>
+      <c r="U35" s="573" t="n"/>
+      <c r="V35" s="573" t="n"/>
+      <c r="W35" s="573" t="n"/>
+      <c r="X35" s="573" t="n"/>
+      <c r="Y35" s="573" t="n"/>
+      <c r="Z35" s="573" t="n"/>
+      <c r="AA35" s="573" t="n"/>
+      <c r="AB35" s="573" t="n"/>
+      <c r="AC35" s="573" t="n"/>
+      <c r="AD35" s="573" t="n"/>
+      <c r="AE35" s="573" t="n"/>
+      <c r="AF35" s="573" t="n"/>
+      <c r="AG35" s="573" t="n"/>
+      <c r="AH35" s="573" t="n"/>
+      <c r="AI35" s="573" t="n"/>
+      <c r="AJ35" s="574" t="n"/>
+      <c r="AK35" s="573" t="n"/>
+      <c r="AL35" s="573" t="n"/>
+      <c r="AM35" s="573" t="n"/>
+      <c r="AN35" s="573" t="n"/>
+      <c r="AO35" s="573" t="n"/>
+      <c r="AP35" s="573" t="n"/>
+      <c r="AQ35" s="573" t="n"/>
+      <c r="AR35" s="573" t="n"/>
+      <c r="AS35" s="573" t="n"/>
+      <c r="AT35" s="573" t="n"/>
+      <c r="AU35" s="573" t="n"/>
+      <c r="AV35" s="573" t="n"/>
+      <c r="AW35" s="573" t="n"/>
+      <c r="AX35" s="573" t="n"/>
+      <c r="AY35" s="573" t="n"/>
+      <c r="AZ35" s="573" t="n"/>
+      <c r="BA35" s="573" t="n"/>
+      <c r="BB35" s="573" t="n"/>
+      <c r="BC35" s="573" t="n"/>
+      <c r="BD35" s="576" t="n"/>
     </row>
     <row r="36" ht="3" customHeight="1">
-      <c r="A36" s="377" t="n"/>
-      <c r="B36" s="353" t="n"/>
-      <c r="C36" s="353" t="n"/>
-      <c r="D36" s="365" t="n"/>
-      <c r="E36" s="353" t="n"/>
-      <c r="F36" s="353" t="n"/>
-      <c r="G36" s="353" t="n"/>
-      <c r="H36" s="353" t="n"/>
-      <c r="I36" s="353" t="n"/>
-      <c r="J36" s="353" t="n"/>
-      <c r="K36" s="353" t="n"/>
-      <c r="L36" s="353" t="n"/>
-      <c r="M36" s="353" t="n"/>
-      <c r="N36" s="353" t="n"/>
-      <c r="O36" s="353" t="n"/>
-      <c r="P36" s="353" t="n"/>
-      <c r="Q36" s="353" t="n"/>
-      <c r="R36" s="365" t="n"/>
-      <c r="S36" s="353" t="n"/>
-      <c r="T36" s="353" t="n"/>
-      <c r="U36" s="353" t="n"/>
-      <c r="V36" s="353" t="n"/>
-      <c r="W36" s="353" t="n"/>
-      <c r="X36" s="353" t="n"/>
-      <c r="Y36" s="353" t="n"/>
-      <c r="Z36" s="353" t="n"/>
-      <c r="AA36" s="353" t="n"/>
-      <c r="AB36" s="353" t="n"/>
-      <c r="AC36" s="353" t="n"/>
-      <c r="AD36" s="353" t="n"/>
-      <c r="AE36" s="353" t="n"/>
-      <c r="AF36" s="353" t="n"/>
-      <c r="AG36" s="353" t="n"/>
-      <c r="AH36" s="353" t="n"/>
-      <c r="AI36" s="380" t="n"/>
-      <c r="AJ36" s="353" t="n"/>
-      <c r="AK36" s="353" t="n"/>
-      <c r="AL36" s="353" t="n"/>
-      <c r="AM36" s="353" t="n"/>
-      <c r="AN36" s="353" t="n"/>
-      <c r="AO36" s="353" t="n"/>
-      <c r="AP36" s="380" t="n"/>
-      <c r="AQ36" s="353" t="n"/>
-      <c r="AR36" s="353" t="n"/>
-      <c r="AS36" s="353" t="n"/>
-      <c r="AT36" s="353" t="n"/>
-      <c r="AU36" s="353" t="n"/>
-      <c r="AV36" s="353" t="n"/>
-      <c r="AW36" s="380" t="n"/>
-      <c r="AX36" s="353" t="n"/>
-      <c r="AY36" s="353" t="n"/>
-      <c r="AZ36" s="353" t="n"/>
-      <c r="BA36" s="380" t="n"/>
-      <c r="BB36" s="353" t="n"/>
-      <c r="BC36" s="353" t="n"/>
-      <c r="BD36" s="353" t="n"/>
+      <c r="A36" s="592" t="n"/>
+      <c r="B36" s="578" t="n"/>
+      <c r="C36" s="578" t="n"/>
+      <c r="D36" s="579" t="n"/>
+      <c r="E36" s="578" t="n"/>
+      <c r="F36" s="578" t="n"/>
+      <c r="G36" s="578" t="n"/>
+      <c r="H36" s="578" t="n"/>
+      <c r="I36" s="578" t="n"/>
+      <c r="J36" s="578" t="n"/>
+      <c r="K36" s="578" t="n"/>
+      <c r="L36" s="578" t="n"/>
+      <c r="M36" s="578" t="n"/>
+      <c r="N36" s="578" t="n"/>
+      <c r="O36" s="578" t="n"/>
+      <c r="P36" s="578" t="n"/>
+      <c r="Q36" s="578" t="n"/>
+      <c r="R36" s="579" t="n"/>
+      <c r="S36" s="578" t="n"/>
+      <c r="T36" s="578" t="n"/>
+      <c r="U36" s="578" t="n"/>
+      <c r="V36" s="578" t="n"/>
+      <c r="W36" s="578" t="n"/>
+      <c r="X36" s="578" t="n"/>
+      <c r="Y36" s="578" t="n"/>
+      <c r="Z36" s="578" t="n"/>
+      <c r="AA36" s="578" t="n"/>
+      <c r="AB36" s="578" t="n"/>
+      <c r="AC36" s="578" t="n"/>
+      <c r="AD36" s="578" t="n"/>
+      <c r="AE36" s="578" t="n"/>
+      <c r="AF36" s="578" t="n"/>
+      <c r="AG36" s="578" t="n"/>
+      <c r="AH36" s="578" t="n"/>
+      <c r="AI36" s="595" t="n"/>
+      <c r="AJ36" s="578" t="n"/>
+      <c r="AK36" s="578" t="n"/>
+      <c r="AL36" s="578" t="n"/>
+      <c r="AM36" s="578" t="n"/>
+      <c r="AN36" s="578" t="n"/>
+      <c r="AO36" s="578" t="n"/>
+      <c r="AP36" s="595" t="n"/>
+      <c r="AQ36" s="578" t="n"/>
+      <c r="AR36" s="578" t="n"/>
+      <c r="AS36" s="578" t="n"/>
+      <c r="AT36" s="578" t="n"/>
+      <c r="AU36" s="578" t="n"/>
+      <c r="AV36" s="578" t="n"/>
+      <c r="AW36" s="595" t="n"/>
+      <c r="AX36" s="578" t="n"/>
+      <c r="AY36" s="578" t="n"/>
+      <c r="AZ36" s="578" t="n"/>
+      <c r="BA36" s="595" t="n"/>
+      <c r="BB36" s="578" t="n"/>
+      <c r="BC36" s="578" t="n"/>
+      <c r="BD36" s="578" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="509" t="inlineStr">
+      <c r="A37" s="602" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="510" t="n"/>
-      <c r="C37" s="510" t="n"/>
-      <c r="D37" s="510" t="n"/>
-      <c r="E37" s="510" t="n"/>
-      <c r="F37" s="510" t="n"/>
-      <c r="G37" s="510" t="n"/>
-      <c r="H37" s="510" t="n"/>
-      <c r="I37" s="510" t="n"/>
-      <c r="J37" s="510" t="n"/>
-      <c r="K37" s="510" t="n"/>
-      <c r="L37" s="510" t="n"/>
-      <c r="M37" s="510" t="n"/>
-      <c r="N37" s="510" t="n"/>
-      <c r="O37" s="510" t="n"/>
-      <c r="P37" s="510" t="n"/>
-      <c r="Q37" s="510" t="n"/>
-      <c r="R37" s="510" t="n"/>
-      <c r="S37" s="510" t="n"/>
-      <c r="T37" s="510" t="n"/>
-      <c r="U37" s="510" t="n"/>
-      <c r="V37" s="510" t="n"/>
-      <c r="W37" s="510" t="n"/>
-      <c r="X37" s="510" t="n"/>
-      <c r="Y37" s="510" t="n"/>
-      <c r="Z37" s="510" t="n"/>
-      <c r="AA37" s="510" t="n"/>
-      <c r="AB37" s="510" t="n"/>
-      <c r="AC37" s="510" t="n"/>
-      <c r="AD37" s="510" t="n"/>
-      <c r="AE37" s="510" t="n"/>
-      <c r="AF37" s="510" t="n"/>
-      <c r="AG37" s="510" t="n"/>
-      <c r="AH37" s="510" t="n"/>
-      <c r="AI37" s="510" t="n"/>
-      <c r="AJ37" s="510" t="n"/>
-      <c r="AK37" s="510" t="n"/>
-      <c r="AL37" s="510" t="n"/>
-      <c r="AM37" s="510" t="n"/>
-      <c r="AN37" s="510" t="n"/>
-      <c r="AO37" s="510" t="n"/>
-      <c r="AP37" s="510" t="n"/>
-      <c r="AQ37" s="510" t="n"/>
-      <c r="AR37" s="510" t="n"/>
-      <c r="AS37" s="510" t="n"/>
-      <c r="AT37" s="510" t="n"/>
-      <c r="AU37" s="510" t="n"/>
-      <c r="AV37" s="510" t="n"/>
-      <c r="AW37" s="510" t="n"/>
-      <c r="AX37" s="510" t="n"/>
-      <c r="AY37" s="510" t="n"/>
-      <c r="AZ37" s="510" t="n"/>
-      <c r="BA37" s="510" t="n"/>
-      <c r="BB37" s="510" t="n"/>
-      <c r="BC37" s="510" t="n"/>
-      <c r="BD37" s="511" t="n"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="27" t="n"/>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="27" t="n"/>
+      <c r="M37" s="27" t="n"/>
+      <c r="N37" s="27" t="n"/>
+      <c r="O37" s="27" t="n"/>
+      <c r="P37" s="27" t="n"/>
+      <c r="Q37" s="27" t="n"/>
+      <c r="R37" s="27" t="n"/>
+      <c r="S37" s="27" t="n"/>
+      <c r="T37" s="27" t="n"/>
+      <c r="U37" s="27" t="n"/>
+      <c r="V37" s="27" t="n"/>
+      <c r="W37" s="27" t="n"/>
+      <c r="X37" s="27" t="n"/>
+      <c r="Y37" s="27" t="n"/>
+      <c r="Z37" s="27" t="n"/>
+      <c r="AA37" s="27" t="n"/>
+      <c r="AB37" s="27" t="n"/>
+      <c r="AC37" s="27" t="n"/>
+      <c r="AD37" s="27" t="n"/>
+      <c r="AE37" s="27" t="n"/>
+      <c r="AF37" s="27" t="n"/>
+      <c r="AG37" s="27" t="n"/>
+      <c r="AH37" s="27" t="n"/>
+      <c r="AI37" s="27" t="n"/>
+      <c r="AJ37" s="27" t="n"/>
+      <c r="AK37" s="27" t="n"/>
+      <c r="AL37" s="27" t="n"/>
+      <c r="AM37" s="27" t="n"/>
+      <c r="AN37" s="27" t="n"/>
+      <c r="AO37" s="27" t="n"/>
+      <c r="AP37" s="27" t="n"/>
+      <c r="AQ37" s="27" t="n"/>
+      <c r="AR37" s="27" t="n"/>
+      <c r="AS37" s="27" t="n"/>
+      <c r="AT37" s="27" t="n"/>
+      <c r="AU37" s="27" t="n"/>
+      <c r="AV37" s="27" t="n"/>
+      <c r="AW37" s="27" t="n"/>
+      <c r="AX37" s="27" t="n"/>
+      <c r="AY37" s="27" t="n"/>
+      <c r="AZ37" s="27" t="n"/>
+      <c r="BA37" s="27" t="n"/>
+      <c r="BB37" s="27" t="n"/>
+      <c r="BC37" s="27" t="n"/>
+      <c r="BD37" s="28" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -8637,7 +9303,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"-,Regular"&amp;7 FRM-621  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-621  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8653,7 +9319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8984,7 +9650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9035,12 +9701,12 @@
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="428" t="n"/>
-      <c r="C1" s="428" t="n"/>
-      <c r="D1" s="428" t="n"/>
-      <c r="E1" s="428" t="n"/>
-      <c r="F1" s="428" t="n"/>
-      <c r="G1" s="428" t="n"/>
+      <c r="B1" s="603" t="n"/>
+      <c r="C1" s="603" t="n"/>
+      <c r="D1" s="603" t="n"/>
+      <c r="E1" s="603" t="n"/>
+      <c r="F1" s="603" t="n"/>
+      <c r="G1" s="603" t="n"/>
       <c r="H1" s="513" t="n"/>
       <c r="I1" s="430" t="n"/>
       <c r="J1" s="431" t="n"/>
@@ -9081,12 +9747,6 @@
           <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="515" t="n"/>
       <c r="I2" s="441" t="n"/>
       <c r="J2" s="442" t="n"/>
@@ -9938,7 +10598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:CU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9989,12 +10649,12 @@
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="428" t="n"/>
-      <c r="C1" s="428" t="n"/>
-      <c r="D1" s="428" t="n"/>
-      <c r="E1" s="428" t="n"/>
-      <c r="F1" s="428" t="n"/>
-      <c r="G1" s="428" t="n"/>
+      <c r="B1" s="603" t="n"/>
+      <c r="C1" s="603" t="n"/>
+      <c r="D1" s="603" t="n"/>
+      <c r="E1" s="603" t="n"/>
+      <c r="F1" s="603" t="n"/>
+      <c r="G1" s="603" t="n"/>
       <c r="H1" s="513" t="n"/>
       <c r="I1" s="430" t="n"/>
       <c r="J1" s="431" t="n"/>
@@ -10035,12 +10695,6 @@
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="515" t="n"/>
       <c r="I2" s="441" t="n"/>
       <c r="J2" s="442" t="n"/>
@@ -10787,7 +11441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:CU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10838,12 +11492,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="428" t="n"/>
-      <c r="C1" s="428" t="n"/>
-      <c r="D1" s="428" t="n"/>
-      <c r="E1" s="428" t="n"/>
-      <c r="F1" s="428" t="n"/>
-      <c r="G1" s="428" t="n"/>
+      <c r="B1" s="603" t="n"/>
+      <c r="C1" s="603" t="n"/>
+      <c r="D1" s="603" t="n"/>
+      <c r="E1" s="603" t="n"/>
+      <c r="F1" s="603" t="n"/>
+      <c r="G1" s="603" t="n"/>
       <c r="H1" s="513" t="n"/>
       <c r="I1" s="430" t="n"/>
       <c r="J1" s="431" t="n"/>
@@ -10884,12 +11538,6 @@
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="515" t="n"/>
       <c r="I2" s="441" t="n"/>
       <c r="J2" s="442" t="n"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AQL_RECORD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AQL_RECORD'!$A$1:$BD$37</definedName>
@@ -766,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="360">
+  <borders count="369">
     <border>
       <left/>
       <right/>
@@ -4641,11 +4641,117 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="604">
+  <cellXfs count="646">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6175,6 +6281,128 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6274,6 +6502,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6748,346 +6979,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="542" t="inlineStr"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="53" t="n"/>
+      <c r="A1" s="604" t="inlineStr"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
+      <c r="I1" s="268" t="n"/>
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="310" t="n"/>
       <c r="L1" s="543" t="inlineStr">
         <is>
           <t>AQL Inspection Record</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="544" t="inlineStr">
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="268" t="n"/>
+      <c r="Q1" s="268" t="n"/>
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="268" t="n"/>
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="268" t="n"/>
+      <c r="AI1" s="268" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="268" t="n"/>
+      <c r="AO1" s="268" t="n"/>
+      <c r="AP1" s="268" t="n"/>
+      <c r="AQ1" s="605" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="545" t="n"/>
-      <c r="AW1" s="546" t="inlineStr">
+      <c r="AR1" s="268" t="n"/>
+      <c r="AS1" s="268" t="n"/>
+      <c r="AT1" s="268" t="n"/>
+      <c r="AU1" s="268" t="n"/>
+      <c r="AV1" s="606" t="n"/>
+      <c r="AW1" s="607" t="inlineStr">
         <is>
           <t>FRM-621</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="53" t="n"/>
+      <c r="AX1" s="268" t="n"/>
+      <c r="AY1" s="268" t="n"/>
+      <c r="AZ1" s="268" t="n"/>
+      <c r="BA1" s="268" t="n"/>
+      <c r="BB1" s="268" t="n"/>
+      <c r="BC1" s="268" t="n"/>
+      <c r="BD1" s="310" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="54" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="10" t="n"/>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="10" t="n"/>
-      <c r="AI2" s="10" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="10" t="n"/>
-      <c r="AO2" s="10" t="n"/>
-      <c r="AP2" s="10" t="n"/>
-      <c r="AQ2" s="547" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="K2" s="311" t="n"/>
+      <c r="L2" s="275" t="n"/>
+      <c r="AQ2" s="608" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="548" t="n"/>
-      <c r="AS2" s="548" t="n"/>
-      <c r="AT2" s="548" t="n"/>
-      <c r="AU2" s="548" t="n"/>
-      <c r="AV2" s="549" t="n"/>
-      <c r="AW2" s="550" t="inlineStr">
+      <c r="AR2" s="609" t="n"/>
+      <c r="AS2" s="609" t="n"/>
+      <c r="AT2" s="609" t="n"/>
+      <c r="AU2" s="609" t="n"/>
+      <c r="AV2" s="610" t="n"/>
+      <c r="AW2" s="611" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="548" t="n"/>
-      <c r="AY2" s="548" t="n"/>
-      <c r="AZ2" s="548" t="n"/>
-      <c r="BA2" s="548" t="n"/>
-      <c r="BB2" s="548" t="n"/>
-      <c r="BC2" s="548" t="n"/>
-      <c r="BD2" s="551" t="n"/>
+      <c r="AX2" s="609" t="n"/>
+      <c r="AY2" s="609" t="n"/>
+      <c r="AZ2" s="609" t="n"/>
+      <c r="BA2" s="609" t="n"/>
+      <c r="BB2" s="609" t="n"/>
+      <c r="BC2" s="609" t="n"/>
+      <c r="BD2" s="612" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="54" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="10" t="n"/>
-      <c r="AI3" s="10" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="10" t="n"/>
-      <c r="AO3" s="10" t="n"/>
-      <c r="AP3" s="10" t="n"/>
-      <c r="AQ3" s="547" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="K3" s="311" t="n"/>
+      <c r="L3" s="275" t="n"/>
+      <c r="AQ3" s="608" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="548" t="n"/>
-      <c r="AS3" s="548" t="n"/>
-      <c r="AT3" s="548" t="n"/>
-      <c r="AU3" s="548" t="n"/>
-      <c r="AV3" s="549" t="n"/>
-      <c r="AW3" s="550" t="inlineStr">
+      <c r="AR3" s="609" t="n"/>
+      <c r="AS3" s="609" t="n"/>
+      <c r="AT3" s="609" t="n"/>
+      <c r="AU3" s="609" t="n"/>
+      <c r="AV3" s="610" t="n"/>
+      <c r="AW3" s="611" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="548" t="n"/>
-      <c r="AY3" s="548" t="n"/>
-      <c r="AZ3" s="548" t="n"/>
-      <c r="BA3" s="548" t="n"/>
-      <c r="BB3" s="548" t="n"/>
-      <c r="BC3" s="548" t="n"/>
-      <c r="BD3" s="551" t="n"/>
+      <c r="AX3" s="609" t="n"/>
+      <c r="AY3" s="609" t="n"/>
+      <c r="AZ3" s="609" t="n"/>
+      <c r="BA3" s="609" t="n"/>
+      <c r="BB3" s="609" t="n"/>
+      <c r="BC3" s="609" t="n"/>
+      <c r="BD3" s="612" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="K4" s="311" t="n"/>
       <c r="L4" s="552" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="10" t="n"/>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="10" t="n"/>
-      <c r="AI4" s="10" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="10" t="n"/>
-      <c r="AO4" s="10" t="n"/>
-      <c r="AP4" s="10" t="n"/>
-      <c r="AQ4" s="547" t="inlineStr">
+      <c r="AQ4" s="608" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="548" t="n"/>
-      <c r="AS4" s="548" t="n"/>
-      <c r="AT4" s="548" t="n"/>
-      <c r="AU4" s="548" t="n"/>
-      <c r="AV4" s="549" t="n"/>
-      <c r="AW4" s="550" t="inlineStr">
+      <c r="AR4" s="609" t="n"/>
+      <c r="AS4" s="609" t="n"/>
+      <c r="AT4" s="609" t="n"/>
+      <c r="AU4" s="609" t="n"/>
+      <c r="AV4" s="610" t="n"/>
+      <c r="AW4" s="611" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="548" t="n"/>
-      <c r="AY4" s="548" t="n"/>
-      <c r="AZ4" s="548" t="n"/>
-      <c r="BA4" s="548" t="n"/>
-      <c r="BB4" s="548" t="n"/>
-      <c r="BC4" s="548" t="n"/>
-      <c r="BD4" s="551" t="n"/>
+      <c r="AX4" s="609" t="n"/>
+      <c r="AY4" s="609" t="n"/>
+      <c r="AZ4" s="609" t="n"/>
+      <c r="BA4" s="609" t="n"/>
+      <c r="BB4" s="609" t="n"/>
+      <c r="BC4" s="609" t="n"/>
+      <c r="BD4" s="612" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="24" t="n"/>
+      <c r="A5" s="280" t="n"/>
+      <c r="B5" s="281" t="n"/>
+      <c r="C5" s="281" t="n"/>
+      <c r="D5" s="281" t="n"/>
+      <c r="E5" s="281" t="n"/>
+      <c r="F5" s="281" t="n"/>
+      <c r="G5" s="281" t="n"/>
+      <c r="H5" s="281" t="n"/>
+      <c r="I5" s="281" t="n"/>
+      <c r="J5" s="281" t="n"/>
+      <c r="K5" s="283" t="n"/>
       <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="19" t="n"/>
-      <c r="AF5" s="19" t="n"/>
-      <c r="AG5" s="19" t="n"/>
-      <c r="AH5" s="19" t="n"/>
-      <c r="AI5" s="19" t="n"/>
-      <c r="AJ5" s="19" t="n"/>
-      <c r="AK5" s="19" t="n"/>
-      <c r="AL5" s="19" t="n"/>
-      <c r="AM5" s="19" t="n"/>
-      <c r="AN5" s="19" t="n"/>
-      <c r="AO5" s="19" t="n"/>
-      <c r="AP5" s="19" t="n"/>
-      <c r="AQ5" s="553" t="inlineStr">
+      <c r="M5" s="281" t="n"/>
+      <c r="N5" s="281" t="n"/>
+      <c r="O5" s="281" t="n"/>
+      <c r="P5" s="281" t="n"/>
+      <c r="Q5" s="281" t="n"/>
+      <c r="R5" s="281" t="n"/>
+      <c r="S5" s="281" t="n"/>
+      <c r="T5" s="281" t="n"/>
+      <c r="U5" s="281" t="n"/>
+      <c r="V5" s="281" t="n"/>
+      <c r="W5" s="281" t="n"/>
+      <c r="X5" s="281" t="n"/>
+      <c r="Y5" s="281" t="n"/>
+      <c r="Z5" s="281" t="n"/>
+      <c r="AA5" s="281" t="n"/>
+      <c r="AB5" s="281" t="n"/>
+      <c r="AC5" s="281" t="n"/>
+      <c r="AD5" s="281" t="n"/>
+      <c r="AE5" s="281" t="n"/>
+      <c r="AF5" s="281" t="n"/>
+      <c r="AG5" s="281" t="n"/>
+      <c r="AH5" s="281" t="n"/>
+      <c r="AI5" s="281" t="n"/>
+      <c r="AJ5" s="281" t="n"/>
+      <c r="AK5" s="281" t="n"/>
+      <c r="AL5" s="281" t="n"/>
+      <c r="AM5" s="281" t="n"/>
+      <c r="AN5" s="281" t="n"/>
+      <c r="AO5" s="281" t="n"/>
+      <c r="AP5" s="281" t="n"/>
+      <c r="AQ5" s="613" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="554" t="n"/>
-      <c r="AS5" s="554" t="n"/>
-      <c r="AT5" s="554" t="n"/>
-      <c r="AU5" s="554" t="n"/>
-      <c r="AV5" s="555" t="n"/>
-      <c r="AW5" s="556" t="inlineStr">
+      <c r="AR5" s="614" t="n"/>
+      <c r="AS5" s="614" t="n"/>
+      <c r="AT5" s="614" t="n"/>
+      <c r="AU5" s="614" t="n"/>
+      <c r="AV5" s="615" t="n"/>
+      <c r="AW5" s="616" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="554" t="n"/>
-      <c r="AY5" s="554" t="n"/>
-      <c r="AZ5" s="554" t="n"/>
-      <c r="BA5" s="554" t="n"/>
-      <c r="BB5" s="554" t="n"/>
-      <c r="BC5" s="554" t="n"/>
-      <c r="BD5" s="557" t="n"/>
+      <c r="AX5" s="614" t="n"/>
+      <c r="AY5" s="614" t="n"/>
+      <c r="AZ5" s="614" t="n"/>
+      <c r="BA5" s="614" t="n"/>
+      <c r="BB5" s="614" t="n"/>
+      <c r="BC5" s="614" t="n"/>
+      <c r="BD5" s="617" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="517" t="n"/>
@@ -7148,594 +7262,594 @@
       <c r="BD6" s="517" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="558" t="inlineStr">
+      <c r="A7" s="618" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="27" t="n"/>
-      <c r="AO7" s="27" t="n"/>
-      <c r="AP7" s="27" t="n"/>
-      <c r="AQ7" s="27" t="n"/>
-      <c r="AR7" s="27" t="n"/>
-      <c r="AS7" s="27" t="n"/>
-      <c r="AT7" s="27" t="n"/>
-      <c r="AU7" s="27" t="n"/>
-      <c r="AV7" s="27" t="n"/>
-      <c r="AW7" s="27" t="n"/>
-      <c r="AX7" s="27" t="n"/>
-      <c r="AY7" s="27" t="n"/>
-      <c r="AZ7" s="27" t="n"/>
-      <c r="BA7" s="27" t="n"/>
-      <c r="BB7" s="27" t="n"/>
-      <c r="BC7" s="27" t="n"/>
-      <c r="BD7" s="28" t="n"/>
+      <c r="B7" s="285" t="n"/>
+      <c r="C7" s="285" t="n"/>
+      <c r="D7" s="285" t="n"/>
+      <c r="E7" s="285" t="n"/>
+      <c r="F7" s="285" t="n"/>
+      <c r="G7" s="285" t="n"/>
+      <c r="H7" s="285" t="n"/>
+      <c r="I7" s="285" t="n"/>
+      <c r="J7" s="285" t="n"/>
+      <c r="K7" s="285" t="n"/>
+      <c r="L7" s="285" t="n"/>
+      <c r="M7" s="285" t="n"/>
+      <c r="N7" s="285" t="n"/>
+      <c r="O7" s="285" t="n"/>
+      <c r="P7" s="285" t="n"/>
+      <c r="Q7" s="285" t="n"/>
+      <c r="R7" s="285" t="n"/>
+      <c r="S7" s="285" t="n"/>
+      <c r="T7" s="285" t="n"/>
+      <c r="U7" s="285" t="n"/>
+      <c r="V7" s="285" t="n"/>
+      <c r="W7" s="285" t="n"/>
+      <c r="X7" s="285" t="n"/>
+      <c r="Y7" s="285" t="n"/>
+      <c r="Z7" s="285" t="n"/>
+      <c r="AA7" s="285" t="n"/>
+      <c r="AB7" s="285" t="n"/>
+      <c r="AC7" s="285" t="n"/>
+      <c r="AD7" s="285" t="n"/>
+      <c r="AE7" s="285" t="n"/>
+      <c r="AF7" s="285" t="n"/>
+      <c r="AG7" s="285" t="n"/>
+      <c r="AH7" s="285" t="n"/>
+      <c r="AI7" s="285" t="n"/>
+      <c r="AJ7" s="285" t="n"/>
+      <c r="AK7" s="285" t="n"/>
+      <c r="AL7" s="285" t="n"/>
+      <c r="AM7" s="285" t="n"/>
+      <c r="AN7" s="285" t="n"/>
+      <c r="AO7" s="285" t="n"/>
+      <c r="AP7" s="285" t="n"/>
+      <c r="AQ7" s="285" t="n"/>
+      <c r="AR7" s="285" t="n"/>
+      <c r="AS7" s="285" t="n"/>
+      <c r="AT7" s="285" t="n"/>
+      <c r="AU7" s="285" t="n"/>
+      <c r="AV7" s="285" t="n"/>
+      <c r="AW7" s="285" t="n"/>
+      <c r="AX7" s="285" t="n"/>
+      <c r="AY7" s="285" t="n"/>
+      <c r="AZ7" s="285" t="n"/>
+      <c r="BA7" s="285" t="n"/>
+      <c r="BB7" s="285" t="n"/>
+      <c r="BC7" s="285" t="n"/>
+      <c r="BD7" s="286" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="559" t="inlineStr">
+      <c r="A8" s="619" t="inlineStr">
         <is>
           <t>Customer / PO Line</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="560" t="n"/>
-      <c r="L8" s="561" t="n"/>
-      <c r="M8" s="561" t="n"/>
-      <c r="N8" s="561" t="n"/>
-      <c r="O8" s="561" t="n"/>
-      <c r="P8" s="561" t="n"/>
-      <c r="Q8" s="561" t="n"/>
-      <c r="R8" s="561" t="n"/>
-      <c r="S8" s="561" t="n"/>
-      <c r="T8" s="561" t="n"/>
-      <c r="U8" s="561" t="n"/>
-      <c r="V8" s="561" t="n"/>
-      <c r="W8" s="561" t="n"/>
-      <c r="X8" s="561" t="n"/>
-      <c r="Y8" s="561" t="n"/>
-      <c r="Z8" s="561" t="n"/>
-      <c r="AA8" s="561" t="n"/>
-      <c r="AB8" s="562" t="n"/>
-      <c r="AC8" s="563" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="271" t="n"/>
+      <c r="H8" s="271" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="272" t="n"/>
+      <c r="K8" s="288" t="n"/>
+      <c r="L8" s="325" t="n"/>
+      <c r="M8" s="325" t="n"/>
+      <c r="N8" s="325" t="n"/>
+      <c r="O8" s="325" t="n"/>
+      <c r="P8" s="325" t="n"/>
+      <c r="Q8" s="325" t="n"/>
+      <c r="R8" s="325" t="n"/>
+      <c r="S8" s="325" t="n"/>
+      <c r="T8" s="325" t="n"/>
+      <c r="U8" s="325" t="n"/>
+      <c r="V8" s="325" t="n"/>
+      <c r="W8" s="325" t="n"/>
+      <c r="X8" s="325" t="n"/>
+      <c r="Y8" s="325" t="n"/>
+      <c r="Z8" s="325" t="n"/>
+      <c r="AA8" s="325" t="n"/>
+      <c r="AB8" s="326" t="n"/>
+      <c r="AC8" s="620" t="inlineStr">
         <is>
           <t>Inspection Record ID</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="560" t="n"/>
-      <c r="AN8" s="561" t="n"/>
-      <c r="AO8" s="561" t="n"/>
-      <c r="AP8" s="561" t="n"/>
-      <c r="AQ8" s="561" t="n"/>
-      <c r="AR8" s="561" t="n"/>
-      <c r="AS8" s="561" t="n"/>
-      <c r="AT8" s="561" t="n"/>
-      <c r="AU8" s="561" t="n"/>
-      <c r="AV8" s="561" t="n"/>
-      <c r="AW8" s="561" t="n"/>
-      <c r="AX8" s="561" t="n"/>
-      <c r="AY8" s="561" t="n"/>
-      <c r="AZ8" s="561" t="n"/>
-      <c r="BA8" s="561" t="n"/>
-      <c r="BB8" s="561" t="n"/>
-      <c r="BC8" s="561" t="n"/>
-      <c r="BD8" s="564" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="272" t="n"/>
+      <c r="AM8" s="290" t="n"/>
+      <c r="AN8" s="325" t="n"/>
+      <c r="AO8" s="325" t="n"/>
+      <c r="AP8" s="325" t="n"/>
+      <c r="AQ8" s="325" t="n"/>
+      <c r="AR8" s="325" t="n"/>
+      <c r="AS8" s="325" t="n"/>
+      <c r="AT8" s="325" t="n"/>
+      <c r="AU8" s="325" t="n"/>
+      <c r="AV8" s="325" t="n"/>
+      <c r="AW8" s="325" t="n"/>
+      <c r="AX8" s="325" t="n"/>
+      <c r="AY8" s="325" t="n"/>
+      <c r="AZ8" s="325" t="n"/>
+      <c r="BA8" s="325" t="n"/>
+      <c r="BB8" s="325" t="n"/>
+      <c r="BC8" s="325" t="n"/>
+      <c r="BD8" s="327" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="565" t="inlineStr">
+      <c r="A9" s="621" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="566" t="n"/>
-      <c r="L9" s="567" t="n"/>
-      <c r="M9" s="567" t="n"/>
-      <c r="N9" s="567" t="n"/>
-      <c r="O9" s="567" t="n"/>
-      <c r="P9" s="567" t="n"/>
-      <c r="Q9" s="567" t="n"/>
-      <c r="R9" s="567" t="n"/>
-      <c r="S9" s="567" t="n"/>
-      <c r="T9" s="567" t="n"/>
-      <c r="U9" s="567" t="n"/>
-      <c r="V9" s="567" t="n"/>
-      <c r="W9" s="567" t="n"/>
-      <c r="X9" s="567" t="n"/>
-      <c r="Y9" s="567" t="n"/>
-      <c r="Z9" s="567" t="n"/>
-      <c r="AA9" s="567" t="n"/>
-      <c r="AB9" s="568" t="n"/>
-      <c r="AC9" s="569" t="inlineStr">
+      <c r="B9" s="276" t="n"/>
+      <c r="C9" s="276" t="n"/>
+      <c r="D9" s="276" t="n"/>
+      <c r="E9" s="276" t="n"/>
+      <c r="F9" s="276" t="n"/>
+      <c r="G9" s="276" t="n"/>
+      <c r="H9" s="276" t="n"/>
+      <c r="I9" s="276" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="300" t="n"/>
+      <c r="L9" s="328" t="n"/>
+      <c r="M9" s="328" t="n"/>
+      <c r="N9" s="328" t="n"/>
+      <c r="O9" s="328" t="n"/>
+      <c r="P9" s="328" t="n"/>
+      <c r="Q9" s="328" t="n"/>
+      <c r="R9" s="328" t="n"/>
+      <c r="S9" s="328" t="n"/>
+      <c r="T9" s="328" t="n"/>
+      <c r="U9" s="328" t="n"/>
+      <c r="V9" s="328" t="n"/>
+      <c r="W9" s="328" t="n"/>
+      <c r="X9" s="328" t="n"/>
+      <c r="Y9" s="328" t="n"/>
+      <c r="Z9" s="328" t="n"/>
+      <c r="AA9" s="328" t="n"/>
+      <c r="AB9" s="329" t="n"/>
+      <c r="AC9" s="622" t="inlineStr">
         <is>
           <t>Job / Lot / Serial</t>
         </is>
       </c>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="13" t="n"/>
-      <c r="AM9" s="566" t="n"/>
-      <c r="AN9" s="567" t="n"/>
-      <c r="AO9" s="567" t="n"/>
-      <c r="AP9" s="567" t="n"/>
-      <c r="AQ9" s="567" t="n"/>
-      <c r="AR9" s="567" t="n"/>
-      <c r="AS9" s="567" t="n"/>
-      <c r="AT9" s="567" t="n"/>
-      <c r="AU9" s="567" t="n"/>
-      <c r="AV9" s="567" t="n"/>
-      <c r="AW9" s="567" t="n"/>
-      <c r="AX9" s="567" t="n"/>
-      <c r="AY9" s="567" t="n"/>
-      <c r="AZ9" s="567" t="n"/>
-      <c r="BA9" s="567" t="n"/>
-      <c r="BB9" s="567" t="n"/>
-      <c r="BC9" s="567" t="n"/>
-      <c r="BD9" s="570" t="n"/>
+      <c r="AD9" s="276" t="n"/>
+      <c r="AE9" s="276" t="n"/>
+      <c r="AF9" s="276" t="n"/>
+      <c r="AG9" s="276" t="n"/>
+      <c r="AH9" s="276" t="n"/>
+      <c r="AI9" s="276" t="n"/>
+      <c r="AJ9" s="276" t="n"/>
+      <c r="AK9" s="276" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="623" t="n"/>
+      <c r="AN9" s="328" t="n"/>
+      <c r="AO9" s="328" t="n"/>
+      <c r="AP9" s="328" t="n"/>
+      <c r="AQ9" s="328" t="n"/>
+      <c r="AR9" s="328" t="n"/>
+      <c r="AS9" s="328" t="n"/>
+      <c r="AT9" s="328" t="n"/>
+      <c r="AU9" s="328" t="n"/>
+      <c r="AV9" s="328" t="n"/>
+      <c r="AW9" s="328" t="n"/>
+      <c r="AX9" s="328" t="n"/>
+      <c r="AY9" s="328" t="n"/>
+      <c r="AZ9" s="328" t="n"/>
+      <c r="BA9" s="328" t="n"/>
+      <c r="BB9" s="328" t="n"/>
+      <c r="BC9" s="328" t="n"/>
+      <c r="BD9" s="330" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="565" t="inlineStr">
+      <c r="A10" s="621" t="inlineStr">
         <is>
           <t>Lot Qty</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="566" t="n"/>
-      <c r="L10" s="567" t="n"/>
-      <c r="M10" s="567" t="n"/>
-      <c r="N10" s="567" t="n"/>
-      <c r="O10" s="567" t="n"/>
-      <c r="P10" s="567" t="n"/>
-      <c r="Q10" s="567" t="n"/>
-      <c r="R10" s="567" t="n"/>
-      <c r="S10" s="567" t="n"/>
-      <c r="T10" s="567" t="n"/>
-      <c r="U10" s="567" t="n"/>
-      <c r="V10" s="567" t="n"/>
-      <c r="W10" s="567" t="n"/>
-      <c r="X10" s="567" t="n"/>
-      <c r="Y10" s="567" t="n"/>
-      <c r="Z10" s="567" t="n"/>
-      <c r="AA10" s="567" t="n"/>
-      <c r="AB10" s="568" t="n"/>
-      <c r="AC10" s="569" t="inlineStr">
+      <c r="B10" s="276" t="n"/>
+      <c r="C10" s="276" t="n"/>
+      <c r="D10" s="276" t="n"/>
+      <c r="E10" s="276" t="n"/>
+      <c r="F10" s="276" t="n"/>
+      <c r="G10" s="276" t="n"/>
+      <c r="H10" s="276" t="n"/>
+      <c r="I10" s="276" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="300" t="n"/>
+      <c r="L10" s="328" t="n"/>
+      <c r="M10" s="328" t="n"/>
+      <c r="N10" s="328" t="n"/>
+      <c r="O10" s="328" t="n"/>
+      <c r="P10" s="328" t="n"/>
+      <c r="Q10" s="328" t="n"/>
+      <c r="R10" s="328" t="n"/>
+      <c r="S10" s="328" t="n"/>
+      <c r="T10" s="328" t="n"/>
+      <c r="U10" s="328" t="n"/>
+      <c r="V10" s="328" t="n"/>
+      <c r="W10" s="328" t="n"/>
+      <c r="X10" s="328" t="n"/>
+      <c r="Y10" s="328" t="n"/>
+      <c r="Z10" s="328" t="n"/>
+      <c r="AA10" s="328" t="n"/>
+      <c r="AB10" s="329" t="n"/>
+      <c r="AC10" s="622" t="inlineStr">
         <is>
           <t>Characteristic Class</t>
         </is>
       </c>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="13" t="n"/>
-      <c r="AM10" s="566" t="n"/>
-      <c r="AN10" s="567" t="n"/>
-      <c r="AO10" s="567" t="n"/>
-      <c r="AP10" s="567" t="n"/>
-      <c r="AQ10" s="567" t="n"/>
-      <c r="AR10" s="567" t="n"/>
-      <c r="AS10" s="567" t="n"/>
-      <c r="AT10" s="567" t="n"/>
-      <c r="AU10" s="567" t="n"/>
-      <c r="AV10" s="567" t="n"/>
-      <c r="AW10" s="567" t="n"/>
-      <c r="AX10" s="567" t="n"/>
-      <c r="AY10" s="567" t="n"/>
-      <c r="AZ10" s="567" t="n"/>
-      <c r="BA10" s="567" t="n"/>
-      <c r="BB10" s="567" t="n"/>
-      <c r="BC10" s="567" t="n"/>
-      <c r="BD10" s="570" t="n"/>
+      <c r="AD10" s="276" t="n"/>
+      <c r="AE10" s="276" t="n"/>
+      <c r="AF10" s="276" t="n"/>
+      <c r="AG10" s="276" t="n"/>
+      <c r="AH10" s="276" t="n"/>
+      <c r="AI10" s="276" t="n"/>
+      <c r="AJ10" s="276" t="n"/>
+      <c r="AK10" s="276" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="623" t="n"/>
+      <c r="AN10" s="328" t="n"/>
+      <c r="AO10" s="328" t="n"/>
+      <c r="AP10" s="328" t="n"/>
+      <c r="AQ10" s="328" t="n"/>
+      <c r="AR10" s="328" t="n"/>
+      <c r="AS10" s="328" t="n"/>
+      <c r="AT10" s="328" t="n"/>
+      <c r="AU10" s="328" t="n"/>
+      <c r="AV10" s="328" t="n"/>
+      <c r="AW10" s="328" t="n"/>
+      <c r="AX10" s="328" t="n"/>
+      <c r="AY10" s="328" t="n"/>
+      <c r="AZ10" s="328" t="n"/>
+      <c r="BA10" s="328" t="n"/>
+      <c r="BB10" s="328" t="n"/>
+      <c r="BC10" s="328" t="n"/>
+      <c r="BD10" s="330" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="565" t="inlineStr">
+      <c r="A11" s="621" t="inlineStr">
         <is>
           <t>AQL</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="566" t="n"/>
-      <c r="L11" s="567" t="n"/>
-      <c r="M11" s="567" t="n"/>
-      <c r="N11" s="567" t="n"/>
-      <c r="O11" s="567" t="n"/>
-      <c r="P11" s="567" t="n"/>
-      <c r="Q11" s="567" t="n"/>
-      <c r="R11" s="567" t="n"/>
-      <c r="S11" s="567" t="n"/>
-      <c r="T11" s="567" t="n"/>
-      <c r="U11" s="567" t="n"/>
-      <c r="V11" s="567" t="n"/>
-      <c r="W11" s="567" t="n"/>
-      <c r="X11" s="567" t="n"/>
-      <c r="Y11" s="567" t="n"/>
-      <c r="Z11" s="567" t="n"/>
-      <c r="AA11" s="567" t="n"/>
-      <c r="AB11" s="568" t="n"/>
-      <c r="AC11" s="569" t="inlineStr">
+      <c r="B11" s="276" t="n"/>
+      <c r="C11" s="276" t="n"/>
+      <c r="D11" s="276" t="n"/>
+      <c r="E11" s="276" t="n"/>
+      <c r="F11" s="276" t="n"/>
+      <c r="G11" s="276" t="n"/>
+      <c r="H11" s="276" t="n"/>
+      <c r="I11" s="276" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="300" t="n"/>
+      <c r="L11" s="328" t="n"/>
+      <c r="M11" s="328" t="n"/>
+      <c r="N11" s="328" t="n"/>
+      <c r="O11" s="328" t="n"/>
+      <c r="P11" s="328" t="n"/>
+      <c r="Q11" s="328" t="n"/>
+      <c r="R11" s="328" t="n"/>
+      <c r="S11" s="328" t="n"/>
+      <c r="T11" s="328" t="n"/>
+      <c r="U11" s="328" t="n"/>
+      <c r="V11" s="328" t="n"/>
+      <c r="W11" s="328" t="n"/>
+      <c r="X11" s="328" t="n"/>
+      <c r="Y11" s="328" t="n"/>
+      <c r="Z11" s="328" t="n"/>
+      <c r="AA11" s="328" t="n"/>
+      <c r="AB11" s="329" t="n"/>
+      <c r="AC11" s="622" t="inlineStr">
         <is>
           <t>Inspection Level</t>
         </is>
       </c>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="13" t="n"/>
-      <c r="AM11" s="566" t="n"/>
-      <c r="AN11" s="567" t="n"/>
-      <c r="AO11" s="567" t="n"/>
-      <c r="AP11" s="567" t="n"/>
-      <c r="AQ11" s="567" t="n"/>
-      <c r="AR11" s="567" t="n"/>
-      <c r="AS11" s="567" t="n"/>
-      <c r="AT11" s="567" t="n"/>
-      <c r="AU11" s="567" t="n"/>
-      <c r="AV11" s="567" t="n"/>
-      <c r="AW11" s="567" t="n"/>
-      <c r="AX11" s="567" t="n"/>
-      <c r="AY11" s="567" t="n"/>
-      <c r="AZ11" s="567" t="n"/>
-      <c r="BA11" s="567" t="n"/>
-      <c r="BB11" s="567" t="n"/>
-      <c r="BC11" s="567" t="n"/>
-      <c r="BD11" s="570" t="n"/>
+      <c r="AD11" s="276" t="n"/>
+      <c r="AE11" s="276" t="n"/>
+      <c r="AF11" s="276" t="n"/>
+      <c r="AG11" s="276" t="n"/>
+      <c r="AH11" s="276" t="n"/>
+      <c r="AI11" s="276" t="n"/>
+      <c r="AJ11" s="276" t="n"/>
+      <c r="AK11" s="276" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="623" t="n"/>
+      <c r="AN11" s="328" t="n"/>
+      <c r="AO11" s="328" t="n"/>
+      <c r="AP11" s="328" t="n"/>
+      <c r="AQ11" s="328" t="n"/>
+      <c r="AR11" s="328" t="n"/>
+      <c r="AS11" s="328" t="n"/>
+      <c r="AT11" s="328" t="n"/>
+      <c r="AU11" s="328" t="n"/>
+      <c r="AV11" s="328" t="n"/>
+      <c r="AW11" s="328" t="n"/>
+      <c r="AX11" s="328" t="n"/>
+      <c r="AY11" s="328" t="n"/>
+      <c r="AZ11" s="328" t="n"/>
+      <c r="BA11" s="328" t="n"/>
+      <c r="BB11" s="328" t="n"/>
+      <c r="BC11" s="328" t="n"/>
+      <c r="BD11" s="330" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="565" t="inlineStr">
+      <c r="A12" s="621" t="inlineStr">
         <is>
           <t>Code Letter</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="566" t="n"/>
-      <c r="L12" s="567" t="n"/>
-      <c r="M12" s="567" t="n"/>
-      <c r="N12" s="567" t="n"/>
-      <c r="O12" s="567" t="n"/>
-      <c r="P12" s="567" t="n"/>
-      <c r="Q12" s="567" t="n"/>
-      <c r="R12" s="567" t="n"/>
-      <c r="S12" s="567" t="n"/>
-      <c r="T12" s="567" t="n"/>
-      <c r="U12" s="567" t="n"/>
-      <c r="V12" s="567" t="n"/>
-      <c r="W12" s="567" t="n"/>
-      <c r="X12" s="567" t="n"/>
-      <c r="Y12" s="567" t="n"/>
-      <c r="Z12" s="567" t="n"/>
-      <c r="AA12" s="567" t="n"/>
-      <c r="AB12" s="568" t="n"/>
-      <c r="AC12" s="569" t="inlineStr">
+      <c r="B12" s="276" t="n"/>
+      <c r="C12" s="276" t="n"/>
+      <c r="D12" s="276" t="n"/>
+      <c r="E12" s="276" t="n"/>
+      <c r="F12" s="276" t="n"/>
+      <c r="G12" s="276" t="n"/>
+      <c r="H12" s="276" t="n"/>
+      <c r="I12" s="276" t="n"/>
+      <c r="J12" s="277" t="n"/>
+      <c r="K12" s="300" t="n"/>
+      <c r="L12" s="328" t="n"/>
+      <c r="M12" s="328" t="n"/>
+      <c r="N12" s="328" t="n"/>
+      <c r="O12" s="328" t="n"/>
+      <c r="P12" s="328" t="n"/>
+      <c r="Q12" s="328" t="n"/>
+      <c r="R12" s="328" t="n"/>
+      <c r="S12" s="328" t="n"/>
+      <c r="T12" s="328" t="n"/>
+      <c r="U12" s="328" t="n"/>
+      <c r="V12" s="328" t="n"/>
+      <c r="W12" s="328" t="n"/>
+      <c r="X12" s="328" t="n"/>
+      <c r="Y12" s="328" t="n"/>
+      <c r="Z12" s="328" t="n"/>
+      <c r="AA12" s="328" t="n"/>
+      <c r="AB12" s="329" t="n"/>
+      <c r="AC12" s="622" t="inlineStr">
         <is>
           <t>Sample Size</t>
         </is>
       </c>
-      <c r="AD12" s="12" t="n"/>
-      <c r="AE12" s="12" t="n"/>
-      <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="12" t="n"/>
-      <c r="AH12" s="12" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="12" t="n"/>
-      <c r="AK12" s="12" t="n"/>
-      <c r="AL12" s="13" t="n"/>
-      <c r="AM12" s="566" t="n"/>
-      <c r="AN12" s="567" t="n"/>
-      <c r="AO12" s="567" t="n"/>
-      <c r="AP12" s="567" t="n"/>
-      <c r="AQ12" s="567" t="n"/>
-      <c r="AR12" s="567" t="n"/>
-      <c r="AS12" s="567" t="n"/>
-      <c r="AT12" s="567" t="n"/>
-      <c r="AU12" s="567" t="n"/>
-      <c r="AV12" s="567" t="n"/>
-      <c r="AW12" s="567" t="n"/>
-      <c r="AX12" s="567" t="n"/>
-      <c r="AY12" s="567" t="n"/>
-      <c r="AZ12" s="567" t="n"/>
-      <c r="BA12" s="567" t="n"/>
-      <c r="BB12" s="567" t="n"/>
-      <c r="BC12" s="567" t="n"/>
-      <c r="BD12" s="570" t="n"/>
+      <c r="AD12" s="276" t="n"/>
+      <c r="AE12" s="276" t="n"/>
+      <c r="AF12" s="276" t="n"/>
+      <c r="AG12" s="276" t="n"/>
+      <c r="AH12" s="276" t="n"/>
+      <c r="AI12" s="276" t="n"/>
+      <c r="AJ12" s="276" t="n"/>
+      <c r="AK12" s="276" t="n"/>
+      <c r="AL12" s="277" t="n"/>
+      <c r="AM12" s="623" t="n"/>
+      <c r="AN12" s="328" t="n"/>
+      <c r="AO12" s="328" t="n"/>
+      <c r="AP12" s="328" t="n"/>
+      <c r="AQ12" s="328" t="n"/>
+      <c r="AR12" s="328" t="n"/>
+      <c r="AS12" s="328" t="n"/>
+      <c r="AT12" s="328" t="n"/>
+      <c r="AU12" s="328" t="n"/>
+      <c r="AV12" s="328" t="n"/>
+      <c r="AW12" s="328" t="n"/>
+      <c r="AX12" s="328" t="n"/>
+      <c r="AY12" s="328" t="n"/>
+      <c r="AZ12" s="328" t="n"/>
+      <c r="BA12" s="328" t="n"/>
+      <c r="BB12" s="328" t="n"/>
+      <c r="BC12" s="328" t="n"/>
+      <c r="BD12" s="330" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="565" t="inlineStr">
+      <c r="A13" s="621" t="inlineStr">
         <is>
           <t>Ac / Re</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="566" t="n"/>
-      <c r="L13" s="567" t="n"/>
-      <c r="M13" s="567" t="n"/>
-      <c r="N13" s="567" t="n"/>
-      <c r="O13" s="567" t="n"/>
-      <c r="P13" s="567" t="n"/>
-      <c r="Q13" s="567" t="n"/>
-      <c r="R13" s="567" t="n"/>
-      <c r="S13" s="567" t="n"/>
-      <c r="T13" s="567" t="n"/>
-      <c r="U13" s="567" t="n"/>
-      <c r="V13" s="567" t="n"/>
-      <c r="W13" s="567" t="n"/>
-      <c r="X13" s="567" t="n"/>
-      <c r="Y13" s="567" t="n"/>
-      <c r="Z13" s="567" t="n"/>
-      <c r="AA13" s="567" t="n"/>
-      <c r="AB13" s="568" t="n"/>
-      <c r="AC13" s="569" t="inlineStr">
+      <c r="B13" s="276" t="n"/>
+      <c r="C13" s="276" t="n"/>
+      <c r="D13" s="276" t="n"/>
+      <c r="E13" s="276" t="n"/>
+      <c r="F13" s="276" t="n"/>
+      <c r="G13" s="276" t="n"/>
+      <c r="H13" s="276" t="n"/>
+      <c r="I13" s="276" t="n"/>
+      <c r="J13" s="277" t="n"/>
+      <c r="K13" s="300" t="n"/>
+      <c r="L13" s="328" t="n"/>
+      <c r="M13" s="328" t="n"/>
+      <c r="N13" s="328" t="n"/>
+      <c r="O13" s="328" t="n"/>
+      <c r="P13" s="328" t="n"/>
+      <c r="Q13" s="328" t="n"/>
+      <c r="R13" s="328" t="n"/>
+      <c r="S13" s="328" t="n"/>
+      <c r="T13" s="328" t="n"/>
+      <c r="U13" s="328" t="n"/>
+      <c r="V13" s="328" t="n"/>
+      <c r="W13" s="328" t="n"/>
+      <c r="X13" s="328" t="n"/>
+      <c r="Y13" s="328" t="n"/>
+      <c r="Z13" s="328" t="n"/>
+      <c r="AA13" s="328" t="n"/>
+      <c r="AB13" s="329" t="n"/>
+      <c r="AC13" s="622" t="inlineStr">
         <is>
           <t>Switching Status</t>
         </is>
       </c>
-      <c r="AD13" s="12" t="n"/>
-      <c r="AE13" s="12" t="n"/>
-      <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="12" t="n"/>
-      <c r="AH13" s="12" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="12" t="n"/>
-      <c r="AK13" s="12" t="n"/>
-      <c r="AL13" s="13" t="n"/>
-      <c r="AM13" s="566" t="n"/>
-      <c r="AN13" s="567" t="n"/>
-      <c r="AO13" s="567" t="n"/>
-      <c r="AP13" s="567" t="n"/>
-      <c r="AQ13" s="567" t="n"/>
-      <c r="AR13" s="567" t="n"/>
-      <c r="AS13" s="567" t="n"/>
-      <c r="AT13" s="567" t="n"/>
-      <c r="AU13" s="567" t="n"/>
-      <c r="AV13" s="567" t="n"/>
-      <c r="AW13" s="567" t="n"/>
-      <c r="AX13" s="567" t="n"/>
-      <c r="AY13" s="567" t="n"/>
-      <c r="AZ13" s="567" t="n"/>
-      <c r="BA13" s="567" t="n"/>
-      <c r="BB13" s="567" t="n"/>
-      <c r="BC13" s="567" t="n"/>
-      <c r="BD13" s="570" t="n"/>
+      <c r="AD13" s="276" t="n"/>
+      <c r="AE13" s="276" t="n"/>
+      <c r="AF13" s="276" t="n"/>
+      <c r="AG13" s="276" t="n"/>
+      <c r="AH13" s="276" t="n"/>
+      <c r="AI13" s="276" t="n"/>
+      <c r="AJ13" s="276" t="n"/>
+      <c r="AK13" s="276" t="n"/>
+      <c r="AL13" s="277" t="n"/>
+      <c r="AM13" s="623" t="n"/>
+      <c r="AN13" s="328" t="n"/>
+      <c r="AO13" s="328" t="n"/>
+      <c r="AP13" s="328" t="n"/>
+      <c r="AQ13" s="328" t="n"/>
+      <c r="AR13" s="328" t="n"/>
+      <c r="AS13" s="328" t="n"/>
+      <c r="AT13" s="328" t="n"/>
+      <c r="AU13" s="328" t="n"/>
+      <c r="AV13" s="328" t="n"/>
+      <c r="AW13" s="328" t="n"/>
+      <c r="AX13" s="328" t="n"/>
+      <c r="AY13" s="328" t="n"/>
+      <c r="AZ13" s="328" t="n"/>
+      <c r="BA13" s="328" t="n"/>
+      <c r="BB13" s="328" t="n"/>
+      <c r="BC13" s="328" t="n"/>
+      <c r="BD13" s="330" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="565" t="inlineStr">
+      <c r="A14" s="621" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="566" t="n"/>
-      <c r="L14" s="567" t="n"/>
-      <c r="M14" s="567" t="n"/>
-      <c r="N14" s="567" t="n"/>
-      <c r="O14" s="567" t="n"/>
-      <c r="P14" s="567" t="n"/>
-      <c r="Q14" s="567" t="n"/>
-      <c r="R14" s="567" t="n"/>
-      <c r="S14" s="567" t="n"/>
-      <c r="T14" s="567" t="n"/>
-      <c r="U14" s="567" t="n"/>
-      <c r="V14" s="567" t="n"/>
-      <c r="W14" s="567" t="n"/>
-      <c r="X14" s="567" t="n"/>
-      <c r="Y14" s="567" t="n"/>
-      <c r="Z14" s="567" t="n"/>
-      <c r="AA14" s="567" t="n"/>
-      <c r="AB14" s="568" t="n"/>
-      <c r="AC14" s="569" t="inlineStr">
+      <c r="B14" s="276" t="n"/>
+      <c r="C14" s="276" t="n"/>
+      <c r="D14" s="276" t="n"/>
+      <c r="E14" s="276" t="n"/>
+      <c r="F14" s="276" t="n"/>
+      <c r="G14" s="276" t="n"/>
+      <c r="H14" s="276" t="n"/>
+      <c r="I14" s="276" t="n"/>
+      <c r="J14" s="277" t="n"/>
+      <c r="K14" s="300" t="n"/>
+      <c r="L14" s="328" t="n"/>
+      <c r="M14" s="328" t="n"/>
+      <c r="N14" s="328" t="n"/>
+      <c r="O14" s="328" t="n"/>
+      <c r="P14" s="328" t="n"/>
+      <c r="Q14" s="328" t="n"/>
+      <c r="R14" s="328" t="n"/>
+      <c r="S14" s="328" t="n"/>
+      <c r="T14" s="328" t="n"/>
+      <c r="U14" s="328" t="n"/>
+      <c r="V14" s="328" t="n"/>
+      <c r="W14" s="328" t="n"/>
+      <c r="X14" s="328" t="n"/>
+      <c r="Y14" s="328" t="n"/>
+      <c r="Z14" s="328" t="n"/>
+      <c r="AA14" s="328" t="n"/>
+      <c r="AB14" s="329" t="n"/>
+      <c r="AC14" s="622" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD14" s="12" t="n"/>
-      <c r="AE14" s="12" t="n"/>
-      <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="12" t="n"/>
-      <c r="AH14" s="12" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="12" t="n"/>
-      <c r="AK14" s="12" t="n"/>
-      <c r="AL14" s="13" t="n"/>
-      <c r="AM14" s="566" t="n"/>
-      <c r="AN14" s="567" t="n"/>
-      <c r="AO14" s="567" t="n"/>
-      <c r="AP14" s="567" t="n"/>
-      <c r="AQ14" s="567" t="n"/>
-      <c r="AR14" s="567" t="n"/>
-      <c r="AS14" s="567" t="n"/>
-      <c r="AT14" s="567" t="n"/>
-      <c r="AU14" s="567" t="n"/>
-      <c r="AV14" s="567" t="n"/>
-      <c r="AW14" s="567" t="n"/>
-      <c r="AX14" s="567" t="n"/>
-      <c r="AY14" s="567" t="n"/>
-      <c r="AZ14" s="567" t="n"/>
-      <c r="BA14" s="567" t="n"/>
-      <c r="BB14" s="567" t="n"/>
-      <c r="BC14" s="567" t="n"/>
-      <c r="BD14" s="570" t="n"/>
+      <c r="AD14" s="276" t="n"/>
+      <c r="AE14" s="276" t="n"/>
+      <c r="AF14" s="276" t="n"/>
+      <c r="AG14" s="276" t="n"/>
+      <c r="AH14" s="276" t="n"/>
+      <c r="AI14" s="276" t="n"/>
+      <c r="AJ14" s="276" t="n"/>
+      <c r="AK14" s="276" t="n"/>
+      <c r="AL14" s="277" t="n"/>
+      <c r="AM14" s="623" t="n"/>
+      <c r="AN14" s="328" t="n"/>
+      <c r="AO14" s="328" t="n"/>
+      <c r="AP14" s="328" t="n"/>
+      <c r="AQ14" s="328" t="n"/>
+      <c r="AR14" s="328" t="n"/>
+      <c r="AS14" s="328" t="n"/>
+      <c r="AT14" s="328" t="n"/>
+      <c r="AU14" s="328" t="n"/>
+      <c r="AV14" s="328" t="n"/>
+      <c r="AW14" s="328" t="n"/>
+      <c r="AX14" s="328" t="n"/>
+      <c r="AY14" s="328" t="n"/>
+      <c r="AZ14" s="328" t="n"/>
+      <c r="BA14" s="328" t="n"/>
+      <c r="BB14" s="328" t="n"/>
+      <c r="BC14" s="328" t="n"/>
+      <c r="BD14" s="330" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="571" t="inlineStr">
+      <c r="A15" s="624" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="572" t="n"/>
-      <c r="L15" s="573" t="n"/>
-      <c r="M15" s="573" t="n"/>
-      <c r="N15" s="573" t="n"/>
-      <c r="O15" s="573" t="n"/>
-      <c r="P15" s="573" t="n"/>
-      <c r="Q15" s="573" t="n"/>
-      <c r="R15" s="573" t="n"/>
-      <c r="S15" s="573" t="n"/>
-      <c r="T15" s="573" t="n"/>
-      <c r="U15" s="573" t="n"/>
-      <c r="V15" s="573" t="n"/>
-      <c r="W15" s="573" t="n"/>
-      <c r="X15" s="573" t="n"/>
-      <c r="Y15" s="573" t="n"/>
-      <c r="Z15" s="573" t="n"/>
-      <c r="AA15" s="573" t="n"/>
-      <c r="AB15" s="574" t="n"/>
-      <c r="AC15" s="575" t="inlineStr">
+      <c r="B15" s="281" t="n"/>
+      <c r="C15" s="281" t="n"/>
+      <c r="D15" s="281" t="n"/>
+      <c r="E15" s="281" t="n"/>
+      <c r="F15" s="281" t="n"/>
+      <c r="G15" s="281" t="n"/>
+      <c r="H15" s="281" t="n"/>
+      <c r="I15" s="281" t="n"/>
+      <c r="J15" s="282" t="n"/>
+      <c r="K15" s="625" t="n"/>
+      <c r="L15" s="337" t="n"/>
+      <c r="M15" s="337" t="n"/>
+      <c r="N15" s="337" t="n"/>
+      <c r="O15" s="337" t="n"/>
+      <c r="P15" s="337" t="n"/>
+      <c r="Q15" s="337" t="n"/>
+      <c r="R15" s="337" t="n"/>
+      <c r="S15" s="337" t="n"/>
+      <c r="T15" s="337" t="n"/>
+      <c r="U15" s="337" t="n"/>
+      <c r="V15" s="337" t="n"/>
+      <c r="W15" s="337" t="n"/>
+      <c r="X15" s="337" t="n"/>
+      <c r="Y15" s="337" t="n"/>
+      <c r="Z15" s="337" t="n"/>
+      <c r="AA15" s="337" t="n"/>
+      <c r="AB15" s="626" t="n"/>
+      <c r="AC15" s="627" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="AD15" s="19" t="n"/>
-      <c r="AE15" s="19" t="n"/>
-      <c r="AF15" s="19" t="n"/>
-      <c r="AG15" s="19" t="n"/>
-      <c r="AH15" s="19" t="n"/>
-      <c r="AI15" s="19" t="n"/>
-      <c r="AJ15" s="19" t="n"/>
-      <c r="AK15" s="19" t="n"/>
-      <c r="AL15" s="22" t="n"/>
-      <c r="AM15" s="572" t="n"/>
-      <c r="AN15" s="573" t="n"/>
-      <c r="AO15" s="573" t="n"/>
-      <c r="AP15" s="573" t="n"/>
-      <c r="AQ15" s="573" t="n"/>
-      <c r="AR15" s="573" t="n"/>
-      <c r="AS15" s="573" t="n"/>
-      <c r="AT15" s="573" t="n"/>
-      <c r="AU15" s="573" t="n"/>
-      <c r="AV15" s="573" t="n"/>
-      <c r="AW15" s="573" t="n"/>
-      <c r="AX15" s="573" t="n"/>
-      <c r="AY15" s="573" t="n"/>
-      <c r="AZ15" s="573" t="n"/>
-      <c r="BA15" s="573" t="n"/>
-      <c r="BB15" s="573" t="n"/>
-      <c r="BC15" s="573" t="n"/>
-      <c r="BD15" s="576" t="n"/>
+      <c r="AD15" s="281" t="n"/>
+      <c r="AE15" s="281" t="n"/>
+      <c r="AF15" s="281" t="n"/>
+      <c r="AG15" s="281" t="n"/>
+      <c r="AH15" s="281" t="n"/>
+      <c r="AI15" s="281" t="n"/>
+      <c r="AJ15" s="281" t="n"/>
+      <c r="AK15" s="281" t="n"/>
+      <c r="AL15" s="282" t="n"/>
+      <c r="AM15" s="628" t="n"/>
+      <c r="AN15" s="337" t="n"/>
+      <c r="AO15" s="337" t="n"/>
+      <c r="AP15" s="337" t="n"/>
+      <c r="AQ15" s="337" t="n"/>
+      <c r="AR15" s="337" t="n"/>
+      <c r="AS15" s="337" t="n"/>
+      <c r="AT15" s="337" t="n"/>
+      <c r="AU15" s="337" t="n"/>
+      <c r="AV15" s="337" t="n"/>
+      <c r="AW15" s="337" t="n"/>
+      <c r="AX15" s="337" t="n"/>
+      <c r="AY15" s="337" t="n"/>
+      <c r="AZ15" s="337" t="n"/>
+      <c r="BA15" s="337" t="n"/>
+      <c r="BB15" s="337" t="n"/>
+      <c r="BC15" s="337" t="n"/>
+      <c r="BD15" s="338" t="n"/>
     </row>
     <row r="16" ht="3" customHeight="1">
       <c r="A16" s="577" t="n"/>
@@ -7796,542 +7910,542 @@
       <c r="BD16" s="578" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="558" t="inlineStr">
+      <c r="A17" s="618" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="27" t="n"/>
-      <c r="R17" s="27" t="n"/>
-      <c r="S17" s="27" t="n"/>
-      <c r="T17" s="27" t="n"/>
-      <c r="U17" s="27" t="n"/>
-      <c r="V17" s="27" t="n"/>
-      <c r="W17" s="27" t="n"/>
-      <c r="X17" s="27" t="n"/>
-      <c r="Y17" s="27" t="n"/>
-      <c r="Z17" s="27" t="n"/>
-      <c r="AA17" s="27" t="n"/>
-      <c r="AB17" s="27" t="n"/>
-      <c r="AC17" s="27" t="n"/>
-      <c r="AD17" s="27" t="n"/>
-      <c r="AE17" s="27" t="n"/>
-      <c r="AF17" s="27" t="n"/>
-      <c r="AG17" s="27" t="n"/>
-      <c r="AH17" s="27" t="n"/>
-      <c r="AI17" s="27" t="n"/>
-      <c r="AJ17" s="27" t="n"/>
-      <c r="AK17" s="27" t="n"/>
-      <c r="AL17" s="27" t="n"/>
-      <c r="AM17" s="27" t="n"/>
-      <c r="AN17" s="27" t="n"/>
-      <c r="AO17" s="27" t="n"/>
-      <c r="AP17" s="27" t="n"/>
-      <c r="AQ17" s="27" t="n"/>
-      <c r="AR17" s="27" t="n"/>
-      <c r="AS17" s="27" t="n"/>
-      <c r="AT17" s="27" t="n"/>
-      <c r="AU17" s="27" t="n"/>
-      <c r="AV17" s="27" t="n"/>
-      <c r="AW17" s="27" t="n"/>
-      <c r="AX17" s="27" t="n"/>
-      <c r="AY17" s="27" t="n"/>
-      <c r="AZ17" s="27" t="n"/>
-      <c r="BA17" s="27" t="n"/>
-      <c r="BB17" s="27" t="n"/>
-      <c r="BC17" s="27" t="n"/>
-      <c r="BD17" s="28" t="n"/>
+      <c r="B17" s="285" t="n"/>
+      <c r="C17" s="285" t="n"/>
+      <c r="D17" s="285" t="n"/>
+      <c r="E17" s="285" t="n"/>
+      <c r="F17" s="285" t="n"/>
+      <c r="G17" s="285" t="n"/>
+      <c r="H17" s="285" t="n"/>
+      <c r="I17" s="285" t="n"/>
+      <c r="J17" s="285" t="n"/>
+      <c r="K17" s="285" t="n"/>
+      <c r="L17" s="285" t="n"/>
+      <c r="M17" s="285" t="n"/>
+      <c r="N17" s="285" t="n"/>
+      <c r="O17" s="285" t="n"/>
+      <c r="P17" s="285" t="n"/>
+      <c r="Q17" s="285" t="n"/>
+      <c r="R17" s="285" t="n"/>
+      <c r="S17" s="285" t="n"/>
+      <c r="T17" s="285" t="n"/>
+      <c r="U17" s="285" t="n"/>
+      <c r="V17" s="285" t="n"/>
+      <c r="W17" s="285" t="n"/>
+      <c r="X17" s="285" t="n"/>
+      <c r="Y17" s="285" t="n"/>
+      <c r="Z17" s="285" t="n"/>
+      <c r="AA17" s="285" t="n"/>
+      <c r="AB17" s="285" t="n"/>
+      <c r="AC17" s="285" t="n"/>
+      <c r="AD17" s="285" t="n"/>
+      <c r="AE17" s="285" t="n"/>
+      <c r="AF17" s="285" t="n"/>
+      <c r="AG17" s="285" t="n"/>
+      <c r="AH17" s="285" t="n"/>
+      <c r="AI17" s="285" t="n"/>
+      <c r="AJ17" s="285" t="n"/>
+      <c r="AK17" s="285" t="n"/>
+      <c r="AL17" s="285" t="n"/>
+      <c r="AM17" s="285" t="n"/>
+      <c r="AN17" s="285" t="n"/>
+      <c r="AO17" s="285" t="n"/>
+      <c r="AP17" s="285" t="n"/>
+      <c r="AQ17" s="285" t="n"/>
+      <c r="AR17" s="285" t="n"/>
+      <c r="AS17" s="285" t="n"/>
+      <c r="AT17" s="285" t="n"/>
+      <c r="AU17" s="285" t="n"/>
+      <c r="AV17" s="285" t="n"/>
+      <c r="AW17" s="285" t="n"/>
+      <c r="AX17" s="285" t="n"/>
+      <c r="AY17" s="285" t="n"/>
+      <c r="AZ17" s="285" t="n"/>
+      <c r="BA17" s="285" t="n"/>
+      <c r="BB17" s="285" t="n"/>
+      <c r="BC17" s="285" t="n"/>
+      <c r="BD17" s="286" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="295" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="B18" s="271" t="n"/>
+      <c r="C18" s="272" t="n"/>
+      <c r="D18" s="296" t="inlineStr">
         <is>
           <t>Defect Class</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="37" t="inlineStr">
+      <c r="E18" s="271" t="n"/>
+      <c r="F18" s="271" t="n"/>
+      <c r="G18" s="272" t="n"/>
+      <c r="H18" s="296" t="inlineStr">
         <is>
           <t>Sample ID / Serial</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-      <c r="Y18" s="5" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="37" t="inlineStr">
+      <c r="I18" s="271" t="n"/>
+      <c r="J18" s="271" t="n"/>
+      <c r="K18" s="271" t="n"/>
+      <c r="L18" s="271" t="n"/>
+      <c r="M18" s="271" t="n"/>
+      <c r="N18" s="271" t="n"/>
+      <c r="O18" s="271" t="n"/>
+      <c r="P18" s="271" t="n"/>
+      <c r="Q18" s="271" t="n"/>
+      <c r="R18" s="271" t="n"/>
+      <c r="S18" s="271" t="n"/>
+      <c r="T18" s="271" t="n"/>
+      <c r="U18" s="271" t="n"/>
+      <c r="V18" s="271" t="n"/>
+      <c r="W18" s="271" t="n"/>
+      <c r="X18" s="271" t="n"/>
+      <c r="Y18" s="271" t="n"/>
+      <c r="Z18" s="272" t="n"/>
+      <c r="AA18" s="296" t="inlineStr">
         <is>
           <t>Observation / Measured Result</t>
         </is>
       </c>
-      <c r="AB18" s="5" t="n"/>
-      <c r="AC18" s="5" t="n"/>
-      <c r="AD18" s="5" t="n"/>
-      <c r="AE18" s="5" t="n"/>
-      <c r="AF18" s="5" t="n"/>
-      <c r="AG18" s="5" t="n"/>
-      <c r="AH18" s="5" t="n"/>
-      <c r="AI18" s="5" t="n"/>
-      <c r="AJ18" s="5" t="n"/>
-      <c r="AK18" s="5" t="n"/>
-      <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="5" t="n"/>
-      <c r="AN18" s="5" t="n"/>
-      <c r="AO18" s="5" t="n"/>
-      <c r="AP18" s="5" t="n"/>
-      <c r="AQ18" s="6" t="n"/>
-      <c r="AR18" s="37" t="inlineStr">
+      <c r="AB18" s="271" t="n"/>
+      <c r="AC18" s="271" t="n"/>
+      <c r="AD18" s="271" t="n"/>
+      <c r="AE18" s="271" t="n"/>
+      <c r="AF18" s="271" t="n"/>
+      <c r="AG18" s="271" t="n"/>
+      <c r="AH18" s="271" t="n"/>
+      <c r="AI18" s="271" t="n"/>
+      <c r="AJ18" s="271" t="n"/>
+      <c r="AK18" s="271" t="n"/>
+      <c r="AL18" s="271" t="n"/>
+      <c r="AM18" s="271" t="n"/>
+      <c r="AN18" s="271" t="n"/>
+      <c r="AO18" s="271" t="n"/>
+      <c r="AP18" s="271" t="n"/>
+      <c r="AQ18" s="272" t="n"/>
+      <c r="AR18" s="296" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS18" s="5" t="n"/>
-      <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="5" t="n"/>
-      <c r="AV18" s="5" t="n"/>
-      <c r="AW18" s="6" t="n"/>
-      <c r="AX18" s="37" t="inlineStr">
+      <c r="AS18" s="271" t="n"/>
+      <c r="AT18" s="271" t="n"/>
+      <c r="AU18" s="271" t="n"/>
+      <c r="AV18" s="271" t="n"/>
+      <c r="AW18" s="272" t="n"/>
+      <c r="AX18" s="296" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY18" s="5" t="n"/>
-      <c r="AZ18" s="5" t="n"/>
-      <c r="BA18" s="6" t="n"/>
-      <c r="BB18" s="37" t="inlineStr">
+      <c r="AY18" s="271" t="n"/>
+      <c r="AZ18" s="271" t="n"/>
+      <c r="BA18" s="272" t="n"/>
+      <c r="BB18" s="297" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC18" s="5" t="n"/>
-      <c r="BD18" s="8" t="n"/>
+      <c r="BC18" s="271" t="n"/>
+      <c r="BD18" s="274" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="580">
+      <c r="A19" s="629">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="581" t="inlineStr">
+      <c r="B19" s="271" t="n"/>
+      <c r="C19" s="272" t="n"/>
+      <c r="D19" s="630" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="561" t="n"/>
-      <c r="F19" s="561" t="n"/>
-      <c r="G19" s="562" t="n"/>
-      <c r="H19" s="560" t="n"/>
-      <c r="I19" s="561" t="n"/>
-      <c r="J19" s="561" t="n"/>
-      <c r="K19" s="561" t="n"/>
-      <c r="L19" s="561" t="n"/>
-      <c r="M19" s="561" t="n"/>
-      <c r="N19" s="561" t="n"/>
-      <c r="O19" s="561" t="n"/>
-      <c r="P19" s="561" t="n"/>
-      <c r="Q19" s="561" t="n"/>
-      <c r="R19" s="561" t="n"/>
-      <c r="S19" s="561" t="n"/>
-      <c r="T19" s="561" t="n"/>
-      <c r="U19" s="561" t="n"/>
-      <c r="V19" s="561" t="n"/>
-      <c r="W19" s="561" t="n"/>
-      <c r="X19" s="561" t="n"/>
-      <c r="Y19" s="561" t="n"/>
-      <c r="Z19" s="562" t="n"/>
-      <c r="AA19" s="582" t="n"/>
-      <c r="AB19" s="561" t="n"/>
-      <c r="AC19" s="561" t="n"/>
-      <c r="AD19" s="561" t="n"/>
-      <c r="AE19" s="561" t="n"/>
-      <c r="AF19" s="561" t="n"/>
-      <c r="AG19" s="561" t="n"/>
-      <c r="AH19" s="561" t="n"/>
-      <c r="AI19" s="561" t="n"/>
-      <c r="AJ19" s="561" t="n"/>
-      <c r="AK19" s="561" t="n"/>
-      <c r="AL19" s="561" t="n"/>
-      <c r="AM19" s="561" t="n"/>
-      <c r="AN19" s="561" t="n"/>
-      <c r="AO19" s="561" t="n"/>
-      <c r="AP19" s="561" t="n"/>
-      <c r="AQ19" s="562" t="n"/>
-      <c r="AR19" s="560" t="n"/>
-      <c r="AS19" s="561" t="n"/>
-      <c r="AT19" s="561" t="n"/>
-      <c r="AU19" s="561" t="n"/>
-      <c r="AV19" s="561" t="n"/>
-      <c r="AW19" s="562" t="n"/>
-      <c r="AX19" s="560" t="n"/>
-      <c r="AY19" s="561" t="n"/>
-      <c r="AZ19" s="561" t="n"/>
-      <c r="BA19" s="562" t="n"/>
-      <c r="BB19" s="583" t="n"/>
-      <c r="BC19" s="561" t="n"/>
-      <c r="BD19" s="564" t="n"/>
+      <c r="E19" s="325" t="n"/>
+      <c r="F19" s="325" t="n"/>
+      <c r="G19" s="326" t="n"/>
+      <c r="H19" s="288" t="n"/>
+      <c r="I19" s="325" t="n"/>
+      <c r="J19" s="325" t="n"/>
+      <c r="K19" s="325" t="n"/>
+      <c r="L19" s="325" t="n"/>
+      <c r="M19" s="325" t="n"/>
+      <c r="N19" s="325" t="n"/>
+      <c r="O19" s="325" t="n"/>
+      <c r="P19" s="325" t="n"/>
+      <c r="Q19" s="325" t="n"/>
+      <c r="R19" s="325" t="n"/>
+      <c r="S19" s="325" t="n"/>
+      <c r="T19" s="325" t="n"/>
+      <c r="U19" s="325" t="n"/>
+      <c r="V19" s="325" t="n"/>
+      <c r="W19" s="325" t="n"/>
+      <c r="X19" s="325" t="n"/>
+      <c r="Y19" s="325" t="n"/>
+      <c r="Z19" s="326" t="n"/>
+      <c r="AA19" s="631" t="n"/>
+      <c r="AB19" s="325" t="n"/>
+      <c r="AC19" s="325" t="n"/>
+      <c r="AD19" s="325" t="n"/>
+      <c r="AE19" s="325" t="n"/>
+      <c r="AF19" s="325" t="n"/>
+      <c r="AG19" s="325" t="n"/>
+      <c r="AH19" s="325" t="n"/>
+      <c r="AI19" s="325" t="n"/>
+      <c r="AJ19" s="325" t="n"/>
+      <c r="AK19" s="325" t="n"/>
+      <c r="AL19" s="325" t="n"/>
+      <c r="AM19" s="325" t="n"/>
+      <c r="AN19" s="325" t="n"/>
+      <c r="AO19" s="325" t="n"/>
+      <c r="AP19" s="325" t="n"/>
+      <c r="AQ19" s="326" t="n"/>
+      <c r="AR19" s="288" t="n"/>
+      <c r="AS19" s="325" t="n"/>
+      <c r="AT19" s="325" t="n"/>
+      <c r="AU19" s="325" t="n"/>
+      <c r="AV19" s="325" t="n"/>
+      <c r="AW19" s="326" t="n"/>
+      <c r="AX19" s="288" t="n"/>
+      <c r="AY19" s="325" t="n"/>
+      <c r="AZ19" s="325" t="n"/>
+      <c r="BA19" s="326" t="n"/>
+      <c r="BB19" s="632" t="n"/>
+      <c r="BC19" s="325" t="n"/>
+      <c r="BD19" s="327" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="584">
+      <c r="A20" s="633">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="585" t="inlineStr">
+      <c r="B20" s="276" t="n"/>
+      <c r="C20" s="277" t="n"/>
+      <c r="D20" s="299" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="567" t="n"/>
-      <c r="F20" s="567" t="n"/>
-      <c r="G20" s="568" t="n"/>
-      <c r="H20" s="566" t="n"/>
-      <c r="I20" s="567" t="n"/>
-      <c r="J20" s="567" t="n"/>
-      <c r="K20" s="567" t="n"/>
-      <c r="L20" s="567" t="n"/>
-      <c r="M20" s="567" t="n"/>
-      <c r="N20" s="567" t="n"/>
-      <c r="O20" s="567" t="n"/>
-      <c r="P20" s="567" t="n"/>
-      <c r="Q20" s="567" t="n"/>
-      <c r="R20" s="567" t="n"/>
-      <c r="S20" s="567" t="n"/>
-      <c r="T20" s="567" t="n"/>
-      <c r="U20" s="567" t="n"/>
-      <c r="V20" s="567" t="n"/>
-      <c r="W20" s="567" t="n"/>
-      <c r="X20" s="567" t="n"/>
-      <c r="Y20" s="567" t="n"/>
-      <c r="Z20" s="568" t="n"/>
-      <c r="AA20" s="586" t="n"/>
-      <c r="AB20" s="567" t="n"/>
-      <c r="AC20" s="567" t="n"/>
-      <c r="AD20" s="567" t="n"/>
-      <c r="AE20" s="567" t="n"/>
-      <c r="AF20" s="567" t="n"/>
-      <c r="AG20" s="567" t="n"/>
-      <c r="AH20" s="567" t="n"/>
-      <c r="AI20" s="567" t="n"/>
-      <c r="AJ20" s="567" t="n"/>
-      <c r="AK20" s="567" t="n"/>
-      <c r="AL20" s="567" t="n"/>
-      <c r="AM20" s="567" t="n"/>
-      <c r="AN20" s="567" t="n"/>
-      <c r="AO20" s="567" t="n"/>
-      <c r="AP20" s="567" t="n"/>
-      <c r="AQ20" s="568" t="n"/>
-      <c r="AR20" s="566" t="n"/>
-      <c r="AS20" s="567" t="n"/>
-      <c r="AT20" s="567" t="n"/>
-      <c r="AU20" s="567" t="n"/>
-      <c r="AV20" s="567" t="n"/>
-      <c r="AW20" s="568" t="n"/>
-      <c r="AX20" s="566" t="n"/>
-      <c r="AY20" s="567" t="n"/>
-      <c r="AZ20" s="567" t="n"/>
-      <c r="BA20" s="568" t="n"/>
-      <c r="BB20" s="587" t="n"/>
-      <c r="BC20" s="567" t="n"/>
-      <c r="BD20" s="570" t="n"/>
+      <c r="E20" s="328" t="n"/>
+      <c r="F20" s="328" t="n"/>
+      <c r="G20" s="329" t="n"/>
+      <c r="H20" s="300" t="n"/>
+      <c r="I20" s="328" t="n"/>
+      <c r="J20" s="328" t="n"/>
+      <c r="K20" s="328" t="n"/>
+      <c r="L20" s="328" t="n"/>
+      <c r="M20" s="328" t="n"/>
+      <c r="N20" s="328" t="n"/>
+      <c r="O20" s="328" t="n"/>
+      <c r="P20" s="328" t="n"/>
+      <c r="Q20" s="328" t="n"/>
+      <c r="R20" s="328" t="n"/>
+      <c r="S20" s="328" t="n"/>
+      <c r="T20" s="328" t="n"/>
+      <c r="U20" s="328" t="n"/>
+      <c r="V20" s="328" t="n"/>
+      <c r="W20" s="328" t="n"/>
+      <c r="X20" s="328" t="n"/>
+      <c r="Y20" s="328" t="n"/>
+      <c r="Z20" s="329" t="n"/>
+      <c r="AA20" s="301" t="n"/>
+      <c r="AB20" s="328" t="n"/>
+      <c r="AC20" s="328" t="n"/>
+      <c r="AD20" s="328" t="n"/>
+      <c r="AE20" s="328" t="n"/>
+      <c r="AF20" s="328" t="n"/>
+      <c r="AG20" s="328" t="n"/>
+      <c r="AH20" s="328" t="n"/>
+      <c r="AI20" s="328" t="n"/>
+      <c r="AJ20" s="328" t="n"/>
+      <c r="AK20" s="328" t="n"/>
+      <c r="AL20" s="328" t="n"/>
+      <c r="AM20" s="328" t="n"/>
+      <c r="AN20" s="328" t="n"/>
+      <c r="AO20" s="328" t="n"/>
+      <c r="AP20" s="328" t="n"/>
+      <c r="AQ20" s="329" t="n"/>
+      <c r="AR20" s="300" t="n"/>
+      <c r="AS20" s="328" t="n"/>
+      <c r="AT20" s="328" t="n"/>
+      <c r="AU20" s="328" t="n"/>
+      <c r="AV20" s="328" t="n"/>
+      <c r="AW20" s="329" t="n"/>
+      <c r="AX20" s="300" t="n"/>
+      <c r="AY20" s="328" t="n"/>
+      <c r="AZ20" s="328" t="n"/>
+      <c r="BA20" s="329" t="n"/>
+      <c r="BB20" s="302" t="n"/>
+      <c r="BC20" s="328" t="n"/>
+      <c r="BD20" s="330" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="584">
+      <c r="A21" s="633">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="585" t="inlineStr">
+      <c r="B21" s="276" t="n"/>
+      <c r="C21" s="277" t="n"/>
+      <c r="D21" s="299" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="567" t="n"/>
-      <c r="F21" s="567" t="n"/>
-      <c r="G21" s="568" t="n"/>
-      <c r="H21" s="566" t="n"/>
-      <c r="I21" s="567" t="n"/>
-      <c r="J21" s="567" t="n"/>
-      <c r="K21" s="567" t="n"/>
-      <c r="L21" s="567" t="n"/>
-      <c r="M21" s="567" t="n"/>
-      <c r="N21" s="567" t="n"/>
-      <c r="O21" s="567" t="n"/>
-      <c r="P21" s="567" t="n"/>
-      <c r="Q21" s="567" t="n"/>
-      <c r="R21" s="567" t="n"/>
-      <c r="S21" s="567" t="n"/>
-      <c r="T21" s="567" t="n"/>
-      <c r="U21" s="567" t="n"/>
-      <c r="V21" s="567" t="n"/>
-      <c r="W21" s="567" t="n"/>
-      <c r="X21" s="567" t="n"/>
-      <c r="Y21" s="567" t="n"/>
-      <c r="Z21" s="568" t="n"/>
-      <c r="AA21" s="586" t="n"/>
-      <c r="AB21" s="567" t="n"/>
-      <c r="AC21" s="567" t="n"/>
-      <c r="AD21" s="567" t="n"/>
-      <c r="AE21" s="567" t="n"/>
-      <c r="AF21" s="567" t="n"/>
-      <c r="AG21" s="567" t="n"/>
-      <c r="AH21" s="567" t="n"/>
-      <c r="AI21" s="567" t="n"/>
-      <c r="AJ21" s="567" t="n"/>
-      <c r="AK21" s="567" t="n"/>
-      <c r="AL21" s="567" t="n"/>
-      <c r="AM21" s="567" t="n"/>
-      <c r="AN21" s="567" t="n"/>
-      <c r="AO21" s="567" t="n"/>
-      <c r="AP21" s="567" t="n"/>
-      <c r="AQ21" s="568" t="n"/>
-      <c r="AR21" s="566" t="n"/>
-      <c r="AS21" s="567" t="n"/>
-      <c r="AT21" s="567" t="n"/>
-      <c r="AU21" s="567" t="n"/>
-      <c r="AV21" s="567" t="n"/>
-      <c r="AW21" s="568" t="n"/>
-      <c r="AX21" s="566" t="n"/>
-      <c r="AY21" s="567" t="n"/>
-      <c r="AZ21" s="567" t="n"/>
-      <c r="BA21" s="568" t="n"/>
-      <c r="BB21" s="587" t="n"/>
-      <c r="BC21" s="567" t="n"/>
-      <c r="BD21" s="570" t="n"/>
+      <c r="E21" s="328" t="n"/>
+      <c r="F21" s="328" t="n"/>
+      <c r="G21" s="329" t="n"/>
+      <c r="H21" s="300" t="n"/>
+      <c r="I21" s="328" t="n"/>
+      <c r="J21" s="328" t="n"/>
+      <c r="K21" s="328" t="n"/>
+      <c r="L21" s="328" t="n"/>
+      <c r="M21" s="328" t="n"/>
+      <c r="N21" s="328" t="n"/>
+      <c r="O21" s="328" t="n"/>
+      <c r="P21" s="328" t="n"/>
+      <c r="Q21" s="328" t="n"/>
+      <c r="R21" s="328" t="n"/>
+      <c r="S21" s="328" t="n"/>
+      <c r="T21" s="328" t="n"/>
+      <c r="U21" s="328" t="n"/>
+      <c r="V21" s="328" t="n"/>
+      <c r="W21" s="328" t="n"/>
+      <c r="X21" s="328" t="n"/>
+      <c r="Y21" s="328" t="n"/>
+      <c r="Z21" s="329" t="n"/>
+      <c r="AA21" s="301" t="n"/>
+      <c r="AB21" s="328" t="n"/>
+      <c r="AC21" s="328" t="n"/>
+      <c r="AD21" s="328" t="n"/>
+      <c r="AE21" s="328" t="n"/>
+      <c r="AF21" s="328" t="n"/>
+      <c r="AG21" s="328" t="n"/>
+      <c r="AH21" s="328" t="n"/>
+      <c r="AI21" s="328" t="n"/>
+      <c r="AJ21" s="328" t="n"/>
+      <c r="AK21" s="328" t="n"/>
+      <c r="AL21" s="328" t="n"/>
+      <c r="AM21" s="328" t="n"/>
+      <c r="AN21" s="328" t="n"/>
+      <c r="AO21" s="328" t="n"/>
+      <c r="AP21" s="328" t="n"/>
+      <c r="AQ21" s="329" t="n"/>
+      <c r="AR21" s="300" t="n"/>
+      <c r="AS21" s="328" t="n"/>
+      <c r="AT21" s="328" t="n"/>
+      <c r="AU21" s="328" t="n"/>
+      <c r="AV21" s="328" t="n"/>
+      <c r="AW21" s="329" t="n"/>
+      <c r="AX21" s="300" t="n"/>
+      <c r="AY21" s="328" t="n"/>
+      <c r="AZ21" s="328" t="n"/>
+      <c r="BA21" s="329" t="n"/>
+      <c r="BB21" s="302" t="n"/>
+      <c r="BC21" s="328" t="n"/>
+      <c r="BD21" s="330" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="584">
+      <c r="A22" s="633">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="585" t="inlineStr">
+      <c r="B22" s="276" t="n"/>
+      <c r="C22" s="277" t="n"/>
+      <c r="D22" s="299" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="567" t="n"/>
-      <c r="F22" s="567" t="n"/>
-      <c r="G22" s="568" t="n"/>
-      <c r="H22" s="566" t="n"/>
-      <c r="I22" s="567" t="n"/>
-      <c r="J22" s="567" t="n"/>
-      <c r="K22" s="567" t="n"/>
-      <c r="L22" s="567" t="n"/>
-      <c r="M22" s="567" t="n"/>
-      <c r="N22" s="567" t="n"/>
-      <c r="O22" s="567" t="n"/>
-      <c r="P22" s="567" t="n"/>
-      <c r="Q22" s="567" t="n"/>
-      <c r="R22" s="567" t="n"/>
-      <c r="S22" s="567" t="n"/>
-      <c r="T22" s="567" t="n"/>
-      <c r="U22" s="567" t="n"/>
-      <c r="V22" s="567" t="n"/>
-      <c r="W22" s="567" t="n"/>
-      <c r="X22" s="567" t="n"/>
-      <c r="Y22" s="567" t="n"/>
-      <c r="Z22" s="568" t="n"/>
-      <c r="AA22" s="586" t="n"/>
-      <c r="AB22" s="567" t="n"/>
-      <c r="AC22" s="567" t="n"/>
-      <c r="AD22" s="567" t="n"/>
-      <c r="AE22" s="567" t="n"/>
-      <c r="AF22" s="567" t="n"/>
-      <c r="AG22" s="567" t="n"/>
-      <c r="AH22" s="567" t="n"/>
-      <c r="AI22" s="567" t="n"/>
-      <c r="AJ22" s="567" t="n"/>
-      <c r="AK22" s="567" t="n"/>
-      <c r="AL22" s="567" t="n"/>
-      <c r="AM22" s="567" t="n"/>
-      <c r="AN22" s="567" t="n"/>
-      <c r="AO22" s="567" t="n"/>
-      <c r="AP22" s="567" t="n"/>
-      <c r="AQ22" s="568" t="n"/>
-      <c r="AR22" s="566" t="n"/>
-      <c r="AS22" s="567" t="n"/>
-      <c r="AT22" s="567" t="n"/>
-      <c r="AU22" s="567" t="n"/>
-      <c r="AV22" s="567" t="n"/>
-      <c r="AW22" s="568" t="n"/>
-      <c r="AX22" s="566" t="n"/>
-      <c r="AY22" s="567" t="n"/>
-      <c r="AZ22" s="567" t="n"/>
-      <c r="BA22" s="568" t="n"/>
-      <c r="BB22" s="587" t="n"/>
-      <c r="BC22" s="567" t="n"/>
-      <c r="BD22" s="570" t="n"/>
+      <c r="E22" s="328" t="n"/>
+      <c r="F22" s="328" t="n"/>
+      <c r="G22" s="329" t="n"/>
+      <c r="H22" s="300" t="n"/>
+      <c r="I22" s="328" t="n"/>
+      <c r="J22" s="328" t="n"/>
+      <c r="K22" s="328" t="n"/>
+      <c r="L22" s="328" t="n"/>
+      <c r="M22" s="328" t="n"/>
+      <c r="N22" s="328" t="n"/>
+      <c r="O22" s="328" t="n"/>
+      <c r="P22" s="328" t="n"/>
+      <c r="Q22" s="328" t="n"/>
+      <c r="R22" s="328" t="n"/>
+      <c r="S22" s="328" t="n"/>
+      <c r="T22" s="328" t="n"/>
+      <c r="U22" s="328" t="n"/>
+      <c r="V22" s="328" t="n"/>
+      <c r="W22" s="328" t="n"/>
+      <c r="X22" s="328" t="n"/>
+      <c r="Y22" s="328" t="n"/>
+      <c r="Z22" s="329" t="n"/>
+      <c r="AA22" s="301" t="n"/>
+      <c r="AB22" s="328" t="n"/>
+      <c r="AC22" s="328" t="n"/>
+      <c r="AD22" s="328" t="n"/>
+      <c r="AE22" s="328" t="n"/>
+      <c r="AF22" s="328" t="n"/>
+      <c r="AG22" s="328" t="n"/>
+      <c r="AH22" s="328" t="n"/>
+      <c r="AI22" s="328" t="n"/>
+      <c r="AJ22" s="328" t="n"/>
+      <c r="AK22" s="328" t="n"/>
+      <c r="AL22" s="328" t="n"/>
+      <c r="AM22" s="328" t="n"/>
+      <c r="AN22" s="328" t="n"/>
+      <c r="AO22" s="328" t="n"/>
+      <c r="AP22" s="328" t="n"/>
+      <c r="AQ22" s="329" t="n"/>
+      <c r="AR22" s="300" t="n"/>
+      <c r="AS22" s="328" t="n"/>
+      <c r="AT22" s="328" t="n"/>
+      <c r="AU22" s="328" t="n"/>
+      <c r="AV22" s="328" t="n"/>
+      <c r="AW22" s="329" t="n"/>
+      <c r="AX22" s="300" t="n"/>
+      <c r="AY22" s="328" t="n"/>
+      <c r="AZ22" s="328" t="n"/>
+      <c r="BA22" s="329" t="n"/>
+      <c r="BB22" s="302" t="n"/>
+      <c r="BC22" s="328" t="n"/>
+      <c r="BD22" s="330" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="584">
+      <c r="A23" s="633">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="585" t="inlineStr">
+      <c r="B23" s="276" t="n"/>
+      <c r="C23" s="277" t="n"/>
+      <c r="D23" s="299" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="567" t="n"/>
-      <c r="F23" s="567" t="n"/>
-      <c r="G23" s="568" t="n"/>
-      <c r="H23" s="566" t="n"/>
-      <c r="I23" s="567" t="n"/>
-      <c r="J23" s="567" t="n"/>
-      <c r="K23" s="567" t="n"/>
-      <c r="L23" s="567" t="n"/>
-      <c r="M23" s="567" t="n"/>
-      <c r="N23" s="567" t="n"/>
-      <c r="O23" s="567" t="n"/>
-      <c r="P23" s="567" t="n"/>
-      <c r="Q23" s="567" t="n"/>
-      <c r="R23" s="567" t="n"/>
-      <c r="S23" s="567" t="n"/>
-      <c r="T23" s="567" t="n"/>
-      <c r="U23" s="567" t="n"/>
-      <c r="V23" s="567" t="n"/>
-      <c r="W23" s="567" t="n"/>
-      <c r="X23" s="567" t="n"/>
-      <c r="Y23" s="567" t="n"/>
-      <c r="Z23" s="568" t="n"/>
-      <c r="AA23" s="586" t="n"/>
-      <c r="AB23" s="567" t="n"/>
-      <c r="AC23" s="567" t="n"/>
-      <c r="AD23" s="567" t="n"/>
-      <c r="AE23" s="567" t="n"/>
-      <c r="AF23" s="567" t="n"/>
-      <c r="AG23" s="567" t="n"/>
-      <c r="AH23" s="567" t="n"/>
-      <c r="AI23" s="567" t="n"/>
-      <c r="AJ23" s="567" t="n"/>
-      <c r="AK23" s="567" t="n"/>
-      <c r="AL23" s="567" t="n"/>
-      <c r="AM23" s="567" t="n"/>
-      <c r="AN23" s="567" t="n"/>
-      <c r="AO23" s="567" t="n"/>
-      <c r="AP23" s="567" t="n"/>
-      <c r="AQ23" s="568" t="n"/>
-      <c r="AR23" s="566" t="n"/>
-      <c r="AS23" s="567" t="n"/>
-      <c r="AT23" s="567" t="n"/>
-      <c r="AU23" s="567" t="n"/>
-      <c r="AV23" s="567" t="n"/>
-      <c r="AW23" s="568" t="n"/>
-      <c r="AX23" s="566" t="n"/>
-      <c r="AY23" s="567" t="n"/>
-      <c r="AZ23" s="567" t="n"/>
-      <c r="BA23" s="568" t="n"/>
-      <c r="BB23" s="587" t="n"/>
-      <c r="BC23" s="567" t="n"/>
-      <c r="BD23" s="570" t="n"/>
+      <c r="E23" s="328" t="n"/>
+      <c r="F23" s="328" t="n"/>
+      <c r="G23" s="329" t="n"/>
+      <c r="H23" s="300" t="n"/>
+      <c r="I23" s="328" t="n"/>
+      <c r="J23" s="328" t="n"/>
+      <c r="K23" s="328" t="n"/>
+      <c r="L23" s="328" t="n"/>
+      <c r="M23" s="328" t="n"/>
+      <c r="N23" s="328" t="n"/>
+      <c r="O23" s="328" t="n"/>
+      <c r="P23" s="328" t="n"/>
+      <c r="Q23" s="328" t="n"/>
+      <c r="R23" s="328" t="n"/>
+      <c r="S23" s="328" t="n"/>
+      <c r="T23" s="328" t="n"/>
+      <c r="U23" s="328" t="n"/>
+      <c r="V23" s="328" t="n"/>
+      <c r="W23" s="328" t="n"/>
+      <c r="X23" s="328" t="n"/>
+      <c r="Y23" s="328" t="n"/>
+      <c r="Z23" s="329" t="n"/>
+      <c r="AA23" s="301" t="n"/>
+      <c r="AB23" s="328" t="n"/>
+      <c r="AC23" s="328" t="n"/>
+      <c r="AD23" s="328" t="n"/>
+      <c r="AE23" s="328" t="n"/>
+      <c r="AF23" s="328" t="n"/>
+      <c r="AG23" s="328" t="n"/>
+      <c r="AH23" s="328" t="n"/>
+      <c r="AI23" s="328" t="n"/>
+      <c r="AJ23" s="328" t="n"/>
+      <c r="AK23" s="328" t="n"/>
+      <c r="AL23" s="328" t="n"/>
+      <c r="AM23" s="328" t="n"/>
+      <c r="AN23" s="328" t="n"/>
+      <c r="AO23" s="328" t="n"/>
+      <c r="AP23" s="328" t="n"/>
+      <c r="AQ23" s="329" t="n"/>
+      <c r="AR23" s="300" t="n"/>
+      <c r="AS23" s="328" t="n"/>
+      <c r="AT23" s="328" t="n"/>
+      <c r="AU23" s="328" t="n"/>
+      <c r="AV23" s="328" t="n"/>
+      <c r="AW23" s="329" t="n"/>
+      <c r="AX23" s="300" t="n"/>
+      <c r="AY23" s="328" t="n"/>
+      <c r="AZ23" s="328" t="n"/>
+      <c r="BA23" s="329" t="n"/>
+      <c r="BB23" s="302" t="n"/>
+      <c r="BC23" s="328" t="n"/>
+      <c r="BD23" s="330" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="588">
+      <c r="A24" s="634">
         <f>ROW()-ROW($A$19)+1</f>
         <v/>
       </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="589" t="inlineStr">
+      <c r="B24" s="281" t="n"/>
+      <c r="C24" s="282" t="n"/>
+      <c r="D24" s="635" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="573" t="n"/>
-      <c r="F24" s="573" t="n"/>
-      <c r="G24" s="574" t="n"/>
-      <c r="H24" s="572" t="n"/>
-      <c r="I24" s="573" t="n"/>
-      <c r="J24" s="573" t="n"/>
-      <c r="K24" s="573" t="n"/>
-      <c r="L24" s="573" t="n"/>
-      <c r="M24" s="573" t="n"/>
-      <c r="N24" s="573" t="n"/>
-      <c r="O24" s="573" t="n"/>
-      <c r="P24" s="573" t="n"/>
-      <c r="Q24" s="573" t="n"/>
-      <c r="R24" s="573" t="n"/>
-      <c r="S24" s="573" t="n"/>
-      <c r="T24" s="573" t="n"/>
-      <c r="U24" s="573" t="n"/>
-      <c r="V24" s="573" t="n"/>
-      <c r="W24" s="573" t="n"/>
-      <c r="X24" s="573" t="n"/>
-      <c r="Y24" s="573" t="n"/>
-      <c r="Z24" s="574" t="n"/>
-      <c r="AA24" s="590" t="n"/>
-      <c r="AB24" s="573" t="n"/>
-      <c r="AC24" s="573" t="n"/>
-      <c r="AD24" s="573" t="n"/>
-      <c r="AE24" s="573" t="n"/>
-      <c r="AF24" s="573" t="n"/>
-      <c r="AG24" s="573" t="n"/>
-      <c r="AH24" s="573" t="n"/>
-      <c r="AI24" s="573" t="n"/>
-      <c r="AJ24" s="573" t="n"/>
-      <c r="AK24" s="573" t="n"/>
-      <c r="AL24" s="573" t="n"/>
-      <c r="AM24" s="573" t="n"/>
-      <c r="AN24" s="573" t="n"/>
-      <c r="AO24" s="573" t="n"/>
-      <c r="AP24" s="573" t="n"/>
-      <c r="AQ24" s="574" t="n"/>
-      <c r="AR24" s="572" t="n"/>
-      <c r="AS24" s="573" t="n"/>
-      <c r="AT24" s="573" t="n"/>
-      <c r="AU24" s="573" t="n"/>
-      <c r="AV24" s="573" t="n"/>
-      <c r="AW24" s="574" t="n"/>
-      <c r="AX24" s="572" t="n"/>
-      <c r="AY24" s="573" t="n"/>
-      <c r="AZ24" s="573" t="n"/>
-      <c r="BA24" s="574" t="n"/>
-      <c r="BB24" s="591" t="n"/>
-      <c r="BC24" s="573" t="n"/>
-      <c r="BD24" s="576" t="n"/>
+      <c r="E24" s="337" t="n"/>
+      <c r="F24" s="337" t="n"/>
+      <c r="G24" s="626" t="n"/>
+      <c r="H24" s="625" t="n"/>
+      <c r="I24" s="337" t="n"/>
+      <c r="J24" s="337" t="n"/>
+      <c r="K24" s="337" t="n"/>
+      <c r="L24" s="337" t="n"/>
+      <c r="M24" s="337" t="n"/>
+      <c r="N24" s="337" t="n"/>
+      <c r="O24" s="337" t="n"/>
+      <c r="P24" s="337" t="n"/>
+      <c r="Q24" s="337" t="n"/>
+      <c r="R24" s="337" t="n"/>
+      <c r="S24" s="337" t="n"/>
+      <c r="T24" s="337" t="n"/>
+      <c r="U24" s="337" t="n"/>
+      <c r="V24" s="337" t="n"/>
+      <c r="W24" s="337" t="n"/>
+      <c r="X24" s="337" t="n"/>
+      <c r="Y24" s="337" t="n"/>
+      <c r="Z24" s="626" t="n"/>
+      <c r="AA24" s="636" t="n"/>
+      <c r="AB24" s="337" t="n"/>
+      <c r="AC24" s="337" t="n"/>
+      <c r="AD24" s="337" t="n"/>
+      <c r="AE24" s="337" t="n"/>
+      <c r="AF24" s="337" t="n"/>
+      <c r="AG24" s="337" t="n"/>
+      <c r="AH24" s="337" t="n"/>
+      <c r="AI24" s="337" t="n"/>
+      <c r="AJ24" s="337" t="n"/>
+      <c r="AK24" s="337" t="n"/>
+      <c r="AL24" s="337" t="n"/>
+      <c r="AM24" s="337" t="n"/>
+      <c r="AN24" s="337" t="n"/>
+      <c r="AO24" s="337" t="n"/>
+      <c r="AP24" s="337" t="n"/>
+      <c r="AQ24" s="626" t="n"/>
+      <c r="AR24" s="625" t="n"/>
+      <c r="AS24" s="337" t="n"/>
+      <c r="AT24" s="337" t="n"/>
+      <c r="AU24" s="337" t="n"/>
+      <c r="AV24" s="337" t="n"/>
+      <c r="AW24" s="626" t="n"/>
+      <c r="AX24" s="625" t="n"/>
+      <c r="AY24" s="337" t="n"/>
+      <c r="AZ24" s="337" t="n"/>
+      <c r="BA24" s="626" t="n"/>
+      <c r="BB24" s="637" t="n"/>
+      <c r="BC24" s="337" t="n"/>
+      <c r="BD24" s="338" t="n"/>
     </row>
     <row r="25" ht="3" customHeight="1">
       <c r="A25" s="592" t="n"/>
@@ -8392,264 +8506,264 @@
       <c r="BD25" s="578" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="558" t="inlineStr">
+      <c r="A26" s="618" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-      <c r="O26" s="27" t="n"/>
-      <c r="P26" s="27" t="n"/>
-      <c r="Q26" s="27" t="n"/>
-      <c r="R26" s="27" t="n"/>
-      <c r="S26" s="27" t="n"/>
-      <c r="T26" s="27" t="n"/>
-      <c r="U26" s="27" t="n"/>
-      <c r="V26" s="27" t="n"/>
-      <c r="W26" s="27" t="n"/>
-      <c r="X26" s="27" t="n"/>
-      <c r="Y26" s="27" t="n"/>
-      <c r="Z26" s="27" t="n"/>
-      <c r="AA26" s="27" t="n"/>
-      <c r="AB26" s="27" t="n"/>
-      <c r="AC26" s="27" t="n"/>
-      <c r="AD26" s="27" t="n"/>
-      <c r="AE26" s="27" t="n"/>
-      <c r="AF26" s="27" t="n"/>
-      <c r="AG26" s="27" t="n"/>
-      <c r="AH26" s="27" t="n"/>
-      <c r="AI26" s="27" t="n"/>
-      <c r="AJ26" s="27" t="n"/>
-      <c r="AK26" s="27" t="n"/>
-      <c r="AL26" s="27" t="n"/>
-      <c r="AM26" s="27" t="n"/>
-      <c r="AN26" s="27" t="n"/>
-      <c r="AO26" s="27" t="n"/>
-      <c r="AP26" s="27" t="n"/>
-      <c r="AQ26" s="27" t="n"/>
-      <c r="AR26" s="27" t="n"/>
-      <c r="AS26" s="27" t="n"/>
-      <c r="AT26" s="27" t="n"/>
-      <c r="AU26" s="27" t="n"/>
-      <c r="AV26" s="27" t="n"/>
-      <c r="AW26" s="27" t="n"/>
-      <c r="AX26" s="27" t="n"/>
-      <c r="AY26" s="27" t="n"/>
-      <c r="AZ26" s="27" t="n"/>
-      <c r="BA26" s="27" t="n"/>
-      <c r="BB26" s="27" t="n"/>
-      <c r="BC26" s="27" t="n"/>
-      <c r="BD26" s="28" t="n"/>
+      <c r="B26" s="285" t="n"/>
+      <c r="C26" s="285" t="n"/>
+      <c r="D26" s="285" t="n"/>
+      <c r="E26" s="285" t="n"/>
+      <c r="F26" s="285" t="n"/>
+      <c r="G26" s="285" t="n"/>
+      <c r="H26" s="285" t="n"/>
+      <c r="I26" s="285" t="n"/>
+      <c r="J26" s="285" t="n"/>
+      <c r="K26" s="285" t="n"/>
+      <c r="L26" s="285" t="n"/>
+      <c r="M26" s="285" t="n"/>
+      <c r="N26" s="285" t="n"/>
+      <c r="O26" s="285" t="n"/>
+      <c r="P26" s="285" t="n"/>
+      <c r="Q26" s="285" t="n"/>
+      <c r="R26" s="285" t="n"/>
+      <c r="S26" s="285" t="n"/>
+      <c r="T26" s="285" t="n"/>
+      <c r="U26" s="285" t="n"/>
+      <c r="V26" s="285" t="n"/>
+      <c r="W26" s="285" t="n"/>
+      <c r="X26" s="285" t="n"/>
+      <c r="Y26" s="285" t="n"/>
+      <c r="Z26" s="285" t="n"/>
+      <c r="AA26" s="285" t="n"/>
+      <c r="AB26" s="285" t="n"/>
+      <c r="AC26" s="285" t="n"/>
+      <c r="AD26" s="285" t="n"/>
+      <c r="AE26" s="285" t="n"/>
+      <c r="AF26" s="285" t="n"/>
+      <c r="AG26" s="285" t="n"/>
+      <c r="AH26" s="285" t="n"/>
+      <c r="AI26" s="285" t="n"/>
+      <c r="AJ26" s="285" t="n"/>
+      <c r="AK26" s="285" t="n"/>
+      <c r="AL26" s="285" t="n"/>
+      <c r="AM26" s="285" t="n"/>
+      <c r="AN26" s="285" t="n"/>
+      <c r="AO26" s="285" t="n"/>
+      <c r="AP26" s="285" t="n"/>
+      <c r="AQ26" s="285" t="n"/>
+      <c r="AR26" s="285" t="n"/>
+      <c r="AS26" s="285" t="n"/>
+      <c r="AT26" s="285" t="n"/>
+      <c r="AU26" s="285" t="n"/>
+      <c r="AV26" s="285" t="n"/>
+      <c r="AW26" s="285" t="n"/>
+      <c r="AX26" s="285" t="n"/>
+      <c r="AY26" s="285" t="n"/>
+      <c r="AZ26" s="285" t="n"/>
+      <c r="BA26" s="285" t="n"/>
+      <c r="BB26" s="285" t="n"/>
+      <c r="BC26" s="285" t="n"/>
+      <c r="BD26" s="286" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="559" t="inlineStr">
+      <c r="A27" s="619" t="inlineStr">
         <is>
           <t>Defect Count</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="560" t="n"/>
-      <c r="L27" s="561" t="n"/>
-      <c r="M27" s="561" t="n"/>
-      <c r="N27" s="561" t="n"/>
-      <c r="O27" s="561" t="n"/>
-      <c r="P27" s="561" t="n"/>
-      <c r="Q27" s="561" t="n"/>
-      <c r="R27" s="561" t="n"/>
-      <c r="S27" s="561" t="n"/>
-      <c r="T27" s="561" t="n"/>
-      <c r="U27" s="561" t="n"/>
-      <c r="V27" s="561" t="n"/>
-      <c r="W27" s="561" t="n"/>
-      <c r="X27" s="561" t="n"/>
-      <c r="Y27" s="561" t="n"/>
-      <c r="Z27" s="561" t="n"/>
-      <c r="AA27" s="561" t="n"/>
-      <c r="AB27" s="562" t="n"/>
-      <c r="AC27" s="563" t="inlineStr">
+      <c r="B27" s="271" t="n"/>
+      <c r="C27" s="271" t="n"/>
+      <c r="D27" s="271" t="n"/>
+      <c r="E27" s="271" t="n"/>
+      <c r="F27" s="271" t="n"/>
+      <c r="G27" s="271" t="n"/>
+      <c r="H27" s="271" t="n"/>
+      <c r="I27" s="271" t="n"/>
+      <c r="J27" s="272" t="n"/>
+      <c r="K27" s="288" t="n"/>
+      <c r="L27" s="325" t="n"/>
+      <c r="M27" s="325" t="n"/>
+      <c r="N27" s="325" t="n"/>
+      <c r="O27" s="325" t="n"/>
+      <c r="P27" s="325" t="n"/>
+      <c r="Q27" s="325" t="n"/>
+      <c r="R27" s="325" t="n"/>
+      <c r="S27" s="325" t="n"/>
+      <c r="T27" s="325" t="n"/>
+      <c r="U27" s="325" t="n"/>
+      <c r="V27" s="325" t="n"/>
+      <c r="W27" s="325" t="n"/>
+      <c r="X27" s="325" t="n"/>
+      <c r="Y27" s="325" t="n"/>
+      <c r="Z27" s="325" t="n"/>
+      <c r="AA27" s="325" t="n"/>
+      <c r="AB27" s="326" t="n"/>
+      <c r="AC27" s="620" t="inlineStr">
         <is>
           <t>AQL Disposition</t>
         </is>
       </c>
-      <c r="AD27" s="5" t="n"/>
-      <c r="AE27" s="5" t="n"/>
-      <c r="AF27" s="5" t="n"/>
-      <c r="AG27" s="5" t="n"/>
-      <c r="AH27" s="5" t="n"/>
-      <c r="AI27" s="5" t="n"/>
-      <c r="AJ27" s="5" t="n"/>
-      <c r="AK27" s="5" t="n"/>
-      <c r="AL27" s="6" t="n"/>
-      <c r="AM27" s="560" t="n"/>
-      <c r="AN27" s="561" t="n"/>
-      <c r="AO27" s="561" t="n"/>
-      <c r="AP27" s="561" t="n"/>
-      <c r="AQ27" s="561" t="n"/>
-      <c r="AR27" s="561" t="n"/>
-      <c r="AS27" s="561" t="n"/>
-      <c r="AT27" s="561" t="n"/>
-      <c r="AU27" s="561" t="n"/>
-      <c r="AV27" s="561" t="n"/>
-      <c r="AW27" s="561" t="n"/>
-      <c r="AX27" s="561" t="n"/>
-      <c r="AY27" s="561" t="n"/>
-      <c r="AZ27" s="561" t="n"/>
-      <c r="BA27" s="561" t="n"/>
-      <c r="BB27" s="561" t="n"/>
-      <c r="BC27" s="561" t="n"/>
-      <c r="BD27" s="564" t="n"/>
+      <c r="AD27" s="271" t="n"/>
+      <c r="AE27" s="271" t="n"/>
+      <c r="AF27" s="271" t="n"/>
+      <c r="AG27" s="271" t="n"/>
+      <c r="AH27" s="271" t="n"/>
+      <c r="AI27" s="271" t="n"/>
+      <c r="AJ27" s="271" t="n"/>
+      <c r="AK27" s="271" t="n"/>
+      <c r="AL27" s="272" t="n"/>
+      <c r="AM27" s="290" t="n"/>
+      <c r="AN27" s="325" t="n"/>
+      <c r="AO27" s="325" t="n"/>
+      <c r="AP27" s="325" t="n"/>
+      <c r="AQ27" s="325" t="n"/>
+      <c r="AR27" s="325" t="n"/>
+      <c r="AS27" s="325" t="n"/>
+      <c r="AT27" s="325" t="n"/>
+      <c r="AU27" s="325" t="n"/>
+      <c r="AV27" s="325" t="n"/>
+      <c r="AW27" s="325" t="n"/>
+      <c r="AX27" s="325" t="n"/>
+      <c r="AY27" s="325" t="n"/>
+      <c r="AZ27" s="325" t="n"/>
+      <c r="BA27" s="325" t="n"/>
+      <c r="BB27" s="325" t="n"/>
+      <c r="BC27" s="325" t="n"/>
+      <c r="BD27" s="327" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="565" t="inlineStr">
+      <c r="A28" s="621" t="inlineStr">
         <is>
           <t>100% Sort Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="566" t="n"/>
-      <c r="L28" s="567" t="n"/>
-      <c r="M28" s="567" t="n"/>
-      <c r="N28" s="567" t="n"/>
-      <c r="O28" s="567" t="n"/>
-      <c r="P28" s="567" t="n"/>
-      <c r="Q28" s="567" t="n"/>
-      <c r="R28" s="567" t="n"/>
-      <c r="S28" s="567" t="n"/>
-      <c r="T28" s="567" t="n"/>
-      <c r="U28" s="567" t="n"/>
-      <c r="V28" s="567" t="n"/>
-      <c r="W28" s="567" t="n"/>
-      <c r="X28" s="567" t="n"/>
-      <c r="Y28" s="567" t="n"/>
-      <c r="Z28" s="567" t="n"/>
-      <c r="AA28" s="567" t="n"/>
-      <c r="AB28" s="568" t="n"/>
-      <c r="AC28" s="569" t="inlineStr">
+      <c r="B28" s="276" t="n"/>
+      <c r="C28" s="276" t="n"/>
+      <c r="D28" s="276" t="n"/>
+      <c r="E28" s="276" t="n"/>
+      <c r="F28" s="276" t="n"/>
+      <c r="G28" s="276" t="n"/>
+      <c r="H28" s="276" t="n"/>
+      <c r="I28" s="276" t="n"/>
+      <c r="J28" s="277" t="n"/>
+      <c r="K28" s="300" t="n"/>
+      <c r="L28" s="328" t="n"/>
+      <c r="M28" s="328" t="n"/>
+      <c r="N28" s="328" t="n"/>
+      <c r="O28" s="328" t="n"/>
+      <c r="P28" s="328" t="n"/>
+      <c r="Q28" s="328" t="n"/>
+      <c r="R28" s="328" t="n"/>
+      <c r="S28" s="328" t="n"/>
+      <c r="T28" s="328" t="n"/>
+      <c r="U28" s="328" t="n"/>
+      <c r="V28" s="328" t="n"/>
+      <c r="W28" s="328" t="n"/>
+      <c r="X28" s="328" t="n"/>
+      <c r="Y28" s="328" t="n"/>
+      <c r="Z28" s="328" t="n"/>
+      <c r="AA28" s="328" t="n"/>
+      <c r="AB28" s="329" t="n"/>
+      <c r="AC28" s="622" t="inlineStr">
         <is>
           <t>Linked NCR Ref</t>
         </is>
       </c>
-      <c r="AD28" s="12" t="n"/>
-      <c r="AE28" s="12" t="n"/>
-      <c r="AF28" s="12" t="n"/>
-      <c r="AG28" s="12" t="n"/>
-      <c r="AH28" s="12" t="n"/>
-      <c r="AI28" s="12" t="n"/>
-      <c r="AJ28" s="12" t="n"/>
-      <c r="AK28" s="12" t="n"/>
-      <c r="AL28" s="13" t="n"/>
-      <c r="AM28" s="566" t="n"/>
-      <c r="AN28" s="567" t="n"/>
-      <c r="AO28" s="567" t="n"/>
-      <c r="AP28" s="567" t="n"/>
-      <c r="AQ28" s="567" t="n"/>
-      <c r="AR28" s="567" t="n"/>
-      <c r="AS28" s="567" t="n"/>
-      <c r="AT28" s="567" t="n"/>
-      <c r="AU28" s="567" t="n"/>
-      <c r="AV28" s="567" t="n"/>
-      <c r="AW28" s="567" t="n"/>
-      <c r="AX28" s="567" t="n"/>
-      <c r="AY28" s="567" t="n"/>
-      <c r="AZ28" s="567" t="n"/>
-      <c r="BA28" s="567" t="n"/>
-      <c r="BB28" s="567" t="n"/>
-      <c r="BC28" s="567" t="n"/>
-      <c r="BD28" s="570" t="n"/>
+      <c r="AD28" s="276" t="n"/>
+      <c r="AE28" s="276" t="n"/>
+      <c r="AF28" s="276" t="n"/>
+      <c r="AG28" s="276" t="n"/>
+      <c r="AH28" s="276" t="n"/>
+      <c r="AI28" s="276" t="n"/>
+      <c r="AJ28" s="276" t="n"/>
+      <c r="AK28" s="276" t="n"/>
+      <c r="AL28" s="277" t="n"/>
+      <c r="AM28" s="623" t="n"/>
+      <c r="AN28" s="328" t="n"/>
+      <c r="AO28" s="328" t="n"/>
+      <c r="AP28" s="328" t="n"/>
+      <c r="AQ28" s="328" t="n"/>
+      <c r="AR28" s="328" t="n"/>
+      <c r="AS28" s="328" t="n"/>
+      <c r="AT28" s="328" t="n"/>
+      <c r="AU28" s="328" t="n"/>
+      <c r="AV28" s="328" t="n"/>
+      <c r="AW28" s="328" t="n"/>
+      <c r="AX28" s="328" t="n"/>
+      <c r="AY28" s="328" t="n"/>
+      <c r="AZ28" s="328" t="n"/>
+      <c r="BA28" s="328" t="n"/>
+      <c r="BB28" s="328" t="n"/>
+      <c r="BC28" s="328" t="n"/>
+      <c r="BD28" s="330" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="571" t="inlineStr">
+      <c r="A29" s="624" t="inlineStr">
         <is>
           <t>Lot Release Decision</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="572" t="n"/>
-      <c r="L29" s="573" t="n"/>
-      <c r="M29" s="573" t="n"/>
-      <c r="N29" s="573" t="n"/>
-      <c r="O29" s="573" t="n"/>
-      <c r="P29" s="573" t="n"/>
-      <c r="Q29" s="573" t="n"/>
-      <c r="R29" s="573" t="n"/>
-      <c r="S29" s="573" t="n"/>
-      <c r="T29" s="573" t="n"/>
-      <c r="U29" s="573" t="n"/>
-      <c r="V29" s="573" t="n"/>
-      <c r="W29" s="573" t="n"/>
-      <c r="X29" s="573" t="n"/>
-      <c r="Y29" s="573" t="n"/>
-      <c r="Z29" s="573" t="n"/>
-      <c r="AA29" s="573" t="n"/>
-      <c r="AB29" s="574" t="n"/>
-      <c r="AC29" s="575" t="inlineStr">
+      <c r="B29" s="281" t="n"/>
+      <c r="C29" s="281" t="n"/>
+      <c r="D29" s="281" t="n"/>
+      <c r="E29" s="281" t="n"/>
+      <c r="F29" s="281" t="n"/>
+      <c r="G29" s="281" t="n"/>
+      <c r="H29" s="281" t="n"/>
+      <c r="I29" s="281" t="n"/>
+      <c r="J29" s="282" t="n"/>
+      <c r="K29" s="625" t="n"/>
+      <c r="L29" s="337" t="n"/>
+      <c r="M29" s="337" t="n"/>
+      <c r="N29" s="337" t="n"/>
+      <c r="O29" s="337" t="n"/>
+      <c r="P29" s="337" t="n"/>
+      <c r="Q29" s="337" t="n"/>
+      <c r="R29" s="337" t="n"/>
+      <c r="S29" s="337" t="n"/>
+      <c r="T29" s="337" t="n"/>
+      <c r="U29" s="337" t="n"/>
+      <c r="V29" s="337" t="n"/>
+      <c r="W29" s="337" t="n"/>
+      <c r="X29" s="337" t="n"/>
+      <c r="Y29" s="337" t="n"/>
+      <c r="Z29" s="337" t="n"/>
+      <c r="AA29" s="337" t="n"/>
+      <c r="AB29" s="626" t="n"/>
+      <c r="AC29" s="627" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="AD29" s="19" t="n"/>
-      <c r="AE29" s="19" t="n"/>
-      <c r="AF29" s="19" t="n"/>
-      <c r="AG29" s="19" t="n"/>
-      <c r="AH29" s="19" t="n"/>
-      <c r="AI29" s="19" t="n"/>
-      <c r="AJ29" s="19" t="n"/>
-      <c r="AK29" s="19" t="n"/>
-      <c r="AL29" s="22" t="n"/>
-      <c r="AM29" s="572" t="n"/>
-      <c r="AN29" s="573" t="n"/>
-      <c r="AO29" s="573" t="n"/>
-      <c r="AP29" s="573" t="n"/>
-      <c r="AQ29" s="573" t="n"/>
-      <c r="AR29" s="573" t="n"/>
-      <c r="AS29" s="573" t="n"/>
-      <c r="AT29" s="573" t="n"/>
-      <c r="AU29" s="573" t="n"/>
-      <c r="AV29" s="573" t="n"/>
-      <c r="AW29" s="573" t="n"/>
-      <c r="AX29" s="573" t="n"/>
-      <c r="AY29" s="573" t="n"/>
-      <c r="AZ29" s="573" t="n"/>
-      <c r="BA29" s="573" t="n"/>
-      <c r="BB29" s="573" t="n"/>
-      <c r="BC29" s="573" t="n"/>
-      <c r="BD29" s="576" t="n"/>
+      <c r="AD29" s="281" t="n"/>
+      <c r="AE29" s="281" t="n"/>
+      <c r="AF29" s="281" t="n"/>
+      <c r="AG29" s="281" t="n"/>
+      <c r="AH29" s="281" t="n"/>
+      <c r="AI29" s="281" t="n"/>
+      <c r="AJ29" s="281" t="n"/>
+      <c r="AK29" s="281" t="n"/>
+      <c r="AL29" s="282" t="n"/>
+      <c r="AM29" s="628" t="n"/>
+      <c r="AN29" s="337" t="n"/>
+      <c r="AO29" s="337" t="n"/>
+      <c r="AP29" s="337" t="n"/>
+      <c r="AQ29" s="337" t="n"/>
+      <c r="AR29" s="337" t="n"/>
+      <c r="AS29" s="337" t="n"/>
+      <c r="AT29" s="337" t="n"/>
+      <c r="AU29" s="337" t="n"/>
+      <c r="AV29" s="337" t="n"/>
+      <c r="AW29" s="337" t="n"/>
+      <c r="AX29" s="337" t="n"/>
+      <c r="AY29" s="337" t="n"/>
+      <c r="AZ29" s="337" t="n"/>
+      <c r="BA29" s="337" t="n"/>
+      <c r="BB29" s="337" t="n"/>
+      <c r="BC29" s="337" t="n"/>
+      <c r="BD29" s="338" t="n"/>
     </row>
     <row r="30" ht="3" customHeight="1">
       <c r="A30" s="592" t="n"/>
@@ -8710,322 +8824,322 @@
       <c r="BD30" s="578" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="558" t="inlineStr">
+      <c r="A31" s="618" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="27" t="n"/>
-      <c r="K31" s="27" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="27" t="n"/>
-      <c r="N31" s="27" t="n"/>
-      <c r="O31" s="27" t="n"/>
-      <c r="P31" s="27" t="n"/>
-      <c r="Q31" s="27" t="n"/>
-      <c r="R31" s="27" t="n"/>
-      <c r="S31" s="27" t="n"/>
-      <c r="T31" s="27" t="n"/>
-      <c r="U31" s="27" t="n"/>
-      <c r="V31" s="27" t="n"/>
-      <c r="W31" s="27" t="n"/>
-      <c r="X31" s="27" t="n"/>
-      <c r="Y31" s="27" t="n"/>
-      <c r="Z31" s="27" t="n"/>
-      <c r="AA31" s="27" t="n"/>
-      <c r="AB31" s="27" t="n"/>
-      <c r="AC31" s="27" t="n"/>
-      <c r="AD31" s="27" t="n"/>
-      <c r="AE31" s="27" t="n"/>
-      <c r="AF31" s="27" t="n"/>
-      <c r="AG31" s="27" t="n"/>
-      <c r="AH31" s="27" t="n"/>
-      <c r="AI31" s="27" t="n"/>
-      <c r="AJ31" s="27" t="n"/>
-      <c r="AK31" s="27" t="n"/>
-      <c r="AL31" s="27" t="n"/>
-      <c r="AM31" s="27" t="n"/>
-      <c r="AN31" s="27" t="n"/>
-      <c r="AO31" s="27" t="n"/>
-      <c r="AP31" s="27" t="n"/>
-      <c r="AQ31" s="27" t="n"/>
-      <c r="AR31" s="27" t="n"/>
-      <c r="AS31" s="27" t="n"/>
-      <c r="AT31" s="27" t="n"/>
-      <c r="AU31" s="27" t="n"/>
-      <c r="AV31" s="27" t="n"/>
-      <c r="AW31" s="27" t="n"/>
-      <c r="AX31" s="27" t="n"/>
-      <c r="AY31" s="27" t="n"/>
-      <c r="AZ31" s="27" t="n"/>
-      <c r="BA31" s="27" t="n"/>
-      <c r="BB31" s="27" t="n"/>
-      <c r="BC31" s="27" t="n"/>
-      <c r="BD31" s="28" t="n"/>
+      <c r="B31" s="285" t="n"/>
+      <c r="C31" s="285" t="n"/>
+      <c r="D31" s="285" t="n"/>
+      <c r="E31" s="285" t="n"/>
+      <c r="F31" s="285" t="n"/>
+      <c r="G31" s="285" t="n"/>
+      <c r="H31" s="285" t="n"/>
+      <c r="I31" s="285" t="n"/>
+      <c r="J31" s="285" t="n"/>
+      <c r="K31" s="285" t="n"/>
+      <c r="L31" s="285" t="n"/>
+      <c r="M31" s="285" t="n"/>
+      <c r="N31" s="285" t="n"/>
+      <c r="O31" s="285" t="n"/>
+      <c r="P31" s="285" t="n"/>
+      <c r="Q31" s="285" t="n"/>
+      <c r="R31" s="285" t="n"/>
+      <c r="S31" s="285" t="n"/>
+      <c r="T31" s="285" t="n"/>
+      <c r="U31" s="285" t="n"/>
+      <c r="V31" s="285" t="n"/>
+      <c r="W31" s="285" t="n"/>
+      <c r="X31" s="285" t="n"/>
+      <c r="Y31" s="285" t="n"/>
+      <c r="Z31" s="285" t="n"/>
+      <c r="AA31" s="285" t="n"/>
+      <c r="AB31" s="285" t="n"/>
+      <c r="AC31" s="285" t="n"/>
+      <c r="AD31" s="285" t="n"/>
+      <c r="AE31" s="285" t="n"/>
+      <c r="AF31" s="285" t="n"/>
+      <c r="AG31" s="285" t="n"/>
+      <c r="AH31" s="285" t="n"/>
+      <c r="AI31" s="285" t="n"/>
+      <c r="AJ31" s="285" t="n"/>
+      <c r="AK31" s="285" t="n"/>
+      <c r="AL31" s="285" t="n"/>
+      <c r="AM31" s="285" t="n"/>
+      <c r="AN31" s="285" t="n"/>
+      <c r="AO31" s="285" t="n"/>
+      <c r="AP31" s="285" t="n"/>
+      <c r="AQ31" s="285" t="n"/>
+      <c r="AR31" s="285" t="n"/>
+      <c r="AS31" s="285" t="n"/>
+      <c r="AT31" s="285" t="n"/>
+      <c r="AU31" s="285" t="n"/>
+      <c r="AV31" s="285" t="n"/>
+      <c r="AW31" s="285" t="n"/>
+      <c r="AX31" s="285" t="n"/>
+      <c r="AY31" s="285" t="n"/>
+      <c r="AZ31" s="285" t="n"/>
+      <c r="BA31" s="285" t="n"/>
+      <c r="BB31" s="285" t="n"/>
+      <c r="BC31" s="285" t="n"/>
+      <c r="BD31" s="286" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="580" t="inlineStr">
+      <c r="A32" s="629" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="6" t="n"/>
-      <c r="S32" s="597" t="inlineStr">
+      <c r="B32" s="271" t="n"/>
+      <c r="C32" s="271" t="n"/>
+      <c r="D32" s="271" t="n"/>
+      <c r="E32" s="271" t="n"/>
+      <c r="F32" s="271" t="n"/>
+      <c r="G32" s="271" t="n"/>
+      <c r="H32" s="271" t="n"/>
+      <c r="I32" s="271" t="n"/>
+      <c r="J32" s="271" t="n"/>
+      <c r="K32" s="271" t="n"/>
+      <c r="L32" s="271" t="n"/>
+      <c r="M32" s="271" t="n"/>
+      <c r="N32" s="271" t="n"/>
+      <c r="O32" s="271" t="n"/>
+      <c r="P32" s="271" t="n"/>
+      <c r="Q32" s="271" t="n"/>
+      <c r="R32" s="272" t="n"/>
+      <c r="S32" s="638" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-      <c r="Y32" s="5" t="n"/>
-      <c r="Z32" s="5" t="n"/>
-      <c r="AA32" s="5" t="n"/>
-      <c r="AB32" s="5" t="n"/>
-      <c r="AC32" s="5" t="n"/>
-      <c r="AD32" s="5" t="n"/>
-      <c r="AE32" s="5" t="n"/>
-      <c r="AF32" s="5" t="n"/>
-      <c r="AG32" s="5" t="n"/>
-      <c r="AH32" s="5" t="n"/>
-      <c r="AI32" s="5" t="n"/>
-      <c r="AJ32" s="6" t="n"/>
-      <c r="AK32" s="597" t="inlineStr">
+      <c r="T32" s="271" t="n"/>
+      <c r="U32" s="271" t="n"/>
+      <c r="V32" s="271" t="n"/>
+      <c r="W32" s="271" t="n"/>
+      <c r="X32" s="271" t="n"/>
+      <c r="Y32" s="271" t="n"/>
+      <c r="Z32" s="271" t="n"/>
+      <c r="AA32" s="271" t="n"/>
+      <c r="AB32" s="271" t="n"/>
+      <c r="AC32" s="271" t="n"/>
+      <c r="AD32" s="271" t="n"/>
+      <c r="AE32" s="271" t="n"/>
+      <c r="AF32" s="271" t="n"/>
+      <c r="AG32" s="271" t="n"/>
+      <c r="AH32" s="271" t="n"/>
+      <c r="AI32" s="271" t="n"/>
+      <c r="AJ32" s="272" t="n"/>
+      <c r="AK32" s="639" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL32" s="5" t="n"/>
-      <c r="AM32" s="5" t="n"/>
-      <c r="AN32" s="5" t="n"/>
-      <c r="AO32" s="5" t="n"/>
-      <c r="AP32" s="5" t="n"/>
-      <c r="AQ32" s="5" t="n"/>
-      <c r="AR32" s="5" t="n"/>
-      <c r="AS32" s="5" t="n"/>
-      <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="5" t="n"/>
-      <c r="AV32" s="5" t="n"/>
-      <c r="AW32" s="5" t="n"/>
-      <c r="AX32" s="5" t="n"/>
-      <c r="AY32" s="5" t="n"/>
-      <c r="AZ32" s="5" t="n"/>
-      <c r="BA32" s="5" t="n"/>
-      <c r="BB32" s="5" t="n"/>
-      <c r="BC32" s="5" t="n"/>
-      <c r="BD32" s="8" t="n"/>
+      <c r="AL32" s="271" t="n"/>
+      <c r="AM32" s="271" t="n"/>
+      <c r="AN32" s="271" t="n"/>
+      <c r="AO32" s="271" t="n"/>
+      <c r="AP32" s="271" t="n"/>
+      <c r="AQ32" s="271" t="n"/>
+      <c r="AR32" s="271" t="n"/>
+      <c r="AS32" s="271" t="n"/>
+      <c r="AT32" s="271" t="n"/>
+      <c r="AU32" s="271" t="n"/>
+      <c r="AV32" s="271" t="n"/>
+      <c r="AW32" s="271" t="n"/>
+      <c r="AX32" s="271" t="n"/>
+      <c r="AY32" s="271" t="n"/>
+      <c r="AZ32" s="271" t="n"/>
+      <c r="BA32" s="271" t="n"/>
+      <c r="BB32" s="271" t="n"/>
+      <c r="BC32" s="271" t="n"/>
+      <c r="BD32" s="274" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="598" t="inlineStr">
+      <c r="A33" s="640" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B33" s="567" t="n"/>
-      <c r="C33" s="567" t="n"/>
-      <c r="D33" s="567" t="n"/>
-      <c r="E33" s="567" t="n"/>
-      <c r="F33" s="567" t="n"/>
-      <c r="G33" s="567" t="n"/>
-      <c r="H33" s="567" t="n"/>
-      <c r="I33" s="567" t="n"/>
-      <c r="J33" s="567" t="n"/>
-      <c r="K33" s="567" t="n"/>
-      <c r="L33" s="567" t="n"/>
-      <c r="M33" s="567" t="n"/>
-      <c r="N33" s="567" t="n"/>
-      <c r="O33" s="567" t="n"/>
-      <c r="P33" s="567" t="n"/>
-      <c r="Q33" s="567" t="n"/>
-      <c r="R33" s="568" t="n"/>
-      <c r="S33" s="599" t="inlineStr">
+      <c r="B33" s="334" t="n"/>
+      <c r="C33" s="334" t="n"/>
+      <c r="D33" s="334" t="n"/>
+      <c r="E33" s="334" t="n"/>
+      <c r="F33" s="334" t="n"/>
+      <c r="G33" s="334" t="n"/>
+      <c r="H33" s="334" t="n"/>
+      <c r="I33" s="334" t="n"/>
+      <c r="J33" s="334" t="n"/>
+      <c r="K33" s="334" t="n"/>
+      <c r="L33" s="334" t="n"/>
+      <c r="M33" s="334" t="n"/>
+      <c r="N33" s="334" t="n"/>
+      <c r="O33" s="334" t="n"/>
+      <c r="P33" s="334" t="n"/>
+      <c r="Q33" s="334" t="n"/>
+      <c r="R33" s="641" t="n"/>
+      <c r="S33" s="642" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T33" s="567" t="n"/>
-      <c r="U33" s="567" t="n"/>
-      <c r="V33" s="567" t="n"/>
-      <c r="W33" s="567" t="n"/>
-      <c r="X33" s="567" t="n"/>
-      <c r="Y33" s="567" t="n"/>
-      <c r="Z33" s="567" t="n"/>
-      <c r="AA33" s="567" t="n"/>
-      <c r="AB33" s="567" t="n"/>
-      <c r="AC33" s="567" t="n"/>
-      <c r="AD33" s="567" t="n"/>
-      <c r="AE33" s="567" t="n"/>
-      <c r="AF33" s="567" t="n"/>
-      <c r="AG33" s="567" t="n"/>
-      <c r="AH33" s="567" t="n"/>
-      <c r="AI33" s="567" t="n"/>
-      <c r="AJ33" s="568" t="n"/>
-      <c r="AK33" s="599" t="inlineStr">
+      <c r="T33" s="334" t="n"/>
+      <c r="U33" s="334" t="n"/>
+      <c r="V33" s="334" t="n"/>
+      <c r="W33" s="334" t="n"/>
+      <c r="X33" s="334" t="n"/>
+      <c r="Y33" s="334" t="n"/>
+      <c r="Z33" s="334" t="n"/>
+      <c r="AA33" s="334" t="n"/>
+      <c r="AB33" s="334" t="n"/>
+      <c r="AC33" s="334" t="n"/>
+      <c r="AD33" s="334" t="n"/>
+      <c r="AE33" s="334" t="n"/>
+      <c r="AF33" s="334" t="n"/>
+      <c r="AG33" s="334" t="n"/>
+      <c r="AH33" s="334" t="n"/>
+      <c r="AI33" s="334" t="n"/>
+      <c r="AJ33" s="641" t="n"/>
+      <c r="AK33" s="643" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL33" s="567" t="n"/>
-      <c r="AM33" s="567" t="n"/>
-      <c r="AN33" s="567" t="n"/>
-      <c r="AO33" s="567" t="n"/>
-      <c r="AP33" s="567" t="n"/>
-      <c r="AQ33" s="567" t="n"/>
-      <c r="AR33" s="567" t="n"/>
-      <c r="AS33" s="567" t="n"/>
-      <c r="AT33" s="567" t="n"/>
-      <c r="AU33" s="567" t="n"/>
-      <c r="AV33" s="567" t="n"/>
-      <c r="AW33" s="567" t="n"/>
-      <c r="AX33" s="567" t="n"/>
-      <c r="AY33" s="567" t="n"/>
-      <c r="AZ33" s="567" t="n"/>
-      <c r="BA33" s="567" t="n"/>
-      <c r="BB33" s="567" t="n"/>
-      <c r="BC33" s="567" t="n"/>
-      <c r="BD33" s="570" t="n"/>
+      <c r="AL33" s="334" t="n"/>
+      <c r="AM33" s="334" t="n"/>
+      <c r="AN33" s="334" t="n"/>
+      <c r="AO33" s="334" t="n"/>
+      <c r="AP33" s="334" t="n"/>
+      <c r="AQ33" s="334" t="n"/>
+      <c r="AR33" s="334" t="n"/>
+      <c r="AS33" s="334" t="n"/>
+      <c r="AT33" s="334" t="n"/>
+      <c r="AU33" s="334" t="n"/>
+      <c r="AV33" s="334" t="n"/>
+      <c r="AW33" s="334" t="n"/>
+      <c r="AX33" s="334" t="n"/>
+      <c r="AY33" s="334" t="n"/>
+      <c r="AZ33" s="334" t="n"/>
+      <c r="BA33" s="334" t="n"/>
+      <c r="BB33" s="334" t="n"/>
+      <c r="BC33" s="334" t="n"/>
+      <c r="BD33" s="335" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="600" t="n"/>
-      <c r="B34" s="567" t="n"/>
-      <c r="C34" s="567" t="n"/>
-      <c r="D34" s="567" t="n"/>
-      <c r="E34" s="567" t="n"/>
-      <c r="F34" s="567" t="n"/>
-      <c r="G34" s="567" t="n"/>
-      <c r="H34" s="567" t="n"/>
-      <c r="I34" s="567" t="n"/>
-      <c r="J34" s="567" t="n"/>
-      <c r="K34" s="567" t="n"/>
-      <c r="L34" s="567" t="n"/>
-      <c r="M34" s="567" t="n"/>
-      <c r="N34" s="567" t="n"/>
-      <c r="O34" s="567" t="n"/>
-      <c r="P34" s="567" t="n"/>
-      <c r="Q34" s="567" t="n"/>
-      <c r="R34" s="568" t="n"/>
-      <c r="S34" s="567" t="n"/>
-      <c r="T34" s="567" t="n"/>
-      <c r="U34" s="567" t="n"/>
-      <c r="V34" s="567" t="n"/>
-      <c r="W34" s="567" t="n"/>
-      <c r="X34" s="567" t="n"/>
-      <c r="Y34" s="567" t="n"/>
-      <c r="Z34" s="567" t="n"/>
-      <c r="AA34" s="567" t="n"/>
-      <c r="AB34" s="567" t="n"/>
-      <c r="AC34" s="567" t="n"/>
-      <c r="AD34" s="567" t="n"/>
-      <c r="AE34" s="567" t="n"/>
-      <c r="AF34" s="567" t="n"/>
-      <c r="AG34" s="567" t="n"/>
-      <c r="AH34" s="567" t="n"/>
-      <c r="AI34" s="567" t="n"/>
-      <c r="AJ34" s="568" t="n"/>
-      <c r="AK34" s="567" t="n"/>
-      <c r="AL34" s="567" t="n"/>
-      <c r="AM34" s="567" t="n"/>
-      <c r="AN34" s="567" t="n"/>
-      <c r="AO34" s="567" t="n"/>
-      <c r="AP34" s="567" t="n"/>
-      <c r="AQ34" s="567" t="n"/>
-      <c r="AR34" s="567" t="n"/>
-      <c r="AS34" s="567" t="n"/>
-      <c r="AT34" s="567" t="n"/>
-      <c r="AU34" s="567" t="n"/>
-      <c r="AV34" s="567" t="n"/>
-      <c r="AW34" s="567" t="n"/>
-      <c r="AX34" s="567" t="n"/>
-      <c r="AY34" s="567" t="n"/>
-      <c r="AZ34" s="567" t="n"/>
-      <c r="BA34" s="567" t="n"/>
-      <c r="BB34" s="567" t="n"/>
-      <c r="BC34" s="567" t="n"/>
-      <c r="BD34" s="570" t="n"/>
+      <c r="A34" s="333" t="n"/>
+      <c r="B34" s="334" t="n"/>
+      <c r="C34" s="334" t="n"/>
+      <c r="D34" s="334" t="n"/>
+      <c r="E34" s="334" t="n"/>
+      <c r="F34" s="334" t="n"/>
+      <c r="G34" s="334" t="n"/>
+      <c r="H34" s="334" t="n"/>
+      <c r="I34" s="334" t="n"/>
+      <c r="J34" s="334" t="n"/>
+      <c r="K34" s="334" t="n"/>
+      <c r="L34" s="334" t="n"/>
+      <c r="M34" s="334" t="n"/>
+      <c r="N34" s="334" t="n"/>
+      <c r="O34" s="334" t="n"/>
+      <c r="P34" s="334" t="n"/>
+      <c r="Q34" s="334" t="n"/>
+      <c r="R34" s="641" t="n"/>
+      <c r="S34" s="334" t="n"/>
+      <c r="T34" s="334" t="n"/>
+      <c r="U34" s="334" t="n"/>
+      <c r="V34" s="334" t="n"/>
+      <c r="W34" s="334" t="n"/>
+      <c r="X34" s="334" t="n"/>
+      <c r="Y34" s="334" t="n"/>
+      <c r="Z34" s="334" t="n"/>
+      <c r="AA34" s="334" t="n"/>
+      <c r="AB34" s="334" t="n"/>
+      <c r="AC34" s="334" t="n"/>
+      <c r="AD34" s="334" t="n"/>
+      <c r="AE34" s="334" t="n"/>
+      <c r="AF34" s="334" t="n"/>
+      <c r="AG34" s="334" t="n"/>
+      <c r="AH34" s="334" t="n"/>
+      <c r="AI34" s="334" t="n"/>
+      <c r="AJ34" s="641" t="n"/>
+      <c r="AK34" s="334" t="n"/>
+      <c r="AL34" s="334" t="n"/>
+      <c r="AM34" s="334" t="n"/>
+      <c r="AN34" s="334" t="n"/>
+      <c r="AO34" s="334" t="n"/>
+      <c r="AP34" s="334" t="n"/>
+      <c r="AQ34" s="334" t="n"/>
+      <c r="AR34" s="334" t="n"/>
+      <c r="AS34" s="334" t="n"/>
+      <c r="AT34" s="334" t="n"/>
+      <c r="AU34" s="334" t="n"/>
+      <c r="AV34" s="334" t="n"/>
+      <c r="AW34" s="334" t="n"/>
+      <c r="AX34" s="334" t="n"/>
+      <c r="AY34" s="334" t="n"/>
+      <c r="AZ34" s="334" t="n"/>
+      <c r="BA34" s="334" t="n"/>
+      <c r="BB34" s="334" t="n"/>
+      <c r="BC34" s="334" t="n"/>
+      <c r="BD34" s="335" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="601" t="n"/>
-      <c r="B35" s="573" t="n"/>
-      <c r="C35" s="573" t="n"/>
-      <c r="D35" s="573" t="n"/>
-      <c r="E35" s="573" t="n"/>
-      <c r="F35" s="573" t="n"/>
-      <c r="G35" s="573" t="n"/>
-      <c r="H35" s="573" t="n"/>
-      <c r="I35" s="573" t="n"/>
-      <c r="J35" s="573" t="n"/>
-      <c r="K35" s="573" t="n"/>
-      <c r="L35" s="573" t="n"/>
-      <c r="M35" s="573" t="n"/>
-      <c r="N35" s="573" t="n"/>
-      <c r="O35" s="573" t="n"/>
-      <c r="P35" s="573" t="n"/>
-      <c r="Q35" s="573" t="n"/>
-      <c r="R35" s="574" t="n"/>
-      <c r="S35" s="573" t="n"/>
-      <c r="T35" s="573" t="n"/>
-      <c r="U35" s="573" t="n"/>
-      <c r="V35" s="573" t="n"/>
-      <c r="W35" s="573" t="n"/>
-      <c r="X35" s="573" t="n"/>
-      <c r="Y35" s="573" t="n"/>
-      <c r="Z35" s="573" t="n"/>
-      <c r="AA35" s="573" t="n"/>
-      <c r="AB35" s="573" t="n"/>
-      <c r="AC35" s="573" t="n"/>
-      <c r="AD35" s="573" t="n"/>
-      <c r="AE35" s="573" t="n"/>
-      <c r="AF35" s="573" t="n"/>
-      <c r="AG35" s="573" t="n"/>
-      <c r="AH35" s="573" t="n"/>
-      <c r="AI35" s="573" t="n"/>
-      <c r="AJ35" s="574" t="n"/>
-      <c r="AK35" s="573" t="n"/>
-      <c r="AL35" s="573" t="n"/>
-      <c r="AM35" s="573" t="n"/>
-      <c r="AN35" s="573" t="n"/>
-      <c r="AO35" s="573" t="n"/>
-      <c r="AP35" s="573" t="n"/>
-      <c r="AQ35" s="573" t="n"/>
-      <c r="AR35" s="573" t="n"/>
-      <c r="AS35" s="573" t="n"/>
-      <c r="AT35" s="573" t="n"/>
-      <c r="AU35" s="573" t="n"/>
-      <c r="AV35" s="573" t="n"/>
-      <c r="AW35" s="573" t="n"/>
-      <c r="AX35" s="573" t="n"/>
-      <c r="AY35" s="573" t="n"/>
-      <c r="AZ35" s="573" t="n"/>
-      <c r="BA35" s="573" t="n"/>
-      <c r="BB35" s="573" t="n"/>
-      <c r="BC35" s="573" t="n"/>
-      <c r="BD35" s="576" t="n"/>
+      <c r="A35" s="644" t="n"/>
+      <c r="B35" s="328" t="n"/>
+      <c r="C35" s="328" t="n"/>
+      <c r="D35" s="328" t="n"/>
+      <c r="E35" s="328" t="n"/>
+      <c r="F35" s="328" t="n"/>
+      <c r="G35" s="328" t="n"/>
+      <c r="H35" s="328" t="n"/>
+      <c r="I35" s="328" t="n"/>
+      <c r="J35" s="328" t="n"/>
+      <c r="K35" s="328" t="n"/>
+      <c r="L35" s="328" t="n"/>
+      <c r="M35" s="328" t="n"/>
+      <c r="N35" s="328" t="n"/>
+      <c r="O35" s="328" t="n"/>
+      <c r="P35" s="328" t="n"/>
+      <c r="Q35" s="328" t="n"/>
+      <c r="R35" s="329" t="n"/>
+      <c r="S35" s="328" t="n"/>
+      <c r="T35" s="328" t="n"/>
+      <c r="U35" s="328" t="n"/>
+      <c r="V35" s="328" t="n"/>
+      <c r="W35" s="328" t="n"/>
+      <c r="X35" s="328" t="n"/>
+      <c r="Y35" s="328" t="n"/>
+      <c r="Z35" s="328" t="n"/>
+      <c r="AA35" s="328" t="n"/>
+      <c r="AB35" s="328" t="n"/>
+      <c r="AC35" s="328" t="n"/>
+      <c r="AD35" s="328" t="n"/>
+      <c r="AE35" s="328" t="n"/>
+      <c r="AF35" s="328" t="n"/>
+      <c r="AG35" s="328" t="n"/>
+      <c r="AH35" s="328" t="n"/>
+      <c r="AI35" s="328" t="n"/>
+      <c r="AJ35" s="329" t="n"/>
+      <c r="AK35" s="328" t="n"/>
+      <c r="AL35" s="328" t="n"/>
+      <c r="AM35" s="328" t="n"/>
+      <c r="AN35" s="328" t="n"/>
+      <c r="AO35" s="328" t="n"/>
+      <c r="AP35" s="328" t="n"/>
+      <c r="AQ35" s="328" t="n"/>
+      <c r="AR35" s="328" t="n"/>
+      <c r="AS35" s="328" t="n"/>
+      <c r="AT35" s="328" t="n"/>
+      <c r="AU35" s="328" t="n"/>
+      <c r="AV35" s="328" t="n"/>
+      <c r="AW35" s="328" t="n"/>
+      <c r="AX35" s="328" t="n"/>
+      <c r="AY35" s="328" t="n"/>
+      <c r="AZ35" s="328" t="n"/>
+      <c r="BA35" s="328" t="n"/>
+      <c r="BB35" s="328" t="n"/>
+      <c r="BC35" s="328" t="n"/>
+      <c r="BD35" s="330" t="n"/>
     </row>
     <row r="36" ht="3" customHeight="1">
       <c r="A36" s="592" t="n"/>
@@ -9086,66 +9200,66 @@
       <c r="BD36" s="578" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="602" t="inlineStr">
+      <c r="A37" s="645" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-      <c r="Q37" s="27" t="n"/>
-      <c r="R37" s="27" t="n"/>
-      <c r="S37" s="27" t="n"/>
-      <c r="T37" s="27" t="n"/>
-      <c r="U37" s="27" t="n"/>
-      <c r="V37" s="27" t="n"/>
-      <c r="W37" s="27" t="n"/>
-      <c r="X37" s="27" t="n"/>
-      <c r="Y37" s="27" t="n"/>
-      <c r="Z37" s="27" t="n"/>
-      <c r="AA37" s="27" t="n"/>
-      <c r="AB37" s="27" t="n"/>
-      <c r="AC37" s="27" t="n"/>
-      <c r="AD37" s="27" t="n"/>
-      <c r="AE37" s="27" t="n"/>
-      <c r="AF37" s="27" t="n"/>
-      <c r="AG37" s="27" t="n"/>
-      <c r="AH37" s="27" t="n"/>
-      <c r="AI37" s="27" t="n"/>
-      <c r="AJ37" s="27" t="n"/>
-      <c r="AK37" s="27" t="n"/>
-      <c r="AL37" s="27" t="n"/>
-      <c r="AM37" s="27" t="n"/>
-      <c r="AN37" s="27" t="n"/>
-      <c r="AO37" s="27" t="n"/>
-      <c r="AP37" s="27" t="n"/>
-      <c r="AQ37" s="27" t="n"/>
-      <c r="AR37" s="27" t="n"/>
-      <c r="AS37" s="27" t="n"/>
-      <c r="AT37" s="27" t="n"/>
-      <c r="AU37" s="27" t="n"/>
-      <c r="AV37" s="27" t="n"/>
-      <c r="AW37" s="27" t="n"/>
-      <c r="AX37" s="27" t="n"/>
-      <c r="AY37" s="27" t="n"/>
-      <c r="AZ37" s="27" t="n"/>
-      <c r="BA37" s="27" t="n"/>
-      <c r="BB37" s="27" t="n"/>
-      <c r="BC37" s="27" t="n"/>
-      <c r="BD37" s="28" t="n"/>
+      <c r="B37" s="285" t="n"/>
+      <c r="C37" s="285" t="n"/>
+      <c r="D37" s="285" t="n"/>
+      <c r="E37" s="285" t="n"/>
+      <c r="F37" s="285" t="n"/>
+      <c r="G37" s="285" t="n"/>
+      <c r="H37" s="285" t="n"/>
+      <c r="I37" s="285" t="n"/>
+      <c r="J37" s="285" t="n"/>
+      <c r="K37" s="285" t="n"/>
+      <c r="L37" s="285" t="n"/>
+      <c r="M37" s="285" t="n"/>
+      <c r="N37" s="285" t="n"/>
+      <c r="O37" s="285" t="n"/>
+      <c r="P37" s="285" t="n"/>
+      <c r="Q37" s="285" t="n"/>
+      <c r="R37" s="285" t="n"/>
+      <c r="S37" s="285" t="n"/>
+      <c r="T37" s="285" t="n"/>
+      <c r="U37" s="285" t="n"/>
+      <c r="V37" s="285" t="n"/>
+      <c r="W37" s="285" t="n"/>
+      <c r="X37" s="285" t="n"/>
+      <c r="Y37" s="285" t="n"/>
+      <c r="Z37" s="285" t="n"/>
+      <c r="AA37" s="285" t="n"/>
+      <c r="AB37" s="285" t="n"/>
+      <c r="AC37" s="285" t="n"/>
+      <c r="AD37" s="285" t="n"/>
+      <c r="AE37" s="285" t="n"/>
+      <c r="AF37" s="285" t="n"/>
+      <c r="AG37" s="285" t="n"/>
+      <c r="AH37" s="285" t="n"/>
+      <c r="AI37" s="285" t="n"/>
+      <c r="AJ37" s="285" t="n"/>
+      <c r="AK37" s="285" t="n"/>
+      <c r="AL37" s="285" t="n"/>
+      <c r="AM37" s="285" t="n"/>
+      <c r="AN37" s="285" t="n"/>
+      <c r="AO37" s="285" t="n"/>
+      <c r="AP37" s="285" t="n"/>
+      <c r="AQ37" s="285" t="n"/>
+      <c r="AR37" s="285" t="n"/>
+      <c r="AS37" s="285" t="n"/>
+      <c r="AT37" s="285" t="n"/>
+      <c r="AU37" s="285" t="n"/>
+      <c r="AV37" s="285" t="n"/>
+      <c r="AW37" s="285" t="n"/>
+      <c r="AX37" s="285" t="n"/>
+      <c r="AY37" s="285" t="n"/>
+      <c r="AZ37" s="285" t="n"/>
+      <c r="BA37" s="285" t="n"/>
+      <c r="BB37" s="285" t="n"/>
+      <c r="BC37" s="285" t="n"/>
+      <c r="BD37" s="286" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -9319,7 +9433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9650,7 +9764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10598,7 +10712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11441,7 +11555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -22,10 +22,486 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+  <si>
+    <t>  1. LOT / PLAN / REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>  4. DISPOSITION / RELEASE</t>
+  </si>
+  <si>
+    <t>  5. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>100% Sort Required (YES/NO)</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$19)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ACCEPT</t>
+  </si>
+  <si>
+    <t>ACTION_STATUS</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-001</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-002</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-003</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-004</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-006</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-007</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QMS-020</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>AQL</t>
+  </si>
+  <si>
+    <t>AQL Disposition</t>
+  </si>
+  <si>
+    <t>AQL Inspection Record</t>
+  </si>
+  <si>
+    <t>AQL_DISPOSITION</t>
+  </si>
+  <si>
+    <t>Ac / Re</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>CAL STATUS ISSUE</t>
+  </si>
+  <si>
+    <t>CERT MISMATCH</t>
+  </si>
+  <si>
+    <t>CLEANLINESS RISK</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CLOSEOUT_STATE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>Characteristic Class</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
+  </si>
+  <si>
+    <t>Code Letter</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>Customer / PO Line</t>
+  </si>
+  <si>
+    <t>DAMAGE</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>DOC GAP</t>
+  </si>
+  <si>
+    <t>Defect Class</t>
+  </si>
+  <si>
+    <t>Defect Count</t>
+  </si>
+  <si>
+    <t>Disposition Status</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Epicor transaction + M365 evidence</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>Evidence item 1</t>
+  </si>
+  <si>
+    <t>Evidence item 2</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-621</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>ID / Serial</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INEFFECTIVE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Inspection Level</t>
+  </si>
+  <si>
+    <t>Inspection Record ID</t>
+  </si>
+  <si>
+    <t>Inspector</t>
+  </si>
+  <si>
+    <t>Job / Lot / Serial</t>
+  </si>
+  <si>
+    <t>LATE DELIVERY</t>
+  </si>
+  <si>
+    <t>Link or reference ID</t>
+  </si>
+  <si>
+    <t>Linked NCR Ref</t>
+  </si>
+  <si>
+    <t>Lot Qty</t>
+  </si>
+  <si>
+    <t>Lot Release Decision</t>
+  </si>
+  <si>
+    <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Measured Result / Observation</t>
+  </si>
+  <si>
+    <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT CLOSED</t>
+  </si>
+  <si>
+    <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Observation / Measured Result</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PACKAGING ISSUE</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Authority</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REASON_CODE_LIST</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Reference plan / lot / method / release documents from their owning source.</t>
+  </si>
+  <si>
+    <t>Reference to the correct evidence folder, shared location or dossier package.</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Result Detail</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP SOP-603</t>
+  </si>
+  <si>
+    <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
+  </si>
+  <si>
+    <t>SPEC DEVIATION</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Sample ID / Serial</t>
+  </si>
+  <si>
+    <t>Sample No.</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Switching Status</t>
+  </si>
+  <si>
+    <t>TRACEABILITY BREAK</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
+  </si>
+  <si>
+    <t>Upstream References / Import Guidance</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI WI-603</t>
+  </si>
+  <si>
+    <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="85">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -507,8 +983,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -765,8 +1246,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="369">
+  <borders count="372">
     <border>
       <left/>
       <right/>
@@ -4747,11 +5233,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="646">
+  <cellXfs count="649">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6402,6 +6922,15 @@
     </xf>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9200,66 +9729,66 @@
       <c r="BD36" s="578" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="645" t="inlineStr">
+      <c r="A37" s="646" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="285" t="n"/>
-      <c r="C37" s="285" t="n"/>
-      <c r="D37" s="285" t="n"/>
-      <c r="E37" s="285" t="n"/>
-      <c r="F37" s="285" t="n"/>
-      <c r="G37" s="285" t="n"/>
-      <c r="H37" s="285" t="n"/>
-      <c r="I37" s="285" t="n"/>
-      <c r="J37" s="285" t="n"/>
-      <c r="K37" s="285" t="n"/>
-      <c r="L37" s="285" t="n"/>
-      <c r="M37" s="285" t="n"/>
-      <c r="N37" s="285" t="n"/>
-      <c r="O37" s="285" t="n"/>
-      <c r="P37" s="285" t="n"/>
-      <c r="Q37" s="285" t="n"/>
-      <c r="R37" s="285" t="n"/>
-      <c r="S37" s="285" t="n"/>
-      <c r="T37" s="285" t="n"/>
-      <c r="U37" s="285" t="n"/>
-      <c r="V37" s="285" t="n"/>
-      <c r="W37" s="285" t="n"/>
-      <c r="X37" s="285" t="n"/>
-      <c r="Y37" s="285" t="n"/>
-      <c r="Z37" s="285" t="n"/>
-      <c r="AA37" s="285" t="n"/>
-      <c r="AB37" s="285" t="n"/>
-      <c r="AC37" s="285" t="n"/>
-      <c r="AD37" s="285" t="n"/>
-      <c r="AE37" s="285" t="n"/>
-      <c r="AF37" s="285" t="n"/>
-      <c r="AG37" s="285" t="n"/>
-      <c r="AH37" s="285" t="n"/>
-      <c r="AI37" s="285" t="n"/>
-      <c r="AJ37" s="285" t="n"/>
-      <c r="AK37" s="285" t="n"/>
-      <c r="AL37" s="285" t="n"/>
-      <c r="AM37" s="285" t="n"/>
-      <c r="AN37" s="285" t="n"/>
-      <c r="AO37" s="285" t="n"/>
-      <c r="AP37" s="285" t="n"/>
-      <c r="AQ37" s="285" t="n"/>
-      <c r="AR37" s="285" t="n"/>
-      <c r="AS37" s="285" t="n"/>
-      <c r="AT37" s="285" t="n"/>
-      <c r="AU37" s="285" t="n"/>
-      <c r="AV37" s="285" t="n"/>
-      <c r="AW37" s="285" t="n"/>
-      <c r="AX37" s="285" t="n"/>
-      <c r="AY37" s="285" t="n"/>
-      <c r="AZ37" s="285" t="n"/>
-      <c r="BA37" s="285" t="n"/>
-      <c r="BB37" s="285" t="n"/>
-      <c r="BC37" s="285" t="n"/>
-      <c r="BD37" s="286" t="n"/>
+      <c r="B37" s="647" t="n"/>
+      <c r="C37" s="647" t="n"/>
+      <c r="D37" s="647" t="n"/>
+      <c r="E37" s="647" t="n"/>
+      <c r="F37" s="647" t="n"/>
+      <c r="G37" s="647" t="n"/>
+      <c r="H37" s="647" t="n"/>
+      <c r="I37" s="647" t="n"/>
+      <c r="J37" s="647" t="n"/>
+      <c r="K37" s="647" t="n"/>
+      <c r="L37" s="647" t="n"/>
+      <c r="M37" s="647" t="n"/>
+      <c r="N37" s="647" t="n"/>
+      <c r="O37" s="647" t="n"/>
+      <c r="P37" s="647" t="n"/>
+      <c r="Q37" s="647" t="n"/>
+      <c r="R37" s="647" t="n"/>
+      <c r="S37" s="647" t="n"/>
+      <c r="T37" s="647" t="n"/>
+      <c r="U37" s="647" t="n"/>
+      <c r="V37" s="647" t="n"/>
+      <c r="W37" s="647" t="n"/>
+      <c r="X37" s="647" t="n"/>
+      <c r="Y37" s="647" t="n"/>
+      <c r="Z37" s="647" t="n"/>
+      <c r="AA37" s="647" t="n"/>
+      <c r="AB37" s="647" t="n"/>
+      <c r="AC37" s="647" t="n"/>
+      <c r="AD37" s="647" t="n"/>
+      <c r="AE37" s="647" t="n"/>
+      <c r="AF37" s="647" t="n"/>
+      <c r="AG37" s="647" t="n"/>
+      <c r="AH37" s="647" t="n"/>
+      <c r="AI37" s="647" t="n"/>
+      <c r="AJ37" s="647" t="n"/>
+      <c r="AK37" s="647" t="n"/>
+      <c r="AL37" s="647" t="n"/>
+      <c r="AM37" s="647" t="n"/>
+      <c r="AN37" s="647" t="n"/>
+      <c r="AO37" s="647" t="n"/>
+      <c r="AP37" s="647" t="n"/>
+      <c r="AQ37" s="647" t="n"/>
+      <c r="AR37" s="647" t="n"/>
+      <c r="AS37" s="647" t="n"/>
+      <c r="AT37" s="647" t="n"/>
+      <c r="AU37" s="647" t="n"/>
+      <c r="AV37" s="647" t="n"/>
+      <c r="AW37" s="647" t="n"/>
+      <c r="AX37" s="647" t="n"/>
+      <c r="AY37" s="647" t="n"/>
+      <c r="AZ37" s="647" t="n"/>
+      <c r="BA37" s="647" t="n"/>
+      <c r="BB37" s="647" t="n"/>
+      <c r="BC37" s="647" t="n"/>
+      <c r="BD37" s="648" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -1252,7 +1252,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="372">
+  <borders count="377">
     <border>
       <left/>
       <right/>
@@ -5266,6 +5266,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -22,486 +22,10 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
-  <si>
-    <t>  1. LOT / PLAN / REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
-  </si>
-  <si>
-    <t>  4. DISPOSITION / RELEASE</t>
-  </si>
-  <si>
-    <t>  5. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>100% Sort Required (YES/NO)</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$19)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$5)+1</t>
-  </si>
-  <si>
-    <t>ACCEPT</t>
-  </si>
-  <si>
-    <t>ACTION_STATUS</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-001</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-002</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-003</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-004</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-006</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-007</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QMS-020</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-  </si>
-  <si>
-    <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>AQL</t>
-  </si>
-  <si>
-    <t>AQL Disposition</t>
-  </si>
-  <si>
-    <t>AQL Inspection Record</t>
-  </si>
-  <si>
-    <t>AQL_DISPOSITION</t>
-  </si>
-  <si>
-    <t>Ac / Re</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>CAL STATUS ISSUE</t>
-  </si>
-  <si>
-    <t>CERT MISMATCH</t>
-  </si>
-  <si>
-    <t>CLEANLINESS RISK</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CLOSEOUT_STATE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>Characteristic Class</t>
-  </si>
-  <si>
-    <t>Close When</t>
-  </si>
-  <si>
-    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
-  </si>
-  <si>
-    <t>Code Letter</t>
-  </si>
-  <si>
-    <t>Cross-Reference Boundary</t>
-  </si>
-  <si>
-    <t>Customer / PO Line</t>
-  </si>
-  <si>
-    <t>DAMAGE</t>
-  </si>
-  <si>
-    <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>DOC GAP</t>
-  </si>
-  <si>
-    <t>Defect Class</t>
-  </si>
-  <si>
-    <t>Defect Count</t>
-  </si>
-  <si>
-    <t>Disposition Status</t>
-  </si>
-  <si>
-    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Epicor transaction + M365 evidence</t>
-  </si>
-  <si>
-    <t>Evidence Package Ref</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence Reference / Attachment Guidance</t>
-  </si>
-  <si>
-    <t>Evidence item 1</t>
-  </si>
-  <si>
-    <t>Evidence item 2</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-621</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>ID / Serial</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INEFFECTIVE</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Inspection Level</t>
-  </si>
-  <si>
-    <t>Inspection Record ID</t>
-  </si>
-  <si>
-    <t>Inspector</t>
-  </si>
-  <si>
-    <t>Job / Lot / Serial</t>
-  </si>
-  <si>
-    <t>LATE DELIVERY</t>
-  </si>
-  <si>
-    <t>Link or reference ID</t>
-  </si>
-  <si>
-    <t>Linked NCR Ref</t>
-  </si>
-  <si>
-    <t>Lot Qty</t>
-  </si>
-  <si>
-    <t>Lot Release Decision</t>
-  </si>
-  <si>
-    <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Measured Result / Observation</t>
-  </si>
-  <si>
-    <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOT CLOSED</t>
-  </si>
-  <si>
-    <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>OVERDUE</t>
-  </si>
-  <si>
-    <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Observation / Measured Result</t>
-  </si>
-  <si>
-    <t>Open When</t>
-  </si>
-  <si>
-    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-  </si>
-  <si>
-    <t>Operational trigger</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PACKAGING ISSUE</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Part No. / Revision</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Prepared by / Date-Time</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Quality Authority</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REASON_CODE_LIST</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Reference plan / lot / method / release documents from their owning source.</t>
-  </si>
-  <si>
-    <t>Reference to the correct evidence folder, shared location or dossier package.</t>
-  </si>
-  <si>
-    <t>Release / closure rule</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Result Detail</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SOP SOP-603</t>
-  </si>
-  <si>
-    <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
-  </si>
-  <si>
-    <t>SPEC DEVIATION</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>Sample ID / Serial</t>
-  </si>
-  <si>
-    <t>Sample No.</t>
-  </si>
-  <si>
-    <t>Sample Size</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>Switching Status</t>
-  </si>
-  <si>
-    <t>TRACEABILITY BREAK</t>
-  </si>
-  <si>
-    <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-  </si>
-  <si>
-    <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
-  </si>
-  <si>
-    <t>Upstream References / Import Guidance</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VERIFIED</t>
-  </si>
-  <si>
-    <t>Value / Reference</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>WI WI-603</t>
-  </si>
-  <si>
-    <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -988,6 +512,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="53">
     <fill>
@@ -1252,7 +779,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="377">
+  <borders count="385">
     <border>
       <left/>
       <right/>
@@ -5325,11 +4852,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="649">
+  <cellXfs count="752">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6989,6 +6607,265 @@
     </xf>
     <xf numFmtId="0" fontId="85" fillId="52" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="47" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="47" borderId="269" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="269" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="297" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="341" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="269" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="380" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="381" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="381" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7071,11 +6948,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7089,9 +6966,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7108,7 +6982,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7122,9 +6996,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7141,7 +7012,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7155,9 +7026,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7174,7 +7042,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7188,9 +7056,36 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -7565,7 +7460,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="604" t="inlineStr"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
@@ -7577,7 +7472,7 @@
       <c r="I1" s="268" t="n"/>
       <c r="J1" s="268" t="n"/>
       <c r="K1" s="310" t="n"/>
-      <c r="L1" s="543" t="inlineStr">
+      <c r="L1" s="751" t="inlineStr">
         <is>
           <t>AQL Inspection Record</t>
         </is>
@@ -7611,7 +7506,7 @@
       <c r="AM1" s="268" t="n"/>
       <c r="AN1" s="268" t="n"/>
       <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
+      <c r="AP1" s="310" t="n"/>
       <c r="AQ1" s="605" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7636,279 +7531,392 @@
       <c r="BD1" s="310" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="K2" s="311" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="608" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="682" t="n"/>
+      <c r="C2" s="682" t="n"/>
+      <c r="D2" s="682" t="n"/>
+      <c r="E2" s="682" t="n"/>
+      <c r="F2" s="682" t="n"/>
+      <c r="G2" s="682" t="n"/>
+      <c r="H2" s="682" t="n"/>
+      <c r="I2" s="682" t="n"/>
+      <c r="J2" s="682" t="n"/>
+      <c r="K2" s="683" t="n"/>
+      <c r="L2" s="682" t="n"/>
+      <c r="M2" s="682" t="n"/>
+      <c r="N2" s="682" t="n"/>
+      <c r="O2" s="682" t="n"/>
+      <c r="P2" s="682" t="n"/>
+      <c r="Q2" s="682" t="n"/>
+      <c r="R2" s="682" t="n"/>
+      <c r="S2" s="682" t="n"/>
+      <c r="T2" s="682" t="n"/>
+      <c r="U2" s="682" t="n"/>
+      <c r="V2" s="682" t="n"/>
+      <c r="W2" s="682" t="n"/>
+      <c r="X2" s="682" t="n"/>
+      <c r="Y2" s="682" t="n"/>
+      <c r="Z2" s="682" t="n"/>
+      <c r="AA2" s="682" t="n"/>
+      <c r="AB2" s="682" t="n"/>
+      <c r="AC2" s="682" t="n"/>
+      <c r="AD2" s="682" t="n"/>
+      <c r="AE2" s="682" t="n"/>
+      <c r="AF2" s="682" t="n"/>
+      <c r="AG2" s="682" t="n"/>
+      <c r="AH2" s="682" t="n"/>
+      <c r="AI2" s="682" t="n"/>
+      <c r="AJ2" s="682" t="n"/>
+      <c r="AK2" s="682" t="n"/>
+      <c r="AL2" s="682" t="n"/>
+      <c r="AM2" s="682" t="n"/>
+      <c r="AN2" s="682" t="n"/>
+      <c r="AO2" s="682" t="n"/>
+      <c r="AP2" s="683" t="n"/>
+      <c r="AQ2" s="684" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="609" t="n"/>
-      <c r="AS2" s="609" t="n"/>
-      <c r="AT2" s="609" t="n"/>
-      <c r="AU2" s="609" t="n"/>
-      <c r="AV2" s="610" t="n"/>
-      <c r="AW2" s="611" t="inlineStr">
+      <c r="AR2" s="685" t="n"/>
+      <c r="AS2" s="685" t="n"/>
+      <c r="AT2" s="685" t="n"/>
+      <c r="AU2" s="685" t="n"/>
+      <c r="AV2" s="686" t="n"/>
+      <c r="AW2" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="609" t="n"/>
-      <c r="AY2" s="609" t="n"/>
-      <c r="AZ2" s="609" t="n"/>
-      <c r="BA2" s="609" t="n"/>
-      <c r="BB2" s="609" t="n"/>
-      <c r="BC2" s="609" t="n"/>
-      <c r="BD2" s="612" t="n"/>
+      <c r="AX2" s="687" t="n"/>
+      <c r="AY2" s="687" t="n"/>
+      <c r="AZ2" s="687" t="n"/>
+      <c r="BA2" s="687" t="n"/>
+      <c r="BB2" s="687" t="n"/>
+      <c r="BC2" s="687" t="n"/>
+      <c r="BD2" s="688" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="K3" s="311" t="n"/>
-      <c r="L3" s="275" t="n"/>
-      <c r="AQ3" s="608" t="inlineStr">
+      <c r="A3" s="689" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="690" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="690" t="n"/>
+      <c r="AQ3" s="691" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="609" t="n"/>
-      <c r="AS3" s="609" t="n"/>
-      <c r="AT3" s="609" t="n"/>
-      <c r="AU3" s="609" t="n"/>
-      <c r="AV3" s="610" t="n"/>
-      <c r="AW3" s="611" t="inlineStr">
+      <c r="AR3" s="692" t="n"/>
+      <c r="AS3" s="692" t="n"/>
+      <c r="AT3" s="692" t="n"/>
+      <c r="AU3" s="692" t="n"/>
+      <c r="AV3" s="693" t="n"/>
+      <c r="AW3" s="14" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="609" t="n"/>
-      <c r="AY3" s="609" t="n"/>
-      <c r="AZ3" s="609" t="n"/>
-      <c r="BA3" s="609" t="n"/>
-      <c r="BB3" s="609" t="n"/>
-      <c r="BC3" s="609" t="n"/>
-      <c r="BD3" s="612" t="n"/>
+      <c r="AX3" s="694" t="n"/>
+      <c r="AY3" s="694" t="n"/>
+      <c r="AZ3" s="694" t="n"/>
+      <c r="BA3" s="694" t="n"/>
+      <c r="BB3" s="694" t="n"/>
+      <c r="BC3" s="694" t="n"/>
+      <c r="BD3" s="695" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="K4" s="311" t="n"/>
-      <c r="L4" s="552" t="inlineStr">
+      <c r="A4" s="689" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="690" t="n"/>
+      <c r="L4" s="696" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="608" t="inlineStr">
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="690" t="n"/>
+      <c r="AQ4" s="691" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="609" t="n"/>
-      <c r="AS4" s="609" t="n"/>
-      <c r="AT4" s="609" t="n"/>
-      <c r="AU4" s="609" t="n"/>
-      <c r="AV4" s="610" t="n"/>
-      <c r="AW4" s="611" t="inlineStr">
+      <c r="AR4" s="692" t="n"/>
+      <c r="AS4" s="692" t="n"/>
+      <c r="AT4" s="692" t="n"/>
+      <c r="AU4" s="692" t="n"/>
+      <c r="AV4" s="693" t="n"/>
+      <c r="AW4" s="14" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="609" t="n"/>
-      <c r="AY4" s="609" t="n"/>
-      <c r="AZ4" s="609" t="n"/>
-      <c r="BA4" s="609" t="n"/>
-      <c r="BB4" s="609" t="n"/>
-      <c r="BC4" s="609" t="n"/>
-      <c r="BD4" s="612" t="n"/>
+      <c r="AX4" s="694" t="n"/>
+      <c r="AY4" s="694" t="n"/>
+      <c r="AZ4" s="694" t="n"/>
+      <c r="BA4" s="694" t="n"/>
+      <c r="BB4" s="694" t="n"/>
+      <c r="BC4" s="694" t="n"/>
+      <c r="BD4" s="695" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="689" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="690" t="n"/>
+      <c r="L5" s="697" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="613" t="inlineStr">
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="690" t="n"/>
+      <c r="AQ5" s="691" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="614" t="n"/>
-      <c r="AS5" s="614" t="n"/>
-      <c r="AT5" s="614" t="n"/>
-      <c r="AU5" s="614" t="n"/>
-      <c r="AV5" s="615" t="n"/>
-      <c r="AW5" s="616" t="inlineStr">
+      <c r="AR5" s="692" t="n"/>
+      <c r="AS5" s="692" t="n"/>
+      <c r="AT5" s="692" t="n"/>
+      <c r="AU5" s="692" t="n"/>
+      <c r="AV5" s="693" t="n"/>
+      <c r="AW5" s="14" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="614" t="n"/>
-      <c r="AY5" s="614" t="n"/>
-      <c r="AZ5" s="614" t="n"/>
-      <c r="BA5" s="614" t="n"/>
-      <c r="BB5" s="614" t="n"/>
-      <c r="BC5" s="614" t="n"/>
-      <c r="BD5" s="617" t="n"/>
+      <c r="AX5" s="694" t="n"/>
+      <c r="AY5" s="694" t="n"/>
+      <c r="AZ5" s="694" t="n"/>
+      <c r="BA5" s="694" t="n"/>
+      <c r="BB5" s="694" t="n"/>
+      <c r="BC5" s="694" t="n"/>
+      <c r="BD5" s="695" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="517" t="n"/>
-      <c r="B6" s="517" t="n"/>
-      <c r="C6" s="517" t="n"/>
-      <c r="D6" s="517" t="n"/>
-      <c r="E6" s="517" t="n"/>
-      <c r="F6" s="517" t="n"/>
-      <c r="G6" s="517" t="n"/>
-      <c r="H6" s="517" t="n"/>
-      <c r="I6" s="517" t="n"/>
-      <c r="J6" s="517" t="n"/>
-      <c r="K6" s="517" t="n"/>
-      <c r="L6" s="517" t="n"/>
-      <c r="M6" s="517" t="n"/>
-      <c r="N6" s="517" t="n"/>
-      <c r="O6" s="517" t="n"/>
-      <c r="P6" s="517" t="n"/>
-      <c r="Q6" s="517" t="n"/>
-      <c r="R6" s="517" t="n"/>
-      <c r="S6" s="517" t="n"/>
-      <c r="T6" s="517" t="n"/>
-      <c r="U6" s="517" t="n"/>
-      <c r="V6" s="517" t="n"/>
-      <c r="W6" s="517" t="n"/>
-      <c r="X6" s="517" t="n"/>
-      <c r="Y6" s="517" t="n"/>
-      <c r="Z6" s="517" t="n"/>
-      <c r="AA6" s="517" t="n"/>
-      <c r="AB6" s="517" t="n"/>
-      <c r="AC6" s="517" t="n"/>
-      <c r="AD6" s="517" t="n"/>
-      <c r="AE6" s="517" t="n"/>
-      <c r="AF6" s="517" t="n"/>
-      <c r="AG6" s="517" t="n"/>
-      <c r="AH6" s="517" t="n"/>
-      <c r="AI6" s="517" t="n"/>
-      <c r="AJ6" s="517" t="n"/>
-      <c r="AK6" s="517" t="n"/>
-      <c r="AL6" s="517" t="n"/>
-      <c r="AM6" s="517" t="n"/>
-      <c r="AN6" s="517" t="n"/>
-      <c r="AO6" s="517" t="n"/>
-      <c r="AP6" s="517" t="n"/>
-      <c r="AQ6" s="517" t="n"/>
-      <c r="AR6" s="517" t="n"/>
-      <c r="AS6" s="517" t="n"/>
-      <c r="AT6" s="517" t="n"/>
-      <c r="AU6" s="517" t="n"/>
-      <c r="AV6" s="517" t="n"/>
-      <c r="AW6" s="517" t="n"/>
-      <c r="AX6" s="517" t="n"/>
-      <c r="AY6" s="517" t="n"/>
-      <c r="AZ6" s="517" t="n"/>
-      <c r="BA6" s="517" t="n"/>
-      <c r="BB6" s="517" t="n"/>
-      <c r="BC6" s="517" t="n"/>
-      <c r="BD6" s="517" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="698" t="n"/>
+      <c r="B6" s="699" t="n"/>
+      <c r="C6" s="699" t="n"/>
+      <c r="D6" s="699" t="n"/>
+      <c r="E6" s="699" t="n"/>
+      <c r="F6" s="699" t="n"/>
+      <c r="G6" s="699" t="n"/>
+      <c r="H6" s="699" t="n"/>
+      <c r="I6" s="699" t="n"/>
+      <c r="J6" s="699" t="n"/>
+      <c r="K6" s="700" t="n"/>
+      <c r="L6" s="699" t="n"/>
+      <c r="M6" s="699" t="n"/>
+      <c r="N6" s="699" t="n"/>
+      <c r="O6" s="699" t="n"/>
+      <c r="P6" s="699" t="n"/>
+      <c r="Q6" s="699" t="n"/>
+      <c r="R6" s="699" t="n"/>
+      <c r="S6" s="699" t="n"/>
+      <c r="T6" s="699" t="n"/>
+      <c r="U6" s="699" t="n"/>
+      <c r="V6" s="699" t="n"/>
+      <c r="W6" s="699" t="n"/>
+      <c r="X6" s="699" t="n"/>
+      <c r="Y6" s="699" t="n"/>
+      <c r="Z6" s="699" t="n"/>
+      <c r="AA6" s="699" t="n"/>
+      <c r="AB6" s="699" t="n"/>
+      <c r="AC6" s="699" t="n"/>
+      <c r="AD6" s="699" t="n"/>
+      <c r="AE6" s="699" t="n"/>
+      <c r="AF6" s="699" t="n"/>
+      <c r="AG6" s="699" t="n"/>
+      <c r="AH6" s="699" t="n"/>
+      <c r="AI6" s="699" t="n"/>
+      <c r="AJ6" s="699" t="n"/>
+      <c r="AK6" s="699" t="n"/>
+      <c r="AL6" s="699" t="n"/>
+      <c r="AM6" s="699" t="n"/>
+      <c r="AN6" s="699" t="n"/>
+      <c r="AO6" s="699" t="n"/>
+      <c r="AP6" s="700" t="n"/>
+      <c r="AQ6" s="701" t="n"/>
+      <c r="AR6" s="701" t="n"/>
+      <c r="AS6" s="701" t="n"/>
+      <c r="AT6" s="701" t="n"/>
+      <c r="AU6" s="701" t="n"/>
+      <c r="AV6" s="702" t="n"/>
+      <c r="AW6" s="703" t="n"/>
+      <c r="AX6" s="703" t="n"/>
+      <c r="AY6" s="703" t="n"/>
+      <c r="AZ6" s="703" t="n"/>
+      <c r="BA6" s="703" t="n"/>
+      <c r="BB6" s="703" t="n"/>
+      <c r="BC6" s="703" t="n"/>
+      <c r="BD6" s="704" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="618" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="705" t="n"/>
+      <c r="B7" s="706" t="n"/>
+      <c r="C7" s="706" t="n"/>
+      <c r="D7" s="706" t="n"/>
+      <c r="E7" s="706" t="n"/>
+      <c r="F7" s="706" t="n"/>
+      <c r="G7" s="706" t="n"/>
+      <c r="H7" s="706" t="n"/>
+      <c r="I7" s="706" t="n"/>
+      <c r="J7" s="706" t="n"/>
+      <c r="K7" s="706" t="n"/>
+      <c r="L7" s="706" t="n"/>
+      <c r="M7" s="706" t="n"/>
+      <c r="N7" s="706" t="n"/>
+      <c r="O7" s="706" t="n"/>
+      <c r="P7" s="706" t="n"/>
+      <c r="Q7" s="706" t="n"/>
+      <c r="R7" s="706" t="n"/>
+      <c r="S7" s="706" t="n"/>
+      <c r="T7" s="706" t="n"/>
+      <c r="U7" s="706" t="n"/>
+      <c r="V7" s="706" t="n"/>
+      <c r="W7" s="706" t="n"/>
+      <c r="X7" s="706" t="n"/>
+      <c r="Y7" s="706" t="n"/>
+      <c r="Z7" s="706" t="n"/>
+      <c r="AA7" s="706" t="n"/>
+      <c r="AB7" s="706" t="n"/>
+      <c r="AC7" s="706" t="n"/>
+      <c r="AD7" s="706" t="n"/>
+      <c r="AE7" s="706" t="n"/>
+      <c r="AF7" s="706" t="n"/>
+      <c r="AG7" s="706" t="n"/>
+      <c r="AH7" s="706" t="n"/>
+      <c r="AI7" s="706" t="n"/>
+      <c r="AJ7" s="706" t="n"/>
+      <c r="AK7" s="706" t="n"/>
+      <c r="AL7" s="706" t="n"/>
+      <c r="AM7" s="706" t="n"/>
+      <c r="AN7" s="706" t="n"/>
+      <c r="AO7" s="706" t="n"/>
+      <c r="AP7" s="706" t="n"/>
+      <c r="AQ7" s="706" t="n"/>
+      <c r="AR7" s="706" t="n"/>
+      <c r="AS7" s="706" t="n"/>
+      <c r="AT7" s="706" t="n"/>
+      <c r="AU7" s="706" t="n"/>
+      <c r="AV7" s="706" t="n"/>
+      <c r="AW7" s="706" t="n"/>
+      <c r="AX7" s="706" t="n"/>
+      <c r="AY7" s="706" t="n"/>
+      <c r="AZ7" s="706" t="n"/>
+      <c r="BA7" s="706" t="n"/>
+      <c r="BB7" s="706" t="n"/>
+      <c r="BC7" s="706" t="n"/>
+      <c r="BD7" s="706" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="619" t="inlineStr">
@@ -9786,67 +9794,67 @@
       <c r="BC36" s="578" t="n"/>
       <c r="BD36" s="578" t="n"/>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="646" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B37" s="647" t="n"/>
-      <c r="C37" s="647" t="n"/>
-      <c r="D37" s="647" t="n"/>
-      <c r="E37" s="647" t="n"/>
-      <c r="F37" s="647" t="n"/>
-      <c r="G37" s="647" t="n"/>
-      <c r="H37" s="647" t="n"/>
-      <c r="I37" s="647" t="n"/>
-      <c r="J37" s="647" t="n"/>
-      <c r="K37" s="647" t="n"/>
-      <c r="L37" s="647" t="n"/>
-      <c r="M37" s="647" t="n"/>
-      <c r="N37" s="647" t="n"/>
-      <c r="O37" s="647" t="n"/>
-      <c r="P37" s="647" t="n"/>
-      <c r="Q37" s="647" t="n"/>
-      <c r="R37" s="647" t="n"/>
-      <c r="S37" s="647" t="n"/>
-      <c r="T37" s="647" t="n"/>
-      <c r="U37" s="647" t="n"/>
-      <c r="V37" s="647" t="n"/>
-      <c r="W37" s="647" t="n"/>
-      <c r="X37" s="647" t="n"/>
-      <c r="Y37" s="647" t="n"/>
-      <c r="Z37" s="647" t="n"/>
-      <c r="AA37" s="647" t="n"/>
-      <c r="AB37" s="647" t="n"/>
-      <c r="AC37" s="647" t="n"/>
-      <c r="AD37" s="647" t="n"/>
-      <c r="AE37" s="647" t="n"/>
-      <c r="AF37" s="647" t="n"/>
-      <c r="AG37" s="647" t="n"/>
-      <c r="AH37" s="647" t="n"/>
-      <c r="AI37" s="647" t="n"/>
-      <c r="AJ37" s="647" t="n"/>
-      <c r="AK37" s="647" t="n"/>
-      <c r="AL37" s="647" t="n"/>
-      <c r="AM37" s="647" t="n"/>
-      <c r="AN37" s="647" t="n"/>
-      <c r="AO37" s="647" t="n"/>
-      <c r="AP37" s="647" t="n"/>
-      <c r="AQ37" s="647" t="n"/>
-      <c r="AR37" s="647" t="n"/>
-      <c r="AS37" s="647" t="n"/>
-      <c r="AT37" s="647" t="n"/>
-      <c r="AU37" s="647" t="n"/>
-      <c r="AV37" s="647" t="n"/>
-      <c r="AW37" s="647" t="n"/>
-      <c r="AX37" s="647" t="n"/>
-      <c r="AY37" s="647" t="n"/>
-      <c r="AZ37" s="647" t="n"/>
-      <c r="BA37" s="647" t="n"/>
-      <c r="BB37" s="647" t="n"/>
-      <c r="BC37" s="647" t="n"/>
-      <c r="BD37" s="648" t="n"/>
+      <c r="B37" s="707" t="n"/>
+      <c r="C37" s="707" t="n"/>
+      <c r="D37" s="707" t="n"/>
+      <c r="E37" s="707" t="n"/>
+      <c r="F37" s="707" t="n"/>
+      <c r="G37" s="707" t="n"/>
+      <c r="H37" s="707" t="n"/>
+      <c r="I37" s="707" t="n"/>
+      <c r="J37" s="707" t="n"/>
+      <c r="K37" s="707" t="n"/>
+      <c r="L37" s="707" t="n"/>
+      <c r="M37" s="707" t="n"/>
+      <c r="N37" s="707" t="n"/>
+      <c r="O37" s="707" t="n"/>
+      <c r="P37" s="707" t="n"/>
+      <c r="Q37" s="707" t="n"/>
+      <c r="R37" s="707" t="n"/>
+      <c r="S37" s="707" t="n"/>
+      <c r="T37" s="707" t="n"/>
+      <c r="U37" s="707" t="n"/>
+      <c r="V37" s="707" t="n"/>
+      <c r="W37" s="707" t="n"/>
+      <c r="X37" s="707" t="n"/>
+      <c r="Y37" s="707" t="n"/>
+      <c r="Z37" s="707" t="n"/>
+      <c r="AA37" s="707" t="n"/>
+      <c r="AB37" s="707" t="n"/>
+      <c r="AC37" s="707" t="n"/>
+      <c r="AD37" s="707" t="n"/>
+      <c r="AE37" s="707" t="n"/>
+      <c r="AF37" s="707" t="n"/>
+      <c r="AG37" s="707" t="n"/>
+      <c r="AH37" s="707" t="n"/>
+      <c r="AI37" s="707" t="n"/>
+      <c r="AJ37" s="707" t="n"/>
+      <c r="AK37" s="707" t="n"/>
+      <c r="AL37" s="707" t="n"/>
+      <c r="AM37" s="707" t="n"/>
+      <c r="AN37" s="707" t="n"/>
+      <c r="AO37" s="707" t="n"/>
+      <c r="AP37" s="707" t="n"/>
+      <c r="AQ37" s="707" t="n"/>
+      <c r="AR37" s="707" t="n"/>
+      <c r="AS37" s="707" t="n"/>
+      <c r="AT37" s="707" t="n"/>
+      <c r="AU37" s="707" t="n"/>
+      <c r="AV37" s="707" t="n"/>
+      <c r="AW37" s="707" t="n"/>
+      <c r="AX37" s="707" t="n"/>
+      <c r="AY37" s="707" t="n"/>
+      <c r="AZ37" s="707" t="n"/>
+      <c r="BA37" s="707" t="n"/>
+      <c r="BB37" s="707" t="n"/>
+      <c r="BC37" s="707" t="n"/>
+      <c r="BD37" s="708" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -10020,338 +10028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="265" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-      <c r="B1" s="265" t="inlineStr">
-        <is>
-          <t>AQL_DISPOSITION</t>
-        </is>
-      </c>
-      <c r="C1" s="265" t="inlineStr">
-        <is>
-          <t>OWNER_DEPT</t>
-        </is>
-      </c>
-      <c r="D1" s="265" t="inlineStr">
-        <is>
-          <t>DISPOSITION_GATE</t>
-        </is>
-      </c>
-      <c r="E1" s="265" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="F1" s="265" t="inlineStr">
-        <is>
-          <t>YES_NO</t>
-        </is>
-      </c>
-      <c r="G1" s="265" t="inlineStr">
-        <is>
-          <t>CLOSEOUT_STATE</t>
-        </is>
-      </c>
-      <c r="H1" s="348" t="inlineStr">
-        <is>
-          <t>ACTION_STATUS</t>
-        </is>
-      </c>
-      <c r="I1" s="348" t="inlineStr">
-        <is>
-          <t>REASON_CODE_LIST</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="266" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="266" t="inlineStr">
-        <is>
-          <t>ACCEPT</t>
-        </is>
-      </c>
-      <c r="C2" s="266" t="inlineStr">
-        <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="D2" s="266" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="E2" s="266" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F2" s="266" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G2" s="266" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H2" s="348" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="I2" s="348" t="inlineStr">
-        <is>
-          <t>CERT MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B3" s="266" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="C3" s="266" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="D3" s="266" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="E3" s="266" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="F3" s="266" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G3" s="266" t="inlineStr">
-        <is>
-          <t>NOT CLOSED</t>
-        </is>
-      </c>
-      <c r="H3" s="348" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="I3" s="348" t="inlineStr">
-        <is>
-          <t>TRACEABILITY BREAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="266" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B4" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C4" s="266" t="inlineStr">
-        <is>
-          <t>PLANNING</t>
-        </is>
-      </c>
-      <c r="D4" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="E4" s="266" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="F4" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G4" s="266" t="n"/>
-      <c r="H4" s="348" t="inlineStr">
-        <is>
-          <t>OVERDUE</t>
-        </is>
-      </c>
-      <c r="I4" s="348" t="inlineStr">
-        <is>
-          <t>DAMAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" s="266" t="n"/>
-      <c r="C5" s="266" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
-      </c>
-      <c r="D5" s="266" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="E5" s="348" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="F5" s="266" t="n"/>
-      <c r="G5" s="266" t="n"/>
-      <c r="H5" s="348" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="I5" s="348" t="inlineStr">
-        <is>
-          <t>LATE DELIVERY</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="348" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F6" s="266" t="n"/>
-      <c r="G6" s="266" t="n"/>
-      <c r="H6" s="348" t="inlineStr">
-        <is>
-          <t>INEFFECTIVE</t>
-        </is>
-      </c>
-      <c r="I6" s="348" t="inlineStr">
-        <is>
-          <t>SPEC DEVIATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="348" t="inlineStr">
-        <is>
-          <t>PUR</t>
-        </is>
-      </c>
-      <c r="F7" s="266" t="n"/>
-      <c r="H7" s="348" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="I7" s="348" t="inlineStr">
-        <is>
-          <t>PACKAGING ISSUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="348" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="F8" s="266" t="n"/>
-      <c r="I8" s="348" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9" s="348" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F9" s="266" t="n"/>
-      <c r="I9" s="348" t="inlineStr">
-        <is>
-          <t>CAL STATUS ISSUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="348" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F10" s="266" t="n"/>
-      <c r="I10" s="348" t="inlineStr">
-        <is>
-          <t>CLEANLINESS RISK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" s="348" t="inlineStr">
-        <is>
-          <t>MGT</t>
-        </is>
-      </c>
-      <c r="F11" s="266" t="n"/>
-      <c r="I11" s="348" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10396,910 +10073,1112 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="512" t="inlineStr">
-        <is>
-          <t>Result Detail</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="709" t="n"/>
       <c r="B1" s="603" t="n"/>
       <c r="C1" s="603" t="n"/>
       <c r="D1" s="603" t="n"/>
       <c r="E1" s="603" t="n"/>
       <c r="F1" s="603" t="n"/>
       <c r="G1" s="603" t="n"/>
-      <c r="H1" s="513" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="431" t="n"/>
-      <c r="K1" s="431" t="n"/>
-      <c r="L1" s="431" t="n"/>
-      <c r="M1" s="431" t="n"/>
-      <c r="N1" s="431" t="n"/>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="431" t="n"/>
-      <c r="Q1" s="431" t="n"/>
-      <c r="R1" s="431" t="n"/>
-      <c r="S1" s="431" t="n"/>
-      <c r="T1" s="431" t="n"/>
-      <c r="U1" s="431" t="n"/>
-      <c r="V1" s="431" t="n"/>
-      <c r="W1" s="431" t="n"/>
-      <c r="X1" s="431" t="n"/>
-      <c r="Y1" s="431" t="n"/>
-      <c r="Z1" s="431" t="n"/>
-      <c r="AA1" s="431" t="n"/>
-      <c r="AB1" s="431" t="n"/>
-      <c r="AC1" s="431" t="n"/>
-      <c r="AD1" s="432" t="n"/>
-      <c r="AE1" s="433" t="n"/>
-      <c r="AF1" s="434" t="n"/>
-      <c r="AG1" s="434" t="n"/>
-      <c r="AH1" s="435" t="n"/>
-      <c r="AI1" s="436" t="n"/>
-      <c r="AJ1" s="437" t="n"/>
-      <c r="AK1" s="437" t="n"/>
-      <c r="AL1" s="437" t="n"/>
-      <c r="AM1" s="437" t="n"/>
-      <c r="AN1" s="438" t="n"/>
+      <c r="H1" s="710" t="n"/>
+      <c r="I1" s="711" t="inlineStr">
+        <is>
+          <t>AQL Inspection Record</t>
+        </is>
+      </c>
+      <c r="J1" s="603" t="n"/>
+      <c r="K1" s="603" t="n"/>
+      <c r="L1" s="603" t="n"/>
+      <c r="M1" s="603" t="n"/>
+      <c r="N1" s="603" t="n"/>
+      <c r="O1" s="603" t="n"/>
+      <c r="P1" s="603" t="n"/>
+      <c r="Q1" s="603" t="n"/>
+      <c r="R1" s="603" t="n"/>
+      <c r="S1" s="603" t="n"/>
+      <c r="T1" s="603" t="n"/>
+      <c r="U1" s="603" t="n"/>
+      <c r="V1" s="603" t="n"/>
+      <c r="W1" s="603" t="n"/>
+      <c r="X1" s="603" t="n"/>
+      <c r="Y1" s="603" t="n"/>
+      <c r="Z1" s="603" t="n"/>
+      <c r="AA1" s="603" t="n"/>
+      <c r="AB1" s="603" t="n"/>
+      <c r="AC1" s="603" t="n"/>
+      <c r="AD1" s="710" t="n"/>
+      <c r="AE1" s="435" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="603" t="n"/>
+      <c r="AG1" s="603" t="n"/>
+      <c r="AH1" s="712" t="n"/>
+      <c r="AI1" s="438" t="inlineStr">
+        <is>
+          <t>FRM-621</t>
+        </is>
+      </c>
+      <c r="AJ1" s="603" t="n"/>
+      <c r="AK1" s="603" t="n"/>
+      <c r="AL1" s="603" t="n"/>
+      <c r="AM1" s="603" t="n"/>
+      <c r="AN1" s="710" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="514" t="inlineStr">
-        <is>
-          <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
-        </is>
-      </c>
-      <c r="H2" s="515" t="n"/>
-      <c r="I2" s="441" t="n"/>
-      <c r="J2" s="442" t="n"/>
-      <c r="K2" s="442" t="n"/>
-      <c r="L2" s="442" t="n"/>
-      <c r="M2" s="442" t="n"/>
-      <c r="N2" s="442" t="n"/>
-      <c r="O2" s="442" t="n"/>
-      <c r="P2" s="442" t="n"/>
-      <c r="Q2" s="442" t="n"/>
-      <c r="R2" s="442" t="n"/>
-      <c r="S2" s="442" t="n"/>
-      <c r="T2" s="442" t="n"/>
-      <c r="U2" s="442" t="n"/>
-      <c r="V2" s="442" t="n"/>
-      <c r="W2" s="442" t="n"/>
-      <c r="X2" s="442" t="n"/>
-      <c r="Y2" s="442" t="n"/>
-      <c r="Z2" s="442" t="n"/>
-      <c r="AA2" s="442" t="n"/>
-      <c r="AB2" s="442" t="n"/>
-      <c r="AC2" s="442" t="n"/>
-      <c r="AD2" s="443" t="n"/>
-      <c r="AE2" s="444" t="n"/>
-      <c r="AF2" s="445" t="n"/>
-      <c r="AG2" s="445" t="n"/>
-      <c r="AH2" s="446" t="n"/>
-      <c r="AI2" s="447" t="n"/>
-      <c r="AJ2" s="448" t="n"/>
-      <c r="AK2" s="448" t="n"/>
-      <c r="AL2" s="448" t="n"/>
-      <c r="AM2" s="448" t="n"/>
-      <c r="AN2" s="449" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="682" t="n"/>
+      <c r="C2" s="682" t="n"/>
+      <c r="D2" s="682" t="n"/>
+      <c r="E2" s="682" t="n"/>
+      <c r="F2" s="682" t="n"/>
+      <c r="G2" s="682" t="n"/>
+      <c r="H2" s="683" t="n"/>
+      <c r="I2" s="682" t="n"/>
+      <c r="J2" s="682" t="n"/>
+      <c r="K2" s="682" t="n"/>
+      <c r="L2" s="682" t="n"/>
+      <c r="M2" s="682" t="n"/>
+      <c r="N2" s="682" t="n"/>
+      <c r="O2" s="682" t="n"/>
+      <c r="P2" s="682" t="n"/>
+      <c r="Q2" s="682" t="n"/>
+      <c r="R2" s="682" t="n"/>
+      <c r="S2" s="682" t="n"/>
+      <c r="T2" s="682" t="n"/>
+      <c r="U2" s="682" t="n"/>
+      <c r="V2" s="682" t="n"/>
+      <c r="W2" s="682" t="n"/>
+      <c r="X2" s="682" t="n"/>
+      <c r="Y2" s="682" t="n"/>
+      <c r="Z2" s="682" t="n"/>
+      <c r="AA2" s="682" t="n"/>
+      <c r="AB2" s="682" t="n"/>
+      <c r="AC2" s="682" t="n"/>
+      <c r="AD2" s="683" t="n"/>
+      <c r="AE2" s="684" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="685" t="n"/>
+      <c r="AG2" s="685" t="n"/>
+      <c r="AH2" s="686" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="687" t="n"/>
+      <c r="AK2" s="687" t="n"/>
+      <c r="AL2" s="687" t="n"/>
+      <c r="AM2" s="687" t="n"/>
+      <c r="AN2" s="688" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="516" t="n"/>
-      <c r="B3" s="517" t="n"/>
-      <c r="C3" s="517" t="n"/>
-      <c r="D3" s="517" t="n"/>
-      <c r="E3" s="517" t="n"/>
-      <c r="F3" s="517" t="n"/>
-      <c r="G3" s="517" t="n"/>
-      <c r="H3" s="515" t="n"/>
-      <c r="I3" s="441" t="n"/>
-      <c r="J3" s="442" t="n"/>
-      <c r="K3" s="442" t="n"/>
-      <c r="L3" s="442" t="n"/>
-      <c r="M3" s="442" t="n"/>
-      <c r="N3" s="442" t="n"/>
-      <c r="O3" s="442" t="n"/>
-      <c r="P3" s="442" t="n"/>
-      <c r="Q3" s="442" t="n"/>
-      <c r="R3" s="442" t="n"/>
-      <c r="S3" s="442" t="n"/>
-      <c r="T3" s="442" t="n"/>
-      <c r="U3" s="442" t="n"/>
-      <c r="V3" s="442" t="n"/>
-      <c r="W3" s="442" t="n"/>
-      <c r="X3" s="442" t="n"/>
-      <c r="Y3" s="442" t="n"/>
-      <c r="Z3" s="442" t="n"/>
-      <c r="AA3" s="442" t="n"/>
-      <c r="AB3" s="442" t="n"/>
-      <c r="AC3" s="442" t="n"/>
-      <c r="AD3" s="443" t="n"/>
-      <c r="AE3" s="444" t="n"/>
-      <c r="AF3" s="445" t="n"/>
-      <c r="AG3" s="445" t="n"/>
-      <c r="AH3" s="446" t="n"/>
-      <c r="AI3" s="447" t="n"/>
-      <c r="AJ3" s="448" t="n"/>
-      <c r="AK3" s="448" t="n"/>
-      <c r="AL3" s="448" t="n"/>
-      <c r="AM3" s="448" t="n"/>
-      <c r="AN3" s="449" t="n"/>
+      <c r="A3" s="689" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="690" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="690" t="n"/>
+      <c r="AE3" s="691" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="692" t="n"/>
+      <c r="AG3" s="692" t="n"/>
+      <c r="AH3" s="693" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="694" t="n"/>
+      <c r="AK3" s="694" t="n"/>
+      <c r="AL3" s="694" t="n"/>
+      <c r="AM3" s="694" t="n"/>
+      <c r="AN3" s="695" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="518" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="519" t="inlineStr">
-        <is>
-          <t>Sample No.</t>
-        </is>
-      </c>
-      <c r="C4" s="519" t="inlineStr">
-        <is>
-          <t>ID / Serial</t>
-        </is>
-      </c>
-      <c r="D4" s="519" t="inlineStr">
-        <is>
-          <t>Measured Result / Observation</t>
-        </is>
-      </c>
-      <c r="E4" s="519" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="F4" s="519" t="inlineStr">
-        <is>
-          <t>Defect Class</t>
-        </is>
-      </c>
-      <c r="G4" s="519" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="H4" s="520" t="inlineStr">
-        <is>
-          <t>Evidence Ref</t>
-        </is>
-      </c>
-      <c r="I4" s="450" t="n"/>
-      <c r="J4" s="451" t="n"/>
-      <c r="K4" s="451" t="n"/>
-      <c r="L4" s="451" t="n"/>
-      <c r="M4" s="451" t="n"/>
-      <c r="N4" s="451" t="n"/>
-      <c r="O4" s="451" t="n"/>
-      <c r="P4" s="451" t="n"/>
-      <c r="Q4" s="451" t="n"/>
-      <c r="R4" s="451" t="n"/>
-      <c r="S4" s="451" t="n"/>
-      <c r="T4" s="451" t="n"/>
-      <c r="U4" s="451" t="n"/>
-      <c r="V4" s="451" t="n"/>
-      <c r="W4" s="451" t="n"/>
-      <c r="X4" s="451" t="n"/>
-      <c r="Y4" s="451" t="n"/>
-      <c r="Z4" s="451" t="n"/>
-      <c r="AA4" s="451" t="n"/>
-      <c r="AB4" s="451" t="n"/>
-      <c r="AC4" s="451" t="n"/>
-      <c r="AD4" s="452" t="n"/>
-      <c r="AE4" s="444" t="n"/>
-      <c r="AF4" s="445" t="n"/>
-      <c r="AG4" s="445" t="n"/>
-      <c r="AH4" s="446" t="n"/>
-      <c r="AI4" s="447" t="n"/>
-      <c r="AJ4" s="448" t="n"/>
-      <c r="AK4" s="448" t="n"/>
-      <c r="AL4" s="448" t="n"/>
-      <c r="AM4" s="448" t="n"/>
-      <c r="AN4" s="449" t="n"/>
+      <c r="A4" s="689" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="690" t="n"/>
+      <c r="I4" s="696" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="690" t="n"/>
+      <c r="AE4" s="691" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="692" t="n"/>
+      <c r="AG4" s="692" t="n"/>
+      <c r="AH4" s="693" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="694" t="n"/>
+      <c r="AK4" s="694" t="n"/>
+      <c r="AL4" s="694" t="n"/>
+      <c r="AM4" s="694" t="n"/>
+      <c r="AN4" s="695" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="521">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B5" s="522" t="n"/>
-      <c r="C5" s="522" t="n"/>
-      <c r="D5" s="522" t="n"/>
-      <c r="E5" s="522" t="n"/>
-      <c r="F5" s="522" t="n"/>
-      <c r="G5" s="522" t="n"/>
-      <c r="H5" s="523" t="n"/>
-      <c r="I5" s="456" t="n"/>
-      <c r="J5" s="457" t="n"/>
-      <c r="K5" s="457" t="n"/>
-      <c r="L5" s="457" t="n"/>
-      <c r="M5" s="457" t="n"/>
-      <c r="N5" s="457" t="n"/>
-      <c r="O5" s="457" t="n"/>
-      <c r="P5" s="457" t="n"/>
-      <c r="Q5" s="457" t="n"/>
-      <c r="R5" s="457" t="n"/>
-      <c r="S5" s="457" t="n"/>
-      <c r="T5" s="457" t="n"/>
-      <c r="U5" s="457" t="n"/>
-      <c r="V5" s="457" t="n"/>
-      <c r="W5" s="457" t="n"/>
-      <c r="X5" s="457" t="n"/>
-      <c r="Y5" s="457" t="n"/>
-      <c r="Z5" s="457" t="n"/>
-      <c r="AA5" s="457" t="n"/>
-      <c r="AB5" s="457" t="n"/>
-      <c r="AC5" s="457" t="n"/>
-      <c r="AD5" s="458" t="n"/>
-      <c r="AE5" s="459" t="n"/>
-      <c r="AF5" s="460" t="n"/>
-      <c r="AG5" s="460" t="n"/>
-      <c r="AH5" s="461" t="n"/>
-      <c r="AI5" s="462" t="n"/>
-      <c r="AJ5" s="463" t="n"/>
-      <c r="AK5" s="463" t="n"/>
-      <c r="AL5" s="463" t="n"/>
-      <c r="AM5" s="463" t="n"/>
-      <c r="AN5" s="464" t="n"/>
+      <c r="A5" s="689" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="690" t="n"/>
+      <c r="I5" s="697" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="690" t="n"/>
+      <c r="AE5" s="691" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="692" t="n"/>
+      <c r="AG5" s="692" t="n"/>
+      <c r="AH5" s="693" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="694" t="n"/>
+      <c r="AK5" s="694" t="n"/>
+      <c r="AL5" s="694" t="n"/>
+      <c r="AM5" s="694" t="n"/>
+      <c r="AN5" s="695" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="524">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B6" s="525" t="n"/>
-      <c r="C6" s="526" t="n"/>
-      <c r="D6" s="526" t="n"/>
-      <c r="E6" s="526" t="n"/>
-      <c r="F6" s="526" t="n"/>
-      <c r="G6" s="526" t="n"/>
-      <c r="H6" s="526" t="n"/>
-      <c r="I6" s="470" t="n"/>
-      <c r="J6" s="470" t="n"/>
-      <c r="K6" s="470" t="n"/>
-      <c r="L6" s="470" t="n"/>
-      <c r="M6" s="470" t="n"/>
-      <c r="N6" s="470" t="n"/>
-      <c r="O6" s="470" t="n"/>
-      <c r="P6" s="470" t="n"/>
-      <c r="Q6" s="470" t="n"/>
-      <c r="R6" s="470" t="n"/>
-      <c r="S6" s="470" t="n"/>
-      <c r="T6" s="470" t="n"/>
-      <c r="U6" s="470" t="n"/>
-      <c r="V6" s="470" t="n"/>
-      <c r="W6" s="470" t="n"/>
-      <c r="X6" s="470" t="n"/>
-      <c r="Y6" s="470" t="n"/>
-      <c r="Z6" s="470" t="n"/>
-      <c r="AA6" s="470" t="n"/>
-      <c r="AB6" s="470" t="n"/>
-      <c r="AC6" s="470" t="n"/>
-      <c r="AD6" s="470" t="n"/>
-      <c r="AE6" s="470" t="n"/>
-      <c r="AF6" s="470" t="n"/>
-      <c r="AG6" s="470" t="n"/>
-      <c r="AH6" s="470" t="n"/>
-      <c r="AI6" s="470" t="n"/>
-      <c r="AJ6" s="470" t="n"/>
-      <c r="AK6" s="470" t="n"/>
-      <c r="AL6" s="470" t="n"/>
-      <c r="AM6" s="470" t="n"/>
-      <c r="AN6" s="502" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="713" t="n"/>
+      <c r="B6" s="714" t="n"/>
+      <c r="C6" s="714" t="n"/>
+      <c r="D6" s="714" t="n"/>
+      <c r="E6" s="714" t="n"/>
+      <c r="F6" s="714" t="n"/>
+      <c r="G6" s="714" t="n"/>
+      <c r="H6" s="715" t="n"/>
+      <c r="I6" s="714" t="n"/>
+      <c r="J6" s="714" t="n"/>
+      <c r="K6" s="714" t="n"/>
+      <c r="L6" s="714" t="n"/>
+      <c r="M6" s="714" t="n"/>
+      <c r="N6" s="714" t="n"/>
+      <c r="O6" s="714" t="n"/>
+      <c r="P6" s="714" t="n"/>
+      <c r="Q6" s="714" t="n"/>
+      <c r="R6" s="714" t="n"/>
+      <c r="S6" s="714" t="n"/>
+      <c r="T6" s="714" t="n"/>
+      <c r="U6" s="714" t="n"/>
+      <c r="V6" s="714" t="n"/>
+      <c r="W6" s="714" t="n"/>
+      <c r="X6" s="714" t="n"/>
+      <c r="Y6" s="714" t="n"/>
+      <c r="Z6" s="714" t="n"/>
+      <c r="AA6" s="714" t="n"/>
+      <c r="AB6" s="714" t="n"/>
+      <c r="AC6" s="714" t="n"/>
+      <c r="AD6" s="715" t="n"/>
+      <c r="AE6" s="716" t="n"/>
+      <c r="AF6" s="716" t="n"/>
+      <c r="AG6" s="716" t="n"/>
+      <c r="AH6" s="717" t="n"/>
+      <c r="AI6" s="718" t="n"/>
+      <c r="AJ6" s="718" t="n"/>
+      <c r="AK6" s="718" t="n"/>
+      <c r="AL6" s="718" t="n"/>
+      <c r="AM6" s="718" t="n"/>
+      <c r="AN6" s="719" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="527">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B7" s="528" t="n"/>
-      <c r="C7" s="529" t="n"/>
-      <c r="D7" s="529" t="n"/>
-      <c r="E7" s="529" t="n"/>
-      <c r="F7" s="529" t="n"/>
-      <c r="G7" s="529" t="n"/>
-      <c r="H7" s="529" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="530" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="720" t="n"/>
+      <c r="B7" s="720" t="n"/>
+      <c r="C7" s="720" t="n"/>
+      <c r="D7" s="720" t="n"/>
+      <c r="E7" s="720" t="n"/>
+      <c r="F7" s="720" t="n"/>
+      <c r="G7" s="720" t="n"/>
+      <c r="H7" s="721" t="n"/>
+      <c r="I7" s="721" t="n"/>
+      <c r="J7" s="722" t="n"/>
+      <c r="K7" s="722" t="n"/>
+      <c r="L7" s="722" t="n"/>
+      <c r="M7" s="722" t="n"/>
+      <c r="N7" s="722" t="n"/>
+      <c r="O7" s="722" t="n"/>
+      <c r="P7" s="722" t="n"/>
+      <c r="Q7" s="722" t="n"/>
+      <c r="R7" s="722" t="n"/>
+      <c r="S7" s="722" t="n"/>
+      <c r="T7" s="722" t="n"/>
+      <c r="U7" s="722" t="n"/>
+      <c r="V7" s="722" t="n"/>
+      <c r="W7" s="722" t="n"/>
+      <c r="X7" s="722" t="n"/>
+      <c r="Y7" s="722" t="n"/>
+      <c r="Z7" s="722" t="n"/>
+      <c r="AA7" s="722" t="n"/>
+      <c r="AB7" s="722" t="n"/>
+      <c r="AC7" s="722" t="n"/>
+      <c r="AD7" s="722" t="n"/>
+      <c r="AE7" s="722" t="n"/>
+      <c r="AF7" s="722" t="n"/>
+      <c r="AG7" s="722" t="n"/>
+      <c r="AH7" s="722" t="n"/>
+      <c r="AI7" s="722" t="n"/>
+      <c r="AJ7" s="722" t="n"/>
+      <c r="AK7" s="722" t="n"/>
+      <c r="AL7" s="722" t="n"/>
+      <c r="AM7" s="722" t="n"/>
+      <c r="AN7" s="722" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B8" s="532" t="n"/>
-      <c r="C8" s="533" t="n"/>
-      <c r="D8" s="533" t="n"/>
-      <c r="E8" s="533" t="n"/>
-      <c r="F8" s="533" t="n"/>
-      <c r="G8" s="533" t="n"/>
-      <c r="H8" s="533" t="n"/>
-      <c r="I8" s="356" t="n"/>
-      <c r="J8" s="356" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="356" t="n"/>
-      <c r="M8" s="356" t="n"/>
-      <c r="N8" s="356" t="n"/>
-      <c r="O8" s="356" t="n"/>
-      <c r="P8" s="356" t="n"/>
-      <c r="Q8" s="356" t="n"/>
-      <c r="R8" s="356" t="n"/>
-      <c r="S8" s="356" t="n"/>
-      <c r="T8" s="356" t="n"/>
-      <c r="U8" s="356" t="n"/>
-      <c r="V8" s="356" t="n"/>
-      <c r="W8" s="356" t="n"/>
-      <c r="X8" s="356" t="n"/>
-      <c r="Y8" s="356" t="n"/>
-      <c r="Z8" s="356" t="n"/>
-      <c r="AA8" s="356" t="n"/>
-      <c r="AB8" s="356" t="n"/>
-      <c r="AC8" s="356" t="n"/>
-      <c r="AD8" s="356" t="n"/>
-      <c r="AE8" s="356" t="n"/>
-      <c r="AF8" s="356" t="n"/>
-      <c r="AG8" s="356" t="n"/>
-      <c r="AH8" s="356" t="n"/>
-      <c r="AI8" s="356" t="n"/>
-      <c r="AJ8" s="356" t="n"/>
-      <c r="AK8" s="356" t="n"/>
-      <c r="AL8" s="356" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="534" t="n"/>
+    <row r="8">
+      <c r="A8" s="266" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="266" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="C8" s="266" t="inlineStr">
+        <is>
+          <t>SALES</t>
+        </is>
+      </c>
+      <c r="D8" s="266" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="E8" s="266" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F8" s="266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G8" s="266" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H8" s="348" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I8" s="348" t="inlineStr">
+        <is>
+          <t>CERT MISMATCH</t>
+        </is>
+      </c>
+      <c r="J8" s="668" t="n"/>
+      <c r="K8" s="668" t="n"/>
+      <c r="L8" s="668" t="n"/>
+      <c r="M8" s="668" t="n"/>
+      <c r="N8" s="668" t="n"/>
+      <c r="O8" s="668" t="n"/>
+      <c r="P8" s="668" t="n"/>
+      <c r="Q8" s="668" t="n"/>
+      <c r="R8" s="668" t="n"/>
+      <c r="S8" s="668" t="n"/>
+      <c r="T8" s="668" t="n"/>
+      <c r="U8" s="668" t="n"/>
+      <c r="V8" s="668" t="n"/>
+      <c r="W8" s="668" t="n"/>
+      <c r="X8" s="668" t="n"/>
+      <c r="Y8" s="668" t="n"/>
+      <c r="Z8" s="668" t="n"/>
+      <c r="AA8" s="668" t="n"/>
+      <c r="AB8" s="668" t="n"/>
+      <c r="AC8" s="668" t="n"/>
+      <c r="AD8" s="668" t="n"/>
+      <c r="AE8" s="668" t="n"/>
+      <c r="AF8" s="668" t="n"/>
+      <c r="AG8" s="668" t="n"/>
+      <c r="AH8" s="668" t="n"/>
+      <c r="AI8" s="668" t="n"/>
+      <c r="AJ8" s="668" t="n"/>
+      <c r="AK8" s="668" t="n"/>
+      <c r="AL8" s="668" t="n"/>
+      <c r="AM8" s="668" t="n"/>
+      <c r="AN8" s="668" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B9" s="532" t="n"/>
-      <c r="C9" s="533" t="n"/>
-      <c r="D9" s="533" t="n"/>
-      <c r="E9" s="533" t="n"/>
-      <c r="F9" s="533" t="n"/>
-      <c r="G9" s="533" t="n"/>
-      <c r="H9" s="533" t="n"/>
-      <c r="I9" s="356" t="n"/>
-      <c r="J9" s="356" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="356" t="n"/>
-      <c r="M9" s="356" t="n"/>
-      <c r="N9" s="356" t="n"/>
-      <c r="O9" s="356" t="n"/>
-      <c r="P9" s="356" t="n"/>
-      <c r="Q9" s="356" t="n"/>
-      <c r="R9" s="356" t="n"/>
-      <c r="S9" s="356" t="n"/>
-      <c r="T9" s="356" t="n"/>
-      <c r="U9" s="356" t="n"/>
-      <c r="V9" s="356" t="n"/>
-      <c r="W9" s="356" t="n"/>
-      <c r="X9" s="356" t="n"/>
-      <c r="Y9" s="356" t="n"/>
-      <c r="Z9" s="356" t="n"/>
-      <c r="AA9" s="356" t="n"/>
-      <c r="AB9" s="356" t="n"/>
-      <c r="AC9" s="356" t="n"/>
-      <c r="AD9" s="356" t="n"/>
-      <c r="AE9" s="356" t="n"/>
-      <c r="AF9" s="356" t="n"/>
-      <c r="AG9" s="356" t="n"/>
-      <c r="AH9" s="356" t="n"/>
-      <c r="AI9" s="356" t="n"/>
-      <c r="AJ9" s="356" t="n"/>
-      <c r="AK9" s="356" t="n"/>
-      <c r="AL9" s="356" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="534" t="n"/>
+    <row r="9">
+      <c r="A9" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B9" s="266" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="C9" s="266" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="D9" s="266" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="E9" s="266" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F9" s="266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" s="266" t="inlineStr">
+        <is>
+          <t>NOT CLOSED</t>
+        </is>
+      </c>
+      <c r="H9" s="348" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="I9" s="348" t="inlineStr">
+        <is>
+          <t>TRACEABILITY BREAK</t>
+        </is>
+      </c>
+      <c r="J9" s="668" t="n"/>
+      <c r="K9" s="668" t="n"/>
+      <c r="L9" s="668" t="n"/>
+      <c r="M9" s="668" t="n"/>
+      <c r="N9" s="668" t="n"/>
+      <c r="O9" s="668" t="n"/>
+      <c r="P9" s="668" t="n"/>
+      <c r="Q9" s="668" t="n"/>
+      <c r="R9" s="668" t="n"/>
+      <c r="S9" s="668" t="n"/>
+      <c r="T9" s="668" t="n"/>
+      <c r="U9" s="668" t="n"/>
+      <c r="V9" s="668" t="n"/>
+      <c r="W9" s="668" t="n"/>
+      <c r="X9" s="668" t="n"/>
+      <c r="Y9" s="668" t="n"/>
+      <c r="Z9" s="668" t="n"/>
+      <c r="AA9" s="668" t="n"/>
+      <c r="AB9" s="668" t="n"/>
+      <c r="AC9" s="668" t="n"/>
+      <c r="AD9" s="668" t="n"/>
+      <c r="AE9" s="668" t="n"/>
+      <c r="AF9" s="668" t="n"/>
+      <c r="AG9" s="668" t="n"/>
+      <c r="AH9" s="668" t="n"/>
+      <c r="AI9" s="668" t="n"/>
+      <c r="AJ9" s="668" t="n"/>
+      <c r="AK9" s="668" t="n"/>
+      <c r="AL9" s="668" t="n"/>
+      <c r="AM9" s="668" t="n"/>
+      <c r="AN9" s="668" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B10" s="532" t="n"/>
-      <c r="C10" s="533" t="n"/>
-      <c r="D10" s="533" t="n"/>
-      <c r="E10" s="533" t="n"/>
-      <c r="F10" s="533" t="n"/>
-      <c r="G10" s="533" t="n"/>
-      <c r="H10" s="533" t="n"/>
-      <c r="I10" s="356" t="n"/>
-      <c r="J10" s="356" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="356" t="n"/>
-      <c r="M10" s="356" t="n"/>
-      <c r="N10" s="356" t="n"/>
-      <c r="O10" s="356" t="n"/>
-      <c r="P10" s="356" t="n"/>
-      <c r="Q10" s="356" t="n"/>
-      <c r="R10" s="356" t="n"/>
-      <c r="S10" s="356" t="n"/>
-      <c r="T10" s="356" t="n"/>
-      <c r="U10" s="356" t="n"/>
-      <c r="V10" s="356" t="n"/>
-      <c r="W10" s="356" t="n"/>
-      <c r="X10" s="356" t="n"/>
-      <c r="Y10" s="356" t="n"/>
-      <c r="Z10" s="356" t="n"/>
-      <c r="AA10" s="356" t="n"/>
-      <c r="AB10" s="356" t="n"/>
-      <c r="AC10" s="356" t="n"/>
-      <c r="AD10" s="356" t="n"/>
-      <c r="AE10" s="356" t="n"/>
-      <c r="AF10" s="356" t="n"/>
-      <c r="AG10" s="356" t="n"/>
-      <c r="AH10" s="356" t="n"/>
-      <c r="AI10" s="356" t="n"/>
-      <c r="AJ10" s="356" t="n"/>
-      <c r="AK10" s="356" t="n"/>
-      <c r="AL10" s="356" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="534" t="n"/>
+    <row r="10">
+      <c r="A10" s="266" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B10" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="266" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="D10" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E10" s="266" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="F10" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" s="668" t="n"/>
+      <c r="H10" s="348" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="I10" s="348" t="inlineStr">
+        <is>
+          <t>DAMAGE</t>
+        </is>
+      </c>
+      <c r="J10" s="668" t="n"/>
+      <c r="K10" s="668" t="n"/>
+      <c r="L10" s="668" t="n"/>
+      <c r="M10" s="668" t="n"/>
+      <c r="N10" s="668" t="n"/>
+      <c r="O10" s="668" t="n"/>
+      <c r="P10" s="668" t="n"/>
+      <c r="Q10" s="668" t="n"/>
+      <c r="R10" s="668" t="n"/>
+      <c r="S10" s="668" t="n"/>
+      <c r="T10" s="668" t="n"/>
+      <c r="U10" s="668" t="n"/>
+      <c r="V10" s="668" t="n"/>
+      <c r="W10" s="668" t="n"/>
+      <c r="X10" s="668" t="n"/>
+      <c r="Y10" s="668" t="n"/>
+      <c r="Z10" s="668" t="n"/>
+      <c r="AA10" s="668" t="n"/>
+      <c r="AB10" s="668" t="n"/>
+      <c r="AC10" s="668" t="n"/>
+      <c r="AD10" s="668" t="n"/>
+      <c r="AE10" s="668" t="n"/>
+      <c r="AF10" s="668" t="n"/>
+      <c r="AG10" s="668" t="n"/>
+      <c r="AH10" s="668" t="n"/>
+      <c r="AI10" s="668" t="n"/>
+      <c r="AJ10" s="668" t="n"/>
+      <c r="AK10" s="668" t="n"/>
+      <c r="AL10" s="668" t="n"/>
+      <c r="AM10" s="668" t="n"/>
+      <c r="AN10" s="668" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B11" s="532" t="n"/>
-      <c r="C11" s="533" t="n"/>
-      <c r="D11" s="533" t="n"/>
-      <c r="E11" s="533" t="n"/>
-      <c r="F11" s="533" t="n"/>
-      <c r="G11" s="533" t="n"/>
-      <c r="H11" s="533" t="n"/>
-      <c r="I11" s="356" t="n"/>
-      <c r="J11" s="356" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="356" t="n"/>
-      <c r="M11" s="356" t="n"/>
-      <c r="N11" s="356" t="n"/>
-      <c r="O11" s="356" t="n"/>
-      <c r="P11" s="356" t="n"/>
-      <c r="Q11" s="356" t="n"/>
-      <c r="R11" s="356" t="n"/>
-      <c r="S11" s="356" t="n"/>
-      <c r="T11" s="356" t="n"/>
-      <c r="U11" s="356" t="n"/>
-      <c r="V11" s="356" t="n"/>
-      <c r="W11" s="356" t="n"/>
-      <c r="X11" s="356" t="n"/>
-      <c r="Y11" s="356" t="n"/>
-      <c r="Z11" s="356" t="n"/>
-      <c r="AA11" s="356" t="n"/>
-      <c r="AB11" s="356" t="n"/>
-      <c r="AC11" s="356" t="n"/>
-      <c r="AD11" s="356" t="n"/>
-      <c r="AE11" s="356" t="n"/>
-      <c r="AF11" s="356" t="n"/>
-      <c r="AG11" s="356" t="n"/>
-      <c r="AH11" s="356" t="n"/>
-      <c r="AI11" s="356" t="n"/>
-      <c r="AJ11" s="356" t="n"/>
-      <c r="AK11" s="356" t="n"/>
-      <c r="AL11" s="356" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="534" t="n"/>
+    <row r="11">
+      <c r="A11" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B11" s="668" t="n"/>
+      <c r="C11" s="266" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="D11" s="266" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="E11" s="348" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="F11" s="668" t="n"/>
+      <c r="G11" s="668" t="n"/>
+      <c r="H11" s="348" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="I11" s="348" t="inlineStr">
+        <is>
+          <t>LATE DELIVERY</t>
+        </is>
+      </c>
+      <c r="J11" s="668" t="n"/>
+      <c r="K11" s="668" t="n"/>
+      <c r="L11" s="668" t="n"/>
+      <c r="M11" s="668" t="n"/>
+      <c r="N11" s="668" t="n"/>
+      <c r="O11" s="668" t="n"/>
+      <c r="P11" s="668" t="n"/>
+      <c r="Q11" s="668" t="n"/>
+      <c r="R11" s="668" t="n"/>
+      <c r="S11" s="668" t="n"/>
+      <c r="T11" s="668" t="n"/>
+      <c r="U11" s="668" t="n"/>
+      <c r="V11" s="668" t="n"/>
+      <c r="W11" s="668" t="n"/>
+      <c r="X11" s="668" t="n"/>
+      <c r="Y11" s="668" t="n"/>
+      <c r="Z11" s="668" t="n"/>
+      <c r="AA11" s="668" t="n"/>
+      <c r="AB11" s="668" t="n"/>
+      <c r="AC11" s="668" t="n"/>
+      <c r="AD11" s="668" t="n"/>
+      <c r="AE11" s="668" t="n"/>
+      <c r="AF11" s="668" t="n"/>
+      <c r="AG11" s="668" t="n"/>
+      <c r="AH11" s="668" t="n"/>
+      <c r="AI11" s="668" t="n"/>
+      <c r="AJ11" s="668" t="n"/>
+      <c r="AK11" s="668" t="n"/>
+      <c r="AL11" s="668" t="n"/>
+      <c r="AM11" s="668" t="n"/>
+      <c r="AN11" s="668" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B12" s="532" t="n"/>
-      <c r="C12" s="533" t="n"/>
-      <c r="D12" s="533" t="n"/>
-      <c r="E12" s="533" t="n"/>
-      <c r="F12" s="533" t="n"/>
-      <c r="G12" s="533" t="n"/>
-      <c r="H12" s="533" t="n"/>
-      <c r="I12" s="356" t="n"/>
-      <c r="J12" s="356" t="n"/>
-      <c r="K12" s="356" t="n"/>
-      <c r="L12" s="356" t="n"/>
-      <c r="M12" s="356" t="n"/>
-      <c r="N12" s="356" t="n"/>
-      <c r="O12" s="356" t="n"/>
-      <c r="P12" s="356" t="n"/>
-      <c r="Q12" s="356" t="n"/>
-      <c r="R12" s="356" t="n"/>
-      <c r="S12" s="356" t="n"/>
-      <c r="T12" s="356" t="n"/>
-      <c r="U12" s="356" t="n"/>
-      <c r="V12" s="356" t="n"/>
-      <c r="W12" s="356" t="n"/>
-      <c r="X12" s="356" t="n"/>
-      <c r="Y12" s="356" t="n"/>
-      <c r="Z12" s="356" t="n"/>
-      <c r="AA12" s="356" t="n"/>
-      <c r="AB12" s="356" t="n"/>
-      <c r="AC12" s="356" t="n"/>
-      <c r="AD12" s="356" t="n"/>
-      <c r="AE12" s="356" t="n"/>
-      <c r="AF12" s="356" t="n"/>
-      <c r="AG12" s="356" t="n"/>
-      <c r="AH12" s="356" t="n"/>
-      <c r="AI12" s="356" t="n"/>
-      <c r="AJ12" s="356" t="n"/>
-      <c r="AK12" s="356" t="n"/>
-      <c r="AL12" s="356" t="n"/>
-      <c r="AM12" s="356" t="n"/>
-      <c r="AN12" s="534" t="n"/>
+    <row r="12">
+      <c r="A12" s="668" t="n"/>
+      <c r="B12" s="668" t="n"/>
+      <c r="C12" s="348" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D12" s="668" t="n"/>
+      <c r="E12" s="668" t="n"/>
+      <c r="F12" s="668" t="n"/>
+      <c r="G12" s="668" t="n"/>
+      <c r="H12" s="348" t="inlineStr">
+        <is>
+          <t>INEFFECTIVE</t>
+        </is>
+      </c>
+      <c r="I12" s="348" t="inlineStr">
+        <is>
+          <t>SPEC DEVIATION</t>
+        </is>
+      </c>
+      <c r="J12" s="668" t="n"/>
+      <c r="K12" s="668" t="n"/>
+      <c r="L12" s="668" t="n"/>
+      <c r="M12" s="668" t="n"/>
+      <c r="N12" s="668" t="n"/>
+      <c r="O12" s="668" t="n"/>
+      <c r="P12" s="668" t="n"/>
+      <c r="Q12" s="668" t="n"/>
+      <c r="R12" s="668" t="n"/>
+      <c r="S12" s="668" t="n"/>
+      <c r="T12" s="668" t="n"/>
+      <c r="U12" s="668" t="n"/>
+      <c r="V12" s="668" t="n"/>
+      <c r="W12" s="668" t="n"/>
+      <c r="X12" s="668" t="n"/>
+      <c r="Y12" s="668" t="n"/>
+      <c r="Z12" s="668" t="n"/>
+      <c r="AA12" s="668" t="n"/>
+      <c r="AB12" s="668" t="n"/>
+      <c r="AC12" s="668" t="n"/>
+      <c r="AD12" s="668" t="n"/>
+      <c r="AE12" s="668" t="n"/>
+      <c r="AF12" s="668" t="n"/>
+      <c r="AG12" s="668" t="n"/>
+      <c r="AH12" s="668" t="n"/>
+      <c r="AI12" s="668" t="n"/>
+      <c r="AJ12" s="668" t="n"/>
+      <c r="AK12" s="668" t="n"/>
+      <c r="AL12" s="668" t="n"/>
+      <c r="AM12" s="668" t="n"/>
+      <c r="AN12" s="668" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B13" s="532" t="n"/>
-      <c r="C13" s="533" t="n"/>
-      <c r="D13" s="533" t="n"/>
-      <c r="E13" s="533" t="n"/>
-      <c r="F13" s="533" t="n"/>
-      <c r="G13" s="533" t="n"/>
-      <c r="H13" s="533" t="n"/>
-      <c r="I13" s="356" t="n"/>
-      <c r="J13" s="356" t="n"/>
-      <c r="K13" s="356" t="n"/>
-      <c r="L13" s="356" t="n"/>
-      <c r="M13" s="356" t="n"/>
-      <c r="N13" s="356" t="n"/>
-      <c r="O13" s="356" t="n"/>
-      <c r="P13" s="356" t="n"/>
-      <c r="Q13" s="356" t="n"/>
-      <c r="R13" s="356" t="n"/>
-      <c r="S13" s="356" t="n"/>
-      <c r="T13" s="356" t="n"/>
-      <c r="U13" s="356" t="n"/>
-      <c r="V13" s="356" t="n"/>
-      <c r="W13" s="356" t="n"/>
-      <c r="X13" s="356" t="n"/>
-      <c r="Y13" s="356" t="n"/>
-      <c r="Z13" s="356" t="n"/>
-      <c r="AA13" s="356" t="n"/>
-      <c r="AB13" s="356" t="n"/>
-      <c r="AC13" s="356" t="n"/>
-      <c r="AD13" s="356" t="n"/>
-      <c r="AE13" s="356" t="n"/>
-      <c r="AF13" s="356" t="n"/>
-      <c r="AG13" s="356" t="n"/>
-      <c r="AH13" s="356" t="n"/>
-      <c r="AI13" s="356" t="n"/>
-      <c r="AJ13" s="356" t="n"/>
-      <c r="AK13" s="356" t="n"/>
-      <c r="AL13" s="356" t="n"/>
-      <c r="AM13" s="356" t="n"/>
-      <c r="AN13" s="534" t="n"/>
+    <row r="13">
+      <c r="A13" s="668" t="n"/>
+      <c r="B13" s="668" t="n"/>
+      <c r="C13" s="348" t="inlineStr">
+        <is>
+          <t>PUR</t>
+        </is>
+      </c>
+      <c r="D13" s="668" t="n"/>
+      <c r="E13" s="668" t="n"/>
+      <c r="F13" s="668" t="n"/>
+      <c r="G13" s="668" t="n"/>
+      <c r="H13" s="348" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I13" s="348" t="inlineStr">
+        <is>
+          <t>PACKAGING ISSUE</t>
+        </is>
+      </c>
+      <c r="J13" s="668" t="n"/>
+      <c r="K13" s="668" t="n"/>
+      <c r="L13" s="668" t="n"/>
+      <c r="M13" s="668" t="n"/>
+      <c r="N13" s="668" t="n"/>
+      <c r="O13" s="668" t="n"/>
+      <c r="P13" s="668" t="n"/>
+      <c r="Q13" s="668" t="n"/>
+      <c r="R13" s="668" t="n"/>
+      <c r="S13" s="668" t="n"/>
+      <c r="T13" s="668" t="n"/>
+      <c r="U13" s="668" t="n"/>
+      <c r="V13" s="668" t="n"/>
+      <c r="W13" s="668" t="n"/>
+      <c r="X13" s="668" t="n"/>
+      <c r="Y13" s="668" t="n"/>
+      <c r="Z13" s="668" t="n"/>
+      <c r="AA13" s="668" t="n"/>
+      <c r="AB13" s="668" t="n"/>
+      <c r="AC13" s="668" t="n"/>
+      <c r="AD13" s="668" t="n"/>
+      <c r="AE13" s="668" t="n"/>
+      <c r="AF13" s="668" t="n"/>
+      <c r="AG13" s="668" t="n"/>
+      <c r="AH13" s="668" t="n"/>
+      <c r="AI13" s="668" t="n"/>
+      <c r="AJ13" s="668" t="n"/>
+      <c r="AK13" s="668" t="n"/>
+      <c r="AL13" s="668" t="n"/>
+      <c r="AM13" s="668" t="n"/>
+      <c r="AN13" s="668" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B14" s="532" t="n"/>
-      <c r="C14" s="533" t="n"/>
-      <c r="D14" s="533" t="n"/>
-      <c r="E14" s="533" t="n"/>
-      <c r="F14" s="533" t="n"/>
-      <c r="G14" s="533" t="n"/>
-      <c r="H14" s="533" t="n"/>
-      <c r="I14" s="356" t="n"/>
-      <c r="J14" s="356" t="n"/>
-      <c r="K14" s="356" t="n"/>
-      <c r="L14" s="356" t="n"/>
-      <c r="M14" s="356" t="n"/>
-      <c r="N14" s="356" t="n"/>
-      <c r="O14" s="356" t="n"/>
-      <c r="P14" s="356" t="n"/>
-      <c r="Q14" s="356" t="n"/>
-      <c r="R14" s="356" t="n"/>
-      <c r="S14" s="356" t="n"/>
-      <c r="T14" s="356" t="n"/>
-      <c r="U14" s="356" t="n"/>
-      <c r="V14" s="356" t="n"/>
-      <c r="W14" s="356" t="n"/>
-      <c r="X14" s="356" t="n"/>
-      <c r="Y14" s="356" t="n"/>
-      <c r="Z14" s="356" t="n"/>
-      <c r="AA14" s="356" t="n"/>
-      <c r="AB14" s="356" t="n"/>
-      <c r="AC14" s="356" t="n"/>
-      <c r="AD14" s="356" t="n"/>
-      <c r="AE14" s="356" t="n"/>
-      <c r="AF14" s="356" t="n"/>
-      <c r="AG14" s="356" t="n"/>
-      <c r="AH14" s="356" t="n"/>
-      <c r="AI14" s="356" t="n"/>
-      <c r="AJ14" s="356" t="n"/>
-      <c r="AK14" s="356" t="n"/>
-      <c r="AL14" s="356" t="n"/>
-      <c r="AM14" s="356" t="n"/>
-      <c r="AN14" s="534" t="n"/>
+    <row r="14">
+      <c r="A14" s="668" t="n"/>
+      <c r="B14" s="668" t="n"/>
+      <c r="C14" s="348" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="D14" s="668" t="n"/>
+      <c r="E14" s="668" t="n"/>
+      <c r="F14" s="668" t="n"/>
+      <c r="G14" s="668" t="n"/>
+      <c r="H14" s="668" t="n"/>
+      <c r="I14" s="348" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="J14" s="668" t="n"/>
+      <c r="K14" s="668" t="n"/>
+      <c r="L14" s="668" t="n"/>
+      <c r="M14" s="668" t="n"/>
+      <c r="N14" s="668" t="n"/>
+      <c r="O14" s="668" t="n"/>
+      <c r="P14" s="668" t="n"/>
+      <c r="Q14" s="668" t="n"/>
+      <c r="R14" s="668" t="n"/>
+      <c r="S14" s="668" t="n"/>
+      <c r="T14" s="668" t="n"/>
+      <c r="U14" s="668" t="n"/>
+      <c r="V14" s="668" t="n"/>
+      <c r="W14" s="668" t="n"/>
+      <c r="X14" s="668" t="n"/>
+      <c r="Y14" s="668" t="n"/>
+      <c r="Z14" s="668" t="n"/>
+      <c r="AA14" s="668" t="n"/>
+      <c r="AB14" s="668" t="n"/>
+      <c r="AC14" s="668" t="n"/>
+      <c r="AD14" s="668" t="n"/>
+      <c r="AE14" s="668" t="n"/>
+      <c r="AF14" s="668" t="n"/>
+      <c r="AG14" s="668" t="n"/>
+      <c r="AH14" s="668" t="n"/>
+      <c r="AI14" s="668" t="n"/>
+      <c r="AJ14" s="668" t="n"/>
+      <c r="AK14" s="668" t="n"/>
+      <c r="AL14" s="668" t="n"/>
+      <c r="AM14" s="668" t="n"/>
+      <c r="AN14" s="668" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B15" s="532" t="n"/>
-      <c r="C15" s="533" t="n"/>
-      <c r="D15" s="533" t="n"/>
-      <c r="E15" s="533" t="n"/>
-      <c r="F15" s="533" t="n"/>
-      <c r="G15" s="533" t="n"/>
-      <c r="H15" s="533" t="n"/>
-      <c r="I15" s="356" t="n"/>
-      <c r="J15" s="356" t="n"/>
-      <c r="K15" s="356" t="n"/>
-      <c r="L15" s="356" t="n"/>
-      <c r="M15" s="356" t="n"/>
-      <c r="N15" s="356" t="n"/>
-      <c r="O15" s="356" t="n"/>
-      <c r="P15" s="356" t="n"/>
-      <c r="Q15" s="356" t="n"/>
-      <c r="R15" s="356" t="n"/>
-      <c r="S15" s="356" t="n"/>
-      <c r="T15" s="356" t="n"/>
-      <c r="U15" s="356" t="n"/>
-      <c r="V15" s="356" t="n"/>
-      <c r="W15" s="356" t="n"/>
-      <c r="X15" s="356" t="n"/>
-      <c r="Y15" s="356" t="n"/>
-      <c r="Z15" s="356" t="n"/>
-      <c r="AA15" s="356" t="n"/>
-      <c r="AB15" s="356" t="n"/>
-      <c r="AC15" s="356" t="n"/>
-      <c r="AD15" s="356" t="n"/>
-      <c r="AE15" s="356" t="n"/>
-      <c r="AF15" s="356" t="n"/>
-      <c r="AG15" s="356" t="n"/>
-      <c r="AH15" s="356" t="n"/>
-      <c r="AI15" s="356" t="n"/>
-      <c r="AJ15" s="356" t="n"/>
-      <c r="AK15" s="356" t="n"/>
-      <c r="AL15" s="356" t="n"/>
-      <c r="AM15" s="356" t="n"/>
-      <c r="AN15" s="534" t="n"/>
+    <row r="15">
+      <c r="A15" s="668" t="n"/>
+      <c r="B15" s="668" t="n"/>
+      <c r="C15" s="348" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D15" s="668" t="n"/>
+      <c r="E15" s="668" t="n"/>
+      <c r="F15" s="668" t="n"/>
+      <c r="G15" s="668" t="n"/>
+      <c r="H15" s="668" t="n"/>
+      <c r="I15" s="348" t="inlineStr">
+        <is>
+          <t>CAL STATUS ISSUE</t>
+        </is>
+      </c>
+      <c r="J15" s="668" t="n"/>
+      <c r="K15" s="668" t="n"/>
+      <c r="L15" s="668" t="n"/>
+      <c r="M15" s="668" t="n"/>
+      <c r="N15" s="668" t="n"/>
+      <c r="O15" s="668" t="n"/>
+      <c r="P15" s="668" t="n"/>
+      <c r="Q15" s="668" t="n"/>
+      <c r="R15" s="668" t="n"/>
+      <c r="S15" s="668" t="n"/>
+      <c r="T15" s="668" t="n"/>
+      <c r="U15" s="668" t="n"/>
+      <c r="V15" s="668" t="n"/>
+      <c r="W15" s="668" t="n"/>
+      <c r="X15" s="668" t="n"/>
+      <c r="Y15" s="668" t="n"/>
+      <c r="Z15" s="668" t="n"/>
+      <c r="AA15" s="668" t="n"/>
+      <c r="AB15" s="668" t="n"/>
+      <c r="AC15" s="668" t="n"/>
+      <c r="AD15" s="668" t="n"/>
+      <c r="AE15" s="668" t="n"/>
+      <c r="AF15" s="668" t="n"/>
+      <c r="AG15" s="668" t="n"/>
+      <c r="AH15" s="668" t="n"/>
+      <c r="AI15" s="668" t="n"/>
+      <c r="AJ15" s="668" t="n"/>
+      <c r="AK15" s="668" t="n"/>
+      <c r="AL15" s="668" t="n"/>
+      <c r="AM15" s="668" t="n"/>
+      <c r="AN15" s="668" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B16" s="532" t="n"/>
-      <c r="C16" s="533" t="n"/>
-      <c r="D16" s="533" t="n"/>
-      <c r="E16" s="533" t="n"/>
-      <c r="F16" s="533" t="n"/>
-      <c r="G16" s="533" t="n"/>
-      <c r="H16" s="533" t="n"/>
-      <c r="I16" s="356" t="n"/>
-      <c r="J16" s="356" t="n"/>
-      <c r="K16" s="356" t="n"/>
-      <c r="L16" s="356" t="n"/>
-      <c r="M16" s="356" t="n"/>
-      <c r="N16" s="356" t="n"/>
-      <c r="O16" s="356" t="n"/>
-      <c r="P16" s="356" t="n"/>
-      <c r="Q16" s="356" t="n"/>
-      <c r="R16" s="356" t="n"/>
-      <c r="S16" s="356" t="n"/>
-      <c r="T16" s="356" t="n"/>
-      <c r="U16" s="356" t="n"/>
-      <c r="V16" s="356" t="n"/>
-      <c r="W16" s="356" t="n"/>
-      <c r="X16" s="356" t="n"/>
-      <c r="Y16" s="356" t="n"/>
-      <c r="Z16" s="356" t="n"/>
-      <c r="AA16" s="356" t="n"/>
-      <c r="AB16" s="356" t="n"/>
-      <c r="AC16" s="356" t="n"/>
-      <c r="AD16" s="356" t="n"/>
-      <c r="AE16" s="356" t="n"/>
-      <c r="AF16" s="356" t="n"/>
-      <c r="AG16" s="356" t="n"/>
-      <c r="AH16" s="356" t="n"/>
-      <c r="AI16" s="356" t="n"/>
-      <c r="AJ16" s="356" t="n"/>
-      <c r="AK16" s="356" t="n"/>
-      <c r="AL16" s="356" t="n"/>
-      <c r="AM16" s="356" t="n"/>
-      <c r="AN16" s="534" t="n"/>
+    <row r="16">
+      <c r="A16" s="668" t="n"/>
+      <c r="B16" s="668" t="n"/>
+      <c r="C16" s="348" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D16" s="668" t="n"/>
+      <c r="E16" s="668" t="n"/>
+      <c r="F16" s="668" t="n"/>
+      <c r="G16" s="668" t="n"/>
+      <c r="H16" s="668" t="n"/>
+      <c r="I16" s="348" t="inlineStr">
+        <is>
+          <t>CLEANLINESS RISK</t>
+        </is>
+      </c>
+      <c r="J16" s="668" t="n"/>
+      <c r="K16" s="668" t="n"/>
+      <c r="L16" s="668" t="n"/>
+      <c r="M16" s="668" t="n"/>
+      <c r="N16" s="668" t="n"/>
+      <c r="O16" s="668" t="n"/>
+      <c r="P16" s="668" t="n"/>
+      <c r="Q16" s="668" t="n"/>
+      <c r="R16" s="668" t="n"/>
+      <c r="S16" s="668" t="n"/>
+      <c r="T16" s="668" t="n"/>
+      <c r="U16" s="668" t="n"/>
+      <c r="V16" s="668" t="n"/>
+      <c r="W16" s="668" t="n"/>
+      <c r="X16" s="668" t="n"/>
+      <c r="Y16" s="668" t="n"/>
+      <c r="Z16" s="668" t="n"/>
+      <c r="AA16" s="668" t="n"/>
+      <c r="AB16" s="668" t="n"/>
+      <c r="AC16" s="668" t="n"/>
+      <c r="AD16" s="668" t="n"/>
+      <c r="AE16" s="668" t="n"/>
+      <c r="AF16" s="668" t="n"/>
+      <c r="AG16" s="668" t="n"/>
+      <c r="AH16" s="668" t="n"/>
+      <c r="AI16" s="668" t="n"/>
+      <c r="AJ16" s="668" t="n"/>
+      <c r="AK16" s="668" t="n"/>
+      <c r="AL16" s="668" t="n"/>
+      <c r="AM16" s="668" t="n"/>
+      <c r="AN16" s="668" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B17" s="532" t="n"/>
-      <c r="C17" s="533" t="n"/>
-      <c r="D17" s="533" t="n"/>
-      <c r="E17" s="533" t="n"/>
-      <c r="F17" s="533" t="n"/>
-      <c r="G17" s="533" t="n"/>
-      <c r="H17" s="533" t="n"/>
-      <c r="I17" s="356" t="n"/>
-      <c r="J17" s="356" t="n"/>
-      <c r="K17" s="356" t="n"/>
-      <c r="L17" s="356" t="n"/>
-      <c r="M17" s="356" t="n"/>
-      <c r="N17" s="356" t="n"/>
-      <c r="O17" s="356" t="n"/>
-      <c r="P17" s="356" t="n"/>
-      <c r="Q17" s="356" t="n"/>
-      <c r="R17" s="356" t="n"/>
-      <c r="S17" s="356" t="n"/>
-      <c r="T17" s="356" t="n"/>
-      <c r="U17" s="356" t="n"/>
-      <c r="V17" s="356" t="n"/>
-      <c r="W17" s="356" t="n"/>
-      <c r="X17" s="356" t="n"/>
-      <c r="Y17" s="356" t="n"/>
-      <c r="Z17" s="356" t="n"/>
-      <c r="AA17" s="356" t="n"/>
-      <c r="AB17" s="356" t="n"/>
-      <c r="AC17" s="356" t="n"/>
-      <c r="AD17" s="356" t="n"/>
-      <c r="AE17" s="356" t="n"/>
-      <c r="AF17" s="356" t="n"/>
-      <c r="AG17" s="356" t="n"/>
-      <c r="AH17" s="356" t="n"/>
-      <c r="AI17" s="356" t="n"/>
-      <c r="AJ17" s="356" t="n"/>
-      <c r="AK17" s="356" t="n"/>
-      <c r="AL17" s="356" t="n"/>
-      <c r="AM17" s="356" t="n"/>
-      <c r="AN17" s="534" t="n"/>
+    <row r="17">
+      <c r="A17" s="668" t="n"/>
+      <c r="B17" s="668" t="n"/>
+      <c r="C17" s="348" t="inlineStr">
+        <is>
+          <t>MGT</t>
+        </is>
+      </c>
+      <c r="D17" s="668" t="n"/>
+      <c r="E17" s="668" t="n"/>
+      <c r="F17" s="668" t="n"/>
+      <c r="G17" s="668" t="n"/>
+      <c r="H17" s="668" t="n"/>
+      <c r="I17" s="348" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="J17" s="668" t="n"/>
+      <c r="K17" s="668" t="n"/>
+      <c r="L17" s="668" t="n"/>
+      <c r="M17" s="668" t="n"/>
+      <c r="N17" s="668" t="n"/>
+      <c r="O17" s="668" t="n"/>
+      <c r="P17" s="668" t="n"/>
+      <c r="Q17" s="668" t="n"/>
+      <c r="R17" s="668" t="n"/>
+      <c r="S17" s="668" t="n"/>
+      <c r="T17" s="668" t="n"/>
+      <c r="U17" s="668" t="n"/>
+      <c r="V17" s="668" t="n"/>
+      <c r="W17" s="668" t="n"/>
+      <c r="X17" s="668" t="n"/>
+      <c r="Y17" s="668" t="n"/>
+      <c r="Z17" s="668" t="n"/>
+      <c r="AA17" s="668" t="n"/>
+      <c r="AB17" s="668" t="n"/>
+      <c r="AC17" s="668" t="n"/>
+      <c r="AD17" s="668" t="n"/>
+      <c r="AE17" s="668" t="n"/>
+      <c r="AF17" s="668" t="n"/>
+      <c r="AG17" s="668" t="n"/>
+      <c r="AH17" s="668" t="n"/>
+      <c r="AI17" s="668" t="n"/>
+      <c r="AJ17" s="668" t="n"/>
+      <c r="AK17" s="668" t="n"/>
+      <c r="AL17" s="668" t="n"/>
+      <c r="AM17" s="668" t="n"/>
+      <c r="AN17" s="668" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="531">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B18" s="532" t="n"/>
-      <c r="C18" s="533" t="n"/>
-      <c r="D18" s="533" t="n"/>
-      <c r="E18" s="533" t="n"/>
-      <c r="F18" s="533" t="n"/>
-      <c r="G18" s="533" t="n"/>
-      <c r="H18" s="533" t="n"/>
-      <c r="I18" s="356" t="n"/>
-      <c r="J18" s="356" t="n"/>
-      <c r="K18" s="356" t="n"/>
-      <c r="L18" s="356" t="n"/>
-      <c r="M18" s="356" t="n"/>
-      <c r="N18" s="356" t="n"/>
-      <c r="O18" s="356" t="n"/>
-      <c r="P18" s="356" t="n"/>
-      <c r="Q18" s="356" t="n"/>
-      <c r="R18" s="356" t="n"/>
-      <c r="S18" s="356" t="n"/>
-      <c r="T18" s="356" t="n"/>
-      <c r="U18" s="356" t="n"/>
-      <c r="V18" s="356" t="n"/>
-      <c r="W18" s="356" t="n"/>
-      <c r="X18" s="356" t="n"/>
-      <c r="Y18" s="356" t="n"/>
-      <c r="Z18" s="356" t="n"/>
-      <c r="AA18" s="356" t="n"/>
-      <c r="AB18" s="356" t="n"/>
-      <c r="AC18" s="356" t="n"/>
-      <c r="AD18" s="356" t="n"/>
-      <c r="AE18" s="356" t="n"/>
-      <c r="AF18" s="356" t="n"/>
-      <c r="AG18" s="356" t="n"/>
-      <c r="AH18" s="356" t="n"/>
-      <c r="AI18" s="356" t="n"/>
-      <c r="AJ18" s="356" t="n"/>
-      <c r="AK18" s="356" t="n"/>
-      <c r="AL18" s="356" t="n"/>
-      <c r="AM18" s="356" t="n"/>
-      <c r="AN18" s="534" t="n"/>
+    <row r="18">
+      <c r="A18" s="668" t="n"/>
+      <c r="B18" s="668" t="n"/>
+      <c r="C18" s="668" t="n"/>
+      <c r="D18" s="668" t="n"/>
+      <c r="E18" s="668" t="n"/>
+      <c r="F18" s="668" t="n"/>
+      <c r="G18" s="668" t="n"/>
+      <c r="H18" s="668" t="n"/>
+      <c r="I18" s="668" t="n"/>
+      <c r="J18" s="668" t="n"/>
+      <c r="K18" s="668" t="n"/>
+      <c r="L18" s="668" t="n"/>
+      <c r="M18" s="668" t="n"/>
+      <c r="N18" s="668" t="n"/>
+      <c r="O18" s="668" t="n"/>
+      <c r="P18" s="668" t="n"/>
+      <c r="Q18" s="668" t="n"/>
+      <c r="R18" s="668" t="n"/>
+      <c r="S18" s="668" t="n"/>
+      <c r="T18" s="668" t="n"/>
+      <c r="U18" s="668" t="n"/>
+      <c r="V18" s="668" t="n"/>
+      <c r="W18" s="668" t="n"/>
+      <c r="X18" s="668" t="n"/>
+      <c r="Y18" s="668" t="n"/>
+      <c r="Z18" s="668" t="n"/>
+      <c r="AA18" s="668" t="n"/>
+      <c r="AB18" s="668" t="n"/>
+      <c r="AC18" s="668" t="n"/>
+      <c r="AD18" s="668" t="n"/>
+      <c r="AE18" s="668" t="n"/>
+      <c r="AF18" s="668" t="n"/>
+      <c r="AG18" s="668" t="n"/>
+      <c r="AH18" s="668" t="n"/>
+      <c r="AI18" s="668" t="n"/>
+      <c r="AJ18" s="668" t="n"/>
+      <c r="AK18" s="668" t="n"/>
+      <c r="AL18" s="668" t="n"/>
+      <c r="AM18" s="668" t="n"/>
+      <c r="AN18" s="668" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="535">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B19" s="536" t="n"/>
-      <c r="C19" s="537" t="n"/>
-      <c r="D19" s="537" t="n"/>
-      <c r="E19" s="537" t="n"/>
-      <c r="F19" s="537" t="n"/>
-      <c r="G19" s="537" t="n"/>
-      <c r="H19" s="537" t="n"/>
-      <c r="I19" s="538" t="n"/>
-      <c r="J19" s="538" t="n"/>
-      <c r="K19" s="538" t="n"/>
-      <c r="L19" s="538" t="n"/>
-      <c r="M19" s="538" t="n"/>
-      <c r="N19" s="538" t="n"/>
-      <c r="O19" s="538" t="n"/>
-      <c r="P19" s="538" t="n"/>
-      <c r="Q19" s="538" t="n"/>
-      <c r="R19" s="538" t="n"/>
-      <c r="S19" s="538" t="n"/>
-      <c r="T19" s="538" t="n"/>
-      <c r="U19" s="538" t="n"/>
-      <c r="V19" s="538" t="n"/>
-      <c r="W19" s="538" t="n"/>
-      <c r="X19" s="538" t="n"/>
-      <c r="Y19" s="538" t="n"/>
-      <c r="Z19" s="538" t="n"/>
-      <c r="AA19" s="538" t="n"/>
-      <c r="AB19" s="538" t="n"/>
-      <c r="AC19" s="538" t="n"/>
-      <c r="AD19" s="538" t="n"/>
-      <c r="AE19" s="538" t="n"/>
-      <c r="AF19" s="538" t="n"/>
-      <c r="AG19" s="538" t="n"/>
-      <c r="AH19" s="538" t="n"/>
-      <c r="AI19" s="538" t="n"/>
-      <c r="AJ19" s="538" t="n"/>
-      <c r="AK19" s="538" t="n"/>
-      <c r="AL19" s="538" t="n"/>
-      <c r="AM19" s="538" t="n"/>
-      <c r="AN19" s="539" t="n"/>
+    <row r="19">
+      <c r="A19" s="668" t="n"/>
+      <c r="B19" s="668" t="n"/>
+      <c r="C19" s="668" t="n"/>
+      <c r="D19" s="668" t="n"/>
+      <c r="E19" s="668" t="n"/>
+      <c r="F19" s="668" t="n"/>
+      <c r="G19" s="668" t="n"/>
+      <c r="H19" s="668" t="n"/>
+      <c r="I19" s="668" t="n"/>
+      <c r="J19" s="668" t="n"/>
+      <c r="K19" s="668" t="n"/>
+      <c r="L19" s="668" t="n"/>
+      <c r="M19" s="668" t="n"/>
+      <c r="N19" s="668" t="n"/>
+      <c r="O19" s="668" t="n"/>
+      <c r="P19" s="668" t="n"/>
+      <c r="Q19" s="668" t="n"/>
+      <c r="R19" s="668" t="n"/>
+      <c r="S19" s="668" t="n"/>
+      <c r="T19" s="668" t="n"/>
+      <c r="U19" s="668" t="n"/>
+      <c r="V19" s="668" t="n"/>
+      <c r="W19" s="668" t="n"/>
+      <c r="X19" s="668" t="n"/>
+      <c r="Y19" s="668" t="n"/>
+      <c r="Z19" s="668" t="n"/>
+      <c r="AA19" s="668" t="n"/>
+      <c r="AB19" s="668" t="n"/>
+      <c r="AC19" s="668" t="n"/>
+      <c r="AD19" s="668" t="n"/>
+      <c r="AE19" s="668" t="n"/>
+      <c r="AF19" s="668" t="n"/>
+      <c r="AG19" s="668" t="n"/>
+      <c r="AH19" s="668" t="n"/>
+      <c r="AI19" s="668" t="n"/>
+      <c r="AJ19" s="668" t="n"/>
+      <c r="AK19" s="668" t="n"/>
+      <c r="AL19" s="668" t="n"/>
+      <c r="AM19" s="668" t="n"/>
+      <c r="AN19" s="668" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="668" t="n"/>
+      <c r="B20" s="668" t="n"/>
+      <c r="C20" s="668" t="n"/>
+      <c r="D20" s="668" t="n"/>
+      <c r="E20" s="668" t="n"/>
+      <c r="F20" s="668" t="n"/>
+      <c r="G20" s="668" t="n"/>
+      <c r="H20" s="668" t="n"/>
+      <c r="I20" s="668" t="n"/>
+      <c r="J20" s="668" t="n"/>
+      <c r="K20" s="668" t="n"/>
+      <c r="L20" s="668" t="n"/>
+      <c r="M20" s="668" t="n"/>
+      <c r="N20" s="668" t="n"/>
+      <c r="O20" s="668" t="n"/>
+      <c r="P20" s="668" t="n"/>
+      <c r="Q20" s="668" t="n"/>
+      <c r="R20" s="668" t="n"/>
+      <c r="S20" s="668" t="n"/>
+      <c r="T20" s="668" t="n"/>
+      <c r="U20" s="668" t="n"/>
+      <c r="V20" s="668" t="n"/>
+      <c r="W20" s="668" t="n"/>
+      <c r="X20" s="668" t="n"/>
+      <c r="Y20" s="668" t="n"/>
+      <c r="Z20" s="668" t="n"/>
+      <c r="AA20" s="668" t="n"/>
+      <c r="AB20" s="668" t="n"/>
+      <c r="AC20" s="668" t="n"/>
+      <c r="AD20" s="668" t="n"/>
+      <c r="AE20" s="668" t="n"/>
+      <c r="AF20" s="668" t="n"/>
+      <c r="AG20" s="668" t="n"/>
+      <c r="AH20" s="668" t="n"/>
+      <c r="AI20" s="668" t="n"/>
+      <c r="AJ20" s="668" t="n"/>
+      <c r="AK20" s="668" t="n"/>
+      <c r="AL20" s="668" t="n"/>
+      <c r="AM20" s="668" t="n"/>
+      <c r="AN20" s="668" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E5:E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
-      <formula1>'LISTS'!$A$2:$A$5</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11344,805 +11223,1350 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="512" t="inlineStr">
-        <is>
-          <t>Upstream References / Import Guidance</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="709" t="n"/>
       <c r="B1" s="603" t="n"/>
       <c r="C1" s="603" t="n"/>
       <c r="D1" s="603" t="n"/>
       <c r="E1" s="603" t="n"/>
       <c r="F1" s="603" t="n"/>
       <c r="G1" s="603" t="n"/>
-      <c r="H1" s="513" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="431" t="n"/>
-      <c r="K1" s="431" t="n"/>
-      <c r="L1" s="431" t="n"/>
-      <c r="M1" s="431" t="n"/>
-      <c r="N1" s="431" t="n"/>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="431" t="n"/>
-      <c r="Q1" s="431" t="n"/>
-      <c r="R1" s="431" t="n"/>
-      <c r="S1" s="431" t="n"/>
-      <c r="T1" s="431" t="n"/>
-      <c r="U1" s="431" t="n"/>
-      <c r="V1" s="431" t="n"/>
-      <c r="W1" s="431" t="n"/>
-      <c r="X1" s="431" t="n"/>
-      <c r="Y1" s="431" t="n"/>
-      <c r="Z1" s="431" t="n"/>
-      <c r="AA1" s="431" t="n"/>
-      <c r="AB1" s="431" t="n"/>
-      <c r="AC1" s="431" t="n"/>
-      <c r="AD1" s="432" t="n"/>
-      <c r="AE1" s="433" t="n"/>
-      <c r="AF1" s="434" t="n"/>
-      <c r="AG1" s="434" t="n"/>
-      <c r="AH1" s="435" t="n"/>
-      <c r="AI1" s="436" t="n"/>
-      <c r="AJ1" s="437" t="n"/>
-      <c r="AK1" s="437" t="n"/>
-      <c r="AL1" s="437" t="n"/>
-      <c r="AM1" s="437" t="n"/>
-      <c r="AN1" s="438" t="n"/>
+      <c r="H1" s="710" t="n"/>
+      <c r="I1" s="711" t="inlineStr">
+        <is>
+          <t>AQL Inspection Record</t>
+        </is>
+      </c>
+      <c r="J1" s="603" t="n"/>
+      <c r="K1" s="603" t="n"/>
+      <c r="L1" s="603" t="n"/>
+      <c r="M1" s="603" t="n"/>
+      <c r="N1" s="603" t="n"/>
+      <c r="O1" s="603" t="n"/>
+      <c r="P1" s="603" t="n"/>
+      <c r="Q1" s="603" t="n"/>
+      <c r="R1" s="603" t="n"/>
+      <c r="S1" s="603" t="n"/>
+      <c r="T1" s="603" t="n"/>
+      <c r="U1" s="603" t="n"/>
+      <c r="V1" s="603" t="n"/>
+      <c r="W1" s="603" t="n"/>
+      <c r="X1" s="603" t="n"/>
+      <c r="Y1" s="603" t="n"/>
+      <c r="Z1" s="603" t="n"/>
+      <c r="AA1" s="603" t="n"/>
+      <c r="AB1" s="603" t="n"/>
+      <c r="AC1" s="603" t="n"/>
+      <c r="AD1" s="710" t="n"/>
+      <c r="AE1" s="435" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="603" t="n"/>
+      <c r="AG1" s="603" t="n"/>
+      <c r="AH1" s="712" t="n"/>
+      <c r="AI1" s="438" t="inlineStr">
+        <is>
+          <t>FRM-621</t>
+        </is>
+      </c>
+      <c r="AJ1" s="603" t="n"/>
+      <c r="AK1" s="603" t="n"/>
+      <c r="AL1" s="603" t="n"/>
+      <c r="AM1" s="603" t="n"/>
+      <c r="AN1" s="710" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="514" t="inlineStr">
-        <is>
-          <t>Reference plan / lot / method / release documents from their owning source.</t>
-        </is>
-      </c>
-      <c r="H2" s="515" t="n"/>
-      <c r="I2" s="441" t="n"/>
-      <c r="J2" s="442" t="n"/>
-      <c r="K2" s="442" t="n"/>
-      <c r="L2" s="442" t="n"/>
-      <c r="M2" s="442" t="n"/>
-      <c r="N2" s="442" t="n"/>
-      <c r="O2" s="442" t="n"/>
-      <c r="P2" s="442" t="n"/>
-      <c r="Q2" s="442" t="n"/>
-      <c r="R2" s="442" t="n"/>
-      <c r="S2" s="442" t="n"/>
-      <c r="T2" s="442" t="n"/>
-      <c r="U2" s="442" t="n"/>
-      <c r="V2" s="442" t="n"/>
-      <c r="W2" s="442" t="n"/>
-      <c r="X2" s="442" t="n"/>
-      <c r="Y2" s="442" t="n"/>
-      <c r="Z2" s="442" t="n"/>
-      <c r="AA2" s="442" t="n"/>
-      <c r="AB2" s="442" t="n"/>
-      <c r="AC2" s="442" t="n"/>
-      <c r="AD2" s="443" t="n"/>
-      <c r="AE2" s="444" t="n"/>
-      <c r="AF2" s="445" t="n"/>
-      <c r="AG2" s="445" t="n"/>
-      <c r="AH2" s="446" t="n"/>
-      <c r="AI2" s="447" t="n"/>
-      <c r="AJ2" s="448" t="n"/>
-      <c r="AK2" s="448" t="n"/>
-      <c r="AL2" s="448" t="n"/>
-      <c r="AM2" s="448" t="n"/>
-      <c r="AN2" s="449" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="682" t="n"/>
+      <c r="C2" s="682" t="n"/>
+      <c r="D2" s="682" t="n"/>
+      <c r="E2" s="682" t="n"/>
+      <c r="F2" s="682" t="n"/>
+      <c r="G2" s="682" t="n"/>
+      <c r="H2" s="683" t="n"/>
+      <c r="I2" s="682" t="n"/>
+      <c r="J2" s="682" t="n"/>
+      <c r="K2" s="682" t="n"/>
+      <c r="L2" s="682" t="n"/>
+      <c r="M2" s="682" t="n"/>
+      <c r="N2" s="682" t="n"/>
+      <c r="O2" s="682" t="n"/>
+      <c r="P2" s="682" t="n"/>
+      <c r="Q2" s="682" t="n"/>
+      <c r="R2" s="682" t="n"/>
+      <c r="S2" s="682" t="n"/>
+      <c r="T2" s="682" t="n"/>
+      <c r="U2" s="682" t="n"/>
+      <c r="V2" s="682" t="n"/>
+      <c r="W2" s="682" t="n"/>
+      <c r="X2" s="682" t="n"/>
+      <c r="Y2" s="682" t="n"/>
+      <c r="Z2" s="682" t="n"/>
+      <c r="AA2" s="682" t="n"/>
+      <c r="AB2" s="682" t="n"/>
+      <c r="AC2" s="682" t="n"/>
+      <c r="AD2" s="683" t="n"/>
+      <c r="AE2" s="684" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="685" t="n"/>
+      <c r="AG2" s="685" t="n"/>
+      <c r="AH2" s="686" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="687" t="n"/>
+      <c r="AK2" s="687" t="n"/>
+      <c r="AL2" s="687" t="n"/>
+      <c r="AM2" s="687" t="n"/>
+      <c r="AN2" s="688" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="516" t="n"/>
-      <c r="B3" s="517" t="n"/>
-      <c r="C3" s="517" t="n"/>
-      <c r="D3" s="517" t="n"/>
-      <c r="E3" s="517" t="n"/>
-      <c r="F3" s="517" t="n"/>
-      <c r="G3" s="517" t="n"/>
-      <c r="H3" s="515" t="n"/>
-      <c r="I3" s="441" t="n"/>
-      <c r="J3" s="442" t="n"/>
-      <c r="K3" s="442" t="n"/>
-      <c r="L3" s="442" t="n"/>
-      <c r="M3" s="442" t="n"/>
-      <c r="N3" s="442" t="n"/>
-      <c r="O3" s="442" t="n"/>
-      <c r="P3" s="442" t="n"/>
-      <c r="Q3" s="442" t="n"/>
-      <c r="R3" s="442" t="n"/>
-      <c r="S3" s="442" t="n"/>
-      <c r="T3" s="442" t="n"/>
-      <c r="U3" s="442" t="n"/>
-      <c r="V3" s="442" t="n"/>
-      <c r="W3" s="442" t="n"/>
-      <c r="X3" s="442" t="n"/>
-      <c r="Y3" s="442" t="n"/>
-      <c r="Z3" s="442" t="n"/>
-      <c r="AA3" s="442" t="n"/>
-      <c r="AB3" s="442" t="n"/>
-      <c r="AC3" s="442" t="n"/>
-      <c r="AD3" s="443" t="n"/>
-      <c r="AE3" s="444" t="n"/>
-      <c r="AF3" s="445" t="n"/>
-      <c r="AG3" s="445" t="n"/>
-      <c r="AH3" s="446" t="n"/>
-      <c r="AI3" s="447" t="n"/>
-      <c r="AJ3" s="448" t="n"/>
-      <c r="AK3" s="448" t="n"/>
-      <c r="AL3" s="448" t="n"/>
-      <c r="AM3" s="448" t="n"/>
-      <c r="AN3" s="449" t="n"/>
+      <c r="A3" s="689" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="690" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="690" t="n"/>
+      <c r="AE3" s="691" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="692" t="n"/>
+      <c r="AG3" s="692" t="n"/>
+      <c r="AH3" s="693" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="694" t="n"/>
+      <c r="AK3" s="694" t="n"/>
+      <c r="AL3" s="694" t="n"/>
+      <c r="AM3" s="694" t="n"/>
+      <c r="AN3" s="695" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="518" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="519" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="519" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="517" t="n"/>
-      <c r="E4" s="517" t="n"/>
-      <c r="F4" s="517" t="n"/>
-      <c r="G4" s="517" t="n"/>
-      <c r="H4" s="515" t="n"/>
-      <c r="I4" s="450" t="n"/>
-      <c r="J4" s="451" t="n"/>
-      <c r="K4" s="451" t="n"/>
-      <c r="L4" s="451" t="n"/>
-      <c r="M4" s="451" t="n"/>
-      <c r="N4" s="451" t="n"/>
-      <c r="O4" s="451" t="n"/>
-      <c r="P4" s="451" t="n"/>
-      <c r="Q4" s="451" t="n"/>
-      <c r="R4" s="451" t="n"/>
-      <c r="S4" s="451" t="n"/>
-      <c r="T4" s="451" t="n"/>
-      <c r="U4" s="451" t="n"/>
-      <c r="V4" s="451" t="n"/>
-      <c r="W4" s="451" t="n"/>
-      <c r="X4" s="451" t="n"/>
-      <c r="Y4" s="451" t="n"/>
-      <c r="Z4" s="451" t="n"/>
-      <c r="AA4" s="451" t="n"/>
-      <c r="AB4" s="451" t="n"/>
-      <c r="AC4" s="451" t="n"/>
-      <c r="AD4" s="452" t="n"/>
-      <c r="AE4" s="444" t="n"/>
-      <c r="AF4" s="445" t="n"/>
-      <c r="AG4" s="445" t="n"/>
-      <c r="AH4" s="446" t="n"/>
-      <c r="AI4" s="447" t="n"/>
-      <c r="AJ4" s="448" t="n"/>
-      <c r="AK4" s="448" t="n"/>
-      <c r="AL4" s="448" t="n"/>
-      <c r="AM4" s="448" t="n"/>
-      <c r="AN4" s="449" t="n"/>
+      <c r="A4" s="689" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="690" t="n"/>
+      <c r="I4" s="696" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="690" t="n"/>
+      <c r="AE4" s="691" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="692" t="n"/>
+      <c r="AG4" s="692" t="n"/>
+      <c r="AH4" s="693" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="694" t="n"/>
+      <c r="AK4" s="694" t="n"/>
+      <c r="AL4" s="694" t="n"/>
+      <c r="AM4" s="694" t="n"/>
+      <c r="AN4" s="695" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="521" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="522" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="522" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="540" t="n"/>
-      <c r="E5" s="540" t="n"/>
-      <c r="F5" s="540" t="n"/>
-      <c r="G5" s="540" t="n"/>
-      <c r="H5" s="541" t="n"/>
-      <c r="I5" s="456" t="n"/>
-      <c r="J5" s="457" t="n"/>
-      <c r="K5" s="457" t="n"/>
-      <c r="L5" s="457" t="n"/>
-      <c r="M5" s="457" t="n"/>
-      <c r="N5" s="457" t="n"/>
-      <c r="O5" s="457" t="n"/>
-      <c r="P5" s="457" t="n"/>
-      <c r="Q5" s="457" t="n"/>
-      <c r="R5" s="457" t="n"/>
-      <c r="S5" s="457" t="n"/>
-      <c r="T5" s="457" t="n"/>
-      <c r="U5" s="457" t="n"/>
-      <c r="V5" s="457" t="n"/>
-      <c r="W5" s="457" t="n"/>
-      <c r="X5" s="457" t="n"/>
-      <c r="Y5" s="457" t="n"/>
-      <c r="Z5" s="457" t="n"/>
-      <c r="AA5" s="457" t="n"/>
-      <c r="AB5" s="457" t="n"/>
-      <c r="AC5" s="457" t="n"/>
-      <c r="AD5" s="458" t="n"/>
-      <c r="AE5" s="459" t="n"/>
-      <c r="AF5" s="460" t="n"/>
-      <c r="AG5" s="460" t="n"/>
-      <c r="AH5" s="461" t="n"/>
-      <c r="AI5" s="462" t="n"/>
-      <c r="AJ5" s="463" t="n"/>
-      <c r="AK5" s="463" t="n"/>
-      <c r="AL5" s="463" t="n"/>
-      <c r="AM5" s="463" t="n"/>
-      <c r="AN5" s="464" t="n"/>
+      <c r="A5" s="689" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="690" t="n"/>
+      <c r="I5" s="697" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="690" t="n"/>
+      <c r="AE5" s="691" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="692" t="n"/>
+      <c r="AG5" s="692" t="n"/>
+      <c r="AH5" s="693" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="694" t="n"/>
+      <c r="AK5" s="694" t="n"/>
+      <c r="AL5" s="694" t="n"/>
+      <c r="AM5" s="694" t="n"/>
+      <c r="AN5" s="695" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="524" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="525" t="inlineStr">
-        <is>
-          <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
-        </is>
-      </c>
-      <c r="C6" s="526" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="470" t="n"/>
-      <c r="E6" s="470" t="n"/>
-      <c r="F6" s="470" t="n"/>
-      <c r="G6" s="470" t="n"/>
-      <c r="H6" s="470" t="n"/>
-      <c r="I6" s="470" t="n"/>
-      <c r="J6" s="470" t="n"/>
-      <c r="K6" s="470" t="n"/>
-      <c r="L6" s="470" t="n"/>
-      <c r="M6" s="470" t="n"/>
-      <c r="N6" s="470" t="n"/>
-      <c r="O6" s="470" t="n"/>
-      <c r="P6" s="470" t="n"/>
-      <c r="Q6" s="470" t="n"/>
-      <c r="R6" s="470" t="n"/>
-      <c r="S6" s="470" t="n"/>
-      <c r="T6" s="470" t="n"/>
-      <c r="U6" s="470" t="n"/>
-      <c r="V6" s="470" t="n"/>
-      <c r="W6" s="470" t="n"/>
-      <c r="X6" s="470" t="n"/>
-      <c r="Y6" s="470" t="n"/>
-      <c r="Z6" s="470" t="n"/>
-      <c r="AA6" s="470" t="n"/>
-      <c r="AB6" s="470" t="n"/>
-      <c r="AC6" s="470" t="n"/>
-      <c r="AD6" s="470" t="n"/>
-      <c r="AE6" s="470" t="n"/>
-      <c r="AF6" s="470" t="n"/>
-      <c r="AG6" s="470" t="n"/>
-      <c r="AH6" s="470" t="n"/>
-      <c r="AI6" s="470" t="n"/>
-      <c r="AJ6" s="470" t="n"/>
-      <c r="AK6" s="470" t="n"/>
-      <c r="AL6" s="470" t="n"/>
-      <c r="AM6" s="470" t="n"/>
-      <c r="AN6" s="502" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="713" t="n"/>
+      <c r="B6" s="723" t="n"/>
+      <c r="C6" s="723" t="n"/>
+      <c r="D6" s="723" t="n"/>
+      <c r="E6" s="723" t="n"/>
+      <c r="F6" s="723" t="n"/>
+      <c r="G6" s="723" t="n"/>
+      <c r="H6" s="724" t="n"/>
+      <c r="I6" s="714" t="n"/>
+      <c r="J6" s="714" t="n"/>
+      <c r="K6" s="714" t="n"/>
+      <c r="L6" s="714" t="n"/>
+      <c r="M6" s="714" t="n"/>
+      <c r="N6" s="714" t="n"/>
+      <c r="O6" s="714" t="n"/>
+      <c r="P6" s="714" t="n"/>
+      <c r="Q6" s="714" t="n"/>
+      <c r="R6" s="714" t="n"/>
+      <c r="S6" s="714" t="n"/>
+      <c r="T6" s="714" t="n"/>
+      <c r="U6" s="714" t="n"/>
+      <c r="V6" s="714" t="n"/>
+      <c r="W6" s="714" t="n"/>
+      <c r="X6" s="714" t="n"/>
+      <c r="Y6" s="714" t="n"/>
+      <c r="Z6" s="714" t="n"/>
+      <c r="AA6" s="714" t="n"/>
+      <c r="AB6" s="714" t="n"/>
+      <c r="AC6" s="714" t="n"/>
+      <c r="AD6" s="715" t="n"/>
+      <c r="AE6" s="716" t="n"/>
+      <c r="AF6" s="716" t="n"/>
+      <c r="AG6" s="716" t="n"/>
+      <c r="AH6" s="717" t="n"/>
+      <c r="AI6" s="718" t="n"/>
+      <c r="AJ6" s="718" t="n"/>
+      <c r="AK6" s="718" t="n"/>
+      <c r="AL6" s="718" t="n"/>
+      <c r="AM6" s="718" t="n"/>
+      <c r="AN6" s="719" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="527" t="inlineStr">
-        <is>
-          <t>SOP SOP-603</t>
-        </is>
-      </c>
-      <c r="B7" s="528" t="inlineStr">
-        <is>
-          <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="529" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
-        </is>
-      </c>
-      <c r="D7" s="344" t="n"/>
-      <c r="E7" s="344" t="n"/>
-      <c r="F7" s="344" t="n"/>
-      <c r="G7" s="344" t="n"/>
-      <c r="H7" s="344" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="530" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="706" t="n"/>
+      <c r="C7" s="706" t="n"/>
+      <c r="D7" s="706" t="n"/>
+      <c r="E7" s="706" t="n"/>
+      <c r="F7" s="706" t="n"/>
+      <c r="G7" s="706" t="n"/>
+      <c r="H7" s="726" t="n"/>
+      <c r="I7" s="722" t="n"/>
+      <c r="J7" s="722" t="n"/>
+      <c r="K7" s="722" t="n"/>
+      <c r="L7" s="722" t="n"/>
+      <c r="M7" s="722" t="n"/>
+      <c r="N7" s="722" t="n"/>
+      <c r="O7" s="722" t="n"/>
+      <c r="P7" s="722" t="n"/>
+      <c r="Q7" s="722" t="n"/>
+      <c r="R7" s="722" t="n"/>
+      <c r="S7" s="722" t="n"/>
+      <c r="T7" s="722" t="n"/>
+      <c r="U7" s="722" t="n"/>
+      <c r="V7" s="722" t="n"/>
+      <c r="W7" s="722" t="n"/>
+      <c r="X7" s="722" t="n"/>
+      <c r="Y7" s="722" t="n"/>
+      <c r="Z7" s="722" t="n"/>
+      <c r="AA7" s="722" t="n"/>
+      <c r="AB7" s="722" t="n"/>
+      <c r="AC7" s="722" t="n"/>
+      <c r="AD7" s="722" t="n"/>
+      <c r="AE7" s="722" t="n"/>
+      <c r="AF7" s="722" t="n"/>
+      <c r="AG7" s="722" t="n"/>
+      <c r="AH7" s="722" t="n"/>
+      <c r="AI7" s="722" t="n"/>
+      <c r="AJ7" s="722" t="n"/>
+      <c r="AK7" s="722" t="n"/>
+      <c r="AL7" s="722" t="n"/>
+      <c r="AM7" s="722" t="n"/>
+      <c r="AN7" s="722" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="531" t="inlineStr">
-        <is>
-          <t>WI WI-603</t>
-        </is>
-      </c>
-      <c r="B8" s="532" t="inlineStr">
-        <is>
-          <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
-        </is>
-      </c>
-      <c r="C8" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
-        </is>
-      </c>
-      <c r="D8" s="356" t="n"/>
-      <c r="E8" s="356" t="n"/>
-      <c r="F8" s="356" t="n"/>
-      <c r="G8" s="356" t="n"/>
-      <c r="H8" s="356" t="n"/>
-      <c r="I8" s="356" t="n"/>
-      <c r="J8" s="356" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="356" t="n"/>
-      <c r="M8" s="356" t="n"/>
-      <c r="N8" s="356" t="n"/>
-      <c r="O8" s="356" t="n"/>
-      <c r="P8" s="356" t="n"/>
-      <c r="Q8" s="356" t="n"/>
-      <c r="R8" s="356" t="n"/>
-      <c r="S8" s="356" t="n"/>
-      <c r="T8" s="356" t="n"/>
-      <c r="U8" s="356" t="n"/>
-      <c r="V8" s="356" t="n"/>
-      <c r="W8" s="356" t="n"/>
-      <c r="X8" s="356" t="n"/>
-      <c r="Y8" s="356" t="n"/>
-      <c r="Z8" s="356" t="n"/>
-      <c r="AA8" s="356" t="n"/>
-      <c r="AB8" s="356" t="n"/>
-      <c r="AC8" s="356" t="n"/>
-      <c r="AD8" s="356" t="n"/>
-      <c r="AE8" s="356" t="n"/>
-      <c r="AF8" s="356" t="n"/>
-      <c r="AG8" s="356" t="n"/>
-      <c r="AH8" s="356" t="n"/>
-      <c r="AI8" s="356" t="n"/>
-      <c r="AJ8" s="356" t="n"/>
-      <c r="AK8" s="356" t="n"/>
-      <c r="AL8" s="356" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="534" t="n"/>
+      <c r="A8" s="727" t="inlineStr">
+        <is>
+          <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
+        </is>
+      </c>
+      <c r="H8" s="670" t="n"/>
+      <c r="I8" s="668" t="n"/>
+      <c r="J8" s="668" t="n"/>
+      <c r="K8" s="668" t="n"/>
+      <c r="L8" s="668" t="n"/>
+      <c r="M8" s="668" t="n"/>
+      <c r="N8" s="668" t="n"/>
+      <c r="O8" s="668" t="n"/>
+      <c r="P8" s="668" t="n"/>
+      <c r="Q8" s="668" t="n"/>
+      <c r="R8" s="668" t="n"/>
+      <c r="S8" s="668" t="n"/>
+      <c r="T8" s="668" t="n"/>
+      <c r="U8" s="668" t="n"/>
+      <c r="V8" s="668" t="n"/>
+      <c r="W8" s="668" t="n"/>
+      <c r="X8" s="668" t="n"/>
+      <c r="Y8" s="668" t="n"/>
+      <c r="Z8" s="668" t="n"/>
+      <c r="AA8" s="668" t="n"/>
+      <c r="AB8" s="668" t="n"/>
+      <c r="AC8" s="668" t="n"/>
+      <c r="AD8" s="668" t="n"/>
+      <c r="AE8" s="668" t="n"/>
+      <c r="AF8" s="668" t="n"/>
+      <c r="AG8" s="668" t="n"/>
+      <c r="AH8" s="668" t="n"/>
+      <c r="AI8" s="668" t="n"/>
+      <c r="AJ8" s="668" t="n"/>
+      <c r="AK8" s="668" t="n"/>
+      <c r="AL8" s="668" t="n"/>
+      <c r="AM8" s="668" t="n"/>
+      <c r="AN8" s="668" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-001</t>
-        </is>
-      </c>
-      <c r="B9" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
-        </is>
-      </c>
-      <c r="C9" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
-        </is>
-      </c>
-      <c r="D9" s="356" t="n"/>
-      <c r="E9" s="356" t="n"/>
-      <c r="F9" s="356" t="n"/>
-      <c r="G9" s="356" t="n"/>
-      <c r="H9" s="356" t="n"/>
-      <c r="I9" s="356" t="n"/>
-      <c r="J9" s="356" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="356" t="n"/>
-      <c r="M9" s="356" t="n"/>
-      <c r="N9" s="356" t="n"/>
-      <c r="O9" s="356" t="n"/>
-      <c r="P9" s="356" t="n"/>
-      <c r="Q9" s="356" t="n"/>
-      <c r="R9" s="356" t="n"/>
-      <c r="S9" s="356" t="n"/>
-      <c r="T9" s="356" t="n"/>
-      <c r="U9" s="356" t="n"/>
-      <c r="V9" s="356" t="n"/>
-      <c r="W9" s="356" t="n"/>
-      <c r="X9" s="356" t="n"/>
-      <c r="Y9" s="356" t="n"/>
-      <c r="Z9" s="356" t="n"/>
-      <c r="AA9" s="356" t="n"/>
-      <c r="AB9" s="356" t="n"/>
-      <c r="AC9" s="356" t="n"/>
-      <c r="AD9" s="356" t="n"/>
-      <c r="AE9" s="356" t="n"/>
-      <c r="AF9" s="356" t="n"/>
-      <c r="AG9" s="356" t="n"/>
-      <c r="AH9" s="356" t="n"/>
-      <c r="AI9" s="356" t="n"/>
-      <c r="AJ9" s="356" t="n"/>
-      <c r="AK9" s="356" t="n"/>
-      <c r="AL9" s="356" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="534" t="n"/>
+      <c r="A9" s="668" t="n"/>
+      <c r="B9" s="670" t="n"/>
+      <c r="C9" s="670" t="n"/>
+      <c r="D9" s="670" t="n"/>
+      <c r="E9" s="670" t="n"/>
+      <c r="F9" s="670" t="n"/>
+      <c r="G9" s="670" t="n"/>
+      <c r="H9" s="670" t="n"/>
+      <c r="I9" s="668" t="n"/>
+      <c r="J9" s="668" t="n"/>
+      <c r="K9" s="668" t="n"/>
+      <c r="L9" s="668" t="n"/>
+      <c r="M9" s="668" t="n"/>
+      <c r="N9" s="668" t="n"/>
+      <c r="O9" s="668" t="n"/>
+      <c r="P9" s="668" t="n"/>
+      <c r="Q9" s="668" t="n"/>
+      <c r="R9" s="668" t="n"/>
+      <c r="S9" s="668" t="n"/>
+      <c r="T9" s="668" t="n"/>
+      <c r="U9" s="668" t="n"/>
+      <c r="V9" s="668" t="n"/>
+      <c r="W9" s="668" t="n"/>
+      <c r="X9" s="668" t="n"/>
+      <c r="Y9" s="668" t="n"/>
+      <c r="Z9" s="668" t="n"/>
+      <c r="AA9" s="668" t="n"/>
+      <c r="AB9" s="668" t="n"/>
+      <c r="AC9" s="668" t="n"/>
+      <c r="AD9" s="668" t="n"/>
+      <c r="AE9" s="668" t="n"/>
+      <c r="AF9" s="668" t="n"/>
+      <c r="AG9" s="668" t="n"/>
+      <c r="AH9" s="668" t="n"/>
+      <c r="AI9" s="668" t="n"/>
+      <c r="AJ9" s="668" t="n"/>
+      <c r="AK9" s="668" t="n"/>
+      <c r="AL9" s="668" t="n"/>
+      <c r="AM9" s="668" t="n"/>
+      <c r="AN9" s="668" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-002</t>
-        </is>
-      </c>
-      <c r="B10" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
-        </is>
-      </c>
-      <c r="C10" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
-        </is>
-      </c>
-      <c r="D10" s="356" t="n"/>
-      <c r="E10" s="356" t="n"/>
-      <c r="F10" s="356" t="n"/>
-      <c r="G10" s="356" t="n"/>
-      <c r="H10" s="356" t="n"/>
-      <c r="I10" s="356" t="n"/>
-      <c r="J10" s="356" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="356" t="n"/>
-      <c r="M10" s="356" t="n"/>
-      <c r="N10" s="356" t="n"/>
-      <c r="O10" s="356" t="n"/>
-      <c r="P10" s="356" t="n"/>
-      <c r="Q10" s="356" t="n"/>
-      <c r="R10" s="356" t="n"/>
-      <c r="S10" s="356" t="n"/>
-      <c r="T10" s="356" t="n"/>
-      <c r="U10" s="356" t="n"/>
-      <c r="V10" s="356" t="n"/>
-      <c r="W10" s="356" t="n"/>
-      <c r="X10" s="356" t="n"/>
-      <c r="Y10" s="356" t="n"/>
-      <c r="Z10" s="356" t="n"/>
-      <c r="AA10" s="356" t="n"/>
-      <c r="AB10" s="356" t="n"/>
-      <c r="AC10" s="356" t="n"/>
-      <c r="AD10" s="356" t="n"/>
-      <c r="AE10" s="356" t="n"/>
-      <c r="AF10" s="356" t="n"/>
-      <c r="AG10" s="356" t="n"/>
-      <c r="AH10" s="356" t="n"/>
-      <c r="AI10" s="356" t="n"/>
-      <c r="AJ10" s="356" t="n"/>
-      <c r="AK10" s="356" t="n"/>
-      <c r="AL10" s="356" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="534" t="n"/>
+      <c r="A10" s="728" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B10" s="671" t="inlineStr">
+        <is>
+          <t>Sample No.</t>
+        </is>
+      </c>
+      <c r="C10" s="671" t="inlineStr">
+        <is>
+          <t>ID / Serial</t>
+        </is>
+      </c>
+      <c r="D10" s="671" t="inlineStr">
+        <is>
+          <t>Measured Result / Observation</t>
+        </is>
+      </c>
+      <c r="E10" s="671" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F10" s="671" t="inlineStr">
+        <is>
+          <t>Defect Class</t>
+        </is>
+      </c>
+      <c r="G10" s="671" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="H10" s="729" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
+        </is>
+      </c>
+      <c r="I10" s="668" t="n"/>
+      <c r="J10" s="668" t="n"/>
+      <c r="K10" s="668" t="n"/>
+      <c r="L10" s="668" t="n"/>
+      <c r="M10" s="668" t="n"/>
+      <c r="N10" s="668" t="n"/>
+      <c r="O10" s="668" t="n"/>
+      <c r="P10" s="668" t="n"/>
+      <c r="Q10" s="668" t="n"/>
+      <c r="R10" s="668" t="n"/>
+      <c r="S10" s="668" t="n"/>
+      <c r="T10" s="668" t="n"/>
+      <c r="U10" s="668" t="n"/>
+      <c r="V10" s="668" t="n"/>
+      <c r="W10" s="668" t="n"/>
+      <c r="X10" s="668" t="n"/>
+      <c r="Y10" s="668" t="n"/>
+      <c r="Z10" s="668" t="n"/>
+      <c r="AA10" s="668" t="n"/>
+      <c r="AB10" s="668" t="n"/>
+      <c r="AC10" s="668" t="n"/>
+      <c r="AD10" s="668" t="n"/>
+      <c r="AE10" s="668" t="n"/>
+      <c r="AF10" s="668" t="n"/>
+      <c r="AG10" s="668" t="n"/>
+      <c r="AH10" s="668" t="n"/>
+      <c r="AI10" s="668" t="n"/>
+      <c r="AJ10" s="668" t="n"/>
+      <c r="AK10" s="668" t="n"/>
+      <c r="AL10" s="668" t="n"/>
+      <c r="AM10" s="668" t="n"/>
+      <c r="AN10" s="668" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-003</t>
-        </is>
-      </c>
-      <c r="B11" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
-        </is>
-      </c>
-      <c r="C11" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
-        </is>
-      </c>
-      <c r="D11" s="356" t="n"/>
-      <c r="E11" s="356" t="n"/>
-      <c r="F11" s="356" t="n"/>
-      <c r="G11" s="356" t="n"/>
-      <c r="H11" s="356" t="n"/>
-      <c r="I11" s="356" t="n"/>
-      <c r="J11" s="356" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="356" t="n"/>
-      <c r="M11" s="356" t="n"/>
-      <c r="N11" s="356" t="n"/>
-      <c r="O11" s="356" t="n"/>
-      <c r="P11" s="356" t="n"/>
-      <c r="Q11" s="356" t="n"/>
-      <c r="R11" s="356" t="n"/>
-      <c r="S11" s="356" t="n"/>
-      <c r="T11" s="356" t="n"/>
-      <c r="U11" s="356" t="n"/>
-      <c r="V11" s="356" t="n"/>
-      <c r="W11" s="356" t="n"/>
-      <c r="X11" s="356" t="n"/>
-      <c r="Y11" s="356" t="n"/>
-      <c r="Z11" s="356" t="n"/>
-      <c r="AA11" s="356" t="n"/>
-      <c r="AB11" s="356" t="n"/>
-      <c r="AC11" s="356" t="n"/>
-      <c r="AD11" s="356" t="n"/>
-      <c r="AE11" s="356" t="n"/>
-      <c r="AF11" s="356" t="n"/>
-      <c r="AG11" s="356" t="n"/>
-      <c r="AH11" s="356" t="n"/>
-      <c r="AI11" s="356" t="n"/>
-      <c r="AJ11" s="356" t="n"/>
-      <c r="AK11" s="356" t="n"/>
-      <c r="AL11" s="356" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="534" t="n"/>
+      <c r="A11" s="730">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B11" s="670" t="n"/>
+      <c r="C11" s="670" t="n"/>
+      <c r="D11" s="670" t="n"/>
+      <c r="E11" s="670" t="n"/>
+      <c r="F11" s="670" t="n"/>
+      <c r="G11" s="670" t="n"/>
+      <c r="H11" s="670" t="n"/>
+      <c r="I11" s="668" t="n"/>
+      <c r="J11" s="668" t="n"/>
+      <c r="K11" s="668" t="n"/>
+      <c r="L11" s="668" t="n"/>
+      <c r="M11" s="668" t="n"/>
+      <c r="N11" s="668" t="n"/>
+      <c r="O11" s="668" t="n"/>
+      <c r="P11" s="668" t="n"/>
+      <c r="Q11" s="668" t="n"/>
+      <c r="R11" s="668" t="n"/>
+      <c r="S11" s="668" t="n"/>
+      <c r="T11" s="668" t="n"/>
+      <c r="U11" s="668" t="n"/>
+      <c r="V11" s="668" t="n"/>
+      <c r="W11" s="668" t="n"/>
+      <c r="X11" s="668" t="n"/>
+      <c r="Y11" s="668" t="n"/>
+      <c r="Z11" s="668" t="n"/>
+      <c r="AA11" s="668" t="n"/>
+      <c r="AB11" s="668" t="n"/>
+      <c r="AC11" s="668" t="n"/>
+      <c r="AD11" s="668" t="n"/>
+      <c r="AE11" s="668" t="n"/>
+      <c r="AF11" s="668" t="n"/>
+      <c r="AG11" s="668" t="n"/>
+      <c r="AH11" s="668" t="n"/>
+      <c r="AI11" s="668" t="n"/>
+      <c r="AJ11" s="668" t="n"/>
+      <c r="AK11" s="668" t="n"/>
+      <c r="AL11" s="668" t="n"/>
+      <c r="AM11" s="668" t="n"/>
+      <c r="AN11" s="668" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-004</t>
-        </is>
-      </c>
-      <c r="B12" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
-        </is>
-      </c>
-      <c r="C12" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
-        </is>
-      </c>
-      <c r="D12" s="356" t="n"/>
-      <c r="E12" s="356" t="n"/>
-      <c r="F12" s="356" t="n"/>
-      <c r="G12" s="356" t="n"/>
-      <c r="H12" s="356" t="n"/>
-      <c r="I12" s="356" t="n"/>
-      <c r="J12" s="356" t="n"/>
-      <c r="K12" s="356" t="n"/>
-      <c r="L12" s="356" t="n"/>
-      <c r="M12" s="356" t="n"/>
-      <c r="N12" s="356" t="n"/>
-      <c r="O12" s="356" t="n"/>
-      <c r="P12" s="356" t="n"/>
-      <c r="Q12" s="356" t="n"/>
-      <c r="R12" s="356" t="n"/>
-      <c r="S12" s="356" t="n"/>
-      <c r="T12" s="356" t="n"/>
-      <c r="U12" s="356" t="n"/>
-      <c r="V12" s="356" t="n"/>
-      <c r="W12" s="356" t="n"/>
-      <c r="X12" s="356" t="n"/>
-      <c r="Y12" s="356" t="n"/>
-      <c r="Z12" s="356" t="n"/>
-      <c r="AA12" s="356" t="n"/>
-      <c r="AB12" s="356" t="n"/>
-      <c r="AC12" s="356" t="n"/>
-      <c r="AD12" s="356" t="n"/>
-      <c r="AE12" s="356" t="n"/>
-      <c r="AF12" s="356" t="n"/>
-      <c r="AG12" s="356" t="n"/>
-      <c r="AH12" s="356" t="n"/>
-      <c r="AI12" s="356" t="n"/>
-      <c r="AJ12" s="356" t="n"/>
-      <c r="AK12" s="356" t="n"/>
-      <c r="AL12" s="356" t="n"/>
-      <c r="AM12" s="356" t="n"/>
-      <c r="AN12" s="534" t="n"/>
+      <c r="A12" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B12" s="670" t="n"/>
+      <c r="C12" s="670" t="n"/>
+      <c r="D12" s="670" t="n"/>
+      <c r="E12" s="670" t="n"/>
+      <c r="F12" s="670" t="n"/>
+      <c r="G12" s="670" t="n"/>
+      <c r="H12" s="670" t="n"/>
+      <c r="I12" s="668" t="n"/>
+      <c r="J12" s="668" t="n"/>
+      <c r="K12" s="668" t="n"/>
+      <c r="L12" s="668" t="n"/>
+      <c r="M12" s="668" t="n"/>
+      <c r="N12" s="668" t="n"/>
+      <c r="O12" s="668" t="n"/>
+      <c r="P12" s="668" t="n"/>
+      <c r="Q12" s="668" t="n"/>
+      <c r="R12" s="668" t="n"/>
+      <c r="S12" s="668" t="n"/>
+      <c r="T12" s="668" t="n"/>
+      <c r="U12" s="668" t="n"/>
+      <c r="V12" s="668" t="n"/>
+      <c r="W12" s="668" t="n"/>
+      <c r="X12" s="668" t="n"/>
+      <c r="Y12" s="668" t="n"/>
+      <c r="Z12" s="668" t="n"/>
+      <c r="AA12" s="668" t="n"/>
+      <c r="AB12" s="668" t="n"/>
+      <c r="AC12" s="668" t="n"/>
+      <c r="AD12" s="668" t="n"/>
+      <c r="AE12" s="668" t="n"/>
+      <c r="AF12" s="668" t="n"/>
+      <c r="AG12" s="668" t="n"/>
+      <c r="AH12" s="668" t="n"/>
+      <c r="AI12" s="668" t="n"/>
+      <c r="AJ12" s="668" t="n"/>
+      <c r="AK12" s="668" t="n"/>
+      <c r="AL12" s="668" t="n"/>
+      <c r="AM12" s="668" t="n"/>
+      <c r="AN12" s="668" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-006</t>
-        </is>
-      </c>
-      <c r="B13" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
-        </is>
-      </c>
-      <c r="C13" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
-        </is>
-      </c>
-      <c r="D13" s="356" t="n"/>
-      <c r="E13" s="356" t="n"/>
-      <c r="F13" s="356" t="n"/>
-      <c r="G13" s="356" t="n"/>
-      <c r="H13" s="356" t="n"/>
-      <c r="I13" s="356" t="n"/>
-      <c r="J13" s="356" t="n"/>
-      <c r="K13" s="356" t="n"/>
-      <c r="L13" s="356" t="n"/>
-      <c r="M13" s="356" t="n"/>
-      <c r="N13" s="356" t="n"/>
-      <c r="O13" s="356" t="n"/>
-      <c r="P13" s="356" t="n"/>
-      <c r="Q13" s="356" t="n"/>
-      <c r="R13" s="356" t="n"/>
-      <c r="S13" s="356" t="n"/>
-      <c r="T13" s="356" t="n"/>
-      <c r="U13" s="356" t="n"/>
-      <c r="V13" s="356" t="n"/>
-      <c r="W13" s="356" t="n"/>
-      <c r="X13" s="356" t="n"/>
-      <c r="Y13" s="356" t="n"/>
-      <c r="Z13" s="356" t="n"/>
-      <c r="AA13" s="356" t="n"/>
-      <c r="AB13" s="356" t="n"/>
-      <c r="AC13" s="356" t="n"/>
-      <c r="AD13" s="356" t="n"/>
-      <c r="AE13" s="356" t="n"/>
-      <c r="AF13" s="356" t="n"/>
-      <c r="AG13" s="356" t="n"/>
-      <c r="AH13" s="356" t="n"/>
-      <c r="AI13" s="356" t="n"/>
-      <c r="AJ13" s="356" t="n"/>
-      <c r="AK13" s="356" t="n"/>
-      <c r="AL13" s="356" t="n"/>
-      <c r="AM13" s="356" t="n"/>
-      <c r="AN13" s="534" t="n"/>
+      <c r="A13" s="732">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B13" s="670" t="n"/>
+      <c r="C13" s="670" t="n"/>
+      <c r="D13" s="670" t="n"/>
+      <c r="E13" s="670" t="n"/>
+      <c r="F13" s="670" t="n"/>
+      <c r="G13" s="670" t="n"/>
+      <c r="H13" s="670" t="n"/>
+      <c r="I13" s="668" t="n"/>
+      <c r="J13" s="668" t="n"/>
+      <c r="K13" s="668" t="n"/>
+      <c r="L13" s="668" t="n"/>
+      <c r="M13" s="668" t="n"/>
+      <c r="N13" s="668" t="n"/>
+      <c r="O13" s="668" t="n"/>
+      <c r="P13" s="668" t="n"/>
+      <c r="Q13" s="668" t="n"/>
+      <c r="R13" s="668" t="n"/>
+      <c r="S13" s="668" t="n"/>
+      <c r="T13" s="668" t="n"/>
+      <c r="U13" s="668" t="n"/>
+      <c r="V13" s="668" t="n"/>
+      <c r="W13" s="668" t="n"/>
+      <c r="X13" s="668" t="n"/>
+      <c r="Y13" s="668" t="n"/>
+      <c r="Z13" s="668" t="n"/>
+      <c r="AA13" s="668" t="n"/>
+      <c r="AB13" s="668" t="n"/>
+      <c r="AC13" s="668" t="n"/>
+      <c r="AD13" s="668" t="n"/>
+      <c r="AE13" s="668" t="n"/>
+      <c r="AF13" s="668" t="n"/>
+      <c r="AG13" s="668" t="n"/>
+      <c r="AH13" s="668" t="n"/>
+      <c r="AI13" s="668" t="n"/>
+      <c r="AJ13" s="668" t="n"/>
+      <c r="AK13" s="668" t="n"/>
+      <c r="AL13" s="668" t="n"/>
+      <c r="AM13" s="668" t="n"/>
+      <c r="AN13" s="668" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="531" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-007</t>
-        </is>
-      </c>
-      <c r="B14" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-        </is>
-      </c>
-      <c r="C14" s="533" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-        </is>
-      </c>
-      <c r="D14" s="356" t="n"/>
-      <c r="E14" s="356" t="n"/>
-      <c r="F14" s="356" t="n"/>
-      <c r="G14" s="356" t="n"/>
-      <c r="H14" s="356" t="n"/>
-      <c r="I14" s="356" t="n"/>
-      <c r="J14" s="356" t="n"/>
-      <c r="K14" s="356" t="n"/>
-      <c r="L14" s="356" t="n"/>
-      <c r="M14" s="356" t="n"/>
-      <c r="N14" s="356" t="n"/>
-      <c r="O14" s="356" t="n"/>
-      <c r="P14" s="356" t="n"/>
-      <c r="Q14" s="356" t="n"/>
-      <c r="R14" s="356" t="n"/>
-      <c r="S14" s="356" t="n"/>
-      <c r="T14" s="356" t="n"/>
-      <c r="U14" s="356" t="n"/>
-      <c r="V14" s="356" t="n"/>
-      <c r="W14" s="356" t="n"/>
-      <c r="X14" s="356" t="n"/>
-      <c r="Y14" s="356" t="n"/>
-      <c r="Z14" s="356" t="n"/>
-      <c r="AA14" s="356" t="n"/>
-      <c r="AB14" s="356" t="n"/>
-      <c r="AC14" s="356" t="n"/>
-      <c r="AD14" s="356" t="n"/>
-      <c r="AE14" s="356" t="n"/>
-      <c r="AF14" s="356" t="n"/>
-      <c r="AG14" s="356" t="n"/>
-      <c r="AH14" s="356" t="n"/>
-      <c r="AI14" s="356" t="n"/>
-      <c r="AJ14" s="356" t="n"/>
-      <c r="AK14" s="356" t="n"/>
-      <c r="AL14" s="356" t="n"/>
-      <c r="AM14" s="356" t="n"/>
-      <c r="AN14" s="534" t="n"/>
+      <c r="A14" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B14" s="670" t="n"/>
+      <c r="C14" s="670" t="n"/>
+      <c r="D14" s="670" t="n"/>
+      <c r="E14" s="670" t="n"/>
+      <c r="F14" s="670" t="n"/>
+      <c r="G14" s="670" t="n"/>
+      <c r="H14" s="670" t="n"/>
+      <c r="I14" s="668" t="n"/>
+      <c r="J14" s="668" t="n"/>
+      <c r="K14" s="668" t="n"/>
+      <c r="L14" s="668" t="n"/>
+      <c r="M14" s="668" t="n"/>
+      <c r="N14" s="668" t="n"/>
+      <c r="O14" s="668" t="n"/>
+      <c r="P14" s="668" t="n"/>
+      <c r="Q14" s="668" t="n"/>
+      <c r="R14" s="668" t="n"/>
+      <c r="S14" s="668" t="n"/>
+      <c r="T14" s="668" t="n"/>
+      <c r="U14" s="668" t="n"/>
+      <c r="V14" s="668" t="n"/>
+      <c r="W14" s="668" t="n"/>
+      <c r="X14" s="668" t="n"/>
+      <c r="Y14" s="668" t="n"/>
+      <c r="Z14" s="668" t="n"/>
+      <c r="AA14" s="668" t="n"/>
+      <c r="AB14" s="668" t="n"/>
+      <c r="AC14" s="668" t="n"/>
+      <c r="AD14" s="668" t="n"/>
+      <c r="AE14" s="668" t="n"/>
+      <c r="AF14" s="668" t="n"/>
+      <c r="AG14" s="668" t="n"/>
+      <c r="AH14" s="668" t="n"/>
+      <c r="AI14" s="668" t="n"/>
+      <c r="AJ14" s="668" t="n"/>
+      <c r="AK14" s="668" t="n"/>
+      <c r="AL14" s="668" t="n"/>
+      <c r="AM14" s="668" t="n"/>
+      <c r="AN14" s="668" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="535" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QMS-020</t>
-        </is>
-      </c>
-      <c r="B15" s="536" t="inlineStr">
-        <is>
-          <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
-        </is>
-      </c>
-      <c r="C15" s="537" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
-        </is>
-      </c>
-      <c r="D15" s="538" t="n"/>
-      <c r="E15" s="538" t="n"/>
-      <c r="F15" s="538" t="n"/>
-      <c r="G15" s="538" t="n"/>
-      <c r="H15" s="538" t="n"/>
-      <c r="I15" s="538" t="n"/>
-      <c r="J15" s="538" t="n"/>
-      <c r="K15" s="538" t="n"/>
-      <c r="L15" s="538" t="n"/>
-      <c r="M15" s="538" t="n"/>
-      <c r="N15" s="538" t="n"/>
-      <c r="O15" s="538" t="n"/>
-      <c r="P15" s="538" t="n"/>
-      <c r="Q15" s="538" t="n"/>
-      <c r="R15" s="538" t="n"/>
-      <c r="S15" s="538" t="n"/>
-      <c r="T15" s="538" t="n"/>
-      <c r="U15" s="538" t="n"/>
-      <c r="V15" s="538" t="n"/>
-      <c r="W15" s="538" t="n"/>
-      <c r="X15" s="538" t="n"/>
-      <c r="Y15" s="538" t="n"/>
-      <c r="Z15" s="538" t="n"/>
-      <c r="AA15" s="538" t="n"/>
-      <c r="AB15" s="538" t="n"/>
-      <c r="AC15" s="538" t="n"/>
-      <c r="AD15" s="538" t="n"/>
-      <c r="AE15" s="538" t="n"/>
-      <c r="AF15" s="538" t="n"/>
-      <c r="AG15" s="538" t="n"/>
-      <c r="AH15" s="538" t="n"/>
-      <c r="AI15" s="538" t="n"/>
-      <c r="AJ15" s="538" t="n"/>
-      <c r="AK15" s="538" t="n"/>
-      <c r="AL15" s="538" t="n"/>
-      <c r="AM15" s="538" t="n"/>
-      <c r="AN15" s="539" t="n"/>
+      <c r="A15" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B15" s="670" t="n"/>
+      <c r="C15" s="670" t="n"/>
+      <c r="D15" s="670" t="n"/>
+      <c r="E15" s="670" t="n"/>
+      <c r="F15" s="670" t="n"/>
+      <c r="G15" s="670" t="n"/>
+      <c r="H15" s="670" t="n"/>
+      <c r="I15" s="668" t="n"/>
+      <c r="J15" s="668" t="n"/>
+      <c r="K15" s="668" t="n"/>
+      <c r="L15" s="668" t="n"/>
+      <c r="M15" s="668" t="n"/>
+      <c r="N15" s="668" t="n"/>
+      <c r="O15" s="668" t="n"/>
+      <c r="P15" s="668" t="n"/>
+      <c r="Q15" s="668" t="n"/>
+      <c r="R15" s="668" t="n"/>
+      <c r="S15" s="668" t="n"/>
+      <c r="T15" s="668" t="n"/>
+      <c r="U15" s="668" t="n"/>
+      <c r="V15" s="668" t="n"/>
+      <c r="W15" s="668" t="n"/>
+      <c r="X15" s="668" t="n"/>
+      <c r="Y15" s="668" t="n"/>
+      <c r="Z15" s="668" t="n"/>
+      <c r="AA15" s="668" t="n"/>
+      <c r="AB15" s="668" t="n"/>
+      <c r="AC15" s="668" t="n"/>
+      <c r="AD15" s="668" t="n"/>
+      <c r="AE15" s="668" t="n"/>
+      <c r="AF15" s="668" t="n"/>
+      <c r="AG15" s="668" t="n"/>
+      <c r="AH15" s="668" t="n"/>
+      <c r="AI15" s="668" t="n"/>
+      <c r="AJ15" s="668" t="n"/>
+      <c r="AK15" s="668" t="n"/>
+      <c r="AL15" s="668" t="n"/>
+      <c r="AM15" s="668" t="n"/>
+      <c r="AN15" s="668" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B16" s="670" t="n"/>
+      <c r="C16" s="670" t="n"/>
+      <c r="D16" s="670" t="n"/>
+      <c r="E16" s="670" t="n"/>
+      <c r="F16" s="670" t="n"/>
+      <c r="G16" s="670" t="n"/>
+      <c r="H16" s="670" t="n"/>
+      <c r="I16" s="668" t="n"/>
+      <c r="J16" s="668" t="n"/>
+      <c r="K16" s="668" t="n"/>
+      <c r="L16" s="668" t="n"/>
+      <c r="M16" s="668" t="n"/>
+      <c r="N16" s="668" t="n"/>
+      <c r="O16" s="668" t="n"/>
+      <c r="P16" s="668" t="n"/>
+      <c r="Q16" s="668" t="n"/>
+      <c r="R16" s="668" t="n"/>
+      <c r="S16" s="668" t="n"/>
+      <c r="T16" s="668" t="n"/>
+      <c r="U16" s="668" t="n"/>
+      <c r="V16" s="668" t="n"/>
+      <c r="W16" s="668" t="n"/>
+      <c r="X16" s="668" t="n"/>
+      <c r="Y16" s="668" t="n"/>
+      <c r="Z16" s="668" t="n"/>
+      <c r="AA16" s="668" t="n"/>
+      <c r="AB16" s="668" t="n"/>
+      <c r="AC16" s="668" t="n"/>
+      <c r="AD16" s="668" t="n"/>
+      <c r="AE16" s="668" t="n"/>
+      <c r="AF16" s="668" t="n"/>
+      <c r="AG16" s="668" t="n"/>
+      <c r="AH16" s="668" t="n"/>
+      <c r="AI16" s="668" t="n"/>
+      <c r="AJ16" s="668" t="n"/>
+      <c r="AK16" s="668" t="n"/>
+      <c r="AL16" s="668" t="n"/>
+      <c r="AM16" s="668" t="n"/>
+      <c r="AN16" s="668" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B17" s="670" t="n"/>
+      <c r="C17" s="670" t="n"/>
+      <c r="D17" s="670" t="n"/>
+      <c r="E17" s="670" t="n"/>
+      <c r="F17" s="670" t="n"/>
+      <c r="G17" s="670" t="n"/>
+      <c r="H17" s="670" t="n"/>
+      <c r="I17" s="668" t="n"/>
+      <c r="J17" s="668" t="n"/>
+      <c r="K17" s="668" t="n"/>
+      <c r="L17" s="668" t="n"/>
+      <c r="M17" s="668" t="n"/>
+      <c r="N17" s="668" t="n"/>
+      <c r="O17" s="668" t="n"/>
+      <c r="P17" s="668" t="n"/>
+      <c r="Q17" s="668" t="n"/>
+      <c r="R17" s="668" t="n"/>
+      <c r="S17" s="668" t="n"/>
+      <c r="T17" s="668" t="n"/>
+      <c r="U17" s="668" t="n"/>
+      <c r="V17" s="668" t="n"/>
+      <c r="W17" s="668" t="n"/>
+      <c r="X17" s="668" t="n"/>
+      <c r="Y17" s="668" t="n"/>
+      <c r="Z17" s="668" t="n"/>
+      <c r="AA17" s="668" t="n"/>
+      <c r="AB17" s="668" t="n"/>
+      <c r="AC17" s="668" t="n"/>
+      <c r="AD17" s="668" t="n"/>
+      <c r="AE17" s="668" t="n"/>
+      <c r="AF17" s="668" t="n"/>
+      <c r="AG17" s="668" t="n"/>
+      <c r="AH17" s="668" t="n"/>
+      <c r="AI17" s="668" t="n"/>
+      <c r="AJ17" s="668" t="n"/>
+      <c r="AK17" s="668" t="n"/>
+      <c r="AL17" s="668" t="n"/>
+      <c r="AM17" s="668" t="n"/>
+      <c r="AN17" s="668" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B18" s="670" t="n"/>
+      <c r="C18" s="670" t="n"/>
+      <c r="D18" s="670" t="n"/>
+      <c r="E18" s="670" t="n"/>
+      <c r="F18" s="670" t="n"/>
+      <c r="G18" s="670" t="n"/>
+      <c r="H18" s="670" t="n"/>
+      <c r="I18" s="668" t="n"/>
+      <c r="J18" s="668" t="n"/>
+      <c r="K18" s="668" t="n"/>
+      <c r="L18" s="668" t="n"/>
+      <c r="M18" s="668" t="n"/>
+      <c r="N18" s="668" t="n"/>
+      <c r="O18" s="668" t="n"/>
+      <c r="P18" s="668" t="n"/>
+      <c r="Q18" s="668" t="n"/>
+      <c r="R18" s="668" t="n"/>
+      <c r="S18" s="668" t="n"/>
+      <c r="T18" s="668" t="n"/>
+      <c r="U18" s="668" t="n"/>
+      <c r="V18" s="668" t="n"/>
+      <c r="W18" s="668" t="n"/>
+      <c r="X18" s="668" t="n"/>
+      <c r="Y18" s="668" t="n"/>
+      <c r="Z18" s="668" t="n"/>
+      <c r="AA18" s="668" t="n"/>
+      <c r="AB18" s="668" t="n"/>
+      <c r="AC18" s="668" t="n"/>
+      <c r="AD18" s="668" t="n"/>
+      <c r="AE18" s="668" t="n"/>
+      <c r="AF18" s="668" t="n"/>
+      <c r="AG18" s="668" t="n"/>
+      <c r="AH18" s="668" t="n"/>
+      <c r="AI18" s="668" t="n"/>
+      <c r="AJ18" s="668" t="n"/>
+      <c r="AK18" s="668" t="n"/>
+      <c r="AL18" s="668" t="n"/>
+      <c r="AM18" s="668" t="n"/>
+      <c r="AN18" s="668" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B19" s="670" t="n"/>
+      <c r="C19" s="670" t="n"/>
+      <c r="D19" s="670" t="n"/>
+      <c r="E19" s="670" t="n"/>
+      <c r="F19" s="670" t="n"/>
+      <c r="G19" s="670" t="n"/>
+      <c r="H19" s="670" t="n"/>
+      <c r="I19" s="668" t="n"/>
+      <c r="J19" s="668" t="n"/>
+      <c r="K19" s="668" t="n"/>
+      <c r="L19" s="668" t="n"/>
+      <c r="M19" s="668" t="n"/>
+      <c r="N19" s="668" t="n"/>
+      <c r="O19" s="668" t="n"/>
+      <c r="P19" s="668" t="n"/>
+      <c r="Q19" s="668" t="n"/>
+      <c r="R19" s="668" t="n"/>
+      <c r="S19" s="668" t="n"/>
+      <c r="T19" s="668" t="n"/>
+      <c r="U19" s="668" t="n"/>
+      <c r="V19" s="668" t="n"/>
+      <c r="W19" s="668" t="n"/>
+      <c r="X19" s="668" t="n"/>
+      <c r="Y19" s="668" t="n"/>
+      <c r="Z19" s="668" t="n"/>
+      <c r="AA19" s="668" t="n"/>
+      <c r="AB19" s="668" t="n"/>
+      <c r="AC19" s="668" t="n"/>
+      <c r="AD19" s="668" t="n"/>
+      <c r="AE19" s="668" t="n"/>
+      <c r="AF19" s="668" t="n"/>
+      <c r="AG19" s="668" t="n"/>
+      <c r="AH19" s="668" t="n"/>
+      <c r="AI19" s="668" t="n"/>
+      <c r="AJ19" s="668" t="n"/>
+      <c r="AK19" s="668" t="n"/>
+      <c r="AL19" s="668" t="n"/>
+      <c r="AM19" s="668" t="n"/>
+      <c r="AN19" s="668" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B20" s="668" t="n"/>
+      <c r="C20" s="668" t="n"/>
+      <c r="D20" s="668" t="n"/>
+      <c r="E20" s="668" t="n"/>
+      <c r="F20" s="668" t="n"/>
+      <c r="G20" s="668" t="n"/>
+      <c r="H20" s="668" t="n"/>
+      <c r="I20" s="668" t="n"/>
+      <c r="J20" s="668" t="n"/>
+      <c r="K20" s="668" t="n"/>
+      <c r="L20" s="668" t="n"/>
+      <c r="M20" s="668" t="n"/>
+      <c r="N20" s="668" t="n"/>
+      <c r="O20" s="668" t="n"/>
+      <c r="P20" s="668" t="n"/>
+      <c r="Q20" s="668" t="n"/>
+      <c r="R20" s="668" t="n"/>
+      <c r="S20" s="668" t="n"/>
+      <c r="T20" s="668" t="n"/>
+      <c r="U20" s="668" t="n"/>
+      <c r="V20" s="668" t="n"/>
+      <c r="W20" s="668" t="n"/>
+      <c r="X20" s="668" t="n"/>
+      <c r="Y20" s="668" t="n"/>
+      <c r="Z20" s="668" t="n"/>
+      <c r="AA20" s="668" t="n"/>
+      <c r="AB20" s="668" t="n"/>
+      <c r="AC20" s="668" t="n"/>
+      <c r="AD20" s="668" t="n"/>
+      <c r="AE20" s="668" t="n"/>
+      <c r="AF20" s="668" t="n"/>
+      <c r="AG20" s="668" t="n"/>
+      <c r="AH20" s="668" t="n"/>
+      <c r="AI20" s="668" t="n"/>
+      <c r="AJ20" s="668" t="n"/>
+      <c r="AK20" s="668" t="n"/>
+      <c r="AL20" s="668" t="n"/>
+      <c r="AM20" s="668" t="n"/>
+      <c r="AN20" s="668" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B21" s="668" t="n"/>
+      <c r="C21" s="668" t="n"/>
+      <c r="D21" s="668" t="n"/>
+      <c r="E21" s="668" t="n"/>
+      <c r="F21" s="668" t="n"/>
+      <c r="G21" s="668" t="n"/>
+      <c r="H21" s="668" t="n"/>
+      <c r="I21" s="668" t="n"/>
+      <c r="J21" s="668" t="n"/>
+      <c r="K21" s="668" t="n"/>
+      <c r="L21" s="668" t="n"/>
+      <c r="M21" s="668" t="n"/>
+      <c r="N21" s="668" t="n"/>
+      <c r="O21" s="668" t="n"/>
+      <c r="P21" s="668" t="n"/>
+      <c r="Q21" s="668" t="n"/>
+      <c r="R21" s="668" t="n"/>
+      <c r="S21" s="668" t="n"/>
+      <c r="T21" s="668" t="n"/>
+      <c r="U21" s="668" t="n"/>
+      <c r="V21" s="668" t="n"/>
+      <c r="W21" s="668" t="n"/>
+      <c r="X21" s="668" t="n"/>
+      <c r="Y21" s="668" t="n"/>
+      <c r="Z21" s="668" t="n"/>
+      <c r="AA21" s="668" t="n"/>
+      <c r="AB21" s="668" t="n"/>
+      <c r="AC21" s="668" t="n"/>
+      <c r="AD21" s="668" t="n"/>
+      <c r="AE21" s="668" t="n"/>
+      <c r="AF21" s="668" t="n"/>
+      <c r="AG21" s="668" t="n"/>
+      <c r="AH21" s="668" t="n"/>
+      <c r="AI21" s="668" t="n"/>
+      <c r="AJ21" s="668" t="n"/>
+      <c r="AK21" s="668" t="n"/>
+      <c r="AL21" s="668" t="n"/>
+      <c r="AM21" s="668" t="n"/>
+      <c r="AN21" s="668" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B22" s="668" t="n"/>
+      <c r="C22" s="668" t="n"/>
+      <c r="D22" s="668" t="n"/>
+      <c r="E22" s="668" t="n"/>
+      <c r="F22" s="668" t="n"/>
+      <c r="G22" s="668" t="n"/>
+      <c r="H22" s="668" t="n"/>
+      <c r="I22" s="668" t="n"/>
+      <c r="J22" s="668" t="n"/>
+      <c r="K22" s="668" t="n"/>
+      <c r="L22" s="668" t="n"/>
+      <c r="M22" s="668" t="n"/>
+      <c r="N22" s="668" t="n"/>
+      <c r="O22" s="668" t="n"/>
+      <c r="P22" s="668" t="n"/>
+      <c r="Q22" s="668" t="n"/>
+      <c r="R22" s="668" t="n"/>
+      <c r="S22" s="668" t="n"/>
+      <c r="T22" s="668" t="n"/>
+      <c r="U22" s="668" t="n"/>
+      <c r="V22" s="668" t="n"/>
+      <c r="W22" s="668" t="n"/>
+      <c r="X22" s="668" t="n"/>
+      <c r="Y22" s="668" t="n"/>
+      <c r="Z22" s="668" t="n"/>
+      <c r="AA22" s="668" t="n"/>
+      <c r="AB22" s="668" t="n"/>
+      <c r="AC22" s="668" t="n"/>
+      <c r="AD22" s="668" t="n"/>
+      <c r="AE22" s="668" t="n"/>
+      <c r="AF22" s="668" t="n"/>
+      <c r="AG22" s="668" t="n"/>
+      <c r="AH22" s="668" t="n"/>
+      <c r="AI22" s="668" t="n"/>
+      <c r="AJ22" s="668" t="n"/>
+      <c r="AK22" s="668" t="n"/>
+      <c r="AL22" s="668" t="n"/>
+      <c r="AM22" s="668" t="n"/>
+      <c r="AN22" s="668" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B23" s="668" t="n"/>
+      <c r="C23" s="668" t="n"/>
+      <c r="D23" s="668" t="n"/>
+      <c r="E23" s="668" t="n"/>
+      <c r="F23" s="668" t="n"/>
+      <c r="G23" s="668" t="n"/>
+      <c r="H23" s="668" t="n"/>
+      <c r="I23" s="668" t="n"/>
+      <c r="J23" s="668" t="n"/>
+      <c r="K23" s="668" t="n"/>
+      <c r="L23" s="668" t="n"/>
+      <c r="M23" s="668" t="n"/>
+      <c r="N23" s="668" t="n"/>
+      <c r="O23" s="668" t="n"/>
+      <c r="P23" s="668" t="n"/>
+      <c r="Q23" s="668" t="n"/>
+      <c r="R23" s="668" t="n"/>
+      <c r="S23" s="668" t="n"/>
+      <c r="T23" s="668" t="n"/>
+      <c r="U23" s="668" t="n"/>
+      <c r="V23" s="668" t="n"/>
+      <c r="W23" s="668" t="n"/>
+      <c r="X23" s="668" t="n"/>
+      <c r="Y23" s="668" t="n"/>
+      <c r="Z23" s="668" t="n"/>
+      <c r="AA23" s="668" t="n"/>
+      <c r="AB23" s="668" t="n"/>
+      <c r="AC23" s="668" t="n"/>
+      <c r="AD23" s="668" t="n"/>
+      <c r="AE23" s="668" t="n"/>
+      <c r="AF23" s="668" t="n"/>
+      <c r="AG23" s="668" t="n"/>
+      <c r="AH23" s="668" t="n"/>
+      <c r="AI23" s="668" t="n"/>
+      <c r="AJ23" s="668" t="n"/>
+      <c r="AK23" s="668" t="n"/>
+      <c r="AL23" s="668" t="n"/>
+      <c r="AM23" s="668" t="n"/>
+      <c r="AN23" s="668" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="733">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B24" s="668" t="n"/>
+      <c r="C24" s="668" t="n"/>
+      <c r="D24" s="668" t="n"/>
+      <c r="E24" s="668" t="n"/>
+      <c r="F24" s="668" t="n"/>
+      <c r="G24" s="668" t="n"/>
+      <c r="H24" s="668" t="n"/>
+      <c r="I24" s="668" t="n"/>
+      <c r="J24" s="668" t="n"/>
+      <c r="K24" s="668" t="n"/>
+      <c r="L24" s="668" t="n"/>
+      <c r="M24" s="668" t="n"/>
+      <c r="N24" s="668" t="n"/>
+      <c r="O24" s="668" t="n"/>
+      <c r="P24" s="668" t="n"/>
+      <c r="Q24" s="668" t="n"/>
+      <c r="R24" s="668" t="n"/>
+      <c r="S24" s="668" t="n"/>
+      <c r="T24" s="668" t="n"/>
+      <c r="U24" s="668" t="n"/>
+      <c r="V24" s="668" t="n"/>
+      <c r="W24" s="668" t="n"/>
+      <c r="X24" s="668" t="n"/>
+      <c r="Y24" s="668" t="n"/>
+      <c r="Z24" s="668" t="n"/>
+      <c r="AA24" s="668" t="n"/>
+      <c r="AB24" s="668" t="n"/>
+      <c r="AC24" s="668" t="n"/>
+      <c r="AD24" s="668" t="n"/>
+      <c r="AE24" s="668" t="n"/>
+      <c r="AF24" s="668" t="n"/>
+      <c r="AG24" s="668" t="n"/>
+      <c r="AH24" s="668" t="n"/>
+      <c r="AI24" s="668" t="n"/>
+      <c r="AJ24" s="668" t="n"/>
+      <c r="AK24" s="668" t="n"/>
+      <c r="AL24" s="668" t="n"/>
+      <c r="AM24" s="668" t="n"/>
+      <c r="AN24" s="668" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="734">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B25" s="668" t="n"/>
+      <c r="C25" s="668" t="n"/>
+      <c r="D25" s="668" t="n"/>
+      <c r="E25" s="668" t="n"/>
+      <c r="F25" s="668" t="n"/>
+      <c r="G25" s="668" t="n"/>
+      <c r="H25" s="668" t="n"/>
+      <c r="I25" s="668" t="n"/>
+      <c r="J25" s="668" t="n"/>
+      <c r="K25" s="668" t="n"/>
+      <c r="L25" s="668" t="n"/>
+      <c r="M25" s="668" t="n"/>
+      <c r="N25" s="668" t="n"/>
+      <c r="O25" s="668" t="n"/>
+      <c r="P25" s="668" t="n"/>
+      <c r="Q25" s="668" t="n"/>
+      <c r="R25" s="668" t="n"/>
+      <c r="S25" s="668" t="n"/>
+      <c r="T25" s="668" t="n"/>
+      <c r="U25" s="668" t="n"/>
+      <c r="V25" s="668" t="n"/>
+      <c r="W25" s="668" t="n"/>
+      <c r="X25" s="668" t="n"/>
+      <c r="Y25" s="668" t="n"/>
+      <c r="Z25" s="668" t="n"/>
+      <c r="AA25" s="668" t="n"/>
+      <c r="AB25" s="668" t="n"/>
+      <c r="AC25" s="668" t="n"/>
+      <c r="AD25" s="668" t="n"/>
+      <c r="AE25" s="668" t="n"/>
+      <c r="AF25" s="668" t="n"/>
+      <c r="AG25" s="668" t="n"/>
+      <c r="AH25" s="668" t="n"/>
+      <c r="AI25" s="668" t="n"/>
+      <c r="AJ25" s="668" t="n"/>
+      <c r="AK25" s="668" t="n"/>
+      <c r="AL25" s="668" t="n"/>
+      <c r="AM25" s="668" t="n"/>
+      <c r="AN25" s="668" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="668" t="n"/>
+      <c r="B26" s="668" t="n"/>
+      <c r="C26" s="668" t="n"/>
+      <c r="D26" s="668" t="n"/>
+      <c r="E26" s="668" t="n"/>
+      <c r="F26" s="668" t="n"/>
+      <c r="G26" s="668" t="n"/>
+      <c r="H26" s="668" t="n"/>
+      <c r="I26" s="668" t="n"/>
+      <c r="J26" s="668" t="n"/>
+      <c r="K26" s="668" t="n"/>
+      <c r="L26" s="668" t="n"/>
+      <c r="M26" s="668" t="n"/>
+      <c r="N26" s="668" t="n"/>
+      <c r="O26" s="668" t="n"/>
+      <c r="P26" s="668" t="n"/>
+      <c r="Q26" s="668" t="n"/>
+      <c r="R26" s="668" t="n"/>
+      <c r="S26" s="668" t="n"/>
+      <c r="T26" s="668" t="n"/>
+      <c r="U26" s="668" t="n"/>
+      <c r="V26" s="668" t="n"/>
+      <c r="W26" s="668" t="n"/>
+      <c r="X26" s="668" t="n"/>
+      <c r="Y26" s="668" t="n"/>
+      <c r="Z26" s="668" t="n"/>
+      <c r="AA26" s="668" t="n"/>
+      <c r="AB26" s="668" t="n"/>
+      <c r="AC26" s="668" t="n"/>
+      <c r="AD26" s="668" t="n"/>
+      <c r="AE26" s="668" t="n"/>
+      <c r="AF26" s="668" t="n"/>
+      <c r="AG26" s="668" t="n"/>
+      <c r="AH26" s="668" t="n"/>
+      <c r="AI26" s="668" t="n"/>
+      <c r="AJ26" s="668" t="n"/>
+      <c r="AK26" s="668" t="n"/>
+      <c r="AL26" s="668" t="n"/>
+      <c r="AM26" s="668" t="n"/>
+      <c r="AN26" s="668" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="668" t="n"/>
+      <c r="B27" s="668" t="n"/>
+      <c r="C27" s="668" t="n"/>
+      <c r="D27" s="668" t="n"/>
+      <c r="E27" s="668" t="n"/>
+      <c r="F27" s="668" t="n"/>
+      <c r="G27" s="668" t="n"/>
+      <c r="H27" s="668" t="n"/>
+      <c r="I27" s="668" t="n"/>
+      <c r="J27" s="668" t="n"/>
+      <c r="K27" s="668" t="n"/>
+      <c r="L27" s="668" t="n"/>
+      <c r="M27" s="668" t="n"/>
+      <c r="N27" s="668" t="n"/>
+      <c r="O27" s="668" t="n"/>
+      <c r="P27" s="668" t="n"/>
+      <c r="Q27" s="668" t="n"/>
+      <c r="R27" s="668" t="n"/>
+      <c r="S27" s="668" t="n"/>
+      <c r="T27" s="668" t="n"/>
+      <c r="U27" s="668" t="n"/>
+      <c r="V27" s="668" t="n"/>
+      <c r="W27" s="668" t="n"/>
+      <c r="X27" s="668" t="n"/>
+      <c r="Y27" s="668" t="n"/>
+      <c r="Z27" s="668" t="n"/>
+      <c r="AA27" s="668" t="n"/>
+      <c r="AB27" s="668" t="n"/>
+      <c r="AC27" s="668" t="n"/>
+      <c r="AD27" s="668" t="n"/>
+      <c r="AE27" s="668" t="n"/>
+      <c r="AF27" s="668" t="n"/>
+      <c r="AG27" s="668" t="n"/>
+      <c r="AH27" s="668" t="n"/>
+      <c r="AI27" s="668" t="n"/>
+      <c r="AJ27" s="668" t="n"/>
+      <c r="AK27" s="668" t="n"/>
+      <c r="AL27" s="668" t="n"/>
+      <c r="AM27" s="668" t="n"/>
+      <c r="AN27" s="668" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="668" t="n"/>
+      <c r="B28" s="668" t="n"/>
+      <c r="C28" s="668" t="n"/>
+      <c r="D28" s="668" t="n"/>
+      <c r="E28" s="668" t="n"/>
+      <c r="F28" s="668" t="n"/>
+      <c r="G28" s="668" t="n"/>
+      <c r="H28" s="668" t="n"/>
+      <c r="I28" s="668" t="n"/>
+      <c r="J28" s="668" t="n"/>
+      <c r="K28" s="668" t="n"/>
+      <c r="L28" s="668" t="n"/>
+      <c r="M28" s="668" t="n"/>
+      <c r="N28" s="668" t="n"/>
+      <c r="O28" s="668" t="n"/>
+      <c r="P28" s="668" t="n"/>
+      <c r="Q28" s="668" t="n"/>
+      <c r="R28" s="668" t="n"/>
+      <c r="S28" s="668" t="n"/>
+      <c r="T28" s="668" t="n"/>
+      <c r="U28" s="668" t="n"/>
+      <c r="V28" s="668" t="n"/>
+      <c r="W28" s="668" t="n"/>
+      <c r="X28" s="668" t="n"/>
+      <c r="Y28" s="668" t="n"/>
+      <c r="Z28" s="668" t="n"/>
+      <c r="AA28" s="668" t="n"/>
+      <c r="AB28" s="668" t="n"/>
+      <c r="AC28" s="668" t="n"/>
+      <c r="AD28" s="668" t="n"/>
+      <c r="AE28" s="668" t="n"/>
+      <c r="AF28" s="668" t="n"/>
+      <c r="AG28" s="668" t="n"/>
+      <c r="AH28" s="668" t="n"/>
+      <c r="AI28" s="668" t="n"/>
+      <c r="AJ28" s="668" t="n"/>
+      <c r="AK28" s="668" t="n"/>
+      <c r="AL28" s="668" t="n"/>
+      <c r="AM28" s="668" t="n"/>
+      <c r="AN28" s="668" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <autoFilter ref="A4:C15"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
+      <formula1>'LISTS'!$A$2:$A$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -12187,410 +12611,2133 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="512" t="inlineStr">
-        <is>
-          <t>Evidence Reference / Attachment Guidance</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="709" t="n"/>
       <c r="B1" s="603" t="n"/>
       <c r="C1" s="603" t="n"/>
       <c r="D1" s="603" t="n"/>
       <c r="E1" s="603" t="n"/>
       <c r="F1" s="603" t="n"/>
       <c r="G1" s="603" t="n"/>
-      <c r="H1" s="513" t="n"/>
-      <c r="I1" s="430" t="n"/>
-      <c r="J1" s="431" t="n"/>
-      <c r="K1" s="431" t="n"/>
-      <c r="L1" s="431" t="n"/>
-      <c r="M1" s="431" t="n"/>
-      <c r="N1" s="431" t="n"/>
-      <c r="O1" s="431" t="n"/>
-      <c r="P1" s="431" t="n"/>
-      <c r="Q1" s="431" t="n"/>
-      <c r="R1" s="431" t="n"/>
-      <c r="S1" s="431" t="n"/>
-      <c r="T1" s="431" t="n"/>
-      <c r="U1" s="431" t="n"/>
-      <c r="V1" s="431" t="n"/>
-      <c r="W1" s="431" t="n"/>
-      <c r="X1" s="431" t="n"/>
-      <c r="Y1" s="431" t="n"/>
-      <c r="Z1" s="431" t="n"/>
-      <c r="AA1" s="431" t="n"/>
-      <c r="AB1" s="431" t="n"/>
-      <c r="AC1" s="431" t="n"/>
-      <c r="AD1" s="432" t="n"/>
-      <c r="AE1" s="433" t="n"/>
-      <c r="AF1" s="434" t="n"/>
-      <c r="AG1" s="434" t="n"/>
-      <c r="AH1" s="435" t="n"/>
-      <c r="AI1" s="436" t="n"/>
-      <c r="AJ1" s="437" t="n"/>
-      <c r="AK1" s="437" t="n"/>
-      <c r="AL1" s="437" t="n"/>
-      <c r="AM1" s="437" t="n"/>
-      <c r="AN1" s="438" t="n"/>
+      <c r="H1" s="710" t="n"/>
+      <c r="I1" s="711" t="inlineStr">
+        <is>
+          <t>AQL Inspection Record</t>
+        </is>
+      </c>
+      <c r="J1" s="603" t="n"/>
+      <c r="K1" s="603" t="n"/>
+      <c r="L1" s="603" t="n"/>
+      <c r="M1" s="603" t="n"/>
+      <c r="N1" s="603" t="n"/>
+      <c r="O1" s="603" t="n"/>
+      <c r="P1" s="603" t="n"/>
+      <c r="Q1" s="603" t="n"/>
+      <c r="R1" s="603" t="n"/>
+      <c r="S1" s="603" t="n"/>
+      <c r="T1" s="603" t="n"/>
+      <c r="U1" s="603" t="n"/>
+      <c r="V1" s="603" t="n"/>
+      <c r="W1" s="603" t="n"/>
+      <c r="X1" s="603" t="n"/>
+      <c r="Y1" s="603" t="n"/>
+      <c r="Z1" s="603" t="n"/>
+      <c r="AA1" s="603" t="n"/>
+      <c r="AB1" s="603" t="n"/>
+      <c r="AC1" s="603" t="n"/>
+      <c r="AD1" s="710" t="n"/>
+      <c r="AE1" s="435" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="603" t="n"/>
+      <c r="AG1" s="603" t="n"/>
+      <c r="AH1" s="712" t="n"/>
+      <c r="AI1" s="438" t="inlineStr">
+        <is>
+          <t>FRM-621</t>
+        </is>
+      </c>
+      <c r="AJ1" s="603" t="n"/>
+      <c r="AK1" s="603" t="n"/>
+      <c r="AL1" s="603" t="n"/>
+      <c r="AM1" s="603" t="n"/>
+      <c r="AN1" s="710" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="514" t="inlineStr">
-        <is>
-          <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
-        </is>
-      </c>
-      <c r="H2" s="515" t="n"/>
-      <c r="I2" s="441" t="n"/>
-      <c r="J2" s="442" t="n"/>
-      <c r="K2" s="442" t="n"/>
-      <c r="L2" s="442" t="n"/>
-      <c r="M2" s="442" t="n"/>
-      <c r="N2" s="442" t="n"/>
-      <c r="O2" s="442" t="n"/>
-      <c r="P2" s="442" t="n"/>
-      <c r="Q2" s="442" t="n"/>
-      <c r="R2" s="442" t="n"/>
-      <c r="S2" s="442" t="n"/>
-      <c r="T2" s="442" t="n"/>
-      <c r="U2" s="442" t="n"/>
-      <c r="V2" s="442" t="n"/>
-      <c r="W2" s="442" t="n"/>
-      <c r="X2" s="442" t="n"/>
-      <c r="Y2" s="442" t="n"/>
-      <c r="Z2" s="442" t="n"/>
-      <c r="AA2" s="442" t="n"/>
-      <c r="AB2" s="442" t="n"/>
-      <c r="AC2" s="442" t="n"/>
-      <c r="AD2" s="443" t="n"/>
-      <c r="AE2" s="444" t="n"/>
-      <c r="AF2" s="445" t="n"/>
-      <c r="AG2" s="445" t="n"/>
-      <c r="AH2" s="446" t="n"/>
-      <c r="AI2" s="447" t="n"/>
-      <c r="AJ2" s="448" t="n"/>
-      <c r="AK2" s="448" t="n"/>
-      <c r="AL2" s="448" t="n"/>
-      <c r="AM2" s="448" t="n"/>
-      <c r="AN2" s="449" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="682" t="n"/>
+      <c r="C2" s="682" t="n"/>
+      <c r="D2" s="682" t="n"/>
+      <c r="E2" s="682" t="n"/>
+      <c r="F2" s="682" t="n"/>
+      <c r="G2" s="682" t="n"/>
+      <c r="H2" s="683" t="n"/>
+      <c r="I2" s="682" t="n"/>
+      <c r="J2" s="682" t="n"/>
+      <c r="K2" s="682" t="n"/>
+      <c r="L2" s="682" t="n"/>
+      <c r="M2" s="682" t="n"/>
+      <c r="N2" s="682" t="n"/>
+      <c r="O2" s="682" t="n"/>
+      <c r="P2" s="682" t="n"/>
+      <c r="Q2" s="682" t="n"/>
+      <c r="R2" s="682" t="n"/>
+      <c r="S2" s="682" t="n"/>
+      <c r="T2" s="682" t="n"/>
+      <c r="U2" s="682" t="n"/>
+      <c r="V2" s="682" t="n"/>
+      <c r="W2" s="682" t="n"/>
+      <c r="X2" s="682" t="n"/>
+      <c r="Y2" s="682" t="n"/>
+      <c r="Z2" s="682" t="n"/>
+      <c r="AA2" s="682" t="n"/>
+      <c r="AB2" s="682" t="n"/>
+      <c r="AC2" s="682" t="n"/>
+      <c r="AD2" s="683" t="n"/>
+      <c r="AE2" s="684" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="685" t="n"/>
+      <c r="AG2" s="685" t="n"/>
+      <c r="AH2" s="686" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="687" t="n"/>
+      <c r="AK2" s="687" t="n"/>
+      <c r="AL2" s="687" t="n"/>
+      <c r="AM2" s="687" t="n"/>
+      <c r="AN2" s="688" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="516" t="n"/>
-      <c r="B3" s="517" t="n"/>
-      <c r="C3" s="517" t="n"/>
-      <c r="D3" s="517" t="n"/>
-      <c r="E3" s="517" t="n"/>
-      <c r="F3" s="517" t="n"/>
-      <c r="G3" s="517" t="n"/>
-      <c r="H3" s="515" t="n"/>
-      <c r="I3" s="441" t="n"/>
-      <c r="J3" s="442" t="n"/>
-      <c r="K3" s="442" t="n"/>
-      <c r="L3" s="442" t="n"/>
-      <c r="M3" s="442" t="n"/>
-      <c r="N3" s="442" t="n"/>
-      <c r="O3" s="442" t="n"/>
-      <c r="P3" s="442" t="n"/>
-      <c r="Q3" s="442" t="n"/>
-      <c r="R3" s="442" t="n"/>
-      <c r="S3" s="442" t="n"/>
-      <c r="T3" s="442" t="n"/>
-      <c r="U3" s="442" t="n"/>
-      <c r="V3" s="442" t="n"/>
-      <c r="W3" s="442" t="n"/>
-      <c r="X3" s="442" t="n"/>
-      <c r="Y3" s="442" t="n"/>
-      <c r="Z3" s="442" t="n"/>
-      <c r="AA3" s="442" t="n"/>
-      <c r="AB3" s="442" t="n"/>
-      <c r="AC3" s="442" t="n"/>
-      <c r="AD3" s="443" t="n"/>
-      <c r="AE3" s="444" t="n"/>
-      <c r="AF3" s="445" t="n"/>
-      <c r="AG3" s="445" t="n"/>
-      <c r="AH3" s="446" t="n"/>
-      <c r="AI3" s="447" t="n"/>
-      <c r="AJ3" s="448" t="n"/>
-      <c r="AK3" s="448" t="n"/>
-      <c r="AL3" s="448" t="n"/>
-      <c r="AM3" s="448" t="n"/>
-      <c r="AN3" s="449" t="n"/>
+      <c r="A3" s="689" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="690" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="690" t="n"/>
+      <c r="AE3" s="691" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="692" t="n"/>
+      <c r="AG3" s="692" t="n"/>
+      <c r="AH3" s="693" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="694" t="n"/>
+      <c r="AK3" s="694" t="n"/>
+      <c r="AL3" s="694" t="n"/>
+      <c r="AM3" s="694" t="n"/>
+      <c r="AN3" s="695" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="518" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="519" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="519" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="517" t="n"/>
-      <c r="E4" s="517" t="n"/>
-      <c r="F4" s="517" t="n"/>
-      <c r="G4" s="517" t="n"/>
-      <c r="H4" s="515" t="n"/>
-      <c r="I4" s="450" t="n"/>
-      <c r="J4" s="451" t="n"/>
-      <c r="K4" s="451" t="n"/>
-      <c r="L4" s="451" t="n"/>
-      <c r="M4" s="451" t="n"/>
-      <c r="N4" s="451" t="n"/>
-      <c r="O4" s="451" t="n"/>
-      <c r="P4" s="451" t="n"/>
-      <c r="Q4" s="451" t="n"/>
-      <c r="R4" s="451" t="n"/>
-      <c r="S4" s="451" t="n"/>
-      <c r="T4" s="451" t="n"/>
-      <c r="U4" s="451" t="n"/>
-      <c r="V4" s="451" t="n"/>
-      <c r="W4" s="451" t="n"/>
-      <c r="X4" s="451" t="n"/>
-      <c r="Y4" s="451" t="n"/>
-      <c r="Z4" s="451" t="n"/>
-      <c r="AA4" s="451" t="n"/>
-      <c r="AB4" s="451" t="n"/>
-      <c r="AC4" s="451" t="n"/>
-      <c r="AD4" s="452" t="n"/>
-      <c r="AE4" s="444" t="n"/>
-      <c r="AF4" s="445" t="n"/>
-      <c r="AG4" s="445" t="n"/>
-      <c r="AH4" s="446" t="n"/>
-      <c r="AI4" s="447" t="n"/>
-      <c r="AJ4" s="448" t="n"/>
-      <c r="AK4" s="448" t="n"/>
-      <c r="AL4" s="448" t="n"/>
-      <c r="AM4" s="448" t="n"/>
-      <c r="AN4" s="449" t="n"/>
+      <c r="A4" s="689" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="690" t="n"/>
+      <c r="I4" s="696" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="690" t="n"/>
+      <c r="AE4" s="691" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="692" t="n"/>
+      <c r="AG4" s="692" t="n"/>
+      <c r="AH4" s="693" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="694" t="n"/>
+      <c r="AK4" s="694" t="n"/>
+      <c r="AL4" s="694" t="n"/>
+      <c r="AM4" s="694" t="n"/>
+      <c r="AN4" s="695" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="521" t="inlineStr">
-        <is>
-          <t>Evidence item 1</t>
-        </is>
-      </c>
-      <c r="B5" s="522" t="inlineStr">
-        <is>
-          <t>Reference to the correct evidence folder, shared location or dossier package.</t>
-        </is>
-      </c>
-      <c r="C5" s="522" t="inlineStr">
-        <is>
-          <t>Link or reference ID</t>
-        </is>
-      </c>
-      <c r="D5" s="540" t="n"/>
-      <c r="E5" s="540" t="n"/>
-      <c r="F5" s="540" t="n"/>
-      <c r="G5" s="540" t="n"/>
-      <c r="H5" s="541" t="n"/>
-      <c r="I5" s="456" t="n"/>
-      <c r="J5" s="457" t="n"/>
-      <c r="K5" s="457" t="n"/>
-      <c r="L5" s="457" t="n"/>
-      <c r="M5" s="457" t="n"/>
-      <c r="N5" s="457" t="n"/>
-      <c r="O5" s="457" t="n"/>
-      <c r="P5" s="457" t="n"/>
-      <c r="Q5" s="457" t="n"/>
-      <c r="R5" s="457" t="n"/>
-      <c r="S5" s="457" t="n"/>
-      <c r="T5" s="457" t="n"/>
-      <c r="U5" s="457" t="n"/>
-      <c r="V5" s="457" t="n"/>
-      <c r="W5" s="457" t="n"/>
-      <c r="X5" s="457" t="n"/>
-      <c r="Y5" s="457" t="n"/>
-      <c r="Z5" s="457" t="n"/>
-      <c r="AA5" s="457" t="n"/>
-      <c r="AB5" s="457" t="n"/>
-      <c r="AC5" s="457" t="n"/>
-      <c r="AD5" s="458" t="n"/>
-      <c r="AE5" s="459" t="n"/>
-      <c r="AF5" s="460" t="n"/>
-      <c r="AG5" s="460" t="n"/>
-      <c r="AH5" s="461" t="n"/>
-      <c r="AI5" s="462" t="n"/>
-      <c r="AJ5" s="463" t="n"/>
-      <c r="AK5" s="463" t="n"/>
-      <c r="AL5" s="463" t="n"/>
-      <c r="AM5" s="463" t="n"/>
-      <c r="AN5" s="464" t="n"/>
+      <c r="A5" s="689" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="690" t="n"/>
+      <c r="I5" s="697" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="690" t="n"/>
+      <c r="AE5" s="691" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="692" t="n"/>
+      <c r="AG5" s="692" t="n"/>
+      <c r="AH5" s="693" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="694" t="n"/>
+      <c r="AK5" s="694" t="n"/>
+      <c r="AL5" s="694" t="n"/>
+      <c r="AM5" s="694" t="n"/>
+      <c r="AN5" s="695" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="524" t="inlineStr">
-        <is>
-          <t>Evidence item 2</t>
-        </is>
-      </c>
-      <c r="B6" s="525" t="inlineStr">
-        <is>
-          <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
-        </is>
-      </c>
-      <c r="C6" s="526" t="inlineStr">
-        <is>
-          <t>Link or reference ID</t>
-        </is>
-      </c>
-      <c r="D6" s="470" t="n"/>
-      <c r="E6" s="470" t="n"/>
-      <c r="F6" s="470" t="n"/>
-      <c r="G6" s="470" t="n"/>
-      <c r="H6" s="470" t="n"/>
-      <c r="I6" s="470" t="n"/>
-      <c r="J6" s="470" t="n"/>
-      <c r="K6" s="470" t="n"/>
-      <c r="L6" s="470" t="n"/>
-      <c r="M6" s="470" t="n"/>
-      <c r="N6" s="470" t="n"/>
-      <c r="O6" s="470" t="n"/>
-      <c r="P6" s="470" t="n"/>
-      <c r="Q6" s="470" t="n"/>
-      <c r="R6" s="470" t="n"/>
-      <c r="S6" s="470" t="n"/>
-      <c r="T6" s="470" t="n"/>
-      <c r="U6" s="470" t="n"/>
-      <c r="V6" s="470" t="n"/>
-      <c r="W6" s="470" t="n"/>
-      <c r="X6" s="470" t="n"/>
-      <c r="Y6" s="470" t="n"/>
-      <c r="Z6" s="470" t="n"/>
-      <c r="AA6" s="470" t="n"/>
-      <c r="AB6" s="470" t="n"/>
-      <c r="AC6" s="470" t="n"/>
-      <c r="AD6" s="470" t="n"/>
-      <c r="AE6" s="470" t="n"/>
-      <c r="AF6" s="470" t="n"/>
-      <c r="AG6" s="470" t="n"/>
-      <c r="AH6" s="470" t="n"/>
-      <c r="AI6" s="470" t="n"/>
-      <c r="AJ6" s="470" t="n"/>
-      <c r="AK6" s="470" t="n"/>
-      <c r="AL6" s="470" t="n"/>
-      <c r="AM6" s="470" t="n"/>
-      <c r="AN6" s="502" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="713" t="n"/>
+      <c r="B6" s="723" t="n"/>
+      <c r="C6" s="723" t="n"/>
+      <c r="D6" s="714" t="n"/>
+      <c r="E6" s="714" t="n"/>
+      <c r="F6" s="714" t="n"/>
+      <c r="G6" s="714" t="n"/>
+      <c r="H6" s="715" t="n"/>
+      <c r="I6" s="714" t="n"/>
+      <c r="J6" s="714" t="n"/>
+      <c r="K6" s="714" t="n"/>
+      <c r="L6" s="714" t="n"/>
+      <c r="M6" s="714" t="n"/>
+      <c r="N6" s="714" t="n"/>
+      <c r="O6" s="714" t="n"/>
+      <c r="P6" s="714" t="n"/>
+      <c r="Q6" s="714" t="n"/>
+      <c r="R6" s="714" t="n"/>
+      <c r="S6" s="714" t="n"/>
+      <c r="T6" s="714" t="n"/>
+      <c r="U6" s="714" t="n"/>
+      <c r="V6" s="714" t="n"/>
+      <c r="W6" s="714" t="n"/>
+      <c r="X6" s="714" t="n"/>
+      <c r="Y6" s="714" t="n"/>
+      <c r="Z6" s="714" t="n"/>
+      <c r="AA6" s="714" t="n"/>
+      <c r="AB6" s="714" t="n"/>
+      <c r="AC6" s="714" t="n"/>
+      <c r="AD6" s="715" t="n"/>
+      <c r="AE6" s="716" t="n"/>
+      <c r="AF6" s="716" t="n"/>
+      <c r="AG6" s="716" t="n"/>
+      <c r="AH6" s="717" t="n"/>
+      <c r="AI6" s="718" t="n"/>
+      <c r="AJ6" s="718" t="n"/>
+      <c r="AK6" s="718" t="n"/>
+      <c r="AL6" s="718" t="n"/>
+      <c r="AM6" s="718" t="n"/>
+      <c r="AN6" s="719" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="527" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B7" s="528" t="inlineStr">
-        <is>
-          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C7" s="529" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D7" s="344" t="n"/>
-      <c r="E7" s="344" t="n"/>
-      <c r="F7" s="344" t="n"/>
-      <c r="G7" s="344" t="n"/>
-      <c r="H7" s="344" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="530" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="706" t="n"/>
+      <c r="C7" s="706" t="n"/>
+      <c r="D7" s="706" t="n"/>
+      <c r="E7" s="706" t="n"/>
+      <c r="F7" s="706" t="n"/>
+      <c r="G7" s="706" t="n"/>
+      <c r="H7" s="722" t="n"/>
+      <c r="I7" s="722" t="n"/>
+      <c r="J7" s="722" t="n"/>
+      <c r="K7" s="722" t="n"/>
+      <c r="L7" s="722" t="n"/>
+      <c r="M7" s="722" t="n"/>
+      <c r="N7" s="722" t="n"/>
+      <c r="O7" s="722" t="n"/>
+      <c r="P7" s="722" t="n"/>
+      <c r="Q7" s="722" t="n"/>
+      <c r="R7" s="722" t="n"/>
+      <c r="S7" s="722" t="n"/>
+      <c r="T7" s="722" t="n"/>
+      <c r="U7" s="722" t="n"/>
+      <c r="V7" s="722" t="n"/>
+      <c r="W7" s="722" t="n"/>
+      <c r="X7" s="722" t="n"/>
+      <c r="Y7" s="722" t="n"/>
+      <c r="Z7" s="722" t="n"/>
+      <c r="AA7" s="722" t="n"/>
+      <c r="AB7" s="722" t="n"/>
+      <c r="AC7" s="722" t="n"/>
+      <c r="AD7" s="722" t="n"/>
+      <c r="AE7" s="722" t="n"/>
+      <c r="AF7" s="722" t="n"/>
+      <c r="AG7" s="722" t="n"/>
+      <c r="AH7" s="722" t="n"/>
+      <c r="AI7" s="722" t="n"/>
+      <c r="AJ7" s="722" t="n"/>
+      <c r="AK7" s="722" t="n"/>
+      <c r="AL7" s="722" t="n"/>
+      <c r="AM7" s="722" t="n"/>
+      <c r="AN7" s="722" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="535" t="inlineStr">
+      <c r="A8" s="727" t="inlineStr">
+        <is>
+          <t>Reference plan / lot / method / release documents from their owning source.</t>
+        </is>
+      </c>
+      <c r="H8" s="668" t="n"/>
+      <c r="I8" s="668" t="n"/>
+      <c r="J8" s="668" t="n"/>
+      <c r="K8" s="668" t="n"/>
+      <c r="L8" s="668" t="n"/>
+      <c r="M8" s="668" t="n"/>
+      <c r="N8" s="668" t="n"/>
+      <c r="O8" s="668" t="n"/>
+      <c r="P8" s="668" t="n"/>
+      <c r="Q8" s="668" t="n"/>
+      <c r="R8" s="668" t="n"/>
+      <c r="S8" s="668" t="n"/>
+      <c r="T8" s="668" t="n"/>
+      <c r="U8" s="668" t="n"/>
+      <c r="V8" s="668" t="n"/>
+      <c r="W8" s="668" t="n"/>
+      <c r="X8" s="668" t="n"/>
+      <c r="Y8" s="668" t="n"/>
+      <c r="Z8" s="668" t="n"/>
+      <c r="AA8" s="668" t="n"/>
+      <c r="AB8" s="668" t="n"/>
+      <c r="AC8" s="668" t="n"/>
+      <c r="AD8" s="668" t="n"/>
+      <c r="AE8" s="668" t="n"/>
+      <c r="AF8" s="668" t="n"/>
+      <c r="AG8" s="668" t="n"/>
+      <c r="AH8" s="668" t="n"/>
+      <c r="AI8" s="668" t="n"/>
+      <c r="AJ8" s="668" t="n"/>
+      <c r="AK8" s="668" t="n"/>
+      <c r="AL8" s="668" t="n"/>
+      <c r="AM8" s="668" t="n"/>
+      <c r="AN8" s="668" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="668" t="n"/>
+      <c r="B9" s="670" t="n"/>
+      <c r="C9" s="670" t="n"/>
+      <c r="D9" s="668" t="n"/>
+      <c r="E9" s="668" t="n"/>
+      <c r="F9" s="668" t="n"/>
+      <c r="G9" s="668" t="n"/>
+      <c r="H9" s="668" t="n"/>
+      <c r="I9" s="668" t="n"/>
+      <c r="J9" s="668" t="n"/>
+      <c r="K9" s="668" t="n"/>
+      <c r="L9" s="668" t="n"/>
+      <c r="M9" s="668" t="n"/>
+      <c r="N9" s="668" t="n"/>
+      <c r="O9" s="668" t="n"/>
+      <c r="P9" s="668" t="n"/>
+      <c r="Q9" s="668" t="n"/>
+      <c r="R9" s="668" t="n"/>
+      <c r="S9" s="668" t="n"/>
+      <c r="T9" s="668" t="n"/>
+      <c r="U9" s="668" t="n"/>
+      <c r="V9" s="668" t="n"/>
+      <c r="W9" s="668" t="n"/>
+      <c r="X9" s="668" t="n"/>
+      <c r="Y9" s="668" t="n"/>
+      <c r="Z9" s="668" t="n"/>
+      <c r="AA9" s="668" t="n"/>
+      <c r="AB9" s="668" t="n"/>
+      <c r="AC9" s="668" t="n"/>
+      <c r="AD9" s="668" t="n"/>
+      <c r="AE9" s="668" t="n"/>
+      <c r="AF9" s="668" t="n"/>
+      <c r="AG9" s="668" t="n"/>
+      <c r="AH9" s="668" t="n"/>
+      <c r="AI9" s="668" t="n"/>
+      <c r="AJ9" s="668" t="n"/>
+      <c r="AK9" s="668" t="n"/>
+      <c r="AL9" s="668" t="n"/>
+      <c r="AM9" s="668" t="n"/>
+      <c r="AN9" s="668" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="728" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B10" s="671" t="inlineStr">
+        <is>
+          <t>Value / Reference</t>
+        </is>
+      </c>
+      <c r="C10" s="671" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D10" s="668" t="n"/>
+      <c r="E10" s="668" t="n"/>
+      <c r="F10" s="668" t="n"/>
+      <c r="G10" s="668" t="n"/>
+      <c r="H10" s="668" t="n"/>
+      <c r="I10" s="668" t="n"/>
+      <c r="J10" s="668" t="n"/>
+      <c r="K10" s="668" t="n"/>
+      <c r="L10" s="668" t="n"/>
+      <c r="M10" s="668" t="n"/>
+      <c r="N10" s="668" t="n"/>
+      <c r="O10" s="668" t="n"/>
+      <c r="P10" s="668" t="n"/>
+      <c r="Q10" s="668" t="n"/>
+      <c r="R10" s="668" t="n"/>
+      <c r="S10" s="668" t="n"/>
+      <c r="T10" s="668" t="n"/>
+      <c r="U10" s="668" t="n"/>
+      <c r="V10" s="668" t="n"/>
+      <c r="W10" s="668" t="n"/>
+      <c r="X10" s="668" t="n"/>
+      <c r="Y10" s="668" t="n"/>
+      <c r="Z10" s="668" t="n"/>
+      <c r="AA10" s="668" t="n"/>
+      <c r="AB10" s="668" t="n"/>
+      <c r="AC10" s="668" t="n"/>
+      <c r="AD10" s="668" t="n"/>
+      <c r="AE10" s="668" t="n"/>
+      <c r="AF10" s="668" t="n"/>
+      <c r="AG10" s="668" t="n"/>
+      <c r="AH10" s="668" t="n"/>
+      <c r="AI10" s="668" t="n"/>
+      <c r="AJ10" s="668" t="n"/>
+      <c r="AK10" s="668" t="n"/>
+      <c r="AL10" s="668" t="n"/>
+      <c r="AM10" s="668" t="n"/>
+      <c r="AN10" s="668" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="730" t="inlineStr">
+        <is>
+          <t>Source of Truth</t>
+        </is>
+      </c>
+      <c r="B11" s="735" t="inlineStr">
+        <is>
+          <t>Epicor transaction + M365 evidence</t>
+        </is>
+      </c>
+      <c r="C11" s="735" t="inlineStr">
+        <is>
+          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+        </is>
+      </c>
+      <c r="D11" s="668" t="n"/>
+      <c r="E11" s="668" t="n"/>
+      <c r="F11" s="668" t="n"/>
+      <c r="G11" s="668" t="n"/>
+      <c r="H11" s="668" t="n"/>
+      <c r="I11" s="668" t="n"/>
+      <c r="J11" s="668" t="n"/>
+      <c r="K11" s="668" t="n"/>
+      <c r="L11" s="668" t="n"/>
+      <c r="M11" s="668" t="n"/>
+      <c r="N11" s="668" t="n"/>
+      <c r="O11" s="668" t="n"/>
+      <c r="P11" s="668" t="n"/>
+      <c r="Q11" s="668" t="n"/>
+      <c r="R11" s="668" t="n"/>
+      <c r="S11" s="668" t="n"/>
+      <c r="T11" s="668" t="n"/>
+      <c r="U11" s="668" t="n"/>
+      <c r="V11" s="668" t="n"/>
+      <c r="W11" s="668" t="n"/>
+      <c r="X11" s="668" t="n"/>
+      <c r="Y11" s="668" t="n"/>
+      <c r="Z11" s="668" t="n"/>
+      <c r="AA11" s="668" t="n"/>
+      <c r="AB11" s="668" t="n"/>
+      <c r="AC11" s="668" t="n"/>
+      <c r="AD11" s="668" t="n"/>
+      <c r="AE11" s="668" t="n"/>
+      <c r="AF11" s="668" t="n"/>
+      <c r="AG11" s="668" t="n"/>
+      <c r="AH11" s="668" t="n"/>
+      <c r="AI11" s="668" t="n"/>
+      <c r="AJ11" s="668" t="n"/>
+      <c r="AK11" s="668" t="n"/>
+      <c r="AL11" s="668" t="n"/>
+      <c r="AM11" s="668" t="n"/>
+      <c r="AN11" s="668" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="731" t="inlineStr">
+        <is>
+          <t>Cross-Reference Boundary</t>
+        </is>
+      </c>
+      <c r="B12" s="736" t="inlineStr">
+        <is>
+          <t>Lot-acceptance sampling record only. Must stay distinct from FRM-631 SPC/capability monitoring and FRM-641 final-release verification. Nonconforming results route to FRM-413/651.</t>
+        </is>
+      </c>
+      <c r="C12" s="737" t="inlineStr">
+        <is>
+          <t>This form does not replace SOP-603; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-603; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+        </is>
+      </c>
+      <c r="D12" s="668" t="n"/>
+      <c r="E12" s="668" t="n"/>
+      <c r="F12" s="668" t="n"/>
+      <c r="G12" s="668" t="n"/>
+      <c r="H12" s="668" t="n"/>
+      <c r="I12" s="668" t="n"/>
+      <c r="J12" s="668" t="n"/>
+      <c r="K12" s="668" t="n"/>
+      <c r="L12" s="668" t="n"/>
+      <c r="M12" s="668" t="n"/>
+      <c r="N12" s="668" t="n"/>
+      <c r="O12" s="668" t="n"/>
+      <c r="P12" s="668" t="n"/>
+      <c r="Q12" s="668" t="n"/>
+      <c r="R12" s="668" t="n"/>
+      <c r="S12" s="668" t="n"/>
+      <c r="T12" s="668" t="n"/>
+      <c r="U12" s="668" t="n"/>
+      <c r="V12" s="668" t="n"/>
+      <c r="W12" s="668" t="n"/>
+      <c r="X12" s="668" t="n"/>
+      <c r="Y12" s="668" t="n"/>
+      <c r="Z12" s="668" t="n"/>
+      <c r="AA12" s="668" t="n"/>
+      <c r="AB12" s="668" t="n"/>
+      <c r="AC12" s="668" t="n"/>
+      <c r="AD12" s="668" t="n"/>
+      <c r="AE12" s="668" t="n"/>
+      <c r="AF12" s="668" t="n"/>
+      <c r="AG12" s="668" t="n"/>
+      <c r="AH12" s="668" t="n"/>
+      <c r="AI12" s="668" t="n"/>
+      <c r="AJ12" s="668" t="n"/>
+      <c r="AK12" s="668" t="n"/>
+      <c r="AL12" s="668" t="n"/>
+      <c r="AM12" s="668" t="n"/>
+      <c r="AN12" s="668" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="732" t="inlineStr">
+        <is>
+          <t>SOP SOP-603</t>
+        </is>
+      </c>
+      <c r="B13" s="738" t="inlineStr">
+        <is>
+          <t>SOP-603 — Lấy mẫu AQL và quyết định chấp nhận lô | HESEM QMS</t>
+        </is>
+      </c>
+      <c r="C13" s="739" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-603-aql-sampling-inspection.html</t>
+        </is>
+      </c>
+      <c r="D13" s="668" t="n"/>
+      <c r="E13" s="668" t="n"/>
+      <c r="F13" s="668" t="n"/>
+      <c r="G13" s="668" t="n"/>
+      <c r="H13" s="668" t="n"/>
+      <c r="I13" s="668" t="n"/>
+      <c r="J13" s="668" t="n"/>
+      <c r="K13" s="668" t="n"/>
+      <c r="L13" s="668" t="n"/>
+      <c r="M13" s="668" t="n"/>
+      <c r="N13" s="668" t="n"/>
+      <c r="O13" s="668" t="n"/>
+      <c r="P13" s="668" t="n"/>
+      <c r="Q13" s="668" t="n"/>
+      <c r="R13" s="668" t="n"/>
+      <c r="S13" s="668" t="n"/>
+      <c r="T13" s="668" t="n"/>
+      <c r="U13" s="668" t="n"/>
+      <c r="V13" s="668" t="n"/>
+      <c r="W13" s="668" t="n"/>
+      <c r="X13" s="668" t="n"/>
+      <c r="Y13" s="668" t="n"/>
+      <c r="Z13" s="668" t="n"/>
+      <c r="AA13" s="668" t="n"/>
+      <c r="AB13" s="668" t="n"/>
+      <c r="AC13" s="668" t="n"/>
+      <c r="AD13" s="668" t="n"/>
+      <c r="AE13" s="668" t="n"/>
+      <c r="AF13" s="668" t="n"/>
+      <c r="AG13" s="668" t="n"/>
+      <c r="AH13" s="668" t="n"/>
+      <c r="AI13" s="668" t="n"/>
+      <c r="AJ13" s="668" t="n"/>
+      <c r="AK13" s="668" t="n"/>
+      <c r="AL13" s="668" t="n"/>
+      <c r="AM13" s="668" t="n"/>
+      <c r="AN13" s="668" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="733" t="inlineStr">
+        <is>
+          <t>WI WI-603</t>
+        </is>
+      </c>
+      <c r="B14" s="740" t="inlineStr">
+        <is>
+          <t>WI-603 — Thực hiện lấy mẫu AQL, chọn mẫu và quyết định accept/reject lô</t>
+        </is>
+      </c>
+      <c r="C14" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-603-aql-sampling-inspection-execution.html</t>
+        </is>
+      </c>
+      <c r="D14" s="668" t="n"/>
+      <c r="E14" s="668" t="n"/>
+      <c r="F14" s="668" t="n"/>
+      <c r="G14" s="668" t="n"/>
+      <c r="H14" s="668" t="n"/>
+      <c r="I14" s="668" t="n"/>
+      <c r="J14" s="668" t="n"/>
+      <c r="K14" s="668" t="n"/>
+      <c r="L14" s="668" t="n"/>
+      <c r="M14" s="668" t="n"/>
+      <c r="N14" s="668" t="n"/>
+      <c r="O14" s="668" t="n"/>
+      <c r="P14" s="668" t="n"/>
+      <c r="Q14" s="668" t="n"/>
+      <c r="R14" s="668" t="n"/>
+      <c r="S14" s="668" t="n"/>
+      <c r="T14" s="668" t="n"/>
+      <c r="U14" s="668" t="n"/>
+      <c r="V14" s="668" t="n"/>
+      <c r="W14" s="668" t="n"/>
+      <c r="X14" s="668" t="n"/>
+      <c r="Y14" s="668" t="n"/>
+      <c r="Z14" s="668" t="n"/>
+      <c r="AA14" s="668" t="n"/>
+      <c r="AB14" s="668" t="n"/>
+      <c r="AC14" s="668" t="n"/>
+      <c r="AD14" s="668" t="n"/>
+      <c r="AE14" s="668" t="n"/>
+      <c r="AF14" s="668" t="n"/>
+      <c r="AG14" s="668" t="n"/>
+      <c r="AH14" s="668" t="n"/>
+      <c r="AI14" s="668" t="n"/>
+      <c r="AJ14" s="668" t="n"/>
+      <c r="AK14" s="668" t="n"/>
+      <c r="AL14" s="668" t="n"/>
+      <c r="AM14" s="668" t="n"/>
+      <c r="AN14" s="668" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-001</t>
+        </is>
+      </c>
+      <c r="B15" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
+        </is>
+      </c>
+      <c r="C15" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
+        </is>
+      </c>
+      <c r="D15" s="668" t="n"/>
+      <c r="E15" s="668" t="n"/>
+      <c r="F15" s="668" t="n"/>
+      <c r="G15" s="668" t="n"/>
+      <c r="H15" s="668" t="n"/>
+      <c r="I15" s="668" t="n"/>
+      <c r="J15" s="668" t="n"/>
+      <c r="K15" s="668" t="n"/>
+      <c r="L15" s="668" t="n"/>
+      <c r="M15" s="668" t="n"/>
+      <c r="N15" s="668" t="n"/>
+      <c r="O15" s="668" t="n"/>
+      <c r="P15" s="668" t="n"/>
+      <c r="Q15" s="668" t="n"/>
+      <c r="R15" s="668" t="n"/>
+      <c r="S15" s="668" t="n"/>
+      <c r="T15" s="668" t="n"/>
+      <c r="U15" s="668" t="n"/>
+      <c r="V15" s="668" t="n"/>
+      <c r="W15" s="668" t="n"/>
+      <c r="X15" s="668" t="n"/>
+      <c r="Y15" s="668" t="n"/>
+      <c r="Z15" s="668" t="n"/>
+      <c r="AA15" s="668" t="n"/>
+      <c r="AB15" s="668" t="n"/>
+      <c r="AC15" s="668" t="n"/>
+      <c r="AD15" s="668" t="n"/>
+      <c r="AE15" s="668" t="n"/>
+      <c r="AF15" s="668" t="n"/>
+      <c r="AG15" s="668" t="n"/>
+      <c r="AH15" s="668" t="n"/>
+      <c r="AI15" s="668" t="n"/>
+      <c r="AJ15" s="668" t="n"/>
+      <c r="AK15" s="668" t="n"/>
+      <c r="AL15" s="668" t="n"/>
+      <c r="AM15" s="668" t="n"/>
+      <c r="AN15" s="668" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-002</t>
+        </is>
+      </c>
+      <c r="B16" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
+        </is>
+      </c>
+      <c r="C16" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
+        </is>
+      </c>
+      <c r="D16" s="668" t="n"/>
+      <c r="E16" s="668" t="n"/>
+      <c r="F16" s="668" t="n"/>
+      <c r="G16" s="668" t="n"/>
+      <c r="H16" s="668" t="n"/>
+      <c r="I16" s="668" t="n"/>
+      <c r="J16" s="668" t="n"/>
+      <c r="K16" s="668" t="n"/>
+      <c r="L16" s="668" t="n"/>
+      <c r="M16" s="668" t="n"/>
+      <c r="N16" s="668" t="n"/>
+      <c r="O16" s="668" t="n"/>
+      <c r="P16" s="668" t="n"/>
+      <c r="Q16" s="668" t="n"/>
+      <c r="R16" s="668" t="n"/>
+      <c r="S16" s="668" t="n"/>
+      <c r="T16" s="668" t="n"/>
+      <c r="U16" s="668" t="n"/>
+      <c r="V16" s="668" t="n"/>
+      <c r="W16" s="668" t="n"/>
+      <c r="X16" s="668" t="n"/>
+      <c r="Y16" s="668" t="n"/>
+      <c r="Z16" s="668" t="n"/>
+      <c r="AA16" s="668" t="n"/>
+      <c r="AB16" s="668" t="n"/>
+      <c r="AC16" s="668" t="n"/>
+      <c r="AD16" s="668" t="n"/>
+      <c r="AE16" s="668" t="n"/>
+      <c r="AF16" s="668" t="n"/>
+      <c r="AG16" s="668" t="n"/>
+      <c r="AH16" s="668" t="n"/>
+      <c r="AI16" s="668" t="n"/>
+      <c r="AJ16" s="668" t="n"/>
+      <c r="AK16" s="668" t="n"/>
+      <c r="AL16" s="668" t="n"/>
+      <c r="AM16" s="668" t="n"/>
+      <c r="AN16" s="668" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-003</t>
+        </is>
+      </c>
+      <c r="B17" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
+        </is>
+      </c>
+      <c r="C17" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
+        </is>
+      </c>
+      <c r="D17" s="668" t="n"/>
+      <c r="E17" s="668" t="n"/>
+      <c r="F17" s="668" t="n"/>
+      <c r="G17" s="668" t="n"/>
+      <c r="H17" s="668" t="n"/>
+      <c r="I17" s="668" t="n"/>
+      <c r="J17" s="668" t="n"/>
+      <c r="K17" s="668" t="n"/>
+      <c r="L17" s="668" t="n"/>
+      <c r="M17" s="668" t="n"/>
+      <c r="N17" s="668" t="n"/>
+      <c r="O17" s="668" t="n"/>
+      <c r="P17" s="668" t="n"/>
+      <c r="Q17" s="668" t="n"/>
+      <c r="R17" s="668" t="n"/>
+      <c r="S17" s="668" t="n"/>
+      <c r="T17" s="668" t="n"/>
+      <c r="U17" s="668" t="n"/>
+      <c r="V17" s="668" t="n"/>
+      <c r="W17" s="668" t="n"/>
+      <c r="X17" s="668" t="n"/>
+      <c r="Y17" s="668" t="n"/>
+      <c r="Z17" s="668" t="n"/>
+      <c r="AA17" s="668" t="n"/>
+      <c r="AB17" s="668" t="n"/>
+      <c r="AC17" s="668" t="n"/>
+      <c r="AD17" s="668" t="n"/>
+      <c r="AE17" s="668" t="n"/>
+      <c r="AF17" s="668" t="n"/>
+      <c r="AG17" s="668" t="n"/>
+      <c r="AH17" s="668" t="n"/>
+      <c r="AI17" s="668" t="n"/>
+      <c r="AJ17" s="668" t="n"/>
+      <c r="AK17" s="668" t="n"/>
+      <c r="AL17" s="668" t="n"/>
+      <c r="AM17" s="668" t="n"/>
+      <c r="AN17" s="668" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-004</t>
+        </is>
+      </c>
+      <c r="B18" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
+        </is>
+      </c>
+      <c r="C18" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
+        </is>
+      </c>
+      <c r="D18" s="668" t="n"/>
+      <c r="E18" s="668" t="n"/>
+      <c r="F18" s="668" t="n"/>
+      <c r="G18" s="668" t="n"/>
+      <c r="H18" s="668" t="n"/>
+      <c r="I18" s="668" t="n"/>
+      <c r="J18" s="668" t="n"/>
+      <c r="K18" s="668" t="n"/>
+      <c r="L18" s="668" t="n"/>
+      <c r="M18" s="668" t="n"/>
+      <c r="N18" s="668" t="n"/>
+      <c r="O18" s="668" t="n"/>
+      <c r="P18" s="668" t="n"/>
+      <c r="Q18" s="668" t="n"/>
+      <c r="R18" s="668" t="n"/>
+      <c r="S18" s="668" t="n"/>
+      <c r="T18" s="668" t="n"/>
+      <c r="U18" s="668" t="n"/>
+      <c r="V18" s="668" t="n"/>
+      <c r="W18" s="668" t="n"/>
+      <c r="X18" s="668" t="n"/>
+      <c r="Y18" s="668" t="n"/>
+      <c r="Z18" s="668" t="n"/>
+      <c r="AA18" s="668" t="n"/>
+      <c r="AB18" s="668" t="n"/>
+      <c r="AC18" s="668" t="n"/>
+      <c r="AD18" s="668" t="n"/>
+      <c r="AE18" s="668" t="n"/>
+      <c r="AF18" s="668" t="n"/>
+      <c r="AG18" s="668" t="n"/>
+      <c r="AH18" s="668" t="n"/>
+      <c r="AI18" s="668" t="n"/>
+      <c r="AJ18" s="668" t="n"/>
+      <c r="AK18" s="668" t="n"/>
+      <c r="AL18" s="668" t="n"/>
+      <c r="AM18" s="668" t="n"/>
+      <c r="AN18" s="668" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-006</t>
+        </is>
+      </c>
+      <c r="B19" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
+        </is>
+      </c>
+      <c r="C19" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
+        </is>
+      </c>
+      <c r="D19" s="668" t="n"/>
+      <c r="E19" s="668" t="n"/>
+      <c r="F19" s="668" t="n"/>
+      <c r="G19" s="668" t="n"/>
+      <c r="H19" s="668" t="n"/>
+      <c r="I19" s="668" t="n"/>
+      <c r="J19" s="668" t="n"/>
+      <c r="K19" s="668" t="n"/>
+      <c r="L19" s="668" t="n"/>
+      <c r="M19" s="668" t="n"/>
+      <c r="N19" s="668" t="n"/>
+      <c r="O19" s="668" t="n"/>
+      <c r="P19" s="668" t="n"/>
+      <c r="Q19" s="668" t="n"/>
+      <c r="R19" s="668" t="n"/>
+      <c r="S19" s="668" t="n"/>
+      <c r="T19" s="668" t="n"/>
+      <c r="U19" s="668" t="n"/>
+      <c r="V19" s="668" t="n"/>
+      <c r="W19" s="668" t="n"/>
+      <c r="X19" s="668" t="n"/>
+      <c r="Y19" s="668" t="n"/>
+      <c r="Z19" s="668" t="n"/>
+      <c r="AA19" s="668" t="n"/>
+      <c r="AB19" s="668" t="n"/>
+      <c r="AC19" s="668" t="n"/>
+      <c r="AD19" s="668" t="n"/>
+      <c r="AE19" s="668" t="n"/>
+      <c r="AF19" s="668" t="n"/>
+      <c r="AG19" s="668" t="n"/>
+      <c r="AH19" s="668" t="n"/>
+      <c r="AI19" s="668" t="n"/>
+      <c r="AJ19" s="668" t="n"/>
+      <c r="AK19" s="668" t="n"/>
+      <c r="AL19" s="668" t="n"/>
+      <c r="AM19" s="668" t="n"/>
+      <c r="AN19" s="668" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="733" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-007</t>
+        </is>
+      </c>
+      <c r="B20" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+        </is>
+      </c>
+      <c r="C20" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+        </is>
+      </c>
+      <c r="D20" s="668" t="n"/>
+      <c r="E20" s="668" t="n"/>
+      <c r="F20" s="668" t="n"/>
+      <c r="G20" s="668" t="n"/>
+      <c r="H20" s="668" t="n"/>
+      <c r="I20" s="668" t="n"/>
+      <c r="J20" s="668" t="n"/>
+      <c r="K20" s="668" t="n"/>
+      <c r="L20" s="668" t="n"/>
+      <c r="M20" s="668" t="n"/>
+      <c r="N20" s="668" t="n"/>
+      <c r="O20" s="668" t="n"/>
+      <c r="P20" s="668" t="n"/>
+      <c r="Q20" s="668" t="n"/>
+      <c r="R20" s="668" t="n"/>
+      <c r="S20" s="668" t="n"/>
+      <c r="T20" s="668" t="n"/>
+      <c r="U20" s="668" t="n"/>
+      <c r="V20" s="668" t="n"/>
+      <c r="W20" s="668" t="n"/>
+      <c r="X20" s="668" t="n"/>
+      <c r="Y20" s="668" t="n"/>
+      <c r="Z20" s="668" t="n"/>
+      <c r="AA20" s="668" t="n"/>
+      <c r="AB20" s="668" t="n"/>
+      <c r="AC20" s="668" t="n"/>
+      <c r="AD20" s="668" t="n"/>
+      <c r="AE20" s="668" t="n"/>
+      <c r="AF20" s="668" t="n"/>
+      <c r="AG20" s="668" t="n"/>
+      <c r="AH20" s="668" t="n"/>
+      <c r="AI20" s="668" t="n"/>
+      <c r="AJ20" s="668" t="n"/>
+      <c r="AK20" s="668" t="n"/>
+      <c r="AL20" s="668" t="n"/>
+      <c r="AM20" s="668" t="n"/>
+      <c r="AN20" s="668" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="734" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QMS-020</t>
+        </is>
+      </c>
+      <c r="B21" s="744" t="inlineStr">
+        <is>
+          <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
+        </is>
+      </c>
+      <c r="C21" s="745" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
+        </is>
+      </c>
+      <c r="D21" s="668" t="n"/>
+      <c r="E21" s="668" t="n"/>
+      <c r="F21" s="668" t="n"/>
+      <c r="G21" s="668" t="n"/>
+      <c r="H21" s="668" t="n"/>
+      <c r="I21" s="668" t="n"/>
+      <c r="J21" s="668" t="n"/>
+      <c r="K21" s="668" t="n"/>
+      <c r="L21" s="668" t="n"/>
+      <c r="M21" s="668" t="n"/>
+      <c r="N21" s="668" t="n"/>
+      <c r="O21" s="668" t="n"/>
+      <c r="P21" s="668" t="n"/>
+      <c r="Q21" s="668" t="n"/>
+      <c r="R21" s="668" t="n"/>
+      <c r="S21" s="668" t="n"/>
+      <c r="T21" s="668" t="n"/>
+      <c r="U21" s="668" t="n"/>
+      <c r="V21" s="668" t="n"/>
+      <c r="W21" s="668" t="n"/>
+      <c r="X21" s="668" t="n"/>
+      <c r="Y21" s="668" t="n"/>
+      <c r="Z21" s="668" t="n"/>
+      <c r="AA21" s="668" t="n"/>
+      <c r="AB21" s="668" t="n"/>
+      <c r="AC21" s="668" t="n"/>
+      <c r="AD21" s="668" t="n"/>
+      <c r="AE21" s="668" t="n"/>
+      <c r="AF21" s="668" t="n"/>
+      <c r="AG21" s="668" t="n"/>
+      <c r="AH21" s="668" t="n"/>
+      <c r="AI21" s="668" t="n"/>
+      <c r="AJ21" s="668" t="n"/>
+      <c r="AK21" s="668" t="n"/>
+      <c r="AL21" s="668" t="n"/>
+      <c r="AM21" s="668" t="n"/>
+      <c r="AN21" s="668" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="668" t="n"/>
+      <c r="B22" s="668" t="n"/>
+      <c r="C22" s="668" t="n"/>
+      <c r="D22" s="668" t="n"/>
+      <c r="E22" s="668" t="n"/>
+      <c r="F22" s="668" t="n"/>
+      <c r="G22" s="668" t="n"/>
+      <c r="H22" s="668" t="n"/>
+      <c r="I22" s="668" t="n"/>
+      <c r="J22" s="668" t="n"/>
+      <c r="K22" s="668" t="n"/>
+      <c r="L22" s="668" t="n"/>
+      <c r="M22" s="668" t="n"/>
+      <c r="N22" s="668" t="n"/>
+      <c r="O22" s="668" t="n"/>
+      <c r="P22" s="668" t="n"/>
+      <c r="Q22" s="668" t="n"/>
+      <c r="R22" s="668" t="n"/>
+      <c r="S22" s="668" t="n"/>
+      <c r="T22" s="668" t="n"/>
+      <c r="U22" s="668" t="n"/>
+      <c r="V22" s="668" t="n"/>
+      <c r="W22" s="668" t="n"/>
+      <c r="X22" s="668" t="n"/>
+      <c r="Y22" s="668" t="n"/>
+      <c r="Z22" s="668" t="n"/>
+      <c r="AA22" s="668" t="n"/>
+      <c r="AB22" s="668" t="n"/>
+      <c r="AC22" s="668" t="n"/>
+      <c r="AD22" s="668" t="n"/>
+      <c r="AE22" s="668" t="n"/>
+      <c r="AF22" s="668" t="n"/>
+      <c r="AG22" s="668" t="n"/>
+      <c r="AH22" s="668" t="n"/>
+      <c r="AI22" s="668" t="n"/>
+      <c r="AJ22" s="668" t="n"/>
+      <c r="AK22" s="668" t="n"/>
+      <c r="AL22" s="668" t="n"/>
+      <c r="AM22" s="668" t="n"/>
+      <c r="AN22" s="668" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="668" t="n"/>
+      <c r="B23" s="668" t="n"/>
+      <c r="C23" s="668" t="n"/>
+      <c r="D23" s="668" t="n"/>
+      <c r="E23" s="668" t="n"/>
+      <c r="F23" s="668" t="n"/>
+      <c r="G23" s="668" t="n"/>
+      <c r="H23" s="668" t="n"/>
+      <c r="I23" s="668" t="n"/>
+      <c r="J23" s="668" t="n"/>
+      <c r="K23" s="668" t="n"/>
+      <c r="L23" s="668" t="n"/>
+      <c r="M23" s="668" t="n"/>
+      <c r="N23" s="668" t="n"/>
+      <c r="O23" s="668" t="n"/>
+      <c r="P23" s="668" t="n"/>
+      <c r="Q23" s="668" t="n"/>
+      <c r="R23" s="668" t="n"/>
+      <c r="S23" s="668" t="n"/>
+      <c r="T23" s="668" t="n"/>
+      <c r="U23" s="668" t="n"/>
+      <c r="V23" s="668" t="n"/>
+      <c r="W23" s="668" t="n"/>
+      <c r="X23" s="668" t="n"/>
+      <c r="Y23" s="668" t="n"/>
+      <c r="Z23" s="668" t="n"/>
+      <c r="AA23" s="668" t="n"/>
+      <c r="AB23" s="668" t="n"/>
+      <c r="AC23" s="668" t="n"/>
+      <c r="AD23" s="668" t="n"/>
+      <c r="AE23" s="668" t="n"/>
+      <c r="AF23" s="668" t="n"/>
+      <c r="AG23" s="668" t="n"/>
+      <c r="AH23" s="668" t="n"/>
+      <c r="AI23" s="668" t="n"/>
+      <c r="AJ23" s="668" t="n"/>
+      <c r="AK23" s="668" t="n"/>
+      <c r="AL23" s="668" t="n"/>
+      <c r="AM23" s="668" t="n"/>
+      <c r="AN23" s="668" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="668" t="n"/>
+      <c r="B24" s="668" t="n"/>
+      <c r="C24" s="668" t="n"/>
+      <c r="D24" s="668" t="n"/>
+      <c r="E24" s="668" t="n"/>
+      <c r="F24" s="668" t="n"/>
+      <c r="G24" s="668" t="n"/>
+      <c r="H24" s="668" t="n"/>
+      <c r="I24" s="668" t="n"/>
+      <c r="J24" s="668" t="n"/>
+      <c r="K24" s="668" t="n"/>
+      <c r="L24" s="668" t="n"/>
+      <c r="M24" s="668" t="n"/>
+      <c r="N24" s="668" t="n"/>
+      <c r="O24" s="668" t="n"/>
+      <c r="P24" s="668" t="n"/>
+      <c r="Q24" s="668" t="n"/>
+      <c r="R24" s="668" t="n"/>
+      <c r="S24" s="668" t="n"/>
+      <c r="T24" s="668" t="n"/>
+      <c r="U24" s="668" t="n"/>
+      <c r="V24" s="668" t="n"/>
+      <c r="W24" s="668" t="n"/>
+      <c r="X24" s="668" t="n"/>
+      <c r="Y24" s="668" t="n"/>
+      <c r="Z24" s="668" t="n"/>
+      <c r="AA24" s="668" t="n"/>
+      <c r="AB24" s="668" t="n"/>
+      <c r="AC24" s="668" t="n"/>
+      <c r="AD24" s="668" t="n"/>
+      <c r="AE24" s="668" t="n"/>
+      <c r="AF24" s="668" t="n"/>
+      <c r="AG24" s="668" t="n"/>
+      <c r="AH24" s="668" t="n"/>
+      <c r="AI24" s="668" t="n"/>
+      <c r="AJ24" s="668" t="n"/>
+      <c r="AK24" s="668" t="n"/>
+      <c r="AL24" s="668" t="n"/>
+      <c r="AM24" s="668" t="n"/>
+      <c r="AN24" s="668" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C15"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" hidden="1">
+      <c r="A1" s="709" t="n"/>
+      <c r="B1" s="603" t="n"/>
+      <c r="C1" s="603" t="n"/>
+      <c r="D1" s="603" t="n"/>
+      <c r="E1" s="603" t="n"/>
+      <c r="F1" s="603" t="n"/>
+      <c r="G1" s="603" t="n"/>
+      <c r="H1" s="710" t="n"/>
+      <c r="I1" s="711" t="inlineStr">
+        <is>
+          <t>AQL Inspection Record</t>
+        </is>
+      </c>
+      <c r="J1" s="603" t="n"/>
+      <c r="K1" s="603" t="n"/>
+      <c r="L1" s="603" t="n"/>
+      <c r="M1" s="603" t="n"/>
+      <c r="N1" s="603" t="n"/>
+      <c r="O1" s="603" t="n"/>
+      <c r="P1" s="603" t="n"/>
+      <c r="Q1" s="603" t="n"/>
+      <c r="R1" s="603" t="n"/>
+      <c r="S1" s="603" t="n"/>
+      <c r="T1" s="603" t="n"/>
+      <c r="U1" s="603" t="n"/>
+      <c r="V1" s="603" t="n"/>
+      <c r="W1" s="603" t="n"/>
+      <c r="X1" s="603" t="n"/>
+      <c r="Y1" s="603" t="n"/>
+      <c r="Z1" s="603" t="n"/>
+      <c r="AA1" s="603" t="n"/>
+      <c r="AB1" s="603" t="n"/>
+      <c r="AC1" s="603" t="n"/>
+      <c r="AD1" s="710" t="n"/>
+      <c r="AE1" s="435" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="603" t="n"/>
+      <c r="AG1" s="603" t="n"/>
+      <c r="AH1" s="712" t="n"/>
+      <c r="AI1" s="438" t="inlineStr">
+        <is>
+          <t>FRM-621</t>
+        </is>
+      </c>
+      <c r="AJ1" s="603" t="n"/>
+      <c r="AK1" s="603" t="n"/>
+      <c r="AL1" s="603" t="n"/>
+      <c r="AM1" s="603" t="n"/>
+      <c r="AN1" s="710" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="682" t="n"/>
+      <c r="C2" s="682" t="n"/>
+      <c r="D2" s="682" t="n"/>
+      <c r="E2" s="682" t="n"/>
+      <c r="F2" s="682" t="n"/>
+      <c r="G2" s="682" t="n"/>
+      <c r="H2" s="683" t="n"/>
+      <c r="I2" s="682" t="n"/>
+      <c r="J2" s="682" t="n"/>
+      <c r="K2" s="682" t="n"/>
+      <c r="L2" s="682" t="n"/>
+      <c r="M2" s="682" t="n"/>
+      <c r="N2" s="682" t="n"/>
+      <c r="O2" s="682" t="n"/>
+      <c r="P2" s="682" t="n"/>
+      <c r="Q2" s="682" t="n"/>
+      <c r="R2" s="682" t="n"/>
+      <c r="S2" s="682" t="n"/>
+      <c r="T2" s="682" t="n"/>
+      <c r="U2" s="682" t="n"/>
+      <c r="V2" s="682" t="n"/>
+      <c r="W2" s="682" t="n"/>
+      <c r="X2" s="682" t="n"/>
+      <c r="Y2" s="682" t="n"/>
+      <c r="Z2" s="682" t="n"/>
+      <c r="AA2" s="682" t="n"/>
+      <c r="AB2" s="682" t="n"/>
+      <c r="AC2" s="682" t="n"/>
+      <c r="AD2" s="683" t="n"/>
+      <c r="AE2" s="684" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="685" t="n"/>
+      <c r="AG2" s="685" t="n"/>
+      <c r="AH2" s="686" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="687" t="n"/>
+      <c r="AK2" s="687" t="n"/>
+      <c r="AL2" s="687" t="n"/>
+      <c r="AM2" s="687" t="n"/>
+      <c r="AN2" s="688" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="689" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="690" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="690" t="n"/>
+      <c r="AE3" s="691" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="692" t="n"/>
+      <c r="AG3" s="692" t="n"/>
+      <c r="AH3" s="693" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="694" t="n"/>
+      <c r="AK3" s="694" t="n"/>
+      <c r="AL3" s="694" t="n"/>
+      <c r="AM3" s="694" t="n"/>
+      <c r="AN3" s="695" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="689" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="690" t="n"/>
+      <c r="I4" s="696" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="690" t="n"/>
+      <c r="AE4" s="691" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="692" t="n"/>
+      <c r="AG4" s="692" t="n"/>
+      <c r="AH4" s="693" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="694" t="n"/>
+      <c r="AK4" s="694" t="n"/>
+      <c r="AL4" s="694" t="n"/>
+      <c r="AM4" s="694" t="n"/>
+      <c r="AN4" s="695" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="689" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="690" t="n"/>
+      <c r="I5" s="697" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="690" t="n"/>
+      <c r="AE5" s="691" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="692" t="n"/>
+      <c r="AG5" s="692" t="n"/>
+      <c r="AH5" s="693" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="694" t="n"/>
+      <c r="AK5" s="694" t="n"/>
+      <c r="AL5" s="694" t="n"/>
+      <c r="AM5" s="694" t="n"/>
+      <c r="AN5" s="695" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="713" t="n"/>
+      <c r="B6" s="723" t="n"/>
+      <c r="C6" s="723" t="n"/>
+      <c r="D6" s="714" t="n"/>
+      <c r="E6" s="714" t="n"/>
+      <c r="F6" s="714" t="n"/>
+      <c r="G6" s="714" t="n"/>
+      <c r="H6" s="715" t="n"/>
+      <c r="I6" s="714" t="n"/>
+      <c r="J6" s="714" t="n"/>
+      <c r="K6" s="714" t="n"/>
+      <c r="L6" s="714" t="n"/>
+      <c r="M6" s="714" t="n"/>
+      <c r="N6" s="714" t="n"/>
+      <c r="O6" s="714" t="n"/>
+      <c r="P6" s="714" t="n"/>
+      <c r="Q6" s="714" t="n"/>
+      <c r="R6" s="714" t="n"/>
+      <c r="S6" s="714" t="n"/>
+      <c r="T6" s="714" t="n"/>
+      <c r="U6" s="714" t="n"/>
+      <c r="V6" s="714" t="n"/>
+      <c r="W6" s="714" t="n"/>
+      <c r="X6" s="714" t="n"/>
+      <c r="Y6" s="714" t="n"/>
+      <c r="Z6" s="714" t="n"/>
+      <c r="AA6" s="714" t="n"/>
+      <c r="AB6" s="714" t="n"/>
+      <c r="AC6" s="714" t="n"/>
+      <c r="AD6" s="715" t="n"/>
+      <c r="AE6" s="716" t="n"/>
+      <c r="AF6" s="716" t="n"/>
+      <c r="AG6" s="716" t="n"/>
+      <c r="AH6" s="717" t="n"/>
+      <c r="AI6" s="718" t="n"/>
+      <c r="AJ6" s="718" t="n"/>
+      <c r="AK6" s="718" t="n"/>
+      <c r="AL6" s="718" t="n"/>
+      <c r="AM6" s="718" t="n"/>
+      <c r="AN6" s="719" t="n"/>
+    </row>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="706" t="n"/>
+      <c r="C7" s="706" t="n"/>
+      <c r="D7" s="706" t="n"/>
+      <c r="E7" s="706" t="n"/>
+      <c r="F7" s="706" t="n"/>
+      <c r="G7" s="706" t="n"/>
+      <c r="H7" s="722" t="n"/>
+      <c r="I7" s="722" t="n"/>
+      <c r="J7" s="722" t="n"/>
+      <c r="K7" s="722" t="n"/>
+      <c r="L7" s="722" t="n"/>
+      <c r="M7" s="722" t="n"/>
+      <c r="N7" s="722" t="n"/>
+      <c r="O7" s="722" t="n"/>
+      <c r="P7" s="722" t="n"/>
+      <c r="Q7" s="722" t="n"/>
+      <c r="R7" s="722" t="n"/>
+      <c r="S7" s="722" t="n"/>
+      <c r="T7" s="722" t="n"/>
+      <c r="U7" s="722" t="n"/>
+      <c r="V7" s="722" t="n"/>
+      <c r="W7" s="722" t="n"/>
+      <c r="X7" s="722" t="n"/>
+      <c r="Y7" s="722" t="n"/>
+      <c r="Z7" s="722" t="n"/>
+      <c r="AA7" s="722" t="n"/>
+      <c r="AB7" s="722" t="n"/>
+      <c r="AC7" s="722" t="n"/>
+      <c r="AD7" s="722" t="n"/>
+      <c r="AE7" s="722" t="n"/>
+      <c r="AF7" s="722" t="n"/>
+      <c r="AG7" s="722" t="n"/>
+      <c r="AH7" s="722" t="n"/>
+      <c r="AI7" s="722" t="n"/>
+      <c r="AJ7" s="722" t="n"/>
+      <c r="AK7" s="722" t="n"/>
+      <c r="AL7" s="722" t="n"/>
+      <c r="AM7" s="722" t="n"/>
+      <c r="AN7" s="722" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="727" t="inlineStr">
+        <is>
+          <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
+        </is>
+      </c>
+      <c r="H8" s="668" t="n"/>
+      <c r="I8" s="668" t="n"/>
+      <c r="J8" s="668" t="n"/>
+      <c r="K8" s="668" t="n"/>
+      <c r="L8" s="668" t="n"/>
+      <c r="M8" s="668" t="n"/>
+      <c r="N8" s="668" t="n"/>
+      <c r="O8" s="668" t="n"/>
+      <c r="P8" s="668" t="n"/>
+      <c r="Q8" s="668" t="n"/>
+      <c r="R8" s="668" t="n"/>
+      <c r="S8" s="668" t="n"/>
+      <c r="T8" s="668" t="n"/>
+      <c r="U8" s="668" t="n"/>
+      <c r="V8" s="668" t="n"/>
+      <c r="W8" s="668" t="n"/>
+      <c r="X8" s="668" t="n"/>
+      <c r="Y8" s="668" t="n"/>
+      <c r="Z8" s="668" t="n"/>
+      <c r="AA8" s="668" t="n"/>
+      <c r="AB8" s="668" t="n"/>
+      <c r="AC8" s="668" t="n"/>
+      <c r="AD8" s="668" t="n"/>
+      <c r="AE8" s="668" t="n"/>
+      <c r="AF8" s="668" t="n"/>
+      <c r="AG8" s="668" t="n"/>
+      <c r="AH8" s="668" t="n"/>
+      <c r="AI8" s="668" t="n"/>
+      <c r="AJ8" s="668" t="n"/>
+      <c r="AK8" s="668" t="n"/>
+      <c r="AL8" s="668" t="n"/>
+      <c r="AM8" s="668" t="n"/>
+      <c r="AN8" s="668" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="668" t="n"/>
+      <c r="B9" s="668" t="n"/>
+      <c r="C9" s="668" t="n"/>
+      <c r="D9" s="668" t="n"/>
+      <c r="E9" s="668" t="n"/>
+      <c r="F9" s="668" t="n"/>
+      <c r="G9" s="668" t="n"/>
+      <c r="H9" s="668" t="n"/>
+      <c r="I9" s="668" t="n"/>
+      <c r="J9" s="668" t="n"/>
+      <c r="K9" s="668" t="n"/>
+      <c r="L9" s="668" t="n"/>
+      <c r="M9" s="668" t="n"/>
+      <c r="N9" s="668" t="n"/>
+      <c r="O9" s="668" t="n"/>
+      <c r="P9" s="668" t="n"/>
+      <c r="Q9" s="668" t="n"/>
+      <c r="R9" s="668" t="n"/>
+      <c r="S9" s="668" t="n"/>
+      <c r="T9" s="668" t="n"/>
+      <c r="U9" s="668" t="n"/>
+      <c r="V9" s="668" t="n"/>
+      <c r="W9" s="668" t="n"/>
+      <c r="X9" s="668" t="n"/>
+      <c r="Y9" s="668" t="n"/>
+      <c r="Z9" s="668" t="n"/>
+      <c r="AA9" s="668" t="n"/>
+      <c r="AB9" s="668" t="n"/>
+      <c r="AC9" s="668" t="n"/>
+      <c r="AD9" s="668" t="n"/>
+      <c r="AE9" s="668" t="n"/>
+      <c r="AF9" s="668" t="n"/>
+      <c r="AG9" s="668" t="n"/>
+      <c r="AH9" s="668" t="n"/>
+      <c r="AI9" s="668" t="n"/>
+      <c r="AJ9" s="668" t="n"/>
+      <c r="AK9" s="668" t="n"/>
+      <c r="AL9" s="668" t="n"/>
+      <c r="AM9" s="668" t="n"/>
+      <c r="AN9" s="668" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="728" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B10" s="519" t="inlineStr">
+        <is>
+          <t>Value / Reference</t>
+        </is>
+      </c>
+      <c r="C10" s="519" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D10" s="668" t="n"/>
+      <c r="E10" s="668" t="n"/>
+      <c r="F10" s="668" t="n"/>
+      <c r="G10" s="668" t="n"/>
+      <c r="H10" s="668" t="n"/>
+      <c r="I10" s="668" t="n"/>
+      <c r="J10" s="668" t="n"/>
+      <c r="K10" s="668" t="n"/>
+      <c r="L10" s="668" t="n"/>
+      <c r="M10" s="668" t="n"/>
+      <c r="N10" s="668" t="n"/>
+      <c r="O10" s="668" t="n"/>
+      <c r="P10" s="668" t="n"/>
+      <c r="Q10" s="668" t="n"/>
+      <c r="R10" s="668" t="n"/>
+      <c r="S10" s="668" t="n"/>
+      <c r="T10" s="668" t="n"/>
+      <c r="U10" s="668" t="n"/>
+      <c r="V10" s="668" t="n"/>
+      <c r="W10" s="668" t="n"/>
+      <c r="X10" s="668" t="n"/>
+      <c r="Y10" s="668" t="n"/>
+      <c r="Z10" s="668" t="n"/>
+      <c r="AA10" s="668" t="n"/>
+      <c r="AB10" s="668" t="n"/>
+      <c r="AC10" s="668" t="n"/>
+      <c r="AD10" s="668" t="n"/>
+      <c r="AE10" s="668" t="n"/>
+      <c r="AF10" s="668" t="n"/>
+      <c r="AG10" s="668" t="n"/>
+      <c r="AH10" s="668" t="n"/>
+      <c r="AI10" s="668" t="n"/>
+      <c r="AJ10" s="668" t="n"/>
+      <c r="AK10" s="668" t="n"/>
+      <c r="AL10" s="668" t="n"/>
+      <c r="AM10" s="668" t="n"/>
+      <c r="AN10" s="668" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="730" t="inlineStr">
+        <is>
+          <t>Evidence item 1</t>
+        </is>
+      </c>
+      <c r="B11" s="746" t="inlineStr">
+        <is>
+          <t>Reference to the correct evidence folder, shared location or dossier package.</t>
+        </is>
+      </c>
+      <c r="C11" s="746" t="inlineStr">
+        <is>
+          <t>Link or reference ID</t>
+        </is>
+      </c>
+      <c r="D11" s="668" t="n"/>
+      <c r="E11" s="668" t="n"/>
+      <c r="F11" s="668" t="n"/>
+      <c r="G11" s="668" t="n"/>
+      <c r="H11" s="668" t="n"/>
+      <c r="I11" s="668" t="n"/>
+      <c r="J11" s="668" t="n"/>
+      <c r="K11" s="668" t="n"/>
+      <c r="L11" s="668" t="n"/>
+      <c r="M11" s="668" t="n"/>
+      <c r="N11" s="668" t="n"/>
+      <c r="O11" s="668" t="n"/>
+      <c r="P11" s="668" t="n"/>
+      <c r="Q11" s="668" t="n"/>
+      <c r="R11" s="668" t="n"/>
+      <c r="S11" s="668" t="n"/>
+      <c r="T11" s="668" t="n"/>
+      <c r="U11" s="668" t="n"/>
+      <c r="V11" s="668" t="n"/>
+      <c r="W11" s="668" t="n"/>
+      <c r="X11" s="668" t="n"/>
+      <c r="Y11" s="668" t="n"/>
+      <c r="Z11" s="668" t="n"/>
+      <c r="AA11" s="668" t="n"/>
+      <c r="AB11" s="668" t="n"/>
+      <c r="AC11" s="668" t="n"/>
+      <c r="AD11" s="668" t="n"/>
+      <c r="AE11" s="668" t="n"/>
+      <c r="AF11" s="668" t="n"/>
+      <c r="AG11" s="668" t="n"/>
+      <c r="AH11" s="668" t="n"/>
+      <c r="AI11" s="668" t="n"/>
+      <c r="AJ11" s="668" t="n"/>
+      <c r="AK11" s="668" t="n"/>
+      <c r="AL11" s="668" t="n"/>
+      <c r="AM11" s="668" t="n"/>
+      <c r="AN11" s="668" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="731" t="inlineStr">
+        <is>
+          <t>Evidence item 2</t>
+        </is>
+      </c>
+      <c r="B12" s="747" t="inlineStr">
+        <is>
+          <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
+        </is>
+      </c>
+      <c r="C12" s="748" t="inlineStr">
+        <is>
+          <t>Link or reference ID</t>
+        </is>
+      </c>
+      <c r="D12" s="668" t="n"/>
+      <c r="E12" s="668" t="n"/>
+      <c r="F12" s="668" t="n"/>
+      <c r="G12" s="668" t="n"/>
+      <c r="H12" s="668" t="n"/>
+      <c r="I12" s="668" t="n"/>
+      <c r="J12" s="668" t="n"/>
+      <c r="K12" s="668" t="n"/>
+      <c r="L12" s="668" t="n"/>
+      <c r="M12" s="668" t="n"/>
+      <c r="N12" s="668" t="n"/>
+      <c r="O12" s="668" t="n"/>
+      <c r="P12" s="668" t="n"/>
+      <c r="Q12" s="668" t="n"/>
+      <c r="R12" s="668" t="n"/>
+      <c r="S12" s="668" t="n"/>
+      <c r="T12" s="668" t="n"/>
+      <c r="U12" s="668" t="n"/>
+      <c r="V12" s="668" t="n"/>
+      <c r="W12" s="668" t="n"/>
+      <c r="X12" s="668" t="n"/>
+      <c r="Y12" s="668" t="n"/>
+      <c r="Z12" s="668" t="n"/>
+      <c r="AA12" s="668" t="n"/>
+      <c r="AB12" s="668" t="n"/>
+      <c r="AC12" s="668" t="n"/>
+      <c r="AD12" s="668" t="n"/>
+      <c r="AE12" s="668" t="n"/>
+      <c r="AF12" s="668" t="n"/>
+      <c r="AG12" s="668" t="n"/>
+      <c r="AH12" s="668" t="n"/>
+      <c r="AI12" s="668" t="n"/>
+      <c r="AJ12" s="668" t="n"/>
+      <c r="AK12" s="668" t="n"/>
+      <c r="AL12" s="668" t="n"/>
+      <c r="AM12" s="668" t="n"/>
+      <c r="AN12" s="668" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="732" t="inlineStr">
+        <is>
+          <t>Open When</t>
+        </is>
+      </c>
+      <c r="B13" s="749" t="inlineStr">
+        <is>
+          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
+        </is>
+      </c>
+      <c r="C13" s="750" t="inlineStr">
+        <is>
+          <t>Operational trigger</t>
+        </is>
+      </c>
+      <c r="D13" s="668" t="n"/>
+      <c r="E13" s="668" t="n"/>
+      <c r="F13" s="668" t="n"/>
+      <c r="G13" s="668" t="n"/>
+      <c r="H13" s="668" t="n"/>
+      <c r="I13" s="668" t="n"/>
+      <c r="J13" s="668" t="n"/>
+      <c r="K13" s="668" t="n"/>
+      <c r="L13" s="668" t="n"/>
+      <c r="M13" s="668" t="n"/>
+      <c r="N13" s="668" t="n"/>
+      <c r="O13" s="668" t="n"/>
+      <c r="P13" s="668" t="n"/>
+      <c r="Q13" s="668" t="n"/>
+      <c r="R13" s="668" t="n"/>
+      <c r="S13" s="668" t="n"/>
+      <c r="T13" s="668" t="n"/>
+      <c r="U13" s="668" t="n"/>
+      <c r="V13" s="668" t="n"/>
+      <c r="W13" s="668" t="n"/>
+      <c r="X13" s="668" t="n"/>
+      <c r="Y13" s="668" t="n"/>
+      <c r="Z13" s="668" t="n"/>
+      <c r="AA13" s="668" t="n"/>
+      <c r="AB13" s="668" t="n"/>
+      <c r="AC13" s="668" t="n"/>
+      <c r="AD13" s="668" t="n"/>
+      <c r="AE13" s="668" t="n"/>
+      <c r="AF13" s="668" t="n"/>
+      <c r="AG13" s="668" t="n"/>
+      <c r="AH13" s="668" t="n"/>
+      <c r="AI13" s="668" t="n"/>
+      <c r="AJ13" s="668" t="n"/>
+      <c r="AK13" s="668" t="n"/>
+      <c r="AL13" s="668" t="n"/>
+      <c r="AM13" s="668" t="n"/>
+      <c r="AN13" s="668" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="734" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="536" t="inlineStr">
+      <c r="B14" s="744" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="537" t="inlineStr">
+      <c r="C14" s="745" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D8" s="538" t="n"/>
-      <c r="E8" s="538" t="n"/>
-      <c r="F8" s="538" t="n"/>
-      <c r="G8" s="538" t="n"/>
-      <c r="H8" s="538" t="n"/>
-      <c r="I8" s="538" t="n"/>
-      <c r="J8" s="538" t="n"/>
-      <c r="K8" s="538" t="n"/>
-      <c r="L8" s="538" t="n"/>
-      <c r="M8" s="538" t="n"/>
-      <c r="N8" s="538" t="n"/>
-      <c r="O8" s="538" t="n"/>
-      <c r="P8" s="538" t="n"/>
-      <c r="Q8" s="538" t="n"/>
-      <c r="R8" s="538" t="n"/>
-      <c r="S8" s="538" t="n"/>
-      <c r="T8" s="538" t="n"/>
-      <c r="U8" s="538" t="n"/>
-      <c r="V8" s="538" t="n"/>
-      <c r="W8" s="538" t="n"/>
-      <c r="X8" s="538" t="n"/>
-      <c r="Y8" s="538" t="n"/>
-      <c r="Z8" s="538" t="n"/>
-      <c r="AA8" s="538" t="n"/>
-      <c r="AB8" s="538" t="n"/>
-      <c r="AC8" s="538" t="n"/>
-      <c r="AD8" s="538" t="n"/>
-      <c r="AE8" s="538" t="n"/>
-      <c r="AF8" s="538" t="n"/>
-      <c r="AG8" s="538" t="n"/>
-      <c r="AH8" s="538" t="n"/>
-      <c r="AI8" s="538" t="n"/>
-      <c r="AJ8" s="538" t="n"/>
-      <c r="AK8" s="538" t="n"/>
-      <c r="AL8" s="538" t="n"/>
-      <c r="AM8" s="538" t="n"/>
-      <c r="AN8" s="539" t="n"/>
+      <c r="D14" s="668" t="n"/>
+      <c r="E14" s="668" t="n"/>
+      <c r="F14" s="668" t="n"/>
+      <c r="G14" s="668" t="n"/>
+      <c r="H14" s="668" t="n"/>
+      <c r="I14" s="668" t="n"/>
+      <c r="J14" s="668" t="n"/>
+      <c r="K14" s="668" t="n"/>
+      <c r="L14" s="668" t="n"/>
+      <c r="M14" s="668" t="n"/>
+      <c r="N14" s="668" t="n"/>
+      <c r="O14" s="668" t="n"/>
+      <c r="P14" s="668" t="n"/>
+      <c r="Q14" s="668" t="n"/>
+      <c r="R14" s="668" t="n"/>
+      <c r="S14" s="668" t="n"/>
+      <c r="T14" s="668" t="n"/>
+      <c r="U14" s="668" t="n"/>
+      <c r="V14" s="668" t="n"/>
+      <c r="W14" s="668" t="n"/>
+      <c r="X14" s="668" t="n"/>
+      <c r="Y14" s="668" t="n"/>
+      <c r="Z14" s="668" t="n"/>
+      <c r="AA14" s="668" t="n"/>
+      <c r="AB14" s="668" t="n"/>
+      <c r="AC14" s="668" t="n"/>
+      <c r="AD14" s="668" t="n"/>
+      <c r="AE14" s="668" t="n"/>
+      <c r="AF14" s="668" t="n"/>
+      <c r="AG14" s="668" t="n"/>
+      <c r="AH14" s="668" t="n"/>
+      <c r="AI14" s="668" t="n"/>
+      <c r="AJ14" s="668" t="n"/>
+      <c r="AK14" s="668" t="n"/>
+      <c r="AL14" s="668" t="n"/>
+      <c r="AM14" s="668" t="n"/>
+      <c r="AN14" s="668" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="668" t="n"/>
+      <c r="B15" s="668" t="n"/>
+      <c r="C15" s="668" t="n"/>
+      <c r="D15" s="668" t="n"/>
+      <c r="E15" s="668" t="n"/>
+      <c r="F15" s="668" t="n"/>
+      <c r="G15" s="668" t="n"/>
+      <c r="H15" s="668" t="n"/>
+      <c r="I15" s="668" t="n"/>
+      <c r="J15" s="668" t="n"/>
+      <c r="K15" s="668" t="n"/>
+      <c r="L15" s="668" t="n"/>
+      <c r="M15" s="668" t="n"/>
+      <c r="N15" s="668" t="n"/>
+      <c r="O15" s="668" t="n"/>
+      <c r="P15" s="668" t="n"/>
+      <c r="Q15" s="668" t="n"/>
+      <c r="R15" s="668" t="n"/>
+      <c r="S15" s="668" t="n"/>
+      <c r="T15" s="668" t="n"/>
+      <c r="U15" s="668" t="n"/>
+      <c r="V15" s="668" t="n"/>
+      <c r="W15" s="668" t="n"/>
+      <c r="X15" s="668" t="n"/>
+      <c r="Y15" s="668" t="n"/>
+      <c r="Z15" s="668" t="n"/>
+      <c r="AA15" s="668" t="n"/>
+      <c r="AB15" s="668" t="n"/>
+      <c r="AC15" s="668" t="n"/>
+      <c r="AD15" s="668" t="n"/>
+      <c r="AE15" s="668" t="n"/>
+      <c r="AF15" s="668" t="n"/>
+      <c r="AG15" s="668" t="n"/>
+      <c r="AH15" s="668" t="n"/>
+      <c r="AI15" s="668" t="n"/>
+      <c r="AJ15" s="668" t="n"/>
+      <c r="AK15" s="668" t="n"/>
+      <c r="AL15" s="668" t="n"/>
+      <c r="AM15" s="668" t="n"/>
+      <c r="AN15" s="668" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="668" t="n"/>
+      <c r="B16" s="668" t="n"/>
+      <c r="C16" s="668" t="n"/>
+      <c r="D16" s="668" t="n"/>
+      <c r="E16" s="668" t="n"/>
+      <c r="F16" s="668" t="n"/>
+      <c r="G16" s="668" t="n"/>
+      <c r="H16" s="668" t="n"/>
+      <c r="I16" s="668" t="n"/>
+      <c r="J16" s="668" t="n"/>
+      <c r="K16" s="668" t="n"/>
+      <c r="L16" s="668" t="n"/>
+      <c r="M16" s="668" t="n"/>
+      <c r="N16" s="668" t="n"/>
+      <c r="O16" s="668" t="n"/>
+      <c r="P16" s="668" t="n"/>
+      <c r="Q16" s="668" t="n"/>
+      <c r="R16" s="668" t="n"/>
+      <c r="S16" s="668" t="n"/>
+      <c r="T16" s="668" t="n"/>
+      <c r="U16" s="668" t="n"/>
+      <c r="V16" s="668" t="n"/>
+      <c r="W16" s="668" t="n"/>
+      <c r="X16" s="668" t="n"/>
+      <c r="Y16" s="668" t="n"/>
+      <c r="Z16" s="668" t="n"/>
+      <c r="AA16" s="668" t="n"/>
+      <c r="AB16" s="668" t="n"/>
+      <c r="AC16" s="668" t="n"/>
+      <c r="AD16" s="668" t="n"/>
+      <c r="AE16" s="668" t="n"/>
+      <c r="AF16" s="668" t="n"/>
+      <c r="AG16" s="668" t="n"/>
+      <c r="AH16" s="668" t="n"/>
+      <c r="AI16" s="668" t="n"/>
+      <c r="AJ16" s="668" t="n"/>
+      <c r="AK16" s="668" t="n"/>
+      <c r="AL16" s="668" t="n"/>
+      <c r="AM16" s="668" t="n"/>
+      <c r="AN16" s="668" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="668" t="n"/>
+      <c r="B17" s="668" t="n"/>
+      <c r="C17" s="668" t="n"/>
+      <c r="D17" s="668" t="n"/>
+      <c r="E17" s="668" t="n"/>
+      <c r="F17" s="668" t="n"/>
+      <c r="G17" s="668" t="n"/>
+      <c r="H17" s="668" t="n"/>
+      <c r="I17" s="668" t="n"/>
+      <c r="J17" s="668" t="n"/>
+      <c r="K17" s="668" t="n"/>
+      <c r="L17" s="668" t="n"/>
+      <c r="M17" s="668" t="n"/>
+      <c r="N17" s="668" t="n"/>
+      <c r="O17" s="668" t="n"/>
+      <c r="P17" s="668" t="n"/>
+      <c r="Q17" s="668" t="n"/>
+      <c r="R17" s="668" t="n"/>
+      <c r="S17" s="668" t="n"/>
+      <c r="T17" s="668" t="n"/>
+      <c r="U17" s="668" t="n"/>
+      <c r="V17" s="668" t="n"/>
+      <c r="W17" s="668" t="n"/>
+      <c r="X17" s="668" t="n"/>
+      <c r="Y17" s="668" t="n"/>
+      <c r="Z17" s="668" t="n"/>
+      <c r="AA17" s="668" t="n"/>
+      <c r="AB17" s="668" t="n"/>
+      <c r="AC17" s="668" t="n"/>
+      <c r="AD17" s="668" t="n"/>
+      <c r="AE17" s="668" t="n"/>
+      <c r="AF17" s="668" t="n"/>
+      <c r="AG17" s="668" t="n"/>
+      <c r="AH17" s="668" t="n"/>
+      <c r="AI17" s="668" t="n"/>
+      <c r="AJ17" s="668" t="n"/>
+      <c r="AK17" s="668" t="n"/>
+      <c r="AL17" s="668" t="n"/>
+      <c r="AM17" s="668" t="n"/>
+      <c r="AN17" s="668" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -4509,6 +4509,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4539,6 +4542,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4569,6 +4575,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7010,7 +7019,6 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="119">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AK32:BD32"/>
@@ -7536,6 +7544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>
@@ -7774,7 +7783,6 @@
       <c r="H19" s="324" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7830,6 +7838,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>
@@ -8038,7 +8047,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -8087,6 +8095,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>
@@ -8173,7 +8182,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AQL_RECORD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AQL_RECORD'!$A$1:$BD$37</definedName>
@@ -7544,7 +7544,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>
@@ -7838,7 +7837,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>
@@ -8095,7 +8093,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="322" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -15,8 +15,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AQL_RECORD'!$A$1:$BD$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8045,7 +8043,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -8179,7 +8176,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AQL_RECORD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AQL_RECORD'!$A$1:$BD$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4484,105 +4487,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FRM_621_DETAIL" displayName="FRM_621_DETAIL" ref="A4:H19" headerRowCount="1">
   <autoFilter ref="A4:H19"/>
@@ -5035,7 +4939,7 @@
       <c r="AV2" s="272" t="n"/>
       <c r="AW2" s="273" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="271" t="n"/>
@@ -5091,7 +4995,7 @@
       <c r="AV3" s="272" t="n"/>
       <c r="AW3" s="273" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="271" t="n"/>
@@ -5732,7 +5636,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="287" t="inlineStr">
         <is>
-          <t>Evidence Package Ref</t>
+          <t>Linked FRM-641</t>
         </is>
       </c>
       <c r="B15" s="271" t="n"/>
@@ -5764,7 +5668,7 @@
       <c r="AB15" s="326" t="n"/>
       <c r="AC15" s="289" t="inlineStr">
         <is>
-          <t>Disposition Status</t>
+          <t>Ref: SOP-605</t>
         </is>
       </c>
       <c r="AD15" s="271" t="n"/>
@@ -5776,7 +5680,11 @@
       <c r="AJ15" s="271" t="n"/>
       <c r="AK15" s="271" t="n"/>
       <c r="AL15" s="272" t="n"/>
-      <c r="AM15" s="290" t="n"/>
+      <c r="AM15" s="290" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN15" s="325" t="n"/>
       <c r="AO15" s="325" t="n"/>
       <c r="AP15" s="325" t="n"/>
@@ -7017,6 +6925,7 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="119">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AK32:BD32"/>
@@ -7780,6 +7689,7 @@
       <c r="H19" s="324" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7790,9 +7700,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8043,12 +7952,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8176,11 +8086,92 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-641; Parent ref: SOP-605</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-621_AQL_Inspection_Record.xlsx
@@ -5006,6 +5006,95 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số công việc
+Job hoặc Work Order.</t>
+      </text>
+    </comment>
+    <comment ref="AC9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part number và revision.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Cỡ lô / Cỡ mẫu
+Tra bảng ISO 2859-1 theo AQL Level.
+Ví dụ: Lot=100, Sample=13 (Level II, AQL 1.0).</t>
+      </text>
+    </comment>
+    <comment ref="AC10" authorId="0" shapeId="0">
+      <text>
+        <t>Mức AQL / Mức kiểm tra
+AQL = Acceptable Quality Level.
+Inspection Level thường dùng Level II.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả kiểm tra
+Mỗi dòng = 1 đặc tính từ bản vẽ.
+Ghi giá trị đo thực tế và kết quả PASS/FAIL.</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Đặc tính kiểm tra
+Ghi kích thước hoặc yêu cầu từ bản vẽ.
+Ví dụ: OD 25.00 ±0.02, Ra 0.8, Visual.</t>
+      </text>
+    </comment>
+    <comment ref="AD13" authorId="0" shapeId="0">
+      <text>
+        <t>Phương pháp / Dụng cụ
+Ghi cách đo và ID dụng cụ.
+Dụng cụ phải còn hiệu chuẩn.</t>
+      </text>
+    </comment>
+    <comment ref="AR13" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS / FAIL / HOLD / NA.</t>
+      </text>
+    </comment>
+    <comment ref="AX13" authorId="0" shapeId="0">
+      <text>
+        <t>Người kiểm tra
+Ký tắt. Phải có năng lực.</t>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định lô hàng
+Sau khi kiểm tra → quyết định cho toàn lô.</t>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0">
+      <text>
+        <t>Số đạt / Số lỗi
+Ghi số lượng.</t>
+      </text>
+    </comment>
+    <comment ref="AC31" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định
+ACCEPT = chấp nhận lô.
+REJECT = từ chối → NCR (FRM-651).
+SORT = kiểm 100% phân loại.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6031,7 +6120,7 @@
       <c r="G13" s="475" t="n"/>
       <c r="H13" s="488" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Check Item</t>
         </is>
       </c>
       <c r="I13" s="474" t="n"/>
@@ -6057,7 +6146,7 @@
       <c r="AC13" s="475" t="n"/>
       <c r="AD13" s="488" t="inlineStr">
         <is>
-          <t>Method / Instrument</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="AE13" s="474" t="n"/>
@@ -6085,7 +6174,7 @@
       <c r="AW13" s="475" t="n"/>
       <c r="AX13" s="489" t="inlineStr">
         <is>
-          <t>Inspector</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="AY13" s="474" t="n"/>
@@ -6096,8 +6185,9 @@
       <c r="BD13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="n"/>
@@ -6168,8 +6258,9 @@
       <c r="BD14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="n"/>
@@ -6240,8 +6331,9 @@
       <c r="BD15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="n"/>
@@ -6312,8 +6404,9 @@
       <c r="BD16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="n"/>
@@ -6384,8 +6477,9 @@
       <c r="BD17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="n"/>
@@ -6456,8 +6550,9 @@
       <c r="BD18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="n"/>
@@ -6516,8 +6611,9 @@
       <c r="BD19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="492" t="n"/>
@@ -6576,8 +6672,9 @@
       <c r="BD20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="492" t="n"/>
@@ -6636,8 +6733,9 @@
       <c r="BD21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="492" t="n"/>
@@ -6696,8 +6794,9 @@
       <c r="BD22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="490" t="n">
-        <v>10</v>
+      <c r="A23" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="491" t="n"/>
       <c r="C23" s="492" t="n"/>
@@ -6756,8 +6855,9 @@
       <c r="BD23" s="498" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
-      <c r="A24" s="490" t="n">
-        <v>11</v>
+      <c r="A24" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B24" s="491" t="n"/>
       <c r="C24" s="492" t="n"/>
@@ -6816,8 +6916,9 @@
       <c r="BD24" s="498" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
-      <c r="A25" s="490" t="n">
-        <v>12</v>
+      <c r="A25" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B25" s="491" t="n"/>
       <c r="C25" s="492" t="n"/>
@@ -6876,8 +6977,9 @@
       <c r="BD25" s="498" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
-      <c r="A26" s="490" t="n">
-        <v>13</v>
+      <c r="A26" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B26" s="491" t="n"/>
       <c r="C26" s="492" t="n"/>
@@ -6936,8 +7038,9 @@
       <c r="BD26" s="498" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
-      <c r="A27" s="490" t="n">
-        <v>14</v>
+      <c r="A27" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B27" s="491" t="n"/>
       <c r="C27" s="492" t="n"/>
@@ -6996,8 +7099,9 @@
       <c r="BD27" s="498" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
-      <c r="A28" s="503" t="n">
-        <v>15</v>
+      <c r="A28" s="503">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B28" s="481" t="n"/>
       <c r="C28" s="482" t="n"/>
@@ -7618,7 +7722,7 @@
     <row r="39" ht="24" customHeight="1" s="264">
       <c r="A39" s="520" t="inlineStr">
         <is>
-          <t>NOTICE — Per lot inspection. Ref: SOP-605. Retain: 10 years.</t>
+          <t>NOTICE — Per lot. If REJECT/SORT → raise NCR (FRM-651). Ref: SOP-605. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B39" s="471" t="n"/>
@@ -7835,6 +7939,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
